--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:H62"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,19 +421,19 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אוליביה דין The Art of Loving</v>
+        <v>אשכול נוכחות למשתמשים פעילים</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-01-04</v>
+        <v>2025  16:32 מאת freund-10-16</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=23455&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E2" t="str">
-        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
+        <v/>
       </c>
       <c r="F2" t="str">
         <v>אלבומים חדשים</v>
@@ -441,19 +441,19 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Geese Getting Killed</v>
+        <v>כיצד להוריד מהאתרים המפורסמים</v>
       </c>
       <c r="B3" t="str">
-        <v>2025-12-29</v>
+        <v>2023  16:23 מאת petel1-08-08</v>
       </c>
       <c r="C3" t="str">
-        <v>https://yosmusic.com/geese-getting-killed/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=22411&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E3" t="str">
-        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
+        <v/>
       </c>
       <c r="F3" t="str">
         <v>אלבומים חדשים</v>
@@ -461,19 +461,19 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>רוסליה Lux</v>
+        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
       </c>
       <c r="B4" t="str">
-        <v>2025-12-25</v>
+        <v>2026  22:40 מאת מוטי_ד-01-01</v>
       </c>
       <c r="C4" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24435&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E4" t="str">
-        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
+        <v/>
       </c>
       <c r="F4" t="str">
         <v>אלבומים חדשים</v>
@@ -481,19 +481,19 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>יאנגבלאד אירוסמית' one more time</v>
+        <v>|אלבום חדש| אייל גולן - בית מפואר (2025)</v>
       </c>
       <c r="B5" t="str">
-        <v>2025-12-17</v>
+        <v>2025  02:18 מאת DiSHi-12-31</v>
       </c>
       <c r="C5" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E5" t="str">
-        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
+        <v/>
       </c>
       <c r="F5" t="str">
         <v>אלבומים חדשים</v>
@@ -501,19 +501,19 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>פינק פלויד Wish You Were Here 50</v>
+        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע (2025)</v>
       </c>
       <c r="B6" t="str">
-        <v>2025-12-14</v>
+        <v>2025  02:17 מאת DiSHi-12-31</v>
       </c>
       <c r="C6" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E6" t="str">
-        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
+        <v/>
       </c>
       <c r="F6" t="str">
         <v>אלבומים חדשים</v>
@@ -521,19 +521,19 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+        <v>|אלבום חדש| הפרויקט של דודי לוי ואבטיפוס - הפטריקים (2025)</v>
       </c>
       <c r="B7" t="str">
-        <v>2025-12-08</v>
+        <v>2025  02:16 מאת DiSHi-12-31</v>
       </c>
       <c r="C7" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E7" t="str">
-        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
+        <v/>
       </c>
       <c r="F7" t="str">
         <v>אלבומים חדשים</v>
@@ -541,19 +541,19 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>סטריי קידס DO IT (EP)</v>
+        <v>|אלבום חדש| אברהם טל - חי (2025)</v>
       </c>
       <c r="B8" t="str">
-        <v>2025-12-04</v>
+        <v>2025  02:16 מאת DiSHi-12-31</v>
       </c>
       <c r="C8" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E8" t="str">
-        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
+        <v/>
       </c>
       <c r="F8" t="str">
         <v>אלבומים חדשים</v>
@@ -561,19 +561,19 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>דויד ברוזה BROZAJAZZ</v>
+        <v>|אלבום חדש| שיר לוי - ילד מוזר (2025)</v>
       </c>
       <c r="B9" t="str">
-        <v>2025-11-30</v>
+        <v>2025  02:14 מאת DiSHi-12-31</v>
       </c>
       <c r="C9" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E9" t="str">
-        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
+        <v/>
       </c>
       <c r="F9" t="str">
         <v>אלבומים חדשים</v>
@@ -581,19 +581,19 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Five Seconds of Summer – Everyone's A Star</v>
+        <v>|אלבום חדש| מיקי גבריאלוב - שלום (2025)</v>
       </c>
       <c r="B10" t="str">
-        <v>2025-11-24</v>
+        <v>2025  02:13 מאת DiSHi-12-31</v>
       </c>
       <c r="C10" t="str">
-        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E10" t="str">
-        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
+        <v/>
       </c>
       <c r="F10" t="str">
         <v>אלבומים חדשים</v>
@@ -601,19 +601,19 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>התקווה 6 – ויהי אור</v>
+        <v>|אלבום חדש| פיטר רוט - 50 (2025)</v>
       </c>
       <c r="B11" t="str">
-        <v>2025-11-20</v>
+        <v>2025  02:13 מאת DiSHi-12-31</v>
       </c>
       <c r="C11" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E11" t="str">
-        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
+        <v/>
       </c>
       <c r="F11" t="str">
         <v>אלבומים חדשים</v>
@@ -621,19 +621,19 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>פלורנס אנד דה משין Everybody Scream</v>
+        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם (2025)</v>
       </c>
       <c r="B12" t="str">
-        <v>2025-11-13</v>
+        <v>2025  02:12 מאת DiSHi-12-31</v>
       </c>
       <c r="C12" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E12" t="str">
-        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
+        <v/>
       </c>
       <c r="F12" t="str">
         <v>אלבומים חדשים</v>
@@ -641,19 +641,19 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>טיים אימפלה Deadbeat</v>
+        <v>|אלבום חדש| אגם בוחבוט - עשרים ואחת (2025)</v>
       </c>
       <c r="B13" t="str">
-        <v>2025-11-03</v>
+        <v>2025  02:11 מאת DiSHi-12-31</v>
       </c>
       <c r="C13" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E13" t="str">
-        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
+        <v/>
       </c>
       <c r="F13" t="str">
         <v>אלבומים חדשים</v>
@@ -661,19 +661,19 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון (2025)</v>
       </c>
       <c r="B14" t="str">
-        <v>2025-10-20</v>
+        <v>2025  02:10 מאת DiSHi-12-31</v>
       </c>
       <c r="C14" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E14" t="str">
-        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
+        <v/>
       </c>
       <c r="F14" t="str">
         <v>אלבומים חדשים</v>
@@ -681,19 +681,19 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>שלמה גרוניך – תודה אהבה</v>
+        <v>|אלבום חדש| רבקה זוהר - רסיסים של אור (2025)</v>
       </c>
       <c r="B15" t="str">
-        <v>2025-10-18</v>
+        <v>2025  02:09 מאת DiSHi-12-31</v>
       </c>
       <c r="C15" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E15" t="str">
-        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
+        <v/>
       </c>
       <c r="F15" t="str">
         <v>אלבומים חדשים</v>
@@ -701,19 +701,19 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>טיילור סוויפט The Life Of A Showgirl</v>
+        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה (2025)</v>
       </c>
       <c r="B16" t="str">
-        <v>2025-10-11</v>
+        <v>2025  02:09 מאת DiSHi-12-31</v>
       </c>
       <c r="C16" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E16" t="str">
-        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
+        <v/>
       </c>
       <c r="F16" t="str">
         <v>אלבומים חדשים</v>
@@ -721,19 +721,19 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>דוג'ה קאט Vie</v>
+        <v>|אלבום חדש| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות (2025)</v>
       </c>
       <c r="B17" t="str">
-        <v>2025-10-04</v>
+        <v>2025  02:08 מאת DiSHi-12-31</v>
       </c>
       <c r="C17" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E17" t="str">
-        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
+        <v/>
       </c>
       <c r="F17" t="str">
         <v>אלבומים חדשים</v>
@@ -741,19 +741,19 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ג'וי קרוקס Juniper</v>
+        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים (2025)</v>
       </c>
       <c r="B18" t="str">
-        <v>2025-10-03</v>
+        <v>2025  02:06 מאת DiSHi-12-31</v>
       </c>
       <c r="C18" t="str">
-        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E18" t="str">
-        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
+        <v/>
       </c>
       <c r="F18" t="str">
         <v>אלבומים חדשים</v>
@@ -761,19 +761,19 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ביפי קליירו Futique</v>
+        <v>|אלבום חדש| אהוד בנאי ובנו הנדלר - פליטי הדאב (2025)</v>
       </c>
       <c r="B19" t="str">
-        <v>2025-09-30</v>
+        <v>2025  02:05 מאת DiSHi-12-31</v>
       </c>
       <c r="C19" t="str">
-        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E19" t="str">
-        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
+        <v/>
       </c>
       <c r="F19" t="str">
         <v>אלבומים חדשים</v>
@@ -781,19 +781,19 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>אד שירן Play</v>
+        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם (2025)</v>
       </c>
       <c r="B20" t="str">
-        <v>2025-09-24</v>
+        <v>2025  02:05 מאת DiSHi-12-31</v>
       </c>
       <c r="C20" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E20" t="str">
-        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
+        <v/>
       </c>
       <c r="F20" t="str">
         <v>אלבומים חדשים</v>
@@ -801,19 +801,19 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+        <v>|אלבום חדש| Imagine פסטיגל - שירי התחרות (2025)</v>
       </c>
       <c r="B21" t="str">
-        <v>2025-09-21</v>
+        <v>2025  02:04 מאת DiSHi-12-31</v>
       </c>
       <c r="C21" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E21" t="str">
-        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
+        <v/>
       </c>
       <c r="F21" t="str">
         <v>אלבומים חדשים</v>
@@ -821,19 +821,19 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>סוויד Antidepressants</v>
+        <v>|אלבום חדש| סטטיק - קעקועים (2025)</v>
       </c>
       <c r="B22" t="str">
-        <v>2025-09-12</v>
+        <v>2025  02:03 מאת DiSHi-12-31</v>
       </c>
       <c r="C22" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E22" t="str">
-        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
+        <v/>
       </c>
       <c r="F22" t="str">
         <v>אלבומים חדשים</v>
@@ -841,19 +841,19 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>וולף אליס The Clearing</v>
+        <v>|אלבום חדש| השמחות - חובות אבודים (2025)</v>
       </c>
       <c r="B23" t="str">
-        <v>2025-09-01</v>
+        <v>2025  02:02 מאת DiSHi-12-31</v>
       </c>
       <c r="C23" t="str">
-        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E23" t="str">
-        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
+        <v/>
       </c>
       <c r="F23" t="str">
         <v>אלבומים חדשים</v>
@@ -861,19 +861,19 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+        <v>|אלבום חדש| ליאור נרקיס - דיסוננס (2025)</v>
       </c>
       <c r="B24" t="str">
-        <v>2025-08-29</v>
+        <v>2025  02:01 מאת DiSHi-12-31</v>
       </c>
       <c r="C24" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E24" t="str">
-        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
+        <v/>
       </c>
       <c r="F24" t="str">
         <v>אלבומים חדשים</v>
@@ -881,19 +881,19 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+        <v>|אלבום חדש| שלמה גרוניך - כמו כוכבים (2025)</v>
       </c>
       <c r="B25" t="str">
-        <v>2025-08-24</v>
+        <v>2025  02:00 מאת DiSHi-12-31</v>
       </c>
       <c r="C25" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E25" t="str">
-        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
+        <v/>
       </c>
       <c r="F25" t="str">
         <v>אלבומים חדשים</v>
@@ -901,19 +901,19 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) (2025)</v>
       </c>
       <c r="B26" t="str">
-        <v>2025-08-21</v>
+        <v>2025  01:57 מאת DiSHi-12-31</v>
       </c>
       <c r="C26" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E26" t="str">
-        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
+        <v/>
       </c>
       <c r="F26" t="str">
         <v>אלבומים חדשים</v>
@@ -921,19 +921,19 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>אברהם טל – חי</v>
+        <v>|אלבום חדש| יוני רועה - מפוזרים (2025)</v>
       </c>
       <c r="B27" t="str">
-        <v>2025-08-17</v>
+        <v>2025  01:56 מאת DiSHi-12-31</v>
       </c>
       <c r="C27" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E27" t="str">
-        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
+        <v/>
       </c>
       <c r="F27" t="str">
         <v>אלבומים חדשים</v>
@@ -941,19 +941,19 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>רנה ראפ Bite Me</v>
+        <v>|אלבום חדש| אתניקס - איטליה (2025)</v>
       </c>
       <c r="B28" t="str">
-        <v>2025-08-12</v>
+        <v>2025  01:55 מאת DiSHi-12-31</v>
       </c>
       <c r="C28" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E28" t="str">
-        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
+        <v/>
       </c>
       <c r="F28" t="str">
         <v>אלבומים חדשים</v>
@@ -961,19 +961,19 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>The K's – Pretty On The Internet</v>
+        <v>|אלבום חדש| התקווה 6 - ויהי אור (2025)</v>
       </c>
       <c r="B29" t="str">
-        <v>2025-08-03</v>
+        <v>2025  01:54 מאת DiSHi-12-31</v>
       </c>
       <c r="C29" t="str">
-        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E29" t="str">
-        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
+        <v/>
       </c>
       <c r="F29" t="str">
         <v>אלבומים חדשים</v>
@@ -981,19 +981,19 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>פליטווד מק Fifty Years – Don’t Stop</v>
+        <v>|אלבום חדש| שלומי סרנגה - איפרכו (2025)</v>
       </c>
       <c r="B30" t="str">
-        <v>2025-07-30</v>
+        <v>2025  01:53 מאת DiSHi-12-31</v>
       </c>
       <c r="C30" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%99%d7%98%d7%95%d7%95%d7%93-%d7%9e%d7%a7-fifty-years-dont-stop/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24430&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E30" t="str">
-        <v>פליטווד מק (Fleetwood Mac) חוגגים חצי מאה של מוזיקה עם אוסף חדש בן 50 שירים, שמתפרש על כל הקריירה של הלהקה, מימיה הראשונים בסגנון בלוז, ועד להצלחתה העולמית כאחת מלהקות הגדולות בהיסטוריה של הרוק. פליטווד מק הם לא רק להקה</v>
+        <v/>
       </c>
       <c r="F30" t="str">
         <v>אלבומים חדשים</v>
@@ -1001,27 +1001,827 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
+        <v>|אלבום חדש| שאנן סטריט ודי ג׳יי מש - באתי לבדר (2025)</v>
+      </c>
+      <c r="B31" t="str">
+        <v>2025  01:53 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C31" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D31" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>הרשם לחברות מלאה</v>
+      </c>
+      <c r="B32" t="str">
+        <v/>
+      </c>
+      <c r="C32" t="str">
+        <v>https://rotter.name/nor/members-new.html</v>
+      </c>
+      <c r="D32" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>אוליביה דין The Art of Loving</v>
+      </c>
+      <c r="B33" t="str">
+        <v>2026-01-04</v>
+      </c>
+      <c r="C33" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
+      </c>
+      <c r="D33" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E33" t="str">
+        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
+      </c>
+      <c r="F33" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+      <c r="H33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Geese Getting Killed</v>
+      </c>
+      <c r="B34" t="str">
+        <v>2025-12-29</v>
+      </c>
+      <c r="C34" t="str">
+        <v>https://yosmusic.com/geese-getting-killed/</v>
+      </c>
+      <c r="D34" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E34" t="str">
+        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
+      </c>
+      <c r="F34" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
+      <c r="H34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>רוסליה Lux</v>
+      </c>
+      <c r="B35" t="str">
+        <v>2025-12-25</v>
+      </c>
+      <c r="C35" t="str">
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
+      </c>
+      <c r="D35" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E35" t="str">
+        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
+      </c>
+      <c r="F35" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+      <c r="H35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>יאנגבלאד אירוסמית' one more time</v>
+      </c>
+      <c r="B36" t="str">
+        <v>2025-12-17</v>
+      </c>
+      <c r="C36" t="str">
+        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
+      </c>
+      <c r="D36" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E36" t="str">
+        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
+      </c>
+      <c r="F36" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+      <c r="H36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>פינק פלויד Wish You Were Here 50</v>
+      </c>
+      <c r="B37" t="str">
+        <v>2025-12-14</v>
+      </c>
+      <c r="C37" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
+      </c>
+      <c r="D37" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E37" t="str">
+        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
+      </c>
+      <c r="F37" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+      </c>
+      <c r="B38" t="str">
+        <v>2025-12-08</v>
+      </c>
+      <c r="C38" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
+      </c>
+      <c r="D38" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E38" t="str">
+        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
+      </c>
+      <c r="F38" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>סטריי קידס DO IT (EP)</v>
+      </c>
+      <c r="B39" t="str">
+        <v>2025-12-04</v>
+      </c>
+      <c r="C39" t="str">
+        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
+      </c>
+      <c r="D39" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E39" t="str">
+        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
+      </c>
+      <c r="F39" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+      <c r="H39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>דויד ברוזה BROZAJAZZ</v>
+      </c>
+      <c r="B40" t="str">
+        <v>2025-11-30</v>
+      </c>
+      <c r="C40" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
+      </c>
+      <c r="D40" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E40" t="str">
+        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
+      </c>
+      <c r="F40" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+      <c r="H40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Five Seconds of Summer – Everyone's A Star</v>
+      </c>
+      <c r="B41" t="str">
+        <v>2025-11-24</v>
+      </c>
+      <c r="C41" t="str">
+        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
+      </c>
+      <c r="D41" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E41" t="str">
+        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
+      </c>
+      <c r="F41" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+      <c r="H41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>התקווה 6 – ויהי אור</v>
+      </c>
+      <c r="B42" t="str">
+        <v>2025-11-20</v>
+      </c>
+      <c r="C42" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
+      </c>
+      <c r="D42" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E42" t="str">
+        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
+      </c>
+      <c r="F42" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>פלורנס אנד דה משין Everybody Scream</v>
+      </c>
+      <c r="B43" t="str">
+        <v>2025-11-13</v>
+      </c>
+      <c r="C43" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
+      </c>
+      <c r="D43" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E43" t="str">
+        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
+      </c>
+      <c r="F43" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>טיים אימפלה Deadbeat</v>
+      </c>
+      <c r="B44" t="str">
+        <v>2025-11-03</v>
+      </c>
+      <c r="C44" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
+      </c>
+      <c r="D44" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E44" t="str">
+        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
+      </c>
+      <c r="F44" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+      </c>
+      <c r="B45" t="str">
+        <v>2025-10-20</v>
+      </c>
+      <c r="C45" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
+      </c>
+      <c r="D45" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E45" t="str">
+        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
+      </c>
+      <c r="F45" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
+      <c r="H45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>שלמה גרוניך – תודה אהבה</v>
+      </c>
+      <c r="B46" t="str">
+        <v>2025-10-18</v>
+      </c>
+      <c r="C46" t="str">
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
+      </c>
+      <c r="D46" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E46" t="str">
+        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
+      </c>
+      <c r="F46" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
+      <c r="H46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
+      </c>
+      <c r="B47" t="str">
+        <v>2025-10-11</v>
+      </c>
+      <c r="C47" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
+      </c>
+      <c r="D47" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E47" t="str">
+        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
+      </c>
+      <c r="F47" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G47" t="str">
+        <v/>
+      </c>
+      <c r="H47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>דוג'ה קאט Vie</v>
+      </c>
+      <c r="B48" t="str">
+        <v>2025-10-04</v>
+      </c>
+      <c r="C48" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
+      </c>
+      <c r="D48" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E48" t="str">
+        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
+      </c>
+      <c r="F48" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G48" t="str">
+        <v/>
+      </c>
+      <c r="H48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>ג'וי קרוקס Juniper</v>
+      </c>
+      <c r="B49" t="str">
+        <v>2025-10-03</v>
+      </c>
+      <c r="C49" t="str">
+        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
+      </c>
+      <c r="D49" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E49" t="str">
+        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
+      </c>
+      <c r="F49" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G49" t="str">
+        <v/>
+      </c>
+      <c r="H49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>ביפי קליירו Futique</v>
+      </c>
+      <c r="B50" t="str">
+        <v>2025-09-30</v>
+      </c>
+      <c r="C50" t="str">
+        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
+      </c>
+      <c r="D50" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E50" t="str">
+        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
+      </c>
+      <c r="F50" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G50" t="str">
+        <v/>
+      </c>
+      <c r="H50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>אד שירן Play</v>
+      </c>
+      <c r="B51" t="str">
+        <v>2025-09-24</v>
+      </c>
+      <c r="C51" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
+      </c>
+      <c r="D51" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E51" t="str">
+        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
+      </c>
+      <c r="F51" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G51" t="str">
+        <v/>
+      </c>
+      <c r="H51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+      </c>
+      <c r="B52" t="str">
+        <v>2025-09-21</v>
+      </c>
+      <c r="C52" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
+      </c>
+      <c r="D52" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E52" t="str">
+        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
+      </c>
+      <c r="F52" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G52" t="str">
+        <v/>
+      </c>
+      <c r="H52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>סוויד Antidepressants</v>
+      </c>
+      <c r="B53" t="str">
+        <v>2025-09-12</v>
+      </c>
+      <c r="C53" t="str">
+        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
+      </c>
+      <c r="D53" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E53" t="str">
+        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
+      </c>
+      <c r="F53" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G53" t="str">
+        <v/>
+      </c>
+      <c r="H53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>וולף אליס The Clearing</v>
+      </c>
+      <c r="B54" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="C54" t="str">
+        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
+      </c>
+      <c r="D54" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E54" t="str">
+        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
+      </c>
+      <c r="F54" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G54" t="str">
+        <v/>
+      </c>
+      <c r="H54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+      </c>
+      <c r="B55" t="str">
+        <v>2025-08-29</v>
+      </c>
+      <c r="C55" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
+      </c>
+      <c r="D55" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E55" t="str">
+        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
+      </c>
+      <c r="F55" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G55" t="str">
+        <v/>
+      </c>
+      <c r="H55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+      </c>
+      <c r="B56" t="str">
+        <v>2025-08-24</v>
+      </c>
+      <c r="C56" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
+      </c>
+      <c r="D56" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E56" t="str">
+        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
+      </c>
+      <c r="F56" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G56" t="str">
+        <v/>
+      </c>
+      <c r="H56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+      </c>
+      <c r="B57" t="str">
+        <v>2025-08-21</v>
+      </c>
+      <c r="C57" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
+      </c>
+      <c r="D57" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E57" t="str">
+        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
+      </c>
+      <c r="F57" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G57" t="str">
+        <v/>
+      </c>
+      <c r="H57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>אברהם טל – חי</v>
+      </c>
+      <c r="B58" t="str">
+        <v>2025-08-17</v>
+      </c>
+      <c r="C58" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
+      </c>
+      <c r="D58" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E58" t="str">
+        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
+      </c>
+      <c r="F58" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G58" t="str">
+        <v/>
+      </c>
+      <c r="H58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>רנה ראפ Bite Me</v>
+      </c>
+      <c r="B59" t="str">
+        <v>2025-08-12</v>
+      </c>
+      <c r="C59" t="str">
+        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
+      </c>
+      <c r="D59" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E59" t="str">
+        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
+      </c>
+      <c r="F59" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G59" t="str">
+        <v/>
+      </c>
+      <c r="H59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>The K's – Pretty On The Internet</v>
+      </c>
+      <c r="B60" t="str">
+        <v>2025-08-03</v>
+      </c>
+      <c r="C60" t="str">
+        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
+      </c>
+      <c r="D60" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E60" t="str">
+        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
+      </c>
+      <c r="F60" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G60" t="str">
+        <v/>
+      </c>
+      <c r="H60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>פליטווד מק Fifty Years – Don’t Stop</v>
+      </c>
+      <c r="B61" t="str">
+        <v>2025-07-30</v>
+      </c>
+      <c r="C61" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%99%d7%98%d7%95%d7%95%d7%93-%d7%9e%d7%a7-fifty-years-dont-stop/</v>
+      </c>
+      <c r="D61" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E61" t="str">
+        <v>פליטווד מק (Fleetwood Mac) חוגגים חצי מאה של מוזיקה עם אוסף חדש בן 50 שירים, שמתפרש על כל הקריירה של הלהקה, מימיה הראשונים בסגנון בלוז, ועד להצלחתה העולמית כאחת מלהקות הגדולות בהיסטוריה של הרוק. פליטווד מק הם לא רק להקה</v>
+      </c>
+      <c r="F61" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G61" t="str">
+        <v/>
+      </c>
+      <c r="H61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
         <v>Wet Leg Moisturizer</v>
       </c>
-      <c r="B31" t="str">
+      <c r="B62" t="str">
         <v>2025-07-25</v>
       </c>
-      <c r="C31" t="str">
+      <c r="C62" t="str">
         <v>https://yosmusic.com/wet-leg-moisturizer/</v>
       </c>
-      <c r="D31" t="str">
-        <v>2026-01-08</v>
-      </c>
-      <c r="E31" t="str">
+      <c r="D62" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E62" t="str">
         <v>להקת Wet Leg לא הוציאה קרם לחות (Moisturizer) כמוצר טיפוח. במקום זאת, "Moisturizer" הוא שמו של האלבום השני והחדש שלהם. במרכז –  צמד אינדי-רוק המורכב מהחברות ריין טיסדייל והסטר צ'יימברס. אלבום הבכורה הנושא את שמה, הגיע למקום הראשון במצעד האלבומים</v>
       </c>
-      <c r="F31" t="str">
-        <v>אלבומים חדשים</v>
+      <c r="F62" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G62" t="str">
+        <v/>
+      </c>
+      <c r="H62" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H62"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:J76"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,13 +421,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אשכול נוכחות למשתמשים פעילים</v>
+        <v>|| אייל גולן - בית מפואר ()</v>
       </c>
       <c r="B2" t="str">
-        <v>2025  16:32 מאת freund-10-16</v>
+        <v>2025  02:18-12-31</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=23455&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-08</v>
@@ -441,13 +441,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>כיצד להוריד מהאתרים המפורסמים</v>
+        <v>|| הפרויקט של דודי לוי ואבטיפוס - הפטריקים ()</v>
       </c>
       <c r="B3" t="str">
-        <v>2023  16:23 מאת petel1-08-08</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C3" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=22411&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-08</v>
@@ -461,13 +461,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
+        <v>|| שיר לוי - ילד מוזר ()</v>
       </c>
       <c r="B4" t="str">
-        <v>2026  22:40 מאת מוטי_ד-01-01</v>
+        <v>2025  02:14-12-31</v>
       </c>
       <c r="C4" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24435&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-08</v>
@@ -481,13 +481,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>|אלבום חדש| אייל גולן - בית מפואר (2025)</v>
+        <v>|| פיטר רוט - 50 ()</v>
       </c>
       <c r="B5" t="str">
-        <v>2025  02:18 מאת DiSHi-12-31</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C5" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-08</v>
@@ -501,13 +501,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע (2025)</v>
+        <v>|| אגם בוחבוט - עשרים ואחת ()</v>
       </c>
       <c r="B6" t="str">
-        <v>2025  02:17 מאת DiSHi-12-31</v>
+        <v>2025  02:11-12-31</v>
       </c>
       <c r="C6" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-08</v>
@@ -521,13 +521,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>|אלבום חדש| הפרויקט של דודי לוי ואבטיפוס - הפטריקים (2025)</v>
+        <v>|| רבקה זוהר - רסיסים של אור ()</v>
       </c>
       <c r="B7" t="str">
-        <v>2025  02:16 מאת DiSHi-12-31</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C7" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-08</v>
@@ -541,13 +541,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>|אלבום חדש| אברהם טל - חי (2025)</v>
+        <v>|| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות ()</v>
       </c>
       <c r="B8" t="str">
-        <v>2025  02:16 מאת DiSHi-12-31</v>
+        <v>2025  02:08-12-31</v>
       </c>
       <c r="C8" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-08</v>
@@ -561,13 +561,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>|אלבום חדש| שיר לוי - ילד מוזר (2025)</v>
+        <v>|| אהוד בנאי ובנו הנדלר - פליטי הדאב ()</v>
       </c>
       <c r="B9" t="str">
-        <v>2025  02:14 מאת DiSHi-12-31</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C9" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-08</v>
@@ -581,13 +581,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>|אלבום חדש| מיקי גבריאלוב - שלום (2025)</v>
+        <v>|| Imagine פסטיגל - שירי התחרות ()</v>
       </c>
       <c r="B10" t="str">
-        <v>2025  02:13 מאת DiSHi-12-31</v>
+        <v>2025  02:04-12-31</v>
       </c>
       <c r="C10" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-08</v>
@@ -601,13 +601,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>|אלבום חדש| פיטר רוט - 50 (2025)</v>
+        <v>|| השמחות - חובות אבודים ()</v>
       </c>
       <c r="B11" t="str">
-        <v>2025  02:13 מאת DiSHi-12-31</v>
+        <v>2025  02:02-12-31</v>
       </c>
       <c r="C11" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-08</v>
@@ -621,13 +621,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם (2025)</v>
+        <v>|| שלמה גרוניך - כמו כוכבים ()</v>
       </c>
       <c r="B12" t="str">
-        <v>2025  02:12 מאת DiSHi-12-31</v>
+        <v>2025  02:00-12-31</v>
       </c>
       <c r="C12" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-08</v>
@@ -641,13 +641,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>|אלבום חדש| אגם בוחבוט - עשרים ואחת (2025)</v>
+        <v>|| יוני רועה - מפוזרים ()</v>
       </c>
       <c r="B13" t="str">
-        <v>2025  02:11 מאת DiSHi-12-31</v>
+        <v>2025  01:56-12-31</v>
       </c>
       <c r="C13" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-08</v>
@@ -661,13 +661,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון (2025)</v>
+        <v>|| התקווה 6 - ויהי אור ()</v>
       </c>
       <c r="B14" t="str">
-        <v>2025  02:10 מאת DiSHi-12-31</v>
+        <v>2025  01:54-12-31</v>
       </c>
       <c r="C14" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-08</v>
@@ -681,13 +681,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>|אלבום חדש| רבקה זוהר - רסיסים של אור (2025)</v>
+        <v>|| שאנן סטריט ודי ג׳יי מש - באתי לבדר ()</v>
       </c>
       <c r="B15" t="str">
-        <v>2025  02:09 מאת DiSHi-12-31</v>
+        <v>2025  01:53-12-31</v>
       </c>
       <c r="C15" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-08</v>
@@ -701,13 +701,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה (2025)</v>
+        <v>אשכול נוכחות למשתמשים פעילים</v>
       </c>
       <c r="B16" t="str">
-        <v>2025  02:09 מאת DiSHi-12-31</v>
+        <v>2025  16:32 מאת freund-10-16</v>
       </c>
       <c r="C16" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=23455&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-08</v>
@@ -717,17 +717,23 @@
       </c>
       <c r="F16" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>|אלבום חדש| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות (2025)</v>
+        <v>כיצד להוריד מהאתרים המפורסמים</v>
       </c>
       <c r="B17" t="str">
-        <v>2025  02:08 מאת DiSHi-12-31</v>
+        <v>2023  16:23 מאת petel1-08-08</v>
       </c>
       <c r="C17" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=22411&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-08</v>
@@ -737,17 +743,23 @@
       </c>
       <c r="F17" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים (2025)</v>
+        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
       </c>
       <c r="B18" t="str">
-        <v>2025  02:06 מאת DiSHi-12-31</v>
+        <v>2026  22:40 מאת מוטי_ד-01-01</v>
       </c>
       <c r="C18" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24435&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-08</v>
@@ -757,17 +769,23 @@
       </c>
       <c r="F18" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>|אלבום חדש| אהוד בנאי ובנו הנדלר - פליטי הדאב (2025)</v>
+        <v>|אלבום חדש| אייל גולן - בית מפואר (2025)</v>
       </c>
       <c r="B19" t="str">
-        <v>2025  02:05 מאת DiSHi-12-31</v>
+        <v>2025  02:18 מאת DiSHi-12-31</v>
       </c>
       <c r="C19" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-08</v>
@@ -777,17 +795,23 @@
       </c>
       <c r="F19" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם (2025)</v>
+        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע (2025)</v>
       </c>
       <c r="B20" t="str">
-        <v>2025  02:05 מאת DiSHi-12-31</v>
+        <v>2025  02:17 מאת DiSHi-12-31</v>
       </c>
       <c r="C20" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-08</v>
@@ -797,17 +821,23 @@
       </c>
       <c r="F20" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>|אלבום חדש| Imagine פסטיגל - שירי התחרות (2025)</v>
+        <v>|אלבום חדש| הפרויקט של דודי לוי ואבטיפוס - הפטריקים (2025)</v>
       </c>
       <c r="B21" t="str">
-        <v>2025  02:04 מאת DiSHi-12-31</v>
+        <v>2025  02:16 מאת DiSHi-12-31</v>
       </c>
       <c r="C21" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-08</v>
@@ -817,17 +847,23 @@
       </c>
       <c r="F21" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>|אלבום חדש| סטטיק - קעקועים (2025)</v>
+        <v>|אלבום חדש| אברהם טל - חי (2025)</v>
       </c>
       <c r="B22" t="str">
-        <v>2025  02:03 מאת DiSHi-12-31</v>
+        <v>2025  02:16 מאת DiSHi-12-31</v>
       </c>
       <c r="C22" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-08</v>
@@ -837,17 +873,23 @@
       </c>
       <c r="F22" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>|אלבום חדש| השמחות - חובות אבודים (2025)</v>
+        <v>|אלבום חדש| שיר לוי - ילד מוזר (2025)</v>
       </c>
       <c r="B23" t="str">
-        <v>2025  02:02 מאת DiSHi-12-31</v>
+        <v>2025  02:14 מאת DiSHi-12-31</v>
       </c>
       <c r="C23" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-08</v>
@@ -857,17 +899,23 @@
       </c>
       <c r="F23" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>|אלבום חדש| ליאור נרקיס - דיסוננס (2025)</v>
+        <v>|אלבום חדש| מיקי גבריאלוב - שלום (2025)</v>
       </c>
       <c r="B24" t="str">
-        <v>2025  02:01 מאת DiSHi-12-31</v>
+        <v>2025  02:13 מאת DiSHi-12-31</v>
       </c>
       <c r="C24" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-08</v>
@@ -877,17 +925,23 @@
       </c>
       <c r="F24" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>|אלבום חדש| שלמה גרוניך - כמו כוכבים (2025)</v>
+        <v>|אלבום חדש| פיטר רוט - 50 (2025)</v>
       </c>
       <c r="B25" t="str">
-        <v>2025  02:00 מאת DiSHi-12-31</v>
+        <v>2025  02:13 מאת DiSHi-12-31</v>
       </c>
       <c r="C25" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-08</v>
@@ -897,17 +951,23 @@
       </c>
       <c r="F25" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) (2025)</v>
+        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם (2025)</v>
       </c>
       <c r="B26" t="str">
-        <v>2025  01:57 מאת DiSHi-12-31</v>
+        <v>2025  02:12 מאת DiSHi-12-31</v>
       </c>
       <c r="C26" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-08</v>
@@ -917,17 +977,23 @@
       </c>
       <c r="F26" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>|אלבום חדש| יוני רועה - מפוזרים (2025)</v>
+        <v>|אלבום חדש| אגם בוחבוט - עשרים ואחת (2025)</v>
       </c>
       <c r="B27" t="str">
-        <v>2025  01:56 מאת DiSHi-12-31</v>
+        <v>2025  02:11 מאת DiSHi-12-31</v>
       </c>
       <c r="C27" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-08</v>
@@ -937,17 +1003,23 @@
       </c>
       <c r="F27" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>|אלבום חדש| אתניקס - איטליה (2025)</v>
+        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון (2025)</v>
       </c>
       <c r="B28" t="str">
-        <v>2025  01:55 מאת DiSHi-12-31</v>
+        <v>2025  02:10 מאת DiSHi-12-31</v>
       </c>
       <c r="C28" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-08</v>
@@ -957,17 +1029,23 @@
       </c>
       <c r="F28" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>|אלבום חדש| התקווה 6 - ויהי אור (2025)</v>
+        <v>|אלבום חדש| רבקה זוהר - רסיסים של אור (2025)</v>
       </c>
       <c r="B29" t="str">
-        <v>2025  01:54 מאת DiSHi-12-31</v>
+        <v>2025  02:09 מאת DiSHi-12-31</v>
       </c>
       <c r="C29" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-08</v>
@@ -977,17 +1055,23 @@
       </c>
       <c r="F29" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>|אלבום חדש| שלומי סרנגה - איפרכו (2025)</v>
+        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה (2025)</v>
       </c>
       <c r="B30" t="str">
-        <v>2025  01:53 מאת DiSHi-12-31</v>
+        <v>2025  02:09 מאת DiSHi-12-31</v>
       </c>
       <c r="C30" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24430&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-08</v>
@@ -997,17 +1081,23 @@
       </c>
       <c r="F30" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30" t="str">
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>|אלבום חדש| שאנן סטריט ודי ג׳יי מש - באתי לבדר (2025)</v>
+        <v>|אלבום חדש| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות (2025)</v>
       </c>
       <c r="B31" t="str">
-        <v>2025  01:53 מאת DiSHi-12-31</v>
+        <v>2025  02:08 מאת DiSHi-12-31</v>
       </c>
       <c r="C31" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-08</v>
@@ -1017,17 +1107,23 @@
       </c>
       <c r="F31" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+      <c r="H31" t="str">
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>הרשם לחברות מלאה</v>
+        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים (2025)</v>
       </c>
       <c r="B32" t="str">
-        <v/>
+        <v>2025  02:06 מאת DiSHi-12-31</v>
       </c>
       <c r="C32" t="str">
-        <v>https://rotter.name/nor/members-new.html</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-08</v>
@@ -1037,23 +1133,29 @@
       </c>
       <c r="F32" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+      <c r="H32" t="str">
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>אוליביה דין The Art of Loving</v>
+        <v>|אלבום חדש| אהוד בנאי ובנו הנדלר - פליטי הדאב (2025)</v>
       </c>
       <c r="B33" t="str">
-        <v>2026-01-04</v>
+        <v>2025  02:05 מאת DiSHi-12-31</v>
       </c>
       <c r="C33" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E33" t="str">
-        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
+        <v/>
       </c>
       <c r="F33" t="str">
         <v>אלבומים חדשים</v>
@@ -1067,19 +1169,19 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Geese Getting Killed</v>
+        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם (2025)</v>
       </c>
       <c r="B34" t="str">
-        <v>2025-12-29</v>
+        <v>2025  02:05 מאת DiSHi-12-31</v>
       </c>
       <c r="C34" t="str">
-        <v>https://yosmusic.com/geese-getting-killed/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E34" t="str">
-        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
+        <v/>
       </c>
       <c r="F34" t="str">
         <v>אלבומים חדשים</v>
@@ -1093,19 +1195,19 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>רוסליה Lux</v>
+        <v>|אלבום חדש| Imagine פסטיגל - שירי התחרות (2025)</v>
       </c>
       <c r="B35" t="str">
-        <v>2025-12-25</v>
+        <v>2025  02:04 מאת DiSHi-12-31</v>
       </c>
       <c r="C35" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E35" t="str">
-        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
+        <v/>
       </c>
       <c r="F35" t="str">
         <v>אלבומים חדשים</v>
@@ -1119,19 +1221,19 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>יאנגבלאד אירוסמית' one more time</v>
+        <v>|אלבום חדש| סטטיק - קעקועים (2025)</v>
       </c>
       <c r="B36" t="str">
-        <v>2025-12-17</v>
+        <v>2025  02:03 מאת DiSHi-12-31</v>
       </c>
       <c r="C36" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E36" t="str">
-        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
+        <v/>
       </c>
       <c r="F36" t="str">
         <v>אלבומים חדשים</v>
@@ -1145,19 +1247,19 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>פינק פלויד Wish You Were Here 50</v>
+        <v>|אלבום חדש| השמחות - חובות אבודים (2025)</v>
       </c>
       <c r="B37" t="str">
-        <v>2025-12-14</v>
+        <v>2025  02:02 מאת DiSHi-12-31</v>
       </c>
       <c r="C37" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E37" t="str">
-        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
+        <v/>
       </c>
       <c r="F37" t="str">
         <v>אלבומים חדשים</v>
@@ -1171,19 +1273,19 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+        <v>|אלבום חדש| ליאור נרקיס - דיסוננס (2025)</v>
       </c>
       <c r="B38" t="str">
-        <v>2025-12-08</v>
+        <v>2025  02:01 מאת DiSHi-12-31</v>
       </c>
       <c r="C38" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E38" t="str">
-        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
+        <v/>
       </c>
       <c r="F38" t="str">
         <v>אלבומים חדשים</v>
@@ -1197,19 +1299,19 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>סטריי קידס DO IT (EP)</v>
+        <v>|אלבום חדש| שלמה גרוניך - כמו כוכבים (2025)</v>
       </c>
       <c r="B39" t="str">
-        <v>2025-12-04</v>
+        <v>2025  02:00 מאת DiSHi-12-31</v>
       </c>
       <c r="C39" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E39" t="str">
-        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
+        <v/>
       </c>
       <c r="F39" t="str">
         <v>אלבומים חדשים</v>
@@ -1223,19 +1325,19 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>דויד ברוזה BROZAJAZZ</v>
+        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) (2025)</v>
       </c>
       <c r="B40" t="str">
-        <v>2025-11-30</v>
+        <v>2025  01:57 מאת DiSHi-12-31</v>
       </c>
       <c r="C40" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E40" t="str">
-        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
+        <v/>
       </c>
       <c r="F40" t="str">
         <v>אלבומים חדשים</v>
@@ -1249,19 +1351,19 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Five Seconds of Summer – Everyone's A Star</v>
+        <v>|אלבום חדש| יוני רועה - מפוזרים (2025)</v>
       </c>
       <c r="B41" t="str">
-        <v>2025-11-24</v>
+        <v>2025  01:56 מאת DiSHi-12-31</v>
       </c>
       <c r="C41" t="str">
-        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E41" t="str">
-        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
+        <v/>
       </c>
       <c r="F41" t="str">
         <v>אלבומים חדשים</v>
@@ -1275,19 +1377,19 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>התקווה 6 – ויהי אור</v>
+        <v>|אלבום חדש| אתניקס - איטליה (2025)</v>
       </c>
       <c r="B42" t="str">
-        <v>2025-11-20</v>
+        <v>2025  01:55 מאת DiSHi-12-31</v>
       </c>
       <c r="C42" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E42" t="str">
-        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
+        <v/>
       </c>
       <c r="F42" t="str">
         <v>אלבומים חדשים</v>
@@ -1301,19 +1403,19 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>פלורנס אנד דה משין Everybody Scream</v>
+        <v>|אלבום חדש| התקווה 6 - ויהי אור (2025)</v>
       </c>
       <c r="B43" t="str">
-        <v>2025-11-13</v>
+        <v>2025  01:54 מאת DiSHi-12-31</v>
       </c>
       <c r="C43" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E43" t="str">
-        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
+        <v/>
       </c>
       <c r="F43" t="str">
         <v>אלבומים חדשים</v>
@@ -1327,19 +1429,19 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>טיים אימפלה Deadbeat</v>
+        <v>|אלבום חדש| שלומי סרנגה - איפרכו (2025)</v>
       </c>
       <c r="B44" t="str">
-        <v>2025-11-03</v>
+        <v>2025  01:53 מאת DiSHi-12-31</v>
       </c>
       <c r="C44" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24430&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E44" t="str">
-        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
+        <v/>
       </c>
       <c r="F44" t="str">
         <v>אלבומים חדשים</v>
@@ -1353,19 +1455,19 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+        <v>|אלבום חדש| שאנן סטריט ודי ג׳יי מש - באתי לבדר (2025)</v>
       </c>
       <c r="B45" t="str">
-        <v>2025-10-20</v>
+        <v>2025  01:53 מאת DiSHi-12-31</v>
       </c>
       <c r="C45" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E45" t="str">
-        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
+        <v/>
       </c>
       <c r="F45" t="str">
         <v>אלבומים חדשים</v>
@@ -1379,19 +1481,19 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>שלמה גרוניך – תודה אהבה</v>
+        <v>הרשם לחברות מלאה</v>
       </c>
       <c r="B46" t="str">
-        <v>2025-10-18</v>
+        <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
+        <v>https://rotter.name/nor/members-new.html</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E46" t="str">
-        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
+        <v/>
       </c>
       <c r="F46" t="str">
         <v>אלבומים חדשים</v>
@@ -1405,19 +1507,19 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>טיילור סוויפט The Life Of A Showgirl</v>
+        <v>אוליביה דין The Art of Loving</v>
       </c>
       <c r="B47" t="str">
-        <v>2025-10-11</v>
+        <v>2026-01-04</v>
       </c>
       <c r="C47" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E47" t="str">
-        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
+        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
       </c>
       <c r="F47" t="str">
         <v>אלבומים חדשים</v>
@@ -1426,24 +1528,30 @@
         <v/>
       </c>
       <c r="H47" t="str">
+        <v/>
+      </c>
+      <c r="I47" t="str">
+        <v/>
+      </c>
+      <c r="J47" t="str">
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>דוג'ה קאט Vie</v>
+        <v>Geese Getting Killed</v>
       </c>
       <c r="B48" t="str">
-        <v>2025-10-04</v>
+        <v>2025-12-29</v>
       </c>
       <c r="C48" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
+        <v>https://yosmusic.com/geese-getting-killed/</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E48" t="str">
-        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
+        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
       </c>
       <c r="F48" t="str">
         <v>אלבומים חדשים</v>
@@ -1452,24 +1560,30 @@
         <v/>
       </c>
       <c r="H48" t="str">
+        <v/>
+      </c>
+      <c r="I48" t="str">
+        <v/>
+      </c>
+      <c r="J48" t="str">
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ג'וי קרוקס Juniper</v>
+        <v>רוסליה Lux</v>
       </c>
       <c r="B49" t="str">
-        <v>2025-10-03</v>
+        <v>2025-12-25</v>
       </c>
       <c r="C49" t="str">
-        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E49" t="str">
-        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
+        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
       </c>
       <c r="F49" t="str">
         <v>אלבומים חדשים</v>
@@ -1478,24 +1592,30 @@
         <v/>
       </c>
       <c r="H49" t="str">
+        <v/>
+      </c>
+      <c r="I49" t="str">
+        <v/>
+      </c>
+      <c r="J49" t="str">
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ביפי קליירו Futique</v>
+        <v>יאנגבלאד אירוסמית' one more time</v>
       </c>
       <c r="B50" t="str">
-        <v>2025-09-30</v>
+        <v>2025-12-17</v>
       </c>
       <c r="C50" t="str">
-        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
+        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E50" t="str">
-        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
+        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
       </c>
       <c r="F50" t="str">
         <v>אלבומים חדשים</v>
@@ -1504,24 +1624,30 @@
         <v/>
       </c>
       <c r="H50" t="str">
+        <v/>
+      </c>
+      <c r="I50" t="str">
+        <v/>
+      </c>
+      <c r="J50" t="str">
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>אד שירן Play</v>
+        <v>פינק פלויד Wish You Were Here 50</v>
       </c>
       <c r="B51" t="str">
-        <v>2025-09-24</v>
+        <v>2025-12-14</v>
       </c>
       <c r="C51" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E51" t="str">
-        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
+        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
       </c>
       <c r="F51" t="str">
         <v>אלבומים חדשים</v>
@@ -1530,24 +1656,30 @@
         <v/>
       </c>
       <c r="H51" t="str">
+        <v/>
+      </c>
+      <c r="I51" t="str">
+        <v/>
+      </c>
+      <c r="J51" t="str">
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
       </c>
       <c r="B52" t="str">
-        <v>2025-09-21</v>
+        <v>2025-12-08</v>
       </c>
       <c r="C52" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
+        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E52" t="str">
-        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
+        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
       </c>
       <c r="F52" t="str">
         <v>אלבומים חדשים</v>
@@ -1556,24 +1688,30 @@
         <v/>
       </c>
       <c r="H52" t="str">
+        <v/>
+      </c>
+      <c r="I52" t="str">
+        <v/>
+      </c>
+      <c r="J52" t="str">
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>סוויד Antidepressants</v>
+        <v>סטריי קידס DO IT (EP)</v>
       </c>
       <c r="B53" t="str">
-        <v>2025-09-12</v>
+        <v>2025-12-04</v>
       </c>
       <c r="C53" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
+        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E53" t="str">
-        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
+        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
       </c>
       <c r="F53" t="str">
         <v>אלבומים חדשים</v>
@@ -1582,24 +1720,30 @@
         <v/>
       </c>
       <c r="H53" t="str">
+        <v/>
+      </c>
+      <c r="I53" t="str">
+        <v/>
+      </c>
+      <c r="J53" t="str">
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>וולף אליס The Clearing</v>
+        <v>דויד ברוזה BROZAJAZZ</v>
       </c>
       <c r="B54" t="str">
-        <v>2025-09-01</v>
+        <v>2025-11-30</v>
       </c>
       <c r="C54" t="str">
-        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E54" t="str">
-        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
+        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
       </c>
       <c r="F54" t="str">
         <v>אלבומים חדשים</v>
@@ -1608,24 +1752,30 @@
         <v/>
       </c>
       <c r="H54" t="str">
+        <v/>
+      </c>
+      <c r="I54" t="str">
+        <v/>
+      </c>
+      <c r="J54" t="str">
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+        <v>Five Seconds of Summer – Everyone's A Star</v>
       </c>
       <c r="B55" t="str">
-        <v>2025-08-29</v>
+        <v>2025-11-24</v>
       </c>
       <c r="C55" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
+        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E55" t="str">
-        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
+        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
       </c>
       <c r="F55" t="str">
         <v>אלבומים חדשים</v>
@@ -1634,24 +1784,30 @@
         <v/>
       </c>
       <c r="H55" t="str">
+        <v/>
+      </c>
+      <c r="I55" t="str">
+        <v/>
+      </c>
+      <c r="J55" t="str">
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+        <v>התקווה 6 – ויהי אור</v>
       </c>
       <c r="B56" t="str">
-        <v>2025-08-24</v>
+        <v>2025-11-20</v>
       </c>
       <c r="C56" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
+        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E56" t="str">
-        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
+        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
       </c>
       <c r="F56" t="str">
         <v>אלבומים חדשים</v>
@@ -1660,24 +1816,30 @@
         <v/>
       </c>
       <c r="H56" t="str">
+        <v/>
+      </c>
+      <c r="I56" t="str">
+        <v/>
+      </c>
+      <c r="J56" t="str">
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+        <v>פלורנס אנד דה משין Everybody Scream</v>
       </c>
       <c r="B57" t="str">
-        <v>2025-08-21</v>
+        <v>2025-11-13</v>
       </c>
       <c r="C57" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E57" t="str">
-        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
+        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
       </c>
       <c r="F57" t="str">
         <v>אלבומים חדשים</v>
@@ -1686,24 +1848,30 @@
         <v/>
       </c>
       <c r="H57" t="str">
+        <v/>
+      </c>
+      <c r="I57" t="str">
+        <v/>
+      </c>
+      <c r="J57" t="str">
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>אברהם טל – חי</v>
+        <v>טיים אימפלה Deadbeat</v>
       </c>
       <c r="B58" t="str">
-        <v>2025-08-17</v>
+        <v>2025-11-03</v>
       </c>
       <c r="C58" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E58" t="str">
-        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
+        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
       </c>
       <c r="F58" t="str">
         <v>אלבומים חדשים</v>
@@ -1712,24 +1880,30 @@
         <v/>
       </c>
       <c r="H58" t="str">
+        <v/>
+      </c>
+      <c r="I58" t="str">
+        <v/>
+      </c>
+      <c r="J58" t="str">
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>רנה ראפ Bite Me</v>
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
       </c>
       <c r="B59" t="str">
-        <v>2025-08-12</v>
+        <v>2025-10-20</v>
       </c>
       <c r="C59" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
+        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E59" t="str">
-        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
+        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
       </c>
       <c r="F59" t="str">
         <v>אלבומים חדשים</v>
@@ -1738,24 +1912,30 @@
         <v/>
       </c>
       <c r="H59" t="str">
+        <v/>
+      </c>
+      <c r="I59" t="str">
+        <v/>
+      </c>
+      <c r="J59" t="str">
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>The K's – Pretty On The Internet</v>
+        <v>שלמה גרוניך – תודה אהבה</v>
       </c>
       <c r="B60" t="str">
-        <v>2025-08-03</v>
+        <v>2025-10-18</v>
       </c>
       <c r="C60" t="str">
-        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E60" t="str">
-        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
+        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
       </c>
       <c r="F60" t="str">
         <v>אלבומים חדשים</v>
@@ -1764,24 +1944,30 @@
         <v/>
       </c>
       <c r="H60" t="str">
+        <v/>
+      </c>
+      <c r="I60" t="str">
+        <v/>
+      </c>
+      <c r="J60" t="str">
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>פליטווד מק Fifty Years – Don’t Stop</v>
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
       </c>
       <c r="B61" t="str">
-        <v>2025-07-30</v>
+        <v>2025-10-11</v>
       </c>
       <c r="C61" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%99%d7%98%d7%95%d7%95%d7%93-%d7%9e%d7%a7-fifty-years-dont-stop/</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E61" t="str">
-        <v>פליטווד מק (Fleetwood Mac) חוגגים חצי מאה של מוזיקה עם אוסף חדש בן 50 שירים, שמתפרש על כל הקריירה של הלהקה, מימיה הראשונים בסגנון בלוז, ועד להצלחתה העולמית כאחת מלהקות הגדולות בהיסטוריה של הרוק. פליטווד מק הם לא רק להקה</v>
+        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
       </c>
       <c r="F61" t="str">
         <v>אלבומים חדשים</v>
@@ -1790,38 +1976,498 @@
         <v/>
       </c>
       <c r="H61" t="str">
+        <v/>
+      </c>
+      <c r="I61" t="str">
+        <v/>
+      </c>
+      <c r="J61" t="str">
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
+        <v>דוג'ה קאט Vie</v>
+      </c>
+      <c r="B62" t="str">
+        <v>2025-10-04</v>
+      </c>
+      <c r="C62" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
+      </c>
+      <c r="D62" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E62" t="str">
+        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
+      </c>
+      <c r="F62" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G62" t="str">
+        <v/>
+      </c>
+      <c r="H62" t="str">
+        <v/>
+      </c>
+      <c r="I62" t="str">
+        <v/>
+      </c>
+      <c r="J62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>ג'וי קרוקס Juniper</v>
+      </c>
+      <c r="B63" t="str">
+        <v>2025-10-03</v>
+      </c>
+      <c r="C63" t="str">
+        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
+      </c>
+      <c r="D63" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E63" t="str">
+        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
+      </c>
+      <c r="F63" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G63" t="str">
+        <v/>
+      </c>
+      <c r="H63" t="str">
+        <v/>
+      </c>
+      <c r="I63" t="str">
+        <v/>
+      </c>
+      <c r="J63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>ביפי קליירו Futique</v>
+      </c>
+      <c r="B64" t="str">
+        <v>2025-09-30</v>
+      </c>
+      <c r="C64" t="str">
+        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
+      </c>
+      <c r="D64" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E64" t="str">
+        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
+      </c>
+      <c r="F64" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G64" t="str">
+        <v/>
+      </c>
+      <c r="H64" t="str">
+        <v/>
+      </c>
+      <c r="I64" t="str">
+        <v/>
+      </c>
+      <c r="J64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>אד שירן Play</v>
+      </c>
+      <c r="B65" t="str">
+        <v>2025-09-24</v>
+      </c>
+      <c r="C65" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
+      </c>
+      <c r="D65" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E65" t="str">
+        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
+      </c>
+      <c r="F65" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G65" t="str">
+        <v/>
+      </c>
+      <c r="H65" t="str">
+        <v/>
+      </c>
+      <c r="I65" t="str">
+        <v/>
+      </c>
+      <c r="J65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+      </c>
+      <c r="B66" t="str">
+        <v>2025-09-21</v>
+      </c>
+      <c r="C66" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
+      </c>
+      <c r="D66" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E66" t="str">
+        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
+      </c>
+      <c r="F66" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G66" t="str">
+        <v/>
+      </c>
+      <c r="H66" t="str">
+        <v/>
+      </c>
+      <c r="I66" t="str">
+        <v/>
+      </c>
+      <c r="J66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>סוויד Antidepressants</v>
+      </c>
+      <c r="B67" t="str">
+        <v>2025-09-12</v>
+      </c>
+      <c r="C67" t="str">
+        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
+      </c>
+      <c r="D67" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E67" t="str">
+        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
+      </c>
+      <c r="F67" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G67" t="str">
+        <v/>
+      </c>
+      <c r="H67" t="str">
+        <v/>
+      </c>
+      <c r="I67" t="str">
+        <v/>
+      </c>
+      <c r="J67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>וולף אליס The Clearing</v>
+      </c>
+      <c r="B68" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="C68" t="str">
+        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
+      </c>
+      <c r="D68" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E68" t="str">
+        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
+      </c>
+      <c r="F68" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G68" t="str">
+        <v/>
+      </c>
+      <c r="H68" t="str">
+        <v/>
+      </c>
+      <c r="I68" t="str">
+        <v/>
+      </c>
+      <c r="J68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+      </c>
+      <c r="B69" t="str">
+        <v>2025-08-29</v>
+      </c>
+      <c r="C69" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
+      </c>
+      <c r="D69" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E69" t="str">
+        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
+      </c>
+      <c r="F69" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G69" t="str">
+        <v/>
+      </c>
+      <c r="H69" t="str">
+        <v/>
+      </c>
+      <c r="I69" t="str">
+        <v/>
+      </c>
+      <c r="J69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+      </c>
+      <c r="B70" t="str">
+        <v>2025-08-24</v>
+      </c>
+      <c r="C70" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
+      </c>
+      <c r="D70" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E70" t="str">
+        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
+      </c>
+      <c r="F70" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G70" t="str">
+        <v/>
+      </c>
+      <c r="H70" t="str">
+        <v/>
+      </c>
+      <c r="I70" t="str">
+        <v/>
+      </c>
+      <c r="J70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+      </c>
+      <c r="B71" t="str">
+        <v>2025-08-21</v>
+      </c>
+      <c r="C71" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
+      </c>
+      <c r="D71" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E71" t="str">
+        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
+      </c>
+      <c r="F71" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G71" t="str">
+        <v/>
+      </c>
+      <c r="H71" t="str">
+        <v/>
+      </c>
+      <c r="I71" t="str">
+        <v/>
+      </c>
+      <c r="J71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>אברהם טל – חי</v>
+      </c>
+      <c r="B72" t="str">
+        <v>2025-08-17</v>
+      </c>
+      <c r="C72" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
+      </c>
+      <c r="D72" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E72" t="str">
+        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
+      </c>
+      <c r="F72" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G72" t="str">
+        <v/>
+      </c>
+      <c r="H72" t="str">
+        <v/>
+      </c>
+      <c r="I72" t="str">
+        <v/>
+      </c>
+      <c r="J72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>רנה ראפ Bite Me</v>
+      </c>
+      <c r="B73" t="str">
+        <v>2025-08-12</v>
+      </c>
+      <c r="C73" t="str">
+        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
+      </c>
+      <c r="D73" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E73" t="str">
+        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
+      </c>
+      <c r="F73" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G73" t="str">
+        <v/>
+      </c>
+      <c r="H73" t="str">
+        <v/>
+      </c>
+      <c r="I73" t="str">
+        <v/>
+      </c>
+      <c r="J73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>The K's – Pretty On The Internet</v>
+      </c>
+      <c r="B74" t="str">
+        <v>2025-08-03</v>
+      </c>
+      <c r="C74" t="str">
+        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
+      </c>
+      <c r="D74" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E74" t="str">
+        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
+      </c>
+      <c r="F74" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G74" t="str">
+        <v/>
+      </c>
+      <c r="H74" t="str">
+        <v/>
+      </c>
+      <c r="I74" t="str">
+        <v/>
+      </c>
+      <c r="J74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>פליטווד מק Fifty Years – Don’t Stop</v>
+      </c>
+      <c r="B75" t="str">
+        <v>2025-07-30</v>
+      </c>
+      <c r="C75" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%99%d7%98%d7%95%d7%95%d7%93-%d7%9e%d7%a7-fifty-years-dont-stop/</v>
+      </c>
+      <c r="D75" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E75" t="str">
+        <v>פליטווד מק (Fleetwood Mac) חוגגים חצי מאה של מוזיקה עם אוסף חדש בן 50 שירים, שמתפרש על כל הקריירה של הלהקה, מימיה הראשונים בסגנון בלוז, ועד להצלחתה העולמית כאחת מלהקות הגדולות בהיסטוריה של הרוק. פליטווד מק הם לא רק להקה</v>
+      </c>
+      <c r="F75" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G75" t="str">
+        <v/>
+      </c>
+      <c r="H75" t="str">
+        <v/>
+      </c>
+      <c r="I75" t="str">
+        <v/>
+      </c>
+      <c r="J75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
         <v>Wet Leg Moisturizer</v>
       </c>
-      <c r="B62" t="str">
+      <c r="B76" t="str">
         <v>2025-07-25</v>
       </c>
-      <c r="C62" t="str">
+      <c r="C76" t="str">
         <v>https://yosmusic.com/wet-leg-moisturizer/</v>
       </c>
-      <c r="D62" t="str">
-        <v>2026-01-08</v>
-      </c>
-      <c r="E62" t="str">
+      <c r="D76" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E76" t="str">
         <v>להקת Wet Leg לא הוציאה קרם לחות (Moisturizer) כמוצר טיפוח. במקום זאת, "Moisturizer" הוא שמו של האלבום השני והחדש שלהם. במרכז –  צמד אינדי-רוק המורכב מהחברות ריין טיסדייל והסטר צ'יימברס. אלבום הבכורה הנושא את שמה, הגיע למקום הראשון במצעד האלבומים</v>
       </c>
-      <c r="F62" t="str">
-        <v>אלבומים חדשים</v>
-      </c>
-      <c r="G62" t="str">
-        <v/>
-      </c>
-      <c r="H62" t="str">
+      <c r="F76" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G76" t="str">
+        <v/>
+      </c>
+      <c r="H76" t="str">
+        <v/>
+      </c>
+      <c r="I76" t="str">
+        <v/>
+      </c>
+      <c r="J76" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H62"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J76"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:L77"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,19 +421,19 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>|| אייל גולן - בית מפואר ()</v>
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
       </c>
       <c r="B2" t="str">
-        <v>2025  02:18-12-31</v>
+        <v>2026-01-09</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
       </c>
       <c r="F2" t="str">
         <v>אלבומים חדשים</v>
@@ -441,13 +441,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>|| הפרויקט של דודי לוי ואבטיפוס - הפטריקים ()</v>
+        <v>|| אייל גולן - בית מפואר ()</v>
       </c>
       <c r="B3" t="str">
-        <v>2025  02:16-12-31</v>
+        <v>2025  02:18-12-31</v>
       </c>
       <c r="C3" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-08</v>
@@ -457,17 +457,23 @@
       </c>
       <c r="F3" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>|| שיר לוי - ילד מוזר ()</v>
+        <v>|| הפרויקט של דודי לוי ואבטיפוס - הפטריקים ()</v>
       </c>
       <c r="B4" t="str">
-        <v>2025  02:14-12-31</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C4" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-08</v>
@@ -477,17 +483,23 @@
       </c>
       <c r="F4" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>|| פיטר רוט - 50 ()</v>
+        <v>|| שיר לוי - ילד מוזר ()</v>
       </c>
       <c r="B5" t="str">
-        <v>2025  02:13-12-31</v>
+        <v>2025  02:14-12-31</v>
       </c>
       <c r="C5" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-08</v>
@@ -497,17 +509,23 @@
       </c>
       <c r="F5" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>|| אגם בוחבוט - עשרים ואחת ()</v>
+        <v>|| פיטר רוט - 50 ()</v>
       </c>
       <c r="B6" t="str">
-        <v>2025  02:11-12-31</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C6" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-08</v>
@@ -517,17 +535,23 @@
       </c>
       <c r="F6" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>|| רבקה זוהר - רסיסים של אור ()</v>
+        <v>|| אגם בוחבוט - עשרים ואחת ()</v>
       </c>
       <c r="B7" t="str">
-        <v>2025  02:09-12-31</v>
+        <v>2025  02:11-12-31</v>
       </c>
       <c r="C7" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-08</v>
@@ -537,17 +561,23 @@
       </c>
       <c r="F7" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>|| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות ()</v>
+        <v>|| רבקה זוהר - רסיסים של אור ()</v>
       </c>
       <c r="B8" t="str">
-        <v>2025  02:08-12-31</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C8" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-08</v>
@@ -557,17 +587,23 @@
       </c>
       <c r="F8" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>|| אהוד בנאי ובנו הנדלר - פליטי הדאב ()</v>
+        <v>|| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות ()</v>
       </c>
       <c r="B9" t="str">
-        <v>2025  02:05-12-31</v>
+        <v>2025  02:08-12-31</v>
       </c>
       <c r="C9" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-08</v>
@@ -577,17 +613,23 @@
       </c>
       <c r="F9" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>|| Imagine פסטיגל - שירי התחרות ()</v>
+        <v>|| אהוד בנאי ובנו הנדלר - פליטי הדאב ()</v>
       </c>
       <c r="B10" t="str">
-        <v>2025  02:04-12-31</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C10" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-08</v>
@@ -597,17 +639,23 @@
       </c>
       <c r="F10" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>|| השמחות - חובות אבודים ()</v>
+        <v>|| Imagine פסטיגל - שירי התחרות ()</v>
       </c>
       <c r="B11" t="str">
-        <v>2025  02:02-12-31</v>
+        <v>2025  02:04-12-31</v>
       </c>
       <c r="C11" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-08</v>
@@ -617,17 +665,23 @@
       </c>
       <c r="F11" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>|| שלמה גרוניך - כמו כוכבים ()</v>
+        <v>|| השמחות - חובות אבודים ()</v>
       </c>
       <c r="B12" t="str">
-        <v>2025  02:00-12-31</v>
+        <v>2025  02:02-12-31</v>
       </c>
       <c r="C12" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-08</v>
@@ -637,17 +691,23 @@
       </c>
       <c r="F12" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>|| יוני רועה - מפוזרים ()</v>
+        <v>|| שלמה גרוניך - כמו כוכבים ()</v>
       </c>
       <c r="B13" t="str">
-        <v>2025  01:56-12-31</v>
+        <v>2025  02:00-12-31</v>
       </c>
       <c r="C13" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-08</v>
@@ -657,17 +717,23 @@
       </c>
       <c r="F13" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>|| התקווה 6 - ויהי אור ()</v>
+        <v>|| יוני רועה - מפוזרים ()</v>
       </c>
       <c r="B14" t="str">
-        <v>2025  01:54-12-31</v>
+        <v>2025  01:56-12-31</v>
       </c>
       <c r="C14" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-08</v>
@@ -677,17 +743,23 @@
       </c>
       <c r="F14" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>|| שאנן סטריט ודי ג׳יי מש - באתי לבדר ()</v>
+        <v>|| התקווה 6 - ויהי אור ()</v>
       </c>
       <c r="B15" t="str">
-        <v>2025  01:53-12-31</v>
+        <v>2025  01:54-12-31</v>
       </c>
       <c r="C15" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-08</v>
@@ -697,17 +769,23 @@
       </c>
       <c r="F15" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>אשכול נוכחות למשתמשים פעילים</v>
+        <v>|| שאנן סטריט ודי ג׳יי מש - באתי לבדר ()</v>
       </c>
       <c r="B16" t="str">
-        <v>2025  16:32 מאת freund-10-16</v>
+        <v>2025  01:53-12-31</v>
       </c>
       <c r="C16" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=23455&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-08</v>
@@ -727,13 +805,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>כיצד להוריד מהאתרים המפורסמים</v>
+        <v>אשכול נוכחות למשתמשים פעילים</v>
       </c>
       <c r="B17" t="str">
-        <v>2023  16:23 מאת petel1-08-08</v>
+        <v>2025  16:32 מאת freund-10-16</v>
       </c>
       <c r="C17" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=22411&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=23455&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-08</v>
@@ -748,18 +826,24 @@
         <v/>
       </c>
       <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17" t="str">
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
+        <v>כיצד להוריד מהאתרים המפורסמים</v>
       </c>
       <c r="B18" t="str">
-        <v>2026  22:40 מאת מוטי_ד-01-01</v>
+        <v>2023  16:23 מאת petel1-08-08</v>
       </c>
       <c r="C18" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24435&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=22411&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-08</v>
@@ -774,18 +858,24 @@
         <v/>
       </c>
       <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
+      <c r="J18" t="str">
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>|אלבום חדש| אייל גולן - בית מפואר (2025)</v>
+        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
       </c>
       <c r="B19" t="str">
-        <v>2025  02:18 מאת DiSHi-12-31</v>
+        <v>2026  22:40 מאת מוטי_ד-01-01</v>
       </c>
       <c r="C19" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24435&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-08</v>
@@ -800,18 +890,24 @@
         <v/>
       </c>
       <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v/>
+      </c>
+      <c r="J19" t="str">
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע (2025)</v>
+        <v>|אלבום חדש| אייל גולן - בית מפואר (2025)</v>
       </c>
       <c r="B20" t="str">
-        <v>2025  02:17 מאת DiSHi-12-31</v>
+        <v>2025  02:18 מאת DiSHi-12-31</v>
       </c>
       <c r="C20" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-08</v>
@@ -826,18 +922,24 @@
         <v/>
       </c>
       <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
+      <c r="J20" t="str">
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>|אלבום חדש| הפרויקט של דודי לוי ואבטיפוס - הפטריקים (2025)</v>
+        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע (2025)</v>
       </c>
       <c r="B21" t="str">
-        <v>2025  02:16 מאת DiSHi-12-31</v>
+        <v>2025  02:17 מאת DiSHi-12-31</v>
       </c>
       <c r="C21" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-08</v>
@@ -852,18 +954,24 @@
         <v/>
       </c>
       <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
+      <c r="J21" t="str">
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>|אלבום חדש| אברהם טל - חי (2025)</v>
+        <v>|אלבום חדש| הפרויקט של דודי לוי ואבטיפוס - הפטריקים (2025)</v>
       </c>
       <c r="B22" t="str">
         <v>2025  02:16 מאת DiSHi-12-31</v>
       </c>
       <c r="C22" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-08</v>
@@ -878,18 +986,24 @@
         <v/>
       </c>
       <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v/>
+      </c>
+      <c r="J22" t="str">
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>|אלבום חדש| שיר לוי - ילד מוזר (2025)</v>
+        <v>|אלבום חדש| אברהם טל - חי (2025)</v>
       </c>
       <c r="B23" t="str">
-        <v>2025  02:14 מאת DiSHi-12-31</v>
+        <v>2025  02:16 מאת DiSHi-12-31</v>
       </c>
       <c r="C23" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-08</v>
@@ -904,18 +1018,24 @@
         <v/>
       </c>
       <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v/>
+      </c>
+      <c r="J23" t="str">
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>|אלבום חדש| מיקי גבריאלוב - שלום (2025)</v>
+        <v>|אלבום חדש| שיר לוי - ילד מוזר (2025)</v>
       </c>
       <c r="B24" t="str">
-        <v>2025  02:13 מאת DiSHi-12-31</v>
+        <v>2025  02:14 מאת DiSHi-12-31</v>
       </c>
       <c r="C24" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-08</v>
@@ -930,18 +1050,24 @@
         <v/>
       </c>
       <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v/>
+      </c>
+      <c r="J24" t="str">
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>|אלבום חדש| פיטר רוט - 50 (2025)</v>
+        <v>|אלבום חדש| מיקי גבריאלוב - שלום (2025)</v>
       </c>
       <c r="B25" t="str">
         <v>2025  02:13 מאת DiSHi-12-31</v>
       </c>
       <c r="C25" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-08</v>
@@ -956,18 +1082,24 @@
         <v/>
       </c>
       <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v/>
+      </c>
+      <c r="J25" t="str">
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם (2025)</v>
+        <v>|אלבום חדש| פיטר רוט - 50 (2025)</v>
       </c>
       <c r="B26" t="str">
-        <v>2025  02:12 מאת DiSHi-12-31</v>
+        <v>2025  02:13 מאת DiSHi-12-31</v>
       </c>
       <c r="C26" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-08</v>
@@ -982,18 +1114,24 @@
         <v/>
       </c>
       <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v/>
+      </c>
+      <c r="J26" t="str">
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>|אלבום חדש| אגם בוחבוט - עשרים ואחת (2025)</v>
+        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם (2025)</v>
       </c>
       <c r="B27" t="str">
-        <v>2025  02:11 מאת DiSHi-12-31</v>
+        <v>2025  02:12 מאת DiSHi-12-31</v>
       </c>
       <c r="C27" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-08</v>
@@ -1008,18 +1146,24 @@
         <v/>
       </c>
       <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v/>
+      </c>
+      <c r="J27" t="str">
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון (2025)</v>
+        <v>|אלבום חדש| אגם בוחבוט - עשרים ואחת (2025)</v>
       </c>
       <c r="B28" t="str">
-        <v>2025  02:10 מאת DiSHi-12-31</v>
+        <v>2025  02:11 מאת DiSHi-12-31</v>
       </c>
       <c r="C28" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-08</v>
@@ -1034,18 +1178,24 @@
         <v/>
       </c>
       <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <v/>
+      </c>
+      <c r="J28" t="str">
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>|אלבום חדש| רבקה זוהר - רסיסים של אור (2025)</v>
+        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון (2025)</v>
       </c>
       <c r="B29" t="str">
-        <v>2025  02:09 מאת DiSHi-12-31</v>
+        <v>2025  02:10 מאת DiSHi-12-31</v>
       </c>
       <c r="C29" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-08</v>
@@ -1060,18 +1210,24 @@
         <v/>
       </c>
       <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <v/>
+      </c>
+      <c r="J29" t="str">
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה (2025)</v>
+        <v>|אלבום חדש| רבקה זוהר - רסיסים של אור (2025)</v>
       </c>
       <c r="B30" t="str">
         <v>2025  02:09 מאת DiSHi-12-31</v>
       </c>
       <c r="C30" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-08</v>
@@ -1086,18 +1242,24 @@
         <v/>
       </c>
       <c r="H30" t="str">
+        <v/>
+      </c>
+      <c r="I30" t="str">
+        <v/>
+      </c>
+      <c r="J30" t="str">
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>|אלבום חדש| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות (2025)</v>
+        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה (2025)</v>
       </c>
       <c r="B31" t="str">
-        <v>2025  02:08 מאת DiSHi-12-31</v>
+        <v>2025  02:09 מאת DiSHi-12-31</v>
       </c>
       <c r="C31" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-08</v>
@@ -1112,18 +1274,24 @@
         <v/>
       </c>
       <c r="H31" t="str">
+        <v/>
+      </c>
+      <c r="I31" t="str">
+        <v/>
+      </c>
+      <c r="J31" t="str">
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים (2025)</v>
+        <v>|אלבום חדש| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות (2025)</v>
       </c>
       <c r="B32" t="str">
-        <v>2025  02:06 מאת DiSHi-12-31</v>
+        <v>2025  02:08 מאת DiSHi-12-31</v>
       </c>
       <c r="C32" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-08</v>
@@ -1138,18 +1306,24 @@
         <v/>
       </c>
       <c r="H32" t="str">
+        <v/>
+      </c>
+      <c r="I32" t="str">
+        <v/>
+      </c>
+      <c r="J32" t="str">
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>|אלבום חדש| אהוד בנאי ובנו הנדלר - פליטי הדאב (2025)</v>
+        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים (2025)</v>
       </c>
       <c r="B33" t="str">
-        <v>2025  02:05 מאת DiSHi-12-31</v>
+        <v>2025  02:06 מאת DiSHi-12-31</v>
       </c>
       <c r="C33" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-08</v>
@@ -1164,18 +1338,24 @@
         <v/>
       </c>
       <c r="H33" t="str">
+        <v/>
+      </c>
+      <c r="I33" t="str">
+        <v/>
+      </c>
+      <c r="J33" t="str">
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם (2025)</v>
+        <v>|אלבום חדש| אהוד בנאי ובנו הנדלר - פליטי הדאב (2025)</v>
       </c>
       <c r="B34" t="str">
         <v>2025  02:05 מאת DiSHi-12-31</v>
       </c>
       <c r="C34" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-08</v>
@@ -1190,18 +1370,24 @@
         <v/>
       </c>
       <c r="H34" t="str">
+        <v/>
+      </c>
+      <c r="I34" t="str">
+        <v/>
+      </c>
+      <c r="J34" t="str">
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>|אלבום חדש| Imagine פסטיגל - שירי התחרות (2025)</v>
+        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם (2025)</v>
       </c>
       <c r="B35" t="str">
-        <v>2025  02:04 מאת DiSHi-12-31</v>
+        <v>2025  02:05 מאת DiSHi-12-31</v>
       </c>
       <c r="C35" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-08</v>
@@ -1216,18 +1402,24 @@
         <v/>
       </c>
       <c r="H35" t="str">
+        <v/>
+      </c>
+      <c r="I35" t="str">
+        <v/>
+      </c>
+      <c r="J35" t="str">
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>|אלבום חדש| סטטיק - קעקועים (2025)</v>
+        <v>|אלבום חדש| Imagine פסטיגל - שירי התחרות (2025)</v>
       </c>
       <c r="B36" t="str">
-        <v>2025  02:03 מאת DiSHi-12-31</v>
+        <v>2025  02:04 מאת DiSHi-12-31</v>
       </c>
       <c r="C36" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-08</v>
@@ -1242,18 +1434,24 @@
         <v/>
       </c>
       <c r="H36" t="str">
+        <v/>
+      </c>
+      <c r="I36" t="str">
+        <v/>
+      </c>
+      <c r="J36" t="str">
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>|אלבום חדש| השמחות - חובות אבודים (2025)</v>
+        <v>|אלבום חדש| סטטיק - קעקועים (2025)</v>
       </c>
       <c r="B37" t="str">
-        <v>2025  02:02 מאת DiSHi-12-31</v>
+        <v>2025  02:03 מאת DiSHi-12-31</v>
       </c>
       <c r="C37" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-08</v>
@@ -1268,18 +1466,24 @@
         <v/>
       </c>
       <c r="H37" t="str">
+        <v/>
+      </c>
+      <c r="I37" t="str">
+        <v/>
+      </c>
+      <c r="J37" t="str">
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>|אלבום חדש| ליאור נרקיס - דיסוננס (2025)</v>
+        <v>|אלבום חדש| השמחות - חובות אבודים (2025)</v>
       </c>
       <c r="B38" t="str">
-        <v>2025  02:01 מאת DiSHi-12-31</v>
+        <v>2025  02:02 מאת DiSHi-12-31</v>
       </c>
       <c r="C38" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-08</v>
@@ -1294,18 +1498,24 @@
         <v/>
       </c>
       <c r="H38" t="str">
+        <v/>
+      </c>
+      <c r="I38" t="str">
+        <v/>
+      </c>
+      <c r="J38" t="str">
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>|אלבום חדש| שלמה גרוניך - כמו כוכבים (2025)</v>
+        <v>|אלבום חדש| ליאור נרקיס - דיסוננס (2025)</v>
       </c>
       <c r="B39" t="str">
-        <v>2025  02:00 מאת DiSHi-12-31</v>
+        <v>2025  02:01 מאת DiSHi-12-31</v>
       </c>
       <c r="C39" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-08</v>
@@ -1320,18 +1530,24 @@
         <v/>
       </c>
       <c r="H39" t="str">
+        <v/>
+      </c>
+      <c r="I39" t="str">
+        <v/>
+      </c>
+      <c r="J39" t="str">
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) (2025)</v>
+        <v>|אלבום חדש| שלמה גרוניך - כמו כוכבים (2025)</v>
       </c>
       <c r="B40" t="str">
-        <v>2025  01:57 מאת DiSHi-12-31</v>
+        <v>2025  02:00 מאת DiSHi-12-31</v>
       </c>
       <c r="C40" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-08</v>
@@ -1346,18 +1562,24 @@
         <v/>
       </c>
       <c r="H40" t="str">
+        <v/>
+      </c>
+      <c r="I40" t="str">
+        <v/>
+      </c>
+      <c r="J40" t="str">
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>|אלבום חדש| יוני רועה - מפוזרים (2025)</v>
+        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) (2025)</v>
       </c>
       <c r="B41" t="str">
-        <v>2025  01:56 מאת DiSHi-12-31</v>
+        <v>2025  01:57 מאת DiSHi-12-31</v>
       </c>
       <c r="C41" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-08</v>
@@ -1372,18 +1594,24 @@
         <v/>
       </c>
       <c r="H41" t="str">
+        <v/>
+      </c>
+      <c r="I41" t="str">
+        <v/>
+      </c>
+      <c r="J41" t="str">
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>|אלבום חדש| אתניקס - איטליה (2025)</v>
+        <v>|אלבום חדש| יוני רועה - מפוזרים (2025)</v>
       </c>
       <c r="B42" t="str">
-        <v>2025  01:55 מאת DiSHi-12-31</v>
+        <v>2025  01:56 מאת DiSHi-12-31</v>
       </c>
       <c r="C42" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-08</v>
@@ -1398,18 +1626,24 @@
         <v/>
       </c>
       <c r="H42" t="str">
+        <v/>
+      </c>
+      <c r="I42" t="str">
+        <v/>
+      </c>
+      <c r="J42" t="str">
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>|אלבום חדש| התקווה 6 - ויהי אור (2025)</v>
+        <v>|אלבום חדש| אתניקס - איטליה (2025)</v>
       </c>
       <c r="B43" t="str">
-        <v>2025  01:54 מאת DiSHi-12-31</v>
+        <v>2025  01:55 מאת DiSHi-12-31</v>
       </c>
       <c r="C43" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-08</v>
@@ -1424,18 +1658,24 @@
         <v/>
       </c>
       <c r="H43" t="str">
+        <v/>
+      </c>
+      <c r="I43" t="str">
+        <v/>
+      </c>
+      <c r="J43" t="str">
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>|אלבום חדש| שלומי סרנגה - איפרכו (2025)</v>
+        <v>|אלבום חדש| התקווה 6 - ויהי אור (2025)</v>
       </c>
       <c r="B44" t="str">
-        <v>2025  01:53 מאת DiSHi-12-31</v>
+        <v>2025  01:54 מאת DiSHi-12-31</v>
       </c>
       <c r="C44" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24430&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-08</v>
@@ -1450,18 +1690,24 @@
         <v/>
       </c>
       <c r="H44" t="str">
+        <v/>
+      </c>
+      <c r="I44" t="str">
+        <v/>
+      </c>
+      <c r="J44" t="str">
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>|אלבום חדש| שאנן סטריט ודי ג׳יי מש - באתי לבדר (2025)</v>
+        <v>|אלבום חדש| שלומי סרנגה - איפרכו (2025)</v>
       </c>
       <c r="B45" t="str">
         <v>2025  01:53 מאת DiSHi-12-31</v>
       </c>
       <c r="C45" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24430&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-08</v>
@@ -1476,18 +1722,24 @@
         <v/>
       </c>
       <c r="H45" t="str">
+        <v/>
+      </c>
+      <c r="I45" t="str">
+        <v/>
+      </c>
+      <c r="J45" t="str">
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>הרשם לחברות מלאה</v>
+        <v>|אלבום חדש| שאנן סטריט ודי ג׳יי מש - באתי לבדר (2025)</v>
       </c>
       <c r="B46" t="str">
-        <v/>
+        <v>2025  01:53 מאת DiSHi-12-31</v>
       </c>
       <c r="C46" t="str">
-        <v>https://rotter.name/nor/members-new.html</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-08</v>
@@ -1502,24 +1754,30 @@
         <v/>
       </c>
       <c r="H46" t="str">
+        <v/>
+      </c>
+      <c r="I46" t="str">
+        <v/>
+      </c>
+      <c r="J46" t="str">
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>אוליביה דין The Art of Loving</v>
+        <v>הרשם לחברות מלאה</v>
       </c>
       <c r="B47" t="str">
-        <v>2026-01-04</v>
+        <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
+        <v>https://rotter.name/nor/members-new.html</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E47" t="str">
-        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
+        <v/>
       </c>
       <c r="F47" t="str">
         <v>אלבומים חדשים</v>
@@ -1539,19 +1797,19 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Geese Getting Killed</v>
+        <v>אוליביה דין The Art of Loving</v>
       </c>
       <c r="B48" t="str">
-        <v>2025-12-29</v>
+        <v>2026-01-04</v>
       </c>
       <c r="C48" t="str">
-        <v>https://yosmusic.com/geese-getting-killed/</v>
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E48" t="str">
-        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
+        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
       </c>
       <c r="F48" t="str">
         <v>אלבומים חדשים</v>
@@ -1566,24 +1824,30 @@
         <v/>
       </c>
       <c r="J48" t="str">
+        <v/>
+      </c>
+      <c r="K48" t="str">
+        <v/>
+      </c>
+      <c r="L48" t="str">
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>רוסליה Lux</v>
+        <v>Geese Getting Killed</v>
       </c>
       <c r="B49" t="str">
-        <v>2025-12-25</v>
+        <v>2025-12-29</v>
       </c>
       <c r="C49" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
+        <v>https://yosmusic.com/geese-getting-killed/</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E49" t="str">
-        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
+        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
       </c>
       <c r="F49" t="str">
         <v>אלבומים חדשים</v>
@@ -1598,24 +1862,30 @@
         <v/>
       </c>
       <c r="J49" t="str">
+        <v/>
+      </c>
+      <c r="K49" t="str">
+        <v/>
+      </c>
+      <c r="L49" t="str">
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>יאנגבלאד אירוסמית' one more time</v>
+        <v>רוסליה Lux</v>
       </c>
       <c r="B50" t="str">
-        <v>2025-12-17</v>
+        <v>2025-12-25</v>
       </c>
       <c r="C50" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E50" t="str">
-        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
+        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
       </c>
       <c r="F50" t="str">
         <v>אלבומים חדשים</v>
@@ -1630,24 +1900,30 @@
         <v/>
       </c>
       <c r="J50" t="str">
+        <v/>
+      </c>
+      <c r="K50" t="str">
+        <v/>
+      </c>
+      <c r="L50" t="str">
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>פינק פלויד Wish You Were Here 50</v>
+        <v>יאנגבלאד אירוסמית' one more time</v>
       </c>
       <c r="B51" t="str">
-        <v>2025-12-14</v>
+        <v>2025-12-17</v>
       </c>
       <c r="C51" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
+        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E51" t="str">
-        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
+        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
       </c>
       <c r="F51" t="str">
         <v>אלבומים חדשים</v>
@@ -1662,24 +1938,30 @@
         <v/>
       </c>
       <c r="J51" t="str">
+        <v/>
+      </c>
+      <c r="K51" t="str">
+        <v/>
+      </c>
+      <c r="L51" t="str">
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+        <v>פינק פלויד Wish You Were Here 50</v>
       </c>
       <c r="B52" t="str">
-        <v>2025-12-08</v>
+        <v>2025-12-14</v>
       </c>
       <c r="C52" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E52" t="str">
-        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
+        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
       </c>
       <c r="F52" t="str">
         <v>אלבומים חדשים</v>
@@ -1694,24 +1976,30 @@
         <v/>
       </c>
       <c r="J52" t="str">
+        <v/>
+      </c>
+      <c r="K52" t="str">
+        <v/>
+      </c>
+      <c r="L52" t="str">
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>סטריי קידס DO IT (EP)</v>
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
       </c>
       <c r="B53" t="str">
-        <v>2025-12-04</v>
+        <v>2025-12-08</v>
       </c>
       <c r="C53" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
+        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E53" t="str">
-        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
+        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
       </c>
       <c r="F53" t="str">
         <v>אלבומים חדשים</v>
@@ -1726,24 +2014,30 @@
         <v/>
       </c>
       <c r="J53" t="str">
+        <v/>
+      </c>
+      <c r="K53" t="str">
+        <v/>
+      </c>
+      <c r="L53" t="str">
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>דויד ברוזה BROZAJAZZ</v>
+        <v>סטריי קידס DO IT (EP)</v>
       </c>
       <c r="B54" t="str">
-        <v>2025-11-30</v>
+        <v>2025-12-04</v>
       </c>
       <c r="C54" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
+        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E54" t="str">
-        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
+        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
       </c>
       <c r="F54" t="str">
         <v>אלבומים חדשים</v>
@@ -1758,24 +2052,30 @@
         <v/>
       </c>
       <c r="J54" t="str">
+        <v/>
+      </c>
+      <c r="K54" t="str">
+        <v/>
+      </c>
+      <c r="L54" t="str">
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Five Seconds of Summer – Everyone's A Star</v>
+        <v>דויד ברוזה BROZAJAZZ</v>
       </c>
       <c r="B55" t="str">
-        <v>2025-11-24</v>
+        <v>2025-11-30</v>
       </c>
       <c r="C55" t="str">
-        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E55" t="str">
-        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
+        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
       </c>
       <c r="F55" t="str">
         <v>אלבומים חדשים</v>
@@ -1790,24 +2090,30 @@
         <v/>
       </c>
       <c r="J55" t="str">
+        <v/>
+      </c>
+      <c r="K55" t="str">
+        <v/>
+      </c>
+      <c r="L55" t="str">
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>התקווה 6 – ויהי אור</v>
+        <v>Five Seconds of Summer – Everyone's A Star</v>
       </c>
       <c r="B56" t="str">
-        <v>2025-11-20</v>
+        <v>2025-11-24</v>
       </c>
       <c r="C56" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
+        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E56" t="str">
-        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
+        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
       </c>
       <c r="F56" t="str">
         <v>אלבומים חדשים</v>
@@ -1822,24 +2128,30 @@
         <v/>
       </c>
       <c r="J56" t="str">
+        <v/>
+      </c>
+      <c r="K56" t="str">
+        <v/>
+      </c>
+      <c r="L56" t="str">
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>פלורנס אנד דה משין Everybody Scream</v>
+        <v>התקווה 6 – ויהי אור</v>
       </c>
       <c r="B57" t="str">
-        <v>2025-11-13</v>
+        <v>2025-11-20</v>
       </c>
       <c r="C57" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
+        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E57" t="str">
-        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
+        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
       </c>
       <c r="F57" t="str">
         <v>אלבומים חדשים</v>
@@ -1854,24 +2166,30 @@
         <v/>
       </c>
       <c r="J57" t="str">
+        <v/>
+      </c>
+      <c r="K57" t="str">
+        <v/>
+      </c>
+      <c r="L57" t="str">
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>טיים אימפלה Deadbeat</v>
+        <v>פלורנס אנד דה משין Everybody Scream</v>
       </c>
       <c r="B58" t="str">
-        <v>2025-11-03</v>
+        <v>2025-11-13</v>
       </c>
       <c r="C58" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E58" t="str">
-        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
+        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
       </c>
       <c r="F58" t="str">
         <v>אלבומים חדשים</v>
@@ -1886,24 +2204,30 @@
         <v/>
       </c>
       <c r="J58" t="str">
+        <v/>
+      </c>
+      <c r="K58" t="str">
+        <v/>
+      </c>
+      <c r="L58" t="str">
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+        <v>טיים אימפלה Deadbeat</v>
       </c>
       <c r="B59" t="str">
-        <v>2025-10-20</v>
+        <v>2025-11-03</v>
       </c>
       <c r="C59" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E59" t="str">
-        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
+        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
       </c>
       <c r="F59" t="str">
         <v>אלבומים חדשים</v>
@@ -1918,24 +2242,30 @@
         <v/>
       </c>
       <c r="J59" t="str">
+        <v/>
+      </c>
+      <c r="K59" t="str">
+        <v/>
+      </c>
+      <c r="L59" t="str">
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>שלמה גרוניך – תודה אהבה</v>
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
       </c>
       <c r="B60" t="str">
-        <v>2025-10-18</v>
+        <v>2025-10-20</v>
       </c>
       <c r="C60" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
+        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E60" t="str">
-        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
+        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
       </c>
       <c r="F60" t="str">
         <v>אלבומים חדשים</v>
@@ -1950,24 +2280,30 @@
         <v/>
       </c>
       <c r="J60" t="str">
+        <v/>
+      </c>
+      <c r="K60" t="str">
+        <v/>
+      </c>
+      <c r="L60" t="str">
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>טיילור סוויפט The Life Of A Showgirl</v>
+        <v>שלמה גרוניך – תודה אהבה</v>
       </c>
       <c r="B61" t="str">
-        <v>2025-10-11</v>
+        <v>2025-10-18</v>
       </c>
       <c r="C61" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E61" t="str">
-        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
+        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
       </c>
       <c r="F61" t="str">
         <v>אלבומים חדשים</v>
@@ -1982,24 +2318,30 @@
         <v/>
       </c>
       <c r="J61" t="str">
+        <v/>
+      </c>
+      <c r="K61" t="str">
+        <v/>
+      </c>
+      <c r="L61" t="str">
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>דוג'ה קאט Vie</v>
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
       </c>
       <c r="B62" t="str">
-        <v>2025-10-04</v>
+        <v>2025-10-11</v>
       </c>
       <c r="C62" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E62" t="str">
-        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
+        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
       </c>
       <c r="F62" t="str">
         <v>אלבומים חדשים</v>
@@ -2014,24 +2356,30 @@
         <v/>
       </c>
       <c r="J62" t="str">
+        <v/>
+      </c>
+      <c r="K62" t="str">
+        <v/>
+      </c>
+      <c r="L62" t="str">
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>ג'וי קרוקס Juniper</v>
+        <v>דוג'ה קאט Vie</v>
       </c>
       <c r="B63" t="str">
-        <v>2025-10-03</v>
+        <v>2025-10-04</v>
       </c>
       <c r="C63" t="str">
-        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E63" t="str">
-        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
+        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
       </c>
       <c r="F63" t="str">
         <v>אלבומים חדשים</v>
@@ -2046,24 +2394,30 @@
         <v/>
       </c>
       <c r="J63" t="str">
+        <v/>
+      </c>
+      <c r="K63" t="str">
+        <v/>
+      </c>
+      <c r="L63" t="str">
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>ביפי קליירו Futique</v>
+        <v>ג'וי קרוקס Juniper</v>
       </c>
       <c r="B64" t="str">
-        <v>2025-09-30</v>
+        <v>2025-10-03</v>
       </c>
       <c r="C64" t="str">
-        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
+        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E64" t="str">
-        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
+        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
       </c>
       <c r="F64" t="str">
         <v>אלבומים חדשים</v>
@@ -2078,24 +2432,30 @@
         <v/>
       </c>
       <c r="J64" t="str">
+        <v/>
+      </c>
+      <c r="K64" t="str">
+        <v/>
+      </c>
+      <c r="L64" t="str">
         <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>אד שירן Play</v>
+        <v>ביפי קליירו Futique</v>
       </c>
       <c r="B65" t="str">
-        <v>2025-09-24</v>
+        <v>2025-09-30</v>
       </c>
       <c r="C65" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
+        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E65" t="str">
-        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
+        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
       </c>
       <c r="F65" t="str">
         <v>אלבומים חדשים</v>
@@ -2110,24 +2470,30 @@
         <v/>
       </c>
       <c r="J65" t="str">
+        <v/>
+      </c>
+      <c r="K65" t="str">
+        <v/>
+      </c>
+      <c r="L65" t="str">
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+        <v>אד שירן Play</v>
       </c>
       <c r="B66" t="str">
-        <v>2025-09-21</v>
+        <v>2025-09-24</v>
       </c>
       <c r="C66" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
+        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E66" t="str">
-        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
+        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
       </c>
       <c r="F66" t="str">
         <v>אלבומים חדשים</v>
@@ -2142,24 +2508,30 @@
         <v/>
       </c>
       <c r="J66" t="str">
+        <v/>
+      </c>
+      <c r="K66" t="str">
+        <v/>
+      </c>
+      <c r="L66" t="str">
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>סוויד Antidepressants</v>
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
       </c>
       <c r="B67" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-21</v>
       </c>
       <c r="C67" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
+        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E67" t="str">
-        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
+        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
       </c>
       <c r="F67" t="str">
         <v>אלבומים חדשים</v>
@@ -2174,24 +2546,30 @@
         <v/>
       </c>
       <c r="J67" t="str">
+        <v/>
+      </c>
+      <c r="K67" t="str">
+        <v/>
+      </c>
+      <c r="L67" t="str">
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>וולף אליס The Clearing</v>
+        <v>סוויד Antidepressants</v>
       </c>
       <c r="B68" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-12</v>
       </c>
       <c r="C68" t="str">
-        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
+        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E68" t="str">
-        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
+        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
       </c>
       <c r="F68" t="str">
         <v>אלבומים חדשים</v>
@@ -2206,24 +2584,30 @@
         <v/>
       </c>
       <c r="J68" t="str">
+        <v/>
+      </c>
+      <c r="K68" t="str">
+        <v/>
+      </c>
+      <c r="L68" t="str">
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+        <v>וולף אליס The Clearing</v>
       </c>
       <c r="B69" t="str">
-        <v>2025-08-29</v>
+        <v>2025-09-01</v>
       </c>
       <c r="C69" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
+        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E69" t="str">
-        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
+        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
       </c>
       <c r="F69" t="str">
         <v>אלבומים חדשים</v>
@@ -2238,24 +2622,30 @@
         <v/>
       </c>
       <c r="J69" t="str">
+        <v/>
+      </c>
+      <c r="K69" t="str">
+        <v/>
+      </c>
+      <c r="L69" t="str">
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
       </c>
       <c r="B70" t="str">
-        <v>2025-08-24</v>
+        <v>2025-08-29</v>
       </c>
       <c r="C70" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
+        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E70" t="str">
-        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
+        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
       </c>
       <c r="F70" t="str">
         <v>אלבומים חדשים</v>
@@ -2270,24 +2660,30 @@
         <v/>
       </c>
       <c r="J70" t="str">
+        <v/>
+      </c>
+      <c r="K70" t="str">
+        <v/>
+      </c>
+      <c r="L70" t="str">
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
       </c>
       <c r="B71" t="str">
-        <v>2025-08-21</v>
+        <v>2025-08-24</v>
       </c>
       <c r="C71" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
+        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E71" t="str">
-        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
+        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
       </c>
       <c r="F71" t="str">
         <v>אלבומים חדשים</v>
@@ -2302,24 +2698,30 @@
         <v/>
       </c>
       <c r="J71" t="str">
+        <v/>
+      </c>
+      <c r="K71" t="str">
+        <v/>
+      </c>
+      <c r="L71" t="str">
         <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>אברהם טל – חי</v>
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
       </c>
       <c r="B72" t="str">
-        <v>2025-08-17</v>
+        <v>2025-08-21</v>
       </c>
       <c r="C72" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E72" t="str">
-        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
+        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
       </c>
       <c r="F72" t="str">
         <v>אלבומים חדשים</v>
@@ -2334,24 +2736,30 @@
         <v/>
       </c>
       <c r="J72" t="str">
+        <v/>
+      </c>
+      <c r="K72" t="str">
+        <v/>
+      </c>
+      <c r="L72" t="str">
         <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>רנה ראפ Bite Me</v>
+        <v>אברהם טל – חי</v>
       </c>
       <c r="B73" t="str">
-        <v>2025-08-12</v>
+        <v>2025-08-17</v>
       </c>
       <c r="C73" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E73" t="str">
-        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
+        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
       </c>
       <c r="F73" t="str">
         <v>אלבומים חדשים</v>
@@ -2366,24 +2774,30 @@
         <v/>
       </c>
       <c r="J73" t="str">
+        <v/>
+      </c>
+      <c r="K73" t="str">
+        <v/>
+      </c>
+      <c r="L73" t="str">
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>The K's – Pretty On The Internet</v>
+        <v>רנה ראפ Bite Me</v>
       </c>
       <c r="B74" t="str">
-        <v>2025-08-03</v>
+        <v>2025-08-12</v>
       </c>
       <c r="C74" t="str">
-        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
+        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E74" t="str">
-        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
+        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
       </c>
       <c r="F74" t="str">
         <v>אלבומים חדשים</v>
@@ -2398,24 +2812,30 @@
         <v/>
       </c>
       <c r="J74" t="str">
+        <v/>
+      </c>
+      <c r="K74" t="str">
+        <v/>
+      </c>
+      <c r="L74" t="str">
         <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>פליטווד מק Fifty Years – Don’t Stop</v>
+        <v>The K's – Pretty On The Internet</v>
       </c>
       <c r="B75" t="str">
-        <v>2025-07-30</v>
+        <v>2025-08-03</v>
       </c>
       <c r="C75" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%99%d7%98%d7%95%d7%95%d7%93-%d7%9e%d7%a7-fifty-years-dont-stop/</v>
+        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E75" t="str">
-        <v>פליטווד מק (Fleetwood Mac) חוגגים חצי מאה של מוזיקה עם אוסף חדש בן 50 שירים, שמתפרש על כל הקריירה של הלהקה, מימיה הראשונים בסגנון בלוז, ועד להצלחתה העולמית כאחת מלהקות הגדולות בהיסטוריה של הרוק. פליטווד מק הם לא רק להקה</v>
+        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
       </c>
       <c r="F75" t="str">
         <v>אלבומים חדשים</v>
@@ -2430,44 +2850,94 @@
         <v/>
       </c>
       <c r="J75" t="str">
+        <v/>
+      </c>
+      <c r="K75" t="str">
+        <v/>
+      </c>
+      <c r="L75" t="str">
         <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
+        <v>פליטווד מק Fifty Years – Don’t Stop</v>
+      </c>
+      <c r="B76" t="str">
+        <v>2025-07-30</v>
+      </c>
+      <c r="C76" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%99%d7%98%d7%95%d7%95%d7%93-%d7%9e%d7%a7-fifty-years-dont-stop/</v>
+      </c>
+      <c r="D76" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E76" t="str">
+        <v>פליטווד מק (Fleetwood Mac) חוגגים חצי מאה של מוזיקה עם אוסף חדש בן 50 שירים, שמתפרש על כל הקריירה של הלהקה, מימיה הראשונים בסגנון בלוז, ועד להצלחתה העולמית כאחת מלהקות הגדולות בהיסטוריה של הרוק. פליטווד מק הם לא רק להקה</v>
+      </c>
+      <c r="F76" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G76" t="str">
+        <v/>
+      </c>
+      <c r="H76" t="str">
+        <v/>
+      </c>
+      <c r="I76" t="str">
+        <v/>
+      </c>
+      <c r="J76" t="str">
+        <v/>
+      </c>
+      <c r="K76" t="str">
+        <v/>
+      </c>
+      <c r="L76" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
         <v>Wet Leg Moisturizer</v>
       </c>
-      <c r="B76" t="str">
+      <c r="B77" t="str">
         <v>2025-07-25</v>
       </c>
-      <c r="C76" t="str">
+      <c r="C77" t="str">
         <v>https://yosmusic.com/wet-leg-moisturizer/</v>
       </c>
-      <c r="D76" t="str">
-        <v>2026-01-08</v>
-      </c>
-      <c r="E76" t="str">
+      <c r="D77" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E77" t="str">
         <v>להקת Wet Leg לא הוציאה קרם לחות (Moisturizer) כמוצר טיפוח. במקום זאת, "Moisturizer" הוא שמו של האלבום השני והחדש שלהם. במרכז –  צמד אינדי-רוק המורכב מהחברות ריין טיסדייל והסטר צ'יימברס. אלבום הבכורה הנושא את שמה, הגיע למקום הראשון במצעד האלבומים</v>
       </c>
-      <c r="F76" t="str">
-        <v>אלבומים חדשים</v>
-      </c>
-      <c r="G76" t="str">
-        <v/>
-      </c>
-      <c r="H76" t="str">
-        <v/>
-      </c>
-      <c r="I76" t="str">
-        <v/>
-      </c>
-      <c r="J76" t="str">
+      <c r="F77" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G77" t="str">
+        <v/>
+      </c>
+      <c r="H77" t="str">
+        <v/>
+      </c>
+      <c r="I77" t="str">
+        <v/>
+      </c>
+      <c r="J77" t="str">
+        <v/>
+      </c>
+      <c r="K77" t="str">
+        <v/>
+      </c>
+      <c r="L77" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J76"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L77"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L77"/>
+  <dimension ref="A1:N90"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,19 +421,19 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מארינה מקסימיליאן – ריק בחלל</v>
+        <v>|| תומר יוסף - 360 (2026)</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-01-09</v>
+        <v>2026  11:38-01-09</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-09</v>
       </c>
       <c r="E2" t="str">
-        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
+        <v/>
       </c>
       <c r="F2" t="str">
         <v>אלבומים חדשים</v>
@@ -441,331 +441,259 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>|| אייל גולן - בית מפואר ()</v>
+        <v>|| עמיר בניון - לא נוגע בקרקע ()</v>
       </c>
       <c r="B3" t="str">
-        <v>2025  02:18-12-31</v>
+        <v>2025  02:17-12-31</v>
       </c>
       <c r="C3" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
         <v>אלבומים חדשים</v>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>|| הפרויקט של דודי לוי ואבטיפוס - הפטריקים ()</v>
+        <v>|| אברהם טל - חי ()</v>
       </c>
       <c r="B4" t="str">
         <v>2025  02:16-12-31</v>
       </c>
       <c r="C4" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
         <v>אלבומים חדשים</v>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>|| שיר לוי - ילד מוזר ()</v>
+        <v>|| מיקי גבריאלוב - שלום ()</v>
       </c>
       <c r="B5" t="str">
-        <v>2025  02:14-12-31</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C5" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
         <v>אלבומים חדשים</v>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>|| פיטר רוט - 50 ()</v>
+        <v>|| בזכרי ימים ימימה - מחווה לצלילי הכרם ()</v>
       </c>
       <c r="B6" t="str">
-        <v>2025  02:13-12-31</v>
+        <v>2025  02:12-12-31</v>
       </c>
       <c r="C6" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
         <v>אלבומים חדשים</v>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>|| אגם בוחבוט - עשרים ואחת ()</v>
+        <v>|| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון ()</v>
       </c>
       <c r="B7" t="str">
-        <v>2025  02:11-12-31</v>
+        <v>2025  02:10-12-31</v>
       </c>
       <c r="C7" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
         <v>אלבומים חדשים</v>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>|| רבקה זוהר - רסיסים של אור ()</v>
+        <v>|| שלמה גרוניך - תודה אהבה ()</v>
       </c>
       <c r="B8" t="str">
         <v>2025  02:09-12-31</v>
       </c>
       <c r="C8" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
         <v>אלבומים חדשים</v>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>|| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות ()</v>
+        <v>|| חוה אלברשטיין - חמישה שירים ()</v>
       </c>
       <c r="B9" t="str">
-        <v>2025  02:08-12-31</v>
+        <v>2025  02:06-12-31</v>
       </c>
       <c r="C9" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
         <v>אלבומים חדשים</v>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>|| אהוד בנאי ובנו הנדלר - פליטי הדאב ()</v>
+        <v>|| הפרויקט של עידן רייכל - עד סוף העולם ()</v>
       </c>
       <c r="B10" t="str">
         <v>2025  02:05-12-31</v>
       </c>
       <c r="C10" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
         <v>אלבומים חדשים</v>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>|| Imagine פסטיגל - שירי התחרות ()</v>
+        <v>|| סטטיק - קעקועים ()</v>
       </c>
       <c r="B11" t="str">
-        <v>2025  02:04-12-31</v>
+        <v>2025  02:03-12-31</v>
       </c>
       <c r="C11" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
         <v>אלבומים חדשים</v>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>|| השמחות - חובות אבודים ()</v>
+        <v>|| ליאור נרקיס - דיסוננס ()</v>
       </c>
       <c r="B12" t="str">
-        <v>2025  02:02-12-31</v>
+        <v>2025  02:01-12-31</v>
       </c>
       <c r="C12" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
         <v>אלבומים חדשים</v>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>|| שלמה גרוניך - כמו כוכבים ()</v>
+        <v>|| דיוויד ברוזה - BrozaJazz (Paris Alhambra) ()</v>
       </c>
       <c r="B13" t="str">
-        <v>2025  02:00-12-31</v>
+        <v>2025  01:57-12-31</v>
       </c>
       <c r="C13" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
         <v>אלבומים חדשים</v>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>|| יוני רועה - מפוזרים ()</v>
+        <v>|| אתניקס - איטליה ()</v>
       </c>
       <c r="B14" t="str">
-        <v>2025  01:56-12-31</v>
+        <v>2025  01:55-12-31</v>
       </c>
       <c r="C14" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
         <v>אלבומים חדשים</v>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14" t="str">
-        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>|| התקווה 6 - ויהי אור ()</v>
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
       </c>
       <c r="B15" t="str">
-        <v>2025  01:54-12-31</v>
+        <v>2026-01-09</v>
       </c>
       <c r="C15" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E15" t="str">
-        <v/>
+        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
       </c>
       <c r="F15" t="str">
         <v>אלבומים חדשים</v>
@@ -779,13 +707,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>|| שאנן סטריט ודי ג׳יי מש - באתי לבדר ()</v>
+        <v>|| אייל גולן - בית מפואר ()</v>
       </c>
       <c r="B16" t="str">
-        <v>2025  01:53-12-31</v>
+        <v>2025  02:18-12-31</v>
       </c>
       <c r="C16" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-08</v>
@@ -800,18 +728,24 @@
         <v/>
       </c>
       <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
+      <c r="J16" t="str">
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>אשכול נוכחות למשתמשים פעילים</v>
+        <v>|| הפרויקט של דודי לוי ואבטיפוס - הפטריקים ()</v>
       </c>
       <c r="B17" t="str">
-        <v>2025  16:32 מאת freund-10-16</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C17" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=23455&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-08</v>
@@ -837,13 +771,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>כיצד להוריד מהאתרים המפורסמים</v>
+        <v>|| שיר לוי - ילד מוזר ()</v>
       </c>
       <c r="B18" t="str">
-        <v>2023  16:23 מאת petel1-08-08</v>
+        <v>2025  02:14-12-31</v>
       </c>
       <c r="C18" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=22411&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-08</v>
@@ -869,13 +803,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
+        <v>|| פיטר רוט - 50 ()</v>
       </c>
       <c r="B19" t="str">
-        <v>2026  22:40 מאת מוטי_ד-01-01</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C19" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24435&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-08</v>
@@ -901,13 +835,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>|אלבום חדש| אייל גולן - בית מפואר (2025)</v>
+        <v>|| אגם בוחבוט - עשרים ואחת ()</v>
       </c>
       <c r="B20" t="str">
-        <v>2025  02:18 מאת DiSHi-12-31</v>
+        <v>2025  02:11-12-31</v>
       </c>
       <c r="C20" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-08</v>
@@ -933,13 +867,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע (2025)</v>
+        <v>|| רבקה זוהר - רסיסים של אור ()</v>
       </c>
       <c r="B21" t="str">
-        <v>2025  02:17 מאת DiSHi-12-31</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C21" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-08</v>
@@ -965,13 +899,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>|אלבום חדש| הפרויקט של דודי לוי ואבטיפוס - הפטריקים (2025)</v>
+        <v>|| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות ()</v>
       </c>
       <c r="B22" t="str">
-        <v>2025  02:16 מאת DiSHi-12-31</v>
+        <v>2025  02:08-12-31</v>
       </c>
       <c r="C22" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-08</v>
@@ -997,13 +931,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>|אלבום חדש| אברהם טל - חי (2025)</v>
+        <v>|| אהוד בנאי ובנו הנדלר - פליטי הדאב ()</v>
       </c>
       <c r="B23" t="str">
-        <v>2025  02:16 מאת DiSHi-12-31</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C23" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-08</v>
@@ -1029,13 +963,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>|אלבום חדש| שיר לוי - ילד מוזר (2025)</v>
+        <v>|| Imagine פסטיגל - שירי התחרות ()</v>
       </c>
       <c r="B24" t="str">
-        <v>2025  02:14 מאת DiSHi-12-31</v>
+        <v>2025  02:04-12-31</v>
       </c>
       <c r="C24" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-08</v>
@@ -1061,13 +995,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>|אלבום חדש| מיקי גבריאלוב - שלום (2025)</v>
+        <v>|| השמחות - חובות אבודים ()</v>
       </c>
       <c r="B25" t="str">
-        <v>2025  02:13 מאת DiSHi-12-31</v>
+        <v>2025  02:02-12-31</v>
       </c>
       <c r="C25" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-08</v>
@@ -1093,13 +1027,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>|אלבום חדש| פיטר רוט - 50 (2025)</v>
+        <v>|| שלמה גרוניך - כמו כוכבים ()</v>
       </c>
       <c r="B26" t="str">
-        <v>2025  02:13 מאת DiSHi-12-31</v>
+        <v>2025  02:00-12-31</v>
       </c>
       <c r="C26" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-08</v>
@@ -1125,13 +1059,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם (2025)</v>
+        <v>|| יוני רועה - מפוזרים ()</v>
       </c>
       <c r="B27" t="str">
-        <v>2025  02:12 מאת DiSHi-12-31</v>
+        <v>2025  01:56-12-31</v>
       </c>
       <c r="C27" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-08</v>
@@ -1157,13 +1091,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>|אלבום חדש| אגם בוחבוט - עשרים ואחת (2025)</v>
+        <v>|| התקווה 6 - ויהי אור ()</v>
       </c>
       <c r="B28" t="str">
-        <v>2025  02:11 מאת DiSHi-12-31</v>
+        <v>2025  01:54-12-31</v>
       </c>
       <c r="C28" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-08</v>
@@ -1189,13 +1123,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון (2025)</v>
+        <v>|| שאנן סטריט ודי ג׳יי מש - באתי לבדר ()</v>
       </c>
       <c r="B29" t="str">
-        <v>2025  02:10 מאת DiSHi-12-31</v>
+        <v>2025  01:53-12-31</v>
       </c>
       <c r="C29" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-08</v>
@@ -1221,13 +1155,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>|אלבום חדש| רבקה זוהר - רסיסים של אור (2025)</v>
+        <v>אשכול נוכחות למשתמשים פעילים</v>
       </c>
       <c r="B30" t="str">
-        <v>2025  02:09 מאת DiSHi-12-31</v>
+        <v>2025  16:32 מאת freund-10-16</v>
       </c>
       <c r="C30" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=23455&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-08</v>
@@ -1248,18 +1182,24 @@
         <v/>
       </c>
       <c r="J30" t="str">
+        <v/>
+      </c>
+      <c r="K30" t="str">
+        <v/>
+      </c>
+      <c r="L30" t="str">
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה (2025)</v>
+        <v>כיצד להוריד מהאתרים המפורסמים</v>
       </c>
       <c r="B31" t="str">
-        <v>2025  02:09 מאת DiSHi-12-31</v>
+        <v>2023  16:23 מאת petel1-08-08</v>
       </c>
       <c r="C31" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=22411&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-08</v>
@@ -1280,18 +1220,24 @@
         <v/>
       </c>
       <c r="J31" t="str">
+        <v/>
+      </c>
+      <c r="K31" t="str">
+        <v/>
+      </c>
+      <c r="L31" t="str">
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>|אלבום חדש| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות (2025)</v>
+        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
       </c>
       <c r="B32" t="str">
-        <v>2025  02:08 מאת DiSHi-12-31</v>
+        <v>2026  22:40 מאת מוטי_ד-01-01</v>
       </c>
       <c r="C32" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24435&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-08</v>
@@ -1312,18 +1258,24 @@
         <v/>
       </c>
       <c r="J32" t="str">
+        <v/>
+      </c>
+      <c r="K32" t="str">
+        <v/>
+      </c>
+      <c r="L32" t="str">
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים (2025)</v>
+        <v>|אלבום חדש| אייל גולן - בית מפואר (2025)</v>
       </c>
       <c r="B33" t="str">
-        <v>2025  02:06 מאת DiSHi-12-31</v>
+        <v>2025  02:18 מאת DiSHi-12-31</v>
       </c>
       <c r="C33" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-08</v>
@@ -1344,18 +1296,24 @@
         <v/>
       </c>
       <c r="J33" t="str">
+        <v/>
+      </c>
+      <c r="K33" t="str">
+        <v/>
+      </c>
+      <c r="L33" t="str">
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>|אלבום חדש| אהוד בנאי ובנו הנדלר - פליטי הדאב (2025)</v>
+        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע (2025)</v>
       </c>
       <c r="B34" t="str">
-        <v>2025  02:05 מאת DiSHi-12-31</v>
+        <v>2025  02:17 מאת DiSHi-12-31</v>
       </c>
       <c r="C34" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-08</v>
@@ -1376,18 +1334,24 @@
         <v/>
       </c>
       <c r="J34" t="str">
+        <v/>
+      </c>
+      <c r="K34" t="str">
+        <v/>
+      </c>
+      <c r="L34" t="str">
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם (2025)</v>
+        <v>|אלבום חדש| הפרויקט של דודי לוי ואבטיפוס - הפטריקים (2025)</v>
       </c>
       <c r="B35" t="str">
-        <v>2025  02:05 מאת DiSHi-12-31</v>
+        <v>2025  02:16 מאת DiSHi-12-31</v>
       </c>
       <c r="C35" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-08</v>
@@ -1408,18 +1372,24 @@
         <v/>
       </c>
       <c r="J35" t="str">
+        <v/>
+      </c>
+      <c r="K35" t="str">
+        <v/>
+      </c>
+      <c r="L35" t="str">
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>|אלבום חדש| Imagine פסטיגל - שירי התחרות (2025)</v>
+        <v>|אלבום חדש| אברהם טל - חי (2025)</v>
       </c>
       <c r="B36" t="str">
-        <v>2025  02:04 מאת DiSHi-12-31</v>
+        <v>2025  02:16 מאת DiSHi-12-31</v>
       </c>
       <c r="C36" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-08</v>
@@ -1440,18 +1410,24 @@
         <v/>
       </c>
       <c r="J36" t="str">
+        <v/>
+      </c>
+      <c r="K36" t="str">
+        <v/>
+      </c>
+      <c r="L36" t="str">
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>|אלבום חדש| סטטיק - קעקועים (2025)</v>
+        <v>|אלבום חדש| שיר לוי - ילד מוזר (2025)</v>
       </c>
       <c r="B37" t="str">
-        <v>2025  02:03 מאת DiSHi-12-31</v>
+        <v>2025  02:14 מאת DiSHi-12-31</v>
       </c>
       <c r="C37" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-08</v>
@@ -1472,18 +1448,24 @@
         <v/>
       </c>
       <c r="J37" t="str">
+        <v/>
+      </c>
+      <c r="K37" t="str">
+        <v/>
+      </c>
+      <c r="L37" t="str">
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>|אלבום חדש| השמחות - חובות אבודים (2025)</v>
+        <v>|אלבום חדש| מיקי גבריאלוב - שלום (2025)</v>
       </c>
       <c r="B38" t="str">
-        <v>2025  02:02 מאת DiSHi-12-31</v>
+        <v>2025  02:13 מאת DiSHi-12-31</v>
       </c>
       <c r="C38" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-08</v>
@@ -1504,18 +1486,24 @@
         <v/>
       </c>
       <c r="J38" t="str">
+        <v/>
+      </c>
+      <c r="K38" t="str">
+        <v/>
+      </c>
+      <c r="L38" t="str">
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>|אלבום חדש| ליאור נרקיס - דיסוננס (2025)</v>
+        <v>|אלבום חדש| פיטר רוט - 50 (2025)</v>
       </c>
       <c r="B39" t="str">
-        <v>2025  02:01 מאת DiSHi-12-31</v>
+        <v>2025  02:13 מאת DiSHi-12-31</v>
       </c>
       <c r="C39" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-08</v>
@@ -1536,18 +1524,24 @@
         <v/>
       </c>
       <c r="J39" t="str">
+        <v/>
+      </c>
+      <c r="K39" t="str">
+        <v/>
+      </c>
+      <c r="L39" t="str">
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>|אלבום חדש| שלמה גרוניך - כמו כוכבים (2025)</v>
+        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם (2025)</v>
       </c>
       <c r="B40" t="str">
-        <v>2025  02:00 מאת DiSHi-12-31</v>
+        <v>2025  02:12 מאת DiSHi-12-31</v>
       </c>
       <c r="C40" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-08</v>
@@ -1568,18 +1562,24 @@
         <v/>
       </c>
       <c r="J40" t="str">
+        <v/>
+      </c>
+      <c r="K40" t="str">
+        <v/>
+      </c>
+      <c r="L40" t="str">
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) (2025)</v>
+        <v>|אלבום חדש| אגם בוחבוט - עשרים ואחת (2025)</v>
       </c>
       <c r="B41" t="str">
-        <v>2025  01:57 מאת DiSHi-12-31</v>
+        <v>2025  02:11 מאת DiSHi-12-31</v>
       </c>
       <c r="C41" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-08</v>
@@ -1600,18 +1600,24 @@
         <v/>
       </c>
       <c r="J41" t="str">
+        <v/>
+      </c>
+      <c r="K41" t="str">
+        <v/>
+      </c>
+      <c r="L41" t="str">
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>|אלבום חדש| יוני רועה - מפוזרים (2025)</v>
+        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון (2025)</v>
       </c>
       <c r="B42" t="str">
-        <v>2025  01:56 מאת DiSHi-12-31</v>
+        <v>2025  02:10 מאת DiSHi-12-31</v>
       </c>
       <c r="C42" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-08</v>
@@ -1632,18 +1638,24 @@
         <v/>
       </c>
       <c r="J42" t="str">
+        <v/>
+      </c>
+      <c r="K42" t="str">
+        <v/>
+      </c>
+      <c r="L42" t="str">
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>|אלבום חדש| אתניקס - איטליה (2025)</v>
+        <v>|אלבום חדש| רבקה זוהר - רסיסים של אור (2025)</v>
       </c>
       <c r="B43" t="str">
-        <v>2025  01:55 מאת DiSHi-12-31</v>
+        <v>2025  02:09 מאת DiSHi-12-31</v>
       </c>
       <c r="C43" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-08</v>
@@ -1664,18 +1676,24 @@
         <v/>
       </c>
       <c r="J43" t="str">
+        <v/>
+      </c>
+      <c r="K43" t="str">
+        <v/>
+      </c>
+      <c r="L43" t="str">
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>|אלבום חדש| התקווה 6 - ויהי אור (2025)</v>
+        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה (2025)</v>
       </c>
       <c r="B44" t="str">
-        <v>2025  01:54 מאת DiSHi-12-31</v>
+        <v>2025  02:09 מאת DiSHi-12-31</v>
       </c>
       <c r="C44" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-08</v>
@@ -1696,18 +1714,24 @@
         <v/>
       </c>
       <c r="J44" t="str">
+        <v/>
+      </c>
+      <c r="K44" t="str">
+        <v/>
+      </c>
+      <c r="L44" t="str">
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>|אלבום חדש| שלומי סרנגה - איפרכו (2025)</v>
+        <v>|אלבום חדש| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות (2025)</v>
       </c>
       <c r="B45" t="str">
-        <v>2025  01:53 מאת DiSHi-12-31</v>
+        <v>2025  02:08 מאת DiSHi-12-31</v>
       </c>
       <c r="C45" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24430&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-08</v>
@@ -1728,18 +1752,24 @@
         <v/>
       </c>
       <c r="J45" t="str">
+        <v/>
+      </c>
+      <c r="K45" t="str">
+        <v/>
+      </c>
+      <c r="L45" t="str">
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>|אלבום חדש| שאנן סטריט ודי ג׳יי מש - באתי לבדר (2025)</v>
+        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים (2025)</v>
       </c>
       <c r="B46" t="str">
-        <v>2025  01:53 מאת DiSHi-12-31</v>
+        <v>2025  02:06 מאת DiSHi-12-31</v>
       </c>
       <c r="C46" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-08</v>
@@ -1760,18 +1790,24 @@
         <v/>
       </c>
       <c r="J46" t="str">
+        <v/>
+      </c>
+      <c r="K46" t="str">
+        <v/>
+      </c>
+      <c r="L46" t="str">
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>הרשם לחברות מלאה</v>
+        <v>|אלבום חדש| אהוד בנאי ובנו הנדלר - פליטי הדאב (2025)</v>
       </c>
       <c r="B47" t="str">
-        <v/>
+        <v>2025  02:05 מאת DiSHi-12-31</v>
       </c>
       <c r="C47" t="str">
-        <v>https://rotter.name/nor/members-new.html</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-08</v>
@@ -1792,24 +1828,30 @@
         <v/>
       </c>
       <c r="J47" t="str">
+        <v/>
+      </c>
+      <c r="K47" t="str">
+        <v/>
+      </c>
+      <c r="L47" t="str">
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>אוליביה דין The Art of Loving</v>
+        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם (2025)</v>
       </c>
       <c r="B48" t="str">
-        <v>2026-01-04</v>
+        <v>2025  02:05 מאת DiSHi-12-31</v>
       </c>
       <c r="C48" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E48" t="str">
-        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
+        <v/>
       </c>
       <c r="F48" t="str">
         <v>אלבומים חדשים</v>
@@ -1835,19 +1877,19 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Geese Getting Killed</v>
+        <v>|אלבום חדש| Imagine פסטיגל - שירי התחרות (2025)</v>
       </c>
       <c r="B49" t="str">
-        <v>2025-12-29</v>
+        <v>2025  02:04 מאת DiSHi-12-31</v>
       </c>
       <c r="C49" t="str">
-        <v>https://yosmusic.com/geese-getting-killed/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E49" t="str">
-        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
+        <v/>
       </c>
       <c r="F49" t="str">
         <v>אלבומים חדשים</v>
@@ -1873,19 +1915,19 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>רוסליה Lux</v>
+        <v>|אלבום חדש| סטטיק - קעקועים (2025)</v>
       </c>
       <c r="B50" t="str">
-        <v>2025-12-25</v>
+        <v>2025  02:03 מאת DiSHi-12-31</v>
       </c>
       <c r="C50" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E50" t="str">
-        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
+        <v/>
       </c>
       <c r="F50" t="str">
         <v>אלבומים חדשים</v>
@@ -1911,19 +1953,19 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>יאנגבלאד אירוסמית' one more time</v>
+        <v>|אלבום חדש| השמחות - חובות אבודים (2025)</v>
       </c>
       <c r="B51" t="str">
-        <v>2025-12-17</v>
+        <v>2025  02:02 מאת DiSHi-12-31</v>
       </c>
       <c r="C51" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E51" t="str">
-        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
+        <v/>
       </c>
       <c r="F51" t="str">
         <v>אלבומים חדשים</v>
@@ -1949,19 +1991,19 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>פינק פלויד Wish You Were Here 50</v>
+        <v>|אלבום חדש| ליאור נרקיס - דיסוננס (2025)</v>
       </c>
       <c r="B52" t="str">
-        <v>2025-12-14</v>
+        <v>2025  02:01 מאת DiSHi-12-31</v>
       </c>
       <c r="C52" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E52" t="str">
-        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
+        <v/>
       </c>
       <c r="F52" t="str">
         <v>אלבומים חדשים</v>
@@ -1987,19 +2029,19 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+        <v>|אלבום חדש| שלמה גרוניך - כמו כוכבים (2025)</v>
       </c>
       <c r="B53" t="str">
-        <v>2025-12-08</v>
+        <v>2025  02:00 מאת DiSHi-12-31</v>
       </c>
       <c r="C53" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E53" t="str">
-        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
+        <v/>
       </c>
       <c r="F53" t="str">
         <v>אלבומים חדשים</v>
@@ -2025,19 +2067,19 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>סטריי קידס DO IT (EP)</v>
+        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) (2025)</v>
       </c>
       <c r="B54" t="str">
-        <v>2025-12-04</v>
+        <v>2025  01:57 מאת DiSHi-12-31</v>
       </c>
       <c r="C54" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E54" t="str">
-        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
+        <v/>
       </c>
       <c r="F54" t="str">
         <v>אלבומים חדשים</v>
@@ -2063,19 +2105,19 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>דויד ברוזה BROZAJAZZ</v>
+        <v>|אלבום חדש| יוני רועה - מפוזרים (2025)</v>
       </c>
       <c r="B55" t="str">
-        <v>2025-11-30</v>
+        <v>2025  01:56 מאת DiSHi-12-31</v>
       </c>
       <c r="C55" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E55" t="str">
-        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
+        <v/>
       </c>
       <c r="F55" t="str">
         <v>אלבומים חדשים</v>
@@ -2101,19 +2143,19 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Five Seconds of Summer – Everyone's A Star</v>
+        <v>|אלבום חדש| אתניקס - איטליה (2025)</v>
       </c>
       <c r="B56" t="str">
-        <v>2025-11-24</v>
+        <v>2025  01:55 מאת DiSHi-12-31</v>
       </c>
       <c r="C56" t="str">
-        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E56" t="str">
-        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
+        <v/>
       </c>
       <c r="F56" t="str">
         <v>אלבומים חדשים</v>
@@ -2139,19 +2181,19 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>התקווה 6 – ויהי אור</v>
+        <v>|אלבום חדש| התקווה 6 - ויהי אור (2025)</v>
       </c>
       <c r="B57" t="str">
-        <v>2025-11-20</v>
+        <v>2025  01:54 מאת DiSHi-12-31</v>
       </c>
       <c r="C57" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E57" t="str">
-        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
+        <v/>
       </c>
       <c r="F57" t="str">
         <v>אלבומים חדשים</v>
@@ -2177,19 +2219,19 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>פלורנס אנד דה משין Everybody Scream</v>
+        <v>|אלבום חדש| שלומי סרנגה - איפרכו (2025)</v>
       </c>
       <c r="B58" t="str">
-        <v>2025-11-13</v>
+        <v>2025  01:53 מאת DiSHi-12-31</v>
       </c>
       <c r="C58" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24430&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E58" t="str">
-        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
+        <v/>
       </c>
       <c r="F58" t="str">
         <v>אלבומים חדשים</v>
@@ -2215,19 +2257,19 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>טיים אימפלה Deadbeat</v>
+        <v>|אלבום חדש| שאנן סטריט ודי ג׳יי מש - באתי לבדר (2025)</v>
       </c>
       <c r="B59" t="str">
-        <v>2025-11-03</v>
+        <v>2025  01:53 מאת DiSHi-12-31</v>
       </c>
       <c r="C59" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E59" t="str">
-        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
+        <v/>
       </c>
       <c r="F59" t="str">
         <v>אלבומים חדשים</v>
@@ -2253,19 +2295,19 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+        <v>הרשם לחברות מלאה</v>
       </c>
       <c r="B60" t="str">
-        <v>2025-10-20</v>
+        <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
+        <v>https://rotter.name/nor/members-new.html</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E60" t="str">
-        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
+        <v/>
       </c>
       <c r="F60" t="str">
         <v>אלבומים חדשים</v>
@@ -2291,19 +2333,19 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>שלמה גרוניך – תודה אהבה</v>
+        <v>אוליביה דין The Art of Loving</v>
       </c>
       <c r="B61" t="str">
-        <v>2025-10-18</v>
+        <v>2026-01-04</v>
       </c>
       <c r="C61" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E61" t="str">
-        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
+        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
       </c>
       <c r="F61" t="str">
         <v>אלבומים חדשים</v>
@@ -2324,24 +2366,30 @@
         <v/>
       </c>
       <c r="L61" t="str">
+        <v/>
+      </c>
+      <c r="M61" t="str">
+        <v/>
+      </c>
+      <c r="N61" t="str">
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>טיילור סוויפט The Life Of A Showgirl</v>
+        <v>Geese Getting Killed</v>
       </c>
       <c r="B62" t="str">
-        <v>2025-10-11</v>
+        <v>2025-12-29</v>
       </c>
       <c r="C62" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
+        <v>https://yosmusic.com/geese-getting-killed/</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E62" t="str">
-        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
+        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
       </c>
       <c r="F62" t="str">
         <v>אלבומים חדשים</v>
@@ -2362,24 +2410,30 @@
         <v/>
       </c>
       <c r="L62" t="str">
+        <v/>
+      </c>
+      <c r="M62" t="str">
+        <v/>
+      </c>
+      <c r="N62" t="str">
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>דוג'ה קאט Vie</v>
+        <v>רוסליה Lux</v>
       </c>
       <c r="B63" t="str">
-        <v>2025-10-04</v>
+        <v>2025-12-25</v>
       </c>
       <c r="C63" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E63" t="str">
-        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
+        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
       </c>
       <c r="F63" t="str">
         <v>אלבומים חדשים</v>
@@ -2400,24 +2454,30 @@
         <v/>
       </c>
       <c r="L63" t="str">
+        <v/>
+      </c>
+      <c r="M63" t="str">
+        <v/>
+      </c>
+      <c r="N63" t="str">
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>ג'וי קרוקס Juniper</v>
+        <v>יאנגבלאד אירוסמית' one more time</v>
       </c>
       <c r="B64" t="str">
-        <v>2025-10-03</v>
+        <v>2025-12-17</v>
       </c>
       <c r="C64" t="str">
-        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
+        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E64" t="str">
-        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
+        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
       </c>
       <c r="F64" t="str">
         <v>אלבומים חדשים</v>
@@ -2438,24 +2498,30 @@
         <v/>
       </c>
       <c r="L64" t="str">
+        <v/>
+      </c>
+      <c r="M64" t="str">
+        <v/>
+      </c>
+      <c r="N64" t="str">
         <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>ביפי קליירו Futique</v>
+        <v>פינק פלויד Wish You Were Here 50</v>
       </c>
       <c r="B65" t="str">
-        <v>2025-09-30</v>
+        <v>2025-12-14</v>
       </c>
       <c r="C65" t="str">
-        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E65" t="str">
-        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
+        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
       </c>
       <c r="F65" t="str">
         <v>אלבומים חדשים</v>
@@ -2476,24 +2542,30 @@
         <v/>
       </c>
       <c r="L65" t="str">
+        <v/>
+      </c>
+      <c r="M65" t="str">
+        <v/>
+      </c>
+      <c r="N65" t="str">
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>אד שירן Play</v>
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
       </c>
       <c r="B66" t="str">
-        <v>2025-09-24</v>
+        <v>2025-12-08</v>
       </c>
       <c r="C66" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
+        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E66" t="str">
-        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
+        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
       </c>
       <c r="F66" t="str">
         <v>אלבומים חדשים</v>
@@ -2514,24 +2586,30 @@
         <v/>
       </c>
       <c r="L66" t="str">
+        <v/>
+      </c>
+      <c r="M66" t="str">
+        <v/>
+      </c>
+      <c r="N66" t="str">
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+        <v>סטריי קידס DO IT (EP)</v>
       </c>
       <c r="B67" t="str">
-        <v>2025-09-21</v>
+        <v>2025-12-04</v>
       </c>
       <c r="C67" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
+        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E67" t="str">
-        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
+        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
       </c>
       <c r="F67" t="str">
         <v>אלבומים חדשים</v>
@@ -2552,24 +2630,30 @@
         <v/>
       </c>
       <c r="L67" t="str">
+        <v/>
+      </c>
+      <c r="M67" t="str">
+        <v/>
+      </c>
+      <c r="N67" t="str">
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>סוויד Antidepressants</v>
+        <v>דויד ברוזה BROZAJAZZ</v>
       </c>
       <c r="B68" t="str">
-        <v>2025-09-12</v>
+        <v>2025-11-30</v>
       </c>
       <c r="C68" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E68" t="str">
-        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
+        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
       </c>
       <c r="F68" t="str">
         <v>אלבומים חדשים</v>
@@ -2590,24 +2674,30 @@
         <v/>
       </c>
       <c r="L68" t="str">
+        <v/>
+      </c>
+      <c r="M68" t="str">
+        <v/>
+      </c>
+      <c r="N68" t="str">
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>וולף אליס The Clearing</v>
+        <v>Five Seconds of Summer – Everyone's A Star</v>
       </c>
       <c r="B69" t="str">
-        <v>2025-09-01</v>
+        <v>2025-11-24</v>
       </c>
       <c r="C69" t="str">
-        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
+        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E69" t="str">
-        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
+        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
       </c>
       <c r="F69" t="str">
         <v>אלבומים חדשים</v>
@@ -2628,24 +2718,30 @@
         <v/>
       </c>
       <c r="L69" t="str">
+        <v/>
+      </c>
+      <c r="M69" t="str">
+        <v/>
+      </c>
+      <c r="N69" t="str">
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+        <v>התקווה 6 – ויהי אור</v>
       </c>
       <c r="B70" t="str">
-        <v>2025-08-29</v>
+        <v>2025-11-20</v>
       </c>
       <c r="C70" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
+        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E70" t="str">
-        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
+        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
       </c>
       <c r="F70" t="str">
         <v>אלבומים חדשים</v>
@@ -2666,24 +2762,30 @@
         <v/>
       </c>
       <c r="L70" t="str">
+        <v/>
+      </c>
+      <c r="M70" t="str">
+        <v/>
+      </c>
+      <c r="N70" t="str">
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+        <v>פלורנס אנד דה משין Everybody Scream</v>
       </c>
       <c r="B71" t="str">
-        <v>2025-08-24</v>
+        <v>2025-11-13</v>
       </c>
       <c r="C71" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E71" t="str">
-        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
+        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
       </c>
       <c r="F71" t="str">
         <v>אלבומים חדשים</v>
@@ -2704,24 +2806,30 @@
         <v/>
       </c>
       <c r="L71" t="str">
+        <v/>
+      </c>
+      <c r="M71" t="str">
+        <v/>
+      </c>
+      <c r="N71" t="str">
         <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+        <v>טיים אימפלה Deadbeat</v>
       </c>
       <c r="B72" t="str">
-        <v>2025-08-21</v>
+        <v>2025-11-03</v>
       </c>
       <c r="C72" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E72" t="str">
-        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
+        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
       </c>
       <c r="F72" t="str">
         <v>אלבומים חדשים</v>
@@ -2742,24 +2850,30 @@
         <v/>
       </c>
       <c r="L72" t="str">
+        <v/>
+      </c>
+      <c r="M72" t="str">
+        <v/>
+      </c>
+      <c r="N72" t="str">
         <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>אברהם טל – חי</v>
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
       </c>
       <c r="B73" t="str">
-        <v>2025-08-17</v>
+        <v>2025-10-20</v>
       </c>
       <c r="C73" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
+        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E73" t="str">
-        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
+        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
       </c>
       <c r="F73" t="str">
         <v>אלבומים חדשים</v>
@@ -2780,24 +2894,30 @@
         <v/>
       </c>
       <c r="L73" t="str">
+        <v/>
+      </c>
+      <c r="M73" t="str">
+        <v/>
+      </c>
+      <c r="N73" t="str">
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>רנה ראפ Bite Me</v>
+        <v>שלמה גרוניך – תודה אהבה</v>
       </c>
       <c r="B74" t="str">
-        <v>2025-08-12</v>
+        <v>2025-10-18</v>
       </c>
       <c r="C74" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E74" t="str">
-        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
+        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
       </c>
       <c r="F74" t="str">
         <v>אלבומים חדשים</v>
@@ -2818,24 +2938,30 @@
         <v/>
       </c>
       <c r="L74" t="str">
+        <v/>
+      </c>
+      <c r="M74" t="str">
+        <v/>
+      </c>
+      <c r="N74" t="str">
         <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>The K's – Pretty On The Internet</v>
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
       </c>
       <c r="B75" t="str">
-        <v>2025-08-03</v>
+        <v>2025-10-11</v>
       </c>
       <c r="C75" t="str">
-        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E75" t="str">
-        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
+        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
       </c>
       <c r="F75" t="str">
         <v>אלבומים חדשים</v>
@@ -2856,24 +2982,30 @@
         <v/>
       </c>
       <c r="L75" t="str">
+        <v/>
+      </c>
+      <c r="M75" t="str">
+        <v/>
+      </c>
+      <c r="N75" t="str">
         <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>פליטווד מק Fifty Years – Don’t Stop</v>
+        <v>דוג'ה קאט Vie</v>
       </c>
       <c r="B76" t="str">
-        <v>2025-07-30</v>
+        <v>2025-10-04</v>
       </c>
       <c r="C76" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%99%d7%98%d7%95%d7%95%d7%93-%d7%9e%d7%a7-fifty-years-dont-stop/</v>
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E76" t="str">
-        <v>פליטווד מק (Fleetwood Mac) חוגגים חצי מאה של מוזיקה עם אוסף חדש בן 50 שירים, שמתפרש על כל הקריירה של הלהקה, מימיה הראשונים בסגנון בלוז, ועד להצלחתה העולמית כאחת מלהקות הגדולות בהיסטוריה של הרוק. פליטווד מק הם לא רק להקה</v>
+        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
       </c>
       <c r="F76" t="str">
         <v>אלבומים חדשים</v>
@@ -2894,50 +3026,634 @@
         <v/>
       </c>
       <c r="L76" t="str">
+        <v/>
+      </c>
+      <c r="M76" t="str">
+        <v/>
+      </c>
+      <c r="N76" t="str">
         <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
+        <v>ג'וי קרוקס Juniper</v>
+      </c>
+      <c r="B77" t="str">
+        <v>2025-10-03</v>
+      </c>
+      <c r="C77" t="str">
+        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
+      </c>
+      <c r="D77" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E77" t="str">
+        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
+      </c>
+      <c r="F77" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G77" t="str">
+        <v/>
+      </c>
+      <c r="H77" t="str">
+        <v/>
+      </c>
+      <c r="I77" t="str">
+        <v/>
+      </c>
+      <c r="J77" t="str">
+        <v/>
+      </c>
+      <c r="K77" t="str">
+        <v/>
+      </c>
+      <c r="L77" t="str">
+        <v/>
+      </c>
+      <c r="M77" t="str">
+        <v/>
+      </c>
+      <c r="N77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>ביפי קליירו Futique</v>
+      </c>
+      <c r="B78" t="str">
+        <v>2025-09-30</v>
+      </c>
+      <c r="C78" t="str">
+        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
+      </c>
+      <c r="D78" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E78" t="str">
+        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
+      </c>
+      <c r="F78" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G78" t="str">
+        <v/>
+      </c>
+      <c r="H78" t="str">
+        <v/>
+      </c>
+      <c r="I78" t="str">
+        <v/>
+      </c>
+      <c r="J78" t="str">
+        <v/>
+      </c>
+      <c r="K78" t="str">
+        <v/>
+      </c>
+      <c r="L78" t="str">
+        <v/>
+      </c>
+      <c r="M78" t="str">
+        <v/>
+      </c>
+      <c r="N78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>אד שירן Play</v>
+      </c>
+      <c r="B79" t="str">
+        <v>2025-09-24</v>
+      </c>
+      <c r="C79" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
+      </c>
+      <c r="D79" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E79" t="str">
+        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
+      </c>
+      <c r="F79" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G79" t="str">
+        <v/>
+      </c>
+      <c r="H79" t="str">
+        <v/>
+      </c>
+      <c r="I79" t="str">
+        <v/>
+      </c>
+      <c r="J79" t="str">
+        <v/>
+      </c>
+      <c r="K79" t="str">
+        <v/>
+      </c>
+      <c r="L79" t="str">
+        <v/>
+      </c>
+      <c r="M79" t="str">
+        <v/>
+      </c>
+      <c r="N79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+      </c>
+      <c r="B80" t="str">
+        <v>2025-09-21</v>
+      </c>
+      <c r="C80" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
+      </c>
+      <c r="D80" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E80" t="str">
+        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
+      </c>
+      <c r="F80" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G80" t="str">
+        <v/>
+      </c>
+      <c r="H80" t="str">
+        <v/>
+      </c>
+      <c r="I80" t="str">
+        <v/>
+      </c>
+      <c r="J80" t="str">
+        <v/>
+      </c>
+      <c r="K80" t="str">
+        <v/>
+      </c>
+      <c r="L80" t="str">
+        <v/>
+      </c>
+      <c r="M80" t="str">
+        <v/>
+      </c>
+      <c r="N80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>סוויד Antidepressants</v>
+      </c>
+      <c r="B81" t="str">
+        <v>2025-09-12</v>
+      </c>
+      <c r="C81" t="str">
+        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
+      </c>
+      <c r="D81" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E81" t="str">
+        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
+      </c>
+      <c r="F81" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G81" t="str">
+        <v/>
+      </c>
+      <c r="H81" t="str">
+        <v/>
+      </c>
+      <c r="I81" t="str">
+        <v/>
+      </c>
+      <c r="J81" t="str">
+        <v/>
+      </c>
+      <c r="K81" t="str">
+        <v/>
+      </c>
+      <c r="L81" t="str">
+        <v/>
+      </c>
+      <c r="M81" t="str">
+        <v/>
+      </c>
+      <c r="N81" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>וולף אליס The Clearing</v>
+      </c>
+      <c r="B82" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="C82" t="str">
+        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
+      </c>
+      <c r="D82" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E82" t="str">
+        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
+      </c>
+      <c r="F82" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G82" t="str">
+        <v/>
+      </c>
+      <c r="H82" t="str">
+        <v/>
+      </c>
+      <c r="I82" t="str">
+        <v/>
+      </c>
+      <c r="J82" t="str">
+        <v/>
+      </c>
+      <c r="K82" t="str">
+        <v/>
+      </c>
+      <c r="L82" t="str">
+        <v/>
+      </c>
+      <c r="M82" t="str">
+        <v/>
+      </c>
+      <c r="N82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+      </c>
+      <c r="B83" t="str">
+        <v>2025-08-29</v>
+      </c>
+      <c r="C83" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
+      </c>
+      <c r="D83" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E83" t="str">
+        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
+      </c>
+      <c r="F83" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G83" t="str">
+        <v/>
+      </c>
+      <c r="H83" t="str">
+        <v/>
+      </c>
+      <c r="I83" t="str">
+        <v/>
+      </c>
+      <c r="J83" t="str">
+        <v/>
+      </c>
+      <c r="K83" t="str">
+        <v/>
+      </c>
+      <c r="L83" t="str">
+        <v/>
+      </c>
+      <c r="M83" t="str">
+        <v/>
+      </c>
+      <c r="N83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+      </c>
+      <c r="B84" t="str">
+        <v>2025-08-24</v>
+      </c>
+      <c r="C84" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
+      </c>
+      <c r="D84" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E84" t="str">
+        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
+      </c>
+      <c r="F84" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G84" t="str">
+        <v/>
+      </c>
+      <c r="H84" t="str">
+        <v/>
+      </c>
+      <c r="I84" t="str">
+        <v/>
+      </c>
+      <c r="J84" t="str">
+        <v/>
+      </c>
+      <c r="K84" t="str">
+        <v/>
+      </c>
+      <c r="L84" t="str">
+        <v/>
+      </c>
+      <c r="M84" t="str">
+        <v/>
+      </c>
+      <c r="N84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+      </c>
+      <c r="B85" t="str">
+        <v>2025-08-21</v>
+      </c>
+      <c r="C85" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
+      </c>
+      <c r="D85" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E85" t="str">
+        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
+      </c>
+      <c r="F85" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G85" t="str">
+        <v/>
+      </c>
+      <c r="H85" t="str">
+        <v/>
+      </c>
+      <c r="I85" t="str">
+        <v/>
+      </c>
+      <c r="J85" t="str">
+        <v/>
+      </c>
+      <c r="K85" t="str">
+        <v/>
+      </c>
+      <c r="L85" t="str">
+        <v/>
+      </c>
+      <c r="M85" t="str">
+        <v/>
+      </c>
+      <c r="N85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>אברהם טל – חי</v>
+      </c>
+      <c r="B86" t="str">
+        <v>2025-08-17</v>
+      </c>
+      <c r="C86" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
+      </c>
+      <c r="D86" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E86" t="str">
+        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
+      </c>
+      <c r="F86" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G86" t="str">
+        <v/>
+      </c>
+      <c r="H86" t="str">
+        <v/>
+      </c>
+      <c r="I86" t="str">
+        <v/>
+      </c>
+      <c r="J86" t="str">
+        <v/>
+      </c>
+      <c r="K86" t="str">
+        <v/>
+      </c>
+      <c r="L86" t="str">
+        <v/>
+      </c>
+      <c r="M86" t="str">
+        <v/>
+      </c>
+      <c r="N86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>רנה ראפ Bite Me</v>
+      </c>
+      <c r="B87" t="str">
+        <v>2025-08-12</v>
+      </c>
+      <c r="C87" t="str">
+        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
+      </c>
+      <c r="D87" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E87" t="str">
+        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
+      </c>
+      <c r="F87" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G87" t="str">
+        <v/>
+      </c>
+      <c r="H87" t="str">
+        <v/>
+      </c>
+      <c r="I87" t="str">
+        <v/>
+      </c>
+      <c r="J87" t="str">
+        <v/>
+      </c>
+      <c r="K87" t="str">
+        <v/>
+      </c>
+      <c r="L87" t="str">
+        <v/>
+      </c>
+      <c r="M87" t="str">
+        <v/>
+      </c>
+      <c r="N87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>The K's – Pretty On The Internet</v>
+      </c>
+      <c r="B88" t="str">
+        <v>2025-08-03</v>
+      </c>
+      <c r="C88" t="str">
+        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
+      </c>
+      <c r="D88" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E88" t="str">
+        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
+      </c>
+      <c r="F88" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G88" t="str">
+        <v/>
+      </c>
+      <c r="H88" t="str">
+        <v/>
+      </c>
+      <c r="I88" t="str">
+        <v/>
+      </c>
+      <c r="J88" t="str">
+        <v/>
+      </c>
+      <c r="K88" t="str">
+        <v/>
+      </c>
+      <c r="L88" t="str">
+        <v/>
+      </c>
+      <c r="M88" t="str">
+        <v/>
+      </c>
+      <c r="N88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>פליטווד מק Fifty Years – Don’t Stop</v>
+      </c>
+      <c r="B89" t="str">
+        <v>2025-07-30</v>
+      </c>
+      <c r="C89" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%99%d7%98%d7%95%d7%95%d7%93-%d7%9e%d7%a7-fifty-years-dont-stop/</v>
+      </c>
+      <c r="D89" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E89" t="str">
+        <v>פליטווד מק (Fleetwood Mac) חוגגים חצי מאה של מוזיקה עם אוסף חדש בן 50 שירים, שמתפרש על כל הקריירה של הלהקה, מימיה הראשונים בסגנון בלוז, ועד להצלחתה העולמית כאחת מלהקות הגדולות בהיסטוריה של הרוק. פליטווד מק הם לא רק להקה</v>
+      </c>
+      <c r="F89" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G89" t="str">
+        <v/>
+      </c>
+      <c r="H89" t="str">
+        <v/>
+      </c>
+      <c r="I89" t="str">
+        <v/>
+      </c>
+      <c r="J89" t="str">
+        <v/>
+      </c>
+      <c r="K89" t="str">
+        <v/>
+      </c>
+      <c r="L89" t="str">
+        <v/>
+      </c>
+      <c r="M89" t="str">
+        <v/>
+      </c>
+      <c r="N89" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
         <v>Wet Leg Moisturizer</v>
       </c>
-      <c r="B77" t="str">
+      <c r="B90" t="str">
         <v>2025-07-25</v>
       </c>
-      <c r="C77" t="str">
+      <c r="C90" t="str">
         <v>https://yosmusic.com/wet-leg-moisturizer/</v>
       </c>
-      <c r="D77" t="str">
-        <v>2026-01-08</v>
-      </c>
-      <c r="E77" t="str">
+      <c r="D90" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E90" t="str">
         <v>להקת Wet Leg לא הוציאה קרם לחות (Moisturizer) כמוצר טיפוח. במקום זאת, "Moisturizer" הוא שמו של האלבום השני והחדש שלהם. במרכז –  צמד אינדי-רוק המורכב מהחברות ריין טיסדייל והסטר צ'יימברס. אלבום הבכורה הנושא את שמה, הגיע למקום הראשון במצעד האלבומים</v>
       </c>
-      <c r="F77" t="str">
-        <v>אלבומים חדשים</v>
-      </c>
-      <c r="G77" t="str">
-        <v/>
-      </c>
-      <c r="H77" t="str">
-        <v/>
-      </c>
-      <c r="I77" t="str">
-        <v/>
-      </c>
-      <c r="J77" t="str">
-        <v/>
-      </c>
-      <c r="K77" t="str">
-        <v/>
-      </c>
-      <c r="L77" t="str">
+      <c r="F90" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G90" t="str">
+        <v/>
+      </c>
+      <c r="H90" t="str">
+        <v/>
+      </c>
+      <c r="I90" t="str">
+        <v/>
+      </c>
+      <c r="J90" t="str">
+        <v/>
+      </c>
+      <c r="K90" t="str">
+        <v/>
+      </c>
+      <c r="L90" t="str">
+        <v/>
+      </c>
+      <c r="M90" t="str">
+        <v/>
+      </c>
+      <c r="N90" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L77"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N90"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N90"/>
+  <dimension ref="A1:P103"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,7 +421,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>|| תומר יוסף - 360 (2026)</v>
+        <v>|אלבום חדש| תומר יוסף - 360 ()</v>
       </c>
       <c r="B2" t="str">
         <v>2026  11:38-01-09</v>
@@ -430,7 +430,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -441,7 +441,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>|| עמיר בניון - לא נוגע בקרקע ()</v>
+        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע ()</v>
       </c>
       <c r="B3" t="str">
         <v>2025  02:17-12-31</v>
@@ -450,7 +450,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -461,7 +461,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>|| אברהם טל - חי ()</v>
+        <v>|אלבום חדש| אברהם טל - חי ()</v>
       </c>
       <c r="B4" t="str">
         <v>2025  02:16-12-31</v>
@@ -470,7 +470,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -481,7 +481,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>|| מיקי גבריאלוב - שלום ()</v>
+        <v>|אלבום חדש| מיקי גבריאלוב - שלום ()</v>
       </c>
       <c r="B5" t="str">
         <v>2025  02:13-12-31</v>
@@ -490,7 +490,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -501,7 +501,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>|| בזכרי ימים ימימה - מחווה לצלילי הכרם ()</v>
+        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם ()</v>
       </c>
       <c r="B6" t="str">
         <v>2025  02:12-12-31</v>
@@ -510,7 +510,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -521,7 +521,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>|| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון ()</v>
+        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון ()</v>
       </c>
       <c r="B7" t="str">
         <v>2025  02:10-12-31</v>
@@ -530,7 +530,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -541,7 +541,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>|| שלמה גרוניך - תודה אהבה ()</v>
+        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה ()</v>
       </c>
       <c r="B8" t="str">
         <v>2025  02:09-12-31</v>
@@ -550,7 +550,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -561,7 +561,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>|| חוה אלברשטיין - חמישה שירים ()</v>
+        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים ()</v>
       </c>
       <c r="B9" t="str">
         <v>2025  02:06-12-31</v>
@@ -570,7 +570,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -581,7 +581,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>|| הפרויקט של עידן רייכל - עד סוף העולם ()</v>
+        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם ()</v>
       </c>
       <c r="B10" t="str">
         <v>2025  02:05-12-31</v>
@@ -590,7 +590,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -601,7 +601,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>|| סטטיק - קעקועים ()</v>
+        <v>|אלבום חדש| סטטיק - קעקועים ()</v>
       </c>
       <c r="B11" t="str">
         <v>2025  02:03-12-31</v>
@@ -610,7 +610,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -621,7 +621,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>|| ליאור נרקיס - דיסוננס ()</v>
+        <v>|אלבום חדש| ליאור נרקיס - דיסוננס ()</v>
       </c>
       <c r="B12" t="str">
         <v>2025  02:01-12-31</v>
@@ -630,7 +630,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -641,7 +641,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>|| דיוויד ברוזה - BrozaJazz (Paris Alhambra) ()</v>
+        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) ()</v>
       </c>
       <c r="B13" t="str">
         <v>2025  01:57-12-31</v>
@@ -650,7 +650,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -661,7 +661,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>|| אתניקס - איטליה ()</v>
+        <v>|אלבום חדש| אתניקס - איטליה ()</v>
       </c>
       <c r="B14" t="str">
         <v>2025  01:55-12-31</v>
@@ -670,7 +670,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -681,19 +681,19 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>מארינה מקסימיליאן – ריק בחלל</v>
+        <v>|| תומר יוסף - 360 (2026)</v>
       </c>
       <c r="B15" t="str">
-        <v>2026-01-09</v>
+        <v>2026  11:38-01-09</v>
       </c>
       <c r="C15" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-09</v>
       </c>
       <c r="E15" t="str">
-        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
+        <v/>
       </c>
       <c r="F15" t="str">
         <v>אלבומים חדשים</v>
@@ -707,16 +707,16 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>|| אייל גולן - בית מפואר ()</v>
+        <v>|| עמיר בניון - לא נוגע בקרקע ()</v>
       </c>
       <c r="B16" t="str">
-        <v>2025  02:18-12-31</v>
+        <v>2025  02:17-12-31</v>
       </c>
       <c r="C16" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -728,27 +728,21 @@
         <v/>
       </c>
       <c r="H16" t="str">
-        <v/>
-      </c>
-      <c r="I16" t="str">
-        <v/>
-      </c>
-      <c r="J16" t="str">
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>|| הפרויקט של דודי לוי ואבטיפוס - הפטריקים ()</v>
+        <v>|| אברהם טל - חי ()</v>
       </c>
       <c r="B17" t="str">
         <v>2025  02:16-12-31</v>
       </c>
       <c r="C17" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -760,27 +754,21 @@
         <v/>
       </c>
       <c r="H17" t="str">
-        <v/>
-      </c>
-      <c r="I17" t="str">
-        <v/>
-      </c>
-      <c r="J17" t="str">
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>|| שיר לוי - ילד מוזר ()</v>
+        <v>|| מיקי גבריאלוב - שלום ()</v>
       </c>
       <c r="B18" t="str">
-        <v>2025  02:14-12-31</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C18" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -792,27 +780,21 @@
         <v/>
       </c>
       <c r="H18" t="str">
-        <v/>
-      </c>
-      <c r="I18" t="str">
-        <v/>
-      </c>
-      <c r="J18" t="str">
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>|| פיטר רוט - 50 ()</v>
+        <v>|| בזכרי ימים ימימה - מחווה לצלילי הכרם ()</v>
       </c>
       <c r="B19" t="str">
-        <v>2025  02:13-12-31</v>
+        <v>2025  02:12-12-31</v>
       </c>
       <c r="C19" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -824,27 +806,21 @@
         <v/>
       </c>
       <c r="H19" t="str">
-        <v/>
-      </c>
-      <c r="I19" t="str">
-        <v/>
-      </c>
-      <c r="J19" t="str">
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>|| אגם בוחבוט - עשרים ואחת ()</v>
+        <v>|| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון ()</v>
       </c>
       <c r="B20" t="str">
-        <v>2025  02:11-12-31</v>
+        <v>2025  02:10-12-31</v>
       </c>
       <c r="C20" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -856,27 +832,21 @@
         <v/>
       </c>
       <c r="H20" t="str">
-        <v/>
-      </c>
-      <c r="I20" t="str">
-        <v/>
-      </c>
-      <c r="J20" t="str">
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>|| רבקה זוהר - רסיסים של אור ()</v>
+        <v>|| שלמה גרוניך - תודה אהבה ()</v>
       </c>
       <c r="B21" t="str">
         <v>2025  02:09-12-31</v>
       </c>
       <c r="C21" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -888,27 +858,21 @@
         <v/>
       </c>
       <c r="H21" t="str">
-        <v/>
-      </c>
-      <c r="I21" t="str">
-        <v/>
-      </c>
-      <c r="J21" t="str">
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>|| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות ()</v>
+        <v>|| חוה אלברשטיין - חמישה שירים ()</v>
       </c>
       <c r="B22" t="str">
-        <v>2025  02:08-12-31</v>
+        <v>2025  02:06-12-31</v>
       </c>
       <c r="C22" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -920,27 +884,21 @@
         <v/>
       </c>
       <c r="H22" t="str">
-        <v/>
-      </c>
-      <c r="I22" t="str">
-        <v/>
-      </c>
-      <c r="J22" t="str">
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>|| אהוד בנאי ובנו הנדלר - פליטי הדאב ()</v>
+        <v>|| הפרויקט של עידן רייכל - עד סוף העולם ()</v>
       </c>
       <c r="B23" t="str">
         <v>2025  02:05-12-31</v>
       </c>
       <c r="C23" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -952,27 +910,21 @@
         <v/>
       </c>
       <c r="H23" t="str">
-        <v/>
-      </c>
-      <c r="I23" t="str">
-        <v/>
-      </c>
-      <c r="J23" t="str">
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>|| Imagine פסטיגל - שירי התחרות ()</v>
+        <v>|| סטטיק - קעקועים ()</v>
       </c>
       <c r="B24" t="str">
-        <v>2025  02:04-12-31</v>
+        <v>2025  02:03-12-31</v>
       </c>
       <c r="C24" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -984,27 +936,21 @@
         <v/>
       </c>
       <c r="H24" t="str">
-        <v/>
-      </c>
-      <c r="I24" t="str">
-        <v/>
-      </c>
-      <c r="J24" t="str">
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>|| השמחות - חובות אבודים ()</v>
+        <v>|| ליאור נרקיס - דיסוננס ()</v>
       </c>
       <c r="B25" t="str">
-        <v>2025  02:02-12-31</v>
+        <v>2025  02:01-12-31</v>
       </c>
       <c r="C25" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1016,27 +962,21 @@
         <v/>
       </c>
       <c r="H25" t="str">
-        <v/>
-      </c>
-      <c r="I25" t="str">
-        <v/>
-      </c>
-      <c r="J25" t="str">
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>|| שלמה גרוניך - כמו כוכבים ()</v>
+        <v>|| דיוויד ברוזה - BrozaJazz (Paris Alhambra) ()</v>
       </c>
       <c r="B26" t="str">
-        <v>2025  02:00-12-31</v>
+        <v>2025  01:57-12-31</v>
       </c>
       <c r="C26" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1048,27 +988,21 @@
         <v/>
       </c>
       <c r="H26" t="str">
-        <v/>
-      </c>
-      <c r="I26" t="str">
-        <v/>
-      </c>
-      <c r="J26" t="str">
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>|| יוני רועה - מפוזרים ()</v>
+        <v>|| אתניקס - איטליה ()</v>
       </c>
       <c r="B27" t="str">
-        <v>2025  01:56-12-31</v>
+        <v>2025  01:55-12-31</v>
       </c>
       <c r="C27" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1080,30 +1014,24 @@
         <v/>
       </c>
       <c r="H27" t="str">
-        <v/>
-      </c>
-      <c r="I27" t="str">
-        <v/>
-      </c>
-      <c r="J27" t="str">
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>|| התקווה 6 - ויהי אור ()</v>
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
       </c>
       <c r="B28" t="str">
-        <v>2025  01:54-12-31</v>
+        <v>2026-01-09</v>
       </c>
       <c r="C28" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E28" t="str">
-        <v/>
+        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
       </c>
       <c r="F28" t="str">
         <v>אלבומים חדשים</v>
@@ -1123,13 +1051,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>|| שאנן סטריט ודי ג׳יי מש - באתי לבדר ()</v>
+        <v>|| אייל גולן - בית מפואר ()</v>
       </c>
       <c r="B29" t="str">
-        <v>2025  01:53-12-31</v>
+        <v>2025  02:18-12-31</v>
       </c>
       <c r="C29" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-08</v>
@@ -1150,18 +1078,24 @@
         <v/>
       </c>
       <c r="J29" t="str">
+        <v/>
+      </c>
+      <c r="K29" t="str">
+        <v/>
+      </c>
+      <c r="L29" t="str">
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>אשכול נוכחות למשתמשים פעילים</v>
+        <v>|| הפרויקט של דודי לוי ואבטיפוס - הפטריקים ()</v>
       </c>
       <c r="B30" t="str">
-        <v>2025  16:32 מאת freund-10-16</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C30" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=23455&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-08</v>
@@ -1193,13 +1127,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>כיצד להוריד מהאתרים המפורסמים</v>
+        <v>|| שיר לוי - ילד מוזר ()</v>
       </c>
       <c r="B31" t="str">
-        <v>2023  16:23 מאת petel1-08-08</v>
+        <v>2025  02:14-12-31</v>
       </c>
       <c r="C31" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=22411&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-08</v>
@@ -1231,13 +1165,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
+        <v>|| פיטר רוט - 50 ()</v>
       </c>
       <c r="B32" t="str">
-        <v>2026  22:40 מאת מוטי_ד-01-01</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C32" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24435&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-08</v>
@@ -1269,13 +1203,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>|אלבום חדש| אייל גולן - בית מפואר (2025)</v>
+        <v>|| אגם בוחבוט - עשרים ואחת ()</v>
       </c>
       <c r="B33" t="str">
-        <v>2025  02:18 מאת DiSHi-12-31</v>
+        <v>2025  02:11-12-31</v>
       </c>
       <c r="C33" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-08</v>
@@ -1307,13 +1241,13 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע (2025)</v>
+        <v>|| רבקה זוהר - רסיסים של אור ()</v>
       </c>
       <c r="B34" t="str">
-        <v>2025  02:17 מאת DiSHi-12-31</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C34" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-08</v>
@@ -1345,13 +1279,13 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>|אלבום חדש| הפרויקט של דודי לוי ואבטיפוס - הפטריקים (2025)</v>
+        <v>|| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות ()</v>
       </c>
       <c r="B35" t="str">
-        <v>2025  02:16 מאת DiSHi-12-31</v>
+        <v>2025  02:08-12-31</v>
       </c>
       <c r="C35" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-08</v>
@@ -1383,13 +1317,13 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>|אלבום חדש| אברהם טל - חי (2025)</v>
+        <v>|| אהוד בנאי ובנו הנדלר - פליטי הדאב ()</v>
       </c>
       <c r="B36" t="str">
-        <v>2025  02:16 מאת DiSHi-12-31</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C36" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-08</v>
@@ -1421,13 +1355,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>|אלבום חדש| שיר לוי - ילד מוזר (2025)</v>
+        <v>|| Imagine פסטיגל - שירי התחרות ()</v>
       </c>
       <c r="B37" t="str">
-        <v>2025  02:14 מאת DiSHi-12-31</v>
+        <v>2025  02:04-12-31</v>
       </c>
       <c r="C37" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-08</v>
@@ -1459,13 +1393,13 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>|אלבום חדש| מיקי גבריאלוב - שלום (2025)</v>
+        <v>|| השמחות - חובות אבודים ()</v>
       </c>
       <c r="B38" t="str">
-        <v>2025  02:13 מאת DiSHi-12-31</v>
+        <v>2025  02:02-12-31</v>
       </c>
       <c r="C38" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-08</v>
@@ -1497,13 +1431,13 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>|אלבום חדש| פיטר רוט - 50 (2025)</v>
+        <v>|| שלמה גרוניך - כמו כוכבים ()</v>
       </c>
       <c r="B39" t="str">
-        <v>2025  02:13 מאת DiSHi-12-31</v>
+        <v>2025  02:00-12-31</v>
       </c>
       <c r="C39" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-08</v>
@@ -1535,13 +1469,13 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם (2025)</v>
+        <v>|| יוני רועה - מפוזרים ()</v>
       </c>
       <c r="B40" t="str">
-        <v>2025  02:12 מאת DiSHi-12-31</v>
+        <v>2025  01:56-12-31</v>
       </c>
       <c r="C40" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-08</v>
@@ -1573,13 +1507,13 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>|אלבום חדש| אגם בוחבוט - עשרים ואחת (2025)</v>
+        <v>|| התקווה 6 - ויהי אור ()</v>
       </c>
       <c r="B41" t="str">
-        <v>2025  02:11 מאת DiSHi-12-31</v>
+        <v>2025  01:54-12-31</v>
       </c>
       <c r="C41" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-08</v>
@@ -1611,13 +1545,13 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון (2025)</v>
+        <v>|| שאנן סטריט ודי ג׳יי מש - באתי לבדר ()</v>
       </c>
       <c r="B42" t="str">
-        <v>2025  02:10 מאת DiSHi-12-31</v>
+        <v>2025  01:53-12-31</v>
       </c>
       <c r="C42" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-08</v>
@@ -1649,13 +1583,13 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>|אלבום חדש| רבקה זוהר - רסיסים של אור (2025)</v>
+        <v>אשכול נוכחות למשתמשים פעילים</v>
       </c>
       <c r="B43" t="str">
-        <v>2025  02:09 מאת DiSHi-12-31</v>
+        <v>2025  16:32 מאת freund-10-16</v>
       </c>
       <c r="C43" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=23455&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-08</v>
@@ -1682,18 +1616,24 @@
         <v/>
       </c>
       <c r="L43" t="str">
+        <v/>
+      </c>
+      <c r="M43" t="str">
+        <v/>
+      </c>
+      <c r="N43" t="str">
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה (2025)</v>
+        <v>כיצד להוריד מהאתרים המפורסמים</v>
       </c>
       <c r="B44" t="str">
-        <v>2025  02:09 מאת DiSHi-12-31</v>
+        <v>2023  16:23 מאת petel1-08-08</v>
       </c>
       <c r="C44" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=22411&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-08</v>
@@ -1720,18 +1660,24 @@
         <v/>
       </c>
       <c r="L44" t="str">
+        <v/>
+      </c>
+      <c r="M44" t="str">
+        <v/>
+      </c>
+      <c r="N44" t="str">
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>|אלבום חדש| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות (2025)</v>
+        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
       </c>
       <c r="B45" t="str">
-        <v>2025  02:08 מאת DiSHi-12-31</v>
+        <v>2026  22:40 מאת מוטי_ד-01-01</v>
       </c>
       <c r="C45" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24435&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-08</v>
@@ -1758,18 +1704,24 @@
         <v/>
       </c>
       <c r="L45" t="str">
+        <v/>
+      </c>
+      <c r="M45" t="str">
+        <v/>
+      </c>
+      <c r="N45" t="str">
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים (2025)</v>
+        <v>|אלבום חדש| אייל גולן - בית מפואר (2025)</v>
       </c>
       <c r="B46" t="str">
-        <v>2025  02:06 מאת DiSHi-12-31</v>
+        <v>2025  02:18 מאת DiSHi-12-31</v>
       </c>
       <c r="C46" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-08</v>
@@ -1796,18 +1748,24 @@
         <v/>
       </c>
       <c r="L46" t="str">
+        <v/>
+      </c>
+      <c r="M46" t="str">
+        <v/>
+      </c>
+      <c r="N46" t="str">
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>|אלבום חדש| אהוד בנאי ובנו הנדלר - פליטי הדאב (2025)</v>
+        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע (2025)</v>
       </c>
       <c r="B47" t="str">
-        <v>2025  02:05 מאת DiSHi-12-31</v>
+        <v>2025  02:17 מאת DiSHi-12-31</v>
       </c>
       <c r="C47" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-08</v>
@@ -1834,18 +1792,24 @@
         <v/>
       </c>
       <c r="L47" t="str">
+        <v/>
+      </c>
+      <c r="M47" t="str">
+        <v/>
+      </c>
+      <c r="N47" t="str">
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם (2025)</v>
+        <v>|אלבום חדש| הפרויקט של דודי לוי ואבטיפוס - הפטריקים (2025)</v>
       </c>
       <c r="B48" t="str">
-        <v>2025  02:05 מאת DiSHi-12-31</v>
+        <v>2025  02:16 מאת DiSHi-12-31</v>
       </c>
       <c r="C48" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-08</v>
@@ -1872,18 +1836,24 @@
         <v/>
       </c>
       <c r="L48" t="str">
+        <v/>
+      </c>
+      <c r="M48" t="str">
+        <v/>
+      </c>
+      <c r="N48" t="str">
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>|אלבום חדש| Imagine פסטיגל - שירי התחרות (2025)</v>
+        <v>|אלבום חדש| אברהם טל - חי (2025)</v>
       </c>
       <c r="B49" t="str">
-        <v>2025  02:04 מאת DiSHi-12-31</v>
+        <v>2025  02:16 מאת DiSHi-12-31</v>
       </c>
       <c r="C49" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-08</v>
@@ -1910,18 +1880,24 @@
         <v/>
       </c>
       <c r="L49" t="str">
+        <v/>
+      </c>
+      <c r="M49" t="str">
+        <v/>
+      </c>
+      <c r="N49" t="str">
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>|אלבום חדש| סטטיק - קעקועים (2025)</v>
+        <v>|אלבום חדש| שיר לוי - ילד מוזר (2025)</v>
       </c>
       <c r="B50" t="str">
-        <v>2025  02:03 מאת DiSHi-12-31</v>
+        <v>2025  02:14 מאת DiSHi-12-31</v>
       </c>
       <c r="C50" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-08</v>
@@ -1948,18 +1924,24 @@
         <v/>
       </c>
       <c r="L50" t="str">
+        <v/>
+      </c>
+      <c r="M50" t="str">
+        <v/>
+      </c>
+      <c r="N50" t="str">
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>|אלבום חדש| השמחות - חובות אבודים (2025)</v>
+        <v>|אלבום חדש| מיקי גבריאלוב - שלום (2025)</v>
       </c>
       <c r="B51" t="str">
-        <v>2025  02:02 מאת DiSHi-12-31</v>
+        <v>2025  02:13 מאת DiSHi-12-31</v>
       </c>
       <c r="C51" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-08</v>
@@ -1986,18 +1968,24 @@
         <v/>
       </c>
       <c r="L51" t="str">
+        <v/>
+      </c>
+      <c r="M51" t="str">
+        <v/>
+      </c>
+      <c r="N51" t="str">
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>|אלבום חדש| ליאור נרקיס - דיסוננס (2025)</v>
+        <v>|אלבום חדש| פיטר רוט - 50 (2025)</v>
       </c>
       <c r="B52" t="str">
-        <v>2025  02:01 מאת DiSHi-12-31</v>
+        <v>2025  02:13 מאת DiSHi-12-31</v>
       </c>
       <c r="C52" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-08</v>
@@ -2024,18 +2012,24 @@
         <v/>
       </c>
       <c r="L52" t="str">
+        <v/>
+      </c>
+      <c r="M52" t="str">
+        <v/>
+      </c>
+      <c r="N52" t="str">
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>|אלבום חדש| שלמה גרוניך - כמו כוכבים (2025)</v>
+        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם (2025)</v>
       </c>
       <c r="B53" t="str">
-        <v>2025  02:00 מאת DiSHi-12-31</v>
+        <v>2025  02:12 מאת DiSHi-12-31</v>
       </c>
       <c r="C53" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-08</v>
@@ -2062,18 +2056,24 @@
         <v/>
       </c>
       <c r="L53" t="str">
+        <v/>
+      </c>
+      <c r="M53" t="str">
+        <v/>
+      </c>
+      <c r="N53" t="str">
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) (2025)</v>
+        <v>|אלבום חדש| אגם בוחבוט - עשרים ואחת (2025)</v>
       </c>
       <c r="B54" t="str">
-        <v>2025  01:57 מאת DiSHi-12-31</v>
+        <v>2025  02:11 מאת DiSHi-12-31</v>
       </c>
       <c r="C54" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-08</v>
@@ -2100,18 +2100,24 @@
         <v/>
       </c>
       <c r="L54" t="str">
+        <v/>
+      </c>
+      <c r="M54" t="str">
+        <v/>
+      </c>
+      <c r="N54" t="str">
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>|אלבום חדש| יוני רועה - מפוזרים (2025)</v>
+        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון (2025)</v>
       </c>
       <c r="B55" t="str">
-        <v>2025  01:56 מאת DiSHi-12-31</v>
+        <v>2025  02:10 מאת DiSHi-12-31</v>
       </c>
       <c r="C55" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-08</v>
@@ -2138,18 +2144,24 @@
         <v/>
       </c>
       <c r="L55" t="str">
+        <v/>
+      </c>
+      <c r="M55" t="str">
+        <v/>
+      </c>
+      <c r="N55" t="str">
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>|אלבום חדש| אתניקס - איטליה (2025)</v>
+        <v>|אלבום חדש| רבקה זוהר - רסיסים של אור (2025)</v>
       </c>
       <c r="B56" t="str">
-        <v>2025  01:55 מאת DiSHi-12-31</v>
+        <v>2025  02:09 מאת DiSHi-12-31</v>
       </c>
       <c r="C56" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-08</v>
@@ -2176,18 +2188,24 @@
         <v/>
       </c>
       <c r="L56" t="str">
+        <v/>
+      </c>
+      <c r="M56" t="str">
+        <v/>
+      </c>
+      <c r="N56" t="str">
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>|אלבום חדש| התקווה 6 - ויהי אור (2025)</v>
+        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה (2025)</v>
       </c>
       <c r="B57" t="str">
-        <v>2025  01:54 מאת DiSHi-12-31</v>
+        <v>2025  02:09 מאת DiSHi-12-31</v>
       </c>
       <c r="C57" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-08</v>
@@ -2214,18 +2232,24 @@
         <v/>
       </c>
       <c r="L57" t="str">
+        <v/>
+      </c>
+      <c r="M57" t="str">
+        <v/>
+      </c>
+      <c r="N57" t="str">
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>|אלבום חדש| שלומי סרנגה - איפרכו (2025)</v>
+        <v>|אלבום חדש| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות (2025)</v>
       </c>
       <c r="B58" t="str">
-        <v>2025  01:53 מאת DiSHi-12-31</v>
+        <v>2025  02:08 מאת DiSHi-12-31</v>
       </c>
       <c r="C58" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24430&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-08</v>
@@ -2252,18 +2276,24 @@
         <v/>
       </c>
       <c r="L58" t="str">
+        <v/>
+      </c>
+      <c r="M58" t="str">
+        <v/>
+      </c>
+      <c r="N58" t="str">
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>|אלבום חדש| שאנן סטריט ודי ג׳יי מש - באתי לבדר (2025)</v>
+        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים (2025)</v>
       </c>
       <c r="B59" t="str">
-        <v>2025  01:53 מאת DiSHi-12-31</v>
+        <v>2025  02:06 מאת DiSHi-12-31</v>
       </c>
       <c r="C59" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-08</v>
@@ -2290,18 +2320,24 @@
         <v/>
       </c>
       <c r="L59" t="str">
+        <v/>
+      </c>
+      <c r="M59" t="str">
+        <v/>
+      </c>
+      <c r="N59" t="str">
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>הרשם לחברות מלאה</v>
+        <v>|אלבום חדש| אהוד בנאי ובנו הנדלר - פליטי הדאב (2025)</v>
       </c>
       <c r="B60" t="str">
-        <v/>
+        <v>2025  02:05 מאת DiSHi-12-31</v>
       </c>
       <c r="C60" t="str">
-        <v>https://rotter.name/nor/members-new.html</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-08</v>
@@ -2328,24 +2364,30 @@
         <v/>
       </c>
       <c r="L60" t="str">
+        <v/>
+      </c>
+      <c r="M60" t="str">
+        <v/>
+      </c>
+      <c r="N60" t="str">
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>אוליביה דין The Art of Loving</v>
+        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם (2025)</v>
       </c>
       <c r="B61" t="str">
-        <v>2026-01-04</v>
+        <v>2025  02:05 מאת DiSHi-12-31</v>
       </c>
       <c r="C61" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E61" t="str">
-        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
+        <v/>
       </c>
       <c r="F61" t="str">
         <v>אלבומים חדשים</v>
@@ -2377,19 +2419,19 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Geese Getting Killed</v>
+        <v>|אלבום חדש| Imagine פסטיגל - שירי התחרות (2025)</v>
       </c>
       <c r="B62" t="str">
-        <v>2025-12-29</v>
+        <v>2025  02:04 מאת DiSHi-12-31</v>
       </c>
       <c r="C62" t="str">
-        <v>https://yosmusic.com/geese-getting-killed/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E62" t="str">
-        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
+        <v/>
       </c>
       <c r="F62" t="str">
         <v>אלבומים חדשים</v>
@@ -2421,19 +2463,19 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>רוסליה Lux</v>
+        <v>|אלבום חדש| סטטיק - קעקועים (2025)</v>
       </c>
       <c r="B63" t="str">
-        <v>2025-12-25</v>
+        <v>2025  02:03 מאת DiSHi-12-31</v>
       </c>
       <c r="C63" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E63" t="str">
-        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
+        <v/>
       </c>
       <c r="F63" t="str">
         <v>אלבומים חדשים</v>
@@ -2465,19 +2507,19 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>יאנגבלאד אירוסמית' one more time</v>
+        <v>|אלבום חדש| השמחות - חובות אבודים (2025)</v>
       </c>
       <c r="B64" t="str">
-        <v>2025-12-17</v>
+        <v>2025  02:02 מאת DiSHi-12-31</v>
       </c>
       <c r="C64" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E64" t="str">
-        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
+        <v/>
       </c>
       <c r="F64" t="str">
         <v>אלבומים חדשים</v>
@@ -2509,19 +2551,19 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>פינק פלויד Wish You Were Here 50</v>
+        <v>|אלבום חדש| ליאור נרקיס - דיסוננס (2025)</v>
       </c>
       <c r="B65" t="str">
-        <v>2025-12-14</v>
+        <v>2025  02:01 מאת DiSHi-12-31</v>
       </c>
       <c r="C65" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E65" t="str">
-        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
+        <v/>
       </c>
       <c r="F65" t="str">
         <v>אלבומים חדשים</v>
@@ -2553,19 +2595,19 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+        <v>|אלבום חדש| שלמה גרוניך - כמו כוכבים (2025)</v>
       </c>
       <c r="B66" t="str">
-        <v>2025-12-08</v>
+        <v>2025  02:00 מאת DiSHi-12-31</v>
       </c>
       <c r="C66" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E66" t="str">
-        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
+        <v/>
       </c>
       <c r="F66" t="str">
         <v>אלבומים חדשים</v>
@@ -2597,19 +2639,19 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>סטריי קידס DO IT (EP)</v>
+        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) (2025)</v>
       </c>
       <c r="B67" t="str">
-        <v>2025-12-04</v>
+        <v>2025  01:57 מאת DiSHi-12-31</v>
       </c>
       <c r="C67" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E67" t="str">
-        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
+        <v/>
       </c>
       <c r="F67" t="str">
         <v>אלבומים חדשים</v>
@@ -2641,19 +2683,19 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>דויד ברוזה BROZAJAZZ</v>
+        <v>|אלבום חדש| יוני רועה - מפוזרים (2025)</v>
       </c>
       <c r="B68" t="str">
-        <v>2025-11-30</v>
+        <v>2025  01:56 מאת DiSHi-12-31</v>
       </c>
       <c r="C68" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E68" t="str">
-        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
+        <v/>
       </c>
       <c r="F68" t="str">
         <v>אלבומים חדשים</v>
@@ -2685,19 +2727,19 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Five Seconds of Summer – Everyone's A Star</v>
+        <v>|אלבום חדש| אתניקס - איטליה (2025)</v>
       </c>
       <c r="B69" t="str">
-        <v>2025-11-24</v>
+        <v>2025  01:55 מאת DiSHi-12-31</v>
       </c>
       <c r="C69" t="str">
-        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E69" t="str">
-        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
+        <v/>
       </c>
       <c r="F69" t="str">
         <v>אלבומים חדשים</v>
@@ -2729,19 +2771,19 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>התקווה 6 – ויהי אור</v>
+        <v>|אלבום חדש| התקווה 6 - ויהי אור (2025)</v>
       </c>
       <c r="B70" t="str">
-        <v>2025-11-20</v>
+        <v>2025  01:54 מאת DiSHi-12-31</v>
       </c>
       <c r="C70" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E70" t="str">
-        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
+        <v/>
       </c>
       <c r="F70" t="str">
         <v>אלבומים חדשים</v>
@@ -2773,19 +2815,19 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>פלורנס אנד דה משין Everybody Scream</v>
+        <v>|אלבום חדש| שלומי סרנגה - איפרכו (2025)</v>
       </c>
       <c r="B71" t="str">
-        <v>2025-11-13</v>
+        <v>2025  01:53 מאת DiSHi-12-31</v>
       </c>
       <c r="C71" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24430&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E71" t="str">
-        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
+        <v/>
       </c>
       <c r="F71" t="str">
         <v>אלבומים חדשים</v>
@@ -2817,19 +2859,19 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>טיים אימפלה Deadbeat</v>
+        <v>|אלבום חדש| שאנן סטריט ודי ג׳יי מש - באתי לבדר (2025)</v>
       </c>
       <c r="B72" t="str">
-        <v>2025-11-03</v>
+        <v>2025  01:53 מאת DiSHi-12-31</v>
       </c>
       <c r="C72" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E72" t="str">
-        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
+        <v/>
       </c>
       <c r="F72" t="str">
         <v>אלבומים חדשים</v>
@@ -2861,19 +2903,19 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+        <v>הרשם לחברות מלאה</v>
       </c>
       <c r="B73" t="str">
-        <v>2025-10-20</v>
+        <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
+        <v>https://rotter.name/nor/members-new.html</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E73" t="str">
-        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
+        <v/>
       </c>
       <c r="F73" t="str">
         <v>אלבומים חדשים</v>
@@ -2905,19 +2947,19 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>שלמה גרוניך – תודה אהבה</v>
+        <v>אוליביה דין The Art of Loving</v>
       </c>
       <c r="B74" t="str">
-        <v>2025-10-18</v>
+        <v>2026-01-04</v>
       </c>
       <c r="C74" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E74" t="str">
-        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
+        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
       </c>
       <c r="F74" t="str">
         <v>אלבומים חדשים</v>
@@ -2944,24 +2986,30 @@
         <v/>
       </c>
       <c r="N74" t="str">
+        <v/>
+      </c>
+      <c r="O74" t="str">
+        <v/>
+      </c>
+      <c r="P74" t="str">
         <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>טיילור סוויפט The Life Of A Showgirl</v>
+        <v>Geese Getting Killed</v>
       </c>
       <c r="B75" t="str">
-        <v>2025-10-11</v>
+        <v>2025-12-29</v>
       </c>
       <c r="C75" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
+        <v>https://yosmusic.com/geese-getting-killed/</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E75" t="str">
-        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
+        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
       </c>
       <c r="F75" t="str">
         <v>אלבומים חדשים</v>
@@ -2988,24 +3036,30 @@
         <v/>
       </c>
       <c r="N75" t="str">
+        <v/>
+      </c>
+      <c r="O75" t="str">
+        <v/>
+      </c>
+      <c r="P75" t="str">
         <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>דוג'ה קאט Vie</v>
+        <v>רוסליה Lux</v>
       </c>
       <c r="B76" t="str">
-        <v>2025-10-04</v>
+        <v>2025-12-25</v>
       </c>
       <c r="C76" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E76" t="str">
-        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
+        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
       </c>
       <c r="F76" t="str">
         <v>אלבומים חדשים</v>
@@ -3032,24 +3086,30 @@
         <v/>
       </c>
       <c r="N76" t="str">
+        <v/>
+      </c>
+      <c r="O76" t="str">
+        <v/>
+      </c>
+      <c r="P76" t="str">
         <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>ג'וי קרוקס Juniper</v>
+        <v>יאנגבלאד אירוסמית' one more time</v>
       </c>
       <c r="B77" t="str">
-        <v>2025-10-03</v>
+        <v>2025-12-17</v>
       </c>
       <c r="C77" t="str">
-        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
+        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E77" t="str">
-        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
+        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
       </c>
       <c r="F77" t="str">
         <v>אלבומים חדשים</v>
@@ -3076,24 +3136,30 @@
         <v/>
       </c>
       <c r="N77" t="str">
+        <v/>
+      </c>
+      <c r="O77" t="str">
+        <v/>
+      </c>
+      <c r="P77" t="str">
         <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>ביפי קליירו Futique</v>
+        <v>פינק פלויד Wish You Were Here 50</v>
       </c>
       <c r="B78" t="str">
-        <v>2025-09-30</v>
+        <v>2025-12-14</v>
       </c>
       <c r="C78" t="str">
-        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E78" t="str">
-        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
+        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
       </c>
       <c r="F78" t="str">
         <v>אלבומים חדשים</v>
@@ -3120,24 +3186,30 @@
         <v/>
       </c>
       <c r="N78" t="str">
+        <v/>
+      </c>
+      <c r="O78" t="str">
+        <v/>
+      </c>
+      <c r="P78" t="str">
         <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>אד שירן Play</v>
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
       </c>
       <c r="B79" t="str">
-        <v>2025-09-24</v>
+        <v>2025-12-08</v>
       </c>
       <c r="C79" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
+        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E79" t="str">
-        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
+        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
       </c>
       <c r="F79" t="str">
         <v>אלבומים חדשים</v>
@@ -3164,24 +3236,30 @@
         <v/>
       </c>
       <c r="N79" t="str">
+        <v/>
+      </c>
+      <c r="O79" t="str">
+        <v/>
+      </c>
+      <c r="P79" t="str">
         <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+        <v>סטריי קידס DO IT (EP)</v>
       </c>
       <c r="B80" t="str">
-        <v>2025-09-21</v>
+        <v>2025-12-04</v>
       </c>
       <c r="C80" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
+        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E80" t="str">
-        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
+        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
       </c>
       <c r="F80" t="str">
         <v>אלבומים חדשים</v>
@@ -3208,24 +3286,30 @@
         <v/>
       </c>
       <c r="N80" t="str">
+        <v/>
+      </c>
+      <c r="O80" t="str">
+        <v/>
+      </c>
+      <c r="P80" t="str">
         <v/>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>סוויד Antidepressants</v>
+        <v>דויד ברוזה BROZAJAZZ</v>
       </c>
       <c r="B81" t="str">
-        <v>2025-09-12</v>
+        <v>2025-11-30</v>
       </c>
       <c r="C81" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E81" t="str">
-        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
+        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
       </c>
       <c r="F81" t="str">
         <v>אלבומים חדשים</v>
@@ -3252,24 +3336,30 @@
         <v/>
       </c>
       <c r="N81" t="str">
+        <v/>
+      </c>
+      <c r="O81" t="str">
+        <v/>
+      </c>
+      <c r="P81" t="str">
         <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>וולף אליס The Clearing</v>
+        <v>Five Seconds of Summer – Everyone's A Star</v>
       </c>
       <c r="B82" t="str">
-        <v>2025-09-01</v>
+        <v>2025-11-24</v>
       </c>
       <c r="C82" t="str">
-        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
+        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E82" t="str">
-        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
+        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
       </c>
       <c r="F82" t="str">
         <v>אלבומים חדשים</v>
@@ -3296,24 +3386,30 @@
         <v/>
       </c>
       <c r="N82" t="str">
+        <v/>
+      </c>
+      <c r="O82" t="str">
+        <v/>
+      </c>
+      <c r="P82" t="str">
         <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+        <v>התקווה 6 – ויהי אור</v>
       </c>
       <c r="B83" t="str">
-        <v>2025-08-29</v>
+        <v>2025-11-20</v>
       </c>
       <c r="C83" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
+        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E83" t="str">
-        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
+        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
       </c>
       <c r="F83" t="str">
         <v>אלבומים חדשים</v>
@@ -3340,24 +3436,30 @@
         <v/>
       </c>
       <c r="N83" t="str">
+        <v/>
+      </c>
+      <c r="O83" t="str">
+        <v/>
+      </c>
+      <c r="P83" t="str">
         <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+        <v>פלורנס אנד דה משין Everybody Scream</v>
       </c>
       <c r="B84" t="str">
-        <v>2025-08-24</v>
+        <v>2025-11-13</v>
       </c>
       <c r="C84" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E84" t="str">
-        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
+        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
       </c>
       <c r="F84" t="str">
         <v>אלבומים חדשים</v>
@@ -3384,24 +3486,30 @@
         <v/>
       </c>
       <c r="N84" t="str">
+        <v/>
+      </c>
+      <c r="O84" t="str">
+        <v/>
+      </c>
+      <c r="P84" t="str">
         <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+        <v>טיים אימפלה Deadbeat</v>
       </c>
       <c r="B85" t="str">
-        <v>2025-08-21</v>
+        <v>2025-11-03</v>
       </c>
       <c r="C85" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E85" t="str">
-        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
+        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
       </c>
       <c r="F85" t="str">
         <v>אלבומים חדשים</v>
@@ -3428,24 +3536,30 @@
         <v/>
       </c>
       <c r="N85" t="str">
+        <v/>
+      </c>
+      <c r="O85" t="str">
+        <v/>
+      </c>
+      <c r="P85" t="str">
         <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>אברהם טל – חי</v>
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
       </c>
       <c r="B86" t="str">
-        <v>2025-08-17</v>
+        <v>2025-10-20</v>
       </c>
       <c r="C86" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
+        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E86" t="str">
-        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
+        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
       </c>
       <c r="F86" t="str">
         <v>אלבומים חדשים</v>
@@ -3472,24 +3586,30 @@
         <v/>
       </c>
       <c r="N86" t="str">
+        <v/>
+      </c>
+      <c r="O86" t="str">
+        <v/>
+      </c>
+      <c r="P86" t="str">
         <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>רנה ראפ Bite Me</v>
+        <v>שלמה גרוניך – תודה אהבה</v>
       </c>
       <c r="B87" t="str">
-        <v>2025-08-12</v>
+        <v>2025-10-18</v>
       </c>
       <c r="C87" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E87" t="str">
-        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
+        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
       </c>
       <c r="F87" t="str">
         <v>אלבומים חדשים</v>
@@ -3516,24 +3636,30 @@
         <v/>
       </c>
       <c r="N87" t="str">
+        <v/>
+      </c>
+      <c r="O87" t="str">
+        <v/>
+      </c>
+      <c r="P87" t="str">
         <v/>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>The K's – Pretty On The Internet</v>
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
       </c>
       <c r="B88" t="str">
-        <v>2025-08-03</v>
+        <v>2025-10-11</v>
       </c>
       <c r="C88" t="str">
-        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E88" t="str">
-        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
+        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
       </c>
       <c r="F88" t="str">
         <v>אלבומים חדשים</v>
@@ -3560,24 +3686,30 @@
         <v/>
       </c>
       <c r="N88" t="str">
+        <v/>
+      </c>
+      <c r="O88" t="str">
+        <v/>
+      </c>
+      <c r="P88" t="str">
         <v/>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>פליטווד מק Fifty Years – Don’t Stop</v>
+        <v>דוג'ה קאט Vie</v>
       </c>
       <c r="B89" t="str">
-        <v>2025-07-30</v>
+        <v>2025-10-04</v>
       </c>
       <c r="C89" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%99%d7%98%d7%95%d7%95%d7%93-%d7%9e%d7%a7-fifty-years-dont-stop/</v>
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E89" t="str">
-        <v>פליטווד מק (Fleetwood Mac) חוגגים חצי מאה של מוזיקה עם אוסף חדש בן 50 שירים, שמתפרש על כל הקריירה של הלהקה, מימיה הראשונים בסגנון בלוז, ועד להצלחתה העולמית כאחת מלהקות הגדולות בהיסטוריה של הרוק. פליטווד מק הם לא רק להקה</v>
+        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
       </c>
       <c r="F89" t="str">
         <v>אלבומים חדשים</v>
@@ -3604,56 +3736,718 @@
         <v/>
       </c>
       <c r="N89" t="str">
+        <v/>
+      </c>
+      <c r="O89" t="str">
+        <v/>
+      </c>
+      <c r="P89" t="str">
         <v/>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
+        <v>ג'וי קרוקס Juniper</v>
+      </c>
+      <c r="B90" t="str">
+        <v>2025-10-03</v>
+      </c>
+      <c r="C90" t="str">
+        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
+      </c>
+      <c r="D90" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E90" t="str">
+        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
+      </c>
+      <c r="F90" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G90" t="str">
+        <v/>
+      </c>
+      <c r="H90" t="str">
+        <v/>
+      </c>
+      <c r="I90" t="str">
+        <v/>
+      </c>
+      <c r="J90" t="str">
+        <v/>
+      </c>
+      <c r="K90" t="str">
+        <v/>
+      </c>
+      <c r="L90" t="str">
+        <v/>
+      </c>
+      <c r="M90" t="str">
+        <v/>
+      </c>
+      <c r="N90" t="str">
+        <v/>
+      </c>
+      <c r="O90" t="str">
+        <v/>
+      </c>
+      <c r="P90" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>ביפי קליירו Futique</v>
+      </c>
+      <c r="B91" t="str">
+        <v>2025-09-30</v>
+      </c>
+      <c r="C91" t="str">
+        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
+      </c>
+      <c r="D91" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E91" t="str">
+        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
+      </c>
+      <c r="F91" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G91" t="str">
+        <v/>
+      </c>
+      <c r="H91" t="str">
+        <v/>
+      </c>
+      <c r="I91" t="str">
+        <v/>
+      </c>
+      <c r="J91" t="str">
+        <v/>
+      </c>
+      <c r="K91" t="str">
+        <v/>
+      </c>
+      <c r="L91" t="str">
+        <v/>
+      </c>
+      <c r="M91" t="str">
+        <v/>
+      </c>
+      <c r="N91" t="str">
+        <v/>
+      </c>
+      <c r="O91" t="str">
+        <v/>
+      </c>
+      <c r="P91" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>אד שירן Play</v>
+      </c>
+      <c r="B92" t="str">
+        <v>2025-09-24</v>
+      </c>
+      <c r="C92" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
+      </c>
+      <c r="D92" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E92" t="str">
+        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
+      </c>
+      <c r="F92" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G92" t="str">
+        <v/>
+      </c>
+      <c r="H92" t="str">
+        <v/>
+      </c>
+      <c r="I92" t="str">
+        <v/>
+      </c>
+      <c r="J92" t="str">
+        <v/>
+      </c>
+      <c r="K92" t="str">
+        <v/>
+      </c>
+      <c r="L92" t="str">
+        <v/>
+      </c>
+      <c r="M92" t="str">
+        <v/>
+      </c>
+      <c r="N92" t="str">
+        <v/>
+      </c>
+      <c r="O92" t="str">
+        <v/>
+      </c>
+      <c r="P92" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+      </c>
+      <c r="B93" t="str">
+        <v>2025-09-21</v>
+      </c>
+      <c r="C93" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
+      </c>
+      <c r="D93" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E93" t="str">
+        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
+      </c>
+      <c r="F93" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G93" t="str">
+        <v/>
+      </c>
+      <c r="H93" t="str">
+        <v/>
+      </c>
+      <c r="I93" t="str">
+        <v/>
+      </c>
+      <c r="J93" t="str">
+        <v/>
+      </c>
+      <c r="K93" t="str">
+        <v/>
+      </c>
+      <c r="L93" t="str">
+        <v/>
+      </c>
+      <c r="M93" t="str">
+        <v/>
+      </c>
+      <c r="N93" t="str">
+        <v/>
+      </c>
+      <c r="O93" t="str">
+        <v/>
+      </c>
+      <c r="P93" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>סוויד Antidepressants</v>
+      </c>
+      <c r="B94" t="str">
+        <v>2025-09-12</v>
+      </c>
+      <c r="C94" t="str">
+        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
+      </c>
+      <c r="D94" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E94" t="str">
+        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
+      </c>
+      <c r="F94" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G94" t="str">
+        <v/>
+      </c>
+      <c r="H94" t="str">
+        <v/>
+      </c>
+      <c r="I94" t="str">
+        <v/>
+      </c>
+      <c r="J94" t="str">
+        <v/>
+      </c>
+      <c r="K94" t="str">
+        <v/>
+      </c>
+      <c r="L94" t="str">
+        <v/>
+      </c>
+      <c r="M94" t="str">
+        <v/>
+      </c>
+      <c r="N94" t="str">
+        <v/>
+      </c>
+      <c r="O94" t="str">
+        <v/>
+      </c>
+      <c r="P94" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>וולף אליס The Clearing</v>
+      </c>
+      <c r="B95" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="C95" t="str">
+        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
+      </c>
+      <c r="D95" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E95" t="str">
+        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
+      </c>
+      <c r="F95" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G95" t="str">
+        <v/>
+      </c>
+      <c r="H95" t="str">
+        <v/>
+      </c>
+      <c r="I95" t="str">
+        <v/>
+      </c>
+      <c r="J95" t="str">
+        <v/>
+      </c>
+      <c r="K95" t="str">
+        <v/>
+      </c>
+      <c r="L95" t="str">
+        <v/>
+      </c>
+      <c r="M95" t="str">
+        <v/>
+      </c>
+      <c r="N95" t="str">
+        <v/>
+      </c>
+      <c r="O95" t="str">
+        <v/>
+      </c>
+      <c r="P95" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+      </c>
+      <c r="B96" t="str">
+        <v>2025-08-29</v>
+      </c>
+      <c r="C96" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
+      </c>
+      <c r="D96" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E96" t="str">
+        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
+      </c>
+      <c r="F96" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G96" t="str">
+        <v/>
+      </c>
+      <c r="H96" t="str">
+        <v/>
+      </c>
+      <c r="I96" t="str">
+        <v/>
+      </c>
+      <c r="J96" t="str">
+        <v/>
+      </c>
+      <c r="K96" t="str">
+        <v/>
+      </c>
+      <c r="L96" t="str">
+        <v/>
+      </c>
+      <c r="M96" t="str">
+        <v/>
+      </c>
+      <c r="N96" t="str">
+        <v/>
+      </c>
+      <c r="O96" t="str">
+        <v/>
+      </c>
+      <c r="P96" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+      </c>
+      <c r="B97" t="str">
+        <v>2025-08-24</v>
+      </c>
+      <c r="C97" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
+      </c>
+      <c r="D97" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E97" t="str">
+        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
+      </c>
+      <c r="F97" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G97" t="str">
+        <v/>
+      </c>
+      <c r="H97" t="str">
+        <v/>
+      </c>
+      <c r="I97" t="str">
+        <v/>
+      </c>
+      <c r="J97" t="str">
+        <v/>
+      </c>
+      <c r="K97" t="str">
+        <v/>
+      </c>
+      <c r="L97" t="str">
+        <v/>
+      </c>
+      <c r="M97" t="str">
+        <v/>
+      </c>
+      <c r="N97" t="str">
+        <v/>
+      </c>
+      <c r="O97" t="str">
+        <v/>
+      </c>
+      <c r="P97" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+      </c>
+      <c r="B98" t="str">
+        <v>2025-08-21</v>
+      </c>
+      <c r="C98" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
+      </c>
+      <c r="D98" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E98" t="str">
+        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
+      </c>
+      <c r="F98" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G98" t="str">
+        <v/>
+      </c>
+      <c r="H98" t="str">
+        <v/>
+      </c>
+      <c r="I98" t="str">
+        <v/>
+      </c>
+      <c r="J98" t="str">
+        <v/>
+      </c>
+      <c r="K98" t="str">
+        <v/>
+      </c>
+      <c r="L98" t="str">
+        <v/>
+      </c>
+      <c r="M98" t="str">
+        <v/>
+      </c>
+      <c r="N98" t="str">
+        <v/>
+      </c>
+      <c r="O98" t="str">
+        <v/>
+      </c>
+      <c r="P98" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>אברהם טל – חי</v>
+      </c>
+      <c r="B99" t="str">
+        <v>2025-08-17</v>
+      </c>
+      <c r="C99" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
+      </c>
+      <c r="D99" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E99" t="str">
+        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
+      </c>
+      <c r="F99" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G99" t="str">
+        <v/>
+      </c>
+      <c r="H99" t="str">
+        <v/>
+      </c>
+      <c r="I99" t="str">
+        <v/>
+      </c>
+      <c r="J99" t="str">
+        <v/>
+      </c>
+      <c r="K99" t="str">
+        <v/>
+      </c>
+      <c r="L99" t="str">
+        <v/>
+      </c>
+      <c r="M99" t="str">
+        <v/>
+      </c>
+      <c r="N99" t="str">
+        <v/>
+      </c>
+      <c r="O99" t="str">
+        <v/>
+      </c>
+      <c r="P99" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>רנה ראפ Bite Me</v>
+      </c>
+      <c r="B100" t="str">
+        <v>2025-08-12</v>
+      </c>
+      <c r="C100" t="str">
+        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
+      </c>
+      <c r="D100" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E100" t="str">
+        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
+      </c>
+      <c r="F100" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G100" t="str">
+        <v/>
+      </c>
+      <c r="H100" t="str">
+        <v/>
+      </c>
+      <c r="I100" t="str">
+        <v/>
+      </c>
+      <c r="J100" t="str">
+        <v/>
+      </c>
+      <c r="K100" t="str">
+        <v/>
+      </c>
+      <c r="L100" t="str">
+        <v/>
+      </c>
+      <c r="M100" t="str">
+        <v/>
+      </c>
+      <c r="N100" t="str">
+        <v/>
+      </c>
+      <c r="O100" t="str">
+        <v/>
+      </c>
+      <c r="P100" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>The K's – Pretty On The Internet</v>
+      </c>
+      <c r="B101" t="str">
+        <v>2025-08-03</v>
+      </c>
+      <c r="C101" t="str">
+        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
+      </c>
+      <c r="D101" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E101" t="str">
+        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
+      </c>
+      <c r="F101" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G101" t="str">
+        <v/>
+      </c>
+      <c r="H101" t="str">
+        <v/>
+      </c>
+      <c r="I101" t="str">
+        <v/>
+      </c>
+      <c r="J101" t="str">
+        <v/>
+      </c>
+      <c r="K101" t="str">
+        <v/>
+      </c>
+      <c r="L101" t="str">
+        <v/>
+      </c>
+      <c r="M101" t="str">
+        <v/>
+      </c>
+      <c r="N101" t="str">
+        <v/>
+      </c>
+      <c r="O101" t="str">
+        <v/>
+      </c>
+      <c r="P101" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>פליטווד מק Fifty Years – Don’t Stop</v>
+      </c>
+      <c r="B102" t="str">
+        <v>2025-07-30</v>
+      </c>
+      <c r="C102" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%99%d7%98%d7%95%d7%95%d7%93-%d7%9e%d7%a7-fifty-years-dont-stop/</v>
+      </c>
+      <c r="D102" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E102" t="str">
+        <v>פליטווד מק (Fleetwood Mac) חוגגים חצי מאה של מוזיקה עם אוסף חדש בן 50 שירים, שמתפרש על כל הקריירה של הלהקה, מימיה הראשונים בסגנון בלוז, ועד להצלחתה העולמית כאחת מלהקות הגדולות בהיסטוריה של הרוק. פליטווד מק הם לא רק להקה</v>
+      </c>
+      <c r="F102" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G102" t="str">
+        <v/>
+      </c>
+      <c r="H102" t="str">
+        <v/>
+      </c>
+      <c r="I102" t="str">
+        <v/>
+      </c>
+      <c r="J102" t="str">
+        <v/>
+      </c>
+      <c r="K102" t="str">
+        <v/>
+      </c>
+      <c r="L102" t="str">
+        <v/>
+      </c>
+      <c r="M102" t="str">
+        <v/>
+      </c>
+      <c r="N102" t="str">
+        <v/>
+      </c>
+      <c r="O102" t="str">
+        <v/>
+      </c>
+      <c r="P102" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
         <v>Wet Leg Moisturizer</v>
       </c>
-      <c r="B90" t="str">
+      <c r="B103" t="str">
         <v>2025-07-25</v>
       </c>
-      <c r="C90" t="str">
+      <c r="C103" t="str">
         <v>https://yosmusic.com/wet-leg-moisturizer/</v>
       </c>
-      <c r="D90" t="str">
-        <v>2026-01-08</v>
-      </c>
-      <c r="E90" t="str">
+      <c r="D103" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E103" t="str">
         <v>להקת Wet Leg לא הוציאה קרם לחות (Moisturizer) כמוצר טיפוח. במקום זאת, "Moisturizer" הוא שמו של האלבום השני והחדש שלהם. במרכז –  צמד אינדי-רוק המורכב מהחברות ריין טיסדייל והסטר צ'יימברס. אלבום הבכורה הנושא את שמה, הגיע למקום הראשון במצעד האלבומים</v>
       </c>
-      <c r="F90" t="str">
-        <v>אלבומים חדשים</v>
-      </c>
-      <c r="G90" t="str">
-        <v/>
-      </c>
-      <c r="H90" t="str">
-        <v/>
-      </c>
-      <c r="I90" t="str">
-        <v/>
-      </c>
-      <c r="J90" t="str">
-        <v/>
-      </c>
-      <c r="K90" t="str">
-        <v/>
-      </c>
-      <c r="L90" t="str">
-        <v/>
-      </c>
-      <c r="M90" t="str">
-        <v/>
-      </c>
-      <c r="N90" t="str">
+      <c r="F103" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G103" t="str">
+        <v/>
+      </c>
+      <c r="H103" t="str">
+        <v/>
+      </c>
+      <c r="I103" t="str">
+        <v/>
+      </c>
+      <c r="J103" t="str">
+        <v/>
+      </c>
+      <c r="K103" t="str">
+        <v/>
+      </c>
+      <c r="L103" t="str">
+        <v/>
+      </c>
+      <c r="M103" t="str">
+        <v/>
+      </c>
+      <c r="N103" t="str">
+        <v/>
+      </c>
+      <c r="O103" t="str">
+        <v/>
+      </c>
+      <c r="P103" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N90"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P103"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P103"/>
+  <dimension ref="A1:R104"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,19 +421,19 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>|אלבום חדש| תומר יוסף - 360 ()</v>
+        <v>פטריק סבג Hotel Mogador</v>
       </c>
       <c r="B2" t="str">
-        <v>2026  11:38-01-09</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-13</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>האלבום של פטריק סבג אינו אוסף שירים אקראי, אלא מרחב. מקום לשהות בו.  נכנסים, שומעים, ויוצאים קצת אחרים. הבחירה בשם "הוטל מוגדור” היא כבר הצהרה. מלון = מקום מעבר, לא בית קבוע, מוגדור = עיר נמל, תנועה, ערבוב תרבויות. כך</v>
       </c>
       <c r="F2" t="str">
         <v>אלבומים חדשים</v>
@@ -441,13 +441,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע ()</v>
+        <v>|אלבום חדש| תומר יוסף - 360 ()</v>
       </c>
       <c r="B3" t="str">
-        <v>2025  02:17-12-31</v>
+        <v>2026  11:38-01-09</v>
       </c>
       <c r="C3" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-10</v>
@@ -458,16 +458,22 @@
       <c r="F3" t="str">
         <v>אלבומים חדשים</v>
       </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>|אלבום חדש| אברהם טל - חי ()</v>
+        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע ()</v>
       </c>
       <c r="B4" t="str">
-        <v>2025  02:16-12-31</v>
+        <v>2025  02:17-12-31</v>
       </c>
       <c r="C4" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-10</v>
@@ -478,16 +484,22 @@
       <c r="F4" t="str">
         <v>אלבומים חדשים</v>
       </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>|אלבום חדש| מיקי גבריאלוב - שלום ()</v>
+        <v>|אלבום חדש| אברהם טל - חי ()</v>
       </c>
       <c r="B5" t="str">
-        <v>2025  02:13-12-31</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C5" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-10</v>
@@ -498,16 +510,22 @@
       <c r="F5" t="str">
         <v>אלבומים חדשים</v>
       </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם ()</v>
+        <v>|אלבום חדש| מיקי גבריאלוב - שלום ()</v>
       </c>
       <c r="B6" t="str">
-        <v>2025  02:12-12-31</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C6" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-10</v>
@@ -518,16 +536,22 @@
       <c r="F6" t="str">
         <v>אלבומים חדשים</v>
       </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון ()</v>
+        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם ()</v>
       </c>
       <c r="B7" t="str">
-        <v>2025  02:10-12-31</v>
+        <v>2025  02:12-12-31</v>
       </c>
       <c r="C7" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-10</v>
@@ -538,16 +562,22 @@
       <c r="F7" t="str">
         <v>אלבומים חדשים</v>
       </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה ()</v>
+        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון ()</v>
       </c>
       <c r="B8" t="str">
-        <v>2025  02:09-12-31</v>
+        <v>2025  02:10-12-31</v>
       </c>
       <c r="C8" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-10</v>
@@ -558,16 +588,22 @@
       <c r="F8" t="str">
         <v>אלבומים חדשים</v>
       </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים ()</v>
+        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה ()</v>
       </c>
       <c r="B9" t="str">
-        <v>2025  02:06-12-31</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C9" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-10</v>
@@ -578,16 +614,22 @@
       <c r="F9" t="str">
         <v>אלבומים חדשים</v>
       </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם ()</v>
+        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים ()</v>
       </c>
       <c r="B10" t="str">
-        <v>2025  02:05-12-31</v>
+        <v>2025  02:06-12-31</v>
       </c>
       <c r="C10" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-10</v>
@@ -598,16 +640,22 @@
       <c r="F10" t="str">
         <v>אלבומים חדשים</v>
       </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>|אלבום חדש| סטטיק - קעקועים ()</v>
+        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם ()</v>
       </c>
       <c r="B11" t="str">
-        <v>2025  02:03-12-31</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C11" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-10</v>
@@ -618,16 +666,22 @@
       <c r="F11" t="str">
         <v>אלבומים חדשים</v>
       </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>|אלבום חדש| ליאור נרקיס - דיסוננס ()</v>
+        <v>|אלבום חדש| סטטיק - קעקועים ()</v>
       </c>
       <c r="B12" t="str">
-        <v>2025  02:01-12-31</v>
+        <v>2025  02:03-12-31</v>
       </c>
       <c r="C12" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-10</v>
@@ -638,16 +692,22 @@
       <c r="F12" t="str">
         <v>אלבומים חדשים</v>
       </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) ()</v>
+        <v>|אלבום חדש| ליאור נרקיס - דיסוננס ()</v>
       </c>
       <c r="B13" t="str">
-        <v>2025  01:57-12-31</v>
+        <v>2025  02:01-12-31</v>
       </c>
       <c r="C13" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-10</v>
@@ -658,16 +718,22 @@
       <c r="F13" t="str">
         <v>אלבומים חדשים</v>
       </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>|אלבום חדש| אתניקס - איטליה ()</v>
+        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) ()</v>
       </c>
       <c r="B14" t="str">
-        <v>2025  01:55-12-31</v>
+        <v>2025  01:57-12-31</v>
       </c>
       <c r="C14" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-10</v>
@@ -678,19 +744,25 @@
       <c r="F14" t="str">
         <v>אלבומים חדשים</v>
       </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>|| תומר יוסף - 360 (2026)</v>
+        <v>|אלבום חדש| אתניקס - איטליה ()</v>
       </c>
       <c r="B15" t="str">
-        <v>2026  11:38-01-09</v>
+        <v>2025  01:55-12-31</v>
       </c>
       <c r="C15" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -707,13 +779,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>|| עמיר בניון - לא נוגע בקרקע ()</v>
+        <v>|| תומר יוסף - 360 (2026)</v>
       </c>
       <c r="B16" t="str">
-        <v>2025  02:17-12-31</v>
+        <v>2026  11:38-01-09</v>
       </c>
       <c r="C16" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-09</v>
@@ -730,16 +802,22 @@
       <c r="H16" t="str">
         <v/>
       </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>|| אברהם טל - חי ()</v>
+        <v>|| עמיר בניון - לא נוגע בקרקע ()</v>
       </c>
       <c r="B17" t="str">
-        <v>2025  02:16-12-31</v>
+        <v>2025  02:17-12-31</v>
       </c>
       <c r="C17" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-09</v>
@@ -756,16 +834,22 @@
       <c r="H17" t="str">
         <v/>
       </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>|| מיקי גבריאלוב - שלום ()</v>
+        <v>|| אברהם טל - חי ()</v>
       </c>
       <c r="B18" t="str">
-        <v>2025  02:13-12-31</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C18" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-09</v>
@@ -782,16 +866,22 @@
       <c r="H18" t="str">
         <v/>
       </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>|| בזכרי ימים ימימה - מחווה לצלילי הכרם ()</v>
+        <v>|| מיקי גבריאלוב - שלום ()</v>
       </c>
       <c r="B19" t="str">
-        <v>2025  02:12-12-31</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C19" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-09</v>
@@ -808,16 +898,22 @@
       <c r="H19" t="str">
         <v/>
       </c>
+      <c r="I19" t="str">
+        <v/>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>|| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון ()</v>
+        <v>|| בזכרי ימים ימימה - מחווה לצלילי הכרם ()</v>
       </c>
       <c r="B20" t="str">
-        <v>2025  02:10-12-31</v>
+        <v>2025  02:12-12-31</v>
       </c>
       <c r="C20" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-09</v>
@@ -834,16 +930,22 @@
       <c r="H20" t="str">
         <v/>
       </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>|| שלמה גרוניך - תודה אהבה ()</v>
+        <v>|| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון ()</v>
       </c>
       <c r="B21" t="str">
-        <v>2025  02:09-12-31</v>
+        <v>2025  02:10-12-31</v>
       </c>
       <c r="C21" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-09</v>
@@ -860,16 +962,22 @@
       <c r="H21" t="str">
         <v/>
       </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>|| חוה אלברשטיין - חמישה שירים ()</v>
+        <v>|| שלמה גרוניך - תודה אהבה ()</v>
       </c>
       <c r="B22" t="str">
-        <v>2025  02:06-12-31</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C22" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-09</v>
@@ -886,16 +994,22 @@
       <c r="H22" t="str">
         <v/>
       </c>
+      <c r="I22" t="str">
+        <v/>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>|| הפרויקט של עידן רייכל - עד סוף העולם ()</v>
+        <v>|| חוה אלברשטיין - חמישה שירים ()</v>
       </c>
       <c r="B23" t="str">
-        <v>2025  02:05-12-31</v>
+        <v>2025  02:06-12-31</v>
       </c>
       <c r="C23" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-09</v>
@@ -912,16 +1026,22 @@
       <c r="H23" t="str">
         <v/>
       </c>
+      <c r="I23" t="str">
+        <v/>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>|| סטטיק - קעקועים ()</v>
+        <v>|| הפרויקט של עידן רייכל - עד סוף העולם ()</v>
       </c>
       <c r="B24" t="str">
-        <v>2025  02:03-12-31</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C24" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-09</v>
@@ -938,16 +1058,22 @@
       <c r="H24" t="str">
         <v/>
       </c>
+      <c r="I24" t="str">
+        <v/>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>|| ליאור נרקיס - דיסוננס ()</v>
+        <v>|| סטטיק - קעקועים ()</v>
       </c>
       <c r="B25" t="str">
-        <v>2025  02:01-12-31</v>
+        <v>2025  02:03-12-31</v>
       </c>
       <c r="C25" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-09</v>
@@ -964,16 +1090,22 @@
       <c r="H25" t="str">
         <v/>
       </c>
+      <c r="I25" t="str">
+        <v/>
+      </c>
+      <c r="J25" t="str">
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>|| דיוויד ברוזה - BrozaJazz (Paris Alhambra) ()</v>
+        <v>|| ליאור נרקיס - דיסוננס ()</v>
       </c>
       <c r="B26" t="str">
-        <v>2025  01:57-12-31</v>
+        <v>2025  02:01-12-31</v>
       </c>
       <c r="C26" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-09</v>
@@ -990,16 +1122,22 @@
       <c r="H26" t="str">
         <v/>
       </c>
+      <c r="I26" t="str">
+        <v/>
+      </c>
+      <c r="J26" t="str">
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>|| אתניקס - איטליה ()</v>
+        <v>|| דיוויד ברוזה - BrozaJazz (Paris Alhambra) ()</v>
       </c>
       <c r="B27" t="str">
-        <v>2025  01:55-12-31</v>
+        <v>2025  01:57-12-31</v>
       </c>
       <c r="C27" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-09</v>
@@ -1016,22 +1154,28 @@
       <c r="H27" t="str">
         <v/>
       </c>
+      <c r="I27" t="str">
+        <v/>
+      </c>
+      <c r="J27" t="str">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>מארינה מקסימיליאן – ריק בחלל</v>
+        <v>|| אתניקס - איטליה ()</v>
       </c>
       <c r="B28" t="str">
-        <v>2026-01-09</v>
+        <v>2025  01:55-12-31</v>
       </c>
       <c r="C28" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-09</v>
       </c>
       <c r="E28" t="str">
-        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
+        <v/>
       </c>
       <c r="F28" t="str">
         <v>אלבומים חדשים</v>
@@ -1051,19 +1195,19 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>|| אייל גולן - בית מפואר ()</v>
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
       </c>
       <c r="B29" t="str">
-        <v>2025  02:18-12-31</v>
+        <v>2026-01-09</v>
       </c>
       <c r="C29" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E29" t="str">
-        <v/>
+        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
       </c>
       <c r="F29" t="str">
         <v>אלבומים חדשים</v>
@@ -1089,13 +1233,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>|| הפרויקט של דודי לוי ואבטיפוס - הפטריקים ()</v>
+        <v>|| אייל גולן - בית מפואר ()</v>
       </c>
       <c r="B30" t="str">
-        <v>2025  02:16-12-31</v>
+        <v>2025  02:18-12-31</v>
       </c>
       <c r="C30" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-08</v>
@@ -1122,18 +1266,24 @@
         <v/>
       </c>
       <c r="L30" t="str">
+        <v/>
+      </c>
+      <c r="M30" t="str">
+        <v/>
+      </c>
+      <c r="N30" t="str">
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>|| שיר לוי - ילד מוזר ()</v>
+        <v>|| הפרויקט של דודי לוי ואבטיפוס - הפטריקים ()</v>
       </c>
       <c r="B31" t="str">
-        <v>2025  02:14-12-31</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C31" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-08</v>
@@ -1160,18 +1310,24 @@
         <v/>
       </c>
       <c r="L31" t="str">
+        <v/>
+      </c>
+      <c r="M31" t="str">
+        <v/>
+      </c>
+      <c r="N31" t="str">
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>|| פיטר רוט - 50 ()</v>
+        <v>|| שיר לוי - ילד מוזר ()</v>
       </c>
       <c r="B32" t="str">
-        <v>2025  02:13-12-31</v>
+        <v>2025  02:14-12-31</v>
       </c>
       <c r="C32" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-08</v>
@@ -1198,18 +1354,24 @@
         <v/>
       </c>
       <c r="L32" t="str">
+        <v/>
+      </c>
+      <c r="M32" t="str">
+        <v/>
+      </c>
+      <c r="N32" t="str">
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>|| אגם בוחבוט - עשרים ואחת ()</v>
+        <v>|| פיטר רוט - 50 ()</v>
       </c>
       <c r="B33" t="str">
-        <v>2025  02:11-12-31</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C33" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-08</v>
@@ -1236,18 +1398,24 @@
         <v/>
       </c>
       <c r="L33" t="str">
+        <v/>
+      </c>
+      <c r="M33" t="str">
+        <v/>
+      </c>
+      <c r="N33" t="str">
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>|| רבקה זוהר - רסיסים של אור ()</v>
+        <v>|| אגם בוחבוט - עשרים ואחת ()</v>
       </c>
       <c r="B34" t="str">
-        <v>2025  02:09-12-31</v>
+        <v>2025  02:11-12-31</v>
       </c>
       <c r="C34" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-08</v>
@@ -1274,18 +1442,24 @@
         <v/>
       </c>
       <c r="L34" t="str">
+        <v/>
+      </c>
+      <c r="M34" t="str">
+        <v/>
+      </c>
+      <c r="N34" t="str">
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>|| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות ()</v>
+        <v>|| רבקה זוהר - רסיסים של אור ()</v>
       </c>
       <c r="B35" t="str">
-        <v>2025  02:08-12-31</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C35" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-08</v>
@@ -1312,18 +1486,24 @@
         <v/>
       </c>
       <c r="L35" t="str">
+        <v/>
+      </c>
+      <c r="M35" t="str">
+        <v/>
+      </c>
+      <c r="N35" t="str">
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>|| אהוד בנאי ובנו הנדלר - פליטי הדאב ()</v>
+        <v>|| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות ()</v>
       </c>
       <c r="B36" t="str">
-        <v>2025  02:05-12-31</v>
+        <v>2025  02:08-12-31</v>
       </c>
       <c r="C36" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-08</v>
@@ -1350,18 +1530,24 @@
         <v/>
       </c>
       <c r="L36" t="str">
+        <v/>
+      </c>
+      <c r="M36" t="str">
+        <v/>
+      </c>
+      <c r="N36" t="str">
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>|| Imagine פסטיגל - שירי התחרות ()</v>
+        <v>|| אהוד בנאי ובנו הנדלר - פליטי הדאב ()</v>
       </c>
       <c r="B37" t="str">
-        <v>2025  02:04-12-31</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C37" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-08</v>
@@ -1388,18 +1574,24 @@
         <v/>
       </c>
       <c r="L37" t="str">
+        <v/>
+      </c>
+      <c r="M37" t="str">
+        <v/>
+      </c>
+      <c r="N37" t="str">
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>|| השמחות - חובות אבודים ()</v>
+        <v>|| Imagine פסטיגל - שירי התחרות ()</v>
       </c>
       <c r="B38" t="str">
-        <v>2025  02:02-12-31</v>
+        <v>2025  02:04-12-31</v>
       </c>
       <c r="C38" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-08</v>
@@ -1426,18 +1618,24 @@
         <v/>
       </c>
       <c r="L38" t="str">
+        <v/>
+      </c>
+      <c r="M38" t="str">
+        <v/>
+      </c>
+      <c r="N38" t="str">
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>|| שלמה גרוניך - כמו כוכבים ()</v>
+        <v>|| השמחות - חובות אבודים ()</v>
       </c>
       <c r="B39" t="str">
-        <v>2025  02:00-12-31</v>
+        <v>2025  02:02-12-31</v>
       </c>
       <c r="C39" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-08</v>
@@ -1464,18 +1662,24 @@
         <v/>
       </c>
       <c r="L39" t="str">
+        <v/>
+      </c>
+      <c r="M39" t="str">
+        <v/>
+      </c>
+      <c r="N39" t="str">
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>|| יוני רועה - מפוזרים ()</v>
+        <v>|| שלמה גרוניך - כמו כוכבים ()</v>
       </c>
       <c r="B40" t="str">
-        <v>2025  01:56-12-31</v>
+        <v>2025  02:00-12-31</v>
       </c>
       <c r="C40" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-08</v>
@@ -1502,18 +1706,24 @@
         <v/>
       </c>
       <c r="L40" t="str">
+        <v/>
+      </c>
+      <c r="M40" t="str">
+        <v/>
+      </c>
+      <c r="N40" t="str">
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>|| התקווה 6 - ויהי אור ()</v>
+        <v>|| יוני רועה - מפוזרים ()</v>
       </c>
       <c r="B41" t="str">
-        <v>2025  01:54-12-31</v>
+        <v>2025  01:56-12-31</v>
       </c>
       <c r="C41" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-08</v>
@@ -1540,18 +1750,24 @@
         <v/>
       </c>
       <c r="L41" t="str">
+        <v/>
+      </c>
+      <c r="M41" t="str">
+        <v/>
+      </c>
+      <c r="N41" t="str">
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>|| שאנן סטריט ודי ג׳יי מש - באתי לבדר ()</v>
+        <v>|| התקווה 6 - ויהי אור ()</v>
       </c>
       <c r="B42" t="str">
-        <v>2025  01:53-12-31</v>
+        <v>2025  01:54-12-31</v>
       </c>
       <c r="C42" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-08</v>
@@ -1578,18 +1794,24 @@
         <v/>
       </c>
       <c r="L42" t="str">
+        <v/>
+      </c>
+      <c r="M42" t="str">
+        <v/>
+      </c>
+      <c r="N42" t="str">
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>אשכול נוכחות למשתמשים פעילים</v>
+        <v>|| שאנן סטריט ודי ג׳יי מש - באתי לבדר ()</v>
       </c>
       <c r="B43" t="str">
-        <v>2025  16:32 מאת freund-10-16</v>
+        <v>2025  01:53-12-31</v>
       </c>
       <c r="C43" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=23455&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-08</v>
@@ -1627,13 +1849,13 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>כיצד להוריד מהאתרים המפורסמים</v>
+        <v>אשכול נוכחות למשתמשים פעילים</v>
       </c>
       <c r="B44" t="str">
-        <v>2023  16:23 מאת petel1-08-08</v>
+        <v>2025  16:32 מאת freund-10-16</v>
       </c>
       <c r="C44" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=22411&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=23455&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-08</v>
@@ -1666,18 +1888,24 @@
         <v/>
       </c>
       <c r="N44" t="str">
+        <v/>
+      </c>
+      <c r="O44" t="str">
+        <v/>
+      </c>
+      <c r="P44" t="str">
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
+        <v>כיצד להוריד מהאתרים המפורסמים</v>
       </c>
       <c r="B45" t="str">
-        <v>2026  22:40 מאת מוטי_ד-01-01</v>
+        <v>2023  16:23 מאת petel1-08-08</v>
       </c>
       <c r="C45" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24435&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=22411&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-08</v>
@@ -1710,18 +1938,24 @@
         <v/>
       </c>
       <c r="N45" t="str">
+        <v/>
+      </c>
+      <c r="O45" t="str">
+        <v/>
+      </c>
+      <c r="P45" t="str">
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>|אלבום חדש| אייל גולן - בית מפואר (2025)</v>
+        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
       </c>
       <c r="B46" t="str">
-        <v>2025  02:18 מאת DiSHi-12-31</v>
+        <v>2026  22:40 מאת מוטי_ד-01-01</v>
       </c>
       <c r="C46" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24435&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-08</v>
@@ -1754,18 +1988,24 @@
         <v/>
       </c>
       <c r="N46" t="str">
+        <v/>
+      </c>
+      <c r="O46" t="str">
+        <v/>
+      </c>
+      <c r="P46" t="str">
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע (2025)</v>
+        <v>|אלבום חדש| אייל גולן - בית מפואר (2025)</v>
       </c>
       <c r="B47" t="str">
-        <v>2025  02:17 מאת DiSHi-12-31</v>
+        <v>2025  02:18 מאת DiSHi-12-31</v>
       </c>
       <c r="C47" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-08</v>
@@ -1798,18 +2038,24 @@
         <v/>
       </c>
       <c r="N47" t="str">
+        <v/>
+      </c>
+      <c r="O47" t="str">
+        <v/>
+      </c>
+      <c r="P47" t="str">
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>|אלבום חדש| הפרויקט של דודי לוי ואבטיפוס - הפטריקים (2025)</v>
+        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע (2025)</v>
       </c>
       <c r="B48" t="str">
-        <v>2025  02:16 מאת DiSHi-12-31</v>
+        <v>2025  02:17 מאת DiSHi-12-31</v>
       </c>
       <c r="C48" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-08</v>
@@ -1842,18 +2088,24 @@
         <v/>
       </c>
       <c r="N48" t="str">
+        <v/>
+      </c>
+      <c r="O48" t="str">
+        <v/>
+      </c>
+      <c r="P48" t="str">
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>|אלבום חדש| אברהם טל - חי (2025)</v>
+        <v>|אלבום חדש| הפרויקט של דודי לוי ואבטיפוס - הפטריקים (2025)</v>
       </c>
       <c r="B49" t="str">
         <v>2025  02:16 מאת DiSHi-12-31</v>
       </c>
       <c r="C49" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-08</v>
@@ -1886,18 +2138,24 @@
         <v/>
       </c>
       <c r="N49" t="str">
+        <v/>
+      </c>
+      <c r="O49" t="str">
+        <v/>
+      </c>
+      <c r="P49" t="str">
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>|אלבום חדש| שיר לוי - ילד מוזר (2025)</v>
+        <v>|אלבום חדש| אברהם טל - חי (2025)</v>
       </c>
       <c r="B50" t="str">
-        <v>2025  02:14 מאת DiSHi-12-31</v>
+        <v>2025  02:16 מאת DiSHi-12-31</v>
       </c>
       <c r="C50" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-08</v>
@@ -1930,18 +2188,24 @@
         <v/>
       </c>
       <c r="N50" t="str">
+        <v/>
+      </c>
+      <c r="O50" t="str">
+        <v/>
+      </c>
+      <c r="P50" t="str">
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>|אלבום חדש| מיקי גבריאלוב - שלום (2025)</v>
+        <v>|אלבום חדש| שיר לוי - ילד מוזר (2025)</v>
       </c>
       <c r="B51" t="str">
-        <v>2025  02:13 מאת DiSHi-12-31</v>
+        <v>2025  02:14 מאת DiSHi-12-31</v>
       </c>
       <c r="C51" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-08</v>
@@ -1974,18 +2238,24 @@
         <v/>
       </c>
       <c r="N51" t="str">
+        <v/>
+      </c>
+      <c r="O51" t="str">
+        <v/>
+      </c>
+      <c r="P51" t="str">
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>|אלבום חדש| פיטר רוט - 50 (2025)</v>
+        <v>|אלבום חדש| מיקי גבריאלוב - שלום (2025)</v>
       </c>
       <c r="B52" t="str">
         <v>2025  02:13 מאת DiSHi-12-31</v>
       </c>
       <c r="C52" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-08</v>
@@ -2018,18 +2288,24 @@
         <v/>
       </c>
       <c r="N52" t="str">
+        <v/>
+      </c>
+      <c r="O52" t="str">
+        <v/>
+      </c>
+      <c r="P52" t="str">
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם (2025)</v>
+        <v>|אלבום חדש| פיטר רוט - 50 (2025)</v>
       </c>
       <c r="B53" t="str">
-        <v>2025  02:12 מאת DiSHi-12-31</v>
+        <v>2025  02:13 מאת DiSHi-12-31</v>
       </c>
       <c r="C53" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-08</v>
@@ -2062,18 +2338,24 @@
         <v/>
       </c>
       <c r="N53" t="str">
+        <v/>
+      </c>
+      <c r="O53" t="str">
+        <v/>
+      </c>
+      <c r="P53" t="str">
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>|אלבום חדש| אגם בוחבוט - עשרים ואחת (2025)</v>
+        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם (2025)</v>
       </c>
       <c r="B54" t="str">
-        <v>2025  02:11 מאת DiSHi-12-31</v>
+        <v>2025  02:12 מאת DiSHi-12-31</v>
       </c>
       <c r="C54" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-08</v>
@@ -2106,18 +2388,24 @@
         <v/>
       </c>
       <c r="N54" t="str">
+        <v/>
+      </c>
+      <c r="O54" t="str">
+        <v/>
+      </c>
+      <c r="P54" t="str">
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון (2025)</v>
+        <v>|אלבום חדש| אגם בוחבוט - עשרים ואחת (2025)</v>
       </c>
       <c r="B55" t="str">
-        <v>2025  02:10 מאת DiSHi-12-31</v>
+        <v>2025  02:11 מאת DiSHi-12-31</v>
       </c>
       <c r="C55" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-08</v>
@@ -2150,18 +2438,24 @@
         <v/>
       </c>
       <c r="N55" t="str">
+        <v/>
+      </c>
+      <c r="O55" t="str">
+        <v/>
+      </c>
+      <c r="P55" t="str">
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>|אלבום חדש| רבקה זוהר - רסיסים של אור (2025)</v>
+        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון (2025)</v>
       </c>
       <c r="B56" t="str">
-        <v>2025  02:09 מאת DiSHi-12-31</v>
+        <v>2025  02:10 מאת DiSHi-12-31</v>
       </c>
       <c r="C56" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-08</v>
@@ -2194,18 +2488,24 @@
         <v/>
       </c>
       <c r="N56" t="str">
+        <v/>
+      </c>
+      <c r="O56" t="str">
+        <v/>
+      </c>
+      <c r="P56" t="str">
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה (2025)</v>
+        <v>|אלבום חדש| רבקה זוהר - רסיסים של אור (2025)</v>
       </c>
       <c r="B57" t="str">
         <v>2025  02:09 מאת DiSHi-12-31</v>
       </c>
       <c r="C57" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-08</v>
@@ -2238,18 +2538,24 @@
         <v/>
       </c>
       <c r="N57" t="str">
+        <v/>
+      </c>
+      <c r="O57" t="str">
+        <v/>
+      </c>
+      <c r="P57" t="str">
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>|אלבום חדש| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות (2025)</v>
+        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה (2025)</v>
       </c>
       <c r="B58" t="str">
-        <v>2025  02:08 מאת DiSHi-12-31</v>
+        <v>2025  02:09 מאת DiSHi-12-31</v>
       </c>
       <c r="C58" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-08</v>
@@ -2282,18 +2588,24 @@
         <v/>
       </c>
       <c r="N58" t="str">
+        <v/>
+      </c>
+      <c r="O58" t="str">
+        <v/>
+      </c>
+      <c r="P58" t="str">
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים (2025)</v>
+        <v>|אלבום חדש| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות (2025)</v>
       </c>
       <c r="B59" t="str">
-        <v>2025  02:06 מאת DiSHi-12-31</v>
+        <v>2025  02:08 מאת DiSHi-12-31</v>
       </c>
       <c r="C59" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-08</v>
@@ -2326,18 +2638,24 @@
         <v/>
       </c>
       <c r="N59" t="str">
+        <v/>
+      </c>
+      <c r="O59" t="str">
+        <v/>
+      </c>
+      <c r="P59" t="str">
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>|אלבום חדש| אהוד בנאי ובנו הנדלר - פליטי הדאב (2025)</v>
+        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים (2025)</v>
       </c>
       <c r="B60" t="str">
-        <v>2025  02:05 מאת DiSHi-12-31</v>
+        <v>2025  02:06 מאת DiSHi-12-31</v>
       </c>
       <c r="C60" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-08</v>
@@ -2370,18 +2688,24 @@
         <v/>
       </c>
       <c r="N60" t="str">
+        <v/>
+      </c>
+      <c r="O60" t="str">
+        <v/>
+      </c>
+      <c r="P60" t="str">
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם (2025)</v>
+        <v>|אלבום חדש| אהוד בנאי ובנו הנדלר - פליטי הדאב (2025)</v>
       </c>
       <c r="B61" t="str">
         <v>2025  02:05 מאת DiSHi-12-31</v>
       </c>
       <c r="C61" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-08</v>
@@ -2414,18 +2738,24 @@
         <v/>
       </c>
       <c r="N61" t="str">
+        <v/>
+      </c>
+      <c r="O61" t="str">
+        <v/>
+      </c>
+      <c r="P61" t="str">
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>|אלבום חדש| Imagine פסטיגל - שירי התחרות (2025)</v>
+        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם (2025)</v>
       </c>
       <c r="B62" t="str">
-        <v>2025  02:04 מאת DiSHi-12-31</v>
+        <v>2025  02:05 מאת DiSHi-12-31</v>
       </c>
       <c r="C62" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-08</v>
@@ -2458,18 +2788,24 @@
         <v/>
       </c>
       <c r="N62" t="str">
+        <v/>
+      </c>
+      <c r="O62" t="str">
+        <v/>
+      </c>
+      <c r="P62" t="str">
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>|אלבום חדש| סטטיק - קעקועים (2025)</v>
+        <v>|אלבום חדש| Imagine פסטיגל - שירי התחרות (2025)</v>
       </c>
       <c r="B63" t="str">
-        <v>2025  02:03 מאת DiSHi-12-31</v>
+        <v>2025  02:04 מאת DiSHi-12-31</v>
       </c>
       <c r="C63" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-08</v>
@@ -2502,18 +2838,24 @@
         <v/>
       </c>
       <c r="N63" t="str">
+        <v/>
+      </c>
+      <c r="O63" t="str">
+        <v/>
+      </c>
+      <c r="P63" t="str">
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>|אלבום חדש| השמחות - חובות אבודים (2025)</v>
+        <v>|אלבום חדש| סטטיק - קעקועים (2025)</v>
       </c>
       <c r="B64" t="str">
-        <v>2025  02:02 מאת DiSHi-12-31</v>
+        <v>2025  02:03 מאת DiSHi-12-31</v>
       </c>
       <c r="C64" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-08</v>
@@ -2546,18 +2888,24 @@
         <v/>
       </c>
       <c r="N64" t="str">
+        <v/>
+      </c>
+      <c r="O64" t="str">
+        <v/>
+      </c>
+      <c r="P64" t="str">
         <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>|אלבום חדש| ליאור נרקיס - דיסוננס (2025)</v>
+        <v>|אלבום חדש| השמחות - חובות אבודים (2025)</v>
       </c>
       <c r="B65" t="str">
-        <v>2025  02:01 מאת DiSHi-12-31</v>
+        <v>2025  02:02 מאת DiSHi-12-31</v>
       </c>
       <c r="C65" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-08</v>
@@ -2590,18 +2938,24 @@
         <v/>
       </c>
       <c r="N65" t="str">
+        <v/>
+      </c>
+      <c r="O65" t="str">
+        <v/>
+      </c>
+      <c r="P65" t="str">
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>|אלבום חדש| שלמה גרוניך - כמו כוכבים (2025)</v>
+        <v>|אלבום חדש| ליאור נרקיס - דיסוננס (2025)</v>
       </c>
       <c r="B66" t="str">
-        <v>2025  02:00 מאת DiSHi-12-31</v>
+        <v>2025  02:01 מאת DiSHi-12-31</v>
       </c>
       <c r="C66" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-08</v>
@@ -2634,18 +2988,24 @@
         <v/>
       </c>
       <c r="N66" t="str">
+        <v/>
+      </c>
+      <c r="O66" t="str">
+        <v/>
+      </c>
+      <c r="P66" t="str">
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) (2025)</v>
+        <v>|אלבום חדש| שלמה גרוניך - כמו כוכבים (2025)</v>
       </c>
       <c r="B67" t="str">
-        <v>2025  01:57 מאת DiSHi-12-31</v>
+        <v>2025  02:00 מאת DiSHi-12-31</v>
       </c>
       <c r="C67" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-08</v>
@@ -2678,18 +3038,24 @@
         <v/>
       </c>
       <c r="N67" t="str">
+        <v/>
+      </c>
+      <c r="O67" t="str">
+        <v/>
+      </c>
+      <c r="P67" t="str">
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>|אלבום חדש| יוני רועה - מפוזרים (2025)</v>
+        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) (2025)</v>
       </c>
       <c r="B68" t="str">
-        <v>2025  01:56 מאת DiSHi-12-31</v>
+        <v>2025  01:57 מאת DiSHi-12-31</v>
       </c>
       <c r="C68" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-08</v>
@@ -2722,18 +3088,24 @@
         <v/>
       </c>
       <c r="N68" t="str">
+        <v/>
+      </c>
+      <c r="O68" t="str">
+        <v/>
+      </c>
+      <c r="P68" t="str">
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>|אלבום חדש| אתניקס - איטליה (2025)</v>
+        <v>|אלבום חדש| יוני רועה - מפוזרים (2025)</v>
       </c>
       <c r="B69" t="str">
-        <v>2025  01:55 מאת DiSHi-12-31</v>
+        <v>2025  01:56 מאת DiSHi-12-31</v>
       </c>
       <c r="C69" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-08</v>
@@ -2766,18 +3138,24 @@
         <v/>
       </c>
       <c r="N69" t="str">
+        <v/>
+      </c>
+      <c r="O69" t="str">
+        <v/>
+      </c>
+      <c r="P69" t="str">
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>|אלבום חדש| התקווה 6 - ויהי אור (2025)</v>
+        <v>|אלבום חדש| אתניקס - איטליה (2025)</v>
       </c>
       <c r="B70" t="str">
-        <v>2025  01:54 מאת DiSHi-12-31</v>
+        <v>2025  01:55 מאת DiSHi-12-31</v>
       </c>
       <c r="C70" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-08</v>
@@ -2810,18 +3188,24 @@
         <v/>
       </c>
       <c r="N70" t="str">
+        <v/>
+      </c>
+      <c r="O70" t="str">
+        <v/>
+      </c>
+      <c r="P70" t="str">
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>|אלבום חדש| שלומי סרנגה - איפרכו (2025)</v>
+        <v>|אלבום חדש| התקווה 6 - ויהי אור (2025)</v>
       </c>
       <c r="B71" t="str">
-        <v>2025  01:53 מאת DiSHi-12-31</v>
+        <v>2025  01:54 מאת DiSHi-12-31</v>
       </c>
       <c r="C71" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24430&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-08</v>
@@ -2854,18 +3238,24 @@
         <v/>
       </c>
       <c r="N71" t="str">
+        <v/>
+      </c>
+      <c r="O71" t="str">
+        <v/>
+      </c>
+      <c r="P71" t="str">
         <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>|אלבום חדש| שאנן סטריט ודי ג׳יי מש - באתי לבדר (2025)</v>
+        <v>|אלבום חדש| שלומי סרנגה - איפרכו (2025)</v>
       </c>
       <c r="B72" t="str">
         <v>2025  01:53 מאת DiSHi-12-31</v>
       </c>
       <c r="C72" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24430&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-08</v>
@@ -2898,18 +3288,24 @@
         <v/>
       </c>
       <c r="N72" t="str">
+        <v/>
+      </c>
+      <c r="O72" t="str">
+        <v/>
+      </c>
+      <c r="P72" t="str">
         <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>הרשם לחברות מלאה</v>
+        <v>|אלבום חדש| שאנן סטריט ודי ג׳יי מש - באתי לבדר (2025)</v>
       </c>
       <c r="B73" t="str">
-        <v/>
+        <v>2025  01:53 מאת DiSHi-12-31</v>
       </c>
       <c r="C73" t="str">
-        <v>https://rotter.name/nor/members-new.html</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-08</v>
@@ -2942,24 +3338,30 @@
         <v/>
       </c>
       <c r="N73" t="str">
+        <v/>
+      </c>
+      <c r="O73" t="str">
+        <v/>
+      </c>
+      <c r="P73" t="str">
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>אוליביה דין The Art of Loving</v>
+        <v>הרשם לחברות מלאה</v>
       </c>
       <c r="B74" t="str">
-        <v>2026-01-04</v>
+        <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
+        <v>https://rotter.name/nor/members-new.html</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E74" t="str">
-        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
+        <v/>
       </c>
       <c r="F74" t="str">
         <v>אלבומים חדשים</v>
@@ -2997,19 +3399,19 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Geese Getting Killed</v>
+        <v>אוליביה דין The Art of Loving</v>
       </c>
       <c r="B75" t="str">
-        <v>2025-12-29</v>
+        <v>2026-01-04</v>
       </c>
       <c r="C75" t="str">
-        <v>https://yosmusic.com/geese-getting-killed/</v>
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E75" t="str">
-        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
+        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
       </c>
       <c r="F75" t="str">
         <v>אלבומים חדשים</v>
@@ -3042,24 +3444,30 @@
         <v/>
       </c>
       <c r="P75" t="str">
+        <v/>
+      </c>
+      <c r="Q75" t="str">
+        <v/>
+      </c>
+      <c r="R75" t="str">
         <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>רוסליה Lux</v>
+        <v>Geese Getting Killed</v>
       </c>
       <c r="B76" t="str">
-        <v>2025-12-25</v>
+        <v>2025-12-29</v>
       </c>
       <c r="C76" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
+        <v>https://yosmusic.com/geese-getting-killed/</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E76" t="str">
-        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
+        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
       </c>
       <c r="F76" t="str">
         <v>אלבומים חדשים</v>
@@ -3092,24 +3500,30 @@
         <v/>
       </c>
       <c r="P76" t="str">
+        <v/>
+      </c>
+      <c r="Q76" t="str">
+        <v/>
+      </c>
+      <c r="R76" t="str">
         <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>יאנגבלאד אירוסמית' one more time</v>
+        <v>רוסליה Lux</v>
       </c>
       <c r="B77" t="str">
-        <v>2025-12-17</v>
+        <v>2025-12-25</v>
       </c>
       <c r="C77" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E77" t="str">
-        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
+        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
       </c>
       <c r="F77" t="str">
         <v>אלבומים חדשים</v>
@@ -3142,24 +3556,30 @@
         <v/>
       </c>
       <c r="P77" t="str">
+        <v/>
+      </c>
+      <c r="Q77" t="str">
+        <v/>
+      </c>
+      <c r="R77" t="str">
         <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>פינק פלויד Wish You Were Here 50</v>
+        <v>יאנגבלאד אירוסמית' one more time</v>
       </c>
       <c r="B78" t="str">
-        <v>2025-12-14</v>
+        <v>2025-12-17</v>
       </c>
       <c r="C78" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
+        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E78" t="str">
-        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
+        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
       </c>
       <c r="F78" t="str">
         <v>אלבומים חדשים</v>
@@ -3192,24 +3612,30 @@
         <v/>
       </c>
       <c r="P78" t="str">
+        <v/>
+      </c>
+      <c r="Q78" t="str">
+        <v/>
+      </c>
+      <c r="R78" t="str">
         <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+        <v>פינק פלויד Wish You Were Here 50</v>
       </c>
       <c r="B79" t="str">
-        <v>2025-12-08</v>
+        <v>2025-12-14</v>
       </c>
       <c r="C79" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E79" t="str">
-        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
+        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
       </c>
       <c r="F79" t="str">
         <v>אלבומים חדשים</v>
@@ -3242,24 +3668,30 @@
         <v/>
       </c>
       <c r="P79" t="str">
+        <v/>
+      </c>
+      <c r="Q79" t="str">
+        <v/>
+      </c>
+      <c r="R79" t="str">
         <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>סטריי קידס DO IT (EP)</v>
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
       </c>
       <c r="B80" t="str">
-        <v>2025-12-04</v>
+        <v>2025-12-08</v>
       </c>
       <c r="C80" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
+        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E80" t="str">
-        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
+        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
       </c>
       <c r="F80" t="str">
         <v>אלבומים חדשים</v>
@@ -3292,24 +3724,30 @@
         <v/>
       </c>
       <c r="P80" t="str">
+        <v/>
+      </c>
+      <c r="Q80" t="str">
+        <v/>
+      </c>
+      <c r="R80" t="str">
         <v/>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>דויד ברוזה BROZAJAZZ</v>
+        <v>סטריי קידס DO IT (EP)</v>
       </c>
       <c r="B81" t="str">
-        <v>2025-11-30</v>
+        <v>2025-12-04</v>
       </c>
       <c r="C81" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
+        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E81" t="str">
-        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
+        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
       </c>
       <c r="F81" t="str">
         <v>אלבומים חדשים</v>
@@ -3342,24 +3780,30 @@
         <v/>
       </c>
       <c r="P81" t="str">
+        <v/>
+      </c>
+      <c r="Q81" t="str">
+        <v/>
+      </c>
+      <c r="R81" t="str">
         <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Five Seconds of Summer – Everyone's A Star</v>
+        <v>דויד ברוזה BROZAJAZZ</v>
       </c>
       <c r="B82" t="str">
-        <v>2025-11-24</v>
+        <v>2025-11-30</v>
       </c>
       <c r="C82" t="str">
-        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E82" t="str">
-        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
+        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
       </c>
       <c r="F82" t="str">
         <v>אלבומים חדשים</v>
@@ -3392,24 +3836,30 @@
         <v/>
       </c>
       <c r="P82" t="str">
+        <v/>
+      </c>
+      <c r="Q82" t="str">
+        <v/>
+      </c>
+      <c r="R82" t="str">
         <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>התקווה 6 – ויהי אור</v>
+        <v>Five Seconds of Summer – Everyone's A Star</v>
       </c>
       <c r="B83" t="str">
-        <v>2025-11-20</v>
+        <v>2025-11-24</v>
       </c>
       <c r="C83" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
+        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E83" t="str">
-        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
+        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
       </c>
       <c r="F83" t="str">
         <v>אלבומים חדשים</v>
@@ -3442,24 +3892,30 @@
         <v/>
       </c>
       <c r="P83" t="str">
+        <v/>
+      </c>
+      <c r="Q83" t="str">
+        <v/>
+      </c>
+      <c r="R83" t="str">
         <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>פלורנס אנד דה משין Everybody Scream</v>
+        <v>התקווה 6 – ויהי אור</v>
       </c>
       <c r="B84" t="str">
-        <v>2025-11-13</v>
+        <v>2025-11-20</v>
       </c>
       <c r="C84" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
+        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E84" t="str">
-        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
+        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
       </c>
       <c r="F84" t="str">
         <v>אלבומים חדשים</v>
@@ -3492,24 +3948,30 @@
         <v/>
       </c>
       <c r="P84" t="str">
+        <v/>
+      </c>
+      <c r="Q84" t="str">
+        <v/>
+      </c>
+      <c r="R84" t="str">
         <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>טיים אימפלה Deadbeat</v>
+        <v>פלורנס אנד דה משין Everybody Scream</v>
       </c>
       <c r="B85" t="str">
-        <v>2025-11-03</v>
+        <v>2025-11-13</v>
       </c>
       <c r="C85" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E85" t="str">
-        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
+        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
       </c>
       <c r="F85" t="str">
         <v>אלבומים חדשים</v>
@@ -3542,24 +4004,30 @@
         <v/>
       </c>
       <c r="P85" t="str">
+        <v/>
+      </c>
+      <c r="Q85" t="str">
+        <v/>
+      </c>
+      <c r="R85" t="str">
         <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+        <v>טיים אימפלה Deadbeat</v>
       </c>
       <c r="B86" t="str">
-        <v>2025-10-20</v>
+        <v>2025-11-03</v>
       </c>
       <c r="C86" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E86" t="str">
-        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
+        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
       </c>
       <c r="F86" t="str">
         <v>אלבומים חדשים</v>
@@ -3592,24 +4060,30 @@
         <v/>
       </c>
       <c r="P86" t="str">
+        <v/>
+      </c>
+      <c r="Q86" t="str">
+        <v/>
+      </c>
+      <c r="R86" t="str">
         <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>שלמה גרוניך – תודה אהבה</v>
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
       </c>
       <c r="B87" t="str">
-        <v>2025-10-18</v>
+        <v>2025-10-20</v>
       </c>
       <c r="C87" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
+        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E87" t="str">
-        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
+        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
       </c>
       <c r="F87" t="str">
         <v>אלבומים חדשים</v>
@@ -3642,24 +4116,30 @@
         <v/>
       </c>
       <c r="P87" t="str">
+        <v/>
+      </c>
+      <c r="Q87" t="str">
+        <v/>
+      </c>
+      <c r="R87" t="str">
         <v/>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>טיילור סוויפט The Life Of A Showgirl</v>
+        <v>שלמה גרוניך – תודה אהבה</v>
       </c>
       <c r="B88" t="str">
-        <v>2025-10-11</v>
+        <v>2025-10-18</v>
       </c>
       <c r="C88" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E88" t="str">
-        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
+        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
       </c>
       <c r="F88" t="str">
         <v>אלבומים חדשים</v>
@@ -3692,24 +4172,30 @@
         <v/>
       </c>
       <c r="P88" t="str">
+        <v/>
+      </c>
+      <c r="Q88" t="str">
+        <v/>
+      </c>
+      <c r="R88" t="str">
         <v/>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>דוג'ה קאט Vie</v>
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
       </c>
       <c r="B89" t="str">
-        <v>2025-10-04</v>
+        <v>2025-10-11</v>
       </c>
       <c r="C89" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E89" t="str">
-        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
+        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
       </c>
       <c r="F89" t="str">
         <v>אלבומים חדשים</v>
@@ -3742,24 +4228,30 @@
         <v/>
       </c>
       <c r="P89" t="str">
+        <v/>
+      </c>
+      <c r="Q89" t="str">
+        <v/>
+      </c>
+      <c r="R89" t="str">
         <v/>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>ג'וי קרוקס Juniper</v>
+        <v>דוג'ה קאט Vie</v>
       </c>
       <c r="B90" t="str">
-        <v>2025-10-03</v>
+        <v>2025-10-04</v>
       </c>
       <c r="C90" t="str">
-        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
       </c>
       <c r="D90" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E90" t="str">
-        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
+        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
       </c>
       <c r="F90" t="str">
         <v>אלבומים חדשים</v>
@@ -3792,24 +4284,30 @@
         <v/>
       </c>
       <c r="P90" t="str">
+        <v/>
+      </c>
+      <c r="Q90" t="str">
+        <v/>
+      </c>
+      <c r="R90" t="str">
         <v/>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>ביפי קליירו Futique</v>
+        <v>ג'וי קרוקס Juniper</v>
       </c>
       <c r="B91" t="str">
-        <v>2025-09-30</v>
+        <v>2025-10-03</v>
       </c>
       <c r="C91" t="str">
-        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
+        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
       </c>
       <c r="D91" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E91" t="str">
-        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
+        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
       </c>
       <c r="F91" t="str">
         <v>אלבומים חדשים</v>
@@ -3842,24 +4340,30 @@
         <v/>
       </c>
       <c r="P91" t="str">
+        <v/>
+      </c>
+      <c r="Q91" t="str">
+        <v/>
+      </c>
+      <c r="R91" t="str">
         <v/>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>אד שירן Play</v>
+        <v>ביפי קליירו Futique</v>
       </c>
       <c r="B92" t="str">
-        <v>2025-09-24</v>
+        <v>2025-09-30</v>
       </c>
       <c r="C92" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
+        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
       </c>
       <c r="D92" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E92" t="str">
-        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
+        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
       </c>
       <c r="F92" t="str">
         <v>אלבומים חדשים</v>
@@ -3892,24 +4396,30 @@
         <v/>
       </c>
       <c r="P92" t="str">
+        <v/>
+      </c>
+      <c r="Q92" t="str">
+        <v/>
+      </c>
+      <c r="R92" t="str">
         <v/>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+        <v>אד שירן Play</v>
       </c>
       <c r="B93" t="str">
-        <v>2025-09-21</v>
+        <v>2025-09-24</v>
       </c>
       <c r="C93" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
+        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
       </c>
       <c r="D93" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E93" t="str">
-        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
+        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
       </c>
       <c r="F93" t="str">
         <v>אלבומים חדשים</v>
@@ -3942,24 +4452,30 @@
         <v/>
       </c>
       <c r="P93" t="str">
+        <v/>
+      </c>
+      <c r="Q93" t="str">
+        <v/>
+      </c>
+      <c r="R93" t="str">
         <v/>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>סוויד Antidepressants</v>
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
       </c>
       <c r="B94" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-21</v>
       </c>
       <c r="C94" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
+        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
       </c>
       <c r="D94" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E94" t="str">
-        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
+        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
       </c>
       <c r="F94" t="str">
         <v>אלבומים חדשים</v>
@@ -3992,24 +4508,30 @@
         <v/>
       </c>
       <c r="P94" t="str">
+        <v/>
+      </c>
+      <c r="Q94" t="str">
+        <v/>
+      </c>
+      <c r="R94" t="str">
         <v/>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>וולף אליס The Clearing</v>
+        <v>סוויד Antidepressants</v>
       </c>
       <c r="B95" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-12</v>
       </c>
       <c r="C95" t="str">
-        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
+        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
       </c>
       <c r="D95" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E95" t="str">
-        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
+        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
       </c>
       <c r="F95" t="str">
         <v>אלבומים חדשים</v>
@@ -4042,24 +4564,30 @@
         <v/>
       </c>
       <c r="P95" t="str">
+        <v/>
+      </c>
+      <c r="Q95" t="str">
+        <v/>
+      </c>
+      <c r="R95" t="str">
         <v/>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+        <v>וולף אליס The Clearing</v>
       </c>
       <c r="B96" t="str">
-        <v>2025-08-29</v>
+        <v>2025-09-01</v>
       </c>
       <c r="C96" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
+        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
       </c>
       <c r="D96" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E96" t="str">
-        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
+        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
       </c>
       <c r="F96" t="str">
         <v>אלבומים חדשים</v>
@@ -4092,24 +4620,30 @@
         <v/>
       </c>
       <c r="P96" t="str">
+        <v/>
+      </c>
+      <c r="Q96" t="str">
+        <v/>
+      </c>
+      <c r="R96" t="str">
         <v/>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
       </c>
       <c r="B97" t="str">
-        <v>2025-08-24</v>
+        <v>2025-08-29</v>
       </c>
       <c r="C97" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
+        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
       </c>
       <c r="D97" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E97" t="str">
-        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
+        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
       </c>
       <c r="F97" t="str">
         <v>אלבומים חדשים</v>
@@ -4142,24 +4676,30 @@
         <v/>
       </c>
       <c r="P97" t="str">
+        <v/>
+      </c>
+      <c r="Q97" t="str">
+        <v/>
+      </c>
+      <c r="R97" t="str">
         <v/>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
       </c>
       <c r="B98" t="str">
-        <v>2025-08-21</v>
+        <v>2025-08-24</v>
       </c>
       <c r="C98" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
+        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
       </c>
       <c r="D98" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E98" t="str">
-        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
+        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
       </c>
       <c r="F98" t="str">
         <v>אלבומים חדשים</v>
@@ -4192,24 +4732,30 @@
         <v/>
       </c>
       <c r="P98" t="str">
+        <v/>
+      </c>
+      <c r="Q98" t="str">
+        <v/>
+      </c>
+      <c r="R98" t="str">
         <v/>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>אברהם טל – חי</v>
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
       </c>
       <c r="B99" t="str">
-        <v>2025-08-17</v>
+        <v>2025-08-21</v>
       </c>
       <c r="C99" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
       </c>
       <c r="D99" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E99" t="str">
-        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
+        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
       </c>
       <c r="F99" t="str">
         <v>אלבומים חדשים</v>
@@ -4242,24 +4788,30 @@
         <v/>
       </c>
       <c r="P99" t="str">
+        <v/>
+      </c>
+      <c r="Q99" t="str">
+        <v/>
+      </c>
+      <c r="R99" t="str">
         <v/>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>רנה ראפ Bite Me</v>
+        <v>אברהם טל – חי</v>
       </c>
       <c r="B100" t="str">
-        <v>2025-08-12</v>
+        <v>2025-08-17</v>
       </c>
       <c r="C100" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
       </c>
       <c r="D100" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E100" t="str">
-        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
+        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
       </c>
       <c r="F100" t="str">
         <v>אלבומים חדשים</v>
@@ -4292,24 +4844,30 @@
         <v/>
       </c>
       <c r="P100" t="str">
+        <v/>
+      </c>
+      <c r="Q100" t="str">
+        <v/>
+      </c>
+      <c r="R100" t="str">
         <v/>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>The K's – Pretty On The Internet</v>
+        <v>רנה ראפ Bite Me</v>
       </c>
       <c r="B101" t="str">
-        <v>2025-08-03</v>
+        <v>2025-08-12</v>
       </c>
       <c r="C101" t="str">
-        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
+        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
       </c>
       <c r="D101" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E101" t="str">
-        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
+        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
       </c>
       <c r="F101" t="str">
         <v>אלבומים חדשים</v>
@@ -4342,24 +4900,30 @@
         <v/>
       </c>
       <c r="P101" t="str">
+        <v/>
+      </c>
+      <c r="Q101" t="str">
+        <v/>
+      </c>
+      <c r="R101" t="str">
         <v/>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>פליטווד מק Fifty Years – Don’t Stop</v>
+        <v>The K's – Pretty On The Internet</v>
       </c>
       <c r="B102" t="str">
-        <v>2025-07-30</v>
+        <v>2025-08-03</v>
       </c>
       <c r="C102" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%99%d7%98%d7%95%d7%95%d7%93-%d7%9e%d7%a7-fifty-years-dont-stop/</v>
+        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
       </c>
       <c r="D102" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E102" t="str">
-        <v>פליטווד מק (Fleetwood Mac) חוגגים חצי מאה של מוזיקה עם אוסף חדש בן 50 שירים, שמתפרש על כל הקריירה של הלהקה, מימיה הראשונים בסגנון בלוז, ועד להצלחתה העולמית כאחת מלהקות הגדולות בהיסטוריה של הרוק. פליטווד מק הם לא רק להקה</v>
+        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
       </c>
       <c r="F102" t="str">
         <v>אלבומים חדשים</v>
@@ -4392,62 +4956,130 @@
         <v/>
       </c>
       <c r="P102" t="str">
+        <v/>
+      </c>
+      <c r="Q102" t="str">
+        <v/>
+      </c>
+      <c r="R102" t="str">
         <v/>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
+        <v>פליטווד מק Fifty Years – Don’t Stop</v>
+      </c>
+      <c r="B103" t="str">
+        <v>2025-07-30</v>
+      </c>
+      <c r="C103" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%99%d7%98%d7%95%d7%95%d7%93-%d7%9e%d7%a7-fifty-years-dont-stop/</v>
+      </c>
+      <c r="D103" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E103" t="str">
+        <v>פליטווד מק (Fleetwood Mac) חוגגים חצי מאה של מוזיקה עם אוסף חדש בן 50 שירים, שמתפרש על כל הקריירה של הלהקה, מימיה הראשונים בסגנון בלוז, ועד להצלחתה העולמית כאחת מלהקות הגדולות בהיסטוריה של הרוק. פליטווד מק הם לא רק להקה</v>
+      </c>
+      <c r="F103" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G103" t="str">
+        <v/>
+      </c>
+      <c r="H103" t="str">
+        <v/>
+      </c>
+      <c r="I103" t="str">
+        <v/>
+      </c>
+      <c r="J103" t="str">
+        <v/>
+      </c>
+      <c r="K103" t="str">
+        <v/>
+      </c>
+      <c r="L103" t="str">
+        <v/>
+      </c>
+      <c r="M103" t="str">
+        <v/>
+      </c>
+      <c r="N103" t="str">
+        <v/>
+      </c>
+      <c r="O103" t="str">
+        <v/>
+      </c>
+      <c r="P103" t="str">
+        <v/>
+      </c>
+      <c r="Q103" t="str">
+        <v/>
+      </c>
+      <c r="R103" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
         <v>Wet Leg Moisturizer</v>
       </c>
-      <c r="B103" t="str">
+      <c r="B104" t="str">
         <v>2025-07-25</v>
       </c>
-      <c r="C103" t="str">
+      <c r="C104" t="str">
         <v>https://yosmusic.com/wet-leg-moisturizer/</v>
       </c>
-      <c r="D103" t="str">
-        <v>2026-01-08</v>
-      </c>
-      <c r="E103" t="str">
+      <c r="D104" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E104" t="str">
         <v>להקת Wet Leg לא הוציאה קרם לחות (Moisturizer) כמוצר טיפוח. במקום זאת, "Moisturizer" הוא שמו של האלבום השני והחדש שלהם. במרכז –  צמד אינדי-רוק המורכב מהחברות ריין טיסדייל והסטר צ'יימברס. אלבום הבכורה הנושא את שמה, הגיע למקום הראשון במצעד האלבומים</v>
       </c>
-      <c r="F103" t="str">
-        <v>אלבומים חדשים</v>
-      </c>
-      <c r="G103" t="str">
-        <v/>
-      </c>
-      <c r="H103" t="str">
-        <v/>
-      </c>
-      <c r="I103" t="str">
-        <v/>
-      </c>
-      <c r="J103" t="str">
-        <v/>
-      </c>
-      <c r="K103" t="str">
-        <v/>
-      </c>
-      <c r="L103" t="str">
-        <v/>
-      </c>
-      <c r="M103" t="str">
-        <v/>
-      </c>
-      <c r="N103" t="str">
-        <v/>
-      </c>
-      <c r="O103" t="str">
-        <v/>
-      </c>
-      <c r="P103" t="str">
+      <c r="F104" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G104" t="str">
+        <v/>
+      </c>
+      <c r="H104" t="str">
+        <v/>
+      </c>
+      <c r="I104" t="str">
+        <v/>
+      </c>
+      <c r="J104" t="str">
+        <v/>
+      </c>
+      <c r="K104" t="str">
+        <v/>
+      </c>
+      <c r="L104" t="str">
+        <v/>
+      </c>
+      <c r="M104" t="str">
+        <v/>
+      </c>
+      <c r="N104" t="str">
+        <v/>
+      </c>
+      <c r="O104" t="str">
+        <v/>
+      </c>
+      <c r="P104" t="str">
+        <v/>
+      </c>
+      <c r="Q104" t="str">
+        <v/>
+      </c>
+      <c r="R104" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P103"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R104"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R104"/>
+  <dimension ref="A1:T118"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,19 +421,19 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>פטריק סבג Hotel Mogador</v>
+        <v>תומר יוסף - 360</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-01-13</v>
+        <v>2026  08:40-01-14</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-13</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E2" t="str">
-        <v>האלבום של פטריק סבג אינו אוסף שירים אקראי, אלא מרחב. מקום לשהות בו.  נכנסים, שומעים, ויוצאים קצת אחרים. הבחירה בשם "הוטל מוגדור” היא כבר הצהרה. מלון = מקום מעבר, לא בית קבוע, מוגדור = עיר נמל, תנועה, ערבוב תרבויות. כך</v>
+        <v/>
       </c>
       <c r="F2" t="str">
         <v>אלבומים חדשים</v>
@@ -441,357 +441,279 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>|אלבום חדש| תומר יוסף - 360 ()</v>
+        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
       </c>
       <c r="B3" t="str">
-        <v>2026  11:38-01-09</v>
+        <v>2026  08:40-01-14</v>
       </c>
       <c r="C3" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24439&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
         <v>אלבומים חדשים</v>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע ()</v>
+        <v>אייל גולן - בית מפואר</v>
       </c>
       <c r="B4" t="str">
-        <v>2025  02:17-12-31</v>
+        <v>2025  02:18-12-31</v>
       </c>
       <c r="C4" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
         <v>אלבומים חדשים</v>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>|אלבום חדש| אברהם טל - חי ()</v>
+        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
       </c>
       <c r="B5" t="str">
         <v>2025  02:16-12-31</v>
       </c>
       <c r="C5" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
         <v>אלבומים חדשים</v>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>|אלבום חדש| מיקי גבריאלוב - שלום ()</v>
+        <v>שיר לוי - ילד מוזר</v>
       </c>
       <c r="B6" t="str">
-        <v>2025  02:13-12-31</v>
+        <v>2025  02:14-12-31</v>
       </c>
       <c r="C6" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
         <v>אלבומים חדשים</v>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם ()</v>
+        <v>פיטר רוט - 50</v>
       </c>
       <c r="B7" t="str">
-        <v>2025  02:12-12-31</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C7" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
         <v>אלבומים חדשים</v>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון ()</v>
+        <v>אגם בוחבוט - עשרים ואחת</v>
       </c>
       <c r="B8" t="str">
-        <v>2025  02:10-12-31</v>
+        <v>2025  02:11-12-31</v>
       </c>
       <c r="C8" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
         <v>אלבומים חדשים</v>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה ()</v>
+        <v>רבקה זוהר - רסיסים של אור</v>
       </c>
       <c r="B9" t="str">
         <v>2025  02:09-12-31</v>
       </c>
       <c r="C9" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
         <v>אלבומים חדשים</v>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים ()</v>
+        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
       </c>
       <c r="B10" t="str">
-        <v>2025  02:06-12-31</v>
+        <v>2025  02:08-12-31</v>
       </c>
       <c r="C10" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
         <v>אלבומים חדשים</v>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם ()</v>
+        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
       </c>
       <c r="B11" t="str">
         <v>2025  02:05-12-31</v>
       </c>
       <c r="C11" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
         <v>אלבומים חדשים</v>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>|אלבום חדש| סטטיק - קעקועים ()</v>
+        <v>Imagine פסטיגל - שירי התחרות</v>
       </c>
       <c r="B12" t="str">
-        <v>2025  02:03-12-31</v>
+        <v>2025  02:04-12-31</v>
       </c>
       <c r="C12" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
         <v>אלבומים חדשים</v>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>|אלבום חדש| ליאור נרקיס - דיסוננס ()</v>
+        <v>השמחות - חובות אבודים</v>
       </c>
       <c r="B13" t="str">
-        <v>2025  02:01-12-31</v>
+        <v>2025  02:02-12-31</v>
       </c>
       <c r="C13" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
         <v>אלבומים חדשים</v>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) ()</v>
+        <v>שלמה גרוניך - כמו כוכבים</v>
       </c>
       <c r="B14" t="str">
-        <v>2025  01:57-12-31</v>
+        <v>2025  02:00-12-31</v>
       </c>
       <c r="C14" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
         <v>אלבומים חדשים</v>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14" t="str">
-        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>|אלבום חדש| אתניקס - איטליה ()</v>
+        <v>יוני רועה - מפוזרים</v>
       </c>
       <c r="B15" t="str">
-        <v>2025  01:55-12-31</v>
+        <v>2025  01:56-12-31</v>
       </c>
       <c r="C15" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
         <v>אלבומים חדשים</v>
-      </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
-      <c r="H15" t="str">
-        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>|| תומר יוסף - 360 (2026)</v>
+        <v>פטריק סבג Hotel Mogador</v>
       </c>
       <c r="B16" t="str">
-        <v>2026  11:38-01-09</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C16" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-13</v>
       </c>
       <c r="E16" t="str">
-        <v/>
+        <v>האלבום של פטריק סבג אינו אוסף שירים אקראי, אלא מרחב. מקום לשהות בו.  נכנסים, שומעים, ויוצאים קצת אחרים. הבחירה בשם "הוטל מוגדור” היא כבר הצהרה. מלון = מקום מעבר, לא בית קבוע, מוגדור = עיר נמל, תנועה, ערבוב תרבויות. כך</v>
       </c>
       <c r="F16" t="str">
         <v>אלבומים חדשים</v>
@@ -800,27 +722,21 @@
         <v/>
       </c>
       <c r="H16" t="str">
-        <v/>
-      </c>
-      <c r="I16" t="str">
-        <v/>
-      </c>
-      <c r="J16" t="str">
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>|| עמיר בניון - לא נוגע בקרקע ()</v>
+        <v>|אלבום חדש| תומר יוסף - 360 ()</v>
       </c>
       <c r="B17" t="str">
-        <v>2025  02:17-12-31</v>
+        <v>2026  11:38-01-09</v>
       </c>
       <c r="C17" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -843,16 +759,16 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>|| אברהם טל - חי ()</v>
+        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע ()</v>
       </c>
       <c r="B18" t="str">
-        <v>2025  02:16-12-31</v>
+        <v>2025  02:17-12-31</v>
       </c>
       <c r="C18" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -875,16 +791,16 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>|| מיקי גבריאלוב - שלום ()</v>
+        <v>|אלבום חדש| אברהם טל - חי ()</v>
       </c>
       <c r="B19" t="str">
-        <v>2025  02:13-12-31</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C19" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -907,16 +823,16 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>|| בזכרי ימים ימימה - מחווה לצלילי הכרם ()</v>
+        <v>|אלבום חדש| מיקי גבריאלוב - שלום ()</v>
       </c>
       <c r="B20" t="str">
-        <v>2025  02:12-12-31</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C20" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -939,16 +855,16 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>|| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון ()</v>
+        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם ()</v>
       </c>
       <c r="B21" t="str">
-        <v>2025  02:10-12-31</v>
+        <v>2025  02:12-12-31</v>
       </c>
       <c r="C21" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -971,16 +887,16 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>|| שלמה גרוניך - תודה אהבה ()</v>
+        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון ()</v>
       </c>
       <c r="B22" t="str">
-        <v>2025  02:09-12-31</v>
+        <v>2025  02:10-12-31</v>
       </c>
       <c r="C22" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1003,16 +919,16 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>|| חוה אלברשטיין - חמישה שירים ()</v>
+        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה ()</v>
       </c>
       <c r="B23" t="str">
-        <v>2025  02:06-12-31</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C23" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1035,16 +951,16 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>|| הפרויקט של עידן רייכל - עד סוף העולם ()</v>
+        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים ()</v>
       </c>
       <c r="B24" t="str">
-        <v>2025  02:05-12-31</v>
+        <v>2025  02:06-12-31</v>
       </c>
       <c r="C24" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1067,16 +983,16 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>|| סטטיק - קעקועים ()</v>
+        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם ()</v>
       </c>
       <c r="B25" t="str">
-        <v>2025  02:03-12-31</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C25" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1099,16 +1015,16 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>|| ליאור נרקיס - דיסוננס ()</v>
+        <v>|אלבום חדש| סטטיק - קעקועים ()</v>
       </c>
       <c r="B26" t="str">
-        <v>2025  02:01-12-31</v>
+        <v>2025  02:03-12-31</v>
       </c>
       <c r="C26" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1131,16 +1047,16 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>|| דיוויד ברוזה - BrozaJazz (Paris Alhambra) ()</v>
+        <v>|אלבום חדש| ליאור נרקיס - דיסוננס ()</v>
       </c>
       <c r="B27" t="str">
-        <v>2025  01:57-12-31</v>
+        <v>2025  02:01-12-31</v>
       </c>
       <c r="C27" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1163,16 +1079,16 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>|| אתניקס - איטליה ()</v>
+        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) ()</v>
       </c>
       <c r="B28" t="str">
-        <v>2025  01:55-12-31</v>
+        <v>2025  01:57-12-31</v>
       </c>
       <c r="C28" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1195,19 +1111,19 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>מארינה מקסימיליאן – ריק בחלל</v>
+        <v>|אלבום חדש| אתניקס - איטליה ()</v>
       </c>
       <c r="B29" t="str">
-        <v>2026-01-09</v>
+        <v>2025  01:55-12-31</v>
       </c>
       <c r="C29" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E29" t="str">
-        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
+        <v/>
       </c>
       <c r="F29" t="str">
         <v>אלבומים חדשים</v>
@@ -1222,27 +1138,21 @@
         <v/>
       </c>
       <c r="J29" t="str">
-        <v/>
-      </c>
-      <c r="K29" t="str">
-        <v/>
-      </c>
-      <c r="L29" t="str">
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>|| אייל גולן - בית מפואר ()</v>
+        <v>|| תומר יוסף - 360 (2026)</v>
       </c>
       <c r="B30" t="str">
-        <v>2025  02:18-12-31</v>
+        <v>2026  11:38-01-09</v>
       </c>
       <c r="C30" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1266,27 +1176,21 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v/>
-      </c>
-      <c r="M30" t="str">
-        <v/>
-      </c>
-      <c r="N30" t="str">
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>|| הפרויקט של דודי לוי ואבטיפוס - הפטריקים ()</v>
+        <v>|| עמיר בניון - לא נוגע בקרקע ()</v>
       </c>
       <c r="B31" t="str">
-        <v>2025  02:16-12-31</v>
+        <v>2025  02:17-12-31</v>
       </c>
       <c r="C31" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1310,27 +1214,21 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v/>
-      </c>
-      <c r="M31" t="str">
-        <v/>
-      </c>
-      <c r="N31" t="str">
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>|| שיר לוי - ילד מוזר ()</v>
+        <v>|| אברהם טל - חי ()</v>
       </c>
       <c r="B32" t="str">
-        <v>2025  02:14-12-31</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C32" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1354,27 +1252,21 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v/>
-      </c>
-      <c r="M32" t="str">
-        <v/>
-      </c>
-      <c r="N32" t="str">
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>|| פיטר רוט - 50 ()</v>
+        <v>|| מיקי גבריאלוב - שלום ()</v>
       </c>
       <c r="B33" t="str">
         <v>2025  02:13-12-31</v>
       </c>
       <c r="C33" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1398,27 +1290,21 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v/>
-      </c>
-      <c r="M33" t="str">
-        <v/>
-      </c>
-      <c r="N33" t="str">
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>|| אגם בוחבוט - עשרים ואחת ()</v>
+        <v>|| בזכרי ימים ימימה - מחווה לצלילי הכרם ()</v>
       </c>
       <c r="B34" t="str">
-        <v>2025  02:11-12-31</v>
+        <v>2025  02:12-12-31</v>
       </c>
       <c r="C34" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1442,27 +1328,21 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v/>
-      </c>
-      <c r="M34" t="str">
-        <v/>
-      </c>
-      <c r="N34" t="str">
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>|| רבקה זוהר - רסיסים של אור ()</v>
+        <v>|| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון ()</v>
       </c>
       <c r="B35" t="str">
-        <v>2025  02:09-12-31</v>
+        <v>2025  02:10-12-31</v>
       </c>
       <c r="C35" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1486,27 +1366,21 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v/>
-      </c>
-      <c r="M35" t="str">
-        <v/>
-      </c>
-      <c r="N35" t="str">
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>|| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות ()</v>
+        <v>|| שלמה גרוניך - תודה אהבה ()</v>
       </c>
       <c r="B36" t="str">
-        <v>2025  02:08-12-31</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C36" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1530,27 +1404,21 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v/>
-      </c>
-      <c r="M36" t="str">
-        <v/>
-      </c>
-      <c r="N36" t="str">
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>|| אהוד בנאי ובנו הנדלר - פליטי הדאב ()</v>
+        <v>|| חוה אלברשטיין - חמישה שירים ()</v>
       </c>
       <c r="B37" t="str">
-        <v>2025  02:05-12-31</v>
+        <v>2025  02:06-12-31</v>
       </c>
       <c r="C37" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1574,27 +1442,21 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v/>
-      </c>
-      <c r="M37" t="str">
-        <v/>
-      </c>
-      <c r="N37" t="str">
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>|| Imagine פסטיגל - שירי התחרות ()</v>
+        <v>|| הפרויקט של עידן רייכל - עד סוף העולם ()</v>
       </c>
       <c r="B38" t="str">
-        <v>2025  02:04-12-31</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C38" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1618,27 +1480,21 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v/>
-      </c>
-      <c r="M38" t="str">
-        <v/>
-      </c>
-      <c r="N38" t="str">
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>|| השמחות - חובות אבודים ()</v>
+        <v>|| סטטיק - קעקועים ()</v>
       </c>
       <c r="B39" t="str">
-        <v>2025  02:02-12-31</v>
+        <v>2025  02:03-12-31</v>
       </c>
       <c r="C39" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1662,27 +1518,21 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v/>
-      </c>
-      <c r="M39" t="str">
-        <v/>
-      </c>
-      <c r="N39" t="str">
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>|| שלמה גרוניך - כמו כוכבים ()</v>
+        <v>|| ליאור נרקיס - דיסוננס ()</v>
       </c>
       <c r="B40" t="str">
-        <v>2025  02:00-12-31</v>
+        <v>2025  02:01-12-31</v>
       </c>
       <c r="C40" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1706,27 +1556,21 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v/>
-      </c>
-      <c r="M40" t="str">
-        <v/>
-      </c>
-      <c r="N40" t="str">
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>|| יוני רועה - מפוזרים ()</v>
+        <v>|| דיוויד ברוזה - BrozaJazz (Paris Alhambra) ()</v>
       </c>
       <c r="B41" t="str">
-        <v>2025  01:56-12-31</v>
+        <v>2025  01:57-12-31</v>
       </c>
       <c r="C41" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1750,27 +1594,21 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v/>
-      </c>
-      <c r="M41" t="str">
-        <v/>
-      </c>
-      <c r="N41" t="str">
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>|| התקווה 6 - ויהי אור ()</v>
+        <v>|| אתניקס - איטליה ()</v>
       </c>
       <c r="B42" t="str">
-        <v>2025  01:54-12-31</v>
+        <v>2025  01:55-12-31</v>
       </c>
       <c r="C42" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -1794,30 +1632,24 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v/>
-      </c>
-      <c r="M42" t="str">
-        <v/>
-      </c>
-      <c r="N42" t="str">
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>|| שאנן סטריט ודי ג׳יי מש - באתי לבדר ()</v>
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
       </c>
       <c r="B43" t="str">
-        <v>2025  01:53-12-31</v>
+        <v>2026-01-09</v>
       </c>
       <c r="C43" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E43" t="str">
-        <v/>
+        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
       </c>
       <c r="F43" t="str">
         <v>אלבומים חדשים</v>
@@ -1849,13 +1681,13 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>אשכול נוכחות למשתמשים פעילים</v>
+        <v>|| אייל גולן - בית מפואר ()</v>
       </c>
       <c r="B44" t="str">
-        <v>2025  16:32 מאת freund-10-16</v>
+        <v>2025  02:18-12-31</v>
       </c>
       <c r="C44" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=23455&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-08</v>
@@ -1899,13 +1731,13 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>כיצד להוריד מהאתרים המפורסמים</v>
+        <v>|| הפרויקט של דודי לוי ואבטיפוס - הפטריקים ()</v>
       </c>
       <c r="B45" t="str">
-        <v>2023  16:23 מאת petel1-08-08</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C45" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=22411&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-08</v>
@@ -1949,13 +1781,13 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
+        <v>|| שיר לוי - ילד מוזר ()</v>
       </c>
       <c r="B46" t="str">
-        <v>2026  22:40 מאת מוטי_ד-01-01</v>
+        <v>2025  02:14-12-31</v>
       </c>
       <c r="C46" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24435&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-08</v>
@@ -1999,13 +1831,13 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>|אלבום חדש| אייל גולן - בית מפואר (2025)</v>
+        <v>|| פיטר רוט - 50 ()</v>
       </c>
       <c r="B47" t="str">
-        <v>2025  02:18 מאת DiSHi-12-31</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C47" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-08</v>
@@ -2049,13 +1881,13 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע (2025)</v>
+        <v>|| אגם בוחבוט - עשרים ואחת ()</v>
       </c>
       <c r="B48" t="str">
-        <v>2025  02:17 מאת DiSHi-12-31</v>
+        <v>2025  02:11-12-31</v>
       </c>
       <c r="C48" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-08</v>
@@ -2099,13 +1931,13 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>|אלבום חדש| הפרויקט של דודי לוי ואבטיפוס - הפטריקים (2025)</v>
+        <v>|| רבקה זוהר - רסיסים של אור ()</v>
       </c>
       <c r="B49" t="str">
-        <v>2025  02:16 מאת DiSHi-12-31</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C49" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-08</v>
@@ -2149,13 +1981,13 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>|אלבום חדש| אברהם טל - חי (2025)</v>
+        <v>|| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות ()</v>
       </c>
       <c r="B50" t="str">
-        <v>2025  02:16 מאת DiSHi-12-31</v>
+        <v>2025  02:08-12-31</v>
       </c>
       <c r="C50" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-08</v>
@@ -2199,13 +2031,13 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>|אלבום חדש| שיר לוי - ילד מוזר (2025)</v>
+        <v>|| אהוד בנאי ובנו הנדלר - פליטי הדאב ()</v>
       </c>
       <c r="B51" t="str">
-        <v>2025  02:14 מאת DiSHi-12-31</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C51" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-08</v>
@@ -2249,13 +2081,13 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>|אלבום חדש| מיקי גבריאלוב - שלום (2025)</v>
+        <v>|| Imagine פסטיגל - שירי התחרות ()</v>
       </c>
       <c r="B52" t="str">
-        <v>2025  02:13 מאת DiSHi-12-31</v>
+        <v>2025  02:04-12-31</v>
       </c>
       <c r="C52" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-08</v>
@@ -2299,13 +2131,13 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>|אלבום חדש| פיטר רוט - 50 (2025)</v>
+        <v>|| השמחות - חובות אבודים ()</v>
       </c>
       <c r="B53" t="str">
-        <v>2025  02:13 מאת DiSHi-12-31</v>
+        <v>2025  02:02-12-31</v>
       </c>
       <c r="C53" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-08</v>
@@ -2349,13 +2181,13 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם (2025)</v>
+        <v>|| שלמה גרוניך - כמו כוכבים ()</v>
       </c>
       <c r="B54" t="str">
-        <v>2025  02:12 מאת DiSHi-12-31</v>
+        <v>2025  02:00-12-31</v>
       </c>
       <c r="C54" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-08</v>
@@ -2399,13 +2231,13 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>|אלבום חדש| אגם בוחבוט - עשרים ואחת (2025)</v>
+        <v>|| יוני רועה - מפוזרים ()</v>
       </c>
       <c r="B55" t="str">
-        <v>2025  02:11 מאת DiSHi-12-31</v>
+        <v>2025  01:56-12-31</v>
       </c>
       <c r="C55" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-08</v>
@@ -2449,13 +2281,13 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון (2025)</v>
+        <v>|| התקווה 6 - ויהי אור ()</v>
       </c>
       <c r="B56" t="str">
-        <v>2025  02:10 מאת DiSHi-12-31</v>
+        <v>2025  01:54-12-31</v>
       </c>
       <c r="C56" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-08</v>
@@ -2499,13 +2331,13 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>|אלבום חדש| רבקה זוהר - רסיסים של אור (2025)</v>
+        <v>|| שאנן סטריט ודי ג׳יי מש - באתי לבדר ()</v>
       </c>
       <c r="B57" t="str">
-        <v>2025  02:09 מאת DiSHi-12-31</v>
+        <v>2025  01:53-12-31</v>
       </c>
       <c r="C57" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-08</v>
@@ -2549,13 +2381,13 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה (2025)</v>
+        <v>אשכול נוכחות למשתמשים פעילים</v>
       </c>
       <c r="B58" t="str">
-        <v>2025  02:09 מאת DiSHi-12-31</v>
+        <v>2025  16:32 מאת freund-10-16</v>
       </c>
       <c r="C58" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=23455&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-08</v>
@@ -2594,18 +2426,24 @@
         <v/>
       </c>
       <c r="P58" t="str">
+        <v/>
+      </c>
+      <c r="Q58" t="str">
+        <v/>
+      </c>
+      <c r="R58" t="str">
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>|אלבום חדש| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות (2025)</v>
+        <v>כיצד להוריד מהאתרים המפורסמים</v>
       </c>
       <c r="B59" t="str">
-        <v>2025  02:08 מאת DiSHi-12-31</v>
+        <v>2023  16:23 מאת petel1-08-08</v>
       </c>
       <c r="C59" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=22411&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-08</v>
@@ -2644,18 +2482,24 @@
         <v/>
       </c>
       <c r="P59" t="str">
+        <v/>
+      </c>
+      <c r="Q59" t="str">
+        <v/>
+      </c>
+      <c r="R59" t="str">
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים (2025)</v>
+        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
       </c>
       <c r="B60" t="str">
-        <v>2025  02:06 מאת DiSHi-12-31</v>
+        <v>2026  22:40 מאת מוטי_ד-01-01</v>
       </c>
       <c r="C60" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24435&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-08</v>
@@ -2694,18 +2538,24 @@
         <v/>
       </c>
       <c r="P60" t="str">
+        <v/>
+      </c>
+      <c r="Q60" t="str">
+        <v/>
+      </c>
+      <c r="R60" t="str">
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>|אלבום חדש| אהוד בנאי ובנו הנדלר - פליטי הדאב (2025)</v>
+        <v>|אלבום חדש| אייל גולן - בית מפואר (2025)</v>
       </c>
       <c r="B61" t="str">
-        <v>2025  02:05 מאת DiSHi-12-31</v>
+        <v>2025  02:18 מאת DiSHi-12-31</v>
       </c>
       <c r="C61" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-08</v>
@@ -2744,18 +2594,24 @@
         <v/>
       </c>
       <c r="P61" t="str">
+        <v/>
+      </c>
+      <c r="Q61" t="str">
+        <v/>
+      </c>
+      <c r="R61" t="str">
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם (2025)</v>
+        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע (2025)</v>
       </c>
       <c r="B62" t="str">
-        <v>2025  02:05 מאת DiSHi-12-31</v>
+        <v>2025  02:17 מאת DiSHi-12-31</v>
       </c>
       <c r="C62" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-08</v>
@@ -2794,18 +2650,24 @@
         <v/>
       </c>
       <c r="P62" t="str">
+        <v/>
+      </c>
+      <c r="Q62" t="str">
+        <v/>
+      </c>
+      <c r="R62" t="str">
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>|אלבום חדש| Imagine פסטיגל - שירי התחרות (2025)</v>
+        <v>|אלבום חדש| הפרויקט של דודי לוי ואבטיפוס - הפטריקים (2025)</v>
       </c>
       <c r="B63" t="str">
-        <v>2025  02:04 מאת DiSHi-12-31</v>
+        <v>2025  02:16 מאת DiSHi-12-31</v>
       </c>
       <c r="C63" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-08</v>
@@ -2844,18 +2706,24 @@
         <v/>
       </c>
       <c r="P63" t="str">
+        <v/>
+      </c>
+      <c r="Q63" t="str">
+        <v/>
+      </c>
+      <c r="R63" t="str">
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>|אלבום חדש| סטטיק - קעקועים (2025)</v>
+        <v>|אלבום חדש| אברהם טל - חי (2025)</v>
       </c>
       <c r="B64" t="str">
-        <v>2025  02:03 מאת DiSHi-12-31</v>
+        <v>2025  02:16 מאת DiSHi-12-31</v>
       </c>
       <c r="C64" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-08</v>
@@ -2894,18 +2762,24 @@
         <v/>
       </c>
       <c r="P64" t="str">
+        <v/>
+      </c>
+      <c r="Q64" t="str">
+        <v/>
+      </c>
+      <c r="R64" t="str">
         <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>|אלבום חדש| השמחות - חובות אבודים (2025)</v>
+        <v>|אלבום חדש| שיר לוי - ילד מוזר (2025)</v>
       </c>
       <c r="B65" t="str">
-        <v>2025  02:02 מאת DiSHi-12-31</v>
+        <v>2025  02:14 מאת DiSHi-12-31</v>
       </c>
       <c r="C65" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-08</v>
@@ -2944,18 +2818,24 @@
         <v/>
       </c>
       <c r="P65" t="str">
+        <v/>
+      </c>
+      <c r="Q65" t="str">
+        <v/>
+      </c>
+      <c r="R65" t="str">
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>|אלבום חדש| ליאור נרקיס - דיסוננס (2025)</v>
+        <v>|אלבום חדש| מיקי גבריאלוב - שלום (2025)</v>
       </c>
       <c r="B66" t="str">
-        <v>2025  02:01 מאת DiSHi-12-31</v>
+        <v>2025  02:13 מאת DiSHi-12-31</v>
       </c>
       <c r="C66" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-08</v>
@@ -2994,18 +2874,24 @@
         <v/>
       </c>
       <c r="P66" t="str">
+        <v/>
+      </c>
+      <c r="Q66" t="str">
+        <v/>
+      </c>
+      <c r="R66" t="str">
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>|אלבום חדש| שלמה גרוניך - כמו כוכבים (2025)</v>
+        <v>|אלבום חדש| פיטר רוט - 50 (2025)</v>
       </c>
       <c r="B67" t="str">
-        <v>2025  02:00 מאת DiSHi-12-31</v>
+        <v>2025  02:13 מאת DiSHi-12-31</v>
       </c>
       <c r="C67" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-08</v>
@@ -3044,18 +2930,24 @@
         <v/>
       </c>
       <c r="P67" t="str">
+        <v/>
+      </c>
+      <c r="Q67" t="str">
+        <v/>
+      </c>
+      <c r="R67" t="str">
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) (2025)</v>
+        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם (2025)</v>
       </c>
       <c r="B68" t="str">
-        <v>2025  01:57 מאת DiSHi-12-31</v>
+        <v>2025  02:12 מאת DiSHi-12-31</v>
       </c>
       <c r="C68" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-08</v>
@@ -3094,18 +2986,24 @@
         <v/>
       </c>
       <c r="P68" t="str">
+        <v/>
+      </c>
+      <c r="Q68" t="str">
+        <v/>
+      </c>
+      <c r="R68" t="str">
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>|אלבום חדש| יוני רועה - מפוזרים (2025)</v>
+        <v>|אלבום חדש| אגם בוחבוט - עשרים ואחת (2025)</v>
       </c>
       <c r="B69" t="str">
-        <v>2025  01:56 מאת DiSHi-12-31</v>
+        <v>2025  02:11 מאת DiSHi-12-31</v>
       </c>
       <c r="C69" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-08</v>
@@ -3144,18 +3042,24 @@
         <v/>
       </c>
       <c r="P69" t="str">
+        <v/>
+      </c>
+      <c r="Q69" t="str">
+        <v/>
+      </c>
+      <c r="R69" t="str">
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>|אלבום חדש| אתניקס - איטליה (2025)</v>
+        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון (2025)</v>
       </c>
       <c r="B70" t="str">
-        <v>2025  01:55 מאת DiSHi-12-31</v>
+        <v>2025  02:10 מאת DiSHi-12-31</v>
       </c>
       <c r="C70" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-08</v>
@@ -3194,18 +3098,24 @@
         <v/>
       </c>
       <c r="P70" t="str">
+        <v/>
+      </c>
+      <c r="Q70" t="str">
+        <v/>
+      </c>
+      <c r="R70" t="str">
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>|אלבום חדש| התקווה 6 - ויהי אור (2025)</v>
+        <v>|אלבום חדש| רבקה זוהר - רסיסים של אור (2025)</v>
       </c>
       <c r="B71" t="str">
-        <v>2025  01:54 מאת DiSHi-12-31</v>
+        <v>2025  02:09 מאת DiSHi-12-31</v>
       </c>
       <c r="C71" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-08</v>
@@ -3244,18 +3154,24 @@
         <v/>
       </c>
       <c r="P71" t="str">
+        <v/>
+      </c>
+      <c r="Q71" t="str">
+        <v/>
+      </c>
+      <c r="R71" t="str">
         <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>|אלבום חדש| שלומי סרנגה - איפרכו (2025)</v>
+        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה (2025)</v>
       </c>
       <c r="B72" t="str">
-        <v>2025  01:53 מאת DiSHi-12-31</v>
+        <v>2025  02:09 מאת DiSHi-12-31</v>
       </c>
       <c r="C72" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24430&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-08</v>
@@ -3294,18 +3210,24 @@
         <v/>
       </c>
       <c r="P72" t="str">
+        <v/>
+      </c>
+      <c r="Q72" t="str">
+        <v/>
+      </c>
+      <c r="R72" t="str">
         <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>|אלבום חדש| שאנן סטריט ודי ג׳יי מש - באתי לבדר (2025)</v>
+        <v>|אלבום חדש| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות (2025)</v>
       </c>
       <c r="B73" t="str">
-        <v>2025  01:53 מאת DiSHi-12-31</v>
+        <v>2025  02:08 מאת DiSHi-12-31</v>
       </c>
       <c r="C73" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-08</v>
@@ -3344,18 +3266,24 @@
         <v/>
       </c>
       <c r="P73" t="str">
+        <v/>
+      </c>
+      <c r="Q73" t="str">
+        <v/>
+      </c>
+      <c r="R73" t="str">
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>הרשם לחברות מלאה</v>
+        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים (2025)</v>
       </c>
       <c r="B74" t="str">
-        <v/>
+        <v>2025  02:06 מאת DiSHi-12-31</v>
       </c>
       <c r="C74" t="str">
-        <v>https://rotter.name/nor/members-new.html</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-08</v>
@@ -3394,24 +3322,30 @@
         <v/>
       </c>
       <c r="P74" t="str">
+        <v/>
+      </c>
+      <c r="Q74" t="str">
+        <v/>
+      </c>
+      <c r="R74" t="str">
         <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>אוליביה דין The Art of Loving</v>
+        <v>|אלבום חדש| אהוד בנאי ובנו הנדלר - פליטי הדאב (2025)</v>
       </c>
       <c r="B75" t="str">
-        <v>2026-01-04</v>
+        <v>2025  02:05 מאת DiSHi-12-31</v>
       </c>
       <c r="C75" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E75" t="str">
-        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
+        <v/>
       </c>
       <c r="F75" t="str">
         <v>אלבומים חדשים</v>
@@ -3455,19 +3389,19 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Geese Getting Killed</v>
+        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם (2025)</v>
       </c>
       <c r="B76" t="str">
-        <v>2025-12-29</v>
+        <v>2025  02:05 מאת DiSHi-12-31</v>
       </c>
       <c r="C76" t="str">
-        <v>https://yosmusic.com/geese-getting-killed/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E76" t="str">
-        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
+        <v/>
       </c>
       <c r="F76" t="str">
         <v>אלבומים חדשים</v>
@@ -3511,19 +3445,19 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>רוסליה Lux</v>
+        <v>|אלבום חדש| Imagine פסטיגל - שירי התחרות (2025)</v>
       </c>
       <c r="B77" t="str">
-        <v>2025-12-25</v>
+        <v>2025  02:04 מאת DiSHi-12-31</v>
       </c>
       <c r="C77" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E77" t="str">
-        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
+        <v/>
       </c>
       <c r="F77" t="str">
         <v>אלבומים חדשים</v>
@@ -3567,19 +3501,19 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>יאנגבלאד אירוסמית' one more time</v>
+        <v>|אלבום חדש| סטטיק - קעקועים (2025)</v>
       </c>
       <c r="B78" t="str">
-        <v>2025-12-17</v>
+        <v>2025  02:03 מאת DiSHi-12-31</v>
       </c>
       <c r="C78" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E78" t="str">
-        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
+        <v/>
       </c>
       <c r="F78" t="str">
         <v>אלבומים חדשים</v>
@@ -3623,19 +3557,19 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>פינק פלויד Wish You Were Here 50</v>
+        <v>|אלבום חדש| השמחות - חובות אבודים (2025)</v>
       </c>
       <c r="B79" t="str">
-        <v>2025-12-14</v>
+        <v>2025  02:02 מאת DiSHi-12-31</v>
       </c>
       <c r="C79" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E79" t="str">
-        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
+        <v/>
       </c>
       <c r="F79" t="str">
         <v>אלבומים חדשים</v>
@@ -3679,19 +3613,19 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+        <v>|אלבום חדש| ליאור נרקיס - דיסוננס (2025)</v>
       </c>
       <c r="B80" t="str">
-        <v>2025-12-08</v>
+        <v>2025  02:01 מאת DiSHi-12-31</v>
       </c>
       <c r="C80" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E80" t="str">
-        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
+        <v/>
       </c>
       <c r="F80" t="str">
         <v>אלבומים חדשים</v>
@@ -3735,19 +3669,19 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>סטריי קידס DO IT (EP)</v>
+        <v>|אלבום חדש| שלמה גרוניך - כמו כוכבים (2025)</v>
       </c>
       <c r="B81" t="str">
-        <v>2025-12-04</v>
+        <v>2025  02:00 מאת DiSHi-12-31</v>
       </c>
       <c r="C81" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E81" t="str">
-        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
+        <v/>
       </c>
       <c r="F81" t="str">
         <v>אלבומים חדשים</v>
@@ -3791,19 +3725,19 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>דויד ברוזה BROZAJAZZ</v>
+        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) (2025)</v>
       </c>
       <c r="B82" t="str">
-        <v>2025-11-30</v>
+        <v>2025  01:57 מאת DiSHi-12-31</v>
       </c>
       <c r="C82" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E82" t="str">
-        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
+        <v/>
       </c>
       <c r="F82" t="str">
         <v>אלבומים חדשים</v>
@@ -3847,19 +3781,19 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Five Seconds of Summer – Everyone's A Star</v>
+        <v>|אלבום חדש| יוני רועה - מפוזרים (2025)</v>
       </c>
       <c r="B83" t="str">
-        <v>2025-11-24</v>
+        <v>2025  01:56 מאת DiSHi-12-31</v>
       </c>
       <c r="C83" t="str">
-        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E83" t="str">
-        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
+        <v/>
       </c>
       <c r="F83" t="str">
         <v>אלבומים חדשים</v>
@@ -3903,19 +3837,19 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>התקווה 6 – ויהי אור</v>
+        <v>|אלבום חדש| אתניקס - איטליה (2025)</v>
       </c>
       <c r="B84" t="str">
-        <v>2025-11-20</v>
+        <v>2025  01:55 מאת DiSHi-12-31</v>
       </c>
       <c r="C84" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E84" t="str">
-        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
+        <v/>
       </c>
       <c r="F84" t="str">
         <v>אלבומים חדשים</v>
@@ -3959,19 +3893,19 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>פלורנס אנד דה משין Everybody Scream</v>
+        <v>|אלבום חדש| התקווה 6 - ויהי אור (2025)</v>
       </c>
       <c r="B85" t="str">
-        <v>2025-11-13</v>
+        <v>2025  01:54 מאת DiSHi-12-31</v>
       </c>
       <c r="C85" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E85" t="str">
-        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
+        <v/>
       </c>
       <c r="F85" t="str">
         <v>אלבומים חדשים</v>
@@ -4015,19 +3949,19 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>טיים אימפלה Deadbeat</v>
+        <v>|אלבום חדש| שלומי סרנגה - איפרכו (2025)</v>
       </c>
       <c r="B86" t="str">
-        <v>2025-11-03</v>
+        <v>2025  01:53 מאת DiSHi-12-31</v>
       </c>
       <c r="C86" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24430&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E86" t="str">
-        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
+        <v/>
       </c>
       <c r="F86" t="str">
         <v>אלבומים חדשים</v>
@@ -4071,19 +4005,19 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+        <v>|אלבום חדש| שאנן סטריט ודי ג׳יי מש - באתי לבדר (2025)</v>
       </c>
       <c r="B87" t="str">
-        <v>2025-10-20</v>
+        <v>2025  01:53 מאת DiSHi-12-31</v>
       </c>
       <c r="C87" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E87" t="str">
-        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
+        <v/>
       </c>
       <c r="F87" t="str">
         <v>אלבומים חדשים</v>
@@ -4127,19 +4061,19 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>שלמה גרוניך – תודה אהבה</v>
+        <v>הרשם לחברות מלאה</v>
       </c>
       <c r="B88" t="str">
-        <v>2025-10-18</v>
+        <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
+        <v>https://rotter.name/nor/members-new.html</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E88" t="str">
-        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
+        <v/>
       </c>
       <c r="F88" t="str">
         <v>אלבומים חדשים</v>
@@ -4183,19 +4117,19 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>טיילור סוויפט The Life Of A Showgirl</v>
+        <v>אוליביה דין The Art of Loving</v>
       </c>
       <c r="B89" t="str">
-        <v>2025-10-11</v>
+        <v>2026-01-04</v>
       </c>
       <c r="C89" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E89" t="str">
-        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
+        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
       </c>
       <c r="F89" t="str">
         <v>אלבומים חדשים</v>
@@ -4234,24 +4168,30 @@
         <v/>
       </c>
       <c r="R89" t="str">
+        <v/>
+      </c>
+      <c r="S89" t="str">
+        <v/>
+      </c>
+      <c r="T89" t="str">
         <v/>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>דוג'ה קאט Vie</v>
+        <v>Geese Getting Killed</v>
       </c>
       <c r="B90" t="str">
-        <v>2025-10-04</v>
+        <v>2025-12-29</v>
       </c>
       <c r="C90" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
+        <v>https://yosmusic.com/geese-getting-killed/</v>
       </c>
       <c r="D90" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E90" t="str">
-        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
+        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
       </c>
       <c r="F90" t="str">
         <v>אלבומים חדשים</v>
@@ -4290,24 +4230,30 @@
         <v/>
       </c>
       <c r="R90" t="str">
+        <v/>
+      </c>
+      <c r="S90" t="str">
+        <v/>
+      </c>
+      <c r="T90" t="str">
         <v/>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>ג'וי קרוקס Juniper</v>
+        <v>רוסליה Lux</v>
       </c>
       <c r="B91" t="str">
-        <v>2025-10-03</v>
+        <v>2025-12-25</v>
       </c>
       <c r="C91" t="str">
-        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
       </c>
       <c r="D91" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E91" t="str">
-        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
+        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
       </c>
       <c r="F91" t="str">
         <v>אלבומים חדשים</v>
@@ -4346,24 +4292,30 @@
         <v/>
       </c>
       <c r="R91" t="str">
+        <v/>
+      </c>
+      <c r="S91" t="str">
+        <v/>
+      </c>
+      <c r="T91" t="str">
         <v/>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>ביפי קליירו Futique</v>
+        <v>יאנגבלאד אירוסמית' one more time</v>
       </c>
       <c r="B92" t="str">
-        <v>2025-09-30</v>
+        <v>2025-12-17</v>
       </c>
       <c r="C92" t="str">
-        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
+        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
       </c>
       <c r="D92" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E92" t="str">
-        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
+        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
       </c>
       <c r="F92" t="str">
         <v>אלבומים חדשים</v>
@@ -4402,24 +4354,30 @@
         <v/>
       </c>
       <c r="R92" t="str">
+        <v/>
+      </c>
+      <c r="S92" t="str">
+        <v/>
+      </c>
+      <c r="T92" t="str">
         <v/>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>אד שירן Play</v>
+        <v>פינק פלויד Wish You Were Here 50</v>
       </c>
       <c r="B93" t="str">
-        <v>2025-09-24</v>
+        <v>2025-12-14</v>
       </c>
       <c r="C93" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
       </c>
       <c r="D93" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E93" t="str">
-        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
+        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
       </c>
       <c r="F93" t="str">
         <v>אלבומים חדשים</v>
@@ -4458,24 +4416,30 @@
         <v/>
       </c>
       <c r="R93" t="str">
+        <v/>
+      </c>
+      <c r="S93" t="str">
+        <v/>
+      </c>
+      <c r="T93" t="str">
         <v/>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
       </c>
       <c r="B94" t="str">
-        <v>2025-09-21</v>
+        <v>2025-12-08</v>
       </c>
       <c r="C94" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
+        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
       </c>
       <c r="D94" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E94" t="str">
-        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
+        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
       </c>
       <c r="F94" t="str">
         <v>אלבומים חדשים</v>
@@ -4514,24 +4478,30 @@
         <v/>
       </c>
       <c r="R94" t="str">
+        <v/>
+      </c>
+      <c r="S94" t="str">
+        <v/>
+      </c>
+      <c r="T94" t="str">
         <v/>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>סוויד Antidepressants</v>
+        <v>סטריי קידס DO IT (EP)</v>
       </c>
       <c r="B95" t="str">
-        <v>2025-09-12</v>
+        <v>2025-12-04</v>
       </c>
       <c r="C95" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
+        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
       </c>
       <c r="D95" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E95" t="str">
-        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
+        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
       </c>
       <c r="F95" t="str">
         <v>אלבומים חדשים</v>
@@ -4570,24 +4540,30 @@
         <v/>
       </c>
       <c r="R95" t="str">
+        <v/>
+      </c>
+      <c r="S95" t="str">
+        <v/>
+      </c>
+      <c r="T95" t="str">
         <v/>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>וולף אליס The Clearing</v>
+        <v>דויד ברוזה BROZAJAZZ</v>
       </c>
       <c r="B96" t="str">
-        <v>2025-09-01</v>
+        <v>2025-11-30</v>
       </c>
       <c r="C96" t="str">
-        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
       </c>
       <c r="D96" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E96" t="str">
-        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
+        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
       </c>
       <c r="F96" t="str">
         <v>אלבומים חדשים</v>
@@ -4626,24 +4602,30 @@
         <v/>
       </c>
       <c r="R96" t="str">
+        <v/>
+      </c>
+      <c r="S96" t="str">
+        <v/>
+      </c>
+      <c r="T96" t="str">
         <v/>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+        <v>Five Seconds of Summer – Everyone's A Star</v>
       </c>
       <c r="B97" t="str">
-        <v>2025-08-29</v>
+        <v>2025-11-24</v>
       </c>
       <c r="C97" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
+        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
       </c>
       <c r="D97" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E97" t="str">
-        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
+        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
       </c>
       <c r="F97" t="str">
         <v>אלבומים חדשים</v>
@@ -4682,24 +4664,30 @@
         <v/>
       </c>
       <c r="R97" t="str">
+        <v/>
+      </c>
+      <c r="S97" t="str">
+        <v/>
+      </c>
+      <c r="T97" t="str">
         <v/>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+        <v>התקווה 6 – ויהי אור</v>
       </c>
       <c r="B98" t="str">
-        <v>2025-08-24</v>
+        <v>2025-11-20</v>
       </c>
       <c r="C98" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
+        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
       </c>
       <c r="D98" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E98" t="str">
-        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
+        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
       </c>
       <c r="F98" t="str">
         <v>אלבומים חדשים</v>
@@ -4738,24 +4726,30 @@
         <v/>
       </c>
       <c r="R98" t="str">
+        <v/>
+      </c>
+      <c r="S98" t="str">
+        <v/>
+      </c>
+      <c r="T98" t="str">
         <v/>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+        <v>פלורנס אנד דה משין Everybody Scream</v>
       </c>
       <c r="B99" t="str">
-        <v>2025-08-21</v>
+        <v>2025-11-13</v>
       </c>
       <c r="C99" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
       </c>
       <c r="D99" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E99" t="str">
-        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
+        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
       </c>
       <c r="F99" t="str">
         <v>אלבומים חדשים</v>
@@ -4794,24 +4788,30 @@
         <v/>
       </c>
       <c r="R99" t="str">
+        <v/>
+      </c>
+      <c r="S99" t="str">
+        <v/>
+      </c>
+      <c r="T99" t="str">
         <v/>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>אברהם טל – חי</v>
+        <v>טיים אימפלה Deadbeat</v>
       </c>
       <c r="B100" t="str">
-        <v>2025-08-17</v>
+        <v>2025-11-03</v>
       </c>
       <c r="C100" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
       </c>
       <c r="D100" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E100" t="str">
-        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
+        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
       </c>
       <c r="F100" t="str">
         <v>אלבומים חדשים</v>
@@ -4850,24 +4850,30 @@
         <v/>
       </c>
       <c r="R100" t="str">
+        <v/>
+      </c>
+      <c r="S100" t="str">
+        <v/>
+      </c>
+      <c r="T100" t="str">
         <v/>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>רנה ראפ Bite Me</v>
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
       </c>
       <c r="B101" t="str">
-        <v>2025-08-12</v>
+        <v>2025-10-20</v>
       </c>
       <c r="C101" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
+        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
       </c>
       <c r="D101" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E101" t="str">
-        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
+        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
       </c>
       <c r="F101" t="str">
         <v>אלבומים חדשים</v>
@@ -4906,24 +4912,30 @@
         <v/>
       </c>
       <c r="R101" t="str">
+        <v/>
+      </c>
+      <c r="S101" t="str">
+        <v/>
+      </c>
+      <c r="T101" t="str">
         <v/>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>The K's – Pretty On The Internet</v>
+        <v>שלמה גרוניך – תודה אהבה</v>
       </c>
       <c r="B102" t="str">
-        <v>2025-08-03</v>
+        <v>2025-10-18</v>
       </c>
       <c r="C102" t="str">
-        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
       </c>
       <c r="D102" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E102" t="str">
-        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
+        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
       </c>
       <c r="F102" t="str">
         <v>אלבומים חדשים</v>
@@ -4962,24 +4974,30 @@
         <v/>
       </c>
       <c r="R102" t="str">
+        <v/>
+      </c>
+      <c r="S102" t="str">
+        <v/>
+      </c>
+      <c r="T102" t="str">
         <v/>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>פליטווד מק Fifty Years – Don’t Stop</v>
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
       </c>
       <c r="B103" t="str">
-        <v>2025-07-30</v>
+        <v>2025-10-11</v>
       </c>
       <c r="C103" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%99%d7%98%d7%95%d7%95%d7%93-%d7%9e%d7%a7-fifty-years-dont-stop/</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
       </c>
       <c r="D103" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E103" t="str">
-        <v>פליטווד מק (Fleetwood Mac) חוגגים חצי מאה של מוזיקה עם אוסף חדש בן 50 שירים, שמתפרש על כל הקריירה של הלהקה, מימיה הראשונים בסגנון בלוז, ועד להצלחתה העולמית כאחת מלהקות הגדולות בהיסטוריה של הרוק. פליטווד מק הם לא רק להקה</v>
+        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
       </c>
       <c r="F103" t="str">
         <v>אלבומים חדשים</v>
@@ -5018,68 +5036,948 @@
         <v/>
       </c>
       <c r="R103" t="str">
+        <v/>
+      </c>
+      <c r="S103" t="str">
+        <v/>
+      </c>
+      <c r="T103" t="str">
         <v/>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
+        <v>דוג'ה קאט Vie</v>
+      </c>
+      <c r="B104" t="str">
+        <v>2025-10-04</v>
+      </c>
+      <c r="C104" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
+      </c>
+      <c r="D104" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E104" t="str">
+        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
+      </c>
+      <c r="F104" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G104" t="str">
+        <v/>
+      </c>
+      <c r="H104" t="str">
+        <v/>
+      </c>
+      <c r="I104" t="str">
+        <v/>
+      </c>
+      <c r="J104" t="str">
+        <v/>
+      </c>
+      <c r="K104" t="str">
+        <v/>
+      </c>
+      <c r="L104" t="str">
+        <v/>
+      </c>
+      <c r="M104" t="str">
+        <v/>
+      </c>
+      <c r="N104" t="str">
+        <v/>
+      </c>
+      <c r="O104" t="str">
+        <v/>
+      </c>
+      <c r="P104" t="str">
+        <v/>
+      </c>
+      <c r="Q104" t="str">
+        <v/>
+      </c>
+      <c r="R104" t="str">
+        <v/>
+      </c>
+      <c r="S104" t="str">
+        <v/>
+      </c>
+      <c r="T104" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>ג'וי קרוקס Juniper</v>
+      </c>
+      <c r="B105" t="str">
+        <v>2025-10-03</v>
+      </c>
+      <c r="C105" t="str">
+        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
+      </c>
+      <c r="D105" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E105" t="str">
+        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
+      </c>
+      <c r="F105" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G105" t="str">
+        <v/>
+      </c>
+      <c r="H105" t="str">
+        <v/>
+      </c>
+      <c r="I105" t="str">
+        <v/>
+      </c>
+      <c r="J105" t="str">
+        <v/>
+      </c>
+      <c r="K105" t="str">
+        <v/>
+      </c>
+      <c r="L105" t="str">
+        <v/>
+      </c>
+      <c r="M105" t="str">
+        <v/>
+      </c>
+      <c r="N105" t="str">
+        <v/>
+      </c>
+      <c r="O105" t="str">
+        <v/>
+      </c>
+      <c r="P105" t="str">
+        <v/>
+      </c>
+      <c r="Q105" t="str">
+        <v/>
+      </c>
+      <c r="R105" t="str">
+        <v/>
+      </c>
+      <c r="S105" t="str">
+        <v/>
+      </c>
+      <c r="T105" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>ביפי קליירו Futique</v>
+      </c>
+      <c r="B106" t="str">
+        <v>2025-09-30</v>
+      </c>
+      <c r="C106" t="str">
+        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
+      </c>
+      <c r="D106" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E106" t="str">
+        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
+      </c>
+      <c r="F106" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G106" t="str">
+        <v/>
+      </c>
+      <c r="H106" t="str">
+        <v/>
+      </c>
+      <c r="I106" t="str">
+        <v/>
+      </c>
+      <c r="J106" t="str">
+        <v/>
+      </c>
+      <c r="K106" t="str">
+        <v/>
+      </c>
+      <c r="L106" t="str">
+        <v/>
+      </c>
+      <c r="M106" t="str">
+        <v/>
+      </c>
+      <c r="N106" t="str">
+        <v/>
+      </c>
+      <c r="O106" t="str">
+        <v/>
+      </c>
+      <c r="P106" t="str">
+        <v/>
+      </c>
+      <c r="Q106" t="str">
+        <v/>
+      </c>
+      <c r="R106" t="str">
+        <v/>
+      </c>
+      <c r="S106" t="str">
+        <v/>
+      </c>
+      <c r="T106" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>אד שירן Play</v>
+      </c>
+      <c r="B107" t="str">
+        <v>2025-09-24</v>
+      </c>
+      <c r="C107" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
+      </c>
+      <c r="D107" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E107" t="str">
+        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
+      </c>
+      <c r="F107" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G107" t="str">
+        <v/>
+      </c>
+      <c r="H107" t="str">
+        <v/>
+      </c>
+      <c r="I107" t="str">
+        <v/>
+      </c>
+      <c r="J107" t="str">
+        <v/>
+      </c>
+      <c r="K107" t="str">
+        <v/>
+      </c>
+      <c r="L107" t="str">
+        <v/>
+      </c>
+      <c r="M107" t="str">
+        <v/>
+      </c>
+      <c r="N107" t="str">
+        <v/>
+      </c>
+      <c r="O107" t="str">
+        <v/>
+      </c>
+      <c r="P107" t="str">
+        <v/>
+      </c>
+      <c r="Q107" t="str">
+        <v/>
+      </c>
+      <c r="R107" t="str">
+        <v/>
+      </c>
+      <c r="S107" t="str">
+        <v/>
+      </c>
+      <c r="T107" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+      </c>
+      <c r="B108" t="str">
+        <v>2025-09-21</v>
+      </c>
+      <c r="C108" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
+      </c>
+      <c r="D108" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E108" t="str">
+        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
+      </c>
+      <c r="F108" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G108" t="str">
+        <v/>
+      </c>
+      <c r="H108" t="str">
+        <v/>
+      </c>
+      <c r="I108" t="str">
+        <v/>
+      </c>
+      <c r="J108" t="str">
+        <v/>
+      </c>
+      <c r="K108" t="str">
+        <v/>
+      </c>
+      <c r="L108" t="str">
+        <v/>
+      </c>
+      <c r="M108" t="str">
+        <v/>
+      </c>
+      <c r="N108" t="str">
+        <v/>
+      </c>
+      <c r="O108" t="str">
+        <v/>
+      </c>
+      <c r="P108" t="str">
+        <v/>
+      </c>
+      <c r="Q108" t="str">
+        <v/>
+      </c>
+      <c r="R108" t="str">
+        <v/>
+      </c>
+      <c r="S108" t="str">
+        <v/>
+      </c>
+      <c r="T108" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>סוויד Antidepressants</v>
+      </c>
+      <c r="B109" t="str">
+        <v>2025-09-12</v>
+      </c>
+      <c r="C109" t="str">
+        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
+      </c>
+      <c r="D109" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E109" t="str">
+        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
+      </c>
+      <c r="F109" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G109" t="str">
+        <v/>
+      </c>
+      <c r="H109" t="str">
+        <v/>
+      </c>
+      <c r="I109" t="str">
+        <v/>
+      </c>
+      <c r="J109" t="str">
+        <v/>
+      </c>
+      <c r="K109" t="str">
+        <v/>
+      </c>
+      <c r="L109" t="str">
+        <v/>
+      </c>
+      <c r="M109" t="str">
+        <v/>
+      </c>
+      <c r="N109" t="str">
+        <v/>
+      </c>
+      <c r="O109" t="str">
+        <v/>
+      </c>
+      <c r="P109" t="str">
+        <v/>
+      </c>
+      <c r="Q109" t="str">
+        <v/>
+      </c>
+      <c r="R109" t="str">
+        <v/>
+      </c>
+      <c r="S109" t="str">
+        <v/>
+      </c>
+      <c r="T109" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>וולף אליס The Clearing</v>
+      </c>
+      <c r="B110" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="C110" t="str">
+        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
+      </c>
+      <c r="D110" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E110" t="str">
+        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
+      </c>
+      <c r="F110" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G110" t="str">
+        <v/>
+      </c>
+      <c r="H110" t="str">
+        <v/>
+      </c>
+      <c r="I110" t="str">
+        <v/>
+      </c>
+      <c r="J110" t="str">
+        <v/>
+      </c>
+      <c r="K110" t="str">
+        <v/>
+      </c>
+      <c r="L110" t="str">
+        <v/>
+      </c>
+      <c r="M110" t="str">
+        <v/>
+      </c>
+      <c r="N110" t="str">
+        <v/>
+      </c>
+      <c r="O110" t="str">
+        <v/>
+      </c>
+      <c r="P110" t="str">
+        <v/>
+      </c>
+      <c r="Q110" t="str">
+        <v/>
+      </c>
+      <c r="R110" t="str">
+        <v/>
+      </c>
+      <c r="S110" t="str">
+        <v/>
+      </c>
+      <c r="T110" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+      </c>
+      <c r="B111" t="str">
+        <v>2025-08-29</v>
+      </c>
+      <c r="C111" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
+      </c>
+      <c r="D111" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E111" t="str">
+        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
+      </c>
+      <c r="F111" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G111" t="str">
+        <v/>
+      </c>
+      <c r="H111" t="str">
+        <v/>
+      </c>
+      <c r="I111" t="str">
+        <v/>
+      </c>
+      <c r="J111" t="str">
+        <v/>
+      </c>
+      <c r="K111" t="str">
+        <v/>
+      </c>
+      <c r="L111" t="str">
+        <v/>
+      </c>
+      <c r="M111" t="str">
+        <v/>
+      </c>
+      <c r="N111" t="str">
+        <v/>
+      </c>
+      <c r="O111" t="str">
+        <v/>
+      </c>
+      <c r="P111" t="str">
+        <v/>
+      </c>
+      <c r="Q111" t="str">
+        <v/>
+      </c>
+      <c r="R111" t="str">
+        <v/>
+      </c>
+      <c r="S111" t="str">
+        <v/>
+      </c>
+      <c r="T111" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+      </c>
+      <c r="B112" t="str">
+        <v>2025-08-24</v>
+      </c>
+      <c r="C112" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
+      </c>
+      <c r="D112" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E112" t="str">
+        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
+      </c>
+      <c r="F112" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G112" t="str">
+        <v/>
+      </c>
+      <c r="H112" t="str">
+        <v/>
+      </c>
+      <c r="I112" t="str">
+        <v/>
+      </c>
+      <c r="J112" t="str">
+        <v/>
+      </c>
+      <c r="K112" t="str">
+        <v/>
+      </c>
+      <c r="L112" t="str">
+        <v/>
+      </c>
+      <c r="M112" t="str">
+        <v/>
+      </c>
+      <c r="N112" t="str">
+        <v/>
+      </c>
+      <c r="O112" t="str">
+        <v/>
+      </c>
+      <c r="P112" t="str">
+        <v/>
+      </c>
+      <c r="Q112" t="str">
+        <v/>
+      </c>
+      <c r="R112" t="str">
+        <v/>
+      </c>
+      <c r="S112" t="str">
+        <v/>
+      </c>
+      <c r="T112" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+      </c>
+      <c r="B113" t="str">
+        <v>2025-08-21</v>
+      </c>
+      <c r="C113" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
+      </c>
+      <c r="D113" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E113" t="str">
+        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
+      </c>
+      <c r="F113" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G113" t="str">
+        <v/>
+      </c>
+      <c r="H113" t="str">
+        <v/>
+      </c>
+      <c r="I113" t="str">
+        <v/>
+      </c>
+      <c r="J113" t="str">
+        <v/>
+      </c>
+      <c r="K113" t="str">
+        <v/>
+      </c>
+      <c r="L113" t="str">
+        <v/>
+      </c>
+      <c r="M113" t="str">
+        <v/>
+      </c>
+      <c r="N113" t="str">
+        <v/>
+      </c>
+      <c r="O113" t="str">
+        <v/>
+      </c>
+      <c r="P113" t="str">
+        <v/>
+      </c>
+      <c r="Q113" t="str">
+        <v/>
+      </c>
+      <c r="R113" t="str">
+        <v/>
+      </c>
+      <c r="S113" t="str">
+        <v/>
+      </c>
+      <c r="T113" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>אברהם טל – חי</v>
+      </c>
+      <c r="B114" t="str">
+        <v>2025-08-17</v>
+      </c>
+      <c r="C114" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
+      </c>
+      <c r="D114" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E114" t="str">
+        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
+      </c>
+      <c r="F114" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G114" t="str">
+        <v/>
+      </c>
+      <c r="H114" t="str">
+        <v/>
+      </c>
+      <c r="I114" t="str">
+        <v/>
+      </c>
+      <c r="J114" t="str">
+        <v/>
+      </c>
+      <c r="K114" t="str">
+        <v/>
+      </c>
+      <c r="L114" t="str">
+        <v/>
+      </c>
+      <c r="M114" t="str">
+        <v/>
+      </c>
+      <c r="N114" t="str">
+        <v/>
+      </c>
+      <c r="O114" t="str">
+        <v/>
+      </c>
+      <c r="P114" t="str">
+        <v/>
+      </c>
+      <c r="Q114" t="str">
+        <v/>
+      </c>
+      <c r="R114" t="str">
+        <v/>
+      </c>
+      <c r="S114" t="str">
+        <v/>
+      </c>
+      <c r="T114" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>רנה ראפ Bite Me</v>
+      </c>
+      <c r="B115" t="str">
+        <v>2025-08-12</v>
+      </c>
+      <c r="C115" t="str">
+        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
+      </c>
+      <c r="D115" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E115" t="str">
+        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
+      </c>
+      <c r="F115" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G115" t="str">
+        <v/>
+      </c>
+      <c r="H115" t="str">
+        <v/>
+      </c>
+      <c r="I115" t="str">
+        <v/>
+      </c>
+      <c r="J115" t="str">
+        <v/>
+      </c>
+      <c r="K115" t="str">
+        <v/>
+      </c>
+      <c r="L115" t="str">
+        <v/>
+      </c>
+      <c r="M115" t="str">
+        <v/>
+      </c>
+      <c r="N115" t="str">
+        <v/>
+      </c>
+      <c r="O115" t="str">
+        <v/>
+      </c>
+      <c r="P115" t="str">
+        <v/>
+      </c>
+      <c r="Q115" t="str">
+        <v/>
+      </c>
+      <c r="R115" t="str">
+        <v/>
+      </c>
+      <c r="S115" t="str">
+        <v/>
+      </c>
+      <c r="T115" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>The K's – Pretty On The Internet</v>
+      </c>
+      <c r="B116" t="str">
+        <v>2025-08-03</v>
+      </c>
+      <c r="C116" t="str">
+        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
+      </c>
+      <c r="D116" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E116" t="str">
+        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
+      </c>
+      <c r="F116" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G116" t="str">
+        <v/>
+      </c>
+      <c r="H116" t="str">
+        <v/>
+      </c>
+      <c r="I116" t="str">
+        <v/>
+      </c>
+      <c r="J116" t="str">
+        <v/>
+      </c>
+      <c r="K116" t="str">
+        <v/>
+      </c>
+      <c r="L116" t="str">
+        <v/>
+      </c>
+      <c r="M116" t="str">
+        <v/>
+      </c>
+      <c r="N116" t="str">
+        <v/>
+      </c>
+      <c r="O116" t="str">
+        <v/>
+      </c>
+      <c r="P116" t="str">
+        <v/>
+      </c>
+      <c r="Q116" t="str">
+        <v/>
+      </c>
+      <c r="R116" t="str">
+        <v/>
+      </c>
+      <c r="S116" t="str">
+        <v/>
+      </c>
+      <c r="T116" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>פליטווד מק Fifty Years – Don’t Stop</v>
+      </c>
+      <c r="B117" t="str">
+        <v>2025-07-30</v>
+      </c>
+      <c r="C117" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%99%d7%98%d7%95%d7%95%d7%93-%d7%9e%d7%a7-fifty-years-dont-stop/</v>
+      </c>
+      <c r="D117" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E117" t="str">
+        <v>פליטווד מק (Fleetwood Mac) חוגגים חצי מאה של מוזיקה עם אוסף חדש בן 50 שירים, שמתפרש על כל הקריירה של הלהקה, מימיה הראשונים בסגנון בלוז, ועד להצלחתה העולמית כאחת מלהקות הגדולות בהיסטוריה של הרוק. פליטווד מק הם לא רק להקה</v>
+      </c>
+      <c r="F117" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G117" t="str">
+        <v/>
+      </c>
+      <c r="H117" t="str">
+        <v/>
+      </c>
+      <c r="I117" t="str">
+        <v/>
+      </c>
+      <c r="J117" t="str">
+        <v/>
+      </c>
+      <c r="K117" t="str">
+        <v/>
+      </c>
+      <c r="L117" t="str">
+        <v/>
+      </c>
+      <c r="M117" t="str">
+        <v/>
+      </c>
+      <c r="N117" t="str">
+        <v/>
+      </c>
+      <c r="O117" t="str">
+        <v/>
+      </c>
+      <c r="P117" t="str">
+        <v/>
+      </c>
+      <c r="Q117" t="str">
+        <v/>
+      </c>
+      <c r="R117" t="str">
+        <v/>
+      </c>
+      <c r="S117" t="str">
+        <v/>
+      </c>
+      <c r="T117" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
         <v>Wet Leg Moisturizer</v>
       </c>
-      <c r="B104" t="str">
+      <c r="B118" t="str">
         <v>2025-07-25</v>
       </c>
-      <c r="C104" t="str">
+      <c r="C118" t="str">
         <v>https://yosmusic.com/wet-leg-moisturizer/</v>
       </c>
-      <c r="D104" t="str">
-        <v>2026-01-08</v>
-      </c>
-      <c r="E104" t="str">
+      <c r="D118" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E118" t="str">
         <v>להקת Wet Leg לא הוציאה קרם לחות (Moisturizer) כמוצר טיפוח. במקום זאת, "Moisturizer" הוא שמו של האלבום השני והחדש שלהם. במרכז –  צמד אינדי-רוק המורכב מהחברות ריין טיסדייל והסטר צ'יימברס. אלבום הבכורה הנושא את שמה, הגיע למקום הראשון במצעד האלבומים</v>
       </c>
-      <c r="F104" t="str">
-        <v>אלבומים חדשים</v>
-      </c>
-      <c r="G104" t="str">
-        <v/>
-      </c>
-      <c r="H104" t="str">
-        <v/>
-      </c>
-      <c r="I104" t="str">
-        <v/>
-      </c>
-      <c r="J104" t="str">
-        <v/>
-      </c>
-      <c r="K104" t="str">
-        <v/>
-      </c>
-      <c r="L104" t="str">
-        <v/>
-      </c>
-      <c r="M104" t="str">
-        <v/>
-      </c>
-      <c r="N104" t="str">
-        <v/>
-      </c>
-      <c r="O104" t="str">
-        <v/>
-      </c>
-      <c r="P104" t="str">
-        <v/>
-      </c>
-      <c r="Q104" t="str">
-        <v/>
-      </c>
-      <c r="R104" t="str">
+      <c r="F118" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G118" t="str">
+        <v/>
+      </c>
+      <c r="H118" t="str">
+        <v/>
+      </c>
+      <c r="I118" t="str">
+        <v/>
+      </c>
+      <c r="J118" t="str">
+        <v/>
+      </c>
+      <c r="K118" t="str">
+        <v/>
+      </c>
+      <c r="L118" t="str">
+        <v/>
+      </c>
+      <c r="M118" t="str">
+        <v/>
+      </c>
+      <c r="N118" t="str">
+        <v/>
+      </c>
+      <c r="O118" t="str">
+        <v/>
+      </c>
+      <c r="P118" t="str">
+        <v/>
+      </c>
+      <c r="Q118" t="str">
+        <v/>
+      </c>
+      <c r="R118" t="str">
+        <v/>
+      </c>
+      <c r="S118" t="str">
+        <v/>
+      </c>
+      <c r="T118" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R104"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T118"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T118"/>
+  <dimension ref="A1:V119"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,13 +421,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>תומר יוסף - 360</v>
+        <v>עדן בן זקן - רולקס וקסקט</v>
       </c>
       <c r="B2" t="str">
-        <v>2026  08:40-01-14</v>
+        <v>2026  08:41-01-14</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24436&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-15</v>
@@ -441,13 +441,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
+        <v>תומר יוסף - 360</v>
       </c>
       <c r="B3" t="str">
         <v>2026  08:40-01-14</v>
       </c>
       <c r="C3" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24439&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-15</v>
@@ -458,16 +458,22 @@
       <c r="F3" t="str">
         <v>אלבומים חדשים</v>
       </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>אייל גולן - בית מפואר</v>
+        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
       </c>
       <c r="B4" t="str">
-        <v>2025  02:18-12-31</v>
+        <v>2026  08:40-01-14</v>
       </c>
       <c r="C4" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24439&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-15</v>
@@ -478,16 +484,22 @@
       <c r="F4" t="str">
         <v>אלבומים חדשים</v>
       </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
+        <v>אייל גולן - בית מפואר</v>
       </c>
       <c r="B5" t="str">
-        <v>2025  02:16-12-31</v>
+        <v>2025  02:18-12-31</v>
       </c>
       <c r="C5" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-15</v>
@@ -498,16 +510,22 @@
       <c r="F5" t="str">
         <v>אלבומים חדשים</v>
       </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>שיר לוי - ילד מוזר</v>
+        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
       </c>
       <c r="B6" t="str">
-        <v>2025  02:14-12-31</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C6" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-15</v>
@@ -518,16 +536,22 @@
       <c r="F6" t="str">
         <v>אלבומים חדשים</v>
       </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>פיטר רוט - 50</v>
+        <v>שיר לוי - ילד מוזר</v>
       </c>
       <c r="B7" t="str">
-        <v>2025  02:13-12-31</v>
+        <v>2025  02:14-12-31</v>
       </c>
       <c r="C7" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-15</v>
@@ -538,16 +562,22 @@
       <c r="F7" t="str">
         <v>אלבומים חדשים</v>
       </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>אגם בוחבוט - עשרים ואחת</v>
+        <v>פיטר רוט - 50</v>
       </c>
       <c r="B8" t="str">
-        <v>2025  02:11-12-31</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C8" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-15</v>
@@ -558,16 +588,22 @@
       <c r="F8" t="str">
         <v>אלבומים חדשים</v>
       </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>רבקה זוהר - רסיסים של אור</v>
+        <v>אגם בוחבוט - עשרים ואחת</v>
       </c>
       <c r="B9" t="str">
-        <v>2025  02:09-12-31</v>
+        <v>2025  02:11-12-31</v>
       </c>
       <c r="C9" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-15</v>
@@ -578,16 +614,22 @@
       <c r="F9" t="str">
         <v>אלבומים חדשים</v>
       </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
+        <v>רבקה זוהר - רסיסים של אור</v>
       </c>
       <c r="B10" t="str">
-        <v>2025  02:08-12-31</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C10" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-15</v>
@@ -598,16 +640,22 @@
       <c r="F10" t="str">
         <v>אלבומים חדשים</v>
       </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
+        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
       </c>
       <c r="B11" t="str">
-        <v>2025  02:05-12-31</v>
+        <v>2025  02:08-12-31</v>
       </c>
       <c r="C11" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-15</v>
@@ -618,16 +666,22 @@
       <c r="F11" t="str">
         <v>אלבומים חדשים</v>
       </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Imagine פסטיגל - שירי התחרות</v>
+        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
       </c>
       <c r="B12" t="str">
-        <v>2025  02:04-12-31</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C12" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-15</v>
@@ -638,16 +692,22 @@
       <c r="F12" t="str">
         <v>אלבומים חדשים</v>
       </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>השמחות - חובות אבודים</v>
+        <v>Imagine פסטיגל - שירי התחרות</v>
       </c>
       <c r="B13" t="str">
-        <v>2025  02:02-12-31</v>
+        <v>2025  02:04-12-31</v>
       </c>
       <c r="C13" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-15</v>
@@ -658,16 +718,22 @@
       <c r="F13" t="str">
         <v>אלבומים חדשים</v>
       </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>שלמה גרוניך - כמו כוכבים</v>
+        <v>השמחות - חובות אבודים</v>
       </c>
       <c r="B14" t="str">
-        <v>2025  02:00-12-31</v>
+        <v>2025  02:02-12-31</v>
       </c>
       <c r="C14" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-15</v>
@@ -678,16 +744,22 @@
       <c r="F14" t="str">
         <v>אלבומים חדשים</v>
       </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>יוני רועה - מפוזרים</v>
+        <v>שלמה גרוניך - כמו כוכבים</v>
       </c>
       <c r="B15" t="str">
-        <v>2025  01:56-12-31</v>
+        <v>2025  02:00-12-31</v>
       </c>
       <c r="C15" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-15</v>
@@ -698,22 +770,28 @@
       <c r="F15" t="str">
         <v>אלבומים חדשים</v>
       </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>פטריק סבג Hotel Mogador</v>
+        <v>יוני רועה - מפוזרים</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-01-13</v>
+        <v>2025  01:56-12-31</v>
       </c>
       <c r="C16" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-01-13</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E16" t="str">
-        <v>האלבום של פטריק סבג אינו אוסף שירים אקראי, אלא מרחב. מקום לשהות בו.  נכנסים, שומעים, ויוצאים קצת אחרים. הבחירה בשם "הוטל מוגדור” היא כבר הצהרה. מלון = מקום מעבר, לא בית קבוע, מוגדור = עיר נמל, תנועה, ערבוב תרבויות. כך</v>
+        <v/>
       </c>
       <c r="F16" t="str">
         <v>אלבומים חדשים</v>
@@ -727,19 +805,19 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>|אלבום חדש| תומר יוסף - 360 ()</v>
+        <v>פטריק סבג Hotel Mogador</v>
       </c>
       <c r="B17" t="str">
-        <v>2026  11:38-01-09</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C17" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-13</v>
       </c>
       <c r="E17" t="str">
-        <v/>
+        <v>האלבום של פטריק סבג אינו אוסף שירים אקראי, אלא מרחב. מקום לשהות בו.  נכנסים, שומעים, ויוצאים קצת אחרים. הבחירה בשם "הוטל מוגדור” היא כבר הצהרה. מלון = מקום מעבר, לא בית קבוע, מוגדור = עיר נמל, תנועה, ערבוב תרבויות. כך</v>
       </c>
       <c r="F17" t="str">
         <v>אלבומים חדשים</v>
@@ -759,13 +837,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע ()</v>
+        <v>|אלבום חדש| תומר יוסף - 360 ()</v>
       </c>
       <c r="B18" t="str">
-        <v>2025  02:17-12-31</v>
+        <v>2026  11:38-01-09</v>
       </c>
       <c r="C18" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-10</v>
@@ -788,16 +866,22 @@
       <c r="J18" t="str">
         <v/>
       </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>|אלבום חדש| אברהם טל - חי ()</v>
+        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע ()</v>
       </c>
       <c r="B19" t="str">
-        <v>2025  02:16-12-31</v>
+        <v>2025  02:17-12-31</v>
       </c>
       <c r="C19" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-10</v>
@@ -820,16 +904,22 @@
       <c r="J19" t="str">
         <v/>
       </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>|אלבום חדש| מיקי גבריאלוב - שלום ()</v>
+        <v>|אלבום חדש| אברהם טל - חי ()</v>
       </c>
       <c r="B20" t="str">
-        <v>2025  02:13-12-31</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C20" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-10</v>
@@ -852,16 +942,22 @@
       <c r="J20" t="str">
         <v/>
       </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם ()</v>
+        <v>|אלבום חדש| מיקי גבריאלוב - שלום ()</v>
       </c>
       <c r="B21" t="str">
-        <v>2025  02:12-12-31</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C21" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-10</v>
@@ -884,16 +980,22 @@
       <c r="J21" t="str">
         <v/>
       </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון ()</v>
+        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם ()</v>
       </c>
       <c r="B22" t="str">
-        <v>2025  02:10-12-31</v>
+        <v>2025  02:12-12-31</v>
       </c>
       <c r="C22" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-10</v>
@@ -916,16 +1018,22 @@
       <c r="J22" t="str">
         <v/>
       </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה ()</v>
+        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון ()</v>
       </c>
       <c r="B23" t="str">
-        <v>2025  02:09-12-31</v>
+        <v>2025  02:10-12-31</v>
       </c>
       <c r="C23" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-10</v>
@@ -948,16 +1056,22 @@
       <c r="J23" t="str">
         <v/>
       </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים ()</v>
+        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה ()</v>
       </c>
       <c r="B24" t="str">
-        <v>2025  02:06-12-31</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C24" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-10</v>
@@ -980,16 +1094,22 @@
       <c r="J24" t="str">
         <v/>
       </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם ()</v>
+        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים ()</v>
       </c>
       <c r="B25" t="str">
-        <v>2025  02:05-12-31</v>
+        <v>2025  02:06-12-31</v>
       </c>
       <c r="C25" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-10</v>
@@ -1012,16 +1132,22 @@
       <c r="J25" t="str">
         <v/>
       </c>
+      <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>|אלבום חדש| סטטיק - קעקועים ()</v>
+        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם ()</v>
       </c>
       <c r="B26" t="str">
-        <v>2025  02:03-12-31</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C26" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-10</v>
@@ -1044,16 +1170,22 @@
       <c r="J26" t="str">
         <v/>
       </c>
+      <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>|אלבום חדש| ליאור נרקיס - דיסוננס ()</v>
+        <v>|אלבום חדש| סטטיק - קעקועים ()</v>
       </c>
       <c r="B27" t="str">
-        <v>2025  02:01-12-31</v>
+        <v>2025  02:03-12-31</v>
       </c>
       <c r="C27" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-10</v>
@@ -1076,16 +1208,22 @@
       <c r="J27" t="str">
         <v/>
       </c>
+      <c r="K27" t="str">
+        <v/>
+      </c>
+      <c r="L27" t="str">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) ()</v>
+        <v>|אלבום חדש| ליאור נרקיס - דיסוננס ()</v>
       </c>
       <c r="B28" t="str">
-        <v>2025  01:57-12-31</v>
+        <v>2025  02:01-12-31</v>
       </c>
       <c r="C28" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-10</v>
@@ -1108,16 +1246,22 @@
       <c r="J28" t="str">
         <v/>
       </c>
+      <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28" t="str">
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>|אלבום חדש| אתניקס - איטליה ()</v>
+        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) ()</v>
       </c>
       <c r="B29" t="str">
-        <v>2025  01:55-12-31</v>
+        <v>2025  01:57-12-31</v>
       </c>
       <c r="C29" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-10</v>
@@ -1140,19 +1284,25 @@
       <c r="J29" t="str">
         <v/>
       </c>
+      <c r="K29" t="str">
+        <v/>
+      </c>
+      <c r="L29" t="str">
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>|| תומר יוסף - 360 (2026)</v>
+        <v>|אלבום חדש| אתניקס - איטליה ()</v>
       </c>
       <c r="B30" t="str">
-        <v>2026  11:38-01-09</v>
+        <v>2025  01:55-12-31</v>
       </c>
       <c r="C30" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1181,13 +1331,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>|| עמיר בניון - לא נוגע בקרקע ()</v>
+        <v>|| תומר יוסף - 360 (2026)</v>
       </c>
       <c r="B31" t="str">
-        <v>2025  02:17-12-31</v>
+        <v>2026  11:38-01-09</v>
       </c>
       <c r="C31" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-09</v>
@@ -1216,16 +1366,22 @@
       <c r="L31" t="str">
         <v/>
       </c>
+      <c r="M31" t="str">
+        <v/>
+      </c>
+      <c r="N31" t="str">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>|| אברהם טל - חי ()</v>
+        <v>|| עמיר בניון - לא נוגע בקרקע ()</v>
       </c>
       <c r="B32" t="str">
-        <v>2025  02:16-12-31</v>
+        <v>2025  02:17-12-31</v>
       </c>
       <c r="C32" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-09</v>
@@ -1254,16 +1410,22 @@
       <c r="L32" t="str">
         <v/>
       </c>
+      <c r="M32" t="str">
+        <v/>
+      </c>
+      <c r="N32" t="str">
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>|| מיקי גבריאלוב - שלום ()</v>
+        <v>|| אברהם טל - חי ()</v>
       </c>
       <c r="B33" t="str">
-        <v>2025  02:13-12-31</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C33" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-09</v>
@@ -1292,16 +1454,22 @@
       <c r="L33" t="str">
         <v/>
       </c>
+      <c r="M33" t="str">
+        <v/>
+      </c>
+      <c r="N33" t="str">
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>|| בזכרי ימים ימימה - מחווה לצלילי הכרם ()</v>
+        <v>|| מיקי גבריאלוב - שלום ()</v>
       </c>
       <c r="B34" t="str">
-        <v>2025  02:12-12-31</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C34" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-09</v>
@@ -1330,16 +1498,22 @@
       <c r="L34" t="str">
         <v/>
       </c>
+      <c r="M34" t="str">
+        <v/>
+      </c>
+      <c r="N34" t="str">
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>|| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון ()</v>
+        <v>|| בזכרי ימים ימימה - מחווה לצלילי הכרם ()</v>
       </c>
       <c r="B35" t="str">
-        <v>2025  02:10-12-31</v>
+        <v>2025  02:12-12-31</v>
       </c>
       <c r="C35" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-09</v>
@@ -1368,16 +1542,22 @@
       <c r="L35" t="str">
         <v/>
       </c>
+      <c r="M35" t="str">
+        <v/>
+      </c>
+      <c r="N35" t="str">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>|| שלמה גרוניך - תודה אהבה ()</v>
+        <v>|| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון ()</v>
       </c>
       <c r="B36" t="str">
-        <v>2025  02:09-12-31</v>
+        <v>2025  02:10-12-31</v>
       </c>
       <c r="C36" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-09</v>
@@ -1406,16 +1586,22 @@
       <c r="L36" t="str">
         <v/>
       </c>
+      <c r="M36" t="str">
+        <v/>
+      </c>
+      <c r="N36" t="str">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>|| חוה אלברשטיין - חמישה שירים ()</v>
+        <v>|| שלמה גרוניך - תודה אהבה ()</v>
       </c>
       <c r="B37" t="str">
-        <v>2025  02:06-12-31</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C37" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-09</v>
@@ -1444,16 +1630,22 @@
       <c r="L37" t="str">
         <v/>
       </c>
+      <c r="M37" t="str">
+        <v/>
+      </c>
+      <c r="N37" t="str">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>|| הפרויקט של עידן רייכל - עד סוף העולם ()</v>
+        <v>|| חוה אלברשטיין - חמישה שירים ()</v>
       </c>
       <c r="B38" t="str">
-        <v>2025  02:05-12-31</v>
+        <v>2025  02:06-12-31</v>
       </c>
       <c r="C38" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-09</v>
@@ -1482,16 +1674,22 @@
       <c r="L38" t="str">
         <v/>
       </c>
+      <c r="M38" t="str">
+        <v/>
+      </c>
+      <c r="N38" t="str">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>|| סטטיק - קעקועים ()</v>
+        <v>|| הפרויקט של עידן רייכל - עד סוף העולם ()</v>
       </c>
       <c r="B39" t="str">
-        <v>2025  02:03-12-31</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C39" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-09</v>
@@ -1520,16 +1718,22 @@
       <c r="L39" t="str">
         <v/>
       </c>
+      <c r="M39" t="str">
+        <v/>
+      </c>
+      <c r="N39" t="str">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>|| ליאור נרקיס - דיסוננס ()</v>
+        <v>|| סטטיק - קעקועים ()</v>
       </c>
       <c r="B40" t="str">
-        <v>2025  02:01-12-31</v>
+        <v>2025  02:03-12-31</v>
       </c>
       <c r="C40" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-09</v>
@@ -1558,16 +1762,22 @@
       <c r="L40" t="str">
         <v/>
       </c>
+      <c r="M40" t="str">
+        <v/>
+      </c>
+      <c r="N40" t="str">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>|| דיוויד ברוזה - BrozaJazz (Paris Alhambra) ()</v>
+        <v>|| ליאור נרקיס - דיסוננס ()</v>
       </c>
       <c r="B41" t="str">
-        <v>2025  01:57-12-31</v>
+        <v>2025  02:01-12-31</v>
       </c>
       <c r="C41" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-09</v>
@@ -1596,16 +1806,22 @@
       <c r="L41" t="str">
         <v/>
       </c>
+      <c r="M41" t="str">
+        <v/>
+      </c>
+      <c r="N41" t="str">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>|| אתניקס - איטליה ()</v>
+        <v>|| דיוויד ברוזה - BrozaJazz (Paris Alhambra) ()</v>
       </c>
       <c r="B42" t="str">
-        <v>2025  01:55-12-31</v>
+        <v>2025  01:57-12-31</v>
       </c>
       <c r="C42" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-09</v>
@@ -1634,22 +1850,28 @@
       <c r="L42" t="str">
         <v/>
       </c>
+      <c r="M42" t="str">
+        <v/>
+      </c>
+      <c r="N42" t="str">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>מארינה מקסימיליאן – ריק בחלל</v>
+        <v>|| אתניקס - איטליה ()</v>
       </c>
       <c r="B43" t="str">
-        <v>2026-01-09</v>
+        <v>2025  01:55-12-31</v>
       </c>
       <c r="C43" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-09</v>
       </c>
       <c r="E43" t="str">
-        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
+        <v/>
       </c>
       <c r="F43" t="str">
         <v>אלבומים חדשים</v>
@@ -1681,19 +1903,19 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>|| אייל גולן - בית מפואר ()</v>
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
       </c>
       <c r="B44" t="str">
-        <v>2025  02:18-12-31</v>
+        <v>2026-01-09</v>
       </c>
       <c r="C44" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E44" t="str">
-        <v/>
+        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
       </c>
       <c r="F44" t="str">
         <v>אלבומים חדשים</v>
@@ -1731,13 +1953,13 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>|| הפרויקט של דודי לוי ואבטיפוס - הפטריקים ()</v>
+        <v>|| אייל גולן - בית מפואר ()</v>
       </c>
       <c r="B45" t="str">
-        <v>2025  02:16-12-31</v>
+        <v>2025  02:18-12-31</v>
       </c>
       <c r="C45" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-08</v>
@@ -1776,18 +1998,24 @@
         <v/>
       </c>
       <c r="P45" t="str">
+        <v/>
+      </c>
+      <c r="Q45" t="str">
+        <v/>
+      </c>
+      <c r="R45" t="str">
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>|| שיר לוי - ילד מוזר ()</v>
+        <v>|| הפרויקט של דודי לוי ואבטיפוס - הפטריקים ()</v>
       </c>
       <c r="B46" t="str">
-        <v>2025  02:14-12-31</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C46" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-08</v>
@@ -1826,18 +2054,24 @@
         <v/>
       </c>
       <c r="P46" t="str">
+        <v/>
+      </c>
+      <c r="Q46" t="str">
+        <v/>
+      </c>
+      <c r="R46" t="str">
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>|| פיטר רוט - 50 ()</v>
+        <v>|| שיר לוי - ילד מוזר ()</v>
       </c>
       <c r="B47" t="str">
-        <v>2025  02:13-12-31</v>
+        <v>2025  02:14-12-31</v>
       </c>
       <c r="C47" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-08</v>
@@ -1876,18 +2110,24 @@
         <v/>
       </c>
       <c r="P47" t="str">
+        <v/>
+      </c>
+      <c r="Q47" t="str">
+        <v/>
+      </c>
+      <c r="R47" t="str">
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>|| אגם בוחבוט - עשרים ואחת ()</v>
+        <v>|| פיטר רוט - 50 ()</v>
       </c>
       <c r="B48" t="str">
-        <v>2025  02:11-12-31</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C48" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-08</v>
@@ -1926,18 +2166,24 @@
         <v/>
       </c>
       <c r="P48" t="str">
+        <v/>
+      </c>
+      <c r="Q48" t="str">
+        <v/>
+      </c>
+      <c r="R48" t="str">
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>|| רבקה זוהר - רסיסים של אור ()</v>
+        <v>|| אגם בוחבוט - עשרים ואחת ()</v>
       </c>
       <c r="B49" t="str">
-        <v>2025  02:09-12-31</v>
+        <v>2025  02:11-12-31</v>
       </c>
       <c r="C49" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-08</v>
@@ -1976,18 +2222,24 @@
         <v/>
       </c>
       <c r="P49" t="str">
+        <v/>
+      </c>
+      <c r="Q49" t="str">
+        <v/>
+      </c>
+      <c r="R49" t="str">
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>|| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות ()</v>
+        <v>|| רבקה זוהר - רסיסים של אור ()</v>
       </c>
       <c r="B50" t="str">
-        <v>2025  02:08-12-31</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C50" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-08</v>
@@ -2026,18 +2278,24 @@
         <v/>
       </c>
       <c r="P50" t="str">
+        <v/>
+      </c>
+      <c r="Q50" t="str">
+        <v/>
+      </c>
+      <c r="R50" t="str">
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>|| אהוד בנאי ובנו הנדלר - פליטי הדאב ()</v>
+        <v>|| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות ()</v>
       </c>
       <c r="B51" t="str">
-        <v>2025  02:05-12-31</v>
+        <v>2025  02:08-12-31</v>
       </c>
       <c r="C51" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-08</v>
@@ -2076,18 +2334,24 @@
         <v/>
       </c>
       <c r="P51" t="str">
+        <v/>
+      </c>
+      <c r="Q51" t="str">
+        <v/>
+      </c>
+      <c r="R51" t="str">
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>|| Imagine פסטיגל - שירי התחרות ()</v>
+        <v>|| אהוד בנאי ובנו הנדלר - פליטי הדאב ()</v>
       </c>
       <c r="B52" t="str">
-        <v>2025  02:04-12-31</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C52" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-08</v>
@@ -2126,18 +2390,24 @@
         <v/>
       </c>
       <c r="P52" t="str">
+        <v/>
+      </c>
+      <c r="Q52" t="str">
+        <v/>
+      </c>
+      <c r="R52" t="str">
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>|| השמחות - חובות אבודים ()</v>
+        <v>|| Imagine פסטיגל - שירי התחרות ()</v>
       </c>
       <c r="B53" t="str">
-        <v>2025  02:02-12-31</v>
+        <v>2025  02:04-12-31</v>
       </c>
       <c r="C53" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-08</v>
@@ -2176,18 +2446,24 @@
         <v/>
       </c>
       <c r="P53" t="str">
+        <v/>
+      </c>
+      <c r="Q53" t="str">
+        <v/>
+      </c>
+      <c r="R53" t="str">
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>|| שלמה גרוניך - כמו כוכבים ()</v>
+        <v>|| השמחות - חובות אבודים ()</v>
       </c>
       <c r="B54" t="str">
-        <v>2025  02:00-12-31</v>
+        <v>2025  02:02-12-31</v>
       </c>
       <c r="C54" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-08</v>
@@ -2226,18 +2502,24 @@
         <v/>
       </c>
       <c r="P54" t="str">
+        <v/>
+      </c>
+      <c r="Q54" t="str">
+        <v/>
+      </c>
+      <c r="R54" t="str">
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>|| יוני רועה - מפוזרים ()</v>
+        <v>|| שלמה גרוניך - כמו כוכבים ()</v>
       </c>
       <c r="B55" t="str">
-        <v>2025  01:56-12-31</v>
+        <v>2025  02:00-12-31</v>
       </c>
       <c r="C55" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-08</v>
@@ -2276,18 +2558,24 @@
         <v/>
       </c>
       <c r="P55" t="str">
+        <v/>
+      </c>
+      <c r="Q55" t="str">
+        <v/>
+      </c>
+      <c r="R55" t="str">
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>|| התקווה 6 - ויהי אור ()</v>
+        <v>|| יוני רועה - מפוזרים ()</v>
       </c>
       <c r="B56" t="str">
-        <v>2025  01:54-12-31</v>
+        <v>2025  01:56-12-31</v>
       </c>
       <c r="C56" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-08</v>
@@ -2326,18 +2614,24 @@
         <v/>
       </c>
       <c r="P56" t="str">
+        <v/>
+      </c>
+      <c r="Q56" t="str">
+        <v/>
+      </c>
+      <c r="R56" t="str">
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>|| שאנן סטריט ודי ג׳יי מש - באתי לבדר ()</v>
+        <v>|| התקווה 6 - ויהי אור ()</v>
       </c>
       <c r="B57" t="str">
-        <v>2025  01:53-12-31</v>
+        <v>2025  01:54-12-31</v>
       </c>
       <c r="C57" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-08</v>
@@ -2376,18 +2670,24 @@
         <v/>
       </c>
       <c r="P57" t="str">
+        <v/>
+      </c>
+      <c r="Q57" t="str">
+        <v/>
+      </c>
+      <c r="R57" t="str">
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>אשכול נוכחות למשתמשים פעילים</v>
+        <v>|| שאנן סטריט ודי ג׳יי מש - באתי לבדר ()</v>
       </c>
       <c r="B58" t="str">
-        <v>2025  16:32 מאת freund-10-16</v>
+        <v>2025  01:53-12-31</v>
       </c>
       <c r="C58" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=23455&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-08</v>
@@ -2437,13 +2737,13 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>כיצד להוריד מהאתרים המפורסמים</v>
+        <v>אשכול נוכחות למשתמשים פעילים</v>
       </c>
       <c r="B59" t="str">
-        <v>2023  16:23 מאת petel1-08-08</v>
+        <v>2025  16:32 מאת freund-10-16</v>
       </c>
       <c r="C59" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=22411&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=23455&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-08</v>
@@ -2488,18 +2788,24 @@
         <v/>
       </c>
       <c r="R59" t="str">
+        <v/>
+      </c>
+      <c r="S59" t="str">
+        <v/>
+      </c>
+      <c r="T59" t="str">
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
+        <v>כיצד להוריד מהאתרים המפורסמים</v>
       </c>
       <c r="B60" t="str">
-        <v>2026  22:40 מאת מוטי_ד-01-01</v>
+        <v>2023  16:23 מאת petel1-08-08</v>
       </c>
       <c r="C60" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24435&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=22411&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-08</v>
@@ -2544,18 +2850,24 @@
         <v/>
       </c>
       <c r="R60" t="str">
+        <v/>
+      </c>
+      <c r="S60" t="str">
+        <v/>
+      </c>
+      <c r="T60" t="str">
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>|אלבום חדש| אייל גולן - בית מפואר (2025)</v>
+        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
       </c>
       <c r="B61" t="str">
-        <v>2025  02:18 מאת DiSHi-12-31</v>
+        <v>2026  22:40 מאת מוטי_ד-01-01</v>
       </c>
       <c r="C61" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24435&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-08</v>
@@ -2600,18 +2912,24 @@
         <v/>
       </c>
       <c r="R61" t="str">
+        <v/>
+      </c>
+      <c r="S61" t="str">
+        <v/>
+      </c>
+      <c r="T61" t="str">
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע (2025)</v>
+        <v>|אלבום חדש| אייל גולן - בית מפואר (2025)</v>
       </c>
       <c r="B62" t="str">
-        <v>2025  02:17 מאת DiSHi-12-31</v>
+        <v>2025  02:18 מאת DiSHi-12-31</v>
       </c>
       <c r="C62" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-08</v>
@@ -2656,18 +2974,24 @@
         <v/>
       </c>
       <c r="R62" t="str">
+        <v/>
+      </c>
+      <c r="S62" t="str">
+        <v/>
+      </c>
+      <c r="T62" t="str">
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>|אלבום חדש| הפרויקט של דודי לוי ואבטיפוס - הפטריקים (2025)</v>
+        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע (2025)</v>
       </c>
       <c r="B63" t="str">
-        <v>2025  02:16 מאת DiSHi-12-31</v>
+        <v>2025  02:17 מאת DiSHi-12-31</v>
       </c>
       <c r="C63" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-08</v>
@@ -2712,18 +3036,24 @@
         <v/>
       </c>
       <c r="R63" t="str">
+        <v/>
+      </c>
+      <c r="S63" t="str">
+        <v/>
+      </c>
+      <c r="T63" t="str">
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>|אלבום חדש| אברהם טל - חי (2025)</v>
+        <v>|אלבום חדש| הפרויקט של דודי לוי ואבטיפוס - הפטריקים (2025)</v>
       </c>
       <c r="B64" t="str">
         <v>2025  02:16 מאת DiSHi-12-31</v>
       </c>
       <c r="C64" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-08</v>
@@ -2768,18 +3098,24 @@
         <v/>
       </c>
       <c r="R64" t="str">
+        <v/>
+      </c>
+      <c r="S64" t="str">
+        <v/>
+      </c>
+      <c r="T64" t="str">
         <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>|אלבום חדש| שיר לוי - ילד מוזר (2025)</v>
+        <v>|אלבום חדש| אברהם טל - חי (2025)</v>
       </c>
       <c r="B65" t="str">
-        <v>2025  02:14 מאת DiSHi-12-31</v>
+        <v>2025  02:16 מאת DiSHi-12-31</v>
       </c>
       <c r="C65" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-08</v>
@@ -2824,18 +3160,24 @@
         <v/>
       </c>
       <c r="R65" t="str">
+        <v/>
+      </c>
+      <c r="S65" t="str">
+        <v/>
+      </c>
+      <c r="T65" t="str">
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>|אלבום חדש| מיקי גבריאלוב - שלום (2025)</v>
+        <v>|אלבום חדש| שיר לוי - ילד מוזר (2025)</v>
       </c>
       <c r="B66" t="str">
-        <v>2025  02:13 מאת DiSHi-12-31</v>
+        <v>2025  02:14 מאת DiSHi-12-31</v>
       </c>
       <c r="C66" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-08</v>
@@ -2880,18 +3222,24 @@
         <v/>
       </c>
       <c r="R66" t="str">
+        <v/>
+      </c>
+      <c r="S66" t="str">
+        <v/>
+      </c>
+      <c r="T66" t="str">
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>|אלבום חדש| פיטר רוט - 50 (2025)</v>
+        <v>|אלבום חדש| מיקי גבריאלוב - שלום (2025)</v>
       </c>
       <c r="B67" t="str">
         <v>2025  02:13 מאת DiSHi-12-31</v>
       </c>
       <c r="C67" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-08</v>
@@ -2936,18 +3284,24 @@
         <v/>
       </c>
       <c r="R67" t="str">
+        <v/>
+      </c>
+      <c r="S67" t="str">
+        <v/>
+      </c>
+      <c r="T67" t="str">
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם (2025)</v>
+        <v>|אלבום חדש| פיטר רוט - 50 (2025)</v>
       </c>
       <c r="B68" t="str">
-        <v>2025  02:12 מאת DiSHi-12-31</v>
+        <v>2025  02:13 מאת DiSHi-12-31</v>
       </c>
       <c r="C68" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-08</v>
@@ -2992,18 +3346,24 @@
         <v/>
       </c>
       <c r="R68" t="str">
+        <v/>
+      </c>
+      <c r="S68" t="str">
+        <v/>
+      </c>
+      <c r="T68" t="str">
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>|אלבום חדש| אגם בוחבוט - עשרים ואחת (2025)</v>
+        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם (2025)</v>
       </c>
       <c r="B69" t="str">
-        <v>2025  02:11 מאת DiSHi-12-31</v>
+        <v>2025  02:12 מאת DiSHi-12-31</v>
       </c>
       <c r="C69" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-08</v>
@@ -3048,18 +3408,24 @@
         <v/>
       </c>
       <c r="R69" t="str">
+        <v/>
+      </c>
+      <c r="S69" t="str">
+        <v/>
+      </c>
+      <c r="T69" t="str">
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון (2025)</v>
+        <v>|אלבום חדש| אגם בוחבוט - עשרים ואחת (2025)</v>
       </c>
       <c r="B70" t="str">
-        <v>2025  02:10 מאת DiSHi-12-31</v>
+        <v>2025  02:11 מאת DiSHi-12-31</v>
       </c>
       <c r="C70" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-08</v>
@@ -3104,18 +3470,24 @@
         <v/>
       </c>
       <c r="R70" t="str">
+        <v/>
+      </c>
+      <c r="S70" t="str">
+        <v/>
+      </c>
+      <c r="T70" t="str">
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>|אלבום חדש| רבקה זוהר - רסיסים של אור (2025)</v>
+        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון (2025)</v>
       </c>
       <c r="B71" t="str">
-        <v>2025  02:09 מאת DiSHi-12-31</v>
+        <v>2025  02:10 מאת DiSHi-12-31</v>
       </c>
       <c r="C71" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-08</v>
@@ -3160,18 +3532,24 @@
         <v/>
       </c>
       <c r="R71" t="str">
+        <v/>
+      </c>
+      <c r="S71" t="str">
+        <v/>
+      </c>
+      <c r="T71" t="str">
         <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה (2025)</v>
+        <v>|אלבום חדש| רבקה זוהר - רסיסים של אור (2025)</v>
       </c>
       <c r="B72" t="str">
         <v>2025  02:09 מאת DiSHi-12-31</v>
       </c>
       <c r="C72" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-08</v>
@@ -3216,18 +3594,24 @@
         <v/>
       </c>
       <c r="R72" t="str">
+        <v/>
+      </c>
+      <c r="S72" t="str">
+        <v/>
+      </c>
+      <c r="T72" t="str">
         <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>|אלבום חדש| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות (2025)</v>
+        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה (2025)</v>
       </c>
       <c r="B73" t="str">
-        <v>2025  02:08 מאת DiSHi-12-31</v>
+        <v>2025  02:09 מאת DiSHi-12-31</v>
       </c>
       <c r="C73" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-08</v>
@@ -3272,18 +3656,24 @@
         <v/>
       </c>
       <c r="R73" t="str">
+        <v/>
+      </c>
+      <c r="S73" t="str">
+        <v/>
+      </c>
+      <c r="T73" t="str">
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים (2025)</v>
+        <v>|אלבום חדש| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות (2025)</v>
       </c>
       <c r="B74" t="str">
-        <v>2025  02:06 מאת DiSHi-12-31</v>
+        <v>2025  02:08 מאת DiSHi-12-31</v>
       </c>
       <c r="C74" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-08</v>
@@ -3328,18 +3718,24 @@
         <v/>
       </c>
       <c r="R74" t="str">
+        <v/>
+      </c>
+      <c r="S74" t="str">
+        <v/>
+      </c>
+      <c r="T74" t="str">
         <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>|אלבום חדש| אהוד בנאי ובנו הנדלר - פליטי הדאב (2025)</v>
+        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים (2025)</v>
       </c>
       <c r="B75" t="str">
-        <v>2025  02:05 מאת DiSHi-12-31</v>
+        <v>2025  02:06 מאת DiSHi-12-31</v>
       </c>
       <c r="C75" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-08</v>
@@ -3384,18 +3780,24 @@
         <v/>
       </c>
       <c r="R75" t="str">
+        <v/>
+      </c>
+      <c r="S75" t="str">
+        <v/>
+      </c>
+      <c r="T75" t="str">
         <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם (2025)</v>
+        <v>|אלבום חדש| אהוד בנאי ובנו הנדלר - פליטי הדאב (2025)</v>
       </c>
       <c r="B76" t="str">
         <v>2025  02:05 מאת DiSHi-12-31</v>
       </c>
       <c r="C76" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-08</v>
@@ -3440,18 +3842,24 @@
         <v/>
       </c>
       <c r="R76" t="str">
+        <v/>
+      </c>
+      <c r="S76" t="str">
+        <v/>
+      </c>
+      <c r="T76" t="str">
         <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>|אלבום חדש| Imagine פסטיגל - שירי התחרות (2025)</v>
+        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם (2025)</v>
       </c>
       <c r="B77" t="str">
-        <v>2025  02:04 מאת DiSHi-12-31</v>
+        <v>2025  02:05 מאת DiSHi-12-31</v>
       </c>
       <c r="C77" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-08</v>
@@ -3496,18 +3904,24 @@
         <v/>
       </c>
       <c r="R77" t="str">
+        <v/>
+      </c>
+      <c r="S77" t="str">
+        <v/>
+      </c>
+      <c r="T77" t="str">
         <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>|אלבום חדש| סטטיק - קעקועים (2025)</v>
+        <v>|אלבום חדש| Imagine פסטיגל - שירי התחרות (2025)</v>
       </c>
       <c r="B78" t="str">
-        <v>2025  02:03 מאת DiSHi-12-31</v>
+        <v>2025  02:04 מאת DiSHi-12-31</v>
       </c>
       <c r="C78" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-08</v>
@@ -3552,18 +3966,24 @@
         <v/>
       </c>
       <c r="R78" t="str">
+        <v/>
+      </c>
+      <c r="S78" t="str">
+        <v/>
+      </c>
+      <c r="T78" t="str">
         <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>|אלבום חדש| השמחות - חובות אבודים (2025)</v>
+        <v>|אלבום חדש| סטטיק - קעקועים (2025)</v>
       </c>
       <c r="B79" t="str">
-        <v>2025  02:02 מאת DiSHi-12-31</v>
+        <v>2025  02:03 מאת DiSHi-12-31</v>
       </c>
       <c r="C79" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-08</v>
@@ -3608,18 +4028,24 @@
         <v/>
       </c>
       <c r="R79" t="str">
+        <v/>
+      </c>
+      <c r="S79" t="str">
+        <v/>
+      </c>
+      <c r="T79" t="str">
         <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>|אלבום חדש| ליאור נרקיס - דיסוננס (2025)</v>
+        <v>|אלבום חדש| השמחות - חובות אבודים (2025)</v>
       </c>
       <c r="B80" t="str">
-        <v>2025  02:01 מאת DiSHi-12-31</v>
+        <v>2025  02:02 מאת DiSHi-12-31</v>
       </c>
       <c r="C80" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-08</v>
@@ -3664,18 +4090,24 @@
         <v/>
       </c>
       <c r="R80" t="str">
+        <v/>
+      </c>
+      <c r="S80" t="str">
+        <v/>
+      </c>
+      <c r="T80" t="str">
         <v/>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>|אלבום חדש| שלמה גרוניך - כמו כוכבים (2025)</v>
+        <v>|אלבום חדש| ליאור נרקיס - דיסוננס (2025)</v>
       </c>
       <c r="B81" t="str">
-        <v>2025  02:00 מאת DiSHi-12-31</v>
+        <v>2025  02:01 מאת DiSHi-12-31</v>
       </c>
       <c r="C81" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-08</v>
@@ -3720,18 +4152,24 @@
         <v/>
       </c>
       <c r="R81" t="str">
+        <v/>
+      </c>
+      <c r="S81" t="str">
+        <v/>
+      </c>
+      <c r="T81" t="str">
         <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) (2025)</v>
+        <v>|אלבום חדש| שלמה גרוניך - כמו כוכבים (2025)</v>
       </c>
       <c r="B82" t="str">
-        <v>2025  01:57 מאת DiSHi-12-31</v>
+        <v>2025  02:00 מאת DiSHi-12-31</v>
       </c>
       <c r="C82" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-08</v>
@@ -3776,18 +4214,24 @@
         <v/>
       </c>
       <c r="R82" t="str">
+        <v/>
+      </c>
+      <c r="S82" t="str">
+        <v/>
+      </c>
+      <c r="T82" t="str">
         <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>|אלבום חדש| יוני רועה - מפוזרים (2025)</v>
+        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) (2025)</v>
       </c>
       <c r="B83" t="str">
-        <v>2025  01:56 מאת DiSHi-12-31</v>
+        <v>2025  01:57 מאת DiSHi-12-31</v>
       </c>
       <c r="C83" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-08</v>
@@ -3832,18 +4276,24 @@
         <v/>
       </c>
       <c r="R83" t="str">
+        <v/>
+      </c>
+      <c r="S83" t="str">
+        <v/>
+      </c>
+      <c r="T83" t="str">
         <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>|אלבום חדש| אתניקס - איטליה (2025)</v>
+        <v>|אלבום חדש| יוני רועה - מפוזרים (2025)</v>
       </c>
       <c r="B84" t="str">
-        <v>2025  01:55 מאת DiSHi-12-31</v>
+        <v>2025  01:56 מאת DiSHi-12-31</v>
       </c>
       <c r="C84" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-08</v>
@@ -3888,18 +4338,24 @@
         <v/>
       </c>
       <c r="R84" t="str">
+        <v/>
+      </c>
+      <c r="S84" t="str">
+        <v/>
+      </c>
+      <c r="T84" t="str">
         <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>|אלבום חדש| התקווה 6 - ויהי אור (2025)</v>
+        <v>|אלבום חדש| אתניקס - איטליה (2025)</v>
       </c>
       <c r="B85" t="str">
-        <v>2025  01:54 מאת DiSHi-12-31</v>
+        <v>2025  01:55 מאת DiSHi-12-31</v>
       </c>
       <c r="C85" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-08</v>
@@ -3944,18 +4400,24 @@
         <v/>
       </c>
       <c r="R85" t="str">
+        <v/>
+      </c>
+      <c r="S85" t="str">
+        <v/>
+      </c>
+      <c r="T85" t="str">
         <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>|אלבום חדש| שלומי סרנגה - איפרכו (2025)</v>
+        <v>|אלבום חדש| התקווה 6 - ויהי אור (2025)</v>
       </c>
       <c r="B86" t="str">
-        <v>2025  01:53 מאת DiSHi-12-31</v>
+        <v>2025  01:54 מאת DiSHi-12-31</v>
       </c>
       <c r="C86" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24430&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-08</v>
@@ -4000,18 +4462,24 @@
         <v/>
       </c>
       <c r="R86" t="str">
+        <v/>
+      </c>
+      <c r="S86" t="str">
+        <v/>
+      </c>
+      <c r="T86" t="str">
         <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>|אלבום חדש| שאנן סטריט ודי ג׳יי מש - באתי לבדר (2025)</v>
+        <v>|אלבום חדש| שלומי סרנגה - איפרכו (2025)</v>
       </c>
       <c r="B87" t="str">
         <v>2025  01:53 מאת DiSHi-12-31</v>
       </c>
       <c r="C87" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24430&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-08</v>
@@ -4056,18 +4524,24 @@
         <v/>
       </c>
       <c r="R87" t="str">
+        <v/>
+      </c>
+      <c r="S87" t="str">
+        <v/>
+      </c>
+      <c r="T87" t="str">
         <v/>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>הרשם לחברות מלאה</v>
+        <v>|אלבום חדש| שאנן סטריט ודי ג׳יי מש - באתי לבדר (2025)</v>
       </c>
       <c r="B88" t="str">
-        <v/>
+        <v>2025  01:53 מאת DiSHi-12-31</v>
       </c>
       <c r="C88" t="str">
-        <v>https://rotter.name/nor/members-new.html</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-08</v>
@@ -4112,24 +4586,30 @@
         <v/>
       </c>
       <c r="R88" t="str">
+        <v/>
+      </c>
+      <c r="S88" t="str">
+        <v/>
+      </c>
+      <c r="T88" t="str">
         <v/>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>אוליביה דין The Art of Loving</v>
+        <v>הרשם לחברות מלאה</v>
       </c>
       <c r="B89" t="str">
-        <v>2026-01-04</v>
+        <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
+        <v>https://rotter.name/nor/members-new.html</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E89" t="str">
-        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
+        <v/>
       </c>
       <c r="F89" t="str">
         <v>אלבומים חדשים</v>
@@ -4179,19 +4659,19 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Geese Getting Killed</v>
+        <v>אוליביה דין The Art of Loving</v>
       </c>
       <c r="B90" t="str">
-        <v>2025-12-29</v>
+        <v>2026-01-04</v>
       </c>
       <c r="C90" t="str">
-        <v>https://yosmusic.com/geese-getting-killed/</v>
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
       </c>
       <c r="D90" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E90" t="str">
-        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
+        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
       </c>
       <c r="F90" t="str">
         <v>אלבומים חדשים</v>
@@ -4236,24 +4716,30 @@
         <v/>
       </c>
       <c r="T90" t="str">
+        <v/>
+      </c>
+      <c r="U90" t="str">
+        <v/>
+      </c>
+      <c r="V90" t="str">
         <v/>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>רוסליה Lux</v>
+        <v>Geese Getting Killed</v>
       </c>
       <c r="B91" t="str">
-        <v>2025-12-25</v>
+        <v>2025-12-29</v>
       </c>
       <c r="C91" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
+        <v>https://yosmusic.com/geese-getting-killed/</v>
       </c>
       <c r="D91" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E91" t="str">
-        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
+        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
       </c>
       <c r="F91" t="str">
         <v>אלבומים חדשים</v>
@@ -4298,24 +4784,30 @@
         <v/>
       </c>
       <c r="T91" t="str">
+        <v/>
+      </c>
+      <c r="U91" t="str">
+        <v/>
+      </c>
+      <c r="V91" t="str">
         <v/>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>יאנגבלאד אירוסמית' one more time</v>
+        <v>רוסליה Lux</v>
       </c>
       <c r="B92" t="str">
-        <v>2025-12-17</v>
+        <v>2025-12-25</v>
       </c>
       <c r="C92" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
       </c>
       <c r="D92" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E92" t="str">
-        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
+        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
       </c>
       <c r="F92" t="str">
         <v>אלבומים חדשים</v>
@@ -4360,24 +4852,30 @@
         <v/>
       </c>
       <c r="T92" t="str">
+        <v/>
+      </c>
+      <c r="U92" t="str">
+        <v/>
+      </c>
+      <c r="V92" t="str">
         <v/>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>פינק פלויד Wish You Were Here 50</v>
+        <v>יאנגבלאד אירוסמית' one more time</v>
       </c>
       <c r="B93" t="str">
-        <v>2025-12-14</v>
+        <v>2025-12-17</v>
       </c>
       <c r="C93" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
+        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
       </c>
       <c r="D93" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E93" t="str">
-        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
+        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
       </c>
       <c r="F93" t="str">
         <v>אלבומים חדשים</v>
@@ -4422,24 +4920,30 @@
         <v/>
       </c>
       <c r="T93" t="str">
+        <v/>
+      </c>
+      <c r="U93" t="str">
+        <v/>
+      </c>
+      <c r="V93" t="str">
         <v/>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+        <v>פינק פלויד Wish You Were Here 50</v>
       </c>
       <c r="B94" t="str">
-        <v>2025-12-08</v>
+        <v>2025-12-14</v>
       </c>
       <c r="C94" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
       </c>
       <c r="D94" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E94" t="str">
-        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
+        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
       </c>
       <c r="F94" t="str">
         <v>אלבומים חדשים</v>
@@ -4484,24 +4988,30 @@
         <v/>
       </c>
       <c r="T94" t="str">
+        <v/>
+      </c>
+      <c r="U94" t="str">
+        <v/>
+      </c>
+      <c r="V94" t="str">
         <v/>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>סטריי קידס DO IT (EP)</v>
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
       </c>
       <c r="B95" t="str">
-        <v>2025-12-04</v>
+        <v>2025-12-08</v>
       </c>
       <c r="C95" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
+        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
       </c>
       <c r="D95" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E95" t="str">
-        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
+        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
       </c>
       <c r="F95" t="str">
         <v>אלבומים חדשים</v>
@@ -4546,24 +5056,30 @@
         <v/>
       </c>
       <c r="T95" t="str">
+        <v/>
+      </c>
+      <c r="U95" t="str">
+        <v/>
+      </c>
+      <c r="V95" t="str">
         <v/>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>דויד ברוזה BROZAJAZZ</v>
+        <v>סטריי קידס DO IT (EP)</v>
       </c>
       <c r="B96" t="str">
-        <v>2025-11-30</v>
+        <v>2025-12-04</v>
       </c>
       <c r="C96" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
+        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
       </c>
       <c r="D96" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E96" t="str">
-        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
+        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
       </c>
       <c r="F96" t="str">
         <v>אלבומים חדשים</v>
@@ -4608,24 +5124,30 @@
         <v/>
       </c>
       <c r="T96" t="str">
+        <v/>
+      </c>
+      <c r="U96" t="str">
+        <v/>
+      </c>
+      <c r="V96" t="str">
         <v/>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Five Seconds of Summer – Everyone's A Star</v>
+        <v>דויד ברוזה BROZAJAZZ</v>
       </c>
       <c r="B97" t="str">
-        <v>2025-11-24</v>
+        <v>2025-11-30</v>
       </c>
       <c r="C97" t="str">
-        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
       </c>
       <c r="D97" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E97" t="str">
-        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
+        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
       </c>
       <c r="F97" t="str">
         <v>אלבומים חדשים</v>
@@ -4670,24 +5192,30 @@
         <v/>
       </c>
       <c r="T97" t="str">
+        <v/>
+      </c>
+      <c r="U97" t="str">
+        <v/>
+      </c>
+      <c r="V97" t="str">
         <v/>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>התקווה 6 – ויהי אור</v>
+        <v>Five Seconds of Summer – Everyone's A Star</v>
       </c>
       <c r="B98" t="str">
-        <v>2025-11-20</v>
+        <v>2025-11-24</v>
       </c>
       <c r="C98" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
+        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
       </c>
       <c r="D98" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E98" t="str">
-        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
+        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
       </c>
       <c r="F98" t="str">
         <v>אלבומים חדשים</v>
@@ -4732,24 +5260,30 @@
         <v/>
       </c>
       <c r="T98" t="str">
+        <v/>
+      </c>
+      <c r="U98" t="str">
+        <v/>
+      </c>
+      <c r="V98" t="str">
         <v/>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>פלורנס אנד דה משין Everybody Scream</v>
+        <v>התקווה 6 – ויהי אור</v>
       </c>
       <c r="B99" t="str">
-        <v>2025-11-13</v>
+        <v>2025-11-20</v>
       </c>
       <c r="C99" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
+        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
       </c>
       <c r="D99" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E99" t="str">
-        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
+        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
       </c>
       <c r="F99" t="str">
         <v>אלבומים חדשים</v>
@@ -4794,24 +5328,30 @@
         <v/>
       </c>
       <c r="T99" t="str">
+        <v/>
+      </c>
+      <c r="U99" t="str">
+        <v/>
+      </c>
+      <c r="V99" t="str">
         <v/>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>טיים אימפלה Deadbeat</v>
+        <v>פלורנס אנד דה משין Everybody Scream</v>
       </c>
       <c r="B100" t="str">
-        <v>2025-11-03</v>
+        <v>2025-11-13</v>
       </c>
       <c r="C100" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
       </c>
       <c r="D100" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E100" t="str">
-        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
+        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
       </c>
       <c r="F100" t="str">
         <v>אלבומים חדשים</v>
@@ -4856,24 +5396,30 @@
         <v/>
       </c>
       <c r="T100" t="str">
+        <v/>
+      </c>
+      <c r="U100" t="str">
+        <v/>
+      </c>
+      <c r="V100" t="str">
         <v/>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+        <v>טיים אימפלה Deadbeat</v>
       </c>
       <c r="B101" t="str">
-        <v>2025-10-20</v>
+        <v>2025-11-03</v>
       </c>
       <c r="C101" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
       </c>
       <c r="D101" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E101" t="str">
-        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
+        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
       </c>
       <c r="F101" t="str">
         <v>אלבומים חדשים</v>
@@ -4918,24 +5464,30 @@
         <v/>
       </c>
       <c r="T101" t="str">
+        <v/>
+      </c>
+      <c r="U101" t="str">
+        <v/>
+      </c>
+      <c r="V101" t="str">
         <v/>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>שלמה גרוניך – תודה אהבה</v>
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
       </c>
       <c r="B102" t="str">
-        <v>2025-10-18</v>
+        <v>2025-10-20</v>
       </c>
       <c r="C102" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
+        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
       </c>
       <c r="D102" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E102" t="str">
-        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
+        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
       </c>
       <c r="F102" t="str">
         <v>אלבומים חדשים</v>
@@ -4980,24 +5532,30 @@
         <v/>
       </c>
       <c r="T102" t="str">
+        <v/>
+      </c>
+      <c r="U102" t="str">
+        <v/>
+      </c>
+      <c r="V102" t="str">
         <v/>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>טיילור סוויפט The Life Of A Showgirl</v>
+        <v>שלמה גרוניך – תודה אהבה</v>
       </c>
       <c r="B103" t="str">
-        <v>2025-10-11</v>
+        <v>2025-10-18</v>
       </c>
       <c r="C103" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
       </c>
       <c r="D103" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E103" t="str">
-        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
+        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
       </c>
       <c r="F103" t="str">
         <v>אלבומים חדשים</v>
@@ -5042,24 +5600,30 @@
         <v/>
       </c>
       <c r="T103" t="str">
+        <v/>
+      </c>
+      <c r="U103" t="str">
+        <v/>
+      </c>
+      <c r="V103" t="str">
         <v/>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>דוג'ה קאט Vie</v>
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
       </c>
       <c r="B104" t="str">
-        <v>2025-10-04</v>
+        <v>2025-10-11</v>
       </c>
       <c r="C104" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
       </c>
       <c r="D104" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E104" t="str">
-        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
+        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
       </c>
       <c r="F104" t="str">
         <v>אלבומים חדשים</v>
@@ -5104,24 +5668,30 @@
         <v/>
       </c>
       <c r="T104" t="str">
+        <v/>
+      </c>
+      <c r="U104" t="str">
+        <v/>
+      </c>
+      <c r="V104" t="str">
         <v/>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>ג'וי קרוקס Juniper</v>
+        <v>דוג'ה קאט Vie</v>
       </c>
       <c r="B105" t="str">
-        <v>2025-10-03</v>
+        <v>2025-10-04</v>
       </c>
       <c r="C105" t="str">
-        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
       </c>
       <c r="D105" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E105" t="str">
-        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
+        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
       </c>
       <c r="F105" t="str">
         <v>אלבומים חדשים</v>
@@ -5166,24 +5736,30 @@
         <v/>
       </c>
       <c r="T105" t="str">
+        <v/>
+      </c>
+      <c r="U105" t="str">
+        <v/>
+      </c>
+      <c r="V105" t="str">
         <v/>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>ביפי קליירו Futique</v>
+        <v>ג'וי קרוקס Juniper</v>
       </c>
       <c r="B106" t="str">
-        <v>2025-09-30</v>
+        <v>2025-10-03</v>
       </c>
       <c r="C106" t="str">
-        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
+        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
       </c>
       <c r="D106" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E106" t="str">
-        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
+        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
       </c>
       <c r="F106" t="str">
         <v>אלבומים חדשים</v>
@@ -5228,24 +5804,30 @@
         <v/>
       </c>
       <c r="T106" t="str">
+        <v/>
+      </c>
+      <c r="U106" t="str">
+        <v/>
+      </c>
+      <c r="V106" t="str">
         <v/>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>אד שירן Play</v>
+        <v>ביפי קליירו Futique</v>
       </c>
       <c r="B107" t="str">
-        <v>2025-09-24</v>
+        <v>2025-09-30</v>
       </c>
       <c r="C107" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
+        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
       </c>
       <c r="D107" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E107" t="str">
-        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
+        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
       </c>
       <c r="F107" t="str">
         <v>אלבומים חדשים</v>
@@ -5290,24 +5872,30 @@
         <v/>
       </c>
       <c r="T107" t="str">
+        <v/>
+      </c>
+      <c r="U107" t="str">
+        <v/>
+      </c>
+      <c r="V107" t="str">
         <v/>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+        <v>אד שירן Play</v>
       </c>
       <c r="B108" t="str">
-        <v>2025-09-21</v>
+        <v>2025-09-24</v>
       </c>
       <c r="C108" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
+        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
       </c>
       <c r="D108" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E108" t="str">
-        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
+        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
       </c>
       <c r="F108" t="str">
         <v>אלבומים חדשים</v>
@@ -5352,24 +5940,30 @@
         <v/>
       </c>
       <c r="T108" t="str">
+        <v/>
+      </c>
+      <c r="U108" t="str">
+        <v/>
+      </c>
+      <c r="V108" t="str">
         <v/>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>סוויד Antidepressants</v>
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
       </c>
       <c r="B109" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-21</v>
       </c>
       <c r="C109" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
+        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
       </c>
       <c r="D109" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E109" t="str">
-        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
+        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
       </c>
       <c r="F109" t="str">
         <v>אלבומים חדשים</v>
@@ -5414,24 +6008,30 @@
         <v/>
       </c>
       <c r="T109" t="str">
+        <v/>
+      </c>
+      <c r="U109" t="str">
+        <v/>
+      </c>
+      <c r="V109" t="str">
         <v/>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>וולף אליס The Clearing</v>
+        <v>סוויד Antidepressants</v>
       </c>
       <c r="B110" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-12</v>
       </c>
       <c r="C110" t="str">
-        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
+        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
       </c>
       <c r="D110" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E110" t="str">
-        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
+        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
       </c>
       <c r="F110" t="str">
         <v>אלבומים חדשים</v>
@@ -5476,24 +6076,30 @@
         <v/>
       </c>
       <c r="T110" t="str">
+        <v/>
+      </c>
+      <c r="U110" t="str">
+        <v/>
+      </c>
+      <c r="V110" t="str">
         <v/>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+        <v>וולף אליס The Clearing</v>
       </c>
       <c r="B111" t="str">
-        <v>2025-08-29</v>
+        <v>2025-09-01</v>
       </c>
       <c r="C111" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
+        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
       </c>
       <c r="D111" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E111" t="str">
-        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
+        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
       </c>
       <c r="F111" t="str">
         <v>אלבומים חדשים</v>
@@ -5538,24 +6144,30 @@
         <v/>
       </c>
       <c r="T111" t="str">
+        <v/>
+      </c>
+      <c r="U111" t="str">
+        <v/>
+      </c>
+      <c r="V111" t="str">
         <v/>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
       </c>
       <c r="B112" t="str">
-        <v>2025-08-24</v>
+        <v>2025-08-29</v>
       </c>
       <c r="C112" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
+        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
       </c>
       <c r="D112" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E112" t="str">
-        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
+        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
       </c>
       <c r="F112" t="str">
         <v>אלבומים חדשים</v>
@@ -5600,24 +6212,30 @@
         <v/>
       </c>
       <c r="T112" t="str">
+        <v/>
+      </c>
+      <c r="U112" t="str">
+        <v/>
+      </c>
+      <c r="V112" t="str">
         <v/>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
       </c>
       <c r="B113" t="str">
-        <v>2025-08-21</v>
+        <v>2025-08-24</v>
       </c>
       <c r="C113" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
+        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
       </c>
       <c r="D113" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E113" t="str">
-        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
+        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
       </c>
       <c r="F113" t="str">
         <v>אלבומים חדשים</v>
@@ -5662,24 +6280,30 @@
         <v/>
       </c>
       <c r="T113" t="str">
+        <v/>
+      </c>
+      <c r="U113" t="str">
+        <v/>
+      </c>
+      <c r="V113" t="str">
         <v/>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>אברהם טל – חי</v>
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
       </c>
       <c r="B114" t="str">
-        <v>2025-08-17</v>
+        <v>2025-08-21</v>
       </c>
       <c r="C114" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
       </c>
       <c r="D114" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E114" t="str">
-        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
+        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
       </c>
       <c r="F114" t="str">
         <v>אלבומים חדשים</v>
@@ -5724,24 +6348,30 @@
         <v/>
       </c>
       <c r="T114" t="str">
+        <v/>
+      </c>
+      <c r="U114" t="str">
+        <v/>
+      </c>
+      <c r="V114" t="str">
         <v/>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>רנה ראפ Bite Me</v>
+        <v>אברהם טל – חי</v>
       </c>
       <c r="B115" t="str">
-        <v>2025-08-12</v>
+        <v>2025-08-17</v>
       </c>
       <c r="C115" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
       </c>
       <c r="D115" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E115" t="str">
-        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
+        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
       </c>
       <c r="F115" t="str">
         <v>אלבומים חדשים</v>
@@ -5786,24 +6416,30 @@
         <v/>
       </c>
       <c r="T115" t="str">
+        <v/>
+      </c>
+      <c r="U115" t="str">
+        <v/>
+      </c>
+      <c r="V115" t="str">
         <v/>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>The K's – Pretty On The Internet</v>
+        <v>רנה ראפ Bite Me</v>
       </c>
       <c r="B116" t="str">
-        <v>2025-08-03</v>
+        <v>2025-08-12</v>
       </c>
       <c r="C116" t="str">
-        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
+        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
       </c>
       <c r="D116" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E116" t="str">
-        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
+        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
       </c>
       <c r="F116" t="str">
         <v>אלבומים חדשים</v>
@@ -5848,24 +6484,30 @@
         <v/>
       </c>
       <c r="T116" t="str">
+        <v/>
+      </c>
+      <c r="U116" t="str">
+        <v/>
+      </c>
+      <c r="V116" t="str">
         <v/>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>פליטווד מק Fifty Years – Don’t Stop</v>
+        <v>The K's – Pretty On The Internet</v>
       </c>
       <c r="B117" t="str">
-        <v>2025-07-30</v>
+        <v>2025-08-03</v>
       </c>
       <c r="C117" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%99%d7%98%d7%95%d7%95%d7%93-%d7%9e%d7%a7-fifty-years-dont-stop/</v>
+        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
       </c>
       <c r="D117" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E117" t="str">
-        <v>פליטווד מק (Fleetwood Mac) חוגגים חצי מאה של מוזיקה עם אוסף חדש בן 50 שירים, שמתפרש על כל הקריירה של הלהקה, מימיה הראשונים בסגנון בלוז, ועד להצלחתה העולמית כאחת מלהקות הגדולות בהיסטוריה של הרוק. פליטווד מק הם לא רק להקה</v>
+        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
       </c>
       <c r="F117" t="str">
         <v>אלבומים חדשים</v>
@@ -5910,74 +6552,154 @@
         <v/>
       </c>
       <c r="T117" t="str">
+        <v/>
+      </c>
+      <c r="U117" t="str">
+        <v/>
+      </c>
+      <c r="V117" t="str">
         <v/>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
+        <v>פליטווד מק Fifty Years – Don’t Stop</v>
+      </c>
+      <c r="B118" t="str">
+        <v>2025-07-30</v>
+      </c>
+      <c r="C118" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%99%d7%98%d7%95%d7%95%d7%93-%d7%9e%d7%a7-fifty-years-dont-stop/</v>
+      </c>
+      <c r="D118" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E118" t="str">
+        <v>פליטווד מק (Fleetwood Mac) חוגגים חצי מאה של מוזיקה עם אוסף חדש בן 50 שירים, שמתפרש על כל הקריירה של הלהקה, מימיה הראשונים בסגנון בלוז, ועד להצלחתה העולמית כאחת מלהקות הגדולות בהיסטוריה של הרוק. פליטווד מק הם לא רק להקה</v>
+      </c>
+      <c r="F118" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G118" t="str">
+        <v/>
+      </c>
+      <c r="H118" t="str">
+        <v/>
+      </c>
+      <c r="I118" t="str">
+        <v/>
+      </c>
+      <c r="J118" t="str">
+        <v/>
+      </c>
+      <c r="K118" t="str">
+        <v/>
+      </c>
+      <c r="L118" t="str">
+        <v/>
+      </c>
+      <c r="M118" t="str">
+        <v/>
+      </c>
+      <c r="N118" t="str">
+        <v/>
+      </c>
+      <c r="O118" t="str">
+        <v/>
+      </c>
+      <c r="P118" t="str">
+        <v/>
+      </c>
+      <c r="Q118" t="str">
+        <v/>
+      </c>
+      <c r="R118" t="str">
+        <v/>
+      </c>
+      <c r="S118" t="str">
+        <v/>
+      </c>
+      <c r="T118" t="str">
+        <v/>
+      </c>
+      <c r="U118" t="str">
+        <v/>
+      </c>
+      <c r="V118" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
         <v>Wet Leg Moisturizer</v>
       </c>
-      <c r="B118" t="str">
+      <c r="B119" t="str">
         <v>2025-07-25</v>
       </c>
-      <c r="C118" t="str">
+      <c r="C119" t="str">
         <v>https://yosmusic.com/wet-leg-moisturizer/</v>
       </c>
-      <c r="D118" t="str">
-        <v>2026-01-08</v>
-      </c>
-      <c r="E118" t="str">
+      <c r="D119" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E119" t="str">
         <v>להקת Wet Leg לא הוציאה קרם לחות (Moisturizer) כמוצר טיפוח. במקום זאת, "Moisturizer" הוא שמו של האלבום השני והחדש שלהם. במרכז –  צמד אינדי-רוק המורכב מהחברות ריין טיסדייל והסטר צ'יימברס. אלבום הבכורה הנושא את שמה, הגיע למקום הראשון במצעד האלבומים</v>
       </c>
-      <c r="F118" t="str">
-        <v>אלבומים חדשים</v>
-      </c>
-      <c r="G118" t="str">
-        <v/>
-      </c>
-      <c r="H118" t="str">
-        <v/>
-      </c>
-      <c r="I118" t="str">
-        <v/>
-      </c>
-      <c r="J118" t="str">
-        <v/>
-      </c>
-      <c r="K118" t="str">
-        <v/>
-      </c>
-      <c r="L118" t="str">
-        <v/>
-      </c>
-      <c r="M118" t="str">
-        <v/>
-      </c>
-      <c r="N118" t="str">
-        <v/>
-      </c>
-      <c r="O118" t="str">
-        <v/>
-      </c>
-      <c r="P118" t="str">
-        <v/>
-      </c>
-      <c r="Q118" t="str">
-        <v/>
-      </c>
-      <c r="R118" t="str">
-        <v/>
-      </c>
-      <c r="S118" t="str">
-        <v/>
-      </c>
-      <c r="T118" t="str">
+      <c r="F119" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G119" t="str">
+        <v/>
+      </c>
+      <c r="H119" t="str">
+        <v/>
+      </c>
+      <c r="I119" t="str">
+        <v/>
+      </c>
+      <c r="J119" t="str">
+        <v/>
+      </c>
+      <c r="K119" t="str">
+        <v/>
+      </c>
+      <c r="L119" t="str">
+        <v/>
+      </c>
+      <c r="M119" t="str">
+        <v/>
+      </c>
+      <c r="N119" t="str">
+        <v/>
+      </c>
+      <c r="O119" t="str">
+        <v/>
+      </c>
+      <c r="P119" t="str">
+        <v/>
+      </c>
+      <c r="Q119" t="str">
+        <v/>
+      </c>
+      <c r="R119" t="str">
+        <v/>
+      </c>
+      <c r="S119" t="str">
+        <v/>
+      </c>
+      <c r="T119" t="str">
+        <v/>
+      </c>
+      <c r="U119" t="str">
+        <v/>
+      </c>
+      <c r="V119" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T118"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:V119"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V119"/>
+  <dimension ref="A1:Z163"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -416,449 +416,608 @@
         <v>תיאור</v>
       </c>
       <c r="F1" t="str">
+        <v>משך</v>
+      </c>
+      <c r="G1" t="str">
+        <v>ערוץ</v>
+      </c>
+      <c r="H1" t="str">
         <v>תגית</v>
+      </c>
+      <c r="I1" t="str">
+        <v>קישור אמן</v>
+      </c>
+      <c r="J1" t="str">
+        <v>קישור אלבום</v>
+      </c>
+      <c r="K1" t="str">
+        <v>שיר - אמן</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עדן בן זקן - רולקס וקסקט</v>
+        <v>פטריק סבג Hotel Mogador</v>
       </c>
       <c r="B2" t="str">
-        <v>2026  08:41-01-14</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24436&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-15</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>האלבום של פטריק סבג אינו אוסף שירים אקראי, אלא מרחב. מקום לשהות בו.  נכנסים, שומעים, ויוצאים קצת אחרים. הבחירה בשם "הוטל מוגדור” היא כבר הצהרה. מלון = מקום מעבר, לא בית קבוע, מוגדור = עיר נמל, תנועה, ערבוב תרבויות. כך</v>
       </c>
       <c r="F2" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v>פטריק סבג Hotel Mogador</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>תומר יוסף - 360</v>
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
       </c>
       <c r="B3" t="str">
-        <v>2026  08:40-01-14</v>
+        <v>2026-01-09</v>
       </c>
       <c r="C3" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-15</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
       </c>
       <c r="F3" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
+        <v>אוליביה דין The Art of Loving</v>
       </c>
       <c r="B4" t="str">
-        <v>2026  08:40-01-14</v>
+        <v>2026-01-04</v>
       </c>
       <c r="C4" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24439&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-15</v>
       </c>
       <c r="E4" t="str">
-        <v/>
+        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
       </c>
       <c r="F4" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v>אוליביה דין The Art of Loving</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>אייל גולן - בית מפואר</v>
+        <v>Geese Getting Killed</v>
       </c>
       <c r="B5" t="str">
-        <v>2025  02:18-12-31</v>
+        <v>2025-12-29</v>
       </c>
       <c r="C5" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/geese-getting-killed/</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-15</v>
       </c>
       <c r="E5" t="str">
-        <v/>
+        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
       </c>
       <c r="F5" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v>Geese Getting Killed</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
+        <v>רוסליה Lux</v>
       </c>
       <c r="B6" t="str">
-        <v>2025  02:16-12-31</v>
+        <v>2025-12-25</v>
       </c>
       <c r="C6" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-15</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
       </c>
       <c r="F6" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v>רוסליה Lux</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>שיר לוי - ילד מוזר</v>
+        <v>יאנגבלאד אירוסמית' one more time</v>
       </c>
       <c r="B7" t="str">
-        <v>2025  02:14-12-31</v>
+        <v>2025-12-17</v>
       </c>
       <c r="C7" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-15</v>
       </c>
       <c r="E7" t="str">
-        <v/>
+        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
       </c>
       <c r="F7" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v>יאנגבלאד אירוסמית' one more time</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>פיטר רוט - 50</v>
+        <v>פינק פלויד Wish You Were Here 50</v>
       </c>
       <c r="B8" t="str">
-        <v>2025  02:13-12-31</v>
+        <v>2025-12-14</v>
       </c>
       <c r="C8" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-15</v>
       </c>
       <c r="E8" t="str">
-        <v/>
+        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
       </c>
       <c r="F8" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v>פינק פלויד Wish You Were Here 50</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>אגם בוחבוט - עשרים ואחת</v>
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
       </c>
       <c r="B9" t="str">
-        <v>2025  02:11-12-31</v>
+        <v>2025-12-08</v>
       </c>
       <c r="C9" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-15</v>
       </c>
       <c r="E9" t="str">
-        <v/>
+        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
       </c>
       <c r="F9" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>רבקה זוהר - רסיסים של אור</v>
+        <v>סטריי קידס DO IT (EP)</v>
       </c>
       <c r="B10" t="str">
-        <v>2025  02:09-12-31</v>
+        <v>2025-12-04</v>
       </c>
       <c r="C10" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-15</v>
       </c>
       <c r="E10" t="str">
-        <v/>
+        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
       </c>
       <c r="F10" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v>סטריי קידס DO IT (EP)</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
+        <v>דויד ברוזה BROZAJAZZ</v>
       </c>
       <c r="B11" t="str">
-        <v>2025  02:08-12-31</v>
+        <v>2025-11-30</v>
       </c>
       <c r="C11" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-15</v>
       </c>
       <c r="E11" t="str">
-        <v/>
+        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
       </c>
       <c r="F11" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v>דויד ברוזה BROZAJAZZ</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
+        <v>Five Seconds of Summer – Everyone's A Star</v>
       </c>
       <c r="B12" t="str">
-        <v>2025  02:05-12-31</v>
+        <v>2025-11-24</v>
       </c>
       <c r="C12" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-15</v>
       </c>
       <c r="E12" t="str">
-        <v/>
+        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
       </c>
       <c r="F12" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v>Five Seconds of Summer – Everyone's A Star</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Imagine פסטיגל - שירי התחרות</v>
+        <v>התקווה 6 – ויהי אור</v>
       </c>
       <c r="B13" t="str">
-        <v>2025  02:04-12-31</v>
+        <v>2025-11-20</v>
       </c>
       <c r="C13" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-15</v>
       </c>
       <c r="E13" t="str">
-        <v/>
+        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
       </c>
       <c r="F13" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v>התקווה 6 – ויהי אור</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>השמחות - חובות אבודים</v>
+        <v>פלורנס אנד דה משין Everybody Scream</v>
       </c>
       <c r="B14" t="str">
-        <v>2025  02:02-12-31</v>
+        <v>2025-11-13</v>
       </c>
       <c r="C14" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-15</v>
       </c>
       <c r="E14" t="str">
-        <v/>
+        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
       </c>
       <c r="F14" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v>פלורנס אנד דה משין Everybody Scream</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>שלמה גרוניך - כמו כוכבים</v>
+        <v>טיים אימפלה Deadbeat</v>
       </c>
       <c r="B15" t="str">
-        <v>2025  02:00-12-31</v>
+        <v>2025-11-03</v>
       </c>
       <c r="C15" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-15</v>
       </c>
       <c r="E15" t="str">
-        <v/>
+        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
       </c>
       <c r="F15" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v>טיים אימפלה Deadbeat</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>יוני רועה - מפוזרים</v>
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
       </c>
       <c r="B16" t="str">
-        <v>2025  01:56-12-31</v>
+        <v>2025-10-20</v>
       </c>
       <c r="C16" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-15</v>
       </c>
       <c r="E16" t="str">
-        <v/>
+        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
       </c>
       <c r="F16" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>פטריק סבג Hotel Mogador</v>
+        <v>שלמה גרוניך – תודה אהבה</v>
       </c>
       <c r="B17" t="str">
-        <v>2026-01-13</v>
+        <v>2025-10-18</v>
       </c>
       <c r="C17" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-01-13</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E17" t="str">
-        <v>האלבום של פטריק סבג אינו אוסף שירים אקראי, אלא מרחב. מקום לשהות בו.  נכנסים, שומעים, ויוצאים קצת אחרים. הבחירה בשם "הוטל מוגדור” היא כבר הצהרה. מלון = מקום מעבר, לא בית קבוע, מוגדור = עיר נמל, תנועה, ערבוב תרבויות. כך</v>
+        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
       </c>
       <c r="F17" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I17" t="str">
         <v/>
       </c>
       <c r="J17" t="str">
         <v/>
+      </c>
+      <c r="K17" t="str">
+        <v>שלמה גרוניך – תודה אהבה</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>|אלבום חדש| תומר יוסף - 360 ()</v>
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
       </c>
       <c r="B18" t="str">
-        <v>2026  11:38-01-09</v>
+        <v>2025-10-11</v>
       </c>
       <c r="C18" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E18" t="str">
-        <v/>
+        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
       </c>
       <c r="F18" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I18" t="str">
         <v/>
@@ -867,36 +1026,33 @@
         <v/>
       </c>
       <c r="K18" t="str">
-        <v/>
-      </c>
-      <c r="L18" t="str">
-        <v/>
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע ()</v>
+        <v>דוג'ה קאט Vie</v>
       </c>
       <c r="B19" t="str">
-        <v>2025  02:17-12-31</v>
+        <v>2025-10-04</v>
       </c>
       <c r="C19" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E19" t="str">
-        <v/>
+        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
       </c>
       <c r="F19" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I19" t="str">
         <v/>
@@ -905,36 +1061,33 @@
         <v/>
       </c>
       <c r="K19" t="str">
-        <v/>
-      </c>
-      <c r="L19" t="str">
-        <v/>
+        <v>דוג'ה קאט Vie</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>|אלבום חדש| אברהם טל - חי ()</v>
+        <v>ג'וי קרוקס Juniper</v>
       </c>
       <c r="B20" t="str">
-        <v>2025  02:16-12-31</v>
+        <v>2025-10-03</v>
       </c>
       <c r="C20" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E20" t="str">
-        <v/>
+        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
       </c>
       <c r="F20" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I20" t="str">
         <v/>
@@ -943,36 +1096,33 @@
         <v/>
       </c>
       <c r="K20" t="str">
-        <v/>
-      </c>
-      <c r="L20" t="str">
-        <v/>
+        <v>ג'וי קרוקס Juniper</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>|אלבום חדש| מיקי גבריאלוב - שלום ()</v>
+        <v>ביפי קליירו Futique</v>
       </c>
       <c r="B21" t="str">
-        <v>2025  02:13-12-31</v>
+        <v>2025-09-30</v>
       </c>
       <c r="C21" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E21" t="str">
-        <v/>
+        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
       </c>
       <c r="F21" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I21" t="str">
         <v/>
@@ -981,36 +1131,33 @@
         <v/>
       </c>
       <c r="K21" t="str">
-        <v/>
-      </c>
-      <c r="L21" t="str">
-        <v/>
+        <v>ביפי קליירו Futique</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם ()</v>
+        <v>אד שירן Play</v>
       </c>
       <c r="B22" t="str">
-        <v>2025  02:12-12-31</v>
+        <v>2025-09-24</v>
       </c>
       <c r="C22" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E22" t="str">
-        <v/>
+        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
       </c>
       <c r="F22" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I22" t="str">
         <v/>
@@ -1019,36 +1166,33 @@
         <v/>
       </c>
       <c r="K22" t="str">
-        <v/>
-      </c>
-      <c r="L22" t="str">
-        <v/>
+        <v>אד שירן Play</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון ()</v>
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
       </c>
       <c r="B23" t="str">
-        <v>2025  02:10-12-31</v>
+        <v>2025-09-21</v>
       </c>
       <c r="C23" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E23" t="str">
-        <v/>
+        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
       </c>
       <c r="F23" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I23" t="str">
         <v/>
@@ -1057,36 +1201,33 @@
         <v/>
       </c>
       <c r="K23" t="str">
-        <v/>
-      </c>
-      <c r="L23" t="str">
-        <v/>
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה ()</v>
+        <v>סוויד Antidepressants</v>
       </c>
       <c r="B24" t="str">
-        <v>2025  02:09-12-31</v>
+        <v>2025-09-12</v>
       </c>
       <c r="C24" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E24" t="str">
-        <v/>
+        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
       </c>
       <c r="F24" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I24" t="str">
         <v/>
@@ -1095,36 +1236,33 @@
         <v/>
       </c>
       <c r="K24" t="str">
-        <v/>
-      </c>
-      <c r="L24" t="str">
-        <v/>
+        <v>סוויד Antidepressants</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים ()</v>
+        <v>וולף אליס The Clearing</v>
       </c>
       <c r="B25" t="str">
-        <v>2025  02:06-12-31</v>
+        <v>2025-09-01</v>
       </c>
       <c r="C25" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E25" t="str">
-        <v/>
+        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
       </c>
       <c r="F25" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I25" t="str">
         <v/>
@@ -1133,36 +1271,33 @@
         <v/>
       </c>
       <c r="K25" t="str">
-        <v/>
-      </c>
-      <c r="L25" t="str">
-        <v/>
+        <v>וולף אליס The Clearing</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם ()</v>
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
       </c>
       <c r="B26" t="str">
-        <v>2025  02:05-12-31</v>
+        <v>2025-08-29</v>
       </c>
       <c r="C26" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E26" t="str">
-        <v/>
+        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
       </c>
       <c r="F26" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I26" t="str">
         <v/>
@@ -1171,36 +1306,33 @@
         <v/>
       </c>
       <c r="K26" t="str">
-        <v/>
-      </c>
-      <c r="L26" t="str">
-        <v/>
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>|אלבום חדש| סטטיק - קעקועים ()</v>
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
       </c>
       <c r="B27" t="str">
-        <v>2025  02:03-12-31</v>
+        <v>2025-08-24</v>
       </c>
       <c r="C27" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E27" t="str">
-        <v/>
+        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
       </c>
       <c r="F27" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I27" t="str">
         <v/>
@@ -1209,36 +1341,33 @@
         <v/>
       </c>
       <c r="K27" t="str">
-        <v/>
-      </c>
-      <c r="L27" t="str">
-        <v/>
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>|אלבום חדש| ליאור נרקיס - דיסוננס ()</v>
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
       </c>
       <c r="B28" t="str">
-        <v>2025  02:01-12-31</v>
+        <v>2025-08-21</v>
       </c>
       <c r="C28" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E28" t="str">
-        <v/>
+        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
       </c>
       <c r="F28" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I28" t="str">
         <v/>
@@ -1247,36 +1376,33 @@
         <v/>
       </c>
       <c r="K28" t="str">
-        <v/>
-      </c>
-      <c r="L28" t="str">
-        <v/>
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) ()</v>
+        <v>אברהם טל – חי</v>
       </c>
       <c r="B29" t="str">
-        <v>2025  01:57-12-31</v>
+        <v>2025-08-17</v>
       </c>
       <c r="C29" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E29" t="str">
-        <v/>
+        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
       </c>
       <c r="F29" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I29" t="str">
         <v/>
@@ -1285,36 +1411,33 @@
         <v/>
       </c>
       <c r="K29" t="str">
-        <v/>
-      </c>
-      <c r="L29" t="str">
-        <v/>
+        <v>אברהם טל – חי</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>|אלבום חדש| אתניקס - איטליה ()</v>
+        <v>רנה ראפ Bite Me</v>
       </c>
       <c r="B30" t="str">
-        <v>2025  01:55-12-31</v>
+        <v>2025-08-12</v>
       </c>
       <c r="C30" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E30" t="str">
-        <v/>
+        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
       </c>
       <c r="F30" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I30" t="str">
         <v/>
@@ -1323,36 +1446,33 @@
         <v/>
       </c>
       <c r="K30" t="str">
-        <v/>
-      </c>
-      <c r="L30" t="str">
-        <v/>
+        <v>רנה ראפ Bite Me</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>|| תומר יוסף - 360 (2026)</v>
+        <v>The K's – Pretty On The Internet</v>
       </c>
       <c r="B31" t="str">
-        <v>2026  11:38-01-09</v>
+        <v>2025-08-03</v>
       </c>
       <c r="C31" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E31" t="str">
-        <v/>
+        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
       </c>
       <c r="F31" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I31" t="str">
         <v/>
@@ -1361,42 +1481,33 @@
         <v/>
       </c>
       <c r="K31" t="str">
-        <v/>
-      </c>
-      <c r="L31" t="str">
-        <v/>
-      </c>
-      <c r="M31" t="str">
-        <v/>
-      </c>
-      <c r="N31" t="str">
-        <v/>
+        <v>The K's – Pretty On The Internet</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>|| עמיר בניון - לא נוגע בקרקע ()</v>
+        <v>עדן בן זקן - רולקס וקסקט</v>
       </c>
       <c r="B32" t="str">
-        <v>2025  02:17-12-31</v>
+        <v>2026  08:41-01-14</v>
       </c>
       <c r="C32" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24436&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I32" t="str">
         <v/>
@@ -1405,42 +1516,33 @@
         <v/>
       </c>
       <c r="K32" t="str">
-        <v/>
-      </c>
-      <c r="L32" t="str">
-        <v/>
-      </c>
-      <c r="M32" t="str">
-        <v/>
-      </c>
-      <c r="N32" t="str">
-        <v/>
+        <v>עדן בן זקן - רולקס וקסקט</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>|| אברהם טל - חי ()</v>
+        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
       </c>
       <c r="B33" t="str">
-        <v>2025  02:16-12-31</v>
+        <v>2026  08:40-01-14</v>
       </c>
       <c r="C33" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24439&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E33" t="str">
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I33" t="str">
         <v/>
@@ -1449,42 +1551,33 @@
         <v/>
       </c>
       <c r="K33" t="str">
-        <v/>
-      </c>
-      <c r="L33" t="str">
-        <v/>
-      </c>
-      <c r="M33" t="str">
-        <v/>
-      </c>
-      <c r="N33" t="str">
-        <v/>
+        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>|| מיקי גבריאלוב - שלום ()</v>
+        <v>אייל גולן - בית מפואר</v>
       </c>
       <c r="B34" t="str">
-        <v>2025  02:13-12-31</v>
+        <v>2025  02:18-12-31</v>
       </c>
       <c r="C34" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I34" t="str">
         <v/>
@@ -1493,42 +1586,33 @@
         <v/>
       </c>
       <c r="K34" t="str">
-        <v/>
-      </c>
-      <c r="L34" t="str">
-        <v/>
-      </c>
-      <c r="M34" t="str">
-        <v/>
-      </c>
-      <c r="N34" t="str">
-        <v/>
+        <v>אייל גולן - בית מפואר</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>|| בזכרי ימים ימימה - מחווה לצלילי הכרם ()</v>
+        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
       </c>
       <c r="B35" t="str">
-        <v>2025  02:12-12-31</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C35" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I35" t="str">
         <v/>
@@ -1537,42 +1621,33 @@
         <v/>
       </c>
       <c r="K35" t="str">
-        <v/>
-      </c>
-      <c r="L35" t="str">
-        <v/>
-      </c>
-      <c r="M35" t="str">
-        <v/>
-      </c>
-      <c r="N35" t="str">
-        <v/>
+        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>|| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון ()</v>
+        <v>שיר לוי - ילד מוזר</v>
       </c>
       <c r="B36" t="str">
-        <v>2025  02:10-12-31</v>
+        <v>2025  02:14-12-31</v>
       </c>
       <c r="C36" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I36" t="str">
         <v/>
@@ -1581,42 +1656,33 @@
         <v/>
       </c>
       <c r="K36" t="str">
-        <v/>
-      </c>
-      <c r="L36" t="str">
-        <v/>
-      </c>
-      <c r="M36" t="str">
-        <v/>
-      </c>
-      <c r="N36" t="str">
-        <v/>
+        <v>שיר לוי - ילד מוזר</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>|| שלמה גרוניך - תודה אהבה ()</v>
+        <v>פיטר רוט - 50</v>
       </c>
       <c r="B37" t="str">
-        <v>2025  02:09-12-31</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C37" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I37" t="str">
         <v/>
@@ -1625,42 +1691,33 @@
         <v/>
       </c>
       <c r="K37" t="str">
-        <v/>
-      </c>
-      <c r="L37" t="str">
-        <v/>
-      </c>
-      <c r="M37" t="str">
-        <v/>
-      </c>
-      <c r="N37" t="str">
-        <v/>
+        <v>פיטר רוט - 50</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>|| חוה אלברשטיין - חמישה שירים ()</v>
+        <v>אגם בוחבוט - עשרים ואחת</v>
       </c>
       <c r="B38" t="str">
-        <v>2025  02:06-12-31</v>
+        <v>2025  02:11-12-31</v>
       </c>
       <c r="C38" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I38" t="str">
         <v/>
@@ -1669,42 +1726,33 @@
         <v/>
       </c>
       <c r="K38" t="str">
-        <v/>
-      </c>
-      <c r="L38" t="str">
-        <v/>
-      </c>
-      <c r="M38" t="str">
-        <v/>
-      </c>
-      <c r="N38" t="str">
-        <v/>
+        <v>אגם בוחבוט - עשרים ואחת</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>|| הפרויקט של עידן רייכל - עד סוף העולם ()</v>
+        <v>רבקה זוהר - רסיסים של אור</v>
       </c>
       <c r="B39" t="str">
-        <v>2025  02:05-12-31</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C39" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I39" t="str">
         <v/>
@@ -1713,42 +1761,33 @@
         <v/>
       </c>
       <c r="K39" t="str">
-        <v/>
-      </c>
-      <c r="L39" t="str">
-        <v/>
-      </c>
-      <c r="M39" t="str">
-        <v/>
-      </c>
-      <c r="N39" t="str">
-        <v/>
+        <v>רבקה זוהר - רסיסים של אור</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>|| סטטיק - קעקועים ()</v>
+        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
       </c>
       <c r="B40" t="str">
-        <v>2025  02:03-12-31</v>
+        <v>2025  02:08-12-31</v>
       </c>
       <c r="C40" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I40" t="str">
         <v/>
@@ -1757,42 +1796,33 @@
         <v/>
       </c>
       <c r="K40" t="str">
-        <v/>
-      </c>
-      <c r="L40" t="str">
-        <v/>
-      </c>
-      <c r="M40" t="str">
-        <v/>
-      </c>
-      <c r="N40" t="str">
-        <v/>
+        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>|| ליאור נרקיס - דיסוננס ()</v>
+        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
       </c>
       <c r="B41" t="str">
-        <v>2025  02:01-12-31</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C41" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I41" t="str">
         <v/>
@@ -1801,42 +1831,33 @@
         <v/>
       </c>
       <c r="K41" t="str">
-        <v/>
-      </c>
-      <c r="L41" t="str">
-        <v/>
-      </c>
-      <c r="M41" t="str">
-        <v/>
-      </c>
-      <c r="N41" t="str">
-        <v/>
+        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>|| דיוויד ברוזה - BrozaJazz (Paris Alhambra) ()</v>
+        <v>Imagine פסטיגל - שירי התחרות</v>
       </c>
       <c r="B42" t="str">
-        <v>2025  01:57-12-31</v>
+        <v>2025  02:04-12-31</v>
       </c>
       <c r="C42" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I42" t="str">
         <v/>
@@ -1845,42 +1866,33 @@
         <v/>
       </c>
       <c r="K42" t="str">
-        <v/>
-      </c>
-      <c r="L42" t="str">
-        <v/>
-      </c>
-      <c r="M42" t="str">
-        <v/>
-      </c>
-      <c r="N42" t="str">
-        <v/>
+        <v>Imagine פסטיגל - שירי התחרות</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>|| אתניקס - איטליה ()</v>
+        <v>השמחות - חובות אבודים</v>
       </c>
       <c r="B43" t="str">
-        <v>2025  01:55-12-31</v>
+        <v>2025  02:02-12-31</v>
       </c>
       <c r="C43" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I43" t="str">
         <v/>
@@ -1889,42 +1901,33 @@
         <v/>
       </c>
       <c r="K43" t="str">
-        <v/>
-      </c>
-      <c r="L43" t="str">
-        <v/>
-      </c>
-      <c r="M43" t="str">
-        <v/>
-      </c>
-      <c r="N43" t="str">
-        <v/>
+        <v>השמחות - חובות אבודים</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>מארינה מקסימיליאן – ריק בחלל</v>
+        <v>שלמה גרוניך - כמו כוכבים</v>
       </c>
       <c r="B44" t="str">
-        <v>2026-01-09</v>
+        <v>2025  02:00-12-31</v>
       </c>
       <c r="C44" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E44" t="str">
-        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
+        <v/>
       </c>
       <c r="F44" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I44" t="str">
         <v/>
@@ -1933,48 +1936,33 @@
         <v/>
       </c>
       <c r="K44" t="str">
-        <v/>
-      </c>
-      <c r="L44" t="str">
-        <v/>
-      </c>
-      <c r="M44" t="str">
-        <v/>
-      </c>
-      <c r="N44" t="str">
-        <v/>
-      </c>
-      <c r="O44" t="str">
-        <v/>
-      </c>
-      <c r="P44" t="str">
-        <v/>
+        <v>שלמה גרוניך - כמו כוכבים</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>|| אייל גולן - בית מפואר ()</v>
+        <v>יוני רועה - מפוזרים</v>
       </c>
       <c r="B45" t="str">
-        <v>2025  02:18-12-31</v>
+        <v>2025  01:56-12-31</v>
       </c>
       <c r="C45" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I45" t="str">
         <v/>
@@ -1983,42 +1971,21 @@
         <v/>
       </c>
       <c r="K45" t="str">
-        <v/>
-      </c>
-      <c r="L45" t="str">
-        <v/>
-      </c>
-      <c r="M45" t="str">
-        <v/>
-      </c>
-      <c r="N45" t="str">
-        <v/>
-      </c>
-      <c r="O45" t="str">
-        <v/>
-      </c>
-      <c r="P45" t="str">
-        <v/>
-      </c>
-      <c r="Q45" t="str">
-        <v/>
-      </c>
-      <c r="R45" t="str">
-        <v/>
+        <v>יוני רועה - מפוזרים</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>|| הפרויקט של דודי לוי ואבטיפוס - הפטריקים ()</v>
+        <v>עדן בן זקן - רולקס וקסקט</v>
       </c>
       <c r="B46" t="str">
-        <v>2025  02:16-12-31</v>
+        <v>2026  08:41-01-14</v>
       </c>
       <c r="C46" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24436&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2036,45 +2003,21 @@
         <v/>
       </c>
       <c r="J46" t="str">
-        <v/>
-      </c>
-      <c r="K46" t="str">
-        <v/>
-      </c>
-      <c r="L46" t="str">
-        <v/>
-      </c>
-      <c r="M46" t="str">
-        <v/>
-      </c>
-      <c r="N46" t="str">
-        <v/>
-      </c>
-      <c r="O46" t="str">
-        <v/>
-      </c>
-      <c r="P46" t="str">
-        <v/>
-      </c>
-      <c r="Q46" t="str">
-        <v/>
-      </c>
-      <c r="R46" t="str">
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>|| שיר לוי - ילד מוזר ()</v>
+        <v>תומר יוסף - 360</v>
       </c>
       <c r="B47" t="str">
-        <v>2025  02:14-12-31</v>
+        <v>2026  08:40-01-14</v>
       </c>
       <c r="C47" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2098,39 +2041,21 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v/>
-      </c>
-      <c r="M47" t="str">
-        <v/>
-      </c>
-      <c r="N47" t="str">
-        <v/>
-      </c>
-      <c r="O47" t="str">
-        <v/>
-      </c>
-      <c r="P47" t="str">
-        <v/>
-      </c>
-      <c r="Q47" t="str">
-        <v/>
-      </c>
-      <c r="R47" t="str">
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>|| פיטר רוט - 50 ()</v>
+        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
       </c>
       <c r="B48" t="str">
-        <v>2025  02:13-12-31</v>
+        <v>2026  08:40-01-14</v>
       </c>
       <c r="C48" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24439&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2154,39 +2079,21 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v/>
-      </c>
-      <c r="M48" t="str">
-        <v/>
-      </c>
-      <c r="N48" t="str">
-        <v/>
-      </c>
-      <c r="O48" t="str">
-        <v/>
-      </c>
-      <c r="P48" t="str">
-        <v/>
-      </c>
-      <c r="Q48" t="str">
-        <v/>
-      </c>
-      <c r="R48" t="str">
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>|| אגם בוחבוט - עשרים ואחת ()</v>
+        <v>אייל גולן - בית מפואר</v>
       </c>
       <c r="B49" t="str">
-        <v>2025  02:11-12-31</v>
+        <v>2025  02:18-12-31</v>
       </c>
       <c r="C49" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2210,39 +2117,21 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v/>
-      </c>
-      <c r="M49" t="str">
-        <v/>
-      </c>
-      <c r="N49" t="str">
-        <v/>
-      </c>
-      <c r="O49" t="str">
-        <v/>
-      </c>
-      <c r="P49" t="str">
-        <v/>
-      </c>
-      <c r="Q49" t="str">
-        <v/>
-      </c>
-      <c r="R49" t="str">
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>|| רבקה זוהר - רסיסים של אור ()</v>
+        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
       </c>
       <c r="B50" t="str">
-        <v>2025  02:09-12-31</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C50" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2266,39 +2155,21 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v/>
-      </c>
-      <c r="M50" t="str">
-        <v/>
-      </c>
-      <c r="N50" t="str">
-        <v/>
-      </c>
-      <c r="O50" t="str">
-        <v/>
-      </c>
-      <c r="P50" t="str">
-        <v/>
-      </c>
-      <c r="Q50" t="str">
-        <v/>
-      </c>
-      <c r="R50" t="str">
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>|| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות ()</v>
+        <v>שיר לוי - ילד מוזר</v>
       </c>
       <c r="B51" t="str">
-        <v>2025  02:08-12-31</v>
+        <v>2025  02:14-12-31</v>
       </c>
       <c r="C51" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2322,39 +2193,21 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v/>
-      </c>
-      <c r="M51" t="str">
-        <v/>
-      </c>
-      <c r="N51" t="str">
-        <v/>
-      </c>
-      <c r="O51" t="str">
-        <v/>
-      </c>
-      <c r="P51" t="str">
-        <v/>
-      </c>
-      <c r="Q51" t="str">
-        <v/>
-      </c>
-      <c r="R51" t="str">
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>|| אהוד בנאי ובנו הנדלר - פליטי הדאב ()</v>
+        <v>פיטר רוט - 50</v>
       </c>
       <c r="B52" t="str">
-        <v>2025  02:05-12-31</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C52" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2378,39 +2231,21 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v/>
-      </c>
-      <c r="M52" t="str">
-        <v/>
-      </c>
-      <c r="N52" t="str">
-        <v/>
-      </c>
-      <c r="O52" t="str">
-        <v/>
-      </c>
-      <c r="P52" t="str">
-        <v/>
-      </c>
-      <c r="Q52" t="str">
-        <v/>
-      </c>
-      <c r="R52" t="str">
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>|| Imagine פסטיגל - שירי התחרות ()</v>
+        <v>אגם בוחבוט - עשרים ואחת</v>
       </c>
       <c r="B53" t="str">
-        <v>2025  02:04-12-31</v>
+        <v>2025  02:11-12-31</v>
       </c>
       <c r="C53" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2434,39 +2269,21 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v/>
-      </c>
-      <c r="M53" t="str">
-        <v/>
-      </c>
-      <c r="N53" t="str">
-        <v/>
-      </c>
-      <c r="O53" t="str">
-        <v/>
-      </c>
-      <c r="P53" t="str">
-        <v/>
-      </c>
-      <c r="Q53" t="str">
-        <v/>
-      </c>
-      <c r="R53" t="str">
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>|| השמחות - חובות אבודים ()</v>
+        <v>רבקה זוהר - רסיסים של אור</v>
       </c>
       <c r="B54" t="str">
-        <v>2025  02:02-12-31</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C54" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2490,39 +2307,21 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v/>
-      </c>
-      <c r="M54" t="str">
-        <v/>
-      </c>
-      <c r="N54" t="str">
-        <v/>
-      </c>
-      <c r="O54" t="str">
-        <v/>
-      </c>
-      <c r="P54" t="str">
-        <v/>
-      </c>
-      <c r="Q54" t="str">
-        <v/>
-      </c>
-      <c r="R54" t="str">
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>|| שלמה גרוניך - כמו כוכבים ()</v>
+        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
       </c>
       <c r="B55" t="str">
-        <v>2025  02:00-12-31</v>
+        <v>2025  02:08-12-31</v>
       </c>
       <c r="C55" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2546,39 +2345,21 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v/>
-      </c>
-      <c r="M55" t="str">
-        <v/>
-      </c>
-      <c r="N55" t="str">
-        <v/>
-      </c>
-      <c r="O55" t="str">
-        <v/>
-      </c>
-      <c r="P55" t="str">
-        <v/>
-      </c>
-      <c r="Q55" t="str">
-        <v/>
-      </c>
-      <c r="R55" t="str">
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>|| יוני רועה - מפוזרים ()</v>
+        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
       </c>
       <c r="B56" t="str">
-        <v>2025  01:56-12-31</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C56" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2602,39 +2383,21 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v/>
-      </c>
-      <c r="M56" t="str">
-        <v/>
-      </c>
-      <c r="N56" t="str">
-        <v/>
-      </c>
-      <c r="O56" t="str">
-        <v/>
-      </c>
-      <c r="P56" t="str">
-        <v/>
-      </c>
-      <c r="Q56" t="str">
-        <v/>
-      </c>
-      <c r="R56" t="str">
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>|| התקווה 6 - ויהי אור ()</v>
+        <v>Imagine פסטיגל - שירי התחרות</v>
       </c>
       <c r="B57" t="str">
-        <v>2025  01:54-12-31</v>
+        <v>2025  02:04-12-31</v>
       </c>
       <c r="C57" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2658,39 +2421,21 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v/>
-      </c>
-      <c r="M57" t="str">
-        <v/>
-      </c>
-      <c r="N57" t="str">
-        <v/>
-      </c>
-      <c r="O57" t="str">
-        <v/>
-      </c>
-      <c r="P57" t="str">
-        <v/>
-      </c>
-      <c r="Q57" t="str">
-        <v/>
-      </c>
-      <c r="R57" t="str">
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>|| שאנן סטריט ודי ג׳יי מש - באתי לבדר ()</v>
+        <v>השמחות - חובות אבודים</v>
       </c>
       <c r="B58" t="str">
-        <v>2025  01:53-12-31</v>
+        <v>2025  02:02-12-31</v>
       </c>
       <c r="C58" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2714,39 +2459,21 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v/>
-      </c>
-      <c r="M58" t="str">
-        <v/>
-      </c>
-      <c r="N58" t="str">
-        <v/>
-      </c>
-      <c r="O58" t="str">
-        <v/>
-      </c>
-      <c r="P58" t="str">
-        <v/>
-      </c>
-      <c r="Q58" t="str">
-        <v/>
-      </c>
-      <c r="R58" t="str">
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>אשכול נוכחות למשתמשים פעילים</v>
+        <v>שלמה גרוניך - כמו כוכבים</v>
       </c>
       <c r="B59" t="str">
-        <v>2025  16:32 מאת freund-10-16</v>
+        <v>2025  02:00-12-31</v>
       </c>
       <c r="C59" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=23455&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2770,45 +2497,21 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v/>
-      </c>
-      <c r="M59" t="str">
-        <v/>
-      </c>
-      <c r="N59" t="str">
-        <v/>
-      </c>
-      <c r="O59" t="str">
-        <v/>
-      </c>
-      <c r="P59" t="str">
-        <v/>
-      </c>
-      <c r="Q59" t="str">
-        <v/>
-      </c>
-      <c r="R59" t="str">
-        <v/>
-      </c>
-      <c r="S59" t="str">
-        <v/>
-      </c>
-      <c r="T59" t="str">
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>כיצד להוריד מהאתרים המפורסמים</v>
+        <v>יוני רועה - מפוזרים</v>
       </c>
       <c r="B60" t="str">
-        <v>2023  16:23 מאת petel1-08-08</v>
+        <v>2025  01:56-12-31</v>
       </c>
       <c r="C60" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=22411&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2832,48 +2535,24 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v/>
-      </c>
-      <c r="M60" t="str">
-        <v/>
-      </c>
-      <c r="N60" t="str">
-        <v/>
-      </c>
-      <c r="O60" t="str">
-        <v/>
-      </c>
-      <c r="P60" t="str">
-        <v/>
-      </c>
-      <c r="Q60" t="str">
-        <v/>
-      </c>
-      <c r="R60" t="str">
-        <v/>
-      </c>
-      <c r="S60" t="str">
-        <v/>
-      </c>
-      <c r="T60" t="str">
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
+        <v>פטריק סבג Hotel Mogador</v>
       </c>
       <c r="B61" t="str">
-        <v>2026  22:40 מאת מוטי_ד-01-01</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C61" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24435&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-13</v>
       </c>
       <c r="E61" t="str">
-        <v/>
+        <v>האלבום של פטריק סבג אינו אוסף שירים אקראי, אלא מרחב. מקום לשהות בו.  נכנסים, שומעים, ויוצאים קצת אחרים. הבחירה בשם "הוטל מוגדור” היא כבר הצהרה. מלון = מקום מעבר, לא בית קבוע, מוגדור = עיר נמל, תנועה, ערבוב תרבויות. כך</v>
       </c>
       <c r="F61" t="str">
         <v>אלבומים חדשים</v>
@@ -2900,39 +2579,21 @@
         <v/>
       </c>
       <c r="N61" t="str">
-        <v/>
-      </c>
-      <c r="O61" t="str">
-        <v/>
-      </c>
-      <c r="P61" t="str">
-        <v/>
-      </c>
-      <c r="Q61" t="str">
-        <v/>
-      </c>
-      <c r="R61" t="str">
-        <v/>
-      </c>
-      <c r="S61" t="str">
-        <v/>
-      </c>
-      <c r="T61" t="str">
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>|אלבום חדש| אייל גולן - בית מפואר (2025)</v>
+        <v>|אלבום חדש| תומר יוסף - 360 ()</v>
       </c>
       <c r="B62" t="str">
-        <v>2025  02:18 מאת DiSHi-12-31</v>
+        <v>2026  11:38-01-09</v>
       </c>
       <c r="C62" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2968,33 +2629,21 @@
         <v/>
       </c>
       <c r="P62" t="str">
-        <v/>
-      </c>
-      <c r="Q62" t="str">
-        <v/>
-      </c>
-      <c r="R62" t="str">
-        <v/>
-      </c>
-      <c r="S62" t="str">
-        <v/>
-      </c>
-      <c r="T62" t="str">
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע (2025)</v>
+        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע ()</v>
       </c>
       <c r="B63" t="str">
-        <v>2025  02:17 מאת DiSHi-12-31</v>
+        <v>2025  02:17-12-31</v>
       </c>
       <c r="C63" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -3030,33 +2679,21 @@
         <v/>
       </c>
       <c r="P63" t="str">
-        <v/>
-      </c>
-      <c r="Q63" t="str">
-        <v/>
-      </c>
-      <c r="R63" t="str">
-        <v/>
-      </c>
-      <c r="S63" t="str">
-        <v/>
-      </c>
-      <c r="T63" t="str">
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>|אלבום חדש| הפרויקט של דודי לוי ואבטיפוס - הפטריקים (2025)</v>
+        <v>|אלבום חדש| אברהם טל - חי ()</v>
       </c>
       <c r="B64" t="str">
-        <v>2025  02:16 מאת DiSHi-12-31</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C64" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -3092,33 +2729,21 @@
         <v/>
       </c>
       <c r="P64" t="str">
-        <v/>
-      </c>
-      <c r="Q64" t="str">
-        <v/>
-      </c>
-      <c r="R64" t="str">
-        <v/>
-      </c>
-      <c r="S64" t="str">
-        <v/>
-      </c>
-      <c r="T64" t="str">
         <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>|אלבום חדש| אברהם טל - חי (2025)</v>
+        <v>|אלבום חדש| מיקי גבריאלוב - שלום ()</v>
       </c>
       <c r="B65" t="str">
-        <v>2025  02:16 מאת DiSHi-12-31</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C65" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -3154,33 +2779,21 @@
         <v/>
       </c>
       <c r="P65" t="str">
-        <v/>
-      </c>
-      <c r="Q65" t="str">
-        <v/>
-      </c>
-      <c r="R65" t="str">
-        <v/>
-      </c>
-      <c r="S65" t="str">
-        <v/>
-      </c>
-      <c r="T65" t="str">
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>|אלבום חדש| שיר לוי - ילד מוזר (2025)</v>
+        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם ()</v>
       </c>
       <c r="B66" t="str">
-        <v>2025  02:14 מאת DiSHi-12-31</v>
+        <v>2025  02:12-12-31</v>
       </c>
       <c r="C66" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -3216,33 +2829,21 @@
         <v/>
       </c>
       <c r="P66" t="str">
-        <v/>
-      </c>
-      <c r="Q66" t="str">
-        <v/>
-      </c>
-      <c r="R66" t="str">
-        <v/>
-      </c>
-      <c r="S66" t="str">
-        <v/>
-      </c>
-      <c r="T66" t="str">
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>|אלבום חדש| מיקי גבריאלוב - שלום (2025)</v>
+        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון ()</v>
       </c>
       <c r="B67" t="str">
-        <v>2025  02:13 מאת DiSHi-12-31</v>
+        <v>2025  02:10-12-31</v>
       </c>
       <c r="C67" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -3278,33 +2879,21 @@
         <v/>
       </c>
       <c r="P67" t="str">
-        <v/>
-      </c>
-      <c r="Q67" t="str">
-        <v/>
-      </c>
-      <c r="R67" t="str">
-        <v/>
-      </c>
-      <c r="S67" t="str">
-        <v/>
-      </c>
-      <c r="T67" t="str">
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>|אלבום חדש| פיטר רוט - 50 (2025)</v>
+        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה ()</v>
       </c>
       <c r="B68" t="str">
-        <v>2025  02:13 מאת DiSHi-12-31</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C68" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -3340,33 +2929,21 @@
         <v/>
       </c>
       <c r="P68" t="str">
-        <v/>
-      </c>
-      <c r="Q68" t="str">
-        <v/>
-      </c>
-      <c r="R68" t="str">
-        <v/>
-      </c>
-      <c r="S68" t="str">
-        <v/>
-      </c>
-      <c r="T68" t="str">
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם (2025)</v>
+        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים ()</v>
       </c>
       <c r="B69" t="str">
-        <v>2025  02:12 מאת DiSHi-12-31</v>
+        <v>2025  02:06-12-31</v>
       </c>
       <c r="C69" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3402,33 +2979,21 @@
         <v/>
       </c>
       <c r="P69" t="str">
-        <v/>
-      </c>
-      <c r="Q69" t="str">
-        <v/>
-      </c>
-      <c r="R69" t="str">
-        <v/>
-      </c>
-      <c r="S69" t="str">
-        <v/>
-      </c>
-      <c r="T69" t="str">
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>|אלבום חדש| אגם בוחבוט - עשרים ואחת (2025)</v>
+        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם ()</v>
       </c>
       <c r="B70" t="str">
-        <v>2025  02:11 מאת DiSHi-12-31</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C70" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3464,33 +3029,21 @@
         <v/>
       </c>
       <c r="P70" t="str">
-        <v/>
-      </c>
-      <c r="Q70" t="str">
-        <v/>
-      </c>
-      <c r="R70" t="str">
-        <v/>
-      </c>
-      <c r="S70" t="str">
-        <v/>
-      </c>
-      <c r="T70" t="str">
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון (2025)</v>
+        <v>|אלבום חדש| סטטיק - קעקועים ()</v>
       </c>
       <c r="B71" t="str">
-        <v>2025  02:10 מאת DiSHi-12-31</v>
+        <v>2025  02:03-12-31</v>
       </c>
       <c r="C71" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3526,33 +3079,21 @@
         <v/>
       </c>
       <c r="P71" t="str">
-        <v/>
-      </c>
-      <c r="Q71" t="str">
-        <v/>
-      </c>
-      <c r="R71" t="str">
-        <v/>
-      </c>
-      <c r="S71" t="str">
-        <v/>
-      </c>
-      <c r="T71" t="str">
         <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>|אלבום חדש| רבקה זוהר - רסיסים של אור (2025)</v>
+        <v>|אלבום חדש| ליאור נרקיס - דיסוננס ()</v>
       </c>
       <c r="B72" t="str">
-        <v>2025  02:09 מאת DiSHi-12-31</v>
+        <v>2025  02:01-12-31</v>
       </c>
       <c r="C72" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3588,33 +3129,21 @@
         <v/>
       </c>
       <c r="P72" t="str">
-        <v/>
-      </c>
-      <c r="Q72" t="str">
-        <v/>
-      </c>
-      <c r="R72" t="str">
-        <v/>
-      </c>
-      <c r="S72" t="str">
-        <v/>
-      </c>
-      <c r="T72" t="str">
         <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה (2025)</v>
+        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) ()</v>
       </c>
       <c r="B73" t="str">
-        <v>2025  02:09 מאת DiSHi-12-31</v>
+        <v>2025  01:57-12-31</v>
       </c>
       <c r="C73" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3650,33 +3179,21 @@
         <v/>
       </c>
       <c r="P73" t="str">
-        <v/>
-      </c>
-      <c r="Q73" t="str">
-        <v/>
-      </c>
-      <c r="R73" t="str">
-        <v/>
-      </c>
-      <c r="S73" t="str">
-        <v/>
-      </c>
-      <c r="T73" t="str">
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>|אלבום חדש| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות (2025)</v>
+        <v>|אלבום חדש| אתניקס - איטליה ()</v>
       </c>
       <c r="B74" t="str">
-        <v>2025  02:08 מאת DiSHi-12-31</v>
+        <v>2025  01:55-12-31</v>
       </c>
       <c r="C74" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3712,33 +3229,21 @@
         <v/>
       </c>
       <c r="P74" t="str">
-        <v/>
-      </c>
-      <c r="Q74" t="str">
-        <v/>
-      </c>
-      <c r="R74" t="str">
-        <v/>
-      </c>
-      <c r="S74" t="str">
-        <v/>
-      </c>
-      <c r="T74" t="str">
         <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים (2025)</v>
+        <v>|| תומר יוסף - 360 (2026)</v>
       </c>
       <c r="B75" t="str">
-        <v>2025  02:06 מאת DiSHi-12-31</v>
+        <v>2026  11:38-01-09</v>
       </c>
       <c r="C75" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3780,27 +3285,21 @@
         <v/>
       </c>
       <c r="R75" t="str">
-        <v/>
-      </c>
-      <c r="S75" t="str">
-        <v/>
-      </c>
-      <c r="T75" t="str">
         <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>|אלבום חדש| אהוד בנאי ובנו הנדלר - פליטי הדאב (2025)</v>
+        <v>|| עמיר בניון - לא נוגע בקרקע ()</v>
       </c>
       <c r="B76" t="str">
-        <v>2025  02:05 מאת DiSHi-12-31</v>
+        <v>2025  02:17-12-31</v>
       </c>
       <c r="C76" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3842,27 +3341,21 @@
         <v/>
       </c>
       <c r="R76" t="str">
-        <v/>
-      </c>
-      <c r="S76" t="str">
-        <v/>
-      </c>
-      <c r="T76" t="str">
         <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם (2025)</v>
+        <v>|| אברהם טל - חי ()</v>
       </c>
       <c r="B77" t="str">
-        <v>2025  02:05 מאת DiSHi-12-31</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C77" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3904,27 +3397,21 @@
         <v/>
       </c>
       <c r="R77" t="str">
-        <v/>
-      </c>
-      <c r="S77" t="str">
-        <v/>
-      </c>
-      <c r="T77" t="str">
         <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>|אלבום חדש| Imagine פסטיגל - שירי התחרות (2025)</v>
+        <v>|| מיקי גבריאלוב - שלום ()</v>
       </c>
       <c r="B78" t="str">
-        <v>2025  02:04 מאת DiSHi-12-31</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C78" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3966,27 +3453,21 @@
         <v/>
       </c>
       <c r="R78" t="str">
-        <v/>
-      </c>
-      <c r="S78" t="str">
-        <v/>
-      </c>
-      <c r="T78" t="str">
         <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>|אלבום חדש| סטטיק - קעקועים (2025)</v>
+        <v>|| בזכרי ימים ימימה - מחווה לצלילי הכרם ()</v>
       </c>
       <c r="B79" t="str">
-        <v>2025  02:03 מאת DiSHi-12-31</v>
+        <v>2025  02:12-12-31</v>
       </c>
       <c r="C79" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -4028,27 +3509,21 @@
         <v/>
       </c>
       <c r="R79" t="str">
-        <v/>
-      </c>
-      <c r="S79" t="str">
-        <v/>
-      </c>
-      <c r="T79" t="str">
         <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>|אלבום חדש| השמחות - חובות אבודים (2025)</v>
+        <v>|| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון ()</v>
       </c>
       <c r="B80" t="str">
-        <v>2025  02:02 מאת DiSHi-12-31</v>
+        <v>2025  02:10-12-31</v>
       </c>
       <c r="C80" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -4090,27 +3565,21 @@
         <v/>
       </c>
       <c r="R80" t="str">
-        <v/>
-      </c>
-      <c r="S80" t="str">
-        <v/>
-      </c>
-      <c r="T80" t="str">
         <v/>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>|אלבום חדש| ליאור נרקיס - דיסוננס (2025)</v>
+        <v>|| שלמה גרוניך - תודה אהבה ()</v>
       </c>
       <c r="B81" t="str">
-        <v>2025  02:01 מאת DiSHi-12-31</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C81" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -4152,27 +3621,21 @@
         <v/>
       </c>
       <c r="R81" t="str">
-        <v/>
-      </c>
-      <c r="S81" t="str">
-        <v/>
-      </c>
-      <c r="T81" t="str">
         <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>|אלבום חדש| שלמה גרוניך - כמו כוכבים (2025)</v>
+        <v>|| חוה אלברשטיין - חמישה שירים ()</v>
       </c>
       <c r="B82" t="str">
-        <v>2025  02:00 מאת DiSHi-12-31</v>
+        <v>2025  02:06-12-31</v>
       </c>
       <c r="C82" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -4214,27 +3677,21 @@
         <v/>
       </c>
       <c r="R82" t="str">
-        <v/>
-      </c>
-      <c r="S82" t="str">
-        <v/>
-      </c>
-      <c r="T82" t="str">
         <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) (2025)</v>
+        <v>|| הפרויקט של עידן רייכל - עד סוף העולם ()</v>
       </c>
       <c r="B83" t="str">
-        <v>2025  01:57 מאת DiSHi-12-31</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C83" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -4276,27 +3733,21 @@
         <v/>
       </c>
       <c r="R83" t="str">
-        <v/>
-      </c>
-      <c r="S83" t="str">
-        <v/>
-      </c>
-      <c r="T83" t="str">
         <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>|אלבום חדש| יוני רועה - מפוזרים (2025)</v>
+        <v>|| סטטיק - קעקועים ()</v>
       </c>
       <c r="B84" t="str">
-        <v>2025  01:56 מאת DiSHi-12-31</v>
+        <v>2025  02:03-12-31</v>
       </c>
       <c r="C84" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -4338,27 +3789,21 @@
         <v/>
       </c>
       <c r="R84" t="str">
-        <v/>
-      </c>
-      <c r="S84" t="str">
-        <v/>
-      </c>
-      <c r="T84" t="str">
         <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>|אלבום חדש| אתניקס - איטליה (2025)</v>
+        <v>|| ליאור נרקיס - דיסוננס ()</v>
       </c>
       <c r="B85" t="str">
-        <v>2025  01:55 מאת DiSHi-12-31</v>
+        <v>2025  02:01-12-31</v>
       </c>
       <c r="C85" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -4400,27 +3845,21 @@
         <v/>
       </c>
       <c r="R85" t="str">
-        <v/>
-      </c>
-      <c r="S85" t="str">
-        <v/>
-      </c>
-      <c r="T85" t="str">
         <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>|אלבום חדש| התקווה 6 - ויהי אור (2025)</v>
+        <v>|| דיוויד ברוזה - BrozaJazz (Paris Alhambra) ()</v>
       </c>
       <c r="B86" t="str">
-        <v>2025  01:54 מאת DiSHi-12-31</v>
+        <v>2025  01:57-12-31</v>
       </c>
       <c r="C86" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -4462,27 +3901,21 @@
         <v/>
       </c>
       <c r="R86" t="str">
-        <v/>
-      </c>
-      <c r="S86" t="str">
-        <v/>
-      </c>
-      <c r="T86" t="str">
         <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>|אלבום חדש| שלומי סרנגה - איפרכו (2025)</v>
+        <v>|| אתניקס - איטליה ()</v>
       </c>
       <c r="B87" t="str">
-        <v>2025  01:53 מאת DiSHi-12-31</v>
+        <v>2025  01:55-12-31</v>
       </c>
       <c r="C87" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24430&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -4524,30 +3957,24 @@
         <v/>
       </c>
       <c r="R87" t="str">
-        <v/>
-      </c>
-      <c r="S87" t="str">
-        <v/>
-      </c>
-      <c r="T87" t="str">
         <v/>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>|אלבום חדש| שאנן סטריט ודי ג׳יי מש - באתי לבדר (2025)</v>
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
       </c>
       <c r="B88" t="str">
-        <v>2025  01:53 מאת DiSHi-12-31</v>
+        <v>2026-01-09</v>
       </c>
       <c r="C88" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E88" t="str">
-        <v/>
+        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
       </c>
       <c r="F88" t="str">
         <v>אלבומים חדשים</v>
@@ -4597,13 +4024,13 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>הרשם לחברות מלאה</v>
+        <v>|| אייל גולן - בית מפואר ()</v>
       </c>
       <c r="B89" t="str">
-        <v/>
+        <v>2025  02:18-12-31</v>
       </c>
       <c r="C89" t="str">
-        <v>https://rotter.name/nor/members-new.html</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-08</v>
@@ -4656,22 +4083,28 @@
       <c r="T89" t="str">
         <v/>
       </c>
+      <c r="U89" t="str">
+        <v/>
+      </c>
+      <c r="V89" t="str">
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>אוליביה דין The Art of Loving</v>
+        <v>|| הפרויקט של דודי לוי ואבטיפוס - הפטריקים ()</v>
       </c>
       <c r="B90" t="str">
-        <v>2026-01-04</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C90" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D90" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E90" t="str">
-        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
+        <v/>
       </c>
       <c r="F90" t="str">
         <v>אלבומים חדשים</v>
@@ -4727,19 +4160,19 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Geese Getting Killed</v>
+        <v>|| שיר לוי - ילד מוזר ()</v>
       </c>
       <c r="B91" t="str">
-        <v>2025-12-29</v>
+        <v>2025  02:14-12-31</v>
       </c>
       <c r="C91" t="str">
-        <v>https://yosmusic.com/geese-getting-killed/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D91" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E91" t="str">
-        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
+        <v/>
       </c>
       <c r="F91" t="str">
         <v>אלבומים חדשים</v>
@@ -4795,19 +4228,19 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>רוסליה Lux</v>
+        <v>|| פיטר רוט - 50 ()</v>
       </c>
       <c r="B92" t="str">
-        <v>2025-12-25</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C92" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D92" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E92" t="str">
-        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
+        <v/>
       </c>
       <c r="F92" t="str">
         <v>אלבומים חדשים</v>
@@ -4863,19 +4296,19 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>יאנגבלאד אירוסמית' one more time</v>
+        <v>|| אגם בוחבוט - עשרים ואחת ()</v>
       </c>
       <c r="B93" t="str">
-        <v>2025-12-17</v>
+        <v>2025  02:11-12-31</v>
       </c>
       <c r="C93" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D93" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E93" t="str">
-        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
+        <v/>
       </c>
       <c r="F93" t="str">
         <v>אלבומים חדשים</v>
@@ -4931,19 +4364,19 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>פינק פלויד Wish You Were Here 50</v>
+        <v>|| רבקה זוהר - רסיסים של אור ()</v>
       </c>
       <c r="B94" t="str">
-        <v>2025-12-14</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C94" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D94" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E94" t="str">
-        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
+        <v/>
       </c>
       <c r="F94" t="str">
         <v>אלבומים חדשים</v>
@@ -4999,19 +4432,19 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+        <v>|| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות ()</v>
       </c>
       <c r="B95" t="str">
-        <v>2025-12-08</v>
+        <v>2025  02:08-12-31</v>
       </c>
       <c r="C95" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D95" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E95" t="str">
-        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
+        <v/>
       </c>
       <c r="F95" t="str">
         <v>אלבומים חדשים</v>
@@ -5067,19 +4500,19 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>סטריי קידס DO IT (EP)</v>
+        <v>|| אהוד בנאי ובנו הנדלר - פליטי הדאב ()</v>
       </c>
       <c r="B96" t="str">
-        <v>2025-12-04</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C96" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D96" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E96" t="str">
-        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
+        <v/>
       </c>
       <c r="F96" t="str">
         <v>אלבומים חדשים</v>
@@ -5135,19 +4568,19 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>דויד ברוזה BROZAJAZZ</v>
+        <v>|| Imagine פסטיגל - שירי התחרות ()</v>
       </c>
       <c r="B97" t="str">
-        <v>2025-11-30</v>
+        <v>2025  02:04-12-31</v>
       </c>
       <c r="C97" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D97" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E97" t="str">
-        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
+        <v/>
       </c>
       <c r="F97" t="str">
         <v>אלבומים חדשים</v>
@@ -5203,19 +4636,19 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Five Seconds of Summer – Everyone's A Star</v>
+        <v>|| השמחות - חובות אבודים ()</v>
       </c>
       <c r="B98" t="str">
-        <v>2025-11-24</v>
+        <v>2025  02:02-12-31</v>
       </c>
       <c r="C98" t="str">
-        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D98" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E98" t="str">
-        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
+        <v/>
       </c>
       <c r="F98" t="str">
         <v>אלבומים חדשים</v>
@@ -5271,19 +4704,19 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>התקווה 6 – ויהי אור</v>
+        <v>|| שלמה גרוניך - כמו כוכבים ()</v>
       </c>
       <c r="B99" t="str">
-        <v>2025-11-20</v>
+        <v>2025  02:00-12-31</v>
       </c>
       <c r="C99" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D99" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E99" t="str">
-        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
+        <v/>
       </c>
       <c r="F99" t="str">
         <v>אלבומים חדשים</v>
@@ -5339,19 +4772,19 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>פלורנס אנד דה משין Everybody Scream</v>
+        <v>|| יוני רועה - מפוזרים ()</v>
       </c>
       <c r="B100" t="str">
-        <v>2025-11-13</v>
+        <v>2025  01:56-12-31</v>
       </c>
       <c r="C100" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D100" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E100" t="str">
-        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
+        <v/>
       </c>
       <c r="F100" t="str">
         <v>אלבומים חדשים</v>
@@ -5407,19 +4840,19 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>טיים אימפלה Deadbeat</v>
+        <v>|| התקווה 6 - ויהי אור ()</v>
       </c>
       <c r="B101" t="str">
-        <v>2025-11-03</v>
+        <v>2025  01:54-12-31</v>
       </c>
       <c r="C101" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D101" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E101" t="str">
-        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
+        <v/>
       </c>
       <c r="F101" t="str">
         <v>אלבומים חדשים</v>
@@ -5475,19 +4908,19 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+        <v>|| שאנן סטריט ודי ג׳יי מש - באתי לבדר ()</v>
       </c>
       <c r="B102" t="str">
-        <v>2025-10-20</v>
+        <v>2025  01:53-12-31</v>
       </c>
       <c r="C102" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D102" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E102" t="str">
-        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
+        <v/>
       </c>
       <c r="F102" t="str">
         <v>אלבומים חדשים</v>
@@ -5543,19 +4976,19 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>שלמה גרוניך – תודה אהבה</v>
+        <v>אשכול נוכחות למשתמשים פעילים</v>
       </c>
       <c r="B103" t="str">
-        <v>2025-10-18</v>
+        <v>2025  16:32 מאת freund-10-16</v>
       </c>
       <c r="C103" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=23455&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D103" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E103" t="str">
-        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
+        <v/>
       </c>
       <c r="F103" t="str">
         <v>אלבומים חדשים</v>
@@ -5606,24 +5039,30 @@
         <v/>
       </c>
       <c r="V103" t="str">
+        <v/>
+      </c>
+      <c r="W103" t="str">
+        <v/>
+      </c>
+      <c r="X103" t="str">
         <v/>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>טיילור סוויפט The Life Of A Showgirl</v>
+        <v>כיצד להוריד מהאתרים המפורסמים</v>
       </c>
       <c r="B104" t="str">
-        <v>2025-10-11</v>
+        <v>2023  16:23 מאת petel1-08-08</v>
       </c>
       <c r="C104" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=22411&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D104" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E104" t="str">
-        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
+        <v/>
       </c>
       <c r="F104" t="str">
         <v>אלבומים חדשים</v>
@@ -5674,24 +5113,30 @@
         <v/>
       </c>
       <c r="V104" t="str">
+        <v/>
+      </c>
+      <c r="W104" t="str">
+        <v/>
+      </c>
+      <c r="X104" t="str">
         <v/>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>דוג'ה קאט Vie</v>
+        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
       </c>
       <c r="B105" t="str">
-        <v>2025-10-04</v>
+        <v>2026  22:40 מאת מוטי_ד-01-01</v>
       </c>
       <c r="C105" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24435&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D105" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E105" t="str">
-        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
+        <v/>
       </c>
       <c r="F105" t="str">
         <v>אלבומים חדשים</v>
@@ -5742,24 +5187,30 @@
         <v/>
       </c>
       <c r="V105" t="str">
+        <v/>
+      </c>
+      <c r="W105" t="str">
+        <v/>
+      </c>
+      <c r="X105" t="str">
         <v/>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>ג'וי קרוקס Juniper</v>
+        <v>|אלבום חדש| אייל גולן - בית מפואר (2025)</v>
       </c>
       <c r="B106" t="str">
-        <v>2025-10-03</v>
+        <v>2025  02:18 מאת DiSHi-12-31</v>
       </c>
       <c r="C106" t="str">
-        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D106" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E106" t="str">
-        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
+        <v/>
       </c>
       <c r="F106" t="str">
         <v>אלבומים חדשים</v>
@@ -5810,24 +5261,30 @@
         <v/>
       </c>
       <c r="V106" t="str">
+        <v/>
+      </c>
+      <c r="W106" t="str">
+        <v/>
+      </c>
+      <c r="X106" t="str">
         <v/>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>ביפי קליירו Futique</v>
+        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע (2025)</v>
       </c>
       <c r="B107" t="str">
-        <v>2025-09-30</v>
+        <v>2025  02:17 מאת DiSHi-12-31</v>
       </c>
       <c r="C107" t="str">
-        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D107" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E107" t="str">
-        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
+        <v/>
       </c>
       <c r="F107" t="str">
         <v>אלבומים חדשים</v>
@@ -5878,24 +5335,30 @@
         <v/>
       </c>
       <c r="V107" t="str">
+        <v/>
+      </c>
+      <c r="W107" t="str">
+        <v/>
+      </c>
+      <c r="X107" t="str">
         <v/>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>אד שירן Play</v>
+        <v>|אלבום חדש| הפרויקט של דודי לוי ואבטיפוס - הפטריקים (2025)</v>
       </c>
       <c r="B108" t="str">
-        <v>2025-09-24</v>
+        <v>2025  02:16 מאת DiSHi-12-31</v>
       </c>
       <c r="C108" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D108" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E108" t="str">
-        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
+        <v/>
       </c>
       <c r="F108" t="str">
         <v>אלבומים חדשים</v>
@@ -5946,24 +5409,30 @@
         <v/>
       </c>
       <c r="V108" t="str">
+        <v/>
+      </c>
+      <c r="W108" t="str">
+        <v/>
+      </c>
+      <c r="X108" t="str">
         <v/>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+        <v>|אלבום חדש| אברהם טל - חי (2025)</v>
       </c>
       <c r="B109" t="str">
-        <v>2025-09-21</v>
+        <v>2025  02:16 מאת DiSHi-12-31</v>
       </c>
       <c r="C109" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D109" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E109" t="str">
-        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
+        <v/>
       </c>
       <c r="F109" t="str">
         <v>אלבומים חדשים</v>
@@ -6014,24 +5483,30 @@
         <v/>
       </c>
       <c r="V109" t="str">
+        <v/>
+      </c>
+      <c r="W109" t="str">
+        <v/>
+      </c>
+      <c r="X109" t="str">
         <v/>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>סוויד Antidepressants</v>
+        <v>|אלבום חדש| שיר לוי - ילד מוזר (2025)</v>
       </c>
       <c r="B110" t="str">
-        <v>2025-09-12</v>
+        <v>2025  02:14 מאת DiSHi-12-31</v>
       </c>
       <c r="C110" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D110" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E110" t="str">
-        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
+        <v/>
       </c>
       <c r="F110" t="str">
         <v>אלבומים חדשים</v>
@@ -6082,24 +5557,30 @@
         <v/>
       </c>
       <c r="V110" t="str">
+        <v/>
+      </c>
+      <c r="W110" t="str">
+        <v/>
+      </c>
+      <c r="X110" t="str">
         <v/>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>וולף אליס The Clearing</v>
+        <v>|אלבום חדש| מיקי גבריאלוב - שלום (2025)</v>
       </c>
       <c r="B111" t="str">
-        <v>2025-09-01</v>
+        <v>2025  02:13 מאת DiSHi-12-31</v>
       </c>
       <c r="C111" t="str">
-        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D111" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E111" t="str">
-        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
+        <v/>
       </c>
       <c r="F111" t="str">
         <v>אלבומים חדשים</v>
@@ -6150,24 +5631,30 @@
         <v/>
       </c>
       <c r="V111" t="str">
+        <v/>
+      </c>
+      <c r="W111" t="str">
+        <v/>
+      </c>
+      <c r="X111" t="str">
         <v/>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+        <v>|אלבום חדש| פיטר רוט - 50 (2025)</v>
       </c>
       <c r="B112" t="str">
-        <v>2025-08-29</v>
+        <v>2025  02:13 מאת DiSHi-12-31</v>
       </c>
       <c r="C112" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D112" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E112" t="str">
-        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
+        <v/>
       </c>
       <c r="F112" t="str">
         <v>אלבומים חדשים</v>
@@ -6218,24 +5705,30 @@
         <v/>
       </c>
       <c r="V112" t="str">
+        <v/>
+      </c>
+      <c r="W112" t="str">
+        <v/>
+      </c>
+      <c r="X112" t="str">
         <v/>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם (2025)</v>
       </c>
       <c r="B113" t="str">
-        <v>2025-08-24</v>
+        <v>2025  02:12 מאת DiSHi-12-31</v>
       </c>
       <c r="C113" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D113" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E113" t="str">
-        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
+        <v/>
       </c>
       <c r="F113" t="str">
         <v>אלבומים חדשים</v>
@@ -6286,24 +5779,30 @@
         <v/>
       </c>
       <c r="V113" t="str">
+        <v/>
+      </c>
+      <c r="W113" t="str">
+        <v/>
+      </c>
+      <c r="X113" t="str">
         <v/>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+        <v>|אלבום חדש| אגם בוחבוט - עשרים ואחת (2025)</v>
       </c>
       <c r="B114" t="str">
-        <v>2025-08-21</v>
+        <v>2025  02:11 מאת DiSHi-12-31</v>
       </c>
       <c r="C114" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D114" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E114" t="str">
-        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
+        <v/>
       </c>
       <c r="F114" t="str">
         <v>אלבומים חדשים</v>
@@ -6354,24 +5853,30 @@
         <v/>
       </c>
       <c r="V114" t="str">
+        <v/>
+      </c>
+      <c r="W114" t="str">
+        <v/>
+      </c>
+      <c r="X114" t="str">
         <v/>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>אברהם טל – חי</v>
+        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון (2025)</v>
       </c>
       <c r="B115" t="str">
-        <v>2025-08-17</v>
+        <v>2025  02:10 מאת DiSHi-12-31</v>
       </c>
       <c r="C115" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D115" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E115" t="str">
-        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
+        <v/>
       </c>
       <c r="F115" t="str">
         <v>אלבומים חדשים</v>
@@ -6422,24 +5927,30 @@
         <v/>
       </c>
       <c r="V115" t="str">
+        <v/>
+      </c>
+      <c r="W115" t="str">
+        <v/>
+      </c>
+      <c r="X115" t="str">
         <v/>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>רנה ראפ Bite Me</v>
+        <v>|אלבום חדש| רבקה זוהר - רסיסים של אור (2025)</v>
       </c>
       <c r="B116" t="str">
-        <v>2025-08-12</v>
+        <v>2025  02:09 מאת DiSHi-12-31</v>
       </c>
       <c r="C116" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D116" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E116" t="str">
-        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
+        <v/>
       </c>
       <c r="F116" t="str">
         <v>אלבומים חדשים</v>
@@ -6490,24 +6001,30 @@
         <v/>
       </c>
       <c r="V116" t="str">
+        <v/>
+      </c>
+      <c r="W116" t="str">
+        <v/>
+      </c>
+      <c r="X116" t="str">
         <v/>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>The K's – Pretty On The Internet</v>
+        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה (2025)</v>
       </c>
       <c r="B117" t="str">
-        <v>2025-08-03</v>
+        <v>2025  02:09 מאת DiSHi-12-31</v>
       </c>
       <c r="C117" t="str">
-        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D117" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E117" t="str">
-        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
+        <v/>
       </c>
       <c r="F117" t="str">
         <v>אלבומים חדשים</v>
@@ -6558,24 +6075,30 @@
         <v/>
       </c>
       <c r="V117" t="str">
+        <v/>
+      </c>
+      <c r="W117" t="str">
+        <v/>
+      </c>
+      <c r="X117" t="str">
         <v/>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>פליטווד מק Fifty Years – Don’t Stop</v>
+        <v>|אלבום חדש| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות (2025)</v>
       </c>
       <c r="B118" t="str">
-        <v>2025-07-30</v>
+        <v>2025  02:08 מאת DiSHi-12-31</v>
       </c>
       <c r="C118" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%99%d7%98%d7%95%d7%95%d7%93-%d7%9e%d7%a7-fifty-years-dont-stop/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D118" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E118" t="str">
-        <v>פליטווד מק (Fleetwood Mac) חוגגים חצי מאה של מוזיקה עם אוסף חדש בן 50 שירים, שמתפרש על כל הקריירה של הלהקה, מימיה הראשונים בסגנון בלוז, ועד להצלחתה העולמית כאחת מלהקות הגדולות בהיסטוריה של הרוק. פליטווד מק הם לא רק להקה</v>
+        <v/>
       </c>
       <c r="F118" t="str">
         <v>אלבומים חדשים</v>
@@ -6626,80 +6149,3528 @@
         <v/>
       </c>
       <c r="V118" t="str">
+        <v/>
+      </c>
+      <c r="W118" t="str">
+        <v/>
+      </c>
+      <c r="X118" t="str">
         <v/>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Wet Leg Moisturizer</v>
+        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים (2025)</v>
       </c>
       <c r="B119" t="str">
-        <v>2025-07-25</v>
+        <v>2025  02:06 מאת DiSHi-12-31</v>
       </c>
       <c r="C119" t="str">
-        <v>https://yosmusic.com/wet-leg-moisturizer/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D119" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E119" t="str">
+        <v/>
+      </c>
+      <c r="F119" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G119" t="str">
+        <v/>
+      </c>
+      <c r="H119" t="str">
+        <v/>
+      </c>
+      <c r="I119" t="str">
+        <v/>
+      </c>
+      <c r="J119" t="str">
+        <v/>
+      </c>
+      <c r="K119" t="str">
+        <v/>
+      </c>
+      <c r="L119" t="str">
+        <v/>
+      </c>
+      <c r="M119" t="str">
+        <v/>
+      </c>
+      <c r="N119" t="str">
+        <v/>
+      </c>
+      <c r="O119" t="str">
+        <v/>
+      </c>
+      <c r="P119" t="str">
+        <v/>
+      </c>
+      <c r="Q119" t="str">
+        <v/>
+      </c>
+      <c r="R119" t="str">
+        <v/>
+      </c>
+      <c r="S119" t="str">
+        <v/>
+      </c>
+      <c r="T119" t="str">
+        <v/>
+      </c>
+      <c r="U119" t="str">
+        <v/>
+      </c>
+      <c r="V119" t="str">
+        <v/>
+      </c>
+      <c r="W119" t="str">
+        <v/>
+      </c>
+      <c r="X119" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>|אלבום חדש| אהוד בנאי ובנו הנדלר - פליטי הדאב (2025)</v>
+      </c>
+      <c r="B120" t="str">
+        <v>2025  02:05 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C120" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D120" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E120" t="str">
+        <v/>
+      </c>
+      <c r="F120" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G120" t="str">
+        <v/>
+      </c>
+      <c r="H120" t="str">
+        <v/>
+      </c>
+      <c r="I120" t="str">
+        <v/>
+      </c>
+      <c r="J120" t="str">
+        <v/>
+      </c>
+      <c r="K120" t="str">
+        <v/>
+      </c>
+      <c r="L120" t="str">
+        <v/>
+      </c>
+      <c r="M120" t="str">
+        <v/>
+      </c>
+      <c r="N120" t="str">
+        <v/>
+      </c>
+      <c r="O120" t="str">
+        <v/>
+      </c>
+      <c r="P120" t="str">
+        <v/>
+      </c>
+      <c r="Q120" t="str">
+        <v/>
+      </c>
+      <c r="R120" t="str">
+        <v/>
+      </c>
+      <c r="S120" t="str">
+        <v/>
+      </c>
+      <c r="T120" t="str">
+        <v/>
+      </c>
+      <c r="U120" t="str">
+        <v/>
+      </c>
+      <c r="V120" t="str">
+        <v/>
+      </c>
+      <c r="W120" t="str">
+        <v/>
+      </c>
+      <c r="X120" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם (2025)</v>
+      </c>
+      <c r="B121" t="str">
+        <v>2025  02:05 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C121" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D121" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E121" t="str">
+        <v/>
+      </c>
+      <c r="F121" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G121" t="str">
+        <v/>
+      </c>
+      <c r="H121" t="str">
+        <v/>
+      </c>
+      <c r="I121" t="str">
+        <v/>
+      </c>
+      <c r="J121" t="str">
+        <v/>
+      </c>
+      <c r="K121" t="str">
+        <v/>
+      </c>
+      <c r="L121" t="str">
+        <v/>
+      </c>
+      <c r="M121" t="str">
+        <v/>
+      </c>
+      <c r="N121" t="str">
+        <v/>
+      </c>
+      <c r="O121" t="str">
+        <v/>
+      </c>
+      <c r="P121" t="str">
+        <v/>
+      </c>
+      <c r="Q121" t="str">
+        <v/>
+      </c>
+      <c r="R121" t="str">
+        <v/>
+      </c>
+      <c r="S121" t="str">
+        <v/>
+      </c>
+      <c r="T121" t="str">
+        <v/>
+      </c>
+      <c r="U121" t="str">
+        <v/>
+      </c>
+      <c r="V121" t="str">
+        <v/>
+      </c>
+      <c r="W121" t="str">
+        <v/>
+      </c>
+      <c r="X121" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>|אלבום חדש| Imagine פסטיגל - שירי התחרות (2025)</v>
+      </c>
+      <c r="B122" t="str">
+        <v>2025  02:04 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C122" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D122" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E122" t="str">
+        <v/>
+      </c>
+      <c r="F122" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G122" t="str">
+        <v/>
+      </c>
+      <c r="H122" t="str">
+        <v/>
+      </c>
+      <c r="I122" t="str">
+        <v/>
+      </c>
+      <c r="J122" t="str">
+        <v/>
+      </c>
+      <c r="K122" t="str">
+        <v/>
+      </c>
+      <c r="L122" t="str">
+        <v/>
+      </c>
+      <c r="M122" t="str">
+        <v/>
+      </c>
+      <c r="N122" t="str">
+        <v/>
+      </c>
+      <c r="O122" t="str">
+        <v/>
+      </c>
+      <c r="P122" t="str">
+        <v/>
+      </c>
+      <c r="Q122" t="str">
+        <v/>
+      </c>
+      <c r="R122" t="str">
+        <v/>
+      </c>
+      <c r="S122" t="str">
+        <v/>
+      </c>
+      <c r="T122" t="str">
+        <v/>
+      </c>
+      <c r="U122" t="str">
+        <v/>
+      </c>
+      <c r="V122" t="str">
+        <v/>
+      </c>
+      <c r="W122" t="str">
+        <v/>
+      </c>
+      <c r="X122" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>|אלבום חדש| סטטיק - קעקועים (2025)</v>
+      </c>
+      <c r="B123" t="str">
+        <v>2025  02:03 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C123" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D123" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E123" t="str">
+        <v/>
+      </c>
+      <c r="F123" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G123" t="str">
+        <v/>
+      </c>
+      <c r="H123" t="str">
+        <v/>
+      </c>
+      <c r="I123" t="str">
+        <v/>
+      </c>
+      <c r="J123" t="str">
+        <v/>
+      </c>
+      <c r="K123" t="str">
+        <v/>
+      </c>
+      <c r="L123" t="str">
+        <v/>
+      </c>
+      <c r="M123" t="str">
+        <v/>
+      </c>
+      <c r="N123" t="str">
+        <v/>
+      </c>
+      <c r="O123" t="str">
+        <v/>
+      </c>
+      <c r="P123" t="str">
+        <v/>
+      </c>
+      <c r="Q123" t="str">
+        <v/>
+      </c>
+      <c r="R123" t="str">
+        <v/>
+      </c>
+      <c r="S123" t="str">
+        <v/>
+      </c>
+      <c r="T123" t="str">
+        <v/>
+      </c>
+      <c r="U123" t="str">
+        <v/>
+      </c>
+      <c r="V123" t="str">
+        <v/>
+      </c>
+      <c r="W123" t="str">
+        <v/>
+      </c>
+      <c r="X123" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>|אלבום חדש| השמחות - חובות אבודים (2025)</v>
+      </c>
+      <c r="B124" t="str">
+        <v>2025  02:02 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C124" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D124" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E124" t="str">
+        <v/>
+      </c>
+      <c r="F124" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G124" t="str">
+        <v/>
+      </c>
+      <c r="H124" t="str">
+        <v/>
+      </c>
+      <c r="I124" t="str">
+        <v/>
+      </c>
+      <c r="J124" t="str">
+        <v/>
+      </c>
+      <c r="K124" t="str">
+        <v/>
+      </c>
+      <c r="L124" t="str">
+        <v/>
+      </c>
+      <c r="M124" t="str">
+        <v/>
+      </c>
+      <c r="N124" t="str">
+        <v/>
+      </c>
+      <c r="O124" t="str">
+        <v/>
+      </c>
+      <c r="P124" t="str">
+        <v/>
+      </c>
+      <c r="Q124" t="str">
+        <v/>
+      </c>
+      <c r="R124" t="str">
+        <v/>
+      </c>
+      <c r="S124" t="str">
+        <v/>
+      </c>
+      <c r="T124" t="str">
+        <v/>
+      </c>
+      <c r="U124" t="str">
+        <v/>
+      </c>
+      <c r="V124" t="str">
+        <v/>
+      </c>
+      <c r="W124" t="str">
+        <v/>
+      </c>
+      <c r="X124" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>|אלבום חדש| ליאור נרקיס - דיסוננס (2025)</v>
+      </c>
+      <c r="B125" t="str">
+        <v>2025  02:01 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C125" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D125" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E125" t="str">
+        <v/>
+      </c>
+      <c r="F125" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G125" t="str">
+        <v/>
+      </c>
+      <c r="H125" t="str">
+        <v/>
+      </c>
+      <c r="I125" t="str">
+        <v/>
+      </c>
+      <c r="J125" t="str">
+        <v/>
+      </c>
+      <c r="K125" t="str">
+        <v/>
+      </c>
+      <c r="L125" t="str">
+        <v/>
+      </c>
+      <c r="M125" t="str">
+        <v/>
+      </c>
+      <c r="N125" t="str">
+        <v/>
+      </c>
+      <c r="O125" t="str">
+        <v/>
+      </c>
+      <c r="P125" t="str">
+        <v/>
+      </c>
+      <c r="Q125" t="str">
+        <v/>
+      </c>
+      <c r="R125" t="str">
+        <v/>
+      </c>
+      <c r="S125" t="str">
+        <v/>
+      </c>
+      <c r="T125" t="str">
+        <v/>
+      </c>
+      <c r="U125" t="str">
+        <v/>
+      </c>
+      <c r="V125" t="str">
+        <v/>
+      </c>
+      <c r="W125" t="str">
+        <v/>
+      </c>
+      <c r="X125" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>|אלבום חדש| שלמה גרוניך - כמו כוכבים (2025)</v>
+      </c>
+      <c r="B126" t="str">
+        <v>2025  02:00 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C126" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D126" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E126" t="str">
+        <v/>
+      </c>
+      <c r="F126" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G126" t="str">
+        <v/>
+      </c>
+      <c r="H126" t="str">
+        <v/>
+      </c>
+      <c r="I126" t="str">
+        <v/>
+      </c>
+      <c r="J126" t="str">
+        <v/>
+      </c>
+      <c r="K126" t="str">
+        <v/>
+      </c>
+      <c r="L126" t="str">
+        <v/>
+      </c>
+      <c r="M126" t="str">
+        <v/>
+      </c>
+      <c r="N126" t="str">
+        <v/>
+      </c>
+      <c r="O126" t="str">
+        <v/>
+      </c>
+      <c r="P126" t="str">
+        <v/>
+      </c>
+      <c r="Q126" t="str">
+        <v/>
+      </c>
+      <c r="R126" t="str">
+        <v/>
+      </c>
+      <c r="S126" t="str">
+        <v/>
+      </c>
+      <c r="T126" t="str">
+        <v/>
+      </c>
+      <c r="U126" t="str">
+        <v/>
+      </c>
+      <c r="V126" t="str">
+        <v/>
+      </c>
+      <c r="W126" t="str">
+        <v/>
+      </c>
+      <c r="X126" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) (2025)</v>
+      </c>
+      <c r="B127" t="str">
+        <v>2025  01:57 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C127" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D127" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E127" t="str">
+        <v/>
+      </c>
+      <c r="F127" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G127" t="str">
+        <v/>
+      </c>
+      <c r="H127" t="str">
+        <v/>
+      </c>
+      <c r="I127" t="str">
+        <v/>
+      </c>
+      <c r="J127" t="str">
+        <v/>
+      </c>
+      <c r="K127" t="str">
+        <v/>
+      </c>
+      <c r="L127" t="str">
+        <v/>
+      </c>
+      <c r="M127" t="str">
+        <v/>
+      </c>
+      <c r="N127" t="str">
+        <v/>
+      </c>
+      <c r="O127" t="str">
+        <v/>
+      </c>
+      <c r="P127" t="str">
+        <v/>
+      </c>
+      <c r="Q127" t="str">
+        <v/>
+      </c>
+      <c r="R127" t="str">
+        <v/>
+      </c>
+      <c r="S127" t="str">
+        <v/>
+      </c>
+      <c r="T127" t="str">
+        <v/>
+      </c>
+      <c r="U127" t="str">
+        <v/>
+      </c>
+      <c r="V127" t="str">
+        <v/>
+      </c>
+      <c r="W127" t="str">
+        <v/>
+      </c>
+      <c r="X127" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>|אלבום חדש| יוני רועה - מפוזרים (2025)</v>
+      </c>
+      <c r="B128" t="str">
+        <v>2025  01:56 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C128" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D128" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E128" t="str">
+        <v/>
+      </c>
+      <c r="F128" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G128" t="str">
+        <v/>
+      </c>
+      <c r="H128" t="str">
+        <v/>
+      </c>
+      <c r="I128" t="str">
+        <v/>
+      </c>
+      <c r="J128" t="str">
+        <v/>
+      </c>
+      <c r="K128" t="str">
+        <v/>
+      </c>
+      <c r="L128" t="str">
+        <v/>
+      </c>
+      <c r="M128" t="str">
+        <v/>
+      </c>
+      <c r="N128" t="str">
+        <v/>
+      </c>
+      <c r="O128" t="str">
+        <v/>
+      </c>
+      <c r="P128" t="str">
+        <v/>
+      </c>
+      <c r="Q128" t="str">
+        <v/>
+      </c>
+      <c r="R128" t="str">
+        <v/>
+      </c>
+      <c r="S128" t="str">
+        <v/>
+      </c>
+      <c r="T128" t="str">
+        <v/>
+      </c>
+      <c r="U128" t="str">
+        <v/>
+      </c>
+      <c r="V128" t="str">
+        <v/>
+      </c>
+      <c r="W128" t="str">
+        <v/>
+      </c>
+      <c r="X128" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>|אלבום חדש| אתניקס - איטליה (2025)</v>
+      </c>
+      <c r="B129" t="str">
+        <v>2025  01:55 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C129" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D129" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E129" t="str">
+        <v/>
+      </c>
+      <c r="F129" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G129" t="str">
+        <v/>
+      </c>
+      <c r="H129" t="str">
+        <v/>
+      </c>
+      <c r="I129" t="str">
+        <v/>
+      </c>
+      <c r="J129" t="str">
+        <v/>
+      </c>
+      <c r="K129" t="str">
+        <v/>
+      </c>
+      <c r="L129" t="str">
+        <v/>
+      </c>
+      <c r="M129" t="str">
+        <v/>
+      </c>
+      <c r="N129" t="str">
+        <v/>
+      </c>
+      <c r="O129" t="str">
+        <v/>
+      </c>
+      <c r="P129" t="str">
+        <v/>
+      </c>
+      <c r="Q129" t="str">
+        <v/>
+      </c>
+      <c r="R129" t="str">
+        <v/>
+      </c>
+      <c r="S129" t="str">
+        <v/>
+      </c>
+      <c r="T129" t="str">
+        <v/>
+      </c>
+      <c r="U129" t="str">
+        <v/>
+      </c>
+      <c r="V129" t="str">
+        <v/>
+      </c>
+      <c r="W129" t="str">
+        <v/>
+      </c>
+      <c r="X129" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>|אלבום חדש| התקווה 6 - ויהי אור (2025)</v>
+      </c>
+      <c r="B130" t="str">
+        <v>2025  01:54 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C130" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D130" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E130" t="str">
+        <v/>
+      </c>
+      <c r="F130" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G130" t="str">
+        <v/>
+      </c>
+      <c r="H130" t="str">
+        <v/>
+      </c>
+      <c r="I130" t="str">
+        <v/>
+      </c>
+      <c r="J130" t="str">
+        <v/>
+      </c>
+      <c r="K130" t="str">
+        <v/>
+      </c>
+      <c r="L130" t="str">
+        <v/>
+      </c>
+      <c r="M130" t="str">
+        <v/>
+      </c>
+      <c r="N130" t="str">
+        <v/>
+      </c>
+      <c r="O130" t="str">
+        <v/>
+      </c>
+      <c r="P130" t="str">
+        <v/>
+      </c>
+      <c r="Q130" t="str">
+        <v/>
+      </c>
+      <c r="R130" t="str">
+        <v/>
+      </c>
+      <c r="S130" t="str">
+        <v/>
+      </c>
+      <c r="T130" t="str">
+        <v/>
+      </c>
+      <c r="U130" t="str">
+        <v/>
+      </c>
+      <c r="V130" t="str">
+        <v/>
+      </c>
+      <c r="W130" t="str">
+        <v/>
+      </c>
+      <c r="X130" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>|אלבום חדש| שלומי סרנגה - איפרכו (2025)</v>
+      </c>
+      <c r="B131" t="str">
+        <v>2025  01:53 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C131" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24430&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D131" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E131" t="str">
+        <v/>
+      </c>
+      <c r="F131" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G131" t="str">
+        <v/>
+      </c>
+      <c r="H131" t="str">
+        <v/>
+      </c>
+      <c r="I131" t="str">
+        <v/>
+      </c>
+      <c r="J131" t="str">
+        <v/>
+      </c>
+      <c r="K131" t="str">
+        <v/>
+      </c>
+      <c r="L131" t="str">
+        <v/>
+      </c>
+      <c r="M131" t="str">
+        <v/>
+      </c>
+      <c r="N131" t="str">
+        <v/>
+      </c>
+      <c r="O131" t="str">
+        <v/>
+      </c>
+      <c r="P131" t="str">
+        <v/>
+      </c>
+      <c r="Q131" t="str">
+        <v/>
+      </c>
+      <c r="R131" t="str">
+        <v/>
+      </c>
+      <c r="S131" t="str">
+        <v/>
+      </c>
+      <c r="T131" t="str">
+        <v/>
+      </c>
+      <c r="U131" t="str">
+        <v/>
+      </c>
+      <c r="V131" t="str">
+        <v/>
+      </c>
+      <c r="W131" t="str">
+        <v/>
+      </c>
+      <c r="X131" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>|אלבום חדש| שאנן סטריט ודי ג׳יי מש - באתי לבדר (2025)</v>
+      </c>
+      <c r="B132" t="str">
+        <v>2025  01:53 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C132" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D132" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E132" t="str">
+        <v/>
+      </c>
+      <c r="F132" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G132" t="str">
+        <v/>
+      </c>
+      <c r="H132" t="str">
+        <v/>
+      </c>
+      <c r="I132" t="str">
+        <v/>
+      </c>
+      <c r="J132" t="str">
+        <v/>
+      </c>
+      <c r="K132" t="str">
+        <v/>
+      </c>
+      <c r="L132" t="str">
+        <v/>
+      </c>
+      <c r="M132" t="str">
+        <v/>
+      </c>
+      <c r="N132" t="str">
+        <v/>
+      </c>
+      <c r="O132" t="str">
+        <v/>
+      </c>
+      <c r="P132" t="str">
+        <v/>
+      </c>
+      <c r="Q132" t="str">
+        <v/>
+      </c>
+      <c r="R132" t="str">
+        <v/>
+      </c>
+      <c r="S132" t="str">
+        <v/>
+      </c>
+      <c r="T132" t="str">
+        <v/>
+      </c>
+      <c r="U132" t="str">
+        <v/>
+      </c>
+      <c r="V132" t="str">
+        <v/>
+      </c>
+      <c r="W132" t="str">
+        <v/>
+      </c>
+      <c r="X132" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>הרשם לחברות מלאה</v>
+      </c>
+      <c r="B133" t="str">
+        <v/>
+      </c>
+      <c r="C133" t="str">
+        <v>https://rotter.name/nor/members-new.html</v>
+      </c>
+      <c r="D133" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E133" t="str">
+        <v/>
+      </c>
+      <c r="F133" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G133" t="str">
+        <v/>
+      </c>
+      <c r="H133" t="str">
+        <v/>
+      </c>
+      <c r="I133" t="str">
+        <v/>
+      </c>
+      <c r="J133" t="str">
+        <v/>
+      </c>
+      <c r="K133" t="str">
+        <v/>
+      </c>
+      <c r="L133" t="str">
+        <v/>
+      </c>
+      <c r="M133" t="str">
+        <v/>
+      </c>
+      <c r="N133" t="str">
+        <v/>
+      </c>
+      <c r="O133" t="str">
+        <v/>
+      </c>
+      <c r="P133" t="str">
+        <v/>
+      </c>
+      <c r="Q133" t="str">
+        <v/>
+      </c>
+      <c r="R133" t="str">
+        <v/>
+      </c>
+      <c r="S133" t="str">
+        <v/>
+      </c>
+      <c r="T133" t="str">
+        <v/>
+      </c>
+      <c r="U133" t="str">
+        <v/>
+      </c>
+      <c r="V133" t="str">
+        <v/>
+      </c>
+      <c r="W133" t="str">
+        <v/>
+      </c>
+      <c r="X133" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>אוליביה דין The Art of Loving</v>
+      </c>
+      <c r="B134" t="str">
+        <v>2026-01-04</v>
+      </c>
+      <c r="C134" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
+      </c>
+      <c r="D134" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E134" t="str">
+        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
+      </c>
+      <c r="F134" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G134" t="str">
+        <v/>
+      </c>
+      <c r="H134" t="str">
+        <v/>
+      </c>
+      <c r="I134" t="str">
+        <v/>
+      </c>
+      <c r="J134" t="str">
+        <v/>
+      </c>
+      <c r="K134" t="str">
+        <v/>
+      </c>
+      <c r="L134" t="str">
+        <v/>
+      </c>
+      <c r="M134" t="str">
+        <v/>
+      </c>
+      <c r="N134" t="str">
+        <v/>
+      </c>
+      <c r="O134" t="str">
+        <v/>
+      </c>
+      <c r="P134" t="str">
+        <v/>
+      </c>
+      <c r="Q134" t="str">
+        <v/>
+      </c>
+      <c r="R134" t="str">
+        <v/>
+      </c>
+      <c r="S134" t="str">
+        <v/>
+      </c>
+      <c r="T134" t="str">
+        <v/>
+      </c>
+      <c r="U134" t="str">
+        <v/>
+      </c>
+      <c r="V134" t="str">
+        <v/>
+      </c>
+      <c r="W134" t="str">
+        <v/>
+      </c>
+      <c r="X134" t="str">
+        <v/>
+      </c>
+      <c r="Y134" t="str">
+        <v/>
+      </c>
+      <c r="Z134" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>Geese Getting Killed</v>
+      </c>
+      <c r="B135" t="str">
+        <v>2025-12-29</v>
+      </c>
+      <c r="C135" t="str">
+        <v>https://yosmusic.com/geese-getting-killed/</v>
+      </c>
+      <c r="D135" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E135" t="str">
+        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
+      </c>
+      <c r="F135" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G135" t="str">
+        <v/>
+      </c>
+      <c r="H135" t="str">
+        <v/>
+      </c>
+      <c r="I135" t="str">
+        <v/>
+      </c>
+      <c r="J135" t="str">
+        <v/>
+      </c>
+      <c r="K135" t="str">
+        <v/>
+      </c>
+      <c r="L135" t="str">
+        <v/>
+      </c>
+      <c r="M135" t="str">
+        <v/>
+      </c>
+      <c r="N135" t="str">
+        <v/>
+      </c>
+      <c r="O135" t="str">
+        <v/>
+      </c>
+      <c r="P135" t="str">
+        <v/>
+      </c>
+      <c r="Q135" t="str">
+        <v/>
+      </c>
+      <c r="R135" t="str">
+        <v/>
+      </c>
+      <c r="S135" t="str">
+        <v/>
+      </c>
+      <c r="T135" t="str">
+        <v/>
+      </c>
+      <c r="U135" t="str">
+        <v/>
+      </c>
+      <c r="V135" t="str">
+        <v/>
+      </c>
+      <c r="W135" t="str">
+        <v/>
+      </c>
+      <c r="X135" t="str">
+        <v/>
+      </c>
+      <c r="Y135" t="str">
+        <v/>
+      </c>
+      <c r="Z135" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>רוסליה Lux</v>
+      </c>
+      <c r="B136" t="str">
+        <v>2025-12-25</v>
+      </c>
+      <c r="C136" t="str">
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
+      </c>
+      <c r="D136" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E136" t="str">
+        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
+      </c>
+      <c r="F136" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G136" t="str">
+        <v/>
+      </c>
+      <c r="H136" t="str">
+        <v/>
+      </c>
+      <c r="I136" t="str">
+        <v/>
+      </c>
+      <c r="J136" t="str">
+        <v/>
+      </c>
+      <c r="K136" t="str">
+        <v/>
+      </c>
+      <c r="L136" t="str">
+        <v/>
+      </c>
+      <c r="M136" t="str">
+        <v/>
+      </c>
+      <c r="N136" t="str">
+        <v/>
+      </c>
+      <c r="O136" t="str">
+        <v/>
+      </c>
+      <c r="P136" t="str">
+        <v/>
+      </c>
+      <c r="Q136" t="str">
+        <v/>
+      </c>
+      <c r="R136" t="str">
+        <v/>
+      </c>
+      <c r="S136" t="str">
+        <v/>
+      </c>
+      <c r="T136" t="str">
+        <v/>
+      </c>
+      <c r="U136" t="str">
+        <v/>
+      </c>
+      <c r="V136" t="str">
+        <v/>
+      </c>
+      <c r="W136" t="str">
+        <v/>
+      </c>
+      <c r="X136" t="str">
+        <v/>
+      </c>
+      <c r="Y136" t="str">
+        <v/>
+      </c>
+      <c r="Z136" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>יאנגבלאד אירוסמית' one more time</v>
+      </c>
+      <c r="B137" t="str">
+        <v>2025-12-17</v>
+      </c>
+      <c r="C137" t="str">
+        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
+      </c>
+      <c r="D137" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E137" t="str">
+        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
+      </c>
+      <c r="F137" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G137" t="str">
+        <v/>
+      </c>
+      <c r="H137" t="str">
+        <v/>
+      </c>
+      <c r="I137" t="str">
+        <v/>
+      </c>
+      <c r="J137" t="str">
+        <v/>
+      </c>
+      <c r="K137" t="str">
+        <v/>
+      </c>
+      <c r="L137" t="str">
+        <v/>
+      </c>
+      <c r="M137" t="str">
+        <v/>
+      </c>
+      <c r="N137" t="str">
+        <v/>
+      </c>
+      <c r="O137" t="str">
+        <v/>
+      </c>
+      <c r="P137" t="str">
+        <v/>
+      </c>
+      <c r="Q137" t="str">
+        <v/>
+      </c>
+      <c r="R137" t="str">
+        <v/>
+      </c>
+      <c r="S137" t="str">
+        <v/>
+      </c>
+      <c r="T137" t="str">
+        <v/>
+      </c>
+      <c r="U137" t="str">
+        <v/>
+      </c>
+      <c r="V137" t="str">
+        <v/>
+      </c>
+      <c r="W137" t="str">
+        <v/>
+      </c>
+      <c r="X137" t="str">
+        <v/>
+      </c>
+      <c r="Y137" t="str">
+        <v/>
+      </c>
+      <c r="Z137" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>פינק פלויד Wish You Were Here 50</v>
+      </c>
+      <c r="B138" t="str">
+        <v>2025-12-14</v>
+      </c>
+      <c r="C138" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
+      </c>
+      <c r="D138" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E138" t="str">
+        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
+      </c>
+      <c r="F138" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G138" t="str">
+        <v/>
+      </c>
+      <c r="H138" t="str">
+        <v/>
+      </c>
+      <c r="I138" t="str">
+        <v/>
+      </c>
+      <c r="J138" t="str">
+        <v/>
+      </c>
+      <c r="K138" t="str">
+        <v/>
+      </c>
+      <c r="L138" t="str">
+        <v/>
+      </c>
+      <c r="M138" t="str">
+        <v/>
+      </c>
+      <c r="N138" t="str">
+        <v/>
+      </c>
+      <c r="O138" t="str">
+        <v/>
+      </c>
+      <c r="P138" t="str">
+        <v/>
+      </c>
+      <c r="Q138" t="str">
+        <v/>
+      </c>
+      <c r="R138" t="str">
+        <v/>
+      </c>
+      <c r="S138" t="str">
+        <v/>
+      </c>
+      <c r="T138" t="str">
+        <v/>
+      </c>
+      <c r="U138" t="str">
+        <v/>
+      </c>
+      <c r="V138" t="str">
+        <v/>
+      </c>
+      <c r="W138" t="str">
+        <v/>
+      </c>
+      <c r="X138" t="str">
+        <v/>
+      </c>
+      <c r="Y138" t="str">
+        <v/>
+      </c>
+      <c r="Z138" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+      </c>
+      <c r="B139" t="str">
+        <v>2025-12-08</v>
+      </c>
+      <c r="C139" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
+      </c>
+      <c r="D139" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E139" t="str">
+        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
+      </c>
+      <c r="F139" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G139" t="str">
+        <v/>
+      </c>
+      <c r="H139" t="str">
+        <v/>
+      </c>
+      <c r="I139" t="str">
+        <v/>
+      </c>
+      <c r="J139" t="str">
+        <v/>
+      </c>
+      <c r="K139" t="str">
+        <v/>
+      </c>
+      <c r="L139" t="str">
+        <v/>
+      </c>
+      <c r="M139" t="str">
+        <v/>
+      </c>
+      <c r="N139" t="str">
+        <v/>
+      </c>
+      <c r="O139" t="str">
+        <v/>
+      </c>
+      <c r="P139" t="str">
+        <v/>
+      </c>
+      <c r="Q139" t="str">
+        <v/>
+      </c>
+      <c r="R139" t="str">
+        <v/>
+      </c>
+      <c r="S139" t="str">
+        <v/>
+      </c>
+      <c r="T139" t="str">
+        <v/>
+      </c>
+      <c r="U139" t="str">
+        <v/>
+      </c>
+      <c r="V139" t="str">
+        <v/>
+      </c>
+      <c r="W139" t="str">
+        <v/>
+      </c>
+      <c r="X139" t="str">
+        <v/>
+      </c>
+      <c r="Y139" t="str">
+        <v/>
+      </c>
+      <c r="Z139" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>סטריי קידס DO IT (EP)</v>
+      </c>
+      <c r="B140" t="str">
+        <v>2025-12-04</v>
+      </c>
+      <c r="C140" t="str">
+        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
+      </c>
+      <c r="D140" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E140" t="str">
+        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
+      </c>
+      <c r="F140" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G140" t="str">
+        <v/>
+      </c>
+      <c r="H140" t="str">
+        <v/>
+      </c>
+      <c r="I140" t="str">
+        <v/>
+      </c>
+      <c r="J140" t="str">
+        <v/>
+      </c>
+      <c r="K140" t="str">
+        <v/>
+      </c>
+      <c r="L140" t="str">
+        <v/>
+      </c>
+      <c r="M140" t="str">
+        <v/>
+      </c>
+      <c r="N140" t="str">
+        <v/>
+      </c>
+      <c r="O140" t="str">
+        <v/>
+      </c>
+      <c r="P140" t="str">
+        <v/>
+      </c>
+      <c r="Q140" t="str">
+        <v/>
+      </c>
+      <c r="R140" t="str">
+        <v/>
+      </c>
+      <c r="S140" t="str">
+        <v/>
+      </c>
+      <c r="T140" t="str">
+        <v/>
+      </c>
+      <c r="U140" t="str">
+        <v/>
+      </c>
+      <c r="V140" t="str">
+        <v/>
+      </c>
+      <c r="W140" t="str">
+        <v/>
+      </c>
+      <c r="X140" t="str">
+        <v/>
+      </c>
+      <c r="Y140" t="str">
+        <v/>
+      </c>
+      <c r="Z140" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>דויד ברוזה BROZAJAZZ</v>
+      </c>
+      <c r="B141" t="str">
+        <v>2025-11-30</v>
+      </c>
+      <c r="C141" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
+      </c>
+      <c r="D141" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E141" t="str">
+        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
+      </c>
+      <c r="F141" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G141" t="str">
+        <v/>
+      </c>
+      <c r="H141" t="str">
+        <v/>
+      </c>
+      <c r="I141" t="str">
+        <v/>
+      </c>
+      <c r="J141" t="str">
+        <v/>
+      </c>
+      <c r="K141" t="str">
+        <v/>
+      </c>
+      <c r="L141" t="str">
+        <v/>
+      </c>
+      <c r="M141" t="str">
+        <v/>
+      </c>
+      <c r="N141" t="str">
+        <v/>
+      </c>
+      <c r="O141" t="str">
+        <v/>
+      </c>
+      <c r="P141" t="str">
+        <v/>
+      </c>
+      <c r="Q141" t="str">
+        <v/>
+      </c>
+      <c r="R141" t="str">
+        <v/>
+      </c>
+      <c r="S141" t="str">
+        <v/>
+      </c>
+      <c r="T141" t="str">
+        <v/>
+      </c>
+      <c r="U141" t="str">
+        <v/>
+      </c>
+      <c r="V141" t="str">
+        <v/>
+      </c>
+      <c r="W141" t="str">
+        <v/>
+      </c>
+      <c r="X141" t="str">
+        <v/>
+      </c>
+      <c r="Y141" t="str">
+        <v/>
+      </c>
+      <c r="Z141" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>Five Seconds of Summer – Everyone's A Star</v>
+      </c>
+      <c r="B142" t="str">
+        <v>2025-11-24</v>
+      </c>
+      <c r="C142" t="str">
+        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
+      </c>
+      <c r="D142" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E142" t="str">
+        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
+      </c>
+      <c r="F142" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G142" t="str">
+        <v/>
+      </c>
+      <c r="H142" t="str">
+        <v/>
+      </c>
+      <c r="I142" t="str">
+        <v/>
+      </c>
+      <c r="J142" t="str">
+        <v/>
+      </c>
+      <c r="K142" t="str">
+        <v/>
+      </c>
+      <c r="L142" t="str">
+        <v/>
+      </c>
+      <c r="M142" t="str">
+        <v/>
+      </c>
+      <c r="N142" t="str">
+        <v/>
+      </c>
+      <c r="O142" t="str">
+        <v/>
+      </c>
+      <c r="P142" t="str">
+        <v/>
+      </c>
+      <c r="Q142" t="str">
+        <v/>
+      </c>
+      <c r="R142" t="str">
+        <v/>
+      </c>
+      <c r="S142" t="str">
+        <v/>
+      </c>
+      <c r="T142" t="str">
+        <v/>
+      </c>
+      <c r="U142" t="str">
+        <v/>
+      </c>
+      <c r="V142" t="str">
+        <v/>
+      </c>
+      <c r="W142" t="str">
+        <v/>
+      </c>
+      <c r="X142" t="str">
+        <v/>
+      </c>
+      <c r="Y142" t="str">
+        <v/>
+      </c>
+      <c r="Z142" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>התקווה 6 – ויהי אור</v>
+      </c>
+      <c r="B143" t="str">
+        <v>2025-11-20</v>
+      </c>
+      <c r="C143" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
+      </c>
+      <c r="D143" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E143" t="str">
+        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
+      </c>
+      <c r="F143" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G143" t="str">
+        <v/>
+      </c>
+      <c r="H143" t="str">
+        <v/>
+      </c>
+      <c r="I143" t="str">
+        <v/>
+      </c>
+      <c r="J143" t="str">
+        <v/>
+      </c>
+      <c r="K143" t="str">
+        <v/>
+      </c>
+      <c r="L143" t="str">
+        <v/>
+      </c>
+      <c r="M143" t="str">
+        <v/>
+      </c>
+      <c r="N143" t="str">
+        <v/>
+      </c>
+      <c r="O143" t="str">
+        <v/>
+      </c>
+      <c r="P143" t="str">
+        <v/>
+      </c>
+      <c r="Q143" t="str">
+        <v/>
+      </c>
+      <c r="R143" t="str">
+        <v/>
+      </c>
+      <c r="S143" t="str">
+        <v/>
+      </c>
+      <c r="T143" t="str">
+        <v/>
+      </c>
+      <c r="U143" t="str">
+        <v/>
+      </c>
+      <c r="V143" t="str">
+        <v/>
+      </c>
+      <c r="W143" t="str">
+        <v/>
+      </c>
+      <c r="X143" t="str">
+        <v/>
+      </c>
+      <c r="Y143" t="str">
+        <v/>
+      </c>
+      <c r="Z143" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>פלורנס אנד דה משין Everybody Scream</v>
+      </c>
+      <c r="B144" t="str">
+        <v>2025-11-13</v>
+      </c>
+      <c r="C144" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
+      </c>
+      <c r="D144" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E144" t="str">
+        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
+      </c>
+      <c r="F144" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G144" t="str">
+        <v/>
+      </c>
+      <c r="H144" t="str">
+        <v/>
+      </c>
+      <c r="I144" t="str">
+        <v/>
+      </c>
+      <c r="J144" t="str">
+        <v/>
+      </c>
+      <c r="K144" t="str">
+        <v/>
+      </c>
+      <c r="L144" t="str">
+        <v/>
+      </c>
+      <c r="M144" t="str">
+        <v/>
+      </c>
+      <c r="N144" t="str">
+        <v/>
+      </c>
+      <c r="O144" t="str">
+        <v/>
+      </c>
+      <c r="P144" t="str">
+        <v/>
+      </c>
+      <c r="Q144" t="str">
+        <v/>
+      </c>
+      <c r="R144" t="str">
+        <v/>
+      </c>
+      <c r="S144" t="str">
+        <v/>
+      </c>
+      <c r="T144" t="str">
+        <v/>
+      </c>
+      <c r="U144" t="str">
+        <v/>
+      </c>
+      <c r="V144" t="str">
+        <v/>
+      </c>
+      <c r="W144" t="str">
+        <v/>
+      </c>
+      <c r="X144" t="str">
+        <v/>
+      </c>
+      <c r="Y144" t="str">
+        <v/>
+      </c>
+      <c r="Z144" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>טיים אימפלה Deadbeat</v>
+      </c>
+      <c r="B145" t="str">
+        <v>2025-11-03</v>
+      </c>
+      <c r="C145" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
+      </c>
+      <c r="D145" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E145" t="str">
+        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
+      </c>
+      <c r="F145" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G145" t="str">
+        <v/>
+      </c>
+      <c r="H145" t="str">
+        <v/>
+      </c>
+      <c r="I145" t="str">
+        <v/>
+      </c>
+      <c r="J145" t="str">
+        <v/>
+      </c>
+      <c r="K145" t="str">
+        <v/>
+      </c>
+      <c r="L145" t="str">
+        <v/>
+      </c>
+      <c r="M145" t="str">
+        <v/>
+      </c>
+      <c r="N145" t="str">
+        <v/>
+      </c>
+      <c r="O145" t="str">
+        <v/>
+      </c>
+      <c r="P145" t="str">
+        <v/>
+      </c>
+      <c r="Q145" t="str">
+        <v/>
+      </c>
+      <c r="R145" t="str">
+        <v/>
+      </c>
+      <c r="S145" t="str">
+        <v/>
+      </c>
+      <c r="T145" t="str">
+        <v/>
+      </c>
+      <c r="U145" t="str">
+        <v/>
+      </c>
+      <c r="V145" t="str">
+        <v/>
+      </c>
+      <c r="W145" t="str">
+        <v/>
+      </c>
+      <c r="X145" t="str">
+        <v/>
+      </c>
+      <c r="Y145" t="str">
+        <v/>
+      </c>
+      <c r="Z145" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+      </c>
+      <c r="B146" t="str">
+        <v>2025-10-20</v>
+      </c>
+      <c r="C146" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
+      </c>
+      <c r="D146" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E146" t="str">
+        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
+      </c>
+      <c r="F146" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G146" t="str">
+        <v/>
+      </c>
+      <c r="H146" t="str">
+        <v/>
+      </c>
+      <c r="I146" t="str">
+        <v/>
+      </c>
+      <c r="J146" t="str">
+        <v/>
+      </c>
+      <c r="K146" t="str">
+        <v/>
+      </c>
+      <c r="L146" t="str">
+        <v/>
+      </c>
+      <c r="M146" t="str">
+        <v/>
+      </c>
+      <c r="N146" t="str">
+        <v/>
+      </c>
+      <c r="O146" t="str">
+        <v/>
+      </c>
+      <c r="P146" t="str">
+        <v/>
+      </c>
+      <c r="Q146" t="str">
+        <v/>
+      </c>
+      <c r="R146" t="str">
+        <v/>
+      </c>
+      <c r="S146" t="str">
+        <v/>
+      </c>
+      <c r="T146" t="str">
+        <v/>
+      </c>
+      <c r="U146" t="str">
+        <v/>
+      </c>
+      <c r="V146" t="str">
+        <v/>
+      </c>
+      <c r="W146" t="str">
+        <v/>
+      </c>
+      <c r="X146" t="str">
+        <v/>
+      </c>
+      <c r="Y146" t="str">
+        <v/>
+      </c>
+      <c r="Z146" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>שלמה גרוניך – תודה אהבה</v>
+      </c>
+      <c r="B147" t="str">
+        <v>2025-10-18</v>
+      </c>
+      <c r="C147" t="str">
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
+      </c>
+      <c r="D147" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E147" t="str">
+        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
+      </c>
+      <c r="F147" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G147" t="str">
+        <v/>
+      </c>
+      <c r="H147" t="str">
+        <v/>
+      </c>
+      <c r="I147" t="str">
+        <v/>
+      </c>
+      <c r="J147" t="str">
+        <v/>
+      </c>
+      <c r="K147" t="str">
+        <v/>
+      </c>
+      <c r="L147" t="str">
+        <v/>
+      </c>
+      <c r="M147" t="str">
+        <v/>
+      </c>
+      <c r="N147" t="str">
+        <v/>
+      </c>
+      <c r="O147" t="str">
+        <v/>
+      </c>
+      <c r="P147" t="str">
+        <v/>
+      </c>
+      <c r="Q147" t="str">
+        <v/>
+      </c>
+      <c r="R147" t="str">
+        <v/>
+      </c>
+      <c r="S147" t="str">
+        <v/>
+      </c>
+      <c r="T147" t="str">
+        <v/>
+      </c>
+      <c r="U147" t="str">
+        <v/>
+      </c>
+      <c r="V147" t="str">
+        <v/>
+      </c>
+      <c r="W147" t="str">
+        <v/>
+      </c>
+      <c r="X147" t="str">
+        <v/>
+      </c>
+      <c r="Y147" t="str">
+        <v/>
+      </c>
+      <c r="Z147" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
+      </c>
+      <c r="B148" t="str">
+        <v>2025-10-11</v>
+      </c>
+      <c r="C148" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
+      </c>
+      <c r="D148" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E148" t="str">
+        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
+      </c>
+      <c r="F148" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G148" t="str">
+        <v/>
+      </c>
+      <c r="H148" t="str">
+        <v/>
+      </c>
+      <c r="I148" t="str">
+        <v/>
+      </c>
+      <c r="J148" t="str">
+        <v/>
+      </c>
+      <c r="K148" t="str">
+        <v/>
+      </c>
+      <c r="L148" t="str">
+        <v/>
+      </c>
+      <c r="M148" t="str">
+        <v/>
+      </c>
+      <c r="N148" t="str">
+        <v/>
+      </c>
+      <c r="O148" t="str">
+        <v/>
+      </c>
+      <c r="P148" t="str">
+        <v/>
+      </c>
+      <c r="Q148" t="str">
+        <v/>
+      </c>
+      <c r="R148" t="str">
+        <v/>
+      </c>
+      <c r="S148" t="str">
+        <v/>
+      </c>
+      <c r="T148" t="str">
+        <v/>
+      </c>
+      <c r="U148" t="str">
+        <v/>
+      </c>
+      <c r="V148" t="str">
+        <v/>
+      </c>
+      <c r="W148" t="str">
+        <v/>
+      </c>
+      <c r="X148" t="str">
+        <v/>
+      </c>
+      <c r="Y148" t="str">
+        <v/>
+      </c>
+      <c r="Z148" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>דוג'ה קאט Vie</v>
+      </c>
+      <c r="B149" t="str">
+        <v>2025-10-04</v>
+      </c>
+      <c r="C149" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
+      </c>
+      <c r="D149" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E149" t="str">
+        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
+      </c>
+      <c r="F149" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G149" t="str">
+        <v/>
+      </c>
+      <c r="H149" t="str">
+        <v/>
+      </c>
+      <c r="I149" t="str">
+        <v/>
+      </c>
+      <c r="J149" t="str">
+        <v/>
+      </c>
+      <c r="K149" t="str">
+        <v/>
+      </c>
+      <c r="L149" t="str">
+        <v/>
+      </c>
+      <c r="M149" t="str">
+        <v/>
+      </c>
+      <c r="N149" t="str">
+        <v/>
+      </c>
+      <c r="O149" t="str">
+        <v/>
+      </c>
+      <c r="P149" t="str">
+        <v/>
+      </c>
+      <c r="Q149" t="str">
+        <v/>
+      </c>
+      <c r="R149" t="str">
+        <v/>
+      </c>
+      <c r="S149" t="str">
+        <v/>
+      </c>
+      <c r="T149" t="str">
+        <v/>
+      </c>
+      <c r="U149" t="str">
+        <v/>
+      </c>
+      <c r="V149" t="str">
+        <v/>
+      </c>
+      <c r="W149" t="str">
+        <v/>
+      </c>
+      <c r="X149" t="str">
+        <v/>
+      </c>
+      <c r="Y149" t="str">
+        <v/>
+      </c>
+      <c r="Z149" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>ג'וי קרוקס Juniper</v>
+      </c>
+      <c r="B150" t="str">
+        <v>2025-10-03</v>
+      </c>
+      <c r="C150" t="str">
+        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
+      </c>
+      <c r="D150" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E150" t="str">
+        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
+      </c>
+      <c r="F150" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G150" t="str">
+        <v/>
+      </c>
+      <c r="H150" t="str">
+        <v/>
+      </c>
+      <c r="I150" t="str">
+        <v/>
+      </c>
+      <c r="J150" t="str">
+        <v/>
+      </c>
+      <c r="K150" t="str">
+        <v/>
+      </c>
+      <c r="L150" t="str">
+        <v/>
+      </c>
+      <c r="M150" t="str">
+        <v/>
+      </c>
+      <c r="N150" t="str">
+        <v/>
+      </c>
+      <c r="O150" t="str">
+        <v/>
+      </c>
+      <c r="P150" t="str">
+        <v/>
+      </c>
+      <c r="Q150" t="str">
+        <v/>
+      </c>
+      <c r="R150" t="str">
+        <v/>
+      </c>
+      <c r="S150" t="str">
+        <v/>
+      </c>
+      <c r="T150" t="str">
+        <v/>
+      </c>
+      <c r="U150" t="str">
+        <v/>
+      </c>
+      <c r="V150" t="str">
+        <v/>
+      </c>
+      <c r="W150" t="str">
+        <v/>
+      </c>
+      <c r="X150" t="str">
+        <v/>
+      </c>
+      <c r="Y150" t="str">
+        <v/>
+      </c>
+      <c r="Z150" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>ביפי קליירו Futique</v>
+      </c>
+      <c r="B151" t="str">
+        <v>2025-09-30</v>
+      </c>
+      <c r="C151" t="str">
+        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
+      </c>
+      <c r="D151" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E151" t="str">
+        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
+      </c>
+      <c r="F151" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G151" t="str">
+        <v/>
+      </c>
+      <c r="H151" t="str">
+        <v/>
+      </c>
+      <c r="I151" t="str">
+        <v/>
+      </c>
+      <c r="J151" t="str">
+        <v/>
+      </c>
+      <c r="K151" t="str">
+        <v/>
+      </c>
+      <c r="L151" t="str">
+        <v/>
+      </c>
+      <c r="M151" t="str">
+        <v/>
+      </c>
+      <c r="N151" t="str">
+        <v/>
+      </c>
+      <c r="O151" t="str">
+        <v/>
+      </c>
+      <c r="P151" t="str">
+        <v/>
+      </c>
+      <c r="Q151" t="str">
+        <v/>
+      </c>
+      <c r="R151" t="str">
+        <v/>
+      </c>
+      <c r="S151" t="str">
+        <v/>
+      </c>
+      <c r="T151" t="str">
+        <v/>
+      </c>
+      <c r="U151" t="str">
+        <v/>
+      </c>
+      <c r="V151" t="str">
+        <v/>
+      </c>
+      <c r="W151" t="str">
+        <v/>
+      </c>
+      <c r="X151" t="str">
+        <v/>
+      </c>
+      <c r="Y151" t="str">
+        <v/>
+      </c>
+      <c r="Z151" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>אד שירן Play</v>
+      </c>
+      <c r="B152" t="str">
+        <v>2025-09-24</v>
+      </c>
+      <c r="C152" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
+      </c>
+      <c r="D152" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E152" t="str">
+        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
+      </c>
+      <c r="F152" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G152" t="str">
+        <v/>
+      </c>
+      <c r="H152" t="str">
+        <v/>
+      </c>
+      <c r="I152" t="str">
+        <v/>
+      </c>
+      <c r="J152" t="str">
+        <v/>
+      </c>
+      <c r="K152" t="str">
+        <v/>
+      </c>
+      <c r="L152" t="str">
+        <v/>
+      </c>
+      <c r="M152" t="str">
+        <v/>
+      </c>
+      <c r="N152" t="str">
+        <v/>
+      </c>
+      <c r="O152" t="str">
+        <v/>
+      </c>
+      <c r="P152" t="str">
+        <v/>
+      </c>
+      <c r="Q152" t="str">
+        <v/>
+      </c>
+      <c r="R152" t="str">
+        <v/>
+      </c>
+      <c r="S152" t="str">
+        <v/>
+      </c>
+      <c r="T152" t="str">
+        <v/>
+      </c>
+      <c r="U152" t="str">
+        <v/>
+      </c>
+      <c r="V152" t="str">
+        <v/>
+      </c>
+      <c r="W152" t="str">
+        <v/>
+      </c>
+      <c r="X152" t="str">
+        <v/>
+      </c>
+      <c r="Y152" t="str">
+        <v/>
+      </c>
+      <c r="Z152" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+      </c>
+      <c r="B153" t="str">
+        <v>2025-09-21</v>
+      </c>
+      <c r="C153" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
+      </c>
+      <c r="D153" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E153" t="str">
+        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
+      </c>
+      <c r="F153" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G153" t="str">
+        <v/>
+      </c>
+      <c r="H153" t="str">
+        <v/>
+      </c>
+      <c r="I153" t="str">
+        <v/>
+      </c>
+      <c r="J153" t="str">
+        <v/>
+      </c>
+      <c r="K153" t="str">
+        <v/>
+      </c>
+      <c r="L153" t="str">
+        <v/>
+      </c>
+      <c r="M153" t="str">
+        <v/>
+      </c>
+      <c r="N153" t="str">
+        <v/>
+      </c>
+      <c r="O153" t="str">
+        <v/>
+      </c>
+      <c r="P153" t="str">
+        <v/>
+      </c>
+      <c r="Q153" t="str">
+        <v/>
+      </c>
+      <c r="R153" t="str">
+        <v/>
+      </c>
+      <c r="S153" t="str">
+        <v/>
+      </c>
+      <c r="T153" t="str">
+        <v/>
+      </c>
+      <c r="U153" t="str">
+        <v/>
+      </c>
+      <c r="V153" t="str">
+        <v/>
+      </c>
+      <c r="W153" t="str">
+        <v/>
+      </c>
+      <c r="X153" t="str">
+        <v/>
+      </c>
+      <c r="Y153" t="str">
+        <v/>
+      </c>
+      <c r="Z153" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>סוויד Antidepressants</v>
+      </c>
+      <c r="B154" t="str">
+        <v>2025-09-12</v>
+      </c>
+      <c r="C154" t="str">
+        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
+      </c>
+      <c r="D154" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E154" t="str">
+        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
+      </c>
+      <c r="F154" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G154" t="str">
+        <v/>
+      </c>
+      <c r="H154" t="str">
+        <v/>
+      </c>
+      <c r="I154" t="str">
+        <v/>
+      </c>
+      <c r="J154" t="str">
+        <v/>
+      </c>
+      <c r="K154" t="str">
+        <v/>
+      </c>
+      <c r="L154" t="str">
+        <v/>
+      </c>
+      <c r="M154" t="str">
+        <v/>
+      </c>
+      <c r="N154" t="str">
+        <v/>
+      </c>
+      <c r="O154" t="str">
+        <v/>
+      </c>
+      <c r="P154" t="str">
+        <v/>
+      </c>
+      <c r="Q154" t="str">
+        <v/>
+      </c>
+      <c r="R154" t="str">
+        <v/>
+      </c>
+      <c r="S154" t="str">
+        <v/>
+      </c>
+      <c r="T154" t="str">
+        <v/>
+      </c>
+      <c r="U154" t="str">
+        <v/>
+      </c>
+      <c r="V154" t="str">
+        <v/>
+      </c>
+      <c r="W154" t="str">
+        <v/>
+      </c>
+      <c r="X154" t="str">
+        <v/>
+      </c>
+      <c r="Y154" t="str">
+        <v/>
+      </c>
+      <c r="Z154" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>וולף אליס The Clearing</v>
+      </c>
+      <c r="B155" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="C155" t="str">
+        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
+      </c>
+      <c r="D155" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E155" t="str">
+        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
+      </c>
+      <c r="F155" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G155" t="str">
+        <v/>
+      </c>
+      <c r="H155" t="str">
+        <v/>
+      </c>
+      <c r="I155" t="str">
+        <v/>
+      </c>
+      <c r="J155" t="str">
+        <v/>
+      </c>
+      <c r="K155" t="str">
+        <v/>
+      </c>
+      <c r="L155" t="str">
+        <v/>
+      </c>
+      <c r="M155" t="str">
+        <v/>
+      </c>
+      <c r="N155" t="str">
+        <v/>
+      </c>
+      <c r="O155" t="str">
+        <v/>
+      </c>
+      <c r="P155" t="str">
+        <v/>
+      </c>
+      <c r="Q155" t="str">
+        <v/>
+      </c>
+      <c r="R155" t="str">
+        <v/>
+      </c>
+      <c r="S155" t="str">
+        <v/>
+      </c>
+      <c r="T155" t="str">
+        <v/>
+      </c>
+      <c r="U155" t="str">
+        <v/>
+      </c>
+      <c r="V155" t="str">
+        <v/>
+      </c>
+      <c r="W155" t="str">
+        <v/>
+      </c>
+      <c r="X155" t="str">
+        <v/>
+      </c>
+      <c r="Y155" t="str">
+        <v/>
+      </c>
+      <c r="Z155" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+      </c>
+      <c r="B156" t="str">
+        <v>2025-08-29</v>
+      </c>
+      <c r="C156" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
+      </c>
+      <c r="D156" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E156" t="str">
+        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
+      </c>
+      <c r="F156" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G156" t="str">
+        <v/>
+      </c>
+      <c r="H156" t="str">
+        <v/>
+      </c>
+      <c r="I156" t="str">
+        <v/>
+      </c>
+      <c r="J156" t="str">
+        <v/>
+      </c>
+      <c r="K156" t="str">
+        <v/>
+      </c>
+      <c r="L156" t="str">
+        <v/>
+      </c>
+      <c r="M156" t="str">
+        <v/>
+      </c>
+      <c r="N156" t="str">
+        <v/>
+      </c>
+      <c r="O156" t="str">
+        <v/>
+      </c>
+      <c r="P156" t="str">
+        <v/>
+      </c>
+      <c r="Q156" t="str">
+        <v/>
+      </c>
+      <c r="R156" t="str">
+        <v/>
+      </c>
+      <c r="S156" t="str">
+        <v/>
+      </c>
+      <c r="T156" t="str">
+        <v/>
+      </c>
+      <c r="U156" t="str">
+        <v/>
+      </c>
+      <c r="V156" t="str">
+        <v/>
+      </c>
+      <c r="W156" t="str">
+        <v/>
+      </c>
+      <c r="X156" t="str">
+        <v/>
+      </c>
+      <c r="Y156" t="str">
+        <v/>
+      </c>
+      <c r="Z156" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+      </c>
+      <c r="B157" t="str">
+        <v>2025-08-24</v>
+      </c>
+      <c r="C157" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
+      </c>
+      <c r="D157" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E157" t="str">
+        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
+      </c>
+      <c r="F157" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G157" t="str">
+        <v/>
+      </c>
+      <c r="H157" t="str">
+        <v/>
+      </c>
+      <c r="I157" t="str">
+        <v/>
+      </c>
+      <c r="J157" t="str">
+        <v/>
+      </c>
+      <c r="K157" t="str">
+        <v/>
+      </c>
+      <c r="L157" t="str">
+        <v/>
+      </c>
+      <c r="M157" t="str">
+        <v/>
+      </c>
+      <c r="N157" t="str">
+        <v/>
+      </c>
+      <c r="O157" t="str">
+        <v/>
+      </c>
+      <c r="P157" t="str">
+        <v/>
+      </c>
+      <c r="Q157" t="str">
+        <v/>
+      </c>
+      <c r="R157" t="str">
+        <v/>
+      </c>
+      <c r="S157" t="str">
+        <v/>
+      </c>
+      <c r="T157" t="str">
+        <v/>
+      </c>
+      <c r="U157" t="str">
+        <v/>
+      </c>
+      <c r="V157" t="str">
+        <v/>
+      </c>
+      <c r="W157" t="str">
+        <v/>
+      </c>
+      <c r="X157" t="str">
+        <v/>
+      </c>
+      <c r="Y157" t="str">
+        <v/>
+      </c>
+      <c r="Z157" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+      </c>
+      <c r="B158" t="str">
+        <v>2025-08-21</v>
+      </c>
+      <c r="C158" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
+      </c>
+      <c r="D158" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E158" t="str">
+        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
+      </c>
+      <c r="F158" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G158" t="str">
+        <v/>
+      </c>
+      <c r="H158" t="str">
+        <v/>
+      </c>
+      <c r="I158" t="str">
+        <v/>
+      </c>
+      <c r="J158" t="str">
+        <v/>
+      </c>
+      <c r="K158" t="str">
+        <v/>
+      </c>
+      <c r="L158" t="str">
+        <v/>
+      </c>
+      <c r="M158" t="str">
+        <v/>
+      </c>
+      <c r="N158" t="str">
+        <v/>
+      </c>
+      <c r="O158" t="str">
+        <v/>
+      </c>
+      <c r="P158" t="str">
+        <v/>
+      </c>
+      <c r="Q158" t="str">
+        <v/>
+      </c>
+      <c r="R158" t="str">
+        <v/>
+      </c>
+      <c r="S158" t="str">
+        <v/>
+      </c>
+      <c r="T158" t="str">
+        <v/>
+      </c>
+      <c r="U158" t="str">
+        <v/>
+      </c>
+      <c r="V158" t="str">
+        <v/>
+      </c>
+      <c r="W158" t="str">
+        <v/>
+      </c>
+      <c r="X158" t="str">
+        <v/>
+      </c>
+      <c r="Y158" t="str">
+        <v/>
+      </c>
+      <c r="Z158" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>אברהם טל – חי</v>
+      </c>
+      <c r="B159" t="str">
+        <v>2025-08-17</v>
+      </c>
+      <c r="C159" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
+      </c>
+      <c r="D159" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E159" t="str">
+        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
+      </c>
+      <c r="F159" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G159" t="str">
+        <v/>
+      </c>
+      <c r="H159" t="str">
+        <v/>
+      </c>
+      <c r="I159" t="str">
+        <v/>
+      </c>
+      <c r="J159" t="str">
+        <v/>
+      </c>
+      <c r="K159" t="str">
+        <v/>
+      </c>
+      <c r="L159" t="str">
+        <v/>
+      </c>
+      <c r="M159" t="str">
+        <v/>
+      </c>
+      <c r="N159" t="str">
+        <v/>
+      </c>
+      <c r="O159" t="str">
+        <v/>
+      </c>
+      <c r="P159" t="str">
+        <v/>
+      </c>
+      <c r="Q159" t="str">
+        <v/>
+      </c>
+      <c r="R159" t="str">
+        <v/>
+      </c>
+      <c r="S159" t="str">
+        <v/>
+      </c>
+      <c r="T159" t="str">
+        <v/>
+      </c>
+      <c r="U159" t="str">
+        <v/>
+      </c>
+      <c r="V159" t="str">
+        <v/>
+      </c>
+      <c r="W159" t="str">
+        <v/>
+      </c>
+      <c r="X159" t="str">
+        <v/>
+      </c>
+      <c r="Y159" t="str">
+        <v/>
+      </c>
+      <c r="Z159" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>רנה ראפ Bite Me</v>
+      </c>
+      <c r="B160" t="str">
+        <v>2025-08-12</v>
+      </c>
+      <c r="C160" t="str">
+        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
+      </c>
+      <c r="D160" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E160" t="str">
+        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
+      </c>
+      <c r="F160" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G160" t="str">
+        <v/>
+      </c>
+      <c r="H160" t="str">
+        <v/>
+      </c>
+      <c r="I160" t="str">
+        <v/>
+      </c>
+      <c r="J160" t="str">
+        <v/>
+      </c>
+      <c r="K160" t="str">
+        <v/>
+      </c>
+      <c r="L160" t="str">
+        <v/>
+      </c>
+      <c r="M160" t="str">
+        <v/>
+      </c>
+      <c r="N160" t="str">
+        <v/>
+      </c>
+      <c r="O160" t="str">
+        <v/>
+      </c>
+      <c r="P160" t="str">
+        <v/>
+      </c>
+      <c r="Q160" t="str">
+        <v/>
+      </c>
+      <c r="R160" t="str">
+        <v/>
+      </c>
+      <c r="S160" t="str">
+        <v/>
+      </c>
+      <c r="T160" t="str">
+        <v/>
+      </c>
+      <c r="U160" t="str">
+        <v/>
+      </c>
+      <c r="V160" t="str">
+        <v/>
+      </c>
+      <c r="W160" t="str">
+        <v/>
+      </c>
+      <c r="X160" t="str">
+        <v/>
+      </c>
+      <c r="Y160" t="str">
+        <v/>
+      </c>
+      <c r="Z160" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>The K's – Pretty On The Internet</v>
+      </c>
+      <c r="B161" t="str">
+        <v>2025-08-03</v>
+      </c>
+      <c r="C161" t="str">
+        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
+      </c>
+      <c r="D161" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E161" t="str">
+        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
+      </c>
+      <c r="F161" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G161" t="str">
+        <v/>
+      </c>
+      <c r="H161" t="str">
+        <v/>
+      </c>
+      <c r="I161" t="str">
+        <v/>
+      </c>
+      <c r="J161" t="str">
+        <v/>
+      </c>
+      <c r="K161" t="str">
+        <v/>
+      </c>
+      <c r="L161" t="str">
+        <v/>
+      </c>
+      <c r="M161" t="str">
+        <v/>
+      </c>
+      <c r="N161" t="str">
+        <v/>
+      </c>
+      <c r="O161" t="str">
+        <v/>
+      </c>
+      <c r="P161" t="str">
+        <v/>
+      </c>
+      <c r="Q161" t="str">
+        <v/>
+      </c>
+      <c r="R161" t="str">
+        <v/>
+      </c>
+      <c r="S161" t="str">
+        <v/>
+      </c>
+      <c r="T161" t="str">
+        <v/>
+      </c>
+      <c r="U161" t="str">
+        <v/>
+      </c>
+      <c r="V161" t="str">
+        <v/>
+      </c>
+      <c r="W161" t="str">
+        <v/>
+      </c>
+      <c r="X161" t="str">
+        <v/>
+      </c>
+      <c r="Y161" t="str">
+        <v/>
+      </c>
+      <c r="Z161" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>פליטווד מק Fifty Years – Don’t Stop</v>
+      </c>
+      <c r="B162" t="str">
+        <v>2025-07-30</v>
+      </c>
+      <c r="C162" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%99%d7%98%d7%95%d7%95%d7%93-%d7%9e%d7%a7-fifty-years-dont-stop/</v>
+      </c>
+      <c r="D162" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E162" t="str">
+        <v>פליטווד מק (Fleetwood Mac) חוגגים חצי מאה של מוזיקה עם אוסף חדש בן 50 שירים, שמתפרש על כל הקריירה של הלהקה, מימיה הראשונים בסגנון בלוז, ועד להצלחתה העולמית כאחת מלהקות הגדולות בהיסטוריה של הרוק. פליטווד מק הם לא רק להקה</v>
+      </c>
+      <c r="F162" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G162" t="str">
+        <v/>
+      </c>
+      <c r="H162" t="str">
+        <v/>
+      </c>
+      <c r="I162" t="str">
+        <v/>
+      </c>
+      <c r="J162" t="str">
+        <v/>
+      </c>
+      <c r="K162" t="str">
+        <v/>
+      </c>
+      <c r="L162" t="str">
+        <v/>
+      </c>
+      <c r="M162" t="str">
+        <v/>
+      </c>
+      <c r="N162" t="str">
+        <v/>
+      </c>
+      <c r="O162" t="str">
+        <v/>
+      </c>
+      <c r="P162" t="str">
+        <v/>
+      </c>
+      <c r="Q162" t="str">
+        <v/>
+      </c>
+      <c r="R162" t="str">
+        <v/>
+      </c>
+      <c r="S162" t="str">
+        <v/>
+      </c>
+      <c r="T162" t="str">
+        <v/>
+      </c>
+      <c r="U162" t="str">
+        <v/>
+      </c>
+      <c r="V162" t="str">
+        <v/>
+      </c>
+      <c r="W162" t="str">
+        <v/>
+      </c>
+      <c r="X162" t="str">
+        <v/>
+      </c>
+      <c r="Y162" t="str">
+        <v/>
+      </c>
+      <c r="Z162" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>Wet Leg Moisturizer</v>
+      </c>
+      <c r="B163" t="str">
+        <v>2025-07-25</v>
+      </c>
+      <c r="C163" t="str">
+        <v>https://yosmusic.com/wet-leg-moisturizer/</v>
+      </c>
+      <c r="D163" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E163" t="str">
         <v>להקת Wet Leg לא הוציאה קרם לחות (Moisturizer) כמוצר טיפוח. במקום זאת, "Moisturizer" הוא שמו של האלבום השני והחדש שלהם. במרכז –  צמד אינדי-רוק המורכב מהחברות ריין טיסדייל והסטר צ'יימברס. אלבום הבכורה הנושא את שמה, הגיע למקום הראשון במצעד האלבומים</v>
       </c>
-      <c r="F119" t="str">
-        <v>אלבומים חדשים</v>
-      </c>
-      <c r="G119" t="str">
-        <v/>
-      </c>
-      <c r="H119" t="str">
-        <v/>
-      </c>
-      <c r="I119" t="str">
-        <v/>
-      </c>
-      <c r="J119" t="str">
-        <v/>
-      </c>
-      <c r="K119" t="str">
-        <v/>
-      </c>
-      <c r="L119" t="str">
-        <v/>
-      </c>
-      <c r="M119" t="str">
-        <v/>
-      </c>
-      <c r="N119" t="str">
-        <v/>
-      </c>
-      <c r="O119" t="str">
-        <v/>
-      </c>
-      <c r="P119" t="str">
-        <v/>
-      </c>
-      <c r="Q119" t="str">
-        <v/>
-      </c>
-      <c r="R119" t="str">
-        <v/>
-      </c>
-      <c r="S119" t="str">
-        <v/>
-      </c>
-      <c r="T119" t="str">
-        <v/>
-      </c>
-      <c r="U119" t="str">
-        <v/>
-      </c>
-      <c r="V119" t="str">
+      <c r="F163" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G163" t="str">
+        <v/>
+      </c>
+      <c r="H163" t="str">
+        <v/>
+      </c>
+      <c r="I163" t="str">
+        <v/>
+      </c>
+      <c r="J163" t="str">
+        <v/>
+      </c>
+      <c r="K163" t="str">
+        <v/>
+      </c>
+      <c r="L163" t="str">
+        <v/>
+      </c>
+      <c r="M163" t="str">
+        <v/>
+      </c>
+      <c r="N163" t="str">
+        <v/>
+      </c>
+      <c r="O163" t="str">
+        <v/>
+      </c>
+      <c r="P163" t="str">
+        <v/>
+      </c>
+      <c r="Q163" t="str">
+        <v/>
+      </c>
+      <c r="R163" t="str">
+        <v/>
+      </c>
+      <c r="S163" t="str">
+        <v/>
+      </c>
+      <c r="T163" t="str">
+        <v/>
+      </c>
+      <c r="U163" t="str">
+        <v/>
+      </c>
+      <c r="V163" t="str">
+        <v/>
+      </c>
+      <c r="W163" t="str">
+        <v/>
+      </c>
+      <c r="X163" t="str">
+        <v/>
+      </c>
+      <c r="Y163" t="str">
+        <v/>
+      </c>
+      <c r="Z163" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:V119"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Z163"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z163"/>
+  <dimension ref="A1:AD207"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1976,60 +1976,75 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>עדן בן זקן - רולקס וקסקט</v>
+        <v>פטריק סבג Hotel Mogador</v>
       </c>
       <c r="B46" t="str">
-        <v>2026  08:41-01-14</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C46" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24436&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-15</v>
       </c>
       <c r="E46" t="str">
-        <v/>
+        <v>האלבום של פטריק סבג אינו אוסף שירים אקראי, אלא מרחב. מקום לשהות בו.  נכנסים, שומעים, ויוצאים קצת אחרים. הבחירה בשם "הוטל מוגדור” היא כבר הצהרה. מלון = מקום מעבר, לא בית קבוע, מוגדור = עיר נמל, תנועה, ערבוב תרבויות. כך</v>
       </c>
       <c r="F46" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I46" t="str">
         <v/>
       </c>
       <c r="J46" t="str">
+        <v/>
+      </c>
+      <c r="K46" t="str">
+        <v>פטריק סבג Hotel Mogador</v>
+      </c>
+      <c r="L46" t="str">
+        <v/>
+      </c>
+      <c r="M46" t="str">
+        <v/>
+      </c>
+      <c r="N46" t="str">
+        <v/>
+      </c>
+      <c r="O46" t="str">
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>תומר יוסף - 360</v>
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
       </c>
       <c r="B47" t="str">
-        <v>2026  08:40-01-14</v>
+        <v>2026-01-09</v>
       </c>
       <c r="C47" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-15</v>
       </c>
       <c r="E47" t="str">
-        <v/>
+        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
       </c>
       <c r="F47" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I47" t="str">
         <v/>
@@ -2038,36 +2053,45 @@
         <v/>
       </c>
       <c r="K47" t="str">
-        <v/>
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
       </c>
       <c r="L47" t="str">
+        <v/>
+      </c>
+      <c r="M47" t="str">
+        <v/>
+      </c>
+      <c r="N47" t="str">
+        <v/>
+      </c>
+      <c r="O47" t="str">
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
+        <v>אוליביה דין The Art of Loving</v>
       </c>
       <c r="B48" t="str">
-        <v>2026  08:40-01-14</v>
+        <v>2026-01-04</v>
       </c>
       <c r="C48" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24439&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-15</v>
       </c>
       <c r="E48" t="str">
-        <v/>
+        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
       </c>
       <c r="F48" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I48" t="str">
         <v/>
@@ -2076,36 +2100,45 @@
         <v/>
       </c>
       <c r="K48" t="str">
-        <v/>
+        <v>אוליביה דין The Art of Loving</v>
       </c>
       <c r="L48" t="str">
+        <v/>
+      </c>
+      <c r="M48" t="str">
+        <v/>
+      </c>
+      <c r="N48" t="str">
+        <v/>
+      </c>
+      <c r="O48" t="str">
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>אייל גולן - בית מפואר</v>
+        <v>Geese Getting Killed</v>
       </c>
       <c r="B49" t="str">
-        <v>2025  02:18-12-31</v>
+        <v>2025-12-29</v>
       </c>
       <c r="C49" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/geese-getting-killed/</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-15</v>
       </c>
       <c r="E49" t="str">
-        <v/>
+        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
       </c>
       <c r="F49" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I49" t="str">
         <v/>
@@ -2114,36 +2147,45 @@
         <v/>
       </c>
       <c r="K49" t="str">
-        <v/>
+        <v>Geese Getting Killed</v>
       </c>
       <c r="L49" t="str">
+        <v/>
+      </c>
+      <c r="M49" t="str">
+        <v/>
+      </c>
+      <c r="N49" t="str">
+        <v/>
+      </c>
+      <c r="O49" t="str">
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
+        <v>רוסליה Lux</v>
       </c>
       <c r="B50" t="str">
-        <v>2025  02:16-12-31</v>
+        <v>2025-12-25</v>
       </c>
       <c r="C50" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-15</v>
       </c>
       <c r="E50" t="str">
-        <v/>
+        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
       </c>
       <c r="F50" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I50" t="str">
         <v/>
@@ -2152,36 +2194,45 @@
         <v/>
       </c>
       <c r="K50" t="str">
-        <v/>
+        <v>רוסליה Lux</v>
       </c>
       <c r="L50" t="str">
+        <v/>
+      </c>
+      <c r="M50" t="str">
+        <v/>
+      </c>
+      <c r="N50" t="str">
+        <v/>
+      </c>
+      <c r="O50" t="str">
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>שיר לוי - ילד מוזר</v>
+        <v>יאנגבלאד אירוסמית' one more time</v>
       </c>
       <c r="B51" t="str">
-        <v>2025  02:14-12-31</v>
+        <v>2025-12-17</v>
       </c>
       <c r="C51" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-15</v>
       </c>
       <c r="E51" t="str">
-        <v/>
+        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
       </c>
       <c r="F51" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I51" t="str">
         <v/>
@@ -2190,36 +2241,45 @@
         <v/>
       </c>
       <c r="K51" t="str">
-        <v/>
+        <v>יאנגבלאד אירוסמית' one more time</v>
       </c>
       <c r="L51" t="str">
+        <v/>
+      </c>
+      <c r="M51" t="str">
+        <v/>
+      </c>
+      <c r="N51" t="str">
+        <v/>
+      </c>
+      <c r="O51" t="str">
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>פיטר רוט - 50</v>
+        <v>פינק פלויד Wish You Were Here 50</v>
       </c>
       <c r="B52" t="str">
-        <v>2025  02:13-12-31</v>
+        <v>2025-12-14</v>
       </c>
       <c r="C52" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-15</v>
       </c>
       <c r="E52" t="str">
-        <v/>
+        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
       </c>
       <c r="F52" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -2228,36 +2288,45 @@
         <v/>
       </c>
       <c r="K52" t="str">
-        <v/>
+        <v>פינק פלויד Wish You Were Here 50</v>
       </c>
       <c r="L52" t="str">
+        <v/>
+      </c>
+      <c r="M52" t="str">
+        <v/>
+      </c>
+      <c r="N52" t="str">
+        <v/>
+      </c>
+      <c r="O52" t="str">
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>אגם בוחבוט - עשרים ואחת</v>
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
       </c>
       <c r="B53" t="str">
-        <v>2025  02:11-12-31</v>
+        <v>2025-12-08</v>
       </c>
       <c r="C53" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-15</v>
       </c>
       <c r="E53" t="str">
-        <v/>
+        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
       </c>
       <c r="F53" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I53" t="str">
         <v/>
@@ -2266,36 +2335,45 @@
         <v/>
       </c>
       <c r="K53" t="str">
-        <v/>
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
       </c>
       <c r="L53" t="str">
+        <v/>
+      </c>
+      <c r="M53" t="str">
+        <v/>
+      </c>
+      <c r="N53" t="str">
+        <v/>
+      </c>
+      <c r="O53" t="str">
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>רבקה זוהר - רסיסים של אור</v>
+        <v>סטריי קידס DO IT (EP)</v>
       </c>
       <c r="B54" t="str">
-        <v>2025  02:09-12-31</v>
+        <v>2025-12-04</v>
       </c>
       <c r="C54" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-15</v>
       </c>
       <c r="E54" t="str">
-        <v/>
+        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
       </c>
       <c r="F54" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I54" t="str">
         <v/>
@@ -2304,36 +2382,45 @@
         <v/>
       </c>
       <c r="K54" t="str">
-        <v/>
+        <v>סטריי קידס DO IT (EP)</v>
       </c>
       <c r="L54" t="str">
+        <v/>
+      </c>
+      <c r="M54" t="str">
+        <v/>
+      </c>
+      <c r="N54" t="str">
+        <v/>
+      </c>
+      <c r="O54" t="str">
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
+        <v>דויד ברוזה BROZAJAZZ</v>
       </c>
       <c r="B55" t="str">
-        <v>2025  02:08-12-31</v>
+        <v>2025-11-30</v>
       </c>
       <c r="C55" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-15</v>
       </c>
       <c r="E55" t="str">
-        <v/>
+        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
       </c>
       <c r="F55" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I55" t="str">
         <v/>
@@ -2342,36 +2429,45 @@
         <v/>
       </c>
       <c r="K55" t="str">
-        <v/>
+        <v>דויד ברוזה BROZAJAZZ</v>
       </c>
       <c r="L55" t="str">
+        <v/>
+      </c>
+      <c r="M55" t="str">
+        <v/>
+      </c>
+      <c r="N55" t="str">
+        <v/>
+      </c>
+      <c r="O55" t="str">
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
+        <v>Five Seconds of Summer – Everyone's A Star</v>
       </c>
       <c r="B56" t="str">
-        <v>2025  02:05-12-31</v>
+        <v>2025-11-24</v>
       </c>
       <c r="C56" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-15</v>
       </c>
       <c r="E56" t="str">
-        <v/>
+        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
       </c>
       <c r="F56" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I56" t="str">
         <v/>
@@ -2380,36 +2476,45 @@
         <v/>
       </c>
       <c r="K56" t="str">
-        <v/>
+        <v>Five Seconds of Summer – Everyone's A Star</v>
       </c>
       <c r="L56" t="str">
+        <v/>
+      </c>
+      <c r="M56" t="str">
+        <v/>
+      </c>
+      <c r="N56" t="str">
+        <v/>
+      </c>
+      <c r="O56" t="str">
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Imagine פסטיגל - שירי התחרות</v>
+        <v>התקווה 6 – ויהי אור</v>
       </c>
       <c r="B57" t="str">
-        <v>2025  02:04-12-31</v>
+        <v>2025-11-20</v>
       </c>
       <c r="C57" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-15</v>
       </c>
       <c r="E57" t="str">
-        <v/>
+        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
       </c>
       <c r="F57" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I57" t="str">
         <v/>
@@ -2418,36 +2523,45 @@
         <v/>
       </c>
       <c r="K57" t="str">
-        <v/>
+        <v>התקווה 6 – ויהי אור</v>
       </c>
       <c r="L57" t="str">
+        <v/>
+      </c>
+      <c r="M57" t="str">
+        <v/>
+      </c>
+      <c r="N57" t="str">
+        <v/>
+      </c>
+      <c r="O57" t="str">
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>השמחות - חובות אבודים</v>
+        <v>פלורנס אנד דה משין Everybody Scream</v>
       </c>
       <c r="B58" t="str">
-        <v>2025  02:02-12-31</v>
+        <v>2025-11-13</v>
       </c>
       <c r="C58" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-15</v>
       </c>
       <c r="E58" t="str">
-        <v/>
+        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
       </c>
       <c r="F58" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I58" t="str">
         <v/>
@@ -2456,36 +2570,45 @@
         <v/>
       </c>
       <c r="K58" t="str">
-        <v/>
+        <v>פלורנס אנד דה משין Everybody Scream</v>
       </c>
       <c r="L58" t="str">
+        <v/>
+      </c>
+      <c r="M58" t="str">
+        <v/>
+      </c>
+      <c r="N58" t="str">
+        <v/>
+      </c>
+      <c r="O58" t="str">
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>שלמה גרוניך - כמו כוכבים</v>
+        <v>טיים אימפלה Deadbeat</v>
       </c>
       <c r="B59" t="str">
-        <v>2025  02:00-12-31</v>
+        <v>2025-11-03</v>
       </c>
       <c r="C59" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-15</v>
       </c>
       <c r="E59" t="str">
-        <v/>
+        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
       </c>
       <c r="F59" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I59" t="str">
         <v/>
@@ -2494,36 +2617,45 @@
         <v/>
       </c>
       <c r="K59" t="str">
-        <v/>
+        <v>טיים אימפלה Deadbeat</v>
       </c>
       <c r="L59" t="str">
+        <v/>
+      </c>
+      <c r="M59" t="str">
+        <v/>
+      </c>
+      <c r="N59" t="str">
+        <v/>
+      </c>
+      <c r="O59" t="str">
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>יוני רועה - מפוזרים</v>
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
       </c>
       <c r="B60" t="str">
-        <v>2025  01:56-12-31</v>
+        <v>2025-10-20</v>
       </c>
       <c r="C60" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-15</v>
       </c>
       <c r="E60" t="str">
-        <v/>
+        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
       </c>
       <c r="F60" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I60" t="str">
         <v/>
@@ -2532,36 +2664,45 @@
         <v/>
       </c>
       <c r="K60" t="str">
-        <v/>
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
       </c>
       <c r="L60" t="str">
+        <v/>
+      </c>
+      <c r="M60" t="str">
+        <v/>
+      </c>
+      <c r="N60" t="str">
+        <v/>
+      </c>
+      <c r="O60" t="str">
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>פטריק סבג Hotel Mogador</v>
+        <v>שלמה גרוניך – תודה אהבה</v>
       </c>
       <c r="B61" t="str">
-        <v>2026-01-13</v>
+        <v>2025-10-18</v>
       </c>
       <c r="C61" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-01-13</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E61" t="str">
-        <v>האלבום של פטריק סבג אינו אוסף שירים אקראי, אלא מרחב. מקום לשהות בו.  נכנסים, שומעים, ויוצאים קצת אחרים. הבחירה בשם "הוטל מוגדור” היא כבר הצהרה. מלון = מקום מעבר, לא בית קבוע, מוגדור = עיר נמל, תנועה, ערבוב תרבויות. כך</v>
+        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
       </c>
       <c r="F61" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I61" t="str">
         <v/>
@@ -2570,7 +2711,7 @@
         <v/>
       </c>
       <c r="K61" t="str">
-        <v/>
+        <v>שלמה גרוניך – תודה אהבה</v>
       </c>
       <c r="L61" t="str">
         <v/>
@@ -2579,33 +2720,36 @@
         <v/>
       </c>
       <c r="N61" t="str">
+        <v/>
+      </c>
+      <c r="O61" t="str">
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>|אלבום חדש| תומר יוסף - 360 ()</v>
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
       </c>
       <c r="B62" t="str">
-        <v>2026  11:38-01-09</v>
+        <v>2025-10-11</v>
       </c>
       <c r="C62" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E62" t="str">
-        <v/>
+        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
       </c>
       <c r="F62" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I62" t="str">
         <v/>
@@ -2614,7 +2758,7 @@
         <v/>
       </c>
       <c r="K62" t="str">
-        <v/>
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
       </c>
       <c r="L62" t="str">
         <v/>
@@ -2626,36 +2770,33 @@
         <v/>
       </c>
       <c r="O62" t="str">
-        <v/>
-      </c>
-      <c r="P62" t="str">
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע ()</v>
+        <v>דוג'ה קאט Vie</v>
       </c>
       <c r="B63" t="str">
-        <v>2025  02:17-12-31</v>
+        <v>2025-10-04</v>
       </c>
       <c r="C63" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E63" t="str">
-        <v/>
+        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
       </c>
       <c r="F63" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I63" t="str">
         <v/>
@@ -2664,7 +2805,7 @@
         <v/>
       </c>
       <c r="K63" t="str">
-        <v/>
+        <v>דוג'ה קאט Vie</v>
       </c>
       <c r="L63" t="str">
         <v/>
@@ -2676,36 +2817,33 @@
         <v/>
       </c>
       <c r="O63" t="str">
-        <v/>
-      </c>
-      <c r="P63" t="str">
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>|אלבום חדש| אברהם טל - חי ()</v>
+        <v>ג'וי קרוקס Juniper</v>
       </c>
       <c r="B64" t="str">
-        <v>2025  02:16-12-31</v>
+        <v>2025-10-03</v>
       </c>
       <c r="C64" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E64" t="str">
-        <v/>
+        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
       </c>
       <c r="F64" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I64" t="str">
         <v/>
@@ -2714,7 +2852,7 @@
         <v/>
       </c>
       <c r="K64" t="str">
-        <v/>
+        <v>ג'וי קרוקס Juniper</v>
       </c>
       <c r="L64" t="str">
         <v/>
@@ -2726,36 +2864,33 @@
         <v/>
       </c>
       <c r="O64" t="str">
-        <v/>
-      </c>
-      <c r="P64" t="str">
         <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>|אלבום חדש| מיקי גבריאלוב - שלום ()</v>
+        <v>ביפי קליירו Futique</v>
       </c>
       <c r="B65" t="str">
-        <v>2025  02:13-12-31</v>
+        <v>2025-09-30</v>
       </c>
       <c r="C65" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E65" t="str">
-        <v/>
+        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
       </c>
       <c r="F65" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I65" t="str">
         <v/>
@@ -2764,7 +2899,7 @@
         <v/>
       </c>
       <c r="K65" t="str">
-        <v/>
+        <v>ביפי קליירו Futique</v>
       </c>
       <c r="L65" t="str">
         <v/>
@@ -2776,36 +2911,33 @@
         <v/>
       </c>
       <c r="O65" t="str">
-        <v/>
-      </c>
-      <c r="P65" t="str">
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם ()</v>
+        <v>אד שירן Play</v>
       </c>
       <c r="B66" t="str">
-        <v>2025  02:12-12-31</v>
+        <v>2025-09-24</v>
       </c>
       <c r="C66" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E66" t="str">
-        <v/>
+        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
       </c>
       <c r="F66" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I66" t="str">
         <v/>
@@ -2814,7 +2946,7 @@
         <v/>
       </c>
       <c r="K66" t="str">
-        <v/>
+        <v>אד שירן Play</v>
       </c>
       <c r="L66" t="str">
         <v/>
@@ -2826,36 +2958,33 @@
         <v/>
       </c>
       <c r="O66" t="str">
-        <v/>
-      </c>
-      <c r="P66" t="str">
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון ()</v>
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
       </c>
       <c r="B67" t="str">
-        <v>2025  02:10-12-31</v>
+        <v>2025-09-21</v>
       </c>
       <c r="C67" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E67" t="str">
-        <v/>
+        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
       </c>
       <c r="F67" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I67" t="str">
         <v/>
@@ -2864,7 +2993,7 @@
         <v/>
       </c>
       <c r="K67" t="str">
-        <v/>
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
       </c>
       <c r="L67" t="str">
         <v/>
@@ -2876,36 +3005,33 @@
         <v/>
       </c>
       <c r="O67" t="str">
-        <v/>
-      </c>
-      <c r="P67" t="str">
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה ()</v>
+        <v>סוויד Antidepressants</v>
       </c>
       <c r="B68" t="str">
-        <v>2025  02:09-12-31</v>
+        <v>2025-09-12</v>
       </c>
       <c r="C68" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E68" t="str">
-        <v/>
+        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
       </c>
       <c r="F68" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I68" t="str">
         <v/>
@@ -2914,7 +3040,7 @@
         <v/>
       </c>
       <c r="K68" t="str">
-        <v/>
+        <v>סוויד Antidepressants</v>
       </c>
       <c r="L68" t="str">
         <v/>
@@ -2926,36 +3052,33 @@
         <v/>
       </c>
       <c r="O68" t="str">
-        <v/>
-      </c>
-      <c r="P68" t="str">
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים ()</v>
+        <v>וולף אליס The Clearing</v>
       </c>
       <c r="B69" t="str">
-        <v>2025  02:06-12-31</v>
+        <v>2025-09-01</v>
       </c>
       <c r="C69" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E69" t="str">
-        <v/>
+        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
       </c>
       <c r="F69" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I69" t="str">
         <v/>
@@ -2964,7 +3087,7 @@
         <v/>
       </c>
       <c r="K69" t="str">
-        <v/>
+        <v>וולף אליס The Clearing</v>
       </c>
       <c r="L69" t="str">
         <v/>
@@ -2976,36 +3099,33 @@
         <v/>
       </c>
       <c r="O69" t="str">
-        <v/>
-      </c>
-      <c r="P69" t="str">
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם ()</v>
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
       </c>
       <c r="B70" t="str">
-        <v>2025  02:05-12-31</v>
+        <v>2025-08-29</v>
       </c>
       <c r="C70" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E70" t="str">
-        <v/>
+        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
       </c>
       <c r="F70" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I70" t="str">
         <v/>
@@ -3014,7 +3134,7 @@
         <v/>
       </c>
       <c r="K70" t="str">
-        <v/>
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
       </c>
       <c r="L70" t="str">
         <v/>
@@ -3026,36 +3146,33 @@
         <v/>
       </c>
       <c r="O70" t="str">
-        <v/>
-      </c>
-      <c r="P70" t="str">
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>|אלבום חדש| סטטיק - קעקועים ()</v>
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
       </c>
       <c r="B71" t="str">
-        <v>2025  02:03-12-31</v>
+        <v>2025-08-24</v>
       </c>
       <c r="C71" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E71" t="str">
-        <v/>
+        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
       </c>
       <c r="F71" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I71" t="str">
         <v/>
@@ -3064,7 +3181,7 @@
         <v/>
       </c>
       <c r="K71" t="str">
-        <v/>
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
       </c>
       <c r="L71" t="str">
         <v/>
@@ -3076,36 +3193,33 @@
         <v/>
       </c>
       <c r="O71" t="str">
-        <v/>
-      </c>
-      <c r="P71" t="str">
         <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>|אלבום חדש| ליאור נרקיס - דיסוננס ()</v>
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
       </c>
       <c r="B72" t="str">
-        <v>2025  02:01-12-31</v>
+        <v>2025-08-21</v>
       </c>
       <c r="C72" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E72" t="str">
-        <v/>
+        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
       </c>
       <c r="F72" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I72" t="str">
         <v/>
@@ -3114,7 +3228,7 @@
         <v/>
       </c>
       <c r="K72" t="str">
-        <v/>
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
       </c>
       <c r="L72" t="str">
         <v/>
@@ -3126,36 +3240,33 @@
         <v/>
       </c>
       <c r="O72" t="str">
-        <v/>
-      </c>
-      <c r="P72" t="str">
         <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) ()</v>
+        <v>אברהם טל – חי</v>
       </c>
       <c r="B73" t="str">
-        <v>2025  01:57-12-31</v>
+        <v>2025-08-17</v>
       </c>
       <c r="C73" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E73" t="str">
-        <v/>
+        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
       </c>
       <c r="F73" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I73" t="str">
         <v/>
@@ -3164,7 +3275,7 @@
         <v/>
       </c>
       <c r="K73" t="str">
-        <v/>
+        <v>אברהם טל – חי</v>
       </c>
       <c r="L73" t="str">
         <v/>
@@ -3176,36 +3287,33 @@
         <v/>
       </c>
       <c r="O73" t="str">
-        <v/>
-      </c>
-      <c r="P73" t="str">
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>|אלבום חדש| אתניקס - איטליה ()</v>
+        <v>רנה ראפ Bite Me</v>
       </c>
       <c r="B74" t="str">
-        <v>2025  01:55-12-31</v>
+        <v>2025-08-12</v>
       </c>
       <c r="C74" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E74" t="str">
-        <v/>
+        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
       </c>
       <c r="F74" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I74" t="str">
         <v/>
@@ -3214,7 +3322,7 @@
         <v/>
       </c>
       <c r="K74" t="str">
-        <v/>
+        <v>רנה ראפ Bite Me</v>
       </c>
       <c r="L74" t="str">
         <v/>
@@ -3226,36 +3334,33 @@
         <v/>
       </c>
       <c r="O74" t="str">
-        <v/>
-      </c>
-      <c r="P74" t="str">
         <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>|| תומר יוסף - 360 (2026)</v>
+        <v>The K's – Pretty On The Internet</v>
       </c>
       <c r="B75" t="str">
-        <v>2026  11:38-01-09</v>
+        <v>2025-08-03</v>
       </c>
       <c r="C75" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E75" t="str">
-        <v/>
+        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
       </c>
       <c r="F75" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I75" t="str">
         <v/>
@@ -3264,7 +3369,7 @@
         <v/>
       </c>
       <c r="K75" t="str">
-        <v/>
+        <v>The K's – Pretty On The Internet</v>
       </c>
       <c r="L75" t="str">
         <v/>
@@ -3276,42 +3381,33 @@
         <v/>
       </c>
       <c r="O75" t="str">
-        <v/>
-      </c>
-      <c r="P75" t="str">
-        <v/>
-      </c>
-      <c r="Q75" t="str">
-        <v/>
-      </c>
-      <c r="R75" t="str">
         <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>|| עמיר בניון - לא נוגע בקרקע ()</v>
+        <v>עדן בן זקן - רולקס וקסקט</v>
       </c>
       <c r="B76" t="str">
-        <v>2025  02:17-12-31</v>
+        <v>2026  08:41-01-14</v>
       </c>
       <c r="C76" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24436&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I76" t="str">
         <v/>
@@ -3320,7 +3416,7 @@
         <v/>
       </c>
       <c r="K76" t="str">
-        <v/>
+        <v>עדן בן זקן - רולקס וקסקט</v>
       </c>
       <c r="L76" t="str">
         <v/>
@@ -3332,42 +3428,33 @@
         <v/>
       </c>
       <c r="O76" t="str">
-        <v/>
-      </c>
-      <c r="P76" t="str">
-        <v/>
-      </c>
-      <c r="Q76" t="str">
-        <v/>
-      </c>
-      <c r="R76" t="str">
         <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>|| אברהם טל - חי ()</v>
+        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
       </c>
       <c r="B77" t="str">
-        <v>2025  02:16-12-31</v>
+        <v>2026  08:40-01-14</v>
       </c>
       <c r="C77" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24439&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E77" t="str">
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I77" t="str">
         <v/>
@@ -3376,7 +3463,7 @@
         <v/>
       </c>
       <c r="K77" t="str">
-        <v/>
+        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
       </c>
       <c r="L77" t="str">
         <v/>
@@ -3388,42 +3475,33 @@
         <v/>
       </c>
       <c r="O77" t="str">
-        <v/>
-      </c>
-      <c r="P77" t="str">
-        <v/>
-      </c>
-      <c r="Q77" t="str">
-        <v/>
-      </c>
-      <c r="R77" t="str">
         <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>|| מיקי גבריאלוב - שלום ()</v>
+        <v>אייל גולן - בית מפואר</v>
       </c>
       <c r="B78" t="str">
-        <v>2025  02:13-12-31</v>
+        <v>2025  02:18-12-31</v>
       </c>
       <c r="C78" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I78" t="str">
         <v/>
@@ -3432,7 +3510,7 @@
         <v/>
       </c>
       <c r="K78" t="str">
-        <v/>
+        <v>אייל גולן - בית מפואר</v>
       </c>
       <c r="L78" t="str">
         <v/>
@@ -3444,42 +3522,33 @@
         <v/>
       </c>
       <c r="O78" t="str">
-        <v/>
-      </c>
-      <c r="P78" t="str">
-        <v/>
-      </c>
-      <c r="Q78" t="str">
-        <v/>
-      </c>
-      <c r="R78" t="str">
         <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>|| בזכרי ימים ימימה - מחווה לצלילי הכרם ()</v>
+        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
       </c>
       <c r="B79" t="str">
-        <v>2025  02:12-12-31</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C79" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E79" t="str">
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I79" t="str">
         <v/>
@@ -3488,7 +3557,7 @@
         <v/>
       </c>
       <c r="K79" t="str">
-        <v/>
+        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
       </c>
       <c r="L79" t="str">
         <v/>
@@ -3500,42 +3569,33 @@
         <v/>
       </c>
       <c r="O79" t="str">
-        <v/>
-      </c>
-      <c r="P79" t="str">
-        <v/>
-      </c>
-      <c r="Q79" t="str">
-        <v/>
-      </c>
-      <c r="R79" t="str">
         <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>|| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון ()</v>
+        <v>שיר לוי - ילד מוזר</v>
       </c>
       <c r="B80" t="str">
-        <v>2025  02:10-12-31</v>
+        <v>2025  02:14-12-31</v>
       </c>
       <c r="C80" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I80" t="str">
         <v/>
@@ -3544,7 +3604,7 @@
         <v/>
       </c>
       <c r="K80" t="str">
-        <v/>
+        <v>שיר לוי - ילד מוזר</v>
       </c>
       <c r="L80" t="str">
         <v/>
@@ -3556,42 +3616,33 @@
         <v/>
       </c>
       <c r="O80" t="str">
-        <v/>
-      </c>
-      <c r="P80" t="str">
-        <v/>
-      </c>
-      <c r="Q80" t="str">
-        <v/>
-      </c>
-      <c r="R80" t="str">
         <v/>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>|| שלמה גרוניך - תודה אהבה ()</v>
+        <v>פיטר רוט - 50</v>
       </c>
       <c r="B81" t="str">
-        <v>2025  02:09-12-31</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C81" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E81" t="str">
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I81" t="str">
         <v/>
@@ -3600,7 +3651,7 @@
         <v/>
       </c>
       <c r="K81" t="str">
-        <v/>
+        <v>פיטר רוט - 50</v>
       </c>
       <c r="L81" t="str">
         <v/>
@@ -3612,42 +3663,33 @@
         <v/>
       </c>
       <c r="O81" t="str">
-        <v/>
-      </c>
-      <c r="P81" t="str">
-        <v/>
-      </c>
-      <c r="Q81" t="str">
-        <v/>
-      </c>
-      <c r="R81" t="str">
         <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>|| חוה אלברשטיין - חמישה שירים ()</v>
+        <v>אגם בוחבוט - עשרים ואחת</v>
       </c>
       <c r="B82" t="str">
-        <v>2025  02:06-12-31</v>
+        <v>2025  02:11-12-31</v>
       </c>
       <c r="C82" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E82" t="str">
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I82" t="str">
         <v/>
@@ -3656,7 +3698,7 @@
         <v/>
       </c>
       <c r="K82" t="str">
-        <v/>
+        <v>אגם בוחבוט - עשרים ואחת</v>
       </c>
       <c r="L82" t="str">
         <v/>
@@ -3668,42 +3710,33 @@
         <v/>
       </c>
       <c r="O82" t="str">
-        <v/>
-      </c>
-      <c r="P82" t="str">
-        <v/>
-      </c>
-      <c r="Q82" t="str">
-        <v/>
-      </c>
-      <c r="R82" t="str">
         <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>|| הפרויקט של עידן רייכל - עד סוף העולם ()</v>
+        <v>רבקה זוהר - רסיסים של אור</v>
       </c>
       <c r="B83" t="str">
-        <v>2025  02:05-12-31</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C83" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I83" t="str">
         <v/>
@@ -3712,7 +3745,7 @@
         <v/>
       </c>
       <c r="K83" t="str">
-        <v/>
+        <v>רבקה זוהר - רסיסים של אור</v>
       </c>
       <c r="L83" t="str">
         <v/>
@@ -3724,42 +3757,33 @@
         <v/>
       </c>
       <c r="O83" t="str">
-        <v/>
-      </c>
-      <c r="P83" t="str">
-        <v/>
-      </c>
-      <c r="Q83" t="str">
-        <v/>
-      </c>
-      <c r="R83" t="str">
         <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>|| סטטיק - קעקועים ()</v>
+        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
       </c>
       <c r="B84" t="str">
-        <v>2025  02:03-12-31</v>
+        <v>2025  02:08-12-31</v>
       </c>
       <c r="C84" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E84" t="str">
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I84" t="str">
         <v/>
@@ -3768,7 +3792,7 @@
         <v/>
       </c>
       <c r="K84" t="str">
-        <v/>
+        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
       </c>
       <c r="L84" t="str">
         <v/>
@@ -3780,42 +3804,33 @@
         <v/>
       </c>
       <c r="O84" t="str">
-        <v/>
-      </c>
-      <c r="P84" t="str">
-        <v/>
-      </c>
-      <c r="Q84" t="str">
-        <v/>
-      </c>
-      <c r="R84" t="str">
         <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>|| ליאור נרקיס - דיסוננס ()</v>
+        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
       </c>
       <c r="B85" t="str">
-        <v>2025  02:01-12-31</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C85" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I85" t="str">
         <v/>
@@ -3824,7 +3839,7 @@
         <v/>
       </c>
       <c r="K85" t="str">
-        <v/>
+        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
       </c>
       <c r="L85" t="str">
         <v/>
@@ -3836,42 +3851,33 @@
         <v/>
       </c>
       <c r="O85" t="str">
-        <v/>
-      </c>
-      <c r="P85" t="str">
-        <v/>
-      </c>
-      <c r="Q85" t="str">
-        <v/>
-      </c>
-      <c r="R85" t="str">
         <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>|| דיוויד ברוזה - BrozaJazz (Paris Alhambra) ()</v>
+        <v>Imagine פסטיגל - שירי התחרות</v>
       </c>
       <c r="B86" t="str">
-        <v>2025  01:57-12-31</v>
+        <v>2025  02:04-12-31</v>
       </c>
       <c r="C86" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E86" t="str">
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I86" t="str">
         <v/>
@@ -3880,7 +3886,7 @@
         <v/>
       </c>
       <c r="K86" t="str">
-        <v/>
+        <v>Imagine פסטיגל - שירי התחרות</v>
       </c>
       <c r="L86" t="str">
         <v/>
@@ -3892,42 +3898,33 @@
         <v/>
       </c>
       <c r="O86" t="str">
-        <v/>
-      </c>
-      <c r="P86" t="str">
-        <v/>
-      </c>
-      <c r="Q86" t="str">
-        <v/>
-      </c>
-      <c r="R86" t="str">
         <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>|| אתניקס - איטליה ()</v>
+        <v>השמחות - חובות אבודים</v>
       </c>
       <c r="B87" t="str">
-        <v>2025  01:55-12-31</v>
+        <v>2025  02:02-12-31</v>
       </c>
       <c r="C87" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E87" t="str">
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I87" t="str">
         <v/>
@@ -3936,7 +3933,7 @@
         <v/>
       </c>
       <c r="K87" t="str">
-        <v/>
+        <v>השמחות - חובות אבודים</v>
       </c>
       <c r="L87" t="str">
         <v/>
@@ -3948,42 +3945,33 @@
         <v/>
       </c>
       <c r="O87" t="str">
-        <v/>
-      </c>
-      <c r="P87" t="str">
-        <v/>
-      </c>
-      <c r="Q87" t="str">
-        <v/>
-      </c>
-      <c r="R87" t="str">
         <v/>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>מארינה מקסימיליאן – ריק בחלל</v>
+        <v>שלמה גרוניך - כמו כוכבים</v>
       </c>
       <c r="B88" t="str">
-        <v>2026-01-09</v>
+        <v>2025  02:00-12-31</v>
       </c>
       <c r="C88" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E88" t="str">
-        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
+        <v/>
       </c>
       <c r="F88" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I88" t="str">
         <v/>
@@ -3992,7 +3980,7 @@
         <v/>
       </c>
       <c r="K88" t="str">
-        <v/>
+        <v>שלמה גרוניך - כמו כוכבים</v>
       </c>
       <c r="L88" t="str">
         <v/>
@@ -4004,48 +3992,33 @@
         <v/>
       </c>
       <c r="O88" t="str">
-        <v/>
-      </c>
-      <c r="P88" t="str">
-        <v/>
-      </c>
-      <c r="Q88" t="str">
-        <v/>
-      </c>
-      <c r="R88" t="str">
-        <v/>
-      </c>
-      <c r="S88" t="str">
-        <v/>
-      </c>
-      <c r="T88" t="str">
         <v/>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>|| אייל גולן - בית מפואר ()</v>
+        <v>יוני רועה - מפוזרים</v>
       </c>
       <c r="B89" t="str">
-        <v>2025  02:18-12-31</v>
+        <v>2025  01:56-12-31</v>
       </c>
       <c r="C89" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E89" t="str">
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I89" t="str">
         <v/>
@@ -4054,7 +4027,7 @@
         <v/>
       </c>
       <c r="K89" t="str">
-        <v/>
+        <v>יוני רועה - מפוזרים</v>
       </c>
       <c r="L89" t="str">
         <v/>
@@ -4066,42 +4039,21 @@
         <v/>
       </c>
       <c r="O89" t="str">
-        <v/>
-      </c>
-      <c r="P89" t="str">
-        <v/>
-      </c>
-      <c r="Q89" t="str">
-        <v/>
-      </c>
-      <c r="R89" t="str">
-        <v/>
-      </c>
-      <c r="S89" t="str">
-        <v/>
-      </c>
-      <c r="T89" t="str">
-        <v/>
-      </c>
-      <c r="U89" t="str">
-        <v/>
-      </c>
-      <c r="V89" t="str">
         <v/>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>|| הפרויקט של דודי לוי ואבטיפוס - הפטריקים ()</v>
+        <v>עדן בן זקן - רולקס וקסקט</v>
       </c>
       <c r="B90" t="str">
-        <v>2025  02:16-12-31</v>
+        <v>2026  08:41-01-14</v>
       </c>
       <c r="C90" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24436&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -4131,45 +4083,21 @@
         <v/>
       </c>
       <c r="N90" t="str">
-        <v/>
-      </c>
-      <c r="O90" t="str">
-        <v/>
-      </c>
-      <c r="P90" t="str">
-        <v/>
-      </c>
-      <c r="Q90" t="str">
-        <v/>
-      </c>
-      <c r="R90" t="str">
-        <v/>
-      </c>
-      <c r="S90" t="str">
-        <v/>
-      </c>
-      <c r="T90" t="str">
-        <v/>
-      </c>
-      <c r="U90" t="str">
-        <v/>
-      </c>
-      <c r="V90" t="str">
         <v/>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>|| שיר לוי - ילד מוזר ()</v>
+        <v>תומר יוסף - 360</v>
       </c>
       <c r="B91" t="str">
-        <v>2025  02:14-12-31</v>
+        <v>2026  08:40-01-14</v>
       </c>
       <c r="C91" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -4205,39 +4133,21 @@
         <v/>
       </c>
       <c r="P91" t="str">
-        <v/>
-      </c>
-      <c r="Q91" t="str">
-        <v/>
-      </c>
-      <c r="R91" t="str">
-        <v/>
-      </c>
-      <c r="S91" t="str">
-        <v/>
-      </c>
-      <c r="T91" t="str">
-        <v/>
-      </c>
-      <c r="U91" t="str">
-        <v/>
-      </c>
-      <c r="V91" t="str">
         <v/>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>|| פיטר רוט - 50 ()</v>
+        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
       </c>
       <c r="B92" t="str">
-        <v>2025  02:13-12-31</v>
+        <v>2026  08:40-01-14</v>
       </c>
       <c r="C92" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24439&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -4273,39 +4183,21 @@
         <v/>
       </c>
       <c r="P92" t="str">
-        <v/>
-      </c>
-      <c r="Q92" t="str">
-        <v/>
-      </c>
-      <c r="R92" t="str">
-        <v/>
-      </c>
-      <c r="S92" t="str">
-        <v/>
-      </c>
-      <c r="T92" t="str">
-        <v/>
-      </c>
-      <c r="U92" t="str">
-        <v/>
-      </c>
-      <c r="V92" t="str">
         <v/>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>|| אגם בוחבוט - עשרים ואחת ()</v>
+        <v>אייל גולן - בית מפואר</v>
       </c>
       <c r="B93" t="str">
-        <v>2025  02:11-12-31</v>
+        <v>2025  02:18-12-31</v>
       </c>
       <c r="C93" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -4341,39 +4233,21 @@
         <v/>
       </c>
       <c r="P93" t="str">
-        <v/>
-      </c>
-      <c r="Q93" t="str">
-        <v/>
-      </c>
-      <c r="R93" t="str">
-        <v/>
-      </c>
-      <c r="S93" t="str">
-        <v/>
-      </c>
-      <c r="T93" t="str">
-        <v/>
-      </c>
-      <c r="U93" t="str">
-        <v/>
-      </c>
-      <c r="V93" t="str">
         <v/>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>|| רבקה זוהר - רסיסים של אור ()</v>
+        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
       </c>
       <c r="B94" t="str">
-        <v>2025  02:09-12-31</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C94" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -4409,39 +4283,21 @@
         <v/>
       </c>
       <c r="P94" t="str">
-        <v/>
-      </c>
-      <c r="Q94" t="str">
-        <v/>
-      </c>
-      <c r="R94" t="str">
-        <v/>
-      </c>
-      <c r="S94" t="str">
-        <v/>
-      </c>
-      <c r="T94" t="str">
-        <v/>
-      </c>
-      <c r="U94" t="str">
-        <v/>
-      </c>
-      <c r="V94" t="str">
         <v/>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>|| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות ()</v>
+        <v>שיר לוי - ילד מוזר</v>
       </c>
       <c r="B95" t="str">
-        <v>2025  02:08-12-31</v>
+        <v>2025  02:14-12-31</v>
       </c>
       <c r="C95" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4477,39 +4333,21 @@
         <v/>
       </c>
       <c r="P95" t="str">
-        <v/>
-      </c>
-      <c r="Q95" t="str">
-        <v/>
-      </c>
-      <c r="R95" t="str">
-        <v/>
-      </c>
-      <c r="S95" t="str">
-        <v/>
-      </c>
-      <c r="T95" t="str">
-        <v/>
-      </c>
-      <c r="U95" t="str">
-        <v/>
-      </c>
-      <c r="V95" t="str">
         <v/>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>|| אהוד בנאי ובנו הנדלר - פליטי הדאב ()</v>
+        <v>פיטר רוט - 50</v>
       </c>
       <c r="B96" t="str">
-        <v>2025  02:05-12-31</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C96" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4545,39 +4383,21 @@
         <v/>
       </c>
       <c r="P96" t="str">
-        <v/>
-      </c>
-      <c r="Q96" t="str">
-        <v/>
-      </c>
-      <c r="R96" t="str">
-        <v/>
-      </c>
-      <c r="S96" t="str">
-        <v/>
-      </c>
-      <c r="T96" t="str">
-        <v/>
-      </c>
-      <c r="U96" t="str">
-        <v/>
-      </c>
-      <c r="V96" t="str">
         <v/>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>|| Imagine פסטיגל - שירי התחרות ()</v>
+        <v>אגם בוחבוט - עשרים ואחת</v>
       </c>
       <c r="B97" t="str">
-        <v>2025  02:04-12-31</v>
+        <v>2025  02:11-12-31</v>
       </c>
       <c r="C97" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4613,39 +4433,21 @@
         <v/>
       </c>
       <c r="P97" t="str">
-        <v/>
-      </c>
-      <c r="Q97" t="str">
-        <v/>
-      </c>
-      <c r="R97" t="str">
-        <v/>
-      </c>
-      <c r="S97" t="str">
-        <v/>
-      </c>
-      <c r="T97" t="str">
-        <v/>
-      </c>
-      <c r="U97" t="str">
-        <v/>
-      </c>
-      <c r="V97" t="str">
         <v/>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>|| השמחות - חובות אבודים ()</v>
+        <v>רבקה זוהר - רסיסים של אור</v>
       </c>
       <c r="B98" t="str">
-        <v>2025  02:02-12-31</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C98" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4681,39 +4483,21 @@
         <v/>
       </c>
       <c r="P98" t="str">
-        <v/>
-      </c>
-      <c r="Q98" t="str">
-        <v/>
-      </c>
-      <c r="R98" t="str">
-        <v/>
-      </c>
-      <c r="S98" t="str">
-        <v/>
-      </c>
-      <c r="T98" t="str">
-        <v/>
-      </c>
-      <c r="U98" t="str">
-        <v/>
-      </c>
-      <c r="V98" t="str">
         <v/>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>|| שלמה גרוניך - כמו כוכבים ()</v>
+        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
       </c>
       <c r="B99" t="str">
-        <v>2025  02:00-12-31</v>
+        <v>2025  02:08-12-31</v>
       </c>
       <c r="C99" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4749,39 +4533,21 @@
         <v/>
       </c>
       <c r="P99" t="str">
-        <v/>
-      </c>
-      <c r="Q99" t="str">
-        <v/>
-      </c>
-      <c r="R99" t="str">
-        <v/>
-      </c>
-      <c r="S99" t="str">
-        <v/>
-      </c>
-      <c r="T99" t="str">
-        <v/>
-      </c>
-      <c r="U99" t="str">
-        <v/>
-      </c>
-      <c r="V99" t="str">
         <v/>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>|| יוני רועה - מפוזרים ()</v>
+        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
       </c>
       <c r="B100" t="str">
-        <v>2025  01:56-12-31</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C100" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4817,39 +4583,21 @@
         <v/>
       </c>
       <c r="P100" t="str">
-        <v/>
-      </c>
-      <c r="Q100" t="str">
-        <v/>
-      </c>
-      <c r="R100" t="str">
-        <v/>
-      </c>
-      <c r="S100" t="str">
-        <v/>
-      </c>
-      <c r="T100" t="str">
-        <v/>
-      </c>
-      <c r="U100" t="str">
-        <v/>
-      </c>
-      <c r="V100" t="str">
         <v/>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>|| התקווה 6 - ויהי אור ()</v>
+        <v>Imagine פסטיגל - שירי התחרות</v>
       </c>
       <c r="B101" t="str">
-        <v>2025  01:54-12-31</v>
+        <v>2025  02:04-12-31</v>
       </c>
       <c r="C101" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4885,39 +4633,21 @@
         <v/>
       </c>
       <c r="P101" t="str">
-        <v/>
-      </c>
-      <c r="Q101" t="str">
-        <v/>
-      </c>
-      <c r="R101" t="str">
-        <v/>
-      </c>
-      <c r="S101" t="str">
-        <v/>
-      </c>
-      <c r="T101" t="str">
-        <v/>
-      </c>
-      <c r="U101" t="str">
-        <v/>
-      </c>
-      <c r="V101" t="str">
         <v/>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>|| שאנן סטריט ודי ג׳יי מש - באתי לבדר ()</v>
+        <v>השמחות - חובות אבודים</v>
       </c>
       <c r="B102" t="str">
-        <v>2025  01:53-12-31</v>
+        <v>2025  02:02-12-31</v>
       </c>
       <c r="C102" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4953,39 +4683,21 @@
         <v/>
       </c>
       <c r="P102" t="str">
-        <v/>
-      </c>
-      <c r="Q102" t="str">
-        <v/>
-      </c>
-      <c r="R102" t="str">
-        <v/>
-      </c>
-      <c r="S102" t="str">
-        <v/>
-      </c>
-      <c r="T102" t="str">
-        <v/>
-      </c>
-      <c r="U102" t="str">
-        <v/>
-      </c>
-      <c r="V102" t="str">
         <v/>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>אשכול נוכחות למשתמשים פעילים</v>
+        <v>שלמה גרוניך - כמו כוכבים</v>
       </c>
       <c r="B103" t="str">
-        <v>2025  16:32 מאת freund-10-16</v>
+        <v>2025  02:00-12-31</v>
       </c>
       <c r="C103" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=23455&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -5021,45 +4733,21 @@
         <v/>
       </c>
       <c r="P103" t="str">
-        <v/>
-      </c>
-      <c r="Q103" t="str">
-        <v/>
-      </c>
-      <c r="R103" t="str">
-        <v/>
-      </c>
-      <c r="S103" t="str">
-        <v/>
-      </c>
-      <c r="T103" t="str">
-        <v/>
-      </c>
-      <c r="U103" t="str">
-        <v/>
-      </c>
-      <c r="V103" t="str">
-        <v/>
-      </c>
-      <c r="W103" t="str">
-        <v/>
-      </c>
-      <c r="X103" t="str">
         <v/>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>כיצד להוריד מהאתרים המפורסמים</v>
+        <v>יוני רועה - מפוזרים</v>
       </c>
       <c r="B104" t="str">
-        <v>2023  16:23 מאת petel1-08-08</v>
+        <v>2025  01:56-12-31</v>
       </c>
       <c r="C104" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=22411&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -5095,48 +4783,24 @@
         <v/>
       </c>
       <c r="P104" t="str">
-        <v/>
-      </c>
-      <c r="Q104" t="str">
-        <v/>
-      </c>
-      <c r="R104" t="str">
-        <v/>
-      </c>
-      <c r="S104" t="str">
-        <v/>
-      </c>
-      <c r="T104" t="str">
-        <v/>
-      </c>
-      <c r="U104" t="str">
-        <v/>
-      </c>
-      <c r="V104" t="str">
-        <v/>
-      </c>
-      <c r="W104" t="str">
-        <v/>
-      </c>
-      <c r="X104" t="str">
         <v/>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
+        <v>פטריק סבג Hotel Mogador</v>
       </c>
       <c r="B105" t="str">
-        <v>2026  22:40 מאת מוטי_ד-01-01</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C105" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24435&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-13</v>
       </c>
       <c r="E105" t="str">
-        <v/>
+        <v>האלבום של פטריק סבג אינו אוסף שירים אקראי, אלא מרחב. מקום לשהות בו.  נכנסים, שומעים, ויוצאים קצת אחרים. הבחירה בשם "הוטל מוגדור” היא כבר הצהרה. מלון = מקום מעבר, לא בית קבוע, מוגדור = עיר נמל, תנועה, ערבוב תרבויות. כך</v>
       </c>
       <c r="F105" t="str">
         <v>אלבומים חדשים</v>
@@ -5175,39 +4839,21 @@
         <v/>
       </c>
       <c r="R105" t="str">
-        <v/>
-      </c>
-      <c r="S105" t="str">
-        <v/>
-      </c>
-      <c r="T105" t="str">
-        <v/>
-      </c>
-      <c r="U105" t="str">
-        <v/>
-      </c>
-      <c r="V105" t="str">
-        <v/>
-      </c>
-      <c r="W105" t="str">
-        <v/>
-      </c>
-      <c r="X105" t="str">
         <v/>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>|אלבום חדש| אייל גולן - בית מפואר (2025)</v>
+        <v>|אלבום חדש| תומר יוסף - 360 ()</v>
       </c>
       <c r="B106" t="str">
-        <v>2025  02:18 מאת DiSHi-12-31</v>
+        <v>2026  11:38-01-09</v>
       </c>
       <c r="C106" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -5255,33 +4901,21 @@
         <v/>
       </c>
       <c r="T106" t="str">
-        <v/>
-      </c>
-      <c r="U106" t="str">
-        <v/>
-      </c>
-      <c r="V106" t="str">
-        <v/>
-      </c>
-      <c r="W106" t="str">
-        <v/>
-      </c>
-      <c r="X106" t="str">
         <v/>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע (2025)</v>
+        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע ()</v>
       </c>
       <c r="B107" t="str">
-        <v>2025  02:17 מאת DiSHi-12-31</v>
+        <v>2025  02:17-12-31</v>
       </c>
       <c r="C107" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -5329,33 +4963,21 @@
         <v/>
       </c>
       <c r="T107" t="str">
-        <v/>
-      </c>
-      <c r="U107" t="str">
-        <v/>
-      </c>
-      <c r="V107" t="str">
-        <v/>
-      </c>
-      <c r="W107" t="str">
-        <v/>
-      </c>
-      <c r="X107" t="str">
         <v/>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>|אלבום חדש| הפרויקט של דודי לוי ואבטיפוס - הפטריקים (2025)</v>
+        <v>|אלבום חדש| אברהם טל - חי ()</v>
       </c>
       <c r="B108" t="str">
-        <v>2025  02:16 מאת DiSHi-12-31</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C108" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -5403,33 +5025,21 @@
         <v/>
       </c>
       <c r="T108" t="str">
-        <v/>
-      </c>
-      <c r="U108" t="str">
-        <v/>
-      </c>
-      <c r="V108" t="str">
-        <v/>
-      </c>
-      <c r="W108" t="str">
-        <v/>
-      </c>
-      <c r="X108" t="str">
         <v/>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>|אלבום חדש| אברהם טל - חי (2025)</v>
+        <v>|אלבום חדש| מיקי גבריאלוב - שלום ()</v>
       </c>
       <c r="B109" t="str">
-        <v>2025  02:16 מאת DiSHi-12-31</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C109" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -5477,33 +5087,21 @@
         <v/>
       </c>
       <c r="T109" t="str">
-        <v/>
-      </c>
-      <c r="U109" t="str">
-        <v/>
-      </c>
-      <c r="V109" t="str">
-        <v/>
-      </c>
-      <c r="W109" t="str">
-        <v/>
-      </c>
-      <c r="X109" t="str">
         <v/>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>|אלבום חדש| שיר לוי - ילד מוזר (2025)</v>
+        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם ()</v>
       </c>
       <c r="B110" t="str">
-        <v>2025  02:14 מאת DiSHi-12-31</v>
+        <v>2025  02:12-12-31</v>
       </c>
       <c r="C110" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -5551,33 +5149,21 @@
         <v/>
       </c>
       <c r="T110" t="str">
-        <v/>
-      </c>
-      <c r="U110" t="str">
-        <v/>
-      </c>
-      <c r="V110" t="str">
-        <v/>
-      </c>
-      <c r="W110" t="str">
-        <v/>
-      </c>
-      <c r="X110" t="str">
         <v/>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>|אלבום חדש| מיקי גבריאלוב - שלום (2025)</v>
+        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון ()</v>
       </c>
       <c r="B111" t="str">
-        <v>2025  02:13 מאת DiSHi-12-31</v>
+        <v>2025  02:10-12-31</v>
       </c>
       <c r="C111" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -5625,33 +5211,21 @@
         <v/>
       </c>
       <c r="T111" t="str">
-        <v/>
-      </c>
-      <c r="U111" t="str">
-        <v/>
-      </c>
-      <c r="V111" t="str">
-        <v/>
-      </c>
-      <c r="W111" t="str">
-        <v/>
-      </c>
-      <c r="X111" t="str">
         <v/>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>|אלבום חדש| פיטר רוט - 50 (2025)</v>
+        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה ()</v>
       </c>
       <c r="B112" t="str">
-        <v>2025  02:13 מאת DiSHi-12-31</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C112" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -5699,33 +5273,21 @@
         <v/>
       </c>
       <c r="T112" t="str">
-        <v/>
-      </c>
-      <c r="U112" t="str">
-        <v/>
-      </c>
-      <c r="V112" t="str">
-        <v/>
-      </c>
-      <c r="W112" t="str">
-        <v/>
-      </c>
-      <c r="X112" t="str">
         <v/>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם (2025)</v>
+        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים ()</v>
       </c>
       <c r="B113" t="str">
-        <v>2025  02:12 מאת DiSHi-12-31</v>
+        <v>2025  02:06-12-31</v>
       </c>
       <c r="C113" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -5773,33 +5335,21 @@
         <v/>
       </c>
       <c r="T113" t="str">
-        <v/>
-      </c>
-      <c r="U113" t="str">
-        <v/>
-      </c>
-      <c r="V113" t="str">
-        <v/>
-      </c>
-      <c r="W113" t="str">
-        <v/>
-      </c>
-      <c r="X113" t="str">
         <v/>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>|אלבום חדש| אגם בוחבוט - עשרים ואחת (2025)</v>
+        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם ()</v>
       </c>
       <c r="B114" t="str">
-        <v>2025  02:11 מאת DiSHi-12-31</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C114" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -5847,33 +5397,21 @@
         <v/>
       </c>
       <c r="T114" t="str">
-        <v/>
-      </c>
-      <c r="U114" t="str">
-        <v/>
-      </c>
-      <c r="V114" t="str">
-        <v/>
-      </c>
-      <c r="W114" t="str">
-        <v/>
-      </c>
-      <c r="X114" t="str">
         <v/>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון (2025)</v>
+        <v>|אלבום חדש| סטטיק - קעקועים ()</v>
       </c>
       <c r="B115" t="str">
-        <v>2025  02:10 מאת DiSHi-12-31</v>
+        <v>2025  02:03-12-31</v>
       </c>
       <c r="C115" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -5921,33 +5459,21 @@
         <v/>
       </c>
       <c r="T115" t="str">
-        <v/>
-      </c>
-      <c r="U115" t="str">
-        <v/>
-      </c>
-      <c r="V115" t="str">
-        <v/>
-      </c>
-      <c r="W115" t="str">
-        <v/>
-      </c>
-      <c r="X115" t="str">
         <v/>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>|אלבום חדש| רבקה זוהר - רסיסים של אור (2025)</v>
+        <v>|אלבום חדש| ליאור נרקיס - דיסוננס ()</v>
       </c>
       <c r="B116" t="str">
-        <v>2025  02:09 מאת DiSHi-12-31</v>
+        <v>2025  02:01-12-31</v>
       </c>
       <c r="C116" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -5995,33 +5521,21 @@
         <v/>
       </c>
       <c r="T116" t="str">
-        <v/>
-      </c>
-      <c r="U116" t="str">
-        <v/>
-      </c>
-      <c r="V116" t="str">
-        <v/>
-      </c>
-      <c r="W116" t="str">
-        <v/>
-      </c>
-      <c r="X116" t="str">
         <v/>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה (2025)</v>
+        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) ()</v>
       </c>
       <c r="B117" t="str">
-        <v>2025  02:09 מאת DiSHi-12-31</v>
+        <v>2025  01:57-12-31</v>
       </c>
       <c r="C117" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -6069,33 +5583,21 @@
         <v/>
       </c>
       <c r="T117" t="str">
-        <v/>
-      </c>
-      <c r="U117" t="str">
-        <v/>
-      </c>
-      <c r="V117" t="str">
-        <v/>
-      </c>
-      <c r="W117" t="str">
-        <v/>
-      </c>
-      <c r="X117" t="str">
         <v/>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>|אלבום חדש| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות (2025)</v>
+        <v>|אלבום חדש| אתניקס - איטליה ()</v>
       </c>
       <c r="B118" t="str">
-        <v>2025  02:08 מאת DiSHi-12-31</v>
+        <v>2025  01:55-12-31</v>
       </c>
       <c r="C118" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -6143,33 +5645,21 @@
         <v/>
       </c>
       <c r="T118" t="str">
-        <v/>
-      </c>
-      <c r="U118" t="str">
-        <v/>
-      </c>
-      <c r="V118" t="str">
-        <v/>
-      </c>
-      <c r="W118" t="str">
-        <v/>
-      </c>
-      <c r="X118" t="str">
         <v/>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים (2025)</v>
+        <v>|| תומר יוסף - 360 (2026)</v>
       </c>
       <c r="B119" t="str">
-        <v>2025  02:06 מאת DiSHi-12-31</v>
+        <v>2026  11:38-01-09</v>
       </c>
       <c r="C119" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -6223,27 +5713,21 @@
         <v/>
       </c>
       <c r="V119" t="str">
-        <v/>
-      </c>
-      <c r="W119" t="str">
-        <v/>
-      </c>
-      <c r="X119" t="str">
         <v/>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>|אלבום חדש| אהוד בנאי ובנו הנדלר - פליטי הדאב (2025)</v>
+        <v>|| עמיר בניון - לא נוגע בקרקע ()</v>
       </c>
       <c r="B120" t="str">
-        <v>2025  02:05 מאת DiSHi-12-31</v>
+        <v>2025  02:17-12-31</v>
       </c>
       <c r="C120" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -6297,27 +5781,21 @@
         <v/>
       </c>
       <c r="V120" t="str">
-        <v/>
-      </c>
-      <c r="W120" t="str">
-        <v/>
-      </c>
-      <c r="X120" t="str">
         <v/>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם (2025)</v>
+        <v>|| אברהם טל - חי ()</v>
       </c>
       <c r="B121" t="str">
-        <v>2025  02:05 מאת DiSHi-12-31</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C121" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -6371,27 +5849,21 @@
         <v/>
       </c>
       <c r="V121" t="str">
-        <v/>
-      </c>
-      <c r="W121" t="str">
-        <v/>
-      </c>
-      <c r="X121" t="str">
         <v/>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>|אלבום חדש| Imagine פסטיגל - שירי התחרות (2025)</v>
+        <v>|| מיקי גבריאלוב - שלום ()</v>
       </c>
       <c r="B122" t="str">
-        <v>2025  02:04 מאת DiSHi-12-31</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C122" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -6445,27 +5917,21 @@
         <v/>
       </c>
       <c r="V122" t="str">
-        <v/>
-      </c>
-      <c r="W122" t="str">
-        <v/>
-      </c>
-      <c r="X122" t="str">
         <v/>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>|אלבום חדש| סטטיק - קעקועים (2025)</v>
+        <v>|| בזכרי ימים ימימה - מחווה לצלילי הכרם ()</v>
       </c>
       <c r="B123" t="str">
-        <v>2025  02:03 מאת DiSHi-12-31</v>
+        <v>2025  02:12-12-31</v>
       </c>
       <c r="C123" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -6519,27 +5985,21 @@
         <v/>
       </c>
       <c r="V123" t="str">
-        <v/>
-      </c>
-      <c r="W123" t="str">
-        <v/>
-      </c>
-      <c r="X123" t="str">
         <v/>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>|אלבום חדש| השמחות - חובות אבודים (2025)</v>
+        <v>|| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון ()</v>
       </c>
       <c r="B124" t="str">
-        <v>2025  02:02 מאת DiSHi-12-31</v>
+        <v>2025  02:10-12-31</v>
       </c>
       <c r="C124" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -6593,27 +6053,21 @@
         <v/>
       </c>
       <c r="V124" t="str">
-        <v/>
-      </c>
-      <c r="W124" t="str">
-        <v/>
-      </c>
-      <c r="X124" t="str">
         <v/>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>|אלבום חדש| ליאור נרקיס - דיסוננס (2025)</v>
+        <v>|| שלמה גרוניך - תודה אהבה ()</v>
       </c>
       <c r="B125" t="str">
-        <v>2025  02:01 מאת DiSHi-12-31</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C125" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -6667,27 +6121,21 @@
         <v/>
       </c>
       <c r="V125" t="str">
-        <v/>
-      </c>
-      <c r="W125" t="str">
-        <v/>
-      </c>
-      <c r="X125" t="str">
         <v/>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>|אלבום חדש| שלמה גרוניך - כמו כוכבים (2025)</v>
+        <v>|| חוה אלברשטיין - חמישה שירים ()</v>
       </c>
       <c r="B126" t="str">
-        <v>2025  02:00 מאת DiSHi-12-31</v>
+        <v>2025  02:06-12-31</v>
       </c>
       <c r="C126" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -6741,27 +6189,21 @@
         <v/>
       </c>
       <c r="V126" t="str">
-        <v/>
-      </c>
-      <c r="W126" t="str">
-        <v/>
-      </c>
-      <c r="X126" t="str">
         <v/>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) (2025)</v>
+        <v>|| הפרויקט של עידן רייכל - עד סוף העולם ()</v>
       </c>
       <c r="B127" t="str">
-        <v>2025  01:57 מאת DiSHi-12-31</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C127" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -6815,27 +6257,21 @@
         <v/>
       </c>
       <c r="V127" t="str">
-        <v/>
-      </c>
-      <c r="W127" t="str">
-        <v/>
-      </c>
-      <c r="X127" t="str">
         <v/>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>|אלבום חדש| יוני רועה - מפוזרים (2025)</v>
+        <v>|| סטטיק - קעקועים ()</v>
       </c>
       <c r="B128" t="str">
-        <v>2025  01:56 מאת DiSHi-12-31</v>
+        <v>2025  02:03-12-31</v>
       </c>
       <c r="C128" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -6889,27 +6325,21 @@
         <v/>
       </c>
       <c r="V128" t="str">
-        <v/>
-      </c>
-      <c r="W128" t="str">
-        <v/>
-      </c>
-      <c r="X128" t="str">
         <v/>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>|אלבום חדש| אתניקס - איטליה (2025)</v>
+        <v>|| ליאור נרקיס - דיסוננס ()</v>
       </c>
       <c r="B129" t="str">
-        <v>2025  01:55 מאת DiSHi-12-31</v>
+        <v>2025  02:01-12-31</v>
       </c>
       <c r="C129" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -6963,27 +6393,21 @@
         <v/>
       </c>
       <c r="V129" t="str">
-        <v/>
-      </c>
-      <c r="W129" t="str">
-        <v/>
-      </c>
-      <c r="X129" t="str">
         <v/>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>|אלבום חדש| התקווה 6 - ויהי אור (2025)</v>
+        <v>|| דיוויד ברוזה - BrozaJazz (Paris Alhambra) ()</v>
       </c>
       <c r="B130" t="str">
-        <v>2025  01:54 מאת DiSHi-12-31</v>
+        <v>2025  01:57-12-31</v>
       </c>
       <c r="C130" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -7037,27 +6461,21 @@
         <v/>
       </c>
       <c r="V130" t="str">
-        <v/>
-      </c>
-      <c r="W130" t="str">
-        <v/>
-      </c>
-      <c r="X130" t="str">
         <v/>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>|אלבום חדש| שלומי סרנגה - איפרכו (2025)</v>
+        <v>|| אתניקס - איטליה ()</v>
       </c>
       <c r="B131" t="str">
-        <v>2025  01:53 מאת DiSHi-12-31</v>
+        <v>2025  01:55-12-31</v>
       </c>
       <c r="C131" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24430&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -7111,30 +6529,24 @@
         <v/>
       </c>
       <c r="V131" t="str">
-        <v/>
-      </c>
-      <c r="W131" t="str">
-        <v/>
-      </c>
-      <c r="X131" t="str">
         <v/>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>|אלבום חדש| שאנן סטריט ודי ג׳יי מש - באתי לבדר (2025)</v>
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
       </c>
       <c r="B132" t="str">
-        <v>2025  01:53 מאת DiSHi-12-31</v>
+        <v>2026-01-09</v>
       </c>
       <c r="C132" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E132" t="str">
-        <v/>
+        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
       </c>
       <c r="F132" t="str">
         <v>אלבומים חדשים</v>
@@ -7196,13 +6608,13 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>הרשם לחברות מלאה</v>
+        <v>|| אייל גולן - בית מפואר ()</v>
       </c>
       <c r="B133" t="str">
-        <v/>
+        <v>2025  02:18-12-31</v>
       </c>
       <c r="C133" t="str">
-        <v>https://rotter.name/nor/members-new.html</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D133" t="str">
         <v>2026-01-08</v>
@@ -7267,22 +6679,28 @@
       <c r="X133" t="str">
         <v/>
       </c>
+      <c r="Y133" t="str">
+        <v/>
+      </c>
+      <c r="Z133" t="str">
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>אוליביה דין The Art of Loving</v>
+        <v>|| הפרויקט של דודי לוי ואבטיפוס - הפטריקים ()</v>
       </c>
       <c r="B134" t="str">
-        <v>2026-01-04</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C134" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D134" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E134" t="str">
-        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
+        <v/>
       </c>
       <c r="F134" t="str">
         <v>אלבומים חדשים</v>
@@ -7350,19 +6768,19 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Geese Getting Killed</v>
+        <v>|| שיר לוי - ילד מוזר ()</v>
       </c>
       <c r="B135" t="str">
-        <v>2025-12-29</v>
+        <v>2025  02:14-12-31</v>
       </c>
       <c r="C135" t="str">
-        <v>https://yosmusic.com/geese-getting-killed/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D135" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E135" t="str">
-        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
+        <v/>
       </c>
       <c r="F135" t="str">
         <v>אלבומים חדשים</v>
@@ -7430,19 +6848,19 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>רוסליה Lux</v>
+        <v>|| פיטר רוט - 50 ()</v>
       </c>
       <c r="B136" t="str">
-        <v>2025-12-25</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C136" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D136" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E136" t="str">
-        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
+        <v/>
       </c>
       <c r="F136" t="str">
         <v>אלבומים חדשים</v>
@@ -7510,19 +6928,19 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>יאנגבלאד אירוסמית' one more time</v>
+        <v>|| אגם בוחבוט - עשרים ואחת ()</v>
       </c>
       <c r="B137" t="str">
-        <v>2025-12-17</v>
+        <v>2025  02:11-12-31</v>
       </c>
       <c r="C137" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D137" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E137" t="str">
-        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
+        <v/>
       </c>
       <c r="F137" t="str">
         <v>אלבומים חדשים</v>
@@ -7590,19 +7008,19 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>פינק פלויד Wish You Were Here 50</v>
+        <v>|| רבקה זוהר - רסיסים של אור ()</v>
       </c>
       <c r="B138" t="str">
-        <v>2025-12-14</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C138" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D138" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E138" t="str">
-        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
+        <v/>
       </c>
       <c r="F138" t="str">
         <v>אלבומים חדשים</v>
@@ -7670,19 +7088,19 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+        <v>|| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות ()</v>
       </c>
       <c r="B139" t="str">
-        <v>2025-12-08</v>
+        <v>2025  02:08-12-31</v>
       </c>
       <c r="C139" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D139" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E139" t="str">
-        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
+        <v/>
       </c>
       <c r="F139" t="str">
         <v>אלבומים חדשים</v>
@@ -7750,19 +7168,19 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>סטריי קידס DO IT (EP)</v>
+        <v>|| אהוד בנאי ובנו הנדלר - פליטי הדאב ()</v>
       </c>
       <c r="B140" t="str">
-        <v>2025-12-04</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C140" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D140" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E140" t="str">
-        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
+        <v/>
       </c>
       <c r="F140" t="str">
         <v>אלבומים חדשים</v>
@@ -7830,19 +7248,19 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>דויד ברוזה BROZAJAZZ</v>
+        <v>|| Imagine פסטיגל - שירי התחרות ()</v>
       </c>
       <c r="B141" t="str">
-        <v>2025-11-30</v>
+        <v>2025  02:04-12-31</v>
       </c>
       <c r="C141" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D141" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E141" t="str">
-        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
+        <v/>
       </c>
       <c r="F141" t="str">
         <v>אלבומים חדשים</v>
@@ -7910,19 +7328,19 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Five Seconds of Summer – Everyone's A Star</v>
+        <v>|| השמחות - חובות אבודים ()</v>
       </c>
       <c r="B142" t="str">
-        <v>2025-11-24</v>
+        <v>2025  02:02-12-31</v>
       </c>
       <c r="C142" t="str">
-        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D142" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E142" t="str">
-        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
+        <v/>
       </c>
       <c r="F142" t="str">
         <v>אלבומים חדשים</v>
@@ -7990,19 +7408,19 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>התקווה 6 – ויהי אור</v>
+        <v>|| שלמה גרוניך - כמו כוכבים ()</v>
       </c>
       <c r="B143" t="str">
-        <v>2025-11-20</v>
+        <v>2025  02:00-12-31</v>
       </c>
       <c r="C143" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D143" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E143" t="str">
-        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
+        <v/>
       </c>
       <c r="F143" t="str">
         <v>אלבומים חדשים</v>
@@ -8070,19 +7488,19 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>פלורנס אנד דה משין Everybody Scream</v>
+        <v>|| יוני רועה - מפוזרים ()</v>
       </c>
       <c r="B144" t="str">
-        <v>2025-11-13</v>
+        <v>2025  01:56-12-31</v>
       </c>
       <c r="C144" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D144" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E144" t="str">
-        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
+        <v/>
       </c>
       <c r="F144" t="str">
         <v>אלבומים חדשים</v>
@@ -8150,19 +7568,19 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>טיים אימפלה Deadbeat</v>
+        <v>|| התקווה 6 - ויהי אור ()</v>
       </c>
       <c r="B145" t="str">
-        <v>2025-11-03</v>
+        <v>2025  01:54-12-31</v>
       </c>
       <c r="C145" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D145" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E145" t="str">
-        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
+        <v/>
       </c>
       <c r="F145" t="str">
         <v>אלבומים חדשים</v>
@@ -8230,19 +7648,19 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+        <v>|| שאנן סטריט ודי ג׳יי מש - באתי לבדר ()</v>
       </c>
       <c r="B146" t="str">
-        <v>2025-10-20</v>
+        <v>2025  01:53-12-31</v>
       </c>
       <c r="C146" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D146" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E146" t="str">
-        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
+        <v/>
       </c>
       <c r="F146" t="str">
         <v>אלבומים חדשים</v>
@@ -8310,19 +7728,19 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>שלמה גרוניך – תודה אהבה</v>
+        <v>אשכול נוכחות למשתמשים פעילים</v>
       </c>
       <c r="B147" t="str">
-        <v>2025-10-18</v>
+        <v>2025  16:32 מאת freund-10-16</v>
       </c>
       <c r="C147" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=23455&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D147" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E147" t="str">
-        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
+        <v/>
       </c>
       <c r="F147" t="str">
         <v>אלבומים חדשים</v>
@@ -8385,24 +7803,30 @@
         <v/>
       </c>
       <c r="Z147" t="str">
+        <v/>
+      </c>
+      <c r="AA147" t="str">
+        <v/>
+      </c>
+      <c r="AB147" t="str">
         <v/>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>טיילור סוויפט The Life Of A Showgirl</v>
+        <v>כיצד להוריד מהאתרים המפורסמים</v>
       </c>
       <c r="B148" t="str">
-        <v>2025-10-11</v>
+        <v>2023  16:23 מאת petel1-08-08</v>
       </c>
       <c r="C148" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=22411&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D148" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E148" t="str">
-        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
+        <v/>
       </c>
       <c r="F148" t="str">
         <v>אלבומים חדשים</v>
@@ -8465,24 +7889,30 @@
         <v/>
       </c>
       <c r="Z148" t="str">
+        <v/>
+      </c>
+      <c r="AA148" t="str">
+        <v/>
+      </c>
+      <c r="AB148" t="str">
         <v/>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>דוג'ה קאט Vie</v>
+        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
       </c>
       <c r="B149" t="str">
-        <v>2025-10-04</v>
+        <v>2026  22:40 מאת מוטי_ד-01-01</v>
       </c>
       <c r="C149" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24435&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D149" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E149" t="str">
-        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
+        <v/>
       </c>
       <c r="F149" t="str">
         <v>אלבומים חדשים</v>
@@ -8545,24 +7975,30 @@
         <v/>
       </c>
       <c r="Z149" t="str">
+        <v/>
+      </c>
+      <c r="AA149" t="str">
+        <v/>
+      </c>
+      <c r="AB149" t="str">
         <v/>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>ג'וי קרוקס Juniper</v>
+        <v>|אלבום חדש| אייל גולן - בית מפואר (2025)</v>
       </c>
       <c r="B150" t="str">
-        <v>2025-10-03</v>
+        <v>2025  02:18 מאת DiSHi-12-31</v>
       </c>
       <c r="C150" t="str">
-        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D150" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E150" t="str">
-        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
+        <v/>
       </c>
       <c r="F150" t="str">
         <v>אלבומים חדשים</v>
@@ -8625,24 +8061,30 @@
         <v/>
       </c>
       <c r="Z150" t="str">
+        <v/>
+      </c>
+      <c r="AA150" t="str">
+        <v/>
+      </c>
+      <c r="AB150" t="str">
         <v/>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>ביפי קליירו Futique</v>
+        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע (2025)</v>
       </c>
       <c r="B151" t="str">
-        <v>2025-09-30</v>
+        <v>2025  02:17 מאת DiSHi-12-31</v>
       </c>
       <c r="C151" t="str">
-        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D151" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E151" t="str">
-        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
+        <v/>
       </c>
       <c r="F151" t="str">
         <v>אלבומים חדשים</v>
@@ -8705,24 +8147,30 @@
         <v/>
       </c>
       <c r="Z151" t="str">
+        <v/>
+      </c>
+      <c r="AA151" t="str">
+        <v/>
+      </c>
+      <c r="AB151" t="str">
         <v/>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>אד שירן Play</v>
+        <v>|אלבום חדש| הפרויקט של דודי לוי ואבטיפוס - הפטריקים (2025)</v>
       </c>
       <c r="B152" t="str">
-        <v>2025-09-24</v>
+        <v>2025  02:16 מאת DiSHi-12-31</v>
       </c>
       <c r="C152" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D152" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E152" t="str">
-        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
+        <v/>
       </c>
       <c r="F152" t="str">
         <v>אלבומים חדשים</v>
@@ -8785,24 +8233,30 @@
         <v/>
       </c>
       <c r="Z152" t="str">
+        <v/>
+      </c>
+      <c r="AA152" t="str">
+        <v/>
+      </c>
+      <c r="AB152" t="str">
         <v/>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+        <v>|אלבום חדש| אברהם טל - חי (2025)</v>
       </c>
       <c r="B153" t="str">
-        <v>2025-09-21</v>
+        <v>2025  02:16 מאת DiSHi-12-31</v>
       </c>
       <c r="C153" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D153" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E153" t="str">
-        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
+        <v/>
       </c>
       <c r="F153" t="str">
         <v>אלבומים חדשים</v>
@@ -8865,24 +8319,30 @@
         <v/>
       </c>
       <c r="Z153" t="str">
+        <v/>
+      </c>
+      <c r="AA153" t="str">
+        <v/>
+      </c>
+      <c r="AB153" t="str">
         <v/>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>סוויד Antidepressants</v>
+        <v>|אלבום חדש| שיר לוי - ילד מוזר (2025)</v>
       </c>
       <c r="B154" t="str">
-        <v>2025-09-12</v>
+        <v>2025  02:14 מאת DiSHi-12-31</v>
       </c>
       <c r="C154" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D154" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E154" t="str">
-        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
+        <v/>
       </c>
       <c r="F154" t="str">
         <v>אלבומים חדשים</v>
@@ -8945,24 +8405,30 @@
         <v/>
       </c>
       <c r="Z154" t="str">
+        <v/>
+      </c>
+      <c r="AA154" t="str">
+        <v/>
+      </c>
+      <c r="AB154" t="str">
         <v/>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>וולף אליס The Clearing</v>
+        <v>|אלבום חדש| מיקי גבריאלוב - שלום (2025)</v>
       </c>
       <c r="B155" t="str">
-        <v>2025-09-01</v>
+        <v>2025  02:13 מאת DiSHi-12-31</v>
       </c>
       <c r="C155" t="str">
-        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D155" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E155" t="str">
-        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
+        <v/>
       </c>
       <c r="F155" t="str">
         <v>אלבומים חדשים</v>
@@ -9025,24 +8491,30 @@
         <v/>
       </c>
       <c r="Z155" t="str">
+        <v/>
+      </c>
+      <c r="AA155" t="str">
+        <v/>
+      </c>
+      <c r="AB155" t="str">
         <v/>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+        <v>|אלבום חדש| פיטר רוט - 50 (2025)</v>
       </c>
       <c r="B156" t="str">
-        <v>2025-08-29</v>
+        <v>2025  02:13 מאת DiSHi-12-31</v>
       </c>
       <c r="C156" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D156" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E156" t="str">
-        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
+        <v/>
       </c>
       <c r="F156" t="str">
         <v>אלבומים חדשים</v>
@@ -9105,24 +8577,30 @@
         <v/>
       </c>
       <c r="Z156" t="str">
+        <v/>
+      </c>
+      <c r="AA156" t="str">
+        <v/>
+      </c>
+      <c r="AB156" t="str">
         <v/>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם (2025)</v>
       </c>
       <c r="B157" t="str">
-        <v>2025-08-24</v>
+        <v>2025  02:12 מאת DiSHi-12-31</v>
       </c>
       <c r="C157" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D157" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E157" t="str">
-        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
+        <v/>
       </c>
       <c r="F157" t="str">
         <v>אלבומים חדשים</v>
@@ -9185,24 +8663,30 @@
         <v/>
       </c>
       <c r="Z157" t="str">
+        <v/>
+      </c>
+      <c r="AA157" t="str">
+        <v/>
+      </c>
+      <c r="AB157" t="str">
         <v/>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+        <v>|אלבום חדש| אגם בוחבוט - עשרים ואחת (2025)</v>
       </c>
       <c r="B158" t="str">
-        <v>2025-08-21</v>
+        <v>2025  02:11 מאת DiSHi-12-31</v>
       </c>
       <c r="C158" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D158" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E158" t="str">
-        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
+        <v/>
       </c>
       <c r="F158" t="str">
         <v>אלבומים חדשים</v>
@@ -9265,24 +8749,30 @@
         <v/>
       </c>
       <c r="Z158" t="str">
+        <v/>
+      </c>
+      <c r="AA158" t="str">
+        <v/>
+      </c>
+      <c r="AB158" t="str">
         <v/>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>אברהם טל – חי</v>
+        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון (2025)</v>
       </c>
       <c r="B159" t="str">
-        <v>2025-08-17</v>
+        <v>2025  02:10 מאת DiSHi-12-31</v>
       </c>
       <c r="C159" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D159" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E159" t="str">
-        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
+        <v/>
       </c>
       <c r="F159" t="str">
         <v>אלבומים חדשים</v>
@@ -9345,24 +8835,30 @@
         <v/>
       </c>
       <c r="Z159" t="str">
+        <v/>
+      </c>
+      <c r="AA159" t="str">
+        <v/>
+      </c>
+      <c r="AB159" t="str">
         <v/>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>רנה ראפ Bite Me</v>
+        <v>|אלבום חדש| רבקה זוהר - רסיסים של אור (2025)</v>
       </c>
       <c r="B160" t="str">
-        <v>2025-08-12</v>
+        <v>2025  02:09 מאת DiSHi-12-31</v>
       </c>
       <c r="C160" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D160" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E160" t="str">
-        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
+        <v/>
       </c>
       <c r="F160" t="str">
         <v>אלבומים חדשים</v>
@@ -9425,24 +8921,30 @@
         <v/>
       </c>
       <c r="Z160" t="str">
+        <v/>
+      </c>
+      <c r="AA160" t="str">
+        <v/>
+      </c>
+      <c r="AB160" t="str">
         <v/>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>The K's – Pretty On The Internet</v>
+        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה (2025)</v>
       </c>
       <c r="B161" t="str">
-        <v>2025-08-03</v>
+        <v>2025  02:09 מאת DiSHi-12-31</v>
       </c>
       <c r="C161" t="str">
-        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D161" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E161" t="str">
-        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
+        <v/>
       </c>
       <c r="F161" t="str">
         <v>אלבומים חדשים</v>
@@ -9505,24 +9007,30 @@
         <v/>
       </c>
       <c r="Z161" t="str">
+        <v/>
+      </c>
+      <c r="AA161" t="str">
+        <v/>
+      </c>
+      <c r="AB161" t="str">
         <v/>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>פליטווד מק Fifty Years – Don’t Stop</v>
+        <v>|אלבום חדש| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות (2025)</v>
       </c>
       <c r="B162" t="str">
-        <v>2025-07-30</v>
+        <v>2025  02:08 מאת DiSHi-12-31</v>
       </c>
       <c r="C162" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%99%d7%98%d7%95%d7%95%d7%93-%d7%9e%d7%a7-fifty-years-dont-stop/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D162" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E162" t="str">
-        <v>פליטווד מק (Fleetwood Mac) חוגגים חצי מאה של מוזיקה עם אוסף חדש בן 50 שירים, שמתפרש על כל הקריירה של הלהקה, מימיה הראשונים בסגנון בלוז, ועד להצלחתה העולמית כאחת מלהקות הגדולות בהיסטוריה של הרוק. פליטווד מק הם לא רק להקה</v>
+        <v/>
       </c>
       <c r="F162" t="str">
         <v>אלבומים חדשים</v>
@@ -9585,92 +9093,4068 @@
         <v/>
       </c>
       <c r="Z162" t="str">
+        <v/>
+      </c>
+      <c r="AA162" t="str">
+        <v/>
+      </c>
+      <c r="AB162" t="str">
         <v/>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Wet Leg Moisturizer</v>
+        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים (2025)</v>
       </c>
       <c r="B163" t="str">
-        <v>2025-07-25</v>
+        <v>2025  02:06 מאת DiSHi-12-31</v>
       </c>
       <c r="C163" t="str">
-        <v>https://yosmusic.com/wet-leg-moisturizer/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D163" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E163" t="str">
+        <v/>
+      </c>
+      <c r="F163" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G163" t="str">
+        <v/>
+      </c>
+      <c r="H163" t="str">
+        <v/>
+      </c>
+      <c r="I163" t="str">
+        <v/>
+      </c>
+      <c r="J163" t="str">
+        <v/>
+      </c>
+      <c r="K163" t="str">
+        <v/>
+      </c>
+      <c r="L163" t="str">
+        <v/>
+      </c>
+      <c r="M163" t="str">
+        <v/>
+      </c>
+      <c r="N163" t="str">
+        <v/>
+      </c>
+      <c r="O163" t="str">
+        <v/>
+      </c>
+      <c r="P163" t="str">
+        <v/>
+      </c>
+      <c r="Q163" t="str">
+        <v/>
+      </c>
+      <c r="R163" t="str">
+        <v/>
+      </c>
+      <c r="S163" t="str">
+        <v/>
+      </c>
+      <c r="T163" t="str">
+        <v/>
+      </c>
+      <c r="U163" t="str">
+        <v/>
+      </c>
+      <c r="V163" t="str">
+        <v/>
+      </c>
+      <c r="W163" t="str">
+        <v/>
+      </c>
+      <c r="X163" t="str">
+        <v/>
+      </c>
+      <c r="Y163" t="str">
+        <v/>
+      </c>
+      <c r="Z163" t="str">
+        <v/>
+      </c>
+      <c r="AA163" t="str">
+        <v/>
+      </c>
+      <c r="AB163" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>|אלבום חדש| אהוד בנאי ובנו הנדלר - פליטי הדאב (2025)</v>
+      </c>
+      <c r="B164" t="str">
+        <v>2025  02:05 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C164" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D164" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E164" t="str">
+        <v/>
+      </c>
+      <c r="F164" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G164" t="str">
+        <v/>
+      </c>
+      <c r="H164" t="str">
+        <v/>
+      </c>
+      <c r="I164" t="str">
+        <v/>
+      </c>
+      <c r="J164" t="str">
+        <v/>
+      </c>
+      <c r="K164" t="str">
+        <v/>
+      </c>
+      <c r="L164" t="str">
+        <v/>
+      </c>
+      <c r="M164" t="str">
+        <v/>
+      </c>
+      <c r="N164" t="str">
+        <v/>
+      </c>
+      <c r="O164" t="str">
+        <v/>
+      </c>
+      <c r="P164" t="str">
+        <v/>
+      </c>
+      <c r="Q164" t="str">
+        <v/>
+      </c>
+      <c r="R164" t="str">
+        <v/>
+      </c>
+      <c r="S164" t="str">
+        <v/>
+      </c>
+      <c r="T164" t="str">
+        <v/>
+      </c>
+      <c r="U164" t="str">
+        <v/>
+      </c>
+      <c r="V164" t="str">
+        <v/>
+      </c>
+      <c r="W164" t="str">
+        <v/>
+      </c>
+      <c r="X164" t="str">
+        <v/>
+      </c>
+      <c r="Y164" t="str">
+        <v/>
+      </c>
+      <c r="Z164" t="str">
+        <v/>
+      </c>
+      <c r="AA164" t="str">
+        <v/>
+      </c>
+      <c r="AB164" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם (2025)</v>
+      </c>
+      <c r="B165" t="str">
+        <v>2025  02:05 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C165" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D165" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E165" t="str">
+        <v/>
+      </c>
+      <c r="F165" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G165" t="str">
+        <v/>
+      </c>
+      <c r="H165" t="str">
+        <v/>
+      </c>
+      <c r="I165" t="str">
+        <v/>
+      </c>
+      <c r="J165" t="str">
+        <v/>
+      </c>
+      <c r="K165" t="str">
+        <v/>
+      </c>
+      <c r="L165" t="str">
+        <v/>
+      </c>
+      <c r="M165" t="str">
+        <v/>
+      </c>
+      <c r="N165" t="str">
+        <v/>
+      </c>
+      <c r="O165" t="str">
+        <v/>
+      </c>
+      <c r="P165" t="str">
+        <v/>
+      </c>
+      <c r="Q165" t="str">
+        <v/>
+      </c>
+      <c r="R165" t="str">
+        <v/>
+      </c>
+      <c r="S165" t="str">
+        <v/>
+      </c>
+      <c r="T165" t="str">
+        <v/>
+      </c>
+      <c r="U165" t="str">
+        <v/>
+      </c>
+      <c r="V165" t="str">
+        <v/>
+      </c>
+      <c r="W165" t="str">
+        <v/>
+      </c>
+      <c r="X165" t="str">
+        <v/>
+      </c>
+      <c r="Y165" t="str">
+        <v/>
+      </c>
+      <c r="Z165" t="str">
+        <v/>
+      </c>
+      <c r="AA165" t="str">
+        <v/>
+      </c>
+      <c r="AB165" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>|אלבום חדש| Imagine פסטיגל - שירי התחרות (2025)</v>
+      </c>
+      <c r="B166" t="str">
+        <v>2025  02:04 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C166" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D166" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E166" t="str">
+        <v/>
+      </c>
+      <c r="F166" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G166" t="str">
+        <v/>
+      </c>
+      <c r="H166" t="str">
+        <v/>
+      </c>
+      <c r="I166" t="str">
+        <v/>
+      </c>
+      <c r="J166" t="str">
+        <v/>
+      </c>
+      <c r="K166" t="str">
+        <v/>
+      </c>
+      <c r="L166" t="str">
+        <v/>
+      </c>
+      <c r="M166" t="str">
+        <v/>
+      </c>
+      <c r="N166" t="str">
+        <v/>
+      </c>
+      <c r="O166" t="str">
+        <v/>
+      </c>
+      <c r="P166" t="str">
+        <v/>
+      </c>
+      <c r="Q166" t="str">
+        <v/>
+      </c>
+      <c r="R166" t="str">
+        <v/>
+      </c>
+      <c r="S166" t="str">
+        <v/>
+      </c>
+      <c r="T166" t="str">
+        <v/>
+      </c>
+      <c r="U166" t="str">
+        <v/>
+      </c>
+      <c r="V166" t="str">
+        <v/>
+      </c>
+      <c r="W166" t="str">
+        <v/>
+      </c>
+      <c r="X166" t="str">
+        <v/>
+      </c>
+      <c r="Y166" t="str">
+        <v/>
+      </c>
+      <c r="Z166" t="str">
+        <v/>
+      </c>
+      <c r="AA166" t="str">
+        <v/>
+      </c>
+      <c r="AB166" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>|אלבום חדש| סטטיק - קעקועים (2025)</v>
+      </c>
+      <c r="B167" t="str">
+        <v>2025  02:03 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C167" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D167" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E167" t="str">
+        <v/>
+      </c>
+      <c r="F167" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G167" t="str">
+        <v/>
+      </c>
+      <c r="H167" t="str">
+        <v/>
+      </c>
+      <c r="I167" t="str">
+        <v/>
+      </c>
+      <c r="J167" t="str">
+        <v/>
+      </c>
+      <c r="K167" t="str">
+        <v/>
+      </c>
+      <c r="L167" t="str">
+        <v/>
+      </c>
+      <c r="M167" t="str">
+        <v/>
+      </c>
+      <c r="N167" t="str">
+        <v/>
+      </c>
+      <c r="O167" t="str">
+        <v/>
+      </c>
+      <c r="P167" t="str">
+        <v/>
+      </c>
+      <c r="Q167" t="str">
+        <v/>
+      </c>
+      <c r="R167" t="str">
+        <v/>
+      </c>
+      <c r="S167" t="str">
+        <v/>
+      </c>
+      <c r="T167" t="str">
+        <v/>
+      </c>
+      <c r="U167" t="str">
+        <v/>
+      </c>
+      <c r="V167" t="str">
+        <v/>
+      </c>
+      <c r="W167" t="str">
+        <v/>
+      </c>
+      <c r="X167" t="str">
+        <v/>
+      </c>
+      <c r="Y167" t="str">
+        <v/>
+      </c>
+      <c r="Z167" t="str">
+        <v/>
+      </c>
+      <c r="AA167" t="str">
+        <v/>
+      </c>
+      <c r="AB167" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>|אלבום חדש| השמחות - חובות אבודים (2025)</v>
+      </c>
+      <c r="B168" t="str">
+        <v>2025  02:02 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C168" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D168" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E168" t="str">
+        <v/>
+      </c>
+      <c r="F168" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G168" t="str">
+        <v/>
+      </c>
+      <c r="H168" t="str">
+        <v/>
+      </c>
+      <c r="I168" t="str">
+        <v/>
+      </c>
+      <c r="J168" t="str">
+        <v/>
+      </c>
+      <c r="K168" t="str">
+        <v/>
+      </c>
+      <c r="L168" t="str">
+        <v/>
+      </c>
+      <c r="M168" t="str">
+        <v/>
+      </c>
+      <c r="N168" t="str">
+        <v/>
+      </c>
+      <c r="O168" t="str">
+        <v/>
+      </c>
+      <c r="P168" t="str">
+        <v/>
+      </c>
+      <c r="Q168" t="str">
+        <v/>
+      </c>
+      <c r="R168" t="str">
+        <v/>
+      </c>
+      <c r="S168" t="str">
+        <v/>
+      </c>
+      <c r="T168" t="str">
+        <v/>
+      </c>
+      <c r="U168" t="str">
+        <v/>
+      </c>
+      <c r="V168" t="str">
+        <v/>
+      </c>
+      <c r="W168" t="str">
+        <v/>
+      </c>
+      <c r="X168" t="str">
+        <v/>
+      </c>
+      <c r="Y168" t="str">
+        <v/>
+      </c>
+      <c r="Z168" t="str">
+        <v/>
+      </c>
+      <c r="AA168" t="str">
+        <v/>
+      </c>
+      <c r="AB168" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>|אלבום חדש| ליאור נרקיס - דיסוננס (2025)</v>
+      </c>
+      <c r="B169" t="str">
+        <v>2025  02:01 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C169" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D169" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E169" t="str">
+        <v/>
+      </c>
+      <c r="F169" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G169" t="str">
+        <v/>
+      </c>
+      <c r="H169" t="str">
+        <v/>
+      </c>
+      <c r="I169" t="str">
+        <v/>
+      </c>
+      <c r="J169" t="str">
+        <v/>
+      </c>
+      <c r="K169" t="str">
+        <v/>
+      </c>
+      <c r="L169" t="str">
+        <v/>
+      </c>
+      <c r="M169" t="str">
+        <v/>
+      </c>
+      <c r="N169" t="str">
+        <v/>
+      </c>
+      <c r="O169" t="str">
+        <v/>
+      </c>
+      <c r="P169" t="str">
+        <v/>
+      </c>
+      <c r="Q169" t="str">
+        <v/>
+      </c>
+      <c r="R169" t="str">
+        <v/>
+      </c>
+      <c r="S169" t="str">
+        <v/>
+      </c>
+      <c r="T169" t="str">
+        <v/>
+      </c>
+      <c r="U169" t="str">
+        <v/>
+      </c>
+      <c r="V169" t="str">
+        <v/>
+      </c>
+      <c r="W169" t="str">
+        <v/>
+      </c>
+      <c r="X169" t="str">
+        <v/>
+      </c>
+      <c r="Y169" t="str">
+        <v/>
+      </c>
+      <c r="Z169" t="str">
+        <v/>
+      </c>
+      <c r="AA169" t="str">
+        <v/>
+      </c>
+      <c r="AB169" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>|אלבום חדש| שלמה גרוניך - כמו כוכבים (2025)</v>
+      </c>
+      <c r="B170" t="str">
+        <v>2025  02:00 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C170" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D170" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E170" t="str">
+        <v/>
+      </c>
+      <c r="F170" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G170" t="str">
+        <v/>
+      </c>
+      <c r="H170" t="str">
+        <v/>
+      </c>
+      <c r="I170" t="str">
+        <v/>
+      </c>
+      <c r="J170" t="str">
+        <v/>
+      </c>
+      <c r="K170" t="str">
+        <v/>
+      </c>
+      <c r="L170" t="str">
+        <v/>
+      </c>
+      <c r="M170" t="str">
+        <v/>
+      </c>
+      <c r="N170" t="str">
+        <v/>
+      </c>
+      <c r="O170" t="str">
+        <v/>
+      </c>
+      <c r="P170" t="str">
+        <v/>
+      </c>
+      <c r="Q170" t="str">
+        <v/>
+      </c>
+      <c r="R170" t="str">
+        <v/>
+      </c>
+      <c r="S170" t="str">
+        <v/>
+      </c>
+      <c r="T170" t="str">
+        <v/>
+      </c>
+      <c r="U170" t="str">
+        <v/>
+      </c>
+      <c r="V170" t="str">
+        <v/>
+      </c>
+      <c r="W170" t="str">
+        <v/>
+      </c>
+      <c r="X170" t="str">
+        <v/>
+      </c>
+      <c r="Y170" t="str">
+        <v/>
+      </c>
+      <c r="Z170" t="str">
+        <v/>
+      </c>
+      <c r="AA170" t="str">
+        <v/>
+      </c>
+      <c r="AB170" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) (2025)</v>
+      </c>
+      <c r="B171" t="str">
+        <v>2025  01:57 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C171" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D171" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E171" t="str">
+        <v/>
+      </c>
+      <c r="F171" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G171" t="str">
+        <v/>
+      </c>
+      <c r="H171" t="str">
+        <v/>
+      </c>
+      <c r="I171" t="str">
+        <v/>
+      </c>
+      <c r="J171" t="str">
+        <v/>
+      </c>
+      <c r="K171" t="str">
+        <v/>
+      </c>
+      <c r="L171" t="str">
+        <v/>
+      </c>
+      <c r="M171" t="str">
+        <v/>
+      </c>
+      <c r="N171" t="str">
+        <v/>
+      </c>
+      <c r="O171" t="str">
+        <v/>
+      </c>
+      <c r="P171" t="str">
+        <v/>
+      </c>
+      <c r="Q171" t="str">
+        <v/>
+      </c>
+      <c r="R171" t="str">
+        <v/>
+      </c>
+      <c r="S171" t="str">
+        <v/>
+      </c>
+      <c r="T171" t="str">
+        <v/>
+      </c>
+      <c r="U171" t="str">
+        <v/>
+      </c>
+      <c r="V171" t="str">
+        <v/>
+      </c>
+      <c r="W171" t="str">
+        <v/>
+      </c>
+      <c r="X171" t="str">
+        <v/>
+      </c>
+      <c r="Y171" t="str">
+        <v/>
+      </c>
+      <c r="Z171" t="str">
+        <v/>
+      </c>
+      <c r="AA171" t="str">
+        <v/>
+      </c>
+      <c r="AB171" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>|אלבום חדש| יוני רועה - מפוזרים (2025)</v>
+      </c>
+      <c r="B172" t="str">
+        <v>2025  01:56 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C172" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D172" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E172" t="str">
+        <v/>
+      </c>
+      <c r="F172" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G172" t="str">
+        <v/>
+      </c>
+      <c r="H172" t="str">
+        <v/>
+      </c>
+      <c r="I172" t="str">
+        <v/>
+      </c>
+      <c r="J172" t="str">
+        <v/>
+      </c>
+      <c r="K172" t="str">
+        <v/>
+      </c>
+      <c r="L172" t="str">
+        <v/>
+      </c>
+      <c r="M172" t="str">
+        <v/>
+      </c>
+      <c r="N172" t="str">
+        <v/>
+      </c>
+      <c r="O172" t="str">
+        <v/>
+      </c>
+      <c r="P172" t="str">
+        <v/>
+      </c>
+      <c r="Q172" t="str">
+        <v/>
+      </c>
+      <c r="R172" t="str">
+        <v/>
+      </c>
+      <c r="S172" t="str">
+        <v/>
+      </c>
+      <c r="T172" t="str">
+        <v/>
+      </c>
+      <c r="U172" t="str">
+        <v/>
+      </c>
+      <c r="V172" t="str">
+        <v/>
+      </c>
+      <c r="W172" t="str">
+        <v/>
+      </c>
+      <c r="X172" t="str">
+        <v/>
+      </c>
+      <c r="Y172" t="str">
+        <v/>
+      </c>
+      <c r="Z172" t="str">
+        <v/>
+      </c>
+      <c r="AA172" t="str">
+        <v/>
+      </c>
+      <c r="AB172" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>|אלבום חדש| אתניקס - איטליה (2025)</v>
+      </c>
+      <c r="B173" t="str">
+        <v>2025  01:55 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C173" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D173" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E173" t="str">
+        <v/>
+      </c>
+      <c r="F173" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G173" t="str">
+        <v/>
+      </c>
+      <c r="H173" t="str">
+        <v/>
+      </c>
+      <c r="I173" t="str">
+        <v/>
+      </c>
+      <c r="J173" t="str">
+        <v/>
+      </c>
+      <c r="K173" t="str">
+        <v/>
+      </c>
+      <c r="L173" t="str">
+        <v/>
+      </c>
+      <c r="M173" t="str">
+        <v/>
+      </c>
+      <c r="N173" t="str">
+        <v/>
+      </c>
+      <c r="O173" t="str">
+        <v/>
+      </c>
+      <c r="P173" t="str">
+        <v/>
+      </c>
+      <c r="Q173" t="str">
+        <v/>
+      </c>
+      <c r="R173" t="str">
+        <v/>
+      </c>
+      <c r="S173" t="str">
+        <v/>
+      </c>
+      <c r="T173" t="str">
+        <v/>
+      </c>
+      <c r="U173" t="str">
+        <v/>
+      </c>
+      <c r="V173" t="str">
+        <v/>
+      </c>
+      <c r="W173" t="str">
+        <v/>
+      </c>
+      <c r="X173" t="str">
+        <v/>
+      </c>
+      <c r="Y173" t="str">
+        <v/>
+      </c>
+      <c r="Z173" t="str">
+        <v/>
+      </c>
+      <c r="AA173" t="str">
+        <v/>
+      </c>
+      <c r="AB173" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>|אלבום חדש| התקווה 6 - ויהי אור (2025)</v>
+      </c>
+      <c r="B174" t="str">
+        <v>2025  01:54 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C174" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D174" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E174" t="str">
+        <v/>
+      </c>
+      <c r="F174" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G174" t="str">
+        <v/>
+      </c>
+      <c r="H174" t="str">
+        <v/>
+      </c>
+      <c r="I174" t="str">
+        <v/>
+      </c>
+      <c r="J174" t="str">
+        <v/>
+      </c>
+      <c r="K174" t="str">
+        <v/>
+      </c>
+      <c r="L174" t="str">
+        <v/>
+      </c>
+      <c r="M174" t="str">
+        <v/>
+      </c>
+      <c r="N174" t="str">
+        <v/>
+      </c>
+      <c r="O174" t="str">
+        <v/>
+      </c>
+      <c r="P174" t="str">
+        <v/>
+      </c>
+      <c r="Q174" t="str">
+        <v/>
+      </c>
+      <c r="R174" t="str">
+        <v/>
+      </c>
+      <c r="S174" t="str">
+        <v/>
+      </c>
+      <c r="T174" t="str">
+        <v/>
+      </c>
+      <c r="U174" t="str">
+        <v/>
+      </c>
+      <c r="V174" t="str">
+        <v/>
+      </c>
+      <c r="W174" t="str">
+        <v/>
+      </c>
+      <c r="X174" t="str">
+        <v/>
+      </c>
+      <c r="Y174" t="str">
+        <v/>
+      </c>
+      <c r="Z174" t="str">
+        <v/>
+      </c>
+      <c r="AA174" t="str">
+        <v/>
+      </c>
+      <c r="AB174" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>|אלבום חדש| שלומי סרנגה - איפרכו (2025)</v>
+      </c>
+      <c r="B175" t="str">
+        <v>2025  01:53 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C175" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24430&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D175" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E175" t="str">
+        <v/>
+      </c>
+      <c r="F175" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G175" t="str">
+        <v/>
+      </c>
+      <c r="H175" t="str">
+        <v/>
+      </c>
+      <c r="I175" t="str">
+        <v/>
+      </c>
+      <c r="J175" t="str">
+        <v/>
+      </c>
+      <c r="K175" t="str">
+        <v/>
+      </c>
+      <c r="L175" t="str">
+        <v/>
+      </c>
+      <c r="M175" t="str">
+        <v/>
+      </c>
+      <c r="N175" t="str">
+        <v/>
+      </c>
+      <c r="O175" t="str">
+        <v/>
+      </c>
+      <c r="P175" t="str">
+        <v/>
+      </c>
+      <c r="Q175" t="str">
+        <v/>
+      </c>
+      <c r="R175" t="str">
+        <v/>
+      </c>
+      <c r="S175" t="str">
+        <v/>
+      </c>
+      <c r="T175" t="str">
+        <v/>
+      </c>
+      <c r="U175" t="str">
+        <v/>
+      </c>
+      <c r="V175" t="str">
+        <v/>
+      </c>
+      <c r="W175" t="str">
+        <v/>
+      </c>
+      <c r="X175" t="str">
+        <v/>
+      </c>
+      <c r="Y175" t="str">
+        <v/>
+      </c>
+      <c r="Z175" t="str">
+        <v/>
+      </c>
+      <c r="AA175" t="str">
+        <v/>
+      </c>
+      <c r="AB175" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>|אלבום חדש| שאנן סטריט ודי ג׳יי מש - באתי לבדר (2025)</v>
+      </c>
+      <c r="B176" t="str">
+        <v>2025  01:53 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C176" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D176" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E176" t="str">
+        <v/>
+      </c>
+      <c r="F176" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G176" t="str">
+        <v/>
+      </c>
+      <c r="H176" t="str">
+        <v/>
+      </c>
+      <c r="I176" t="str">
+        <v/>
+      </c>
+      <c r="J176" t="str">
+        <v/>
+      </c>
+      <c r="K176" t="str">
+        <v/>
+      </c>
+      <c r="L176" t="str">
+        <v/>
+      </c>
+      <c r="M176" t="str">
+        <v/>
+      </c>
+      <c r="N176" t="str">
+        <v/>
+      </c>
+      <c r="O176" t="str">
+        <v/>
+      </c>
+      <c r="P176" t="str">
+        <v/>
+      </c>
+      <c r="Q176" t="str">
+        <v/>
+      </c>
+      <c r="R176" t="str">
+        <v/>
+      </c>
+      <c r="S176" t="str">
+        <v/>
+      </c>
+      <c r="T176" t="str">
+        <v/>
+      </c>
+      <c r="U176" t="str">
+        <v/>
+      </c>
+      <c r="V176" t="str">
+        <v/>
+      </c>
+      <c r="W176" t="str">
+        <v/>
+      </c>
+      <c r="X176" t="str">
+        <v/>
+      </c>
+      <c r="Y176" t="str">
+        <v/>
+      </c>
+      <c r="Z176" t="str">
+        <v/>
+      </c>
+      <c r="AA176" t="str">
+        <v/>
+      </c>
+      <c r="AB176" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>הרשם לחברות מלאה</v>
+      </c>
+      <c r="B177" t="str">
+        <v/>
+      </c>
+      <c r="C177" t="str">
+        <v>https://rotter.name/nor/members-new.html</v>
+      </c>
+      <c r="D177" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E177" t="str">
+        <v/>
+      </c>
+      <c r="F177" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G177" t="str">
+        <v/>
+      </c>
+      <c r="H177" t="str">
+        <v/>
+      </c>
+      <c r="I177" t="str">
+        <v/>
+      </c>
+      <c r="J177" t="str">
+        <v/>
+      </c>
+      <c r="K177" t="str">
+        <v/>
+      </c>
+      <c r="L177" t="str">
+        <v/>
+      </c>
+      <c r="M177" t="str">
+        <v/>
+      </c>
+      <c r="N177" t="str">
+        <v/>
+      </c>
+      <c r="O177" t="str">
+        <v/>
+      </c>
+      <c r="P177" t="str">
+        <v/>
+      </c>
+      <c r="Q177" t="str">
+        <v/>
+      </c>
+      <c r="R177" t="str">
+        <v/>
+      </c>
+      <c r="S177" t="str">
+        <v/>
+      </c>
+      <c r="T177" t="str">
+        <v/>
+      </c>
+      <c r="U177" t="str">
+        <v/>
+      </c>
+      <c r="V177" t="str">
+        <v/>
+      </c>
+      <c r="W177" t="str">
+        <v/>
+      </c>
+      <c r="X177" t="str">
+        <v/>
+      </c>
+      <c r="Y177" t="str">
+        <v/>
+      </c>
+      <c r="Z177" t="str">
+        <v/>
+      </c>
+      <c r="AA177" t="str">
+        <v/>
+      </c>
+      <c r="AB177" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>אוליביה דין The Art of Loving</v>
+      </c>
+      <c r="B178" t="str">
+        <v>2026-01-04</v>
+      </c>
+      <c r="C178" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
+      </c>
+      <c r="D178" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E178" t="str">
+        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
+      </c>
+      <c r="F178" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G178" t="str">
+        <v/>
+      </c>
+      <c r="H178" t="str">
+        <v/>
+      </c>
+      <c r="I178" t="str">
+        <v/>
+      </c>
+      <c r="J178" t="str">
+        <v/>
+      </c>
+      <c r="K178" t="str">
+        <v/>
+      </c>
+      <c r="L178" t="str">
+        <v/>
+      </c>
+      <c r="M178" t="str">
+        <v/>
+      </c>
+      <c r="N178" t="str">
+        <v/>
+      </c>
+      <c r="O178" t="str">
+        <v/>
+      </c>
+      <c r="P178" t="str">
+        <v/>
+      </c>
+      <c r="Q178" t="str">
+        <v/>
+      </c>
+      <c r="R178" t="str">
+        <v/>
+      </c>
+      <c r="S178" t="str">
+        <v/>
+      </c>
+      <c r="T178" t="str">
+        <v/>
+      </c>
+      <c r="U178" t="str">
+        <v/>
+      </c>
+      <c r="V178" t="str">
+        <v/>
+      </c>
+      <c r="W178" t="str">
+        <v/>
+      </c>
+      <c r="X178" t="str">
+        <v/>
+      </c>
+      <c r="Y178" t="str">
+        <v/>
+      </c>
+      <c r="Z178" t="str">
+        <v/>
+      </c>
+      <c r="AA178" t="str">
+        <v/>
+      </c>
+      <c r="AB178" t="str">
+        <v/>
+      </c>
+      <c r="AC178" t="str">
+        <v/>
+      </c>
+      <c r="AD178" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>Geese Getting Killed</v>
+      </c>
+      <c r="B179" t="str">
+        <v>2025-12-29</v>
+      </c>
+      <c r="C179" t="str">
+        <v>https://yosmusic.com/geese-getting-killed/</v>
+      </c>
+      <c r="D179" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E179" t="str">
+        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
+      </c>
+      <c r="F179" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G179" t="str">
+        <v/>
+      </c>
+      <c r="H179" t="str">
+        <v/>
+      </c>
+      <c r="I179" t="str">
+        <v/>
+      </c>
+      <c r="J179" t="str">
+        <v/>
+      </c>
+      <c r="K179" t="str">
+        <v/>
+      </c>
+      <c r="L179" t="str">
+        <v/>
+      </c>
+      <c r="M179" t="str">
+        <v/>
+      </c>
+      <c r="N179" t="str">
+        <v/>
+      </c>
+      <c r="O179" t="str">
+        <v/>
+      </c>
+      <c r="P179" t="str">
+        <v/>
+      </c>
+      <c r="Q179" t="str">
+        <v/>
+      </c>
+      <c r="R179" t="str">
+        <v/>
+      </c>
+      <c r="S179" t="str">
+        <v/>
+      </c>
+      <c r="T179" t="str">
+        <v/>
+      </c>
+      <c r="U179" t="str">
+        <v/>
+      </c>
+      <c r="V179" t="str">
+        <v/>
+      </c>
+      <c r="W179" t="str">
+        <v/>
+      </c>
+      <c r="X179" t="str">
+        <v/>
+      </c>
+      <c r="Y179" t="str">
+        <v/>
+      </c>
+      <c r="Z179" t="str">
+        <v/>
+      </c>
+      <c r="AA179" t="str">
+        <v/>
+      </c>
+      <c r="AB179" t="str">
+        <v/>
+      </c>
+      <c r="AC179" t="str">
+        <v/>
+      </c>
+      <c r="AD179" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>רוסליה Lux</v>
+      </c>
+      <c r="B180" t="str">
+        <v>2025-12-25</v>
+      </c>
+      <c r="C180" t="str">
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
+      </c>
+      <c r="D180" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E180" t="str">
+        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
+      </c>
+      <c r="F180" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G180" t="str">
+        <v/>
+      </c>
+      <c r="H180" t="str">
+        <v/>
+      </c>
+      <c r="I180" t="str">
+        <v/>
+      </c>
+      <c r="J180" t="str">
+        <v/>
+      </c>
+      <c r="K180" t="str">
+        <v/>
+      </c>
+      <c r="L180" t="str">
+        <v/>
+      </c>
+      <c r="M180" t="str">
+        <v/>
+      </c>
+      <c r="N180" t="str">
+        <v/>
+      </c>
+      <c r="O180" t="str">
+        <v/>
+      </c>
+      <c r="P180" t="str">
+        <v/>
+      </c>
+      <c r="Q180" t="str">
+        <v/>
+      </c>
+      <c r="R180" t="str">
+        <v/>
+      </c>
+      <c r="S180" t="str">
+        <v/>
+      </c>
+      <c r="T180" t="str">
+        <v/>
+      </c>
+      <c r="U180" t="str">
+        <v/>
+      </c>
+      <c r="V180" t="str">
+        <v/>
+      </c>
+      <c r="W180" t="str">
+        <v/>
+      </c>
+      <c r="X180" t="str">
+        <v/>
+      </c>
+      <c r="Y180" t="str">
+        <v/>
+      </c>
+      <c r="Z180" t="str">
+        <v/>
+      </c>
+      <c r="AA180" t="str">
+        <v/>
+      </c>
+      <c r="AB180" t="str">
+        <v/>
+      </c>
+      <c r="AC180" t="str">
+        <v/>
+      </c>
+      <c r="AD180" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>יאנגבלאד אירוסמית' one more time</v>
+      </c>
+      <c r="B181" t="str">
+        <v>2025-12-17</v>
+      </c>
+      <c r="C181" t="str">
+        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
+      </c>
+      <c r="D181" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E181" t="str">
+        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
+      </c>
+      <c r="F181" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G181" t="str">
+        <v/>
+      </c>
+      <c r="H181" t="str">
+        <v/>
+      </c>
+      <c r="I181" t="str">
+        <v/>
+      </c>
+      <c r="J181" t="str">
+        <v/>
+      </c>
+      <c r="K181" t="str">
+        <v/>
+      </c>
+      <c r="L181" t="str">
+        <v/>
+      </c>
+      <c r="M181" t="str">
+        <v/>
+      </c>
+      <c r="N181" t="str">
+        <v/>
+      </c>
+      <c r="O181" t="str">
+        <v/>
+      </c>
+      <c r="P181" t="str">
+        <v/>
+      </c>
+      <c r="Q181" t="str">
+        <v/>
+      </c>
+      <c r="R181" t="str">
+        <v/>
+      </c>
+      <c r="S181" t="str">
+        <v/>
+      </c>
+      <c r="T181" t="str">
+        <v/>
+      </c>
+      <c r="U181" t="str">
+        <v/>
+      </c>
+      <c r="V181" t="str">
+        <v/>
+      </c>
+      <c r="W181" t="str">
+        <v/>
+      </c>
+      <c r="X181" t="str">
+        <v/>
+      </c>
+      <c r="Y181" t="str">
+        <v/>
+      </c>
+      <c r="Z181" t="str">
+        <v/>
+      </c>
+      <c r="AA181" t="str">
+        <v/>
+      </c>
+      <c r="AB181" t="str">
+        <v/>
+      </c>
+      <c r="AC181" t="str">
+        <v/>
+      </c>
+      <c r="AD181" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>פינק פלויד Wish You Were Here 50</v>
+      </c>
+      <c r="B182" t="str">
+        <v>2025-12-14</v>
+      </c>
+      <c r="C182" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
+      </c>
+      <c r="D182" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E182" t="str">
+        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
+      </c>
+      <c r="F182" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G182" t="str">
+        <v/>
+      </c>
+      <c r="H182" t="str">
+        <v/>
+      </c>
+      <c r="I182" t="str">
+        <v/>
+      </c>
+      <c r="J182" t="str">
+        <v/>
+      </c>
+      <c r="K182" t="str">
+        <v/>
+      </c>
+      <c r="L182" t="str">
+        <v/>
+      </c>
+      <c r="M182" t="str">
+        <v/>
+      </c>
+      <c r="N182" t="str">
+        <v/>
+      </c>
+      <c r="O182" t="str">
+        <v/>
+      </c>
+      <c r="P182" t="str">
+        <v/>
+      </c>
+      <c r="Q182" t="str">
+        <v/>
+      </c>
+      <c r="R182" t="str">
+        <v/>
+      </c>
+      <c r="S182" t="str">
+        <v/>
+      </c>
+      <c r="T182" t="str">
+        <v/>
+      </c>
+      <c r="U182" t="str">
+        <v/>
+      </c>
+      <c r="V182" t="str">
+        <v/>
+      </c>
+      <c r="W182" t="str">
+        <v/>
+      </c>
+      <c r="X182" t="str">
+        <v/>
+      </c>
+      <c r="Y182" t="str">
+        <v/>
+      </c>
+      <c r="Z182" t="str">
+        <v/>
+      </c>
+      <c r="AA182" t="str">
+        <v/>
+      </c>
+      <c r="AB182" t="str">
+        <v/>
+      </c>
+      <c r="AC182" t="str">
+        <v/>
+      </c>
+      <c r="AD182" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+      </c>
+      <c r="B183" t="str">
+        <v>2025-12-08</v>
+      </c>
+      <c r="C183" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
+      </c>
+      <c r="D183" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E183" t="str">
+        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
+      </c>
+      <c r="F183" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G183" t="str">
+        <v/>
+      </c>
+      <c r="H183" t="str">
+        <v/>
+      </c>
+      <c r="I183" t="str">
+        <v/>
+      </c>
+      <c r="J183" t="str">
+        <v/>
+      </c>
+      <c r="K183" t="str">
+        <v/>
+      </c>
+      <c r="L183" t="str">
+        <v/>
+      </c>
+      <c r="M183" t="str">
+        <v/>
+      </c>
+      <c r="N183" t="str">
+        <v/>
+      </c>
+      <c r="O183" t="str">
+        <v/>
+      </c>
+      <c r="P183" t="str">
+        <v/>
+      </c>
+      <c r="Q183" t="str">
+        <v/>
+      </c>
+      <c r="R183" t="str">
+        <v/>
+      </c>
+      <c r="S183" t="str">
+        <v/>
+      </c>
+      <c r="T183" t="str">
+        <v/>
+      </c>
+      <c r="U183" t="str">
+        <v/>
+      </c>
+      <c r="V183" t="str">
+        <v/>
+      </c>
+      <c r="W183" t="str">
+        <v/>
+      </c>
+      <c r="X183" t="str">
+        <v/>
+      </c>
+      <c r="Y183" t="str">
+        <v/>
+      </c>
+      <c r="Z183" t="str">
+        <v/>
+      </c>
+      <c r="AA183" t="str">
+        <v/>
+      </c>
+      <c r="AB183" t="str">
+        <v/>
+      </c>
+      <c r="AC183" t="str">
+        <v/>
+      </c>
+      <c r="AD183" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>סטריי קידס DO IT (EP)</v>
+      </c>
+      <c r="B184" t="str">
+        <v>2025-12-04</v>
+      </c>
+      <c r="C184" t="str">
+        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
+      </c>
+      <c r="D184" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E184" t="str">
+        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
+      </c>
+      <c r="F184" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G184" t="str">
+        <v/>
+      </c>
+      <c r="H184" t="str">
+        <v/>
+      </c>
+      <c r="I184" t="str">
+        <v/>
+      </c>
+      <c r="J184" t="str">
+        <v/>
+      </c>
+      <c r="K184" t="str">
+        <v/>
+      </c>
+      <c r="L184" t="str">
+        <v/>
+      </c>
+      <c r="M184" t="str">
+        <v/>
+      </c>
+      <c r="N184" t="str">
+        <v/>
+      </c>
+      <c r="O184" t="str">
+        <v/>
+      </c>
+      <c r="P184" t="str">
+        <v/>
+      </c>
+      <c r="Q184" t="str">
+        <v/>
+      </c>
+      <c r="R184" t="str">
+        <v/>
+      </c>
+      <c r="S184" t="str">
+        <v/>
+      </c>
+      <c r="T184" t="str">
+        <v/>
+      </c>
+      <c r="U184" t="str">
+        <v/>
+      </c>
+      <c r="V184" t="str">
+        <v/>
+      </c>
+      <c r="W184" t="str">
+        <v/>
+      </c>
+      <c r="X184" t="str">
+        <v/>
+      </c>
+      <c r="Y184" t="str">
+        <v/>
+      </c>
+      <c r="Z184" t="str">
+        <v/>
+      </c>
+      <c r="AA184" t="str">
+        <v/>
+      </c>
+      <c r="AB184" t="str">
+        <v/>
+      </c>
+      <c r="AC184" t="str">
+        <v/>
+      </c>
+      <c r="AD184" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>דויד ברוזה BROZAJAZZ</v>
+      </c>
+      <c r="B185" t="str">
+        <v>2025-11-30</v>
+      </c>
+      <c r="C185" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
+      </c>
+      <c r="D185" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E185" t="str">
+        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
+      </c>
+      <c r="F185" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G185" t="str">
+        <v/>
+      </c>
+      <c r="H185" t="str">
+        <v/>
+      </c>
+      <c r="I185" t="str">
+        <v/>
+      </c>
+      <c r="J185" t="str">
+        <v/>
+      </c>
+      <c r="K185" t="str">
+        <v/>
+      </c>
+      <c r="L185" t="str">
+        <v/>
+      </c>
+      <c r="M185" t="str">
+        <v/>
+      </c>
+      <c r="N185" t="str">
+        <v/>
+      </c>
+      <c r="O185" t="str">
+        <v/>
+      </c>
+      <c r="P185" t="str">
+        <v/>
+      </c>
+      <c r="Q185" t="str">
+        <v/>
+      </c>
+      <c r="R185" t="str">
+        <v/>
+      </c>
+      <c r="S185" t="str">
+        <v/>
+      </c>
+      <c r="T185" t="str">
+        <v/>
+      </c>
+      <c r="U185" t="str">
+        <v/>
+      </c>
+      <c r="V185" t="str">
+        <v/>
+      </c>
+      <c r="W185" t="str">
+        <v/>
+      </c>
+      <c r="X185" t="str">
+        <v/>
+      </c>
+      <c r="Y185" t="str">
+        <v/>
+      </c>
+      <c r="Z185" t="str">
+        <v/>
+      </c>
+      <c r="AA185" t="str">
+        <v/>
+      </c>
+      <c r="AB185" t="str">
+        <v/>
+      </c>
+      <c r="AC185" t="str">
+        <v/>
+      </c>
+      <c r="AD185" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>Five Seconds of Summer – Everyone's A Star</v>
+      </c>
+      <c r="B186" t="str">
+        <v>2025-11-24</v>
+      </c>
+      <c r="C186" t="str">
+        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
+      </c>
+      <c r="D186" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E186" t="str">
+        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
+      </c>
+      <c r="F186" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G186" t="str">
+        <v/>
+      </c>
+      <c r="H186" t="str">
+        <v/>
+      </c>
+      <c r="I186" t="str">
+        <v/>
+      </c>
+      <c r="J186" t="str">
+        <v/>
+      </c>
+      <c r="K186" t="str">
+        <v/>
+      </c>
+      <c r="L186" t="str">
+        <v/>
+      </c>
+      <c r="M186" t="str">
+        <v/>
+      </c>
+      <c r="N186" t="str">
+        <v/>
+      </c>
+      <c r="O186" t="str">
+        <v/>
+      </c>
+      <c r="P186" t="str">
+        <v/>
+      </c>
+      <c r="Q186" t="str">
+        <v/>
+      </c>
+      <c r="R186" t="str">
+        <v/>
+      </c>
+      <c r="S186" t="str">
+        <v/>
+      </c>
+      <c r="T186" t="str">
+        <v/>
+      </c>
+      <c r="U186" t="str">
+        <v/>
+      </c>
+      <c r="V186" t="str">
+        <v/>
+      </c>
+      <c r="W186" t="str">
+        <v/>
+      </c>
+      <c r="X186" t="str">
+        <v/>
+      </c>
+      <c r="Y186" t="str">
+        <v/>
+      </c>
+      <c r="Z186" t="str">
+        <v/>
+      </c>
+      <c r="AA186" t="str">
+        <v/>
+      </c>
+      <c r="AB186" t="str">
+        <v/>
+      </c>
+      <c r="AC186" t="str">
+        <v/>
+      </c>
+      <c r="AD186" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>התקווה 6 – ויהי אור</v>
+      </c>
+      <c r="B187" t="str">
+        <v>2025-11-20</v>
+      </c>
+      <c r="C187" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
+      </c>
+      <c r="D187" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E187" t="str">
+        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
+      </c>
+      <c r="F187" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G187" t="str">
+        <v/>
+      </c>
+      <c r="H187" t="str">
+        <v/>
+      </c>
+      <c r="I187" t="str">
+        <v/>
+      </c>
+      <c r="J187" t="str">
+        <v/>
+      </c>
+      <c r="K187" t="str">
+        <v/>
+      </c>
+      <c r="L187" t="str">
+        <v/>
+      </c>
+      <c r="M187" t="str">
+        <v/>
+      </c>
+      <c r="N187" t="str">
+        <v/>
+      </c>
+      <c r="O187" t="str">
+        <v/>
+      </c>
+      <c r="P187" t="str">
+        <v/>
+      </c>
+      <c r="Q187" t="str">
+        <v/>
+      </c>
+      <c r="R187" t="str">
+        <v/>
+      </c>
+      <c r="S187" t="str">
+        <v/>
+      </c>
+      <c r="T187" t="str">
+        <v/>
+      </c>
+      <c r="U187" t="str">
+        <v/>
+      </c>
+      <c r="V187" t="str">
+        <v/>
+      </c>
+      <c r="W187" t="str">
+        <v/>
+      </c>
+      <c r="X187" t="str">
+        <v/>
+      </c>
+      <c r="Y187" t="str">
+        <v/>
+      </c>
+      <c r="Z187" t="str">
+        <v/>
+      </c>
+      <c r="AA187" t="str">
+        <v/>
+      </c>
+      <c r="AB187" t="str">
+        <v/>
+      </c>
+      <c r="AC187" t="str">
+        <v/>
+      </c>
+      <c r="AD187" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>פלורנס אנד דה משין Everybody Scream</v>
+      </c>
+      <c r="B188" t="str">
+        <v>2025-11-13</v>
+      </c>
+      <c r="C188" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
+      </c>
+      <c r="D188" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E188" t="str">
+        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
+      </c>
+      <c r="F188" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G188" t="str">
+        <v/>
+      </c>
+      <c r="H188" t="str">
+        <v/>
+      </c>
+      <c r="I188" t="str">
+        <v/>
+      </c>
+      <c r="J188" t="str">
+        <v/>
+      </c>
+      <c r="K188" t="str">
+        <v/>
+      </c>
+      <c r="L188" t="str">
+        <v/>
+      </c>
+      <c r="M188" t="str">
+        <v/>
+      </c>
+      <c r="N188" t="str">
+        <v/>
+      </c>
+      <c r="O188" t="str">
+        <v/>
+      </c>
+      <c r="P188" t="str">
+        <v/>
+      </c>
+      <c r="Q188" t="str">
+        <v/>
+      </c>
+      <c r="R188" t="str">
+        <v/>
+      </c>
+      <c r="S188" t="str">
+        <v/>
+      </c>
+      <c r="T188" t="str">
+        <v/>
+      </c>
+      <c r="U188" t="str">
+        <v/>
+      </c>
+      <c r="V188" t="str">
+        <v/>
+      </c>
+      <c r="W188" t="str">
+        <v/>
+      </c>
+      <c r="X188" t="str">
+        <v/>
+      </c>
+      <c r="Y188" t="str">
+        <v/>
+      </c>
+      <c r="Z188" t="str">
+        <v/>
+      </c>
+      <c r="AA188" t="str">
+        <v/>
+      </c>
+      <c r="AB188" t="str">
+        <v/>
+      </c>
+      <c r="AC188" t="str">
+        <v/>
+      </c>
+      <c r="AD188" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>טיים אימפלה Deadbeat</v>
+      </c>
+      <c r="B189" t="str">
+        <v>2025-11-03</v>
+      </c>
+      <c r="C189" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
+      </c>
+      <c r="D189" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E189" t="str">
+        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
+      </c>
+      <c r="F189" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G189" t="str">
+        <v/>
+      </c>
+      <c r="H189" t="str">
+        <v/>
+      </c>
+      <c r="I189" t="str">
+        <v/>
+      </c>
+      <c r="J189" t="str">
+        <v/>
+      </c>
+      <c r="K189" t="str">
+        <v/>
+      </c>
+      <c r="L189" t="str">
+        <v/>
+      </c>
+      <c r="M189" t="str">
+        <v/>
+      </c>
+      <c r="N189" t="str">
+        <v/>
+      </c>
+      <c r="O189" t="str">
+        <v/>
+      </c>
+      <c r="P189" t="str">
+        <v/>
+      </c>
+      <c r="Q189" t="str">
+        <v/>
+      </c>
+      <c r="R189" t="str">
+        <v/>
+      </c>
+      <c r="S189" t="str">
+        <v/>
+      </c>
+      <c r="T189" t="str">
+        <v/>
+      </c>
+      <c r="U189" t="str">
+        <v/>
+      </c>
+      <c r="V189" t="str">
+        <v/>
+      </c>
+      <c r="W189" t="str">
+        <v/>
+      </c>
+      <c r="X189" t="str">
+        <v/>
+      </c>
+      <c r="Y189" t="str">
+        <v/>
+      </c>
+      <c r="Z189" t="str">
+        <v/>
+      </c>
+      <c r="AA189" t="str">
+        <v/>
+      </c>
+      <c r="AB189" t="str">
+        <v/>
+      </c>
+      <c r="AC189" t="str">
+        <v/>
+      </c>
+      <c r="AD189" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+      </c>
+      <c r="B190" t="str">
+        <v>2025-10-20</v>
+      </c>
+      <c r="C190" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
+      </c>
+      <c r="D190" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E190" t="str">
+        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
+      </c>
+      <c r="F190" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G190" t="str">
+        <v/>
+      </c>
+      <c r="H190" t="str">
+        <v/>
+      </c>
+      <c r="I190" t="str">
+        <v/>
+      </c>
+      <c r="J190" t="str">
+        <v/>
+      </c>
+      <c r="K190" t="str">
+        <v/>
+      </c>
+      <c r="L190" t="str">
+        <v/>
+      </c>
+      <c r="M190" t="str">
+        <v/>
+      </c>
+      <c r="N190" t="str">
+        <v/>
+      </c>
+      <c r="O190" t="str">
+        <v/>
+      </c>
+      <c r="P190" t="str">
+        <v/>
+      </c>
+      <c r="Q190" t="str">
+        <v/>
+      </c>
+      <c r="R190" t="str">
+        <v/>
+      </c>
+      <c r="S190" t="str">
+        <v/>
+      </c>
+      <c r="T190" t="str">
+        <v/>
+      </c>
+      <c r="U190" t="str">
+        <v/>
+      </c>
+      <c r="V190" t="str">
+        <v/>
+      </c>
+      <c r="W190" t="str">
+        <v/>
+      </c>
+      <c r="X190" t="str">
+        <v/>
+      </c>
+      <c r="Y190" t="str">
+        <v/>
+      </c>
+      <c r="Z190" t="str">
+        <v/>
+      </c>
+      <c r="AA190" t="str">
+        <v/>
+      </c>
+      <c r="AB190" t="str">
+        <v/>
+      </c>
+      <c r="AC190" t="str">
+        <v/>
+      </c>
+      <c r="AD190" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>שלמה גרוניך – תודה אהבה</v>
+      </c>
+      <c r="B191" t="str">
+        <v>2025-10-18</v>
+      </c>
+      <c r="C191" t="str">
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
+      </c>
+      <c r="D191" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E191" t="str">
+        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
+      </c>
+      <c r="F191" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G191" t="str">
+        <v/>
+      </c>
+      <c r="H191" t="str">
+        <v/>
+      </c>
+      <c r="I191" t="str">
+        <v/>
+      </c>
+      <c r="J191" t="str">
+        <v/>
+      </c>
+      <c r="K191" t="str">
+        <v/>
+      </c>
+      <c r="L191" t="str">
+        <v/>
+      </c>
+      <c r="M191" t="str">
+        <v/>
+      </c>
+      <c r="N191" t="str">
+        <v/>
+      </c>
+      <c r="O191" t="str">
+        <v/>
+      </c>
+      <c r="P191" t="str">
+        <v/>
+      </c>
+      <c r="Q191" t="str">
+        <v/>
+      </c>
+      <c r="R191" t="str">
+        <v/>
+      </c>
+      <c r="S191" t="str">
+        <v/>
+      </c>
+      <c r="T191" t="str">
+        <v/>
+      </c>
+      <c r="U191" t="str">
+        <v/>
+      </c>
+      <c r="V191" t="str">
+        <v/>
+      </c>
+      <c r="W191" t="str">
+        <v/>
+      </c>
+      <c r="X191" t="str">
+        <v/>
+      </c>
+      <c r="Y191" t="str">
+        <v/>
+      </c>
+      <c r="Z191" t="str">
+        <v/>
+      </c>
+      <c r="AA191" t="str">
+        <v/>
+      </c>
+      <c r="AB191" t="str">
+        <v/>
+      </c>
+      <c r="AC191" t="str">
+        <v/>
+      </c>
+      <c r="AD191" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
+      </c>
+      <c r="B192" t="str">
+        <v>2025-10-11</v>
+      </c>
+      <c r="C192" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
+      </c>
+      <c r="D192" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E192" t="str">
+        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
+      </c>
+      <c r="F192" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G192" t="str">
+        <v/>
+      </c>
+      <c r="H192" t="str">
+        <v/>
+      </c>
+      <c r="I192" t="str">
+        <v/>
+      </c>
+      <c r="J192" t="str">
+        <v/>
+      </c>
+      <c r="K192" t="str">
+        <v/>
+      </c>
+      <c r="L192" t="str">
+        <v/>
+      </c>
+      <c r="M192" t="str">
+        <v/>
+      </c>
+      <c r="N192" t="str">
+        <v/>
+      </c>
+      <c r="O192" t="str">
+        <v/>
+      </c>
+      <c r="P192" t="str">
+        <v/>
+      </c>
+      <c r="Q192" t="str">
+        <v/>
+      </c>
+      <c r="R192" t="str">
+        <v/>
+      </c>
+      <c r="S192" t="str">
+        <v/>
+      </c>
+      <c r="T192" t="str">
+        <v/>
+      </c>
+      <c r="U192" t="str">
+        <v/>
+      </c>
+      <c r="V192" t="str">
+        <v/>
+      </c>
+      <c r="W192" t="str">
+        <v/>
+      </c>
+      <c r="X192" t="str">
+        <v/>
+      </c>
+      <c r="Y192" t="str">
+        <v/>
+      </c>
+      <c r="Z192" t="str">
+        <v/>
+      </c>
+      <c r="AA192" t="str">
+        <v/>
+      </c>
+      <c r="AB192" t="str">
+        <v/>
+      </c>
+      <c r="AC192" t="str">
+        <v/>
+      </c>
+      <c r="AD192" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>דוג'ה קאט Vie</v>
+      </c>
+      <c r="B193" t="str">
+        <v>2025-10-04</v>
+      </c>
+      <c r="C193" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
+      </c>
+      <c r="D193" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E193" t="str">
+        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
+      </c>
+      <c r="F193" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G193" t="str">
+        <v/>
+      </c>
+      <c r="H193" t="str">
+        <v/>
+      </c>
+      <c r="I193" t="str">
+        <v/>
+      </c>
+      <c r="J193" t="str">
+        <v/>
+      </c>
+      <c r="K193" t="str">
+        <v/>
+      </c>
+      <c r="L193" t="str">
+        <v/>
+      </c>
+      <c r="M193" t="str">
+        <v/>
+      </c>
+      <c r="N193" t="str">
+        <v/>
+      </c>
+      <c r="O193" t="str">
+        <v/>
+      </c>
+      <c r="P193" t="str">
+        <v/>
+      </c>
+      <c r="Q193" t="str">
+        <v/>
+      </c>
+      <c r="R193" t="str">
+        <v/>
+      </c>
+      <c r="S193" t="str">
+        <v/>
+      </c>
+      <c r="T193" t="str">
+        <v/>
+      </c>
+      <c r="U193" t="str">
+        <v/>
+      </c>
+      <c r="V193" t="str">
+        <v/>
+      </c>
+      <c r="W193" t="str">
+        <v/>
+      </c>
+      <c r="X193" t="str">
+        <v/>
+      </c>
+      <c r="Y193" t="str">
+        <v/>
+      </c>
+      <c r="Z193" t="str">
+        <v/>
+      </c>
+      <c r="AA193" t="str">
+        <v/>
+      </c>
+      <c r="AB193" t="str">
+        <v/>
+      </c>
+      <c r="AC193" t="str">
+        <v/>
+      </c>
+      <c r="AD193" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>ג'וי קרוקס Juniper</v>
+      </c>
+      <c r="B194" t="str">
+        <v>2025-10-03</v>
+      </c>
+      <c r="C194" t="str">
+        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
+      </c>
+      <c r="D194" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E194" t="str">
+        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
+      </c>
+      <c r="F194" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G194" t="str">
+        <v/>
+      </c>
+      <c r="H194" t="str">
+        <v/>
+      </c>
+      <c r="I194" t="str">
+        <v/>
+      </c>
+      <c r="J194" t="str">
+        <v/>
+      </c>
+      <c r="K194" t="str">
+        <v/>
+      </c>
+      <c r="L194" t="str">
+        <v/>
+      </c>
+      <c r="M194" t="str">
+        <v/>
+      </c>
+      <c r="N194" t="str">
+        <v/>
+      </c>
+      <c r="O194" t="str">
+        <v/>
+      </c>
+      <c r="P194" t="str">
+        <v/>
+      </c>
+      <c r="Q194" t="str">
+        <v/>
+      </c>
+      <c r="R194" t="str">
+        <v/>
+      </c>
+      <c r="S194" t="str">
+        <v/>
+      </c>
+      <c r="T194" t="str">
+        <v/>
+      </c>
+      <c r="U194" t="str">
+        <v/>
+      </c>
+      <c r="V194" t="str">
+        <v/>
+      </c>
+      <c r="W194" t="str">
+        <v/>
+      </c>
+      <c r="X194" t="str">
+        <v/>
+      </c>
+      <c r="Y194" t="str">
+        <v/>
+      </c>
+      <c r="Z194" t="str">
+        <v/>
+      </c>
+      <c r="AA194" t="str">
+        <v/>
+      </c>
+      <c r="AB194" t="str">
+        <v/>
+      </c>
+      <c r="AC194" t="str">
+        <v/>
+      </c>
+      <c r="AD194" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>ביפי קליירו Futique</v>
+      </c>
+      <c r="B195" t="str">
+        <v>2025-09-30</v>
+      </c>
+      <c r="C195" t="str">
+        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
+      </c>
+      <c r="D195" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E195" t="str">
+        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
+      </c>
+      <c r="F195" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G195" t="str">
+        <v/>
+      </c>
+      <c r="H195" t="str">
+        <v/>
+      </c>
+      <c r="I195" t="str">
+        <v/>
+      </c>
+      <c r="J195" t="str">
+        <v/>
+      </c>
+      <c r="K195" t="str">
+        <v/>
+      </c>
+      <c r="L195" t="str">
+        <v/>
+      </c>
+      <c r="M195" t="str">
+        <v/>
+      </c>
+      <c r="N195" t="str">
+        <v/>
+      </c>
+      <c r="O195" t="str">
+        <v/>
+      </c>
+      <c r="P195" t="str">
+        <v/>
+      </c>
+      <c r="Q195" t="str">
+        <v/>
+      </c>
+      <c r="R195" t="str">
+        <v/>
+      </c>
+      <c r="S195" t="str">
+        <v/>
+      </c>
+      <c r="T195" t="str">
+        <v/>
+      </c>
+      <c r="U195" t="str">
+        <v/>
+      </c>
+      <c r="V195" t="str">
+        <v/>
+      </c>
+      <c r="W195" t="str">
+        <v/>
+      </c>
+      <c r="X195" t="str">
+        <v/>
+      </c>
+      <c r="Y195" t="str">
+        <v/>
+      </c>
+      <c r="Z195" t="str">
+        <v/>
+      </c>
+      <c r="AA195" t="str">
+        <v/>
+      </c>
+      <c r="AB195" t="str">
+        <v/>
+      </c>
+      <c r="AC195" t="str">
+        <v/>
+      </c>
+      <c r="AD195" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>אד שירן Play</v>
+      </c>
+      <c r="B196" t="str">
+        <v>2025-09-24</v>
+      </c>
+      <c r="C196" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
+      </c>
+      <c r="D196" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E196" t="str">
+        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
+      </c>
+      <c r="F196" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G196" t="str">
+        <v/>
+      </c>
+      <c r="H196" t="str">
+        <v/>
+      </c>
+      <c r="I196" t="str">
+        <v/>
+      </c>
+      <c r="J196" t="str">
+        <v/>
+      </c>
+      <c r="K196" t="str">
+        <v/>
+      </c>
+      <c r="L196" t="str">
+        <v/>
+      </c>
+      <c r="M196" t="str">
+        <v/>
+      </c>
+      <c r="N196" t="str">
+        <v/>
+      </c>
+      <c r="O196" t="str">
+        <v/>
+      </c>
+      <c r="P196" t="str">
+        <v/>
+      </c>
+      <c r="Q196" t="str">
+        <v/>
+      </c>
+      <c r="R196" t="str">
+        <v/>
+      </c>
+      <c r="S196" t="str">
+        <v/>
+      </c>
+      <c r="T196" t="str">
+        <v/>
+      </c>
+      <c r="U196" t="str">
+        <v/>
+      </c>
+      <c r="V196" t="str">
+        <v/>
+      </c>
+      <c r="W196" t="str">
+        <v/>
+      </c>
+      <c r="X196" t="str">
+        <v/>
+      </c>
+      <c r="Y196" t="str">
+        <v/>
+      </c>
+      <c r="Z196" t="str">
+        <v/>
+      </c>
+      <c r="AA196" t="str">
+        <v/>
+      </c>
+      <c r="AB196" t="str">
+        <v/>
+      </c>
+      <c r="AC196" t="str">
+        <v/>
+      </c>
+      <c r="AD196" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+      </c>
+      <c r="B197" t="str">
+        <v>2025-09-21</v>
+      </c>
+      <c r="C197" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
+      </c>
+      <c r="D197" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E197" t="str">
+        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
+      </c>
+      <c r="F197" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G197" t="str">
+        <v/>
+      </c>
+      <c r="H197" t="str">
+        <v/>
+      </c>
+      <c r="I197" t="str">
+        <v/>
+      </c>
+      <c r="J197" t="str">
+        <v/>
+      </c>
+      <c r="K197" t="str">
+        <v/>
+      </c>
+      <c r="L197" t="str">
+        <v/>
+      </c>
+      <c r="M197" t="str">
+        <v/>
+      </c>
+      <c r="N197" t="str">
+        <v/>
+      </c>
+      <c r="O197" t="str">
+        <v/>
+      </c>
+      <c r="P197" t="str">
+        <v/>
+      </c>
+      <c r="Q197" t="str">
+        <v/>
+      </c>
+      <c r="R197" t="str">
+        <v/>
+      </c>
+      <c r="S197" t="str">
+        <v/>
+      </c>
+      <c r="T197" t="str">
+        <v/>
+      </c>
+      <c r="U197" t="str">
+        <v/>
+      </c>
+      <c r="V197" t="str">
+        <v/>
+      </c>
+      <c r="W197" t="str">
+        <v/>
+      </c>
+      <c r="X197" t="str">
+        <v/>
+      </c>
+      <c r="Y197" t="str">
+        <v/>
+      </c>
+      <c r="Z197" t="str">
+        <v/>
+      </c>
+      <c r="AA197" t="str">
+        <v/>
+      </c>
+      <c r="AB197" t="str">
+        <v/>
+      </c>
+      <c r="AC197" t="str">
+        <v/>
+      </c>
+      <c r="AD197" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>סוויד Antidepressants</v>
+      </c>
+      <c r="B198" t="str">
+        <v>2025-09-12</v>
+      </c>
+      <c r="C198" t="str">
+        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
+      </c>
+      <c r="D198" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E198" t="str">
+        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
+      </c>
+      <c r="F198" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G198" t="str">
+        <v/>
+      </c>
+      <c r="H198" t="str">
+        <v/>
+      </c>
+      <c r="I198" t="str">
+        <v/>
+      </c>
+      <c r="J198" t="str">
+        <v/>
+      </c>
+      <c r="K198" t="str">
+        <v/>
+      </c>
+      <c r="L198" t="str">
+        <v/>
+      </c>
+      <c r="M198" t="str">
+        <v/>
+      </c>
+      <c r="N198" t="str">
+        <v/>
+      </c>
+      <c r="O198" t="str">
+        <v/>
+      </c>
+      <c r="P198" t="str">
+        <v/>
+      </c>
+      <c r="Q198" t="str">
+        <v/>
+      </c>
+      <c r="R198" t="str">
+        <v/>
+      </c>
+      <c r="S198" t="str">
+        <v/>
+      </c>
+      <c r="T198" t="str">
+        <v/>
+      </c>
+      <c r="U198" t="str">
+        <v/>
+      </c>
+      <c r="V198" t="str">
+        <v/>
+      </c>
+      <c r="W198" t="str">
+        <v/>
+      </c>
+      <c r="X198" t="str">
+        <v/>
+      </c>
+      <c r="Y198" t="str">
+        <v/>
+      </c>
+      <c r="Z198" t="str">
+        <v/>
+      </c>
+      <c r="AA198" t="str">
+        <v/>
+      </c>
+      <c r="AB198" t="str">
+        <v/>
+      </c>
+      <c r="AC198" t="str">
+        <v/>
+      </c>
+      <c r="AD198" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>וולף אליס The Clearing</v>
+      </c>
+      <c r="B199" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="C199" t="str">
+        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
+      </c>
+      <c r="D199" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E199" t="str">
+        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
+      </c>
+      <c r="F199" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G199" t="str">
+        <v/>
+      </c>
+      <c r="H199" t="str">
+        <v/>
+      </c>
+      <c r="I199" t="str">
+        <v/>
+      </c>
+      <c r="J199" t="str">
+        <v/>
+      </c>
+      <c r="K199" t="str">
+        <v/>
+      </c>
+      <c r="L199" t="str">
+        <v/>
+      </c>
+      <c r="M199" t="str">
+        <v/>
+      </c>
+      <c r="N199" t="str">
+        <v/>
+      </c>
+      <c r="O199" t="str">
+        <v/>
+      </c>
+      <c r="P199" t="str">
+        <v/>
+      </c>
+      <c r="Q199" t="str">
+        <v/>
+      </c>
+      <c r="R199" t="str">
+        <v/>
+      </c>
+      <c r="S199" t="str">
+        <v/>
+      </c>
+      <c r="T199" t="str">
+        <v/>
+      </c>
+      <c r="U199" t="str">
+        <v/>
+      </c>
+      <c r="V199" t="str">
+        <v/>
+      </c>
+      <c r="W199" t="str">
+        <v/>
+      </c>
+      <c r="X199" t="str">
+        <v/>
+      </c>
+      <c r="Y199" t="str">
+        <v/>
+      </c>
+      <c r="Z199" t="str">
+        <v/>
+      </c>
+      <c r="AA199" t="str">
+        <v/>
+      </c>
+      <c r="AB199" t="str">
+        <v/>
+      </c>
+      <c r="AC199" t="str">
+        <v/>
+      </c>
+      <c r="AD199" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+      </c>
+      <c r="B200" t="str">
+        <v>2025-08-29</v>
+      </c>
+      <c r="C200" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
+      </c>
+      <c r="D200" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E200" t="str">
+        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
+      </c>
+      <c r="F200" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G200" t="str">
+        <v/>
+      </c>
+      <c r="H200" t="str">
+        <v/>
+      </c>
+      <c r="I200" t="str">
+        <v/>
+      </c>
+      <c r="J200" t="str">
+        <v/>
+      </c>
+      <c r="K200" t="str">
+        <v/>
+      </c>
+      <c r="L200" t="str">
+        <v/>
+      </c>
+      <c r="M200" t="str">
+        <v/>
+      </c>
+      <c r="N200" t="str">
+        <v/>
+      </c>
+      <c r="O200" t="str">
+        <v/>
+      </c>
+      <c r="P200" t="str">
+        <v/>
+      </c>
+      <c r="Q200" t="str">
+        <v/>
+      </c>
+      <c r="R200" t="str">
+        <v/>
+      </c>
+      <c r="S200" t="str">
+        <v/>
+      </c>
+      <c r="T200" t="str">
+        <v/>
+      </c>
+      <c r="U200" t="str">
+        <v/>
+      </c>
+      <c r="V200" t="str">
+        <v/>
+      </c>
+      <c r="W200" t="str">
+        <v/>
+      </c>
+      <c r="X200" t="str">
+        <v/>
+      </c>
+      <c r="Y200" t="str">
+        <v/>
+      </c>
+      <c r="Z200" t="str">
+        <v/>
+      </c>
+      <c r="AA200" t="str">
+        <v/>
+      </c>
+      <c r="AB200" t="str">
+        <v/>
+      </c>
+      <c r="AC200" t="str">
+        <v/>
+      </c>
+      <c r="AD200" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+      </c>
+      <c r="B201" t="str">
+        <v>2025-08-24</v>
+      </c>
+      <c r="C201" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
+      </c>
+      <c r="D201" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E201" t="str">
+        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
+      </c>
+      <c r="F201" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G201" t="str">
+        <v/>
+      </c>
+      <c r="H201" t="str">
+        <v/>
+      </c>
+      <c r="I201" t="str">
+        <v/>
+      </c>
+      <c r="J201" t="str">
+        <v/>
+      </c>
+      <c r="K201" t="str">
+        <v/>
+      </c>
+      <c r="L201" t="str">
+        <v/>
+      </c>
+      <c r="M201" t="str">
+        <v/>
+      </c>
+      <c r="N201" t="str">
+        <v/>
+      </c>
+      <c r="O201" t="str">
+        <v/>
+      </c>
+      <c r="P201" t="str">
+        <v/>
+      </c>
+      <c r="Q201" t="str">
+        <v/>
+      </c>
+      <c r="R201" t="str">
+        <v/>
+      </c>
+      <c r="S201" t="str">
+        <v/>
+      </c>
+      <c r="T201" t="str">
+        <v/>
+      </c>
+      <c r="U201" t="str">
+        <v/>
+      </c>
+      <c r="V201" t="str">
+        <v/>
+      </c>
+      <c r="W201" t="str">
+        <v/>
+      </c>
+      <c r="X201" t="str">
+        <v/>
+      </c>
+      <c r="Y201" t="str">
+        <v/>
+      </c>
+      <c r="Z201" t="str">
+        <v/>
+      </c>
+      <c r="AA201" t="str">
+        <v/>
+      </c>
+      <c r="AB201" t="str">
+        <v/>
+      </c>
+      <c r="AC201" t="str">
+        <v/>
+      </c>
+      <c r="AD201" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+      </c>
+      <c r="B202" t="str">
+        <v>2025-08-21</v>
+      </c>
+      <c r="C202" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
+      </c>
+      <c r="D202" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E202" t="str">
+        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
+      </c>
+      <c r="F202" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G202" t="str">
+        <v/>
+      </c>
+      <c r="H202" t="str">
+        <v/>
+      </c>
+      <c r="I202" t="str">
+        <v/>
+      </c>
+      <c r="J202" t="str">
+        <v/>
+      </c>
+      <c r="K202" t="str">
+        <v/>
+      </c>
+      <c r="L202" t="str">
+        <v/>
+      </c>
+      <c r="M202" t="str">
+        <v/>
+      </c>
+      <c r="N202" t="str">
+        <v/>
+      </c>
+      <c r="O202" t="str">
+        <v/>
+      </c>
+      <c r="P202" t="str">
+        <v/>
+      </c>
+      <c r="Q202" t="str">
+        <v/>
+      </c>
+      <c r="R202" t="str">
+        <v/>
+      </c>
+      <c r="S202" t="str">
+        <v/>
+      </c>
+      <c r="T202" t="str">
+        <v/>
+      </c>
+      <c r="U202" t="str">
+        <v/>
+      </c>
+      <c r="V202" t="str">
+        <v/>
+      </c>
+      <c r="W202" t="str">
+        <v/>
+      </c>
+      <c r="X202" t="str">
+        <v/>
+      </c>
+      <c r="Y202" t="str">
+        <v/>
+      </c>
+      <c r="Z202" t="str">
+        <v/>
+      </c>
+      <c r="AA202" t="str">
+        <v/>
+      </c>
+      <c r="AB202" t="str">
+        <v/>
+      </c>
+      <c r="AC202" t="str">
+        <v/>
+      </c>
+      <c r="AD202" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>אברהם טל – חי</v>
+      </c>
+      <c r="B203" t="str">
+        <v>2025-08-17</v>
+      </c>
+      <c r="C203" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
+      </c>
+      <c r="D203" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E203" t="str">
+        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
+      </c>
+      <c r="F203" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G203" t="str">
+        <v/>
+      </c>
+      <c r="H203" t="str">
+        <v/>
+      </c>
+      <c r="I203" t="str">
+        <v/>
+      </c>
+      <c r="J203" t="str">
+        <v/>
+      </c>
+      <c r="K203" t="str">
+        <v/>
+      </c>
+      <c r="L203" t="str">
+        <v/>
+      </c>
+      <c r="M203" t="str">
+        <v/>
+      </c>
+      <c r="N203" t="str">
+        <v/>
+      </c>
+      <c r="O203" t="str">
+        <v/>
+      </c>
+      <c r="P203" t="str">
+        <v/>
+      </c>
+      <c r="Q203" t="str">
+        <v/>
+      </c>
+      <c r="R203" t="str">
+        <v/>
+      </c>
+      <c r="S203" t="str">
+        <v/>
+      </c>
+      <c r="T203" t="str">
+        <v/>
+      </c>
+      <c r="U203" t="str">
+        <v/>
+      </c>
+      <c r="V203" t="str">
+        <v/>
+      </c>
+      <c r="W203" t="str">
+        <v/>
+      </c>
+      <c r="X203" t="str">
+        <v/>
+      </c>
+      <c r="Y203" t="str">
+        <v/>
+      </c>
+      <c r="Z203" t="str">
+        <v/>
+      </c>
+      <c r="AA203" t="str">
+        <v/>
+      </c>
+      <c r="AB203" t="str">
+        <v/>
+      </c>
+      <c r="AC203" t="str">
+        <v/>
+      </c>
+      <c r="AD203" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>רנה ראפ Bite Me</v>
+      </c>
+      <c r="B204" t="str">
+        <v>2025-08-12</v>
+      </c>
+      <c r="C204" t="str">
+        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
+      </c>
+      <c r="D204" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E204" t="str">
+        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
+      </c>
+      <c r="F204" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G204" t="str">
+        <v/>
+      </c>
+      <c r="H204" t="str">
+        <v/>
+      </c>
+      <c r="I204" t="str">
+        <v/>
+      </c>
+      <c r="J204" t="str">
+        <v/>
+      </c>
+      <c r="K204" t="str">
+        <v/>
+      </c>
+      <c r="L204" t="str">
+        <v/>
+      </c>
+      <c r="M204" t="str">
+        <v/>
+      </c>
+      <c r="N204" t="str">
+        <v/>
+      </c>
+      <c r="O204" t="str">
+        <v/>
+      </c>
+      <c r="P204" t="str">
+        <v/>
+      </c>
+      <c r="Q204" t="str">
+        <v/>
+      </c>
+      <c r="R204" t="str">
+        <v/>
+      </c>
+      <c r="S204" t="str">
+        <v/>
+      </c>
+      <c r="T204" t="str">
+        <v/>
+      </c>
+      <c r="U204" t="str">
+        <v/>
+      </c>
+      <c r="V204" t="str">
+        <v/>
+      </c>
+      <c r="W204" t="str">
+        <v/>
+      </c>
+      <c r="X204" t="str">
+        <v/>
+      </c>
+      <c r="Y204" t="str">
+        <v/>
+      </c>
+      <c r="Z204" t="str">
+        <v/>
+      </c>
+      <c r="AA204" t="str">
+        <v/>
+      </c>
+      <c r="AB204" t="str">
+        <v/>
+      </c>
+      <c r="AC204" t="str">
+        <v/>
+      </c>
+      <c r="AD204" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>The K's – Pretty On The Internet</v>
+      </c>
+      <c r="B205" t="str">
+        <v>2025-08-03</v>
+      </c>
+      <c r="C205" t="str">
+        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
+      </c>
+      <c r="D205" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E205" t="str">
+        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
+      </c>
+      <c r="F205" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G205" t="str">
+        <v/>
+      </c>
+      <c r="H205" t="str">
+        <v/>
+      </c>
+      <c r="I205" t="str">
+        <v/>
+      </c>
+      <c r="J205" t="str">
+        <v/>
+      </c>
+      <c r="K205" t="str">
+        <v/>
+      </c>
+      <c r="L205" t="str">
+        <v/>
+      </c>
+      <c r="M205" t="str">
+        <v/>
+      </c>
+      <c r="N205" t="str">
+        <v/>
+      </c>
+      <c r="O205" t="str">
+        <v/>
+      </c>
+      <c r="P205" t="str">
+        <v/>
+      </c>
+      <c r="Q205" t="str">
+        <v/>
+      </c>
+      <c r="R205" t="str">
+        <v/>
+      </c>
+      <c r="S205" t="str">
+        <v/>
+      </c>
+      <c r="T205" t="str">
+        <v/>
+      </c>
+      <c r="U205" t="str">
+        <v/>
+      </c>
+      <c r="V205" t="str">
+        <v/>
+      </c>
+      <c r="W205" t="str">
+        <v/>
+      </c>
+      <c r="X205" t="str">
+        <v/>
+      </c>
+      <c r="Y205" t="str">
+        <v/>
+      </c>
+      <c r="Z205" t="str">
+        <v/>
+      </c>
+      <c r="AA205" t="str">
+        <v/>
+      </c>
+      <c r="AB205" t="str">
+        <v/>
+      </c>
+      <c r="AC205" t="str">
+        <v/>
+      </c>
+      <c r="AD205" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>פליטווד מק Fifty Years – Don’t Stop</v>
+      </c>
+      <c r="B206" t="str">
+        <v>2025-07-30</v>
+      </c>
+      <c r="C206" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%99%d7%98%d7%95%d7%95%d7%93-%d7%9e%d7%a7-fifty-years-dont-stop/</v>
+      </c>
+      <c r="D206" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E206" t="str">
+        <v>פליטווד מק (Fleetwood Mac) חוגגים חצי מאה של מוזיקה עם אוסף חדש בן 50 שירים, שמתפרש על כל הקריירה של הלהקה, מימיה הראשונים בסגנון בלוז, ועד להצלחתה העולמית כאחת מלהקות הגדולות בהיסטוריה של הרוק. פליטווד מק הם לא רק להקה</v>
+      </c>
+      <c r="F206" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G206" t="str">
+        <v/>
+      </c>
+      <c r="H206" t="str">
+        <v/>
+      </c>
+      <c r="I206" t="str">
+        <v/>
+      </c>
+      <c r="J206" t="str">
+        <v/>
+      </c>
+      <c r="K206" t="str">
+        <v/>
+      </c>
+      <c r="L206" t="str">
+        <v/>
+      </c>
+      <c r="M206" t="str">
+        <v/>
+      </c>
+      <c r="N206" t="str">
+        <v/>
+      </c>
+      <c r="O206" t="str">
+        <v/>
+      </c>
+      <c r="P206" t="str">
+        <v/>
+      </c>
+      <c r="Q206" t="str">
+        <v/>
+      </c>
+      <c r="R206" t="str">
+        <v/>
+      </c>
+      <c r="S206" t="str">
+        <v/>
+      </c>
+      <c r="T206" t="str">
+        <v/>
+      </c>
+      <c r="U206" t="str">
+        <v/>
+      </c>
+      <c r="V206" t="str">
+        <v/>
+      </c>
+      <c r="W206" t="str">
+        <v/>
+      </c>
+      <c r="X206" t="str">
+        <v/>
+      </c>
+      <c r="Y206" t="str">
+        <v/>
+      </c>
+      <c r="Z206" t="str">
+        <v/>
+      </c>
+      <c r="AA206" t="str">
+        <v/>
+      </c>
+      <c r="AB206" t="str">
+        <v/>
+      </c>
+      <c r="AC206" t="str">
+        <v/>
+      </c>
+      <c r="AD206" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>Wet Leg Moisturizer</v>
+      </c>
+      <c r="B207" t="str">
+        <v>2025-07-25</v>
+      </c>
+      <c r="C207" t="str">
+        <v>https://yosmusic.com/wet-leg-moisturizer/</v>
+      </c>
+      <c r="D207" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E207" t="str">
         <v>להקת Wet Leg לא הוציאה קרם לחות (Moisturizer) כמוצר טיפוח. במקום זאת, "Moisturizer" הוא שמו של האלבום השני והחדש שלהם. במרכז –  צמד אינדי-רוק המורכב מהחברות ריין טיסדייל והסטר צ'יימברס. אלבום הבכורה הנושא את שמה, הגיע למקום הראשון במצעד האלבומים</v>
       </c>
-      <c r="F163" t="str">
-        <v>אלבומים חדשים</v>
-      </c>
-      <c r="G163" t="str">
-        <v/>
-      </c>
-      <c r="H163" t="str">
-        <v/>
-      </c>
-      <c r="I163" t="str">
-        <v/>
-      </c>
-      <c r="J163" t="str">
-        <v/>
-      </c>
-      <c r="K163" t="str">
-        <v/>
-      </c>
-      <c r="L163" t="str">
-        <v/>
-      </c>
-      <c r="M163" t="str">
-        <v/>
-      </c>
-      <c r="N163" t="str">
-        <v/>
-      </c>
-      <c r="O163" t="str">
-        <v/>
-      </c>
-      <c r="P163" t="str">
-        <v/>
-      </c>
-      <c r="Q163" t="str">
-        <v/>
-      </c>
-      <c r="R163" t="str">
-        <v/>
-      </c>
-      <c r="S163" t="str">
-        <v/>
-      </c>
-      <c r="T163" t="str">
-        <v/>
-      </c>
-      <c r="U163" t="str">
-        <v/>
-      </c>
-      <c r="V163" t="str">
-        <v/>
-      </c>
-      <c r="W163" t="str">
-        <v/>
-      </c>
-      <c r="X163" t="str">
-        <v/>
-      </c>
-      <c r="Y163" t="str">
-        <v/>
-      </c>
-      <c r="Z163" t="str">
+      <c r="F207" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G207" t="str">
+        <v/>
+      </c>
+      <c r="H207" t="str">
+        <v/>
+      </c>
+      <c r="I207" t="str">
+        <v/>
+      </c>
+      <c r="J207" t="str">
+        <v/>
+      </c>
+      <c r="K207" t="str">
+        <v/>
+      </c>
+      <c r="L207" t="str">
+        <v/>
+      </c>
+      <c r="M207" t="str">
+        <v/>
+      </c>
+      <c r="N207" t="str">
+        <v/>
+      </c>
+      <c r="O207" t="str">
+        <v/>
+      </c>
+      <c r="P207" t="str">
+        <v/>
+      </c>
+      <c r="Q207" t="str">
+        <v/>
+      </c>
+      <c r="R207" t="str">
+        <v/>
+      </c>
+      <c r="S207" t="str">
+        <v/>
+      </c>
+      <c r="T207" t="str">
+        <v/>
+      </c>
+      <c r="U207" t="str">
+        <v/>
+      </c>
+      <c r="V207" t="str">
+        <v/>
+      </c>
+      <c r="W207" t="str">
+        <v/>
+      </c>
+      <c r="X207" t="str">
+        <v/>
+      </c>
+      <c r="Y207" t="str">
+        <v/>
+      </c>
+      <c r="Z207" t="str">
+        <v/>
+      </c>
+      <c r="AA207" t="str">
+        <v/>
+      </c>
+      <c r="AB207" t="str">
+        <v/>
+      </c>
+      <c r="AC207" t="str">
+        <v/>
+      </c>
+      <c r="AD207" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Z163"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AD207"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:O89"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1489,7 +1489,7 @@
         <v>עדן בן זקן - רולקס וקסקט</v>
       </c>
       <c r="B32" t="str">
-        <v>2026  08:41-01-14</v>
+        <v>2026  08:41-01-14 | מאת</v>
       </c>
       <c r="C32" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24436&amp;forum=music&amp;viewmode=all</v>
@@ -1524,7 +1524,7 @@
         <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
       </c>
       <c r="B33" t="str">
-        <v>2026  08:40-01-14</v>
+        <v>2026  08:40-01-14 | מאת</v>
       </c>
       <c r="C33" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24439&amp;forum=music&amp;viewmode=all</v>
@@ -1559,7 +1559,7 @@
         <v>אייל גולן - בית מפואר</v>
       </c>
       <c r="B34" t="str">
-        <v>2025  02:18-12-31</v>
+        <v>2025  02:18-12-31 | מאת</v>
       </c>
       <c r="C34" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
@@ -1594,7 +1594,7 @@
         <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
       </c>
       <c r="B35" t="str">
-        <v>2025  02:16-12-31</v>
+        <v>2025  02:16-12-31 | מאת</v>
       </c>
       <c r="C35" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
@@ -1629,7 +1629,7 @@
         <v>שיר לוי - ילד מוזר</v>
       </c>
       <c r="B36" t="str">
-        <v>2025  02:14-12-31</v>
+        <v>2025  02:14-12-31 | מאת</v>
       </c>
       <c r="C36" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
@@ -1664,7 +1664,7 @@
         <v>פיטר רוט - 50</v>
       </c>
       <c r="B37" t="str">
-        <v>2025  02:13-12-31</v>
+        <v>2025  02:13-12-31 | מאת</v>
       </c>
       <c r="C37" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
@@ -1699,7 +1699,7 @@
         <v>אגם בוחבוט - עשרים ואחת</v>
       </c>
       <c r="B38" t="str">
-        <v>2025  02:11-12-31</v>
+        <v>2025  02:11-12-31 | מאת</v>
       </c>
       <c r="C38" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
@@ -1734,7 +1734,7 @@
         <v>רבקה זוהר - רסיסים של אור</v>
       </c>
       <c r="B39" t="str">
-        <v>2025  02:09-12-31</v>
+        <v>2025  02:09-12-31 | מאת</v>
       </c>
       <c r="C39" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
@@ -1769,7 +1769,7 @@
         <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
       </c>
       <c r="B40" t="str">
-        <v>2025  02:08-12-31</v>
+        <v>2025  02:08-12-31 | מאת</v>
       </c>
       <c r="C40" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
@@ -1804,7 +1804,7 @@
         <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
       </c>
       <c r="B41" t="str">
-        <v>2025  02:05-12-31</v>
+        <v>2025  02:05-12-31 | מאת</v>
       </c>
       <c r="C41" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
@@ -1839,7 +1839,7 @@
         <v>Imagine פסטיגל - שירי התחרות</v>
       </c>
       <c r="B42" t="str">
-        <v>2025  02:04-12-31</v>
+        <v>2025  02:04-12-31 | מאת</v>
       </c>
       <c r="C42" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
@@ -1874,7 +1874,7 @@
         <v>השמחות - חובות אבודים</v>
       </c>
       <c r="B43" t="str">
-        <v>2025  02:02-12-31</v>
+        <v>2025  02:02-12-31 | מאת</v>
       </c>
       <c r="C43" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
@@ -1909,7 +1909,7 @@
         <v>שלמה גרוניך - כמו כוכבים</v>
       </c>
       <c r="B44" t="str">
-        <v>2025  02:00-12-31</v>
+        <v>2025  02:00-12-31 | מאת</v>
       </c>
       <c r="C44" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
@@ -1944,7 +1944,7 @@
         <v>יוני רועה - מפוזרים</v>
       </c>
       <c r="B45" t="str">
-        <v>2025  01:56-12-31</v>
+        <v>2025  01:56-12-31 | מאת</v>
       </c>
       <c r="C45" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
@@ -1974,9 +1974,2077 @@
         <v>יוני רועה - מפוזרים</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>פטריק סבג Hotel Mogador</v>
+      </c>
+      <c r="B46" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C46" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
+      </c>
+      <c r="D46" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E46" t="str">
+        <v>האלבום של פטריק סבג אינו אוסף שירים אקראי, אלא מרחב. מקום לשהות בו.  נכנסים, שומעים, ויוצאים קצת אחרים. הבחירה בשם "הוטל מוגדור” היא כבר הצהרה. מלון = מקום מעבר, לא בית קבוע, מוגדור = עיר נמל, תנועה, ערבוב תרבויות. כך</v>
+      </c>
+      <c r="F46" t="str">
+        <v/>
+      </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
+      <c r="H46" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I46" t="str">
+        <v/>
+      </c>
+      <c r="J46" t="str">
+        <v/>
+      </c>
+      <c r="K46" t="str">
+        <v>פטריק סבג Hotel Mogador</v>
+      </c>
+      <c r="L46" t="str">
+        <v/>
+      </c>
+      <c r="M46" t="str">
+        <v/>
+      </c>
+      <c r="N46" t="str">
+        <v/>
+      </c>
+      <c r="O46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
+      </c>
+      <c r="B47" t="str">
+        <v>2026-01-09</v>
+      </c>
+      <c r="C47" t="str">
+        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
+      </c>
+      <c r="D47" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E47" t="str">
+        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
+      </c>
+      <c r="F47" t="str">
+        <v/>
+      </c>
+      <c r="G47" t="str">
+        <v/>
+      </c>
+      <c r="H47" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I47" t="str">
+        <v/>
+      </c>
+      <c r="J47" t="str">
+        <v/>
+      </c>
+      <c r="K47" t="str">
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
+      </c>
+      <c r="L47" t="str">
+        <v/>
+      </c>
+      <c r="M47" t="str">
+        <v/>
+      </c>
+      <c r="N47" t="str">
+        <v/>
+      </c>
+      <c r="O47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>אוליביה דין The Art of Loving</v>
+      </c>
+      <c r="B48" t="str">
+        <v>2026-01-04</v>
+      </c>
+      <c r="C48" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
+      </c>
+      <c r="D48" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E48" t="str">
+        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
+      </c>
+      <c r="F48" t="str">
+        <v/>
+      </c>
+      <c r="G48" t="str">
+        <v/>
+      </c>
+      <c r="H48" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I48" t="str">
+        <v/>
+      </c>
+      <c r="J48" t="str">
+        <v/>
+      </c>
+      <c r="K48" t="str">
+        <v>אוליביה דין The Art of Loving</v>
+      </c>
+      <c r="L48" t="str">
+        <v/>
+      </c>
+      <c r="M48" t="str">
+        <v/>
+      </c>
+      <c r="N48" t="str">
+        <v/>
+      </c>
+      <c r="O48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>Geese Getting Killed</v>
+      </c>
+      <c r="B49" t="str">
+        <v>2025-12-29</v>
+      </c>
+      <c r="C49" t="str">
+        <v>https://yosmusic.com/geese-getting-killed/</v>
+      </c>
+      <c r="D49" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E49" t="str">
+        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
+      </c>
+      <c r="F49" t="str">
+        <v/>
+      </c>
+      <c r="G49" t="str">
+        <v/>
+      </c>
+      <c r="H49" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I49" t="str">
+        <v/>
+      </c>
+      <c r="J49" t="str">
+        <v/>
+      </c>
+      <c r="K49" t="str">
+        <v>Geese Getting Killed</v>
+      </c>
+      <c r="L49" t="str">
+        <v/>
+      </c>
+      <c r="M49" t="str">
+        <v/>
+      </c>
+      <c r="N49" t="str">
+        <v/>
+      </c>
+      <c r="O49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>רוסליה Lux</v>
+      </c>
+      <c r="B50" t="str">
+        <v>2025-12-25</v>
+      </c>
+      <c r="C50" t="str">
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
+      </c>
+      <c r="D50" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E50" t="str">
+        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
+      </c>
+      <c r="F50" t="str">
+        <v/>
+      </c>
+      <c r="G50" t="str">
+        <v/>
+      </c>
+      <c r="H50" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I50" t="str">
+        <v/>
+      </c>
+      <c r="J50" t="str">
+        <v/>
+      </c>
+      <c r="K50" t="str">
+        <v>רוסליה Lux</v>
+      </c>
+      <c r="L50" t="str">
+        <v/>
+      </c>
+      <c r="M50" t="str">
+        <v/>
+      </c>
+      <c r="N50" t="str">
+        <v/>
+      </c>
+      <c r="O50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>יאנגבלאד אירוסמית' one more time</v>
+      </c>
+      <c r="B51" t="str">
+        <v>2025-12-17</v>
+      </c>
+      <c r="C51" t="str">
+        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
+      </c>
+      <c r="D51" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E51" t="str">
+        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
+      </c>
+      <c r="F51" t="str">
+        <v/>
+      </c>
+      <c r="G51" t="str">
+        <v/>
+      </c>
+      <c r="H51" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I51" t="str">
+        <v/>
+      </c>
+      <c r="J51" t="str">
+        <v/>
+      </c>
+      <c r="K51" t="str">
+        <v>יאנגבלאד אירוסמית' one more time</v>
+      </c>
+      <c r="L51" t="str">
+        <v/>
+      </c>
+      <c r="M51" t="str">
+        <v/>
+      </c>
+      <c r="N51" t="str">
+        <v/>
+      </c>
+      <c r="O51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>פינק פלויד Wish You Were Here 50</v>
+      </c>
+      <c r="B52" t="str">
+        <v>2025-12-14</v>
+      </c>
+      <c r="C52" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
+      </c>
+      <c r="D52" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E52" t="str">
+        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
+      </c>
+      <c r="F52" t="str">
+        <v/>
+      </c>
+      <c r="G52" t="str">
+        <v/>
+      </c>
+      <c r="H52" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I52" t="str">
+        <v/>
+      </c>
+      <c r="J52" t="str">
+        <v/>
+      </c>
+      <c r="K52" t="str">
+        <v>פינק פלויד Wish You Were Here 50</v>
+      </c>
+      <c r="L52" t="str">
+        <v/>
+      </c>
+      <c r="M52" t="str">
+        <v/>
+      </c>
+      <c r="N52" t="str">
+        <v/>
+      </c>
+      <c r="O52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+      </c>
+      <c r="B53" t="str">
+        <v>2025-12-08</v>
+      </c>
+      <c r="C53" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
+      </c>
+      <c r="D53" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E53" t="str">
+        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
+      </c>
+      <c r="F53" t="str">
+        <v/>
+      </c>
+      <c r="G53" t="str">
+        <v/>
+      </c>
+      <c r="H53" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I53" t="str">
+        <v/>
+      </c>
+      <c r="J53" t="str">
+        <v/>
+      </c>
+      <c r="K53" t="str">
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+      </c>
+      <c r="L53" t="str">
+        <v/>
+      </c>
+      <c r="M53" t="str">
+        <v/>
+      </c>
+      <c r="N53" t="str">
+        <v/>
+      </c>
+      <c r="O53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>סטריי קידס DO IT EP</v>
+      </c>
+      <c r="B54" t="str">
+        <v>2025-12-04</v>
+      </c>
+      <c r="C54" t="str">
+        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
+      </c>
+      <c r="D54" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E54" t="str">
+        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
+      </c>
+      <c r="F54" t="str">
+        <v/>
+      </c>
+      <c r="G54" t="str">
+        <v/>
+      </c>
+      <c r="H54" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I54" t="str">
+        <v/>
+      </c>
+      <c r="J54" t="str">
+        <v/>
+      </c>
+      <c r="K54" t="str">
+        <v>סטריי קידס DO IT EP</v>
+      </c>
+      <c r="L54" t="str">
+        <v/>
+      </c>
+      <c r="M54" t="str">
+        <v/>
+      </c>
+      <c r="N54" t="str">
+        <v/>
+      </c>
+      <c r="O54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>דויד ברוזה BROZAJAZZ</v>
+      </c>
+      <c r="B55" t="str">
+        <v>2025-11-30</v>
+      </c>
+      <c r="C55" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
+      </c>
+      <c r="D55" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E55" t="str">
+        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
+      </c>
+      <c r="F55" t="str">
+        <v/>
+      </c>
+      <c r="G55" t="str">
+        <v/>
+      </c>
+      <c r="H55" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I55" t="str">
+        <v/>
+      </c>
+      <c r="J55" t="str">
+        <v/>
+      </c>
+      <c r="K55" t="str">
+        <v>דויד ברוזה BROZAJAZZ</v>
+      </c>
+      <c r="L55" t="str">
+        <v/>
+      </c>
+      <c r="M55" t="str">
+        <v/>
+      </c>
+      <c r="N55" t="str">
+        <v/>
+      </c>
+      <c r="O55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>Five Seconds of Summer – Everyone's A Star</v>
+      </c>
+      <c r="B56" t="str">
+        <v>2025-11-24</v>
+      </c>
+      <c r="C56" t="str">
+        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
+      </c>
+      <c r="D56" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E56" t="str">
+        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
+      </c>
+      <c r="F56" t="str">
+        <v/>
+      </c>
+      <c r="G56" t="str">
+        <v/>
+      </c>
+      <c r="H56" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I56" t="str">
+        <v/>
+      </c>
+      <c r="J56" t="str">
+        <v/>
+      </c>
+      <c r="K56" t="str">
+        <v>Five Seconds of Summer – Everyone's A Star</v>
+      </c>
+      <c r="L56" t="str">
+        <v/>
+      </c>
+      <c r="M56" t="str">
+        <v/>
+      </c>
+      <c r="N56" t="str">
+        <v/>
+      </c>
+      <c r="O56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>התקווה 6 – ויהי אור</v>
+      </c>
+      <c r="B57" t="str">
+        <v>2025-11-20</v>
+      </c>
+      <c r="C57" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
+      </c>
+      <c r="D57" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E57" t="str">
+        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
+      </c>
+      <c r="F57" t="str">
+        <v/>
+      </c>
+      <c r="G57" t="str">
+        <v/>
+      </c>
+      <c r="H57" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I57" t="str">
+        <v/>
+      </c>
+      <c r="J57" t="str">
+        <v/>
+      </c>
+      <c r="K57" t="str">
+        <v>התקווה 6 – ויהי אור</v>
+      </c>
+      <c r="L57" t="str">
+        <v/>
+      </c>
+      <c r="M57" t="str">
+        <v/>
+      </c>
+      <c r="N57" t="str">
+        <v/>
+      </c>
+      <c r="O57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>פלורנס אנד דה משין Everybody Scream</v>
+      </c>
+      <c r="B58" t="str">
+        <v>2025-11-13</v>
+      </c>
+      <c r="C58" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
+      </c>
+      <c r="D58" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E58" t="str">
+        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
+      </c>
+      <c r="F58" t="str">
+        <v/>
+      </c>
+      <c r="G58" t="str">
+        <v/>
+      </c>
+      <c r="H58" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I58" t="str">
+        <v/>
+      </c>
+      <c r="J58" t="str">
+        <v/>
+      </c>
+      <c r="K58" t="str">
+        <v>פלורנס אנד דה משין Everybody Scream</v>
+      </c>
+      <c r="L58" t="str">
+        <v/>
+      </c>
+      <c r="M58" t="str">
+        <v/>
+      </c>
+      <c r="N58" t="str">
+        <v/>
+      </c>
+      <c r="O58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>טיים אימפלה Deadbeat</v>
+      </c>
+      <c r="B59" t="str">
+        <v>2025-11-03</v>
+      </c>
+      <c r="C59" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
+      </c>
+      <c r="D59" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E59" t="str">
+        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
+      </c>
+      <c r="F59" t="str">
+        <v/>
+      </c>
+      <c r="G59" t="str">
+        <v/>
+      </c>
+      <c r="H59" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I59" t="str">
+        <v/>
+      </c>
+      <c r="J59" t="str">
+        <v/>
+      </c>
+      <c r="K59" t="str">
+        <v>טיים אימפלה Deadbeat</v>
+      </c>
+      <c r="L59" t="str">
+        <v/>
+      </c>
+      <c r="M59" t="str">
+        <v/>
+      </c>
+      <c r="N59" t="str">
+        <v/>
+      </c>
+      <c r="O59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+      </c>
+      <c r="B60" t="str">
+        <v>2025-10-20</v>
+      </c>
+      <c r="C60" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
+      </c>
+      <c r="D60" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E60" t="str">
+        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
+      </c>
+      <c r="F60" t="str">
+        <v/>
+      </c>
+      <c r="G60" t="str">
+        <v/>
+      </c>
+      <c r="H60" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I60" t="str">
+        <v/>
+      </c>
+      <c r="J60" t="str">
+        <v/>
+      </c>
+      <c r="K60" t="str">
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+      </c>
+      <c r="L60" t="str">
+        <v/>
+      </c>
+      <c r="M60" t="str">
+        <v/>
+      </c>
+      <c r="N60" t="str">
+        <v/>
+      </c>
+      <c r="O60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>שלמה גרוניך – תודה אהבה</v>
+      </c>
+      <c r="B61" t="str">
+        <v>2025-10-18</v>
+      </c>
+      <c r="C61" t="str">
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
+      </c>
+      <c r="D61" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E61" t="str">
+        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
+      </c>
+      <c r="F61" t="str">
+        <v/>
+      </c>
+      <c r="G61" t="str">
+        <v/>
+      </c>
+      <c r="H61" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I61" t="str">
+        <v/>
+      </c>
+      <c r="J61" t="str">
+        <v/>
+      </c>
+      <c r="K61" t="str">
+        <v>שלמה גרוניך – תודה אהבה</v>
+      </c>
+      <c r="L61" t="str">
+        <v/>
+      </c>
+      <c r="M61" t="str">
+        <v/>
+      </c>
+      <c r="N61" t="str">
+        <v/>
+      </c>
+      <c r="O61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
+      </c>
+      <c r="B62" t="str">
+        <v>2025-10-11</v>
+      </c>
+      <c r="C62" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
+      </c>
+      <c r="D62" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E62" t="str">
+        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
+      </c>
+      <c r="F62" t="str">
+        <v/>
+      </c>
+      <c r="G62" t="str">
+        <v/>
+      </c>
+      <c r="H62" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I62" t="str">
+        <v/>
+      </c>
+      <c r="J62" t="str">
+        <v/>
+      </c>
+      <c r="K62" t="str">
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
+      </c>
+      <c r="L62" t="str">
+        <v/>
+      </c>
+      <c r="M62" t="str">
+        <v/>
+      </c>
+      <c r="N62" t="str">
+        <v/>
+      </c>
+      <c r="O62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>דוג'ה קאט Vie</v>
+      </c>
+      <c r="B63" t="str">
+        <v>2025-10-04</v>
+      </c>
+      <c r="C63" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
+      </c>
+      <c r="D63" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E63" t="str">
+        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
+      </c>
+      <c r="F63" t="str">
+        <v/>
+      </c>
+      <c r="G63" t="str">
+        <v/>
+      </c>
+      <c r="H63" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I63" t="str">
+        <v/>
+      </c>
+      <c r="J63" t="str">
+        <v/>
+      </c>
+      <c r="K63" t="str">
+        <v>דוג'ה קאט Vie</v>
+      </c>
+      <c r="L63" t="str">
+        <v/>
+      </c>
+      <c r="M63" t="str">
+        <v/>
+      </c>
+      <c r="N63" t="str">
+        <v/>
+      </c>
+      <c r="O63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>ג'וי קרוקס Juniper</v>
+      </c>
+      <c r="B64" t="str">
+        <v>2025-10-03</v>
+      </c>
+      <c r="C64" t="str">
+        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
+      </c>
+      <c r="D64" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E64" t="str">
+        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
+      </c>
+      <c r="F64" t="str">
+        <v/>
+      </c>
+      <c r="G64" t="str">
+        <v/>
+      </c>
+      <c r="H64" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I64" t="str">
+        <v/>
+      </c>
+      <c r="J64" t="str">
+        <v/>
+      </c>
+      <c r="K64" t="str">
+        <v>ג'וי קרוקס Juniper</v>
+      </c>
+      <c r="L64" t="str">
+        <v/>
+      </c>
+      <c r="M64" t="str">
+        <v/>
+      </c>
+      <c r="N64" t="str">
+        <v/>
+      </c>
+      <c r="O64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>ביפי קליירו Futique</v>
+      </c>
+      <c r="B65" t="str">
+        <v>2025-09-30</v>
+      </c>
+      <c r="C65" t="str">
+        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
+      </c>
+      <c r="D65" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E65" t="str">
+        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
+      </c>
+      <c r="F65" t="str">
+        <v/>
+      </c>
+      <c r="G65" t="str">
+        <v/>
+      </c>
+      <c r="H65" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I65" t="str">
+        <v/>
+      </c>
+      <c r="J65" t="str">
+        <v/>
+      </c>
+      <c r="K65" t="str">
+        <v>ביפי קליירו Futique</v>
+      </c>
+      <c r="L65" t="str">
+        <v/>
+      </c>
+      <c r="M65" t="str">
+        <v/>
+      </c>
+      <c r="N65" t="str">
+        <v/>
+      </c>
+      <c r="O65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>אד שירן Play</v>
+      </c>
+      <c r="B66" t="str">
+        <v>2025-09-24</v>
+      </c>
+      <c r="C66" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
+      </c>
+      <c r="D66" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E66" t="str">
+        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
+      </c>
+      <c r="F66" t="str">
+        <v/>
+      </c>
+      <c r="G66" t="str">
+        <v/>
+      </c>
+      <c r="H66" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I66" t="str">
+        <v/>
+      </c>
+      <c r="J66" t="str">
+        <v/>
+      </c>
+      <c r="K66" t="str">
+        <v>אד שירן Play</v>
+      </c>
+      <c r="L66" t="str">
+        <v/>
+      </c>
+      <c r="M66" t="str">
+        <v/>
+      </c>
+      <c r="N66" t="str">
+        <v/>
+      </c>
+      <c r="O66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+      </c>
+      <c r="B67" t="str">
+        <v>2025-09-21</v>
+      </c>
+      <c r="C67" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
+      </c>
+      <c r="D67" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E67" t="str">
+        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
+      </c>
+      <c r="F67" t="str">
+        <v/>
+      </c>
+      <c r="G67" t="str">
+        <v/>
+      </c>
+      <c r="H67" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I67" t="str">
+        <v/>
+      </c>
+      <c r="J67" t="str">
+        <v/>
+      </c>
+      <c r="K67" t="str">
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+      </c>
+      <c r="L67" t="str">
+        <v/>
+      </c>
+      <c r="M67" t="str">
+        <v/>
+      </c>
+      <c r="N67" t="str">
+        <v/>
+      </c>
+      <c r="O67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>סוויד Antidepressants</v>
+      </c>
+      <c r="B68" t="str">
+        <v>2025-09-12</v>
+      </c>
+      <c r="C68" t="str">
+        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
+      </c>
+      <c r="D68" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E68" t="str">
+        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
+      </c>
+      <c r="F68" t="str">
+        <v/>
+      </c>
+      <c r="G68" t="str">
+        <v/>
+      </c>
+      <c r="H68" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I68" t="str">
+        <v/>
+      </c>
+      <c r="J68" t="str">
+        <v/>
+      </c>
+      <c r="K68" t="str">
+        <v>סוויד Antidepressants</v>
+      </c>
+      <c r="L68" t="str">
+        <v/>
+      </c>
+      <c r="M68" t="str">
+        <v/>
+      </c>
+      <c r="N68" t="str">
+        <v/>
+      </c>
+      <c r="O68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>וולף אליס The Clearing</v>
+      </c>
+      <c r="B69" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="C69" t="str">
+        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
+      </c>
+      <c r="D69" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E69" t="str">
+        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
+      </c>
+      <c r="F69" t="str">
+        <v/>
+      </c>
+      <c r="G69" t="str">
+        <v/>
+      </c>
+      <c r="H69" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I69" t="str">
+        <v/>
+      </c>
+      <c r="J69" t="str">
+        <v/>
+      </c>
+      <c r="K69" t="str">
+        <v>וולף אליס The Clearing</v>
+      </c>
+      <c r="L69" t="str">
+        <v/>
+      </c>
+      <c r="M69" t="str">
+        <v/>
+      </c>
+      <c r="N69" t="str">
+        <v/>
+      </c>
+      <c r="O69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+      </c>
+      <c r="B70" t="str">
+        <v>2025-08-29</v>
+      </c>
+      <c r="C70" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
+      </c>
+      <c r="D70" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E70" t="str">
+        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
+      </c>
+      <c r="F70" t="str">
+        <v/>
+      </c>
+      <c r="G70" t="str">
+        <v/>
+      </c>
+      <c r="H70" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I70" t="str">
+        <v/>
+      </c>
+      <c r="J70" t="str">
+        <v/>
+      </c>
+      <c r="K70" t="str">
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+      </c>
+      <c r="L70" t="str">
+        <v/>
+      </c>
+      <c r="M70" t="str">
+        <v/>
+      </c>
+      <c r="N70" t="str">
+        <v/>
+      </c>
+      <c r="O70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+      </c>
+      <c r="B71" t="str">
+        <v>2025-08-24</v>
+      </c>
+      <c r="C71" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
+      </c>
+      <c r="D71" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E71" t="str">
+        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
+      </c>
+      <c r="F71" t="str">
+        <v/>
+      </c>
+      <c r="G71" t="str">
+        <v/>
+      </c>
+      <c r="H71" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I71" t="str">
+        <v/>
+      </c>
+      <c r="J71" t="str">
+        <v/>
+      </c>
+      <c r="K71" t="str">
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+      </c>
+      <c r="L71" t="str">
+        <v/>
+      </c>
+      <c r="M71" t="str">
+        <v/>
+      </c>
+      <c r="N71" t="str">
+        <v/>
+      </c>
+      <c r="O71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+      </c>
+      <c r="B72" t="str">
+        <v>2025-08-21</v>
+      </c>
+      <c r="C72" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
+      </c>
+      <c r="D72" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E72" t="str">
+        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
+      </c>
+      <c r="F72" t="str">
+        <v/>
+      </c>
+      <c r="G72" t="str">
+        <v/>
+      </c>
+      <c r="H72" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I72" t="str">
+        <v/>
+      </c>
+      <c r="J72" t="str">
+        <v/>
+      </c>
+      <c r="K72" t="str">
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+      </c>
+      <c r="L72" t="str">
+        <v/>
+      </c>
+      <c r="M72" t="str">
+        <v/>
+      </c>
+      <c r="N72" t="str">
+        <v/>
+      </c>
+      <c r="O72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>אברהם טל – חי</v>
+      </c>
+      <c r="B73" t="str">
+        <v>2025-08-17</v>
+      </c>
+      <c r="C73" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
+      </c>
+      <c r="D73" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E73" t="str">
+        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
+      </c>
+      <c r="F73" t="str">
+        <v/>
+      </c>
+      <c r="G73" t="str">
+        <v/>
+      </c>
+      <c r="H73" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I73" t="str">
+        <v/>
+      </c>
+      <c r="J73" t="str">
+        <v/>
+      </c>
+      <c r="K73" t="str">
+        <v>אברהם טל – חי</v>
+      </c>
+      <c r="L73" t="str">
+        <v/>
+      </c>
+      <c r="M73" t="str">
+        <v/>
+      </c>
+      <c r="N73" t="str">
+        <v/>
+      </c>
+      <c r="O73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>רנה ראפ Bite Me</v>
+      </c>
+      <c r="B74" t="str">
+        <v>2025-08-12</v>
+      </c>
+      <c r="C74" t="str">
+        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
+      </c>
+      <c r="D74" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E74" t="str">
+        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
+      </c>
+      <c r="F74" t="str">
+        <v/>
+      </c>
+      <c r="G74" t="str">
+        <v/>
+      </c>
+      <c r="H74" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I74" t="str">
+        <v/>
+      </c>
+      <c r="J74" t="str">
+        <v/>
+      </c>
+      <c r="K74" t="str">
+        <v>רנה ראפ Bite Me</v>
+      </c>
+      <c r="L74" t="str">
+        <v/>
+      </c>
+      <c r="M74" t="str">
+        <v/>
+      </c>
+      <c r="N74" t="str">
+        <v/>
+      </c>
+      <c r="O74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>The K's – Pretty On The Internet</v>
+      </c>
+      <c r="B75" t="str">
+        <v>2025-08-03</v>
+      </c>
+      <c r="C75" t="str">
+        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
+      </c>
+      <c r="D75" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E75" t="str">
+        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
+      </c>
+      <c r="F75" t="str">
+        <v/>
+      </c>
+      <c r="G75" t="str">
+        <v/>
+      </c>
+      <c r="H75" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I75" t="str">
+        <v/>
+      </c>
+      <c r="J75" t="str">
+        <v/>
+      </c>
+      <c r="K75" t="str">
+        <v>The K's – Pretty On The Internet</v>
+      </c>
+      <c r="L75" t="str">
+        <v/>
+      </c>
+      <c r="M75" t="str">
+        <v/>
+      </c>
+      <c r="N75" t="str">
+        <v/>
+      </c>
+      <c r="O75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>עדן בן זקן - רולקס וקסקט</v>
+      </c>
+      <c r="B76" t="str">
+        <v>2026  08:41-01-14</v>
+      </c>
+      <c r="C76" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24436&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D76" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E76" t="str">
+        <v/>
+      </c>
+      <c r="F76" t="str">
+        <v/>
+      </c>
+      <c r="G76" t="str">
+        <v/>
+      </c>
+      <c r="H76" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I76" t="str">
+        <v/>
+      </c>
+      <c r="J76" t="str">
+        <v/>
+      </c>
+      <c r="K76" t="str">
+        <v>עדן בן זקן - רולקס וקסקט</v>
+      </c>
+      <c r="L76" t="str">
+        <v/>
+      </c>
+      <c r="M76" t="str">
+        <v/>
+      </c>
+      <c r="N76" t="str">
+        <v/>
+      </c>
+      <c r="O76" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
+      </c>
+      <c r="B77" t="str">
+        <v>2026  08:40-01-14</v>
+      </c>
+      <c r="C77" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24439&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D77" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E77" t="str">
+        <v/>
+      </c>
+      <c r="F77" t="str">
+        <v/>
+      </c>
+      <c r="G77" t="str">
+        <v/>
+      </c>
+      <c r="H77" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I77" t="str">
+        <v/>
+      </c>
+      <c r="J77" t="str">
+        <v/>
+      </c>
+      <c r="K77" t="str">
+        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
+      </c>
+      <c r="L77" t="str">
+        <v/>
+      </c>
+      <c r="M77" t="str">
+        <v/>
+      </c>
+      <c r="N77" t="str">
+        <v/>
+      </c>
+      <c r="O77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>אייל גולן - בית מפואר</v>
+      </c>
+      <c r="B78" t="str">
+        <v>2025  02:18-12-31</v>
+      </c>
+      <c r="C78" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D78" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E78" t="str">
+        <v/>
+      </c>
+      <c r="F78" t="str">
+        <v/>
+      </c>
+      <c r="G78" t="str">
+        <v/>
+      </c>
+      <c r="H78" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I78" t="str">
+        <v/>
+      </c>
+      <c r="J78" t="str">
+        <v/>
+      </c>
+      <c r="K78" t="str">
+        <v>אייל גולן - בית מפואר</v>
+      </c>
+      <c r="L78" t="str">
+        <v/>
+      </c>
+      <c r="M78" t="str">
+        <v/>
+      </c>
+      <c r="N78" t="str">
+        <v/>
+      </c>
+      <c r="O78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
+      </c>
+      <c r="B79" t="str">
+        <v>2025  02:16-12-31</v>
+      </c>
+      <c r="C79" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D79" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E79" t="str">
+        <v/>
+      </c>
+      <c r="F79" t="str">
+        <v/>
+      </c>
+      <c r="G79" t="str">
+        <v/>
+      </c>
+      <c r="H79" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I79" t="str">
+        <v/>
+      </c>
+      <c r="J79" t="str">
+        <v/>
+      </c>
+      <c r="K79" t="str">
+        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
+      </c>
+      <c r="L79" t="str">
+        <v/>
+      </c>
+      <c r="M79" t="str">
+        <v/>
+      </c>
+      <c r="N79" t="str">
+        <v/>
+      </c>
+      <c r="O79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>שיר לוי - ילד מוזר</v>
+      </c>
+      <c r="B80" t="str">
+        <v>2025  02:14-12-31</v>
+      </c>
+      <c r="C80" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D80" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E80" t="str">
+        <v/>
+      </c>
+      <c r="F80" t="str">
+        <v/>
+      </c>
+      <c r="G80" t="str">
+        <v/>
+      </c>
+      <c r="H80" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I80" t="str">
+        <v/>
+      </c>
+      <c r="J80" t="str">
+        <v/>
+      </c>
+      <c r="K80" t="str">
+        <v>שיר לוי - ילד מוזר</v>
+      </c>
+      <c r="L80" t="str">
+        <v/>
+      </c>
+      <c r="M80" t="str">
+        <v/>
+      </c>
+      <c r="N80" t="str">
+        <v/>
+      </c>
+      <c r="O80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>פיטר רוט - 50</v>
+      </c>
+      <c r="B81" t="str">
+        <v>2025  02:13-12-31</v>
+      </c>
+      <c r="C81" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D81" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E81" t="str">
+        <v/>
+      </c>
+      <c r="F81" t="str">
+        <v/>
+      </c>
+      <c r="G81" t="str">
+        <v/>
+      </c>
+      <c r="H81" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I81" t="str">
+        <v/>
+      </c>
+      <c r="J81" t="str">
+        <v/>
+      </c>
+      <c r="K81" t="str">
+        <v>פיטר רוט - 50</v>
+      </c>
+      <c r="L81" t="str">
+        <v/>
+      </c>
+      <c r="M81" t="str">
+        <v/>
+      </c>
+      <c r="N81" t="str">
+        <v/>
+      </c>
+      <c r="O81" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>אגם בוחבוט - עשרים ואחת</v>
+      </c>
+      <c r="B82" t="str">
+        <v>2025  02:11-12-31</v>
+      </c>
+      <c r="C82" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D82" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E82" t="str">
+        <v/>
+      </c>
+      <c r="F82" t="str">
+        <v/>
+      </c>
+      <c r="G82" t="str">
+        <v/>
+      </c>
+      <c r="H82" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I82" t="str">
+        <v/>
+      </c>
+      <c r="J82" t="str">
+        <v/>
+      </c>
+      <c r="K82" t="str">
+        <v>אגם בוחבוט - עשרים ואחת</v>
+      </c>
+      <c r="L82" t="str">
+        <v/>
+      </c>
+      <c r="M82" t="str">
+        <v/>
+      </c>
+      <c r="N82" t="str">
+        <v/>
+      </c>
+      <c r="O82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>רבקה זוהר - רסיסים של אור</v>
+      </c>
+      <c r="B83" t="str">
+        <v>2025  02:09-12-31</v>
+      </c>
+      <c r="C83" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D83" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E83" t="str">
+        <v/>
+      </c>
+      <c r="F83" t="str">
+        <v/>
+      </c>
+      <c r="G83" t="str">
+        <v/>
+      </c>
+      <c r="H83" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I83" t="str">
+        <v/>
+      </c>
+      <c r="J83" t="str">
+        <v/>
+      </c>
+      <c r="K83" t="str">
+        <v>רבקה זוהר - רסיסים של אור</v>
+      </c>
+      <c r="L83" t="str">
+        <v/>
+      </c>
+      <c r="M83" t="str">
+        <v/>
+      </c>
+      <c r="N83" t="str">
+        <v/>
+      </c>
+      <c r="O83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
+      </c>
+      <c r="B84" t="str">
+        <v>2025  02:08-12-31</v>
+      </c>
+      <c r="C84" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D84" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E84" t="str">
+        <v/>
+      </c>
+      <c r="F84" t="str">
+        <v/>
+      </c>
+      <c r="G84" t="str">
+        <v/>
+      </c>
+      <c r="H84" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I84" t="str">
+        <v/>
+      </c>
+      <c r="J84" t="str">
+        <v/>
+      </c>
+      <c r="K84" t="str">
+        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
+      </c>
+      <c r="L84" t="str">
+        <v/>
+      </c>
+      <c r="M84" t="str">
+        <v/>
+      </c>
+      <c r="N84" t="str">
+        <v/>
+      </c>
+      <c r="O84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
+      </c>
+      <c r="B85" t="str">
+        <v>2025  02:05-12-31</v>
+      </c>
+      <c r="C85" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D85" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E85" t="str">
+        <v/>
+      </c>
+      <c r="F85" t="str">
+        <v/>
+      </c>
+      <c r="G85" t="str">
+        <v/>
+      </c>
+      <c r="H85" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I85" t="str">
+        <v/>
+      </c>
+      <c r="J85" t="str">
+        <v/>
+      </c>
+      <c r="K85" t="str">
+        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
+      </c>
+      <c r="L85" t="str">
+        <v/>
+      </c>
+      <c r="M85" t="str">
+        <v/>
+      </c>
+      <c r="N85" t="str">
+        <v/>
+      </c>
+      <c r="O85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>Imagine פסטיגל - שירי התחרות</v>
+      </c>
+      <c r="B86" t="str">
+        <v>2025  02:04-12-31</v>
+      </c>
+      <c r="C86" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D86" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E86" t="str">
+        <v/>
+      </c>
+      <c r="F86" t="str">
+        <v/>
+      </c>
+      <c r="G86" t="str">
+        <v/>
+      </c>
+      <c r="H86" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I86" t="str">
+        <v/>
+      </c>
+      <c r="J86" t="str">
+        <v/>
+      </c>
+      <c r="K86" t="str">
+        <v>Imagine פסטיגל - שירי התחרות</v>
+      </c>
+      <c r="L86" t="str">
+        <v/>
+      </c>
+      <c r="M86" t="str">
+        <v/>
+      </c>
+      <c r="N86" t="str">
+        <v/>
+      </c>
+      <c r="O86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>השמחות - חובות אבודים</v>
+      </c>
+      <c r="B87" t="str">
+        <v>2025  02:02-12-31</v>
+      </c>
+      <c r="C87" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D87" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E87" t="str">
+        <v/>
+      </c>
+      <c r="F87" t="str">
+        <v/>
+      </c>
+      <c r="G87" t="str">
+        <v/>
+      </c>
+      <c r="H87" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I87" t="str">
+        <v/>
+      </c>
+      <c r="J87" t="str">
+        <v/>
+      </c>
+      <c r="K87" t="str">
+        <v>השמחות - חובות אבודים</v>
+      </c>
+      <c r="L87" t="str">
+        <v/>
+      </c>
+      <c r="M87" t="str">
+        <v/>
+      </c>
+      <c r="N87" t="str">
+        <v/>
+      </c>
+      <c r="O87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>שלמה גרוניך - כמו כוכבים</v>
+      </c>
+      <c r="B88" t="str">
+        <v>2025  02:00-12-31</v>
+      </c>
+      <c r="C88" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D88" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E88" t="str">
+        <v/>
+      </c>
+      <c r="F88" t="str">
+        <v/>
+      </c>
+      <c r="G88" t="str">
+        <v/>
+      </c>
+      <c r="H88" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I88" t="str">
+        <v/>
+      </c>
+      <c r="J88" t="str">
+        <v/>
+      </c>
+      <c r="K88" t="str">
+        <v>שלמה גרוניך - כמו כוכבים</v>
+      </c>
+      <c r="L88" t="str">
+        <v/>
+      </c>
+      <c r="M88" t="str">
+        <v/>
+      </c>
+      <c r="N88" t="str">
+        <v/>
+      </c>
+      <c r="O88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>יוני רועה - מפוזרים</v>
+      </c>
+      <c r="B89" t="str">
+        <v>2025  01:56-12-31</v>
+      </c>
+      <c r="C89" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D89" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E89" t="str">
+        <v/>
+      </c>
+      <c r="F89" t="str">
+        <v/>
+      </c>
+      <c r="G89" t="str">
+        <v/>
+      </c>
+      <c r="H89" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I89" t="str">
+        <v/>
+      </c>
+      <c r="J89" t="str">
+        <v/>
+      </c>
+      <c r="K89" t="str">
+        <v>יוני רועה - מפוזרים</v>
+      </c>
+      <c r="L89" t="str">
+        <v/>
+      </c>
+      <c r="M89" t="str">
+        <v/>
+      </c>
+      <c r="N89" t="str">
+        <v/>
+      </c>
+      <c r="O89" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K45"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O89"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O89"/>
+  <dimension ref="A1:S133"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3389,7 +3389,7 @@
         <v>עדן בן זקן - רולקס וקסקט</v>
       </c>
       <c r="B76" t="str">
-        <v>2026  08:41-01-14</v>
+        <v>2026  08:41-01-14 | מאת</v>
       </c>
       <c r="C76" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24436&amp;forum=music&amp;viewmode=all</v>
@@ -3436,7 +3436,7 @@
         <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
       </c>
       <c r="B77" t="str">
-        <v>2026  08:40-01-14</v>
+        <v>2026  08:40-01-14 | מאת</v>
       </c>
       <c r="C77" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24439&amp;forum=music&amp;viewmode=all</v>
@@ -3483,7 +3483,7 @@
         <v>אייל גולן - בית מפואר</v>
       </c>
       <c r="B78" t="str">
-        <v>2025  02:18-12-31</v>
+        <v>2025  02:18-12-31 | מאת</v>
       </c>
       <c r="C78" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
@@ -3530,7 +3530,7 @@
         <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
       </c>
       <c r="B79" t="str">
-        <v>2025  02:16-12-31</v>
+        <v>2025  02:16-12-31 | מאת</v>
       </c>
       <c r="C79" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
@@ -3577,7 +3577,7 @@
         <v>שיר לוי - ילד מוזר</v>
       </c>
       <c r="B80" t="str">
-        <v>2025  02:14-12-31</v>
+        <v>2025  02:14-12-31 | מאת</v>
       </c>
       <c r="C80" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
@@ -3624,7 +3624,7 @@
         <v>פיטר רוט - 50</v>
       </c>
       <c r="B81" t="str">
-        <v>2025  02:13-12-31</v>
+        <v>2025  02:13-12-31 | מאת</v>
       </c>
       <c r="C81" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
@@ -3671,7 +3671,7 @@
         <v>אגם בוחבוט - עשרים ואחת</v>
       </c>
       <c r="B82" t="str">
-        <v>2025  02:11-12-31</v>
+        <v>2025  02:11-12-31 | מאת</v>
       </c>
       <c r="C82" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
@@ -3718,7 +3718,7 @@
         <v>רבקה זוהר - רסיסים של אור</v>
       </c>
       <c r="B83" t="str">
-        <v>2025  02:09-12-31</v>
+        <v>2025  02:09-12-31 | מאת</v>
       </c>
       <c r="C83" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
@@ -3765,7 +3765,7 @@
         <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
       </c>
       <c r="B84" t="str">
-        <v>2025  02:08-12-31</v>
+        <v>2025  02:08-12-31 | מאת</v>
       </c>
       <c r="C84" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
@@ -3812,7 +3812,7 @@
         <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
       </c>
       <c r="B85" t="str">
-        <v>2025  02:05-12-31</v>
+        <v>2025  02:05-12-31 | מאת</v>
       </c>
       <c r="C85" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
@@ -3859,7 +3859,7 @@
         <v>Imagine פסטיגל - שירי התחרות</v>
       </c>
       <c r="B86" t="str">
-        <v>2025  02:04-12-31</v>
+        <v>2025  02:04-12-31 | מאת</v>
       </c>
       <c r="C86" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
@@ -3906,7 +3906,7 @@
         <v>השמחות - חובות אבודים</v>
       </c>
       <c r="B87" t="str">
-        <v>2025  02:02-12-31</v>
+        <v>2025  02:02-12-31 | מאת</v>
       </c>
       <c r="C87" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
@@ -3953,7 +3953,7 @@
         <v>שלמה גרוניך - כמו כוכבים</v>
       </c>
       <c r="B88" t="str">
-        <v>2025  02:00-12-31</v>
+        <v>2025  02:00-12-31 | מאת</v>
       </c>
       <c r="C88" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
@@ -4000,7 +4000,7 @@
         <v>יוני רועה - מפוזרים</v>
       </c>
       <c r="B89" t="str">
-        <v>2025  01:56-12-31</v>
+        <v>2025  01:56-12-31 | מאת</v>
       </c>
       <c r="C89" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
@@ -4042,9 +4042,2605 @@
         <v/>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>פטריק סבג Hotel Mogador</v>
+      </c>
+      <c r="B90" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C90" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
+      </c>
+      <c r="D90" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E90" t="str">
+        <v>האלבום של פטריק סבג אינו אוסף שירים אקראי, אלא מרחב. מקום לשהות בו.  נכנסים, שומעים, ויוצאים קצת אחרים. הבחירה בשם "הוטל מוגדור” היא כבר הצהרה. מלון = מקום מעבר, לא בית קבוע, מוגדור = עיר נמל, תנועה, ערבוב תרבויות. כך</v>
+      </c>
+      <c r="F90" t="str">
+        <v/>
+      </c>
+      <c r="G90" t="str">
+        <v/>
+      </c>
+      <c r="H90" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I90" t="str">
+        <v/>
+      </c>
+      <c r="J90" t="str">
+        <v/>
+      </c>
+      <c r="K90" t="str">
+        <v>פטריק סבג Hotel Mogador</v>
+      </c>
+      <c r="L90" t="str">
+        <v/>
+      </c>
+      <c r="M90" t="str">
+        <v/>
+      </c>
+      <c r="N90" t="str">
+        <v/>
+      </c>
+      <c r="O90" t="str">
+        <v/>
+      </c>
+      <c r="P90" t="str">
+        <v/>
+      </c>
+      <c r="Q90" t="str">
+        <v/>
+      </c>
+      <c r="R90" t="str">
+        <v/>
+      </c>
+      <c r="S90" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
+      </c>
+      <c r="B91" t="str">
+        <v>2026-01-09</v>
+      </c>
+      <c r="C91" t="str">
+        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
+      </c>
+      <c r="D91" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E91" t="str">
+        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
+      </c>
+      <c r="F91" t="str">
+        <v/>
+      </c>
+      <c r="G91" t="str">
+        <v/>
+      </c>
+      <c r="H91" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I91" t="str">
+        <v/>
+      </c>
+      <c r="J91" t="str">
+        <v/>
+      </c>
+      <c r="K91" t="str">
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
+      </c>
+      <c r="L91" t="str">
+        <v/>
+      </c>
+      <c r="M91" t="str">
+        <v/>
+      </c>
+      <c r="N91" t="str">
+        <v/>
+      </c>
+      <c r="O91" t="str">
+        <v/>
+      </c>
+      <c r="P91" t="str">
+        <v/>
+      </c>
+      <c r="Q91" t="str">
+        <v/>
+      </c>
+      <c r="R91" t="str">
+        <v/>
+      </c>
+      <c r="S91" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>אוליביה דין The Art of Loving</v>
+      </c>
+      <c r="B92" t="str">
+        <v>2026-01-04</v>
+      </c>
+      <c r="C92" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
+      </c>
+      <c r="D92" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E92" t="str">
+        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
+      </c>
+      <c r="F92" t="str">
+        <v/>
+      </c>
+      <c r="G92" t="str">
+        <v/>
+      </c>
+      <c r="H92" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I92" t="str">
+        <v/>
+      </c>
+      <c r="J92" t="str">
+        <v/>
+      </c>
+      <c r="K92" t="str">
+        <v>אוליביה דין The Art of Loving</v>
+      </c>
+      <c r="L92" t="str">
+        <v/>
+      </c>
+      <c r="M92" t="str">
+        <v/>
+      </c>
+      <c r="N92" t="str">
+        <v/>
+      </c>
+      <c r="O92" t="str">
+        <v/>
+      </c>
+      <c r="P92" t="str">
+        <v/>
+      </c>
+      <c r="Q92" t="str">
+        <v/>
+      </c>
+      <c r="R92" t="str">
+        <v/>
+      </c>
+      <c r="S92" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>Geese Getting Killed</v>
+      </c>
+      <c r="B93" t="str">
+        <v>2025-12-29</v>
+      </c>
+      <c r="C93" t="str">
+        <v>https://yosmusic.com/geese-getting-killed/</v>
+      </c>
+      <c r="D93" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E93" t="str">
+        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
+      </c>
+      <c r="F93" t="str">
+        <v/>
+      </c>
+      <c r="G93" t="str">
+        <v/>
+      </c>
+      <c r="H93" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I93" t="str">
+        <v/>
+      </c>
+      <c r="J93" t="str">
+        <v/>
+      </c>
+      <c r="K93" t="str">
+        <v>Geese Getting Killed</v>
+      </c>
+      <c r="L93" t="str">
+        <v/>
+      </c>
+      <c r="M93" t="str">
+        <v/>
+      </c>
+      <c r="N93" t="str">
+        <v/>
+      </c>
+      <c r="O93" t="str">
+        <v/>
+      </c>
+      <c r="P93" t="str">
+        <v/>
+      </c>
+      <c r="Q93" t="str">
+        <v/>
+      </c>
+      <c r="R93" t="str">
+        <v/>
+      </c>
+      <c r="S93" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>רוסליה Lux</v>
+      </c>
+      <c r="B94" t="str">
+        <v>2025-12-25</v>
+      </c>
+      <c r="C94" t="str">
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
+      </c>
+      <c r="D94" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E94" t="str">
+        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
+      </c>
+      <c r="F94" t="str">
+        <v/>
+      </c>
+      <c r="G94" t="str">
+        <v/>
+      </c>
+      <c r="H94" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I94" t="str">
+        <v/>
+      </c>
+      <c r="J94" t="str">
+        <v/>
+      </c>
+      <c r="K94" t="str">
+        <v>רוסליה Lux</v>
+      </c>
+      <c r="L94" t="str">
+        <v/>
+      </c>
+      <c r="M94" t="str">
+        <v/>
+      </c>
+      <c r="N94" t="str">
+        <v/>
+      </c>
+      <c r="O94" t="str">
+        <v/>
+      </c>
+      <c r="P94" t="str">
+        <v/>
+      </c>
+      <c r="Q94" t="str">
+        <v/>
+      </c>
+      <c r="R94" t="str">
+        <v/>
+      </c>
+      <c r="S94" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>יאנגבלאד אירוסמית' one more time</v>
+      </c>
+      <c r="B95" t="str">
+        <v>2025-12-17</v>
+      </c>
+      <c r="C95" t="str">
+        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
+      </c>
+      <c r="D95" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E95" t="str">
+        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
+      </c>
+      <c r="F95" t="str">
+        <v/>
+      </c>
+      <c r="G95" t="str">
+        <v/>
+      </c>
+      <c r="H95" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I95" t="str">
+        <v/>
+      </c>
+      <c r="J95" t="str">
+        <v/>
+      </c>
+      <c r="K95" t="str">
+        <v>יאנגבלאד אירוסמית' one more time</v>
+      </c>
+      <c r="L95" t="str">
+        <v/>
+      </c>
+      <c r="M95" t="str">
+        <v/>
+      </c>
+      <c r="N95" t="str">
+        <v/>
+      </c>
+      <c r="O95" t="str">
+        <v/>
+      </c>
+      <c r="P95" t="str">
+        <v/>
+      </c>
+      <c r="Q95" t="str">
+        <v/>
+      </c>
+      <c r="R95" t="str">
+        <v/>
+      </c>
+      <c r="S95" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>פינק פלויד Wish You Were Here 50</v>
+      </c>
+      <c r="B96" t="str">
+        <v>2025-12-14</v>
+      </c>
+      <c r="C96" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
+      </c>
+      <c r="D96" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E96" t="str">
+        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
+      </c>
+      <c r="F96" t="str">
+        <v/>
+      </c>
+      <c r="G96" t="str">
+        <v/>
+      </c>
+      <c r="H96" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I96" t="str">
+        <v/>
+      </c>
+      <c r="J96" t="str">
+        <v/>
+      </c>
+      <c r="K96" t="str">
+        <v>פינק פלויד Wish You Were Here 50</v>
+      </c>
+      <c r="L96" t="str">
+        <v/>
+      </c>
+      <c r="M96" t="str">
+        <v/>
+      </c>
+      <c r="N96" t="str">
+        <v/>
+      </c>
+      <c r="O96" t="str">
+        <v/>
+      </c>
+      <c r="P96" t="str">
+        <v/>
+      </c>
+      <c r="Q96" t="str">
+        <v/>
+      </c>
+      <c r="R96" t="str">
+        <v/>
+      </c>
+      <c r="S96" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+      </c>
+      <c r="B97" t="str">
+        <v>2025-12-08</v>
+      </c>
+      <c r="C97" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
+      </c>
+      <c r="D97" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E97" t="str">
+        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
+      </c>
+      <c r="F97" t="str">
+        <v/>
+      </c>
+      <c r="G97" t="str">
+        <v/>
+      </c>
+      <c r="H97" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I97" t="str">
+        <v/>
+      </c>
+      <c r="J97" t="str">
+        <v/>
+      </c>
+      <c r="K97" t="str">
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+      </c>
+      <c r="L97" t="str">
+        <v/>
+      </c>
+      <c r="M97" t="str">
+        <v/>
+      </c>
+      <c r="N97" t="str">
+        <v/>
+      </c>
+      <c r="O97" t="str">
+        <v/>
+      </c>
+      <c r="P97" t="str">
+        <v/>
+      </c>
+      <c r="Q97" t="str">
+        <v/>
+      </c>
+      <c r="R97" t="str">
+        <v/>
+      </c>
+      <c r="S97" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>סטריי קידס DO IT EP</v>
+      </c>
+      <c r="B98" t="str">
+        <v>2025-12-04</v>
+      </c>
+      <c r="C98" t="str">
+        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
+      </c>
+      <c r="D98" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E98" t="str">
+        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
+      </c>
+      <c r="F98" t="str">
+        <v/>
+      </c>
+      <c r="G98" t="str">
+        <v/>
+      </c>
+      <c r="H98" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I98" t="str">
+        <v/>
+      </c>
+      <c r="J98" t="str">
+        <v/>
+      </c>
+      <c r="K98" t="str">
+        <v>סטריי קידס DO IT EP</v>
+      </c>
+      <c r="L98" t="str">
+        <v/>
+      </c>
+      <c r="M98" t="str">
+        <v/>
+      </c>
+      <c r="N98" t="str">
+        <v/>
+      </c>
+      <c r="O98" t="str">
+        <v/>
+      </c>
+      <c r="P98" t="str">
+        <v/>
+      </c>
+      <c r="Q98" t="str">
+        <v/>
+      </c>
+      <c r="R98" t="str">
+        <v/>
+      </c>
+      <c r="S98" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>דויד ברוזה BROZAJAZZ</v>
+      </c>
+      <c r="B99" t="str">
+        <v>2025-11-30</v>
+      </c>
+      <c r="C99" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
+      </c>
+      <c r="D99" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E99" t="str">
+        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
+      </c>
+      <c r="F99" t="str">
+        <v/>
+      </c>
+      <c r="G99" t="str">
+        <v/>
+      </c>
+      <c r="H99" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I99" t="str">
+        <v/>
+      </c>
+      <c r="J99" t="str">
+        <v/>
+      </c>
+      <c r="K99" t="str">
+        <v>דויד ברוזה BROZAJAZZ</v>
+      </c>
+      <c r="L99" t="str">
+        <v/>
+      </c>
+      <c r="M99" t="str">
+        <v/>
+      </c>
+      <c r="N99" t="str">
+        <v/>
+      </c>
+      <c r="O99" t="str">
+        <v/>
+      </c>
+      <c r="P99" t="str">
+        <v/>
+      </c>
+      <c r="Q99" t="str">
+        <v/>
+      </c>
+      <c r="R99" t="str">
+        <v/>
+      </c>
+      <c r="S99" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>Five Seconds of Summer – Everyone's A Star</v>
+      </c>
+      <c r="B100" t="str">
+        <v>2025-11-24</v>
+      </c>
+      <c r="C100" t="str">
+        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
+      </c>
+      <c r="D100" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E100" t="str">
+        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
+      </c>
+      <c r="F100" t="str">
+        <v/>
+      </c>
+      <c r="G100" t="str">
+        <v/>
+      </c>
+      <c r="H100" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I100" t="str">
+        <v/>
+      </c>
+      <c r="J100" t="str">
+        <v/>
+      </c>
+      <c r="K100" t="str">
+        <v>Five Seconds of Summer – Everyone's A Star</v>
+      </c>
+      <c r="L100" t="str">
+        <v/>
+      </c>
+      <c r="M100" t="str">
+        <v/>
+      </c>
+      <c r="N100" t="str">
+        <v/>
+      </c>
+      <c r="O100" t="str">
+        <v/>
+      </c>
+      <c r="P100" t="str">
+        <v/>
+      </c>
+      <c r="Q100" t="str">
+        <v/>
+      </c>
+      <c r="R100" t="str">
+        <v/>
+      </c>
+      <c r="S100" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>התקווה 6 – ויהי אור</v>
+      </c>
+      <c r="B101" t="str">
+        <v>2025-11-20</v>
+      </c>
+      <c r="C101" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
+      </c>
+      <c r="D101" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E101" t="str">
+        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
+      </c>
+      <c r="F101" t="str">
+        <v/>
+      </c>
+      <c r="G101" t="str">
+        <v/>
+      </c>
+      <c r="H101" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I101" t="str">
+        <v/>
+      </c>
+      <c r="J101" t="str">
+        <v/>
+      </c>
+      <c r="K101" t="str">
+        <v>התקווה 6 – ויהי אור</v>
+      </c>
+      <c r="L101" t="str">
+        <v/>
+      </c>
+      <c r="M101" t="str">
+        <v/>
+      </c>
+      <c r="N101" t="str">
+        <v/>
+      </c>
+      <c r="O101" t="str">
+        <v/>
+      </c>
+      <c r="P101" t="str">
+        <v/>
+      </c>
+      <c r="Q101" t="str">
+        <v/>
+      </c>
+      <c r="R101" t="str">
+        <v/>
+      </c>
+      <c r="S101" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>פלורנס אנד דה משין Everybody Scream</v>
+      </c>
+      <c r="B102" t="str">
+        <v>2025-11-13</v>
+      </c>
+      <c r="C102" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
+      </c>
+      <c r="D102" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E102" t="str">
+        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
+      </c>
+      <c r="F102" t="str">
+        <v/>
+      </c>
+      <c r="G102" t="str">
+        <v/>
+      </c>
+      <c r="H102" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I102" t="str">
+        <v/>
+      </c>
+      <c r="J102" t="str">
+        <v/>
+      </c>
+      <c r="K102" t="str">
+        <v>פלורנס אנד דה משין Everybody Scream</v>
+      </c>
+      <c r="L102" t="str">
+        <v/>
+      </c>
+      <c r="M102" t="str">
+        <v/>
+      </c>
+      <c r="N102" t="str">
+        <v/>
+      </c>
+      <c r="O102" t="str">
+        <v/>
+      </c>
+      <c r="P102" t="str">
+        <v/>
+      </c>
+      <c r="Q102" t="str">
+        <v/>
+      </c>
+      <c r="R102" t="str">
+        <v/>
+      </c>
+      <c r="S102" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>טיים אימפלה Deadbeat</v>
+      </c>
+      <c r="B103" t="str">
+        <v>2025-11-03</v>
+      </c>
+      <c r="C103" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
+      </c>
+      <c r="D103" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E103" t="str">
+        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
+      </c>
+      <c r="F103" t="str">
+        <v/>
+      </c>
+      <c r="G103" t="str">
+        <v/>
+      </c>
+      <c r="H103" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I103" t="str">
+        <v/>
+      </c>
+      <c r="J103" t="str">
+        <v/>
+      </c>
+      <c r="K103" t="str">
+        <v>טיים אימפלה Deadbeat</v>
+      </c>
+      <c r="L103" t="str">
+        <v/>
+      </c>
+      <c r="M103" t="str">
+        <v/>
+      </c>
+      <c r="N103" t="str">
+        <v/>
+      </c>
+      <c r="O103" t="str">
+        <v/>
+      </c>
+      <c r="P103" t="str">
+        <v/>
+      </c>
+      <c r="Q103" t="str">
+        <v/>
+      </c>
+      <c r="R103" t="str">
+        <v/>
+      </c>
+      <c r="S103" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+      </c>
+      <c r="B104" t="str">
+        <v>2025-10-20</v>
+      </c>
+      <c r="C104" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
+      </c>
+      <c r="D104" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E104" t="str">
+        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
+      </c>
+      <c r="F104" t="str">
+        <v/>
+      </c>
+      <c r="G104" t="str">
+        <v/>
+      </c>
+      <c r="H104" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I104" t="str">
+        <v/>
+      </c>
+      <c r="J104" t="str">
+        <v/>
+      </c>
+      <c r="K104" t="str">
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+      </c>
+      <c r="L104" t="str">
+        <v/>
+      </c>
+      <c r="M104" t="str">
+        <v/>
+      </c>
+      <c r="N104" t="str">
+        <v/>
+      </c>
+      <c r="O104" t="str">
+        <v/>
+      </c>
+      <c r="P104" t="str">
+        <v/>
+      </c>
+      <c r="Q104" t="str">
+        <v/>
+      </c>
+      <c r="R104" t="str">
+        <v/>
+      </c>
+      <c r="S104" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>שלמה גרוניך – תודה אהבה</v>
+      </c>
+      <c r="B105" t="str">
+        <v>2025-10-18</v>
+      </c>
+      <c r="C105" t="str">
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
+      </c>
+      <c r="D105" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E105" t="str">
+        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
+      </c>
+      <c r="F105" t="str">
+        <v/>
+      </c>
+      <c r="G105" t="str">
+        <v/>
+      </c>
+      <c r="H105" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I105" t="str">
+        <v/>
+      </c>
+      <c r="J105" t="str">
+        <v/>
+      </c>
+      <c r="K105" t="str">
+        <v>שלמה גרוניך – תודה אהבה</v>
+      </c>
+      <c r="L105" t="str">
+        <v/>
+      </c>
+      <c r="M105" t="str">
+        <v/>
+      </c>
+      <c r="N105" t="str">
+        <v/>
+      </c>
+      <c r="O105" t="str">
+        <v/>
+      </c>
+      <c r="P105" t="str">
+        <v/>
+      </c>
+      <c r="Q105" t="str">
+        <v/>
+      </c>
+      <c r="R105" t="str">
+        <v/>
+      </c>
+      <c r="S105" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
+      </c>
+      <c r="B106" t="str">
+        <v>2025-10-11</v>
+      </c>
+      <c r="C106" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
+      </c>
+      <c r="D106" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E106" t="str">
+        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
+      </c>
+      <c r="F106" t="str">
+        <v/>
+      </c>
+      <c r="G106" t="str">
+        <v/>
+      </c>
+      <c r="H106" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I106" t="str">
+        <v/>
+      </c>
+      <c r="J106" t="str">
+        <v/>
+      </c>
+      <c r="K106" t="str">
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
+      </c>
+      <c r="L106" t="str">
+        <v/>
+      </c>
+      <c r="M106" t="str">
+        <v/>
+      </c>
+      <c r="N106" t="str">
+        <v/>
+      </c>
+      <c r="O106" t="str">
+        <v/>
+      </c>
+      <c r="P106" t="str">
+        <v/>
+      </c>
+      <c r="Q106" t="str">
+        <v/>
+      </c>
+      <c r="R106" t="str">
+        <v/>
+      </c>
+      <c r="S106" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>דוג'ה קאט Vie</v>
+      </c>
+      <c r="B107" t="str">
+        <v>2025-10-04</v>
+      </c>
+      <c r="C107" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
+      </c>
+      <c r="D107" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E107" t="str">
+        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
+      </c>
+      <c r="F107" t="str">
+        <v/>
+      </c>
+      <c r="G107" t="str">
+        <v/>
+      </c>
+      <c r="H107" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I107" t="str">
+        <v/>
+      </c>
+      <c r="J107" t="str">
+        <v/>
+      </c>
+      <c r="K107" t="str">
+        <v>דוג'ה קאט Vie</v>
+      </c>
+      <c r="L107" t="str">
+        <v/>
+      </c>
+      <c r="M107" t="str">
+        <v/>
+      </c>
+      <c r="N107" t="str">
+        <v/>
+      </c>
+      <c r="O107" t="str">
+        <v/>
+      </c>
+      <c r="P107" t="str">
+        <v/>
+      </c>
+      <c r="Q107" t="str">
+        <v/>
+      </c>
+      <c r="R107" t="str">
+        <v/>
+      </c>
+      <c r="S107" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>ג'וי קרוקס Juniper</v>
+      </c>
+      <c r="B108" t="str">
+        <v>2025-10-03</v>
+      </c>
+      <c r="C108" t="str">
+        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
+      </c>
+      <c r="D108" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E108" t="str">
+        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
+      </c>
+      <c r="F108" t="str">
+        <v/>
+      </c>
+      <c r="G108" t="str">
+        <v/>
+      </c>
+      <c r="H108" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I108" t="str">
+        <v/>
+      </c>
+      <c r="J108" t="str">
+        <v/>
+      </c>
+      <c r="K108" t="str">
+        <v>ג'וי קרוקס Juniper</v>
+      </c>
+      <c r="L108" t="str">
+        <v/>
+      </c>
+      <c r="M108" t="str">
+        <v/>
+      </c>
+      <c r="N108" t="str">
+        <v/>
+      </c>
+      <c r="O108" t="str">
+        <v/>
+      </c>
+      <c r="P108" t="str">
+        <v/>
+      </c>
+      <c r="Q108" t="str">
+        <v/>
+      </c>
+      <c r="R108" t="str">
+        <v/>
+      </c>
+      <c r="S108" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>ביפי קליירו Futique</v>
+      </c>
+      <c r="B109" t="str">
+        <v>2025-09-30</v>
+      </c>
+      <c r="C109" t="str">
+        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
+      </c>
+      <c r="D109" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E109" t="str">
+        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
+      </c>
+      <c r="F109" t="str">
+        <v/>
+      </c>
+      <c r="G109" t="str">
+        <v/>
+      </c>
+      <c r="H109" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I109" t="str">
+        <v/>
+      </c>
+      <c r="J109" t="str">
+        <v/>
+      </c>
+      <c r="K109" t="str">
+        <v>ביפי קליירו Futique</v>
+      </c>
+      <c r="L109" t="str">
+        <v/>
+      </c>
+      <c r="M109" t="str">
+        <v/>
+      </c>
+      <c r="N109" t="str">
+        <v/>
+      </c>
+      <c r="O109" t="str">
+        <v/>
+      </c>
+      <c r="P109" t="str">
+        <v/>
+      </c>
+      <c r="Q109" t="str">
+        <v/>
+      </c>
+      <c r="R109" t="str">
+        <v/>
+      </c>
+      <c r="S109" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>אד שירן Play</v>
+      </c>
+      <c r="B110" t="str">
+        <v>2025-09-24</v>
+      </c>
+      <c r="C110" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
+      </c>
+      <c r="D110" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E110" t="str">
+        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
+      </c>
+      <c r="F110" t="str">
+        <v/>
+      </c>
+      <c r="G110" t="str">
+        <v/>
+      </c>
+      <c r="H110" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I110" t="str">
+        <v/>
+      </c>
+      <c r="J110" t="str">
+        <v/>
+      </c>
+      <c r="K110" t="str">
+        <v>אד שירן Play</v>
+      </c>
+      <c r="L110" t="str">
+        <v/>
+      </c>
+      <c r="M110" t="str">
+        <v/>
+      </c>
+      <c r="N110" t="str">
+        <v/>
+      </c>
+      <c r="O110" t="str">
+        <v/>
+      </c>
+      <c r="P110" t="str">
+        <v/>
+      </c>
+      <c r="Q110" t="str">
+        <v/>
+      </c>
+      <c r="R110" t="str">
+        <v/>
+      </c>
+      <c r="S110" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+      </c>
+      <c r="B111" t="str">
+        <v>2025-09-21</v>
+      </c>
+      <c r="C111" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
+      </c>
+      <c r="D111" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E111" t="str">
+        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
+      </c>
+      <c r="F111" t="str">
+        <v/>
+      </c>
+      <c r="G111" t="str">
+        <v/>
+      </c>
+      <c r="H111" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I111" t="str">
+        <v/>
+      </c>
+      <c r="J111" t="str">
+        <v/>
+      </c>
+      <c r="K111" t="str">
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+      </c>
+      <c r="L111" t="str">
+        <v/>
+      </c>
+      <c r="M111" t="str">
+        <v/>
+      </c>
+      <c r="N111" t="str">
+        <v/>
+      </c>
+      <c r="O111" t="str">
+        <v/>
+      </c>
+      <c r="P111" t="str">
+        <v/>
+      </c>
+      <c r="Q111" t="str">
+        <v/>
+      </c>
+      <c r="R111" t="str">
+        <v/>
+      </c>
+      <c r="S111" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>סוויד Antidepressants</v>
+      </c>
+      <c r="B112" t="str">
+        <v>2025-09-12</v>
+      </c>
+      <c r="C112" t="str">
+        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
+      </c>
+      <c r="D112" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E112" t="str">
+        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
+      </c>
+      <c r="F112" t="str">
+        <v/>
+      </c>
+      <c r="G112" t="str">
+        <v/>
+      </c>
+      <c r="H112" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I112" t="str">
+        <v/>
+      </c>
+      <c r="J112" t="str">
+        <v/>
+      </c>
+      <c r="K112" t="str">
+        <v>סוויד Antidepressants</v>
+      </c>
+      <c r="L112" t="str">
+        <v/>
+      </c>
+      <c r="M112" t="str">
+        <v/>
+      </c>
+      <c r="N112" t="str">
+        <v/>
+      </c>
+      <c r="O112" t="str">
+        <v/>
+      </c>
+      <c r="P112" t="str">
+        <v/>
+      </c>
+      <c r="Q112" t="str">
+        <v/>
+      </c>
+      <c r="R112" t="str">
+        <v/>
+      </c>
+      <c r="S112" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>וולף אליס The Clearing</v>
+      </c>
+      <c r="B113" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="C113" t="str">
+        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
+      </c>
+      <c r="D113" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E113" t="str">
+        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
+      </c>
+      <c r="F113" t="str">
+        <v/>
+      </c>
+      <c r="G113" t="str">
+        <v/>
+      </c>
+      <c r="H113" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I113" t="str">
+        <v/>
+      </c>
+      <c r="J113" t="str">
+        <v/>
+      </c>
+      <c r="K113" t="str">
+        <v>וולף אליס The Clearing</v>
+      </c>
+      <c r="L113" t="str">
+        <v/>
+      </c>
+      <c r="M113" t="str">
+        <v/>
+      </c>
+      <c r="N113" t="str">
+        <v/>
+      </c>
+      <c r="O113" t="str">
+        <v/>
+      </c>
+      <c r="P113" t="str">
+        <v/>
+      </c>
+      <c r="Q113" t="str">
+        <v/>
+      </c>
+      <c r="R113" t="str">
+        <v/>
+      </c>
+      <c r="S113" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+      </c>
+      <c r="B114" t="str">
+        <v>2025-08-29</v>
+      </c>
+      <c r="C114" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
+      </c>
+      <c r="D114" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E114" t="str">
+        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
+      </c>
+      <c r="F114" t="str">
+        <v/>
+      </c>
+      <c r="G114" t="str">
+        <v/>
+      </c>
+      <c r="H114" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I114" t="str">
+        <v/>
+      </c>
+      <c r="J114" t="str">
+        <v/>
+      </c>
+      <c r="K114" t="str">
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+      </c>
+      <c r="L114" t="str">
+        <v/>
+      </c>
+      <c r="M114" t="str">
+        <v/>
+      </c>
+      <c r="N114" t="str">
+        <v/>
+      </c>
+      <c r="O114" t="str">
+        <v/>
+      </c>
+      <c r="P114" t="str">
+        <v/>
+      </c>
+      <c r="Q114" t="str">
+        <v/>
+      </c>
+      <c r="R114" t="str">
+        <v/>
+      </c>
+      <c r="S114" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+      </c>
+      <c r="B115" t="str">
+        <v>2025-08-24</v>
+      </c>
+      <c r="C115" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
+      </c>
+      <c r="D115" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E115" t="str">
+        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
+      </c>
+      <c r="F115" t="str">
+        <v/>
+      </c>
+      <c r="G115" t="str">
+        <v/>
+      </c>
+      <c r="H115" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I115" t="str">
+        <v/>
+      </c>
+      <c r="J115" t="str">
+        <v/>
+      </c>
+      <c r="K115" t="str">
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+      </c>
+      <c r="L115" t="str">
+        <v/>
+      </c>
+      <c r="M115" t="str">
+        <v/>
+      </c>
+      <c r="N115" t="str">
+        <v/>
+      </c>
+      <c r="O115" t="str">
+        <v/>
+      </c>
+      <c r="P115" t="str">
+        <v/>
+      </c>
+      <c r="Q115" t="str">
+        <v/>
+      </c>
+      <c r="R115" t="str">
+        <v/>
+      </c>
+      <c r="S115" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+      </c>
+      <c r="B116" t="str">
+        <v>2025-08-21</v>
+      </c>
+      <c r="C116" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
+      </c>
+      <c r="D116" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E116" t="str">
+        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
+      </c>
+      <c r="F116" t="str">
+        <v/>
+      </c>
+      <c r="G116" t="str">
+        <v/>
+      </c>
+      <c r="H116" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I116" t="str">
+        <v/>
+      </c>
+      <c r="J116" t="str">
+        <v/>
+      </c>
+      <c r="K116" t="str">
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+      </c>
+      <c r="L116" t="str">
+        <v/>
+      </c>
+      <c r="M116" t="str">
+        <v/>
+      </c>
+      <c r="N116" t="str">
+        <v/>
+      </c>
+      <c r="O116" t="str">
+        <v/>
+      </c>
+      <c r="P116" t="str">
+        <v/>
+      </c>
+      <c r="Q116" t="str">
+        <v/>
+      </c>
+      <c r="R116" t="str">
+        <v/>
+      </c>
+      <c r="S116" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>אברהם טל – חי</v>
+      </c>
+      <c r="B117" t="str">
+        <v>2025-08-17</v>
+      </c>
+      <c r="C117" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
+      </c>
+      <c r="D117" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E117" t="str">
+        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
+      </c>
+      <c r="F117" t="str">
+        <v/>
+      </c>
+      <c r="G117" t="str">
+        <v/>
+      </c>
+      <c r="H117" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I117" t="str">
+        <v/>
+      </c>
+      <c r="J117" t="str">
+        <v/>
+      </c>
+      <c r="K117" t="str">
+        <v>אברהם טל – חי</v>
+      </c>
+      <c r="L117" t="str">
+        <v/>
+      </c>
+      <c r="M117" t="str">
+        <v/>
+      </c>
+      <c r="N117" t="str">
+        <v/>
+      </c>
+      <c r="O117" t="str">
+        <v/>
+      </c>
+      <c r="P117" t="str">
+        <v/>
+      </c>
+      <c r="Q117" t="str">
+        <v/>
+      </c>
+      <c r="R117" t="str">
+        <v/>
+      </c>
+      <c r="S117" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>רנה ראפ Bite Me</v>
+      </c>
+      <c r="B118" t="str">
+        <v>2025-08-12</v>
+      </c>
+      <c r="C118" t="str">
+        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
+      </c>
+      <c r="D118" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E118" t="str">
+        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
+      </c>
+      <c r="F118" t="str">
+        <v/>
+      </c>
+      <c r="G118" t="str">
+        <v/>
+      </c>
+      <c r="H118" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I118" t="str">
+        <v/>
+      </c>
+      <c r="J118" t="str">
+        <v/>
+      </c>
+      <c r="K118" t="str">
+        <v>רנה ראפ Bite Me</v>
+      </c>
+      <c r="L118" t="str">
+        <v/>
+      </c>
+      <c r="M118" t="str">
+        <v/>
+      </c>
+      <c r="N118" t="str">
+        <v/>
+      </c>
+      <c r="O118" t="str">
+        <v/>
+      </c>
+      <c r="P118" t="str">
+        <v/>
+      </c>
+      <c r="Q118" t="str">
+        <v/>
+      </c>
+      <c r="R118" t="str">
+        <v/>
+      </c>
+      <c r="S118" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>The K's – Pretty On The Internet</v>
+      </c>
+      <c r="B119" t="str">
+        <v>2025-08-03</v>
+      </c>
+      <c r="C119" t="str">
+        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
+      </c>
+      <c r="D119" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E119" t="str">
+        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
+      </c>
+      <c r="F119" t="str">
+        <v/>
+      </c>
+      <c r="G119" t="str">
+        <v/>
+      </c>
+      <c r="H119" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I119" t="str">
+        <v/>
+      </c>
+      <c r="J119" t="str">
+        <v/>
+      </c>
+      <c r="K119" t="str">
+        <v>The K's – Pretty On The Internet</v>
+      </c>
+      <c r="L119" t="str">
+        <v/>
+      </c>
+      <c r="M119" t="str">
+        <v/>
+      </c>
+      <c r="N119" t="str">
+        <v/>
+      </c>
+      <c r="O119" t="str">
+        <v/>
+      </c>
+      <c r="P119" t="str">
+        <v/>
+      </c>
+      <c r="Q119" t="str">
+        <v/>
+      </c>
+      <c r="R119" t="str">
+        <v/>
+      </c>
+      <c r="S119" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>עדן בן זקן - רולקס וקסקט</v>
+      </c>
+      <c r="B120" t="str">
+        <v>2026  08:41-01-14</v>
+      </c>
+      <c r="C120" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24436&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D120" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E120" t="str">
+        <v/>
+      </c>
+      <c r="F120" t="str">
+        <v/>
+      </c>
+      <c r="G120" t="str">
+        <v/>
+      </c>
+      <c r="H120" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I120" t="str">
+        <v/>
+      </c>
+      <c r="J120" t="str">
+        <v/>
+      </c>
+      <c r="K120" t="str">
+        <v>עדן בן זקן - רולקס וקסקט</v>
+      </c>
+      <c r="L120" t="str">
+        <v/>
+      </c>
+      <c r="M120" t="str">
+        <v/>
+      </c>
+      <c r="N120" t="str">
+        <v/>
+      </c>
+      <c r="O120" t="str">
+        <v/>
+      </c>
+      <c r="P120" t="str">
+        <v/>
+      </c>
+      <c r="Q120" t="str">
+        <v/>
+      </c>
+      <c r="R120" t="str">
+        <v/>
+      </c>
+      <c r="S120" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
+      </c>
+      <c r="B121" t="str">
+        <v>2026  08:40-01-14</v>
+      </c>
+      <c r="C121" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24439&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D121" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E121" t="str">
+        <v/>
+      </c>
+      <c r="F121" t="str">
+        <v/>
+      </c>
+      <c r="G121" t="str">
+        <v/>
+      </c>
+      <c r="H121" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I121" t="str">
+        <v/>
+      </c>
+      <c r="J121" t="str">
+        <v/>
+      </c>
+      <c r="K121" t="str">
+        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
+      </c>
+      <c r="L121" t="str">
+        <v/>
+      </c>
+      <c r="M121" t="str">
+        <v/>
+      </c>
+      <c r="N121" t="str">
+        <v/>
+      </c>
+      <c r="O121" t="str">
+        <v/>
+      </c>
+      <c r="P121" t="str">
+        <v/>
+      </c>
+      <c r="Q121" t="str">
+        <v/>
+      </c>
+      <c r="R121" t="str">
+        <v/>
+      </c>
+      <c r="S121" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>אייל גולן - בית מפואר</v>
+      </c>
+      <c r="B122" t="str">
+        <v>2025  02:18-12-31</v>
+      </c>
+      <c r="C122" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D122" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E122" t="str">
+        <v/>
+      </c>
+      <c r="F122" t="str">
+        <v/>
+      </c>
+      <c r="G122" t="str">
+        <v/>
+      </c>
+      <c r="H122" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I122" t="str">
+        <v/>
+      </c>
+      <c r="J122" t="str">
+        <v/>
+      </c>
+      <c r="K122" t="str">
+        <v>אייל גולן - בית מפואר</v>
+      </c>
+      <c r="L122" t="str">
+        <v/>
+      </c>
+      <c r="M122" t="str">
+        <v/>
+      </c>
+      <c r="N122" t="str">
+        <v/>
+      </c>
+      <c r="O122" t="str">
+        <v/>
+      </c>
+      <c r="P122" t="str">
+        <v/>
+      </c>
+      <c r="Q122" t="str">
+        <v/>
+      </c>
+      <c r="R122" t="str">
+        <v/>
+      </c>
+      <c r="S122" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
+      </c>
+      <c r="B123" t="str">
+        <v>2025  02:16-12-31</v>
+      </c>
+      <c r="C123" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D123" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E123" t="str">
+        <v/>
+      </c>
+      <c r="F123" t="str">
+        <v/>
+      </c>
+      <c r="G123" t="str">
+        <v/>
+      </c>
+      <c r="H123" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I123" t="str">
+        <v/>
+      </c>
+      <c r="J123" t="str">
+        <v/>
+      </c>
+      <c r="K123" t="str">
+        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
+      </c>
+      <c r="L123" t="str">
+        <v/>
+      </c>
+      <c r="M123" t="str">
+        <v/>
+      </c>
+      <c r="N123" t="str">
+        <v/>
+      </c>
+      <c r="O123" t="str">
+        <v/>
+      </c>
+      <c r="P123" t="str">
+        <v/>
+      </c>
+      <c r="Q123" t="str">
+        <v/>
+      </c>
+      <c r="R123" t="str">
+        <v/>
+      </c>
+      <c r="S123" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>שיר לוי - ילד מוזר</v>
+      </c>
+      <c r="B124" t="str">
+        <v>2025  02:14-12-31</v>
+      </c>
+      <c r="C124" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D124" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E124" t="str">
+        <v/>
+      </c>
+      <c r="F124" t="str">
+        <v/>
+      </c>
+      <c r="G124" t="str">
+        <v/>
+      </c>
+      <c r="H124" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I124" t="str">
+        <v/>
+      </c>
+      <c r="J124" t="str">
+        <v/>
+      </c>
+      <c r="K124" t="str">
+        <v>שיר לוי - ילד מוזר</v>
+      </c>
+      <c r="L124" t="str">
+        <v/>
+      </c>
+      <c r="M124" t="str">
+        <v/>
+      </c>
+      <c r="N124" t="str">
+        <v/>
+      </c>
+      <c r="O124" t="str">
+        <v/>
+      </c>
+      <c r="P124" t="str">
+        <v/>
+      </c>
+      <c r="Q124" t="str">
+        <v/>
+      </c>
+      <c r="R124" t="str">
+        <v/>
+      </c>
+      <c r="S124" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>פיטר רוט - 50</v>
+      </c>
+      <c r="B125" t="str">
+        <v>2025  02:13-12-31</v>
+      </c>
+      <c r="C125" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D125" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E125" t="str">
+        <v/>
+      </c>
+      <c r="F125" t="str">
+        <v/>
+      </c>
+      <c r="G125" t="str">
+        <v/>
+      </c>
+      <c r="H125" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I125" t="str">
+        <v/>
+      </c>
+      <c r="J125" t="str">
+        <v/>
+      </c>
+      <c r="K125" t="str">
+        <v>פיטר רוט - 50</v>
+      </c>
+      <c r="L125" t="str">
+        <v/>
+      </c>
+      <c r="M125" t="str">
+        <v/>
+      </c>
+      <c r="N125" t="str">
+        <v/>
+      </c>
+      <c r="O125" t="str">
+        <v/>
+      </c>
+      <c r="P125" t="str">
+        <v/>
+      </c>
+      <c r="Q125" t="str">
+        <v/>
+      </c>
+      <c r="R125" t="str">
+        <v/>
+      </c>
+      <c r="S125" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>אגם בוחבוט - עשרים ואחת</v>
+      </c>
+      <c r="B126" t="str">
+        <v>2025  02:11-12-31</v>
+      </c>
+      <c r="C126" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D126" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E126" t="str">
+        <v/>
+      </c>
+      <c r="F126" t="str">
+        <v/>
+      </c>
+      <c r="G126" t="str">
+        <v/>
+      </c>
+      <c r="H126" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I126" t="str">
+        <v/>
+      </c>
+      <c r="J126" t="str">
+        <v/>
+      </c>
+      <c r="K126" t="str">
+        <v>אגם בוחבוט - עשרים ואחת</v>
+      </c>
+      <c r="L126" t="str">
+        <v/>
+      </c>
+      <c r="M126" t="str">
+        <v/>
+      </c>
+      <c r="N126" t="str">
+        <v/>
+      </c>
+      <c r="O126" t="str">
+        <v/>
+      </c>
+      <c r="P126" t="str">
+        <v/>
+      </c>
+      <c r="Q126" t="str">
+        <v/>
+      </c>
+      <c r="R126" t="str">
+        <v/>
+      </c>
+      <c r="S126" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>רבקה זוהר - רסיסים של אור</v>
+      </c>
+      <c r="B127" t="str">
+        <v>2025  02:09-12-31</v>
+      </c>
+      <c r="C127" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D127" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E127" t="str">
+        <v/>
+      </c>
+      <c r="F127" t="str">
+        <v/>
+      </c>
+      <c r="G127" t="str">
+        <v/>
+      </c>
+      <c r="H127" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I127" t="str">
+        <v/>
+      </c>
+      <c r="J127" t="str">
+        <v/>
+      </c>
+      <c r="K127" t="str">
+        <v>רבקה זוהר - רסיסים של אור</v>
+      </c>
+      <c r="L127" t="str">
+        <v/>
+      </c>
+      <c r="M127" t="str">
+        <v/>
+      </c>
+      <c r="N127" t="str">
+        <v/>
+      </c>
+      <c r="O127" t="str">
+        <v/>
+      </c>
+      <c r="P127" t="str">
+        <v/>
+      </c>
+      <c r="Q127" t="str">
+        <v/>
+      </c>
+      <c r="R127" t="str">
+        <v/>
+      </c>
+      <c r="S127" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
+      </c>
+      <c r="B128" t="str">
+        <v>2025  02:08-12-31</v>
+      </c>
+      <c r="C128" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D128" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E128" t="str">
+        <v/>
+      </c>
+      <c r="F128" t="str">
+        <v/>
+      </c>
+      <c r="G128" t="str">
+        <v/>
+      </c>
+      <c r="H128" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I128" t="str">
+        <v/>
+      </c>
+      <c r="J128" t="str">
+        <v/>
+      </c>
+      <c r="K128" t="str">
+        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
+      </c>
+      <c r="L128" t="str">
+        <v/>
+      </c>
+      <c r="M128" t="str">
+        <v/>
+      </c>
+      <c r="N128" t="str">
+        <v/>
+      </c>
+      <c r="O128" t="str">
+        <v/>
+      </c>
+      <c r="P128" t="str">
+        <v/>
+      </c>
+      <c r="Q128" t="str">
+        <v/>
+      </c>
+      <c r="R128" t="str">
+        <v/>
+      </c>
+      <c r="S128" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
+      </c>
+      <c r="B129" t="str">
+        <v>2025  02:05-12-31</v>
+      </c>
+      <c r="C129" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D129" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E129" t="str">
+        <v/>
+      </c>
+      <c r="F129" t="str">
+        <v/>
+      </c>
+      <c r="G129" t="str">
+        <v/>
+      </c>
+      <c r="H129" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I129" t="str">
+        <v/>
+      </c>
+      <c r="J129" t="str">
+        <v/>
+      </c>
+      <c r="K129" t="str">
+        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
+      </c>
+      <c r="L129" t="str">
+        <v/>
+      </c>
+      <c r="M129" t="str">
+        <v/>
+      </c>
+      <c r="N129" t="str">
+        <v/>
+      </c>
+      <c r="O129" t="str">
+        <v/>
+      </c>
+      <c r="P129" t="str">
+        <v/>
+      </c>
+      <c r="Q129" t="str">
+        <v/>
+      </c>
+      <c r="R129" t="str">
+        <v/>
+      </c>
+      <c r="S129" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>Imagine פסטיגל - שירי התחרות</v>
+      </c>
+      <c r="B130" t="str">
+        <v>2025  02:04-12-31</v>
+      </c>
+      <c r="C130" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D130" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E130" t="str">
+        <v/>
+      </c>
+      <c r="F130" t="str">
+        <v/>
+      </c>
+      <c r="G130" t="str">
+        <v/>
+      </c>
+      <c r="H130" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I130" t="str">
+        <v/>
+      </c>
+      <c r="J130" t="str">
+        <v/>
+      </c>
+      <c r="K130" t="str">
+        <v>Imagine פסטיגל - שירי התחרות</v>
+      </c>
+      <c r="L130" t="str">
+        <v/>
+      </c>
+      <c r="M130" t="str">
+        <v/>
+      </c>
+      <c r="N130" t="str">
+        <v/>
+      </c>
+      <c r="O130" t="str">
+        <v/>
+      </c>
+      <c r="P130" t="str">
+        <v/>
+      </c>
+      <c r="Q130" t="str">
+        <v/>
+      </c>
+      <c r="R130" t="str">
+        <v/>
+      </c>
+      <c r="S130" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>השמחות - חובות אבודים</v>
+      </c>
+      <c r="B131" t="str">
+        <v>2025  02:02-12-31</v>
+      </c>
+      <c r="C131" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D131" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E131" t="str">
+        <v/>
+      </c>
+      <c r="F131" t="str">
+        <v/>
+      </c>
+      <c r="G131" t="str">
+        <v/>
+      </c>
+      <c r="H131" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I131" t="str">
+        <v/>
+      </c>
+      <c r="J131" t="str">
+        <v/>
+      </c>
+      <c r="K131" t="str">
+        <v>השמחות - חובות אבודים</v>
+      </c>
+      <c r="L131" t="str">
+        <v/>
+      </c>
+      <c r="M131" t="str">
+        <v/>
+      </c>
+      <c r="N131" t="str">
+        <v/>
+      </c>
+      <c r="O131" t="str">
+        <v/>
+      </c>
+      <c r="P131" t="str">
+        <v/>
+      </c>
+      <c r="Q131" t="str">
+        <v/>
+      </c>
+      <c r="R131" t="str">
+        <v/>
+      </c>
+      <c r="S131" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>שלמה גרוניך - כמו כוכבים</v>
+      </c>
+      <c r="B132" t="str">
+        <v>2025  02:00-12-31</v>
+      </c>
+      <c r="C132" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D132" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E132" t="str">
+        <v/>
+      </c>
+      <c r="F132" t="str">
+        <v/>
+      </c>
+      <c r="G132" t="str">
+        <v/>
+      </c>
+      <c r="H132" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I132" t="str">
+        <v/>
+      </c>
+      <c r="J132" t="str">
+        <v/>
+      </c>
+      <c r="K132" t="str">
+        <v>שלמה גרוניך - כמו כוכבים</v>
+      </c>
+      <c r="L132" t="str">
+        <v/>
+      </c>
+      <c r="M132" t="str">
+        <v/>
+      </c>
+      <c r="N132" t="str">
+        <v/>
+      </c>
+      <c r="O132" t="str">
+        <v/>
+      </c>
+      <c r="P132" t="str">
+        <v/>
+      </c>
+      <c r="Q132" t="str">
+        <v/>
+      </c>
+      <c r="R132" t="str">
+        <v/>
+      </c>
+      <c r="S132" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>יוני רועה - מפוזרים</v>
+      </c>
+      <c r="B133" t="str">
+        <v>2025  01:56-12-31</v>
+      </c>
+      <c r="C133" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D133" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E133" t="str">
+        <v/>
+      </c>
+      <c r="F133" t="str">
+        <v/>
+      </c>
+      <c r="G133" t="str">
+        <v/>
+      </c>
+      <c r="H133" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I133" t="str">
+        <v/>
+      </c>
+      <c r="J133" t="str">
+        <v/>
+      </c>
+      <c r="K133" t="str">
+        <v>יוני רועה - מפוזרים</v>
+      </c>
+      <c r="L133" t="str">
+        <v/>
+      </c>
+      <c r="M133" t="str">
+        <v/>
+      </c>
+      <c r="N133" t="str">
+        <v/>
+      </c>
+      <c r="O133" t="str">
+        <v/>
+      </c>
+      <c r="P133" t="str">
+        <v/>
+      </c>
+      <c r="Q133" t="str">
+        <v/>
+      </c>
+      <c r="R133" t="str">
+        <v/>
+      </c>
+      <c r="S133" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O89"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S133"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S133"/>
+  <dimension ref="A1:W177"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5817,7 +5817,7 @@
         <v>עדן בן זקן - רולקס וקסקט</v>
       </c>
       <c r="B120" t="str">
-        <v>2026  08:41-01-14</v>
+        <v>2026  08:41-01-14 | מאת</v>
       </c>
       <c r="C120" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24436&amp;forum=music&amp;viewmode=all</v>
@@ -5876,7 +5876,7 @@
         <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
       </c>
       <c r="B121" t="str">
-        <v>2026  08:40-01-14</v>
+        <v>2026  08:40-01-14 | מאת</v>
       </c>
       <c r="C121" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24439&amp;forum=music&amp;viewmode=all</v>
@@ -5935,7 +5935,7 @@
         <v>אייל גולן - בית מפואר</v>
       </c>
       <c r="B122" t="str">
-        <v>2025  02:18-12-31</v>
+        <v>2025  02:18-12-31 | מאת</v>
       </c>
       <c r="C122" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
@@ -5994,7 +5994,7 @@
         <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
       </c>
       <c r="B123" t="str">
-        <v>2025  02:16-12-31</v>
+        <v>2025  02:16-12-31 | מאת</v>
       </c>
       <c r="C123" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
@@ -6053,7 +6053,7 @@
         <v>שיר לוי - ילד מוזר</v>
       </c>
       <c r="B124" t="str">
-        <v>2025  02:14-12-31</v>
+        <v>2025  02:14-12-31 | מאת</v>
       </c>
       <c r="C124" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
@@ -6112,7 +6112,7 @@
         <v>פיטר רוט - 50</v>
       </c>
       <c r="B125" t="str">
-        <v>2025  02:13-12-31</v>
+        <v>2025  02:13-12-31 | מאת</v>
       </c>
       <c r="C125" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
@@ -6171,7 +6171,7 @@
         <v>אגם בוחבוט - עשרים ואחת</v>
       </c>
       <c r="B126" t="str">
-        <v>2025  02:11-12-31</v>
+        <v>2025  02:11-12-31 | מאת</v>
       </c>
       <c r="C126" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
@@ -6230,7 +6230,7 @@
         <v>רבקה זוהר - רסיסים של אור</v>
       </c>
       <c r="B127" t="str">
-        <v>2025  02:09-12-31</v>
+        <v>2025  02:09-12-31 | מאת</v>
       </c>
       <c r="C127" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
@@ -6289,7 +6289,7 @@
         <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
       </c>
       <c r="B128" t="str">
-        <v>2025  02:08-12-31</v>
+        <v>2025  02:08-12-31 | מאת</v>
       </c>
       <c r="C128" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
@@ -6348,7 +6348,7 @@
         <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
       </c>
       <c r="B129" t="str">
-        <v>2025  02:05-12-31</v>
+        <v>2025  02:05-12-31 | מאת</v>
       </c>
       <c r="C129" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
@@ -6407,7 +6407,7 @@
         <v>Imagine פסטיגל - שירי התחרות</v>
       </c>
       <c r="B130" t="str">
-        <v>2025  02:04-12-31</v>
+        <v>2025  02:04-12-31 | מאת</v>
       </c>
       <c r="C130" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
@@ -6466,7 +6466,7 @@
         <v>השמחות - חובות אבודים</v>
       </c>
       <c r="B131" t="str">
-        <v>2025  02:02-12-31</v>
+        <v>2025  02:02-12-31 | מאת</v>
       </c>
       <c r="C131" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
@@ -6525,7 +6525,7 @@
         <v>שלמה גרוניך - כמו כוכבים</v>
       </c>
       <c r="B132" t="str">
-        <v>2025  02:00-12-31</v>
+        <v>2025  02:00-12-31 | מאת</v>
       </c>
       <c r="C132" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
@@ -6584,7 +6584,7 @@
         <v>יוני רועה - מפוזרים</v>
       </c>
       <c r="B133" t="str">
-        <v>2025  01:56-12-31</v>
+        <v>2025  01:56-12-31 | מאת</v>
       </c>
       <c r="C133" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
@@ -6638,9 +6638,3133 @@
         <v/>
       </c>
     </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>פטריק סבג Hotel Mogador</v>
+      </c>
+      <c r="B134" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C134" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
+      </c>
+      <c r="D134" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E134" t="str">
+        <v>האלבום של פטריק סבג אינו אוסף שירים אקראי, אלא מרחב. מקום לשהות בו.  נכנסים, שומעים, ויוצאים קצת אחרים. הבחירה בשם "הוטל מוגדור” היא כבר הצהרה. מלון = מקום מעבר, לא בית קבוע, מוגדור = עיר נמל, תנועה, ערבוב תרבויות. כך</v>
+      </c>
+      <c r="F134" t="str">
+        <v/>
+      </c>
+      <c r="G134" t="str">
+        <v/>
+      </c>
+      <c r="H134" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I134" t="str">
+        <v/>
+      </c>
+      <c r="J134" t="str">
+        <v/>
+      </c>
+      <c r="K134" t="str">
+        <v>פטריק סבג Hotel Mogador</v>
+      </c>
+      <c r="L134" t="str">
+        <v/>
+      </c>
+      <c r="M134" t="str">
+        <v/>
+      </c>
+      <c r="N134" t="str">
+        <v/>
+      </c>
+      <c r="O134" t="str">
+        <v/>
+      </c>
+      <c r="P134" t="str">
+        <v/>
+      </c>
+      <c r="Q134" t="str">
+        <v/>
+      </c>
+      <c r="R134" t="str">
+        <v/>
+      </c>
+      <c r="S134" t="str">
+        <v/>
+      </c>
+      <c r="T134" t="str">
+        <v/>
+      </c>
+      <c r="U134" t="str">
+        <v/>
+      </c>
+      <c r="V134" t="str">
+        <v/>
+      </c>
+      <c r="W134" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
+      </c>
+      <c r="B135" t="str">
+        <v>2026-01-09</v>
+      </c>
+      <c r="C135" t="str">
+        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
+      </c>
+      <c r="D135" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E135" t="str">
+        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
+      </c>
+      <c r="F135" t="str">
+        <v/>
+      </c>
+      <c r="G135" t="str">
+        <v/>
+      </c>
+      <c r="H135" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I135" t="str">
+        <v/>
+      </c>
+      <c r="J135" t="str">
+        <v/>
+      </c>
+      <c r="K135" t="str">
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
+      </c>
+      <c r="L135" t="str">
+        <v/>
+      </c>
+      <c r="M135" t="str">
+        <v/>
+      </c>
+      <c r="N135" t="str">
+        <v/>
+      </c>
+      <c r="O135" t="str">
+        <v/>
+      </c>
+      <c r="P135" t="str">
+        <v/>
+      </c>
+      <c r="Q135" t="str">
+        <v/>
+      </c>
+      <c r="R135" t="str">
+        <v/>
+      </c>
+      <c r="S135" t="str">
+        <v/>
+      </c>
+      <c r="T135" t="str">
+        <v/>
+      </c>
+      <c r="U135" t="str">
+        <v/>
+      </c>
+      <c r="V135" t="str">
+        <v/>
+      </c>
+      <c r="W135" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>אוליביה דין The Art of Loving</v>
+      </c>
+      <c r="B136" t="str">
+        <v>2026-01-04</v>
+      </c>
+      <c r="C136" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
+      </c>
+      <c r="D136" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E136" t="str">
+        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
+      </c>
+      <c r="F136" t="str">
+        <v/>
+      </c>
+      <c r="G136" t="str">
+        <v/>
+      </c>
+      <c r="H136" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I136" t="str">
+        <v/>
+      </c>
+      <c r="J136" t="str">
+        <v/>
+      </c>
+      <c r="K136" t="str">
+        <v>אוליביה דין The Art of Loving</v>
+      </c>
+      <c r="L136" t="str">
+        <v/>
+      </c>
+      <c r="M136" t="str">
+        <v/>
+      </c>
+      <c r="N136" t="str">
+        <v/>
+      </c>
+      <c r="O136" t="str">
+        <v/>
+      </c>
+      <c r="P136" t="str">
+        <v/>
+      </c>
+      <c r="Q136" t="str">
+        <v/>
+      </c>
+      <c r="R136" t="str">
+        <v/>
+      </c>
+      <c r="S136" t="str">
+        <v/>
+      </c>
+      <c r="T136" t="str">
+        <v/>
+      </c>
+      <c r="U136" t="str">
+        <v/>
+      </c>
+      <c r="V136" t="str">
+        <v/>
+      </c>
+      <c r="W136" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>Geese Getting Killed</v>
+      </c>
+      <c r="B137" t="str">
+        <v>2025-12-29</v>
+      </c>
+      <c r="C137" t="str">
+        <v>https://yosmusic.com/geese-getting-killed/</v>
+      </c>
+      <c r="D137" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E137" t="str">
+        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
+      </c>
+      <c r="F137" t="str">
+        <v/>
+      </c>
+      <c r="G137" t="str">
+        <v/>
+      </c>
+      <c r="H137" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I137" t="str">
+        <v/>
+      </c>
+      <c r="J137" t="str">
+        <v/>
+      </c>
+      <c r="K137" t="str">
+        <v>Geese Getting Killed</v>
+      </c>
+      <c r="L137" t="str">
+        <v/>
+      </c>
+      <c r="M137" t="str">
+        <v/>
+      </c>
+      <c r="N137" t="str">
+        <v/>
+      </c>
+      <c r="O137" t="str">
+        <v/>
+      </c>
+      <c r="P137" t="str">
+        <v/>
+      </c>
+      <c r="Q137" t="str">
+        <v/>
+      </c>
+      <c r="R137" t="str">
+        <v/>
+      </c>
+      <c r="S137" t="str">
+        <v/>
+      </c>
+      <c r="T137" t="str">
+        <v/>
+      </c>
+      <c r="U137" t="str">
+        <v/>
+      </c>
+      <c r="V137" t="str">
+        <v/>
+      </c>
+      <c r="W137" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>רוסליה Lux</v>
+      </c>
+      <c r="B138" t="str">
+        <v>2025-12-25</v>
+      </c>
+      <c r="C138" t="str">
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
+      </c>
+      <c r="D138" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E138" t="str">
+        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
+      </c>
+      <c r="F138" t="str">
+        <v/>
+      </c>
+      <c r="G138" t="str">
+        <v/>
+      </c>
+      <c r="H138" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I138" t="str">
+        <v/>
+      </c>
+      <c r="J138" t="str">
+        <v/>
+      </c>
+      <c r="K138" t="str">
+        <v>רוסליה Lux</v>
+      </c>
+      <c r="L138" t="str">
+        <v/>
+      </c>
+      <c r="M138" t="str">
+        <v/>
+      </c>
+      <c r="N138" t="str">
+        <v/>
+      </c>
+      <c r="O138" t="str">
+        <v/>
+      </c>
+      <c r="P138" t="str">
+        <v/>
+      </c>
+      <c r="Q138" t="str">
+        <v/>
+      </c>
+      <c r="R138" t="str">
+        <v/>
+      </c>
+      <c r="S138" t="str">
+        <v/>
+      </c>
+      <c r="T138" t="str">
+        <v/>
+      </c>
+      <c r="U138" t="str">
+        <v/>
+      </c>
+      <c r="V138" t="str">
+        <v/>
+      </c>
+      <c r="W138" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>יאנגבלאד אירוסמית' one more time</v>
+      </c>
+      <c r="B139" t="str">
+        <v>2025-12-17</v>
+      </c>
+      <c r="C139" t="str">
+        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
+      </c>
+      <c r="D139" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E139" t="str">
+        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
+      </c>
+      <c r="F139" t="str">
+        <v/>
+      </c>
+      <c r="G139" t="str">
+        <v/>
+      </c>
+      <c r="H139" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I139" t="str">
+        <v/>
+      </c>
+      <c r="J139" t="str">
+        <v/>
+      </c>
+      <c r="K139" t="str">
+        <v>יאנגבלאד אירוסמית' one more time</v>
+      </c>
+      <c r="L139" t="str">
+        <v/>
+      </c>
+      <c r="M139" t="str">
+        <v/>
+      </c>
+      <c r="N139" t="str">
+        <v/>
+      </c>
+      <c r="O139" t="str">
+        <v/>
+      </c>
+      <c r="P139" t="str">
+        <v/>
+      </c>
+      <c r="Q139" t="str">
+        <v/>
+      </c>
+      <c r="R139" t="str">
+        <v/>
+      </c>
+      <c r="S139" t="str">
+        <v/>
+      </c>
+      <c r="T139" t="str">
+        <v/>
+      </c>
+      <c r="U139" t="str">
+        <v/>
+      </c>
+      <c r="V139" t="str">
+        <v/>
+      </c>
+      <c r="W139" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>פינק פלויד Wish You Were Here 50</v>
+      </c>
+      <c r="B140" t="str">
+        <v>2025-12-14</v>
+      </c>
+      <c r="C140" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
+      </c>
+      <c r="D140" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E140" t="str">
+        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
+      </c>
+      <c r="F140" t="str">
+        <v/>
+      </c>
+      <c r="G140" t="str">
+        <v/>
+      </c>
+      <c r="H140" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I140" t="str">
+        <v/>
+      </c>
+      <c r="J140" t="str">
+        <v/>
+      </c>
+      <c r="K140" t="str">
+        <v>פינק פלויד Wish You Were Here 50</v>
+      </c>
+      <c r="L140" t="str">
+        <v/>
+      </c>
+      <c r="M140" t="str">
+        <v/>
+      </c>
+      <c r="N140" t="str">
+        <v/>
+      </c>
+      <c r="O140" t="str">
+        <v/>
+      </c>
+      <c r="P140" t="str">
+        <v/>
+      </c>
+      <c r="Q140" t="str">
+        <v/>
+      </c>
+      <c r="R140" t="str">
+        <v/>
+      </c>
+      <c r="S140" t="str">
+        <v/>
+      </c>
+      <c r="T140" t="str">
+        <v/>
+      </c>
+      <c r="U140" t="str">
+        <v/>
+      </c>
+      <c r="V140" t="str">
+        <v/>
+      </c>
+      <c r="W140" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+      </c>
+      <c r="B141" t="str">
+        <v>2025-12-08</v>
+      </c>
+      <c r="C141" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
+      </c>
+      <c r="D141" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E141" t="str">
+        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
+      </c>
+      <c r="F141" t="str">
+        <v/>
+      </c>
+      <c r="G141" t="str">
+        <v/>
+      </c>
+      <c r="H141" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I141" t="str">
+        <v/>
+      </c>
+      <c r="J141" t="str">
+        <v/>
+      </c>
+      <c r="K141" t="str">
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+      </c>
+      <c r="L141" t="str">
+        <v/>
+      </c>
+      <c r="M141" t="str">
+        <v/>
+      </c>
+      <c r="N141" t="str">
+        <v/>
+      </c>
+      <c r="O141" t="str">
+        <v/>
+      </c>
+      <c r="P141" t="str">
+        <v/>
+      </c>
+      <c r="Q141" t="str">
+        <v/>
+      </c>
+      <c r="R141" t="str">
+        <v/>
+      </c>
+      <c r="S141" t="str">
+        <v/>
+      </c>
+      <c r="T141" t="str">
+        <v/>
+      </c>
+      <c r="U141" t="str">
+        <v/>
+      </c>
+      <c r="V141" t="str">
+        <v/>
+      </c>
+      <c r="W141" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>סטריי קידס DO IT EP</v>
+      </c>
+      <c r="B142" t="str">
+        <v>2025-12-04</v>
+      </c>
+      <c r="C142" t="str">
+        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
+      </c>
+      <c r="D142" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E142" t="str">
+        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
+      </c>
+      <c r="F142" t="str">
+        <v/>
+      </c>
+      <c r="G142" t="str">
+        <v/>
+      </c>
+      <c r="H142" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I142" t="str">
+        <v/>
+      </c>
+      <c r="J142" t="str">
+        <v/>
+      </c>
+      <c r="K142" t="str">
+        <v>סטריי קידס DO IT EP</v>
+      </c>
+      <c r="L142" t="str">
+        <v/>
+      </c>
+      <c r="M142" t="str">
+        <v/>
+      </c>
+      <c r="N142" t="str">
+        <v/>
+      </c>
+      <c r="O142" t="str">
+        <v/>
+      </c>
+      <c r="P142" t="str">
+        <v/>
+      </c>
+      <c r="Q142" t="str">
+        <v/>
+      </c>
+      <c r="R142" t="str">
+        <v/>
+      </c>
+      <c r="S142" t="str">
+        <v/>
+      </c>
+      <c r="T142" t="str">
+        <v/>
+      </c>
+      <c r="U142" t="str">
+        <v/>
+      </c>
+      <c r="V142" t="str">
+        <v/>
+      </c>
+      <c r="W142" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>דויד ברוזה BROZAJAZZ</v>
+      </c>
+      <c r="B143" t="str">
+        <v>2025-11-30</v>
+      </c>
+      <c r="C143" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
+      </c>
+      <c r="D143" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E143" t="str">
+        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
+      </c>
+      <c r="F143" t="str">
+        <v/>
+      </c>
+      <c r="G143" t="str">
+        <v/>
+      </c>
+      <c r="H143" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I143" t="str">
+        <v/>
+      </c>
+      <c r="J143" t="str">
+        <v/>
+      </c>
+      <c r="K143" t="str">
+        <v>דויד ברוזה BROZAJAZZ</v>
+      </c>
+      <c r="L143" t="str">
+        <v/>
+      </c>
+      <c r="M143" t="str">
+        <v/>
+      </c>
+      <c r="N143" t="str">
+        <v/>
+      </c>
+      <c r="O143" t="str">
+        <v/>
+      </c>
+      <c r="P143" t="str">
+        <v/>
+      </c>
+      <c r="Q143" t="str">
+        <v/>
+      </c>
+      <c r="R143" t="str">
+        <v/>
+      </c>
+      <c r="S143" t="str">
+        <v/>
+      </c>
+      <c r="T143" t="str">
+        <v/>
+      </c>
+      <c r="U143" t="str">
+        <v/>
+      </c>
+      <c r="V143" t="str">
+        <v/>
+      </c>
+      <c r="W143" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>Five Seconds of Summer – Everyone's A Star</v>
+      </c>
+      <c r="B144" t="str">
+        <v>2025-11-24</v>
+      </c>
+      <c r="C144" t="str">
+        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
+      </c>
+      <c r="D144" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E144" t="str">
+        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
+      </c>
+      <c r="F144" t="str">
+        <v/>
+      </c>
+      <c r="G144" t="str">
+        <v/>
+      </c>
+      <c r="H144" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I144" t="str">
+        <v/>
+      </c>
+      <c r="J144" t="str">
+        <v/>
+      </c>
+      <c r="K144" t="str">
+        <v>Five Seconds of Summer – Everyone's A Star</v>
+      </c>
+      <c r="L144" t="str">
+        <v/>
+      </c>
+      <c r="M144" t="str">
+        <v/>
+      </c>
+      <c r="N144" t="str">
+        <v/>
+      </c>
+      <c r="O144" t="str">
+        <v/>
+      </c>
+      <c r="P144" t="str">
+        <v/>
+      </c>
+      <c r="Q144" t="str">
+        <v/>
+      </c>
+      <c r="R144" t="str">
+        <v/>
+      </c>
+      <c r="S144" t="str">
+        <v/>
+      </c>
+      <c r="T144" t="str">
+        <v/>
+      </c>
+      <c r="U144" t="str">
+        <v/>
+      </c>
+      <c r="V144" t="str">
+        <v/>
+      </c>
+      <c r="W144" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>התקווה 6 – ויהי אור</v>
+      </c>
+      <c r="B145" t="str">
+        <v>2025-11-20</v>
+      </c>
+      <c r="C145" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
+      </c>
+      <c r="D145" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E145" t="str">
+        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
+      </c>
+      <c r="F145" t="str">
+        <v/>
+      </c>
+      <c r="G145" t="str">
+        <v/>
+      </c>
+      <c r="H145" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I145" t="str">
+        <v/>
+      </c>
+      <c r="J145" t="str">
+        <v/>
+      </c>
+      <c r="K145" t="str">
+        <v>התקווה 6 – ויהי אור</v>
+      </c>
+      <c r="L145" t="str">
+        <v/>
+      </c>
+      <c r="M145" t="str">
+        <v/>
+      </c>
+      <c r="N145" t="str">
+        <v/>
+      </c>
+      <c r="O145" t="str">
+        <v/>
+      </c>
+      <c r="P145" t="str">
+        <v/>
+      </c>
+      <c r="Q145" t="str">
+        <v/>
+      </c>
+      <c r="R145" t="str">
+        <v/>
+      </c>
+      <c r="S145" t="str">
+        <v/>
+      </c>
+      <c r="T145" t="str">
+        <v/>
+      </c>
+      <c r="U145" t="str">
+        <v/>
+      </c>
+      <c r="V145" t="str">
+        <v/>
+      </c>
+      <c r="W145" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>פלורנס אנד דה משין Everybody Scream</v>
+      </c>
+      <c r="B146" t="str">
+        <v>2025-11-13</v>
+      </c>
+      <c r="C146" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
+      </c>
+      <c r="D146" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E146" t="str">
+        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
+      </c>
+      <c r="F146" t="str">
+        <v/>
+      </c>
+      <c r="G146" t="str">
+        <v/>
+      </c>
+      <c r="H146" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I146" t="str">
+        <v/>
+      </c>
+      <c r="J146" t="str">
+        <v/>
+      </c>
+      <c r="K146" t="str">
+        <v>פלורנס אנד דה משין Everybody Scream</v>
+      </c>
+      <c r="L146" t="str">
+        <v/>
+      </c>
+      <c r="M146" t="str">
+        <v/>
+      </c>
+      <c r="N146" t="str">
+        <v/>
+      </c>
+      <c r="O146" t="str">
+        <v/>
+      </c>
+      <c r="P146" t="str">
+        <v/>
+      </c>
+      <c r="Q146" t="str">
+        <v/>
+      </c>
+      <c r="R146" t="str">
+        <v/>
+      </c>
+      <c r="S146" t="str">
+        <v/>
+      </c>
+      <c r="T146" t="str">
+        <v/>
+      </c>
+      <c r="U146" t="str">
+        <v/>
+      </c>
+      <c r="V146" t="str">
+        <v/>
+      </c>
+      <c r="W146" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>טיים אימפלה Deadbeat</v>
+      </c>
+      <c r="B147" t="str">
+        <v>2025-11-03</v>
+      </c>
+      <c r="C147" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
+      </c>
+      <c r="D147" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E147" t="str">
+        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
+      </c>
+      <c r="F147" t="str">
+        <v/>
+      </c>
+      <c r="G147" t="str">
+        <v/>
+      </c>
+      <c r="H147" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I147" t="str">
+        <v/>
+      </c>
+      <c r="J147" t="str">
+        <v/>
+      </c>
+      <c r="K147" t="str">
+        <v>טיים אימפלה Deadbeat</v>
+      </c>
+      <c r="L147" t="str">
+        <v/>
+      </c>
+      <c r="M147" t="str">
+        <v/>
+      </c>
+      <c r="N147" t="str">
+        <v/>
+      </c>
+      <c r="O147" t="str">
+        <v/>
+      </c>
+      <c r="P147" t="str">
+        <v/>
+      </c>
+      <c r="Q147" t="str">
+        <v/>
+      </c>
+      <c r="R147" t="str">
+        <v/>
+      </c>
+      <c r="S147" t="str">
+        <v/>
+      </c>
+      <c r="T147" t="str">
+        <v/>
+      </c>
+      <c r="U147" t="str">
+        <v/>
+      </c>
+      <c r="V147" t="str">
+        <v/>
+      </c>
+      <c r="W147" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+      </c>
+      <c r="B148" t="str">
+        <v>2025-10-20</v>
+      </c>
+      <c r="C148" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
+      </c>
+      <c r="D148" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E148" t="str">
+        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
+      </c>
+      <c r="F148" t="str">
+        <v/>
+      </c>
+      <c r="G148" t="str">
+        <v/>
+      </c>
+      <c r="H148" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I148" t="str">
+        <v/>
+      </c>
+      <c r="J148" t="str">
+        <v/>
+      </c>
+      <c r="K148" t="str">
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+      </c>
+      <c r="L148" t="str">
+        <v/>
+      </c>
+      <c r="M148" t="str">
+        <v/>
+      </c>
+      <c r="N148" t="str">
+        <v/>
+      </c>
+      <c r="O148" t="str">
+        <v/>
+      </c>
+      <c r="P148" t="str">
+        <v/>
+      </c>
+      <c r="Q148" t="str">
+        <v/>
+      </c>
+      <c r="R148" t="str">
+        <v/>
+      </c>
+      <c r="S148" t="str">
+        <v/>
+      </c>
+      <c r="T148" t="str">
+        <v/>
+      </c>
+      <c r="U148" t="str">
+        <v/>
+      </c>
+      <c r="V148" t="str">
+        <v/>
+      </c>
+      <c r="W148" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>שלמה גרוניך – תודה אהבה</v>
+      </c>
+      <c r="B149" t="str">
+        <v>2025-10-18</v>
+      </c>
+      <c r="C149" t="str">
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
+      </c>
+      <c r="D149" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E149" t="str">
+        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
+      </c>
+      <c r="F149" t="str">
+        <v/>
+      </c>
+      <c r="G149" t="str">
+        <v/>
+      </c>
+      <c r="H149" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I149" t="str">
+        <v/>
+      </c>
+      <c r="J149" t="str">
+        <v/>
+      </c>
+      <c r="K149" t="str">
+        <v>שלמה גרוניך – תודה אהבה</v>
+      </c>
+      <c r="L149" t="str">
+        <v/>
+      </c>
+      <c r="M149" t="str">
+        <v/>
+      </c>
+      <c r="N149" t="str">
+        <v/>
+      </c>
+      <c r="O149" t="str">
+        <v/>
+      </c>
+      <c r="P149" t="str">
+        <v/>
+      </c>
+      <c r="Q149" t="str">
+        <v/>
+      </c>
+      <c r="R149" t="str">
+        <v/>
+      </c>
+      <c r="S149" t="str">
+        <v/>
+      </c>
+      <c r="T149" t="str">
+        <v/>
+      </c>
+      <c r="U149" t="str">
+        <v/>
+      </c>
+      <c r="V149" t="str">
+        <v/>
+      </c>
+      <c r="W149" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
+      </c>
+      <c r="B150" t="str">
+        <v>2025-10-11</v>
+      </c>
+      <c r="C150" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
+      </c>
+      <c r="D150" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E150" t="str">
+        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
+      </c>
+      <c r="F150" t="str">
+        <v/>
+      </c>
+      <c r="G150" t="str">
+        <v/>
+      </c>
+      <c r="H150" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I150" t="str">
+        <v/>
+      </c>
+      <c r="J150" t="str">
+        <v/>
+      </c>
+      <c r="K150" t="str">
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
+      </c>
+      <c r="L150" t="str">
+        <v/>
+      </c>
+      <c r="M150" t="str">
+        <v/>
+      </c>
+      <c r="N150" t="str">
+        <v/>
+      </c>
+      <c r="O150" t="str">
+        <v/>
+      </c>
+      <c r="P150" t="str">
+        <v/>
+      </c>
+      <c r="Q150" t="str">
+        <v/>
+      </c>
+      <c r="R150" t="str">
+        <v/>
+      </c>
+      <c r="S150" t="str">
+        <v/>
+      </c>
+      <c r="T150" t="str">
+        <v/>
+      </c>
+      <c r="U150" t="str">
+        <v/>
+      </c>
+      <c r="V150" t="str">
+        <v/>
+      </c>
+      <c r="W150" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>דוג'ה קאט Vie</v>
+      </c>
+      <c r="B151" t="str">
+        <v>2025-10-04</v>
+      </c>
+      <c r="C151" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
+      </c>
+      <c r="D151" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E151" t="str">
+        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
+      </c>
+      <c r="F151" t="str">
+        <v/>
+      </c>
+      <c r="G151" t="str">
+        <v/>
+      </c>
+      <c r="H151" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I151" t="str">
+        <v/>
+      </c>
+      <c r="J151" t="str">
+        <v/>
+      </c>
+      <c r="K151" t="str">
+        <v>דוג'ה קאט Vie</v>
+      </c>
+      <c r="L151" t="str">
+        <v/>
+      </c>
+      <c r="M151" t="str">
+        <v/>
+      </c>
+      <c r="N151" t="str">
+        <v/>
+      </c>
+      <c r="O151" t="str">
+        <v/>
+      </c>
+      <c r="P151" t="str">
+        <v/>
+      </c>
+      <c r="Q151" t="str">
+        <v/>
+      </c>
+      <c r="R151" t="str">
+        <v/>
+      </c>
+      <c r="S151" t="str">
+        <v/>
+      </c>
+      <c r="T151" t="str">
+        <v/>
+      </c>
+      <c r="U151" t="str">
+        <v/>
+      </c>
+      <c r="V151" t="str">
+        <v/>
+      </c>
+      <c r="W151" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>ג'וי קרוקס Juniper</v>
+      </c>
+      <c r="B152" t="str">
+        <v>2025-10-03</v>
+      </c>
+      <c r="C152" t="str">
+        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
+      </c>
+      <c r="D152" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E152" t="str">
+        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
+      </c>
+      <c r="F152" t="str">
+        <v/>
+      </c>
+      <c r="G152" t="str">
+        <v/>
+      </c>
+      <c r="H152" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I152" t="str">
+        <v/>
+      </c>
+      <c r="J152" t="str">
+        <v/>
+      </c>
+      <c r="K152" t="str">
+        <v>ג'וי קרוקס Juniper</v>
+      </c>
+      <c r="L152" t="str">
+        <v/>
+      </c>
+      <c r="M152" t="str">
+        <v/>
+      </c>
+      <c r="N152" t="str">
+        <v/>
+      </c>
+      <c r="O152" t="str">
+        <v/>
+      </c>
+      <c r="P152" t="str">
+        <v/>
+      </c>
+      <c r="Q152" t="str">
+        <v/>
+      </c>
+      <c r="R152" t="str">
+        <v/>
+      </c>
+      <c r="S152" t="str">
+        <v/>
+      </c>
+      <c r="T152" t="str">
+        <v/>
+      </c>
+      <c r="U152" t="str">
+        <v/>
+      </c>
+      <c r="V152" t="str">
+        <v/>
+      </c>
+      <c r="W152" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>ביפי קליירו Futique</v>
+      </c>
+      <c r="B153" t="str">
+        <v>2025-09-30</v>
+      </c>
+      <c r="C153" t="str">
+        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
+      </c>
+      <c r="D153" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E153" t="str">
+        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
+      </c>
+      <c r="F153" t="str">
+        <v/>
+      </c>
+      <c r="G153" t="str">
+        <v/>
+      </c>
+      <c r="H153" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I153" t="str">
+        <v/>
+      </c>
+      <c r="J153" t="str">
+        <v/>
+      </c>
+      <c r="K153" t="str">
+        <v>ביפי קליירו Futique</v>
+      </c>
+      <c r="L153" t="str">
+        <v/>
+      </c>
+      <c r="M153" t="str">
+        <v/>
+      </c>
+      <c r="N153" t="str">
+        <v/>
+      </c>
+      <c r="O153" t="str">
+        <v/>
+      </c>
+      <c r="P153" t="str">
+        <v/>
+      </c>
+      <c r="Q153" t="str">
+        <v/>
+      </c>
+      <c r="R153" t="str">
+        <v/>
+      </c>
+      <c r="S153" t="str">
+        <v/>
+      </c>
+      <c r="T153" t="str">
+        <v/>
+      </c>
+      <c r="U153" t="str">
+        <v/>
+      </c>
+      <c r="V153" t="str">
+        <v/>
+      </c>
+      <c r="W153" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>אד שירן Play</v>
+      </c>
+      <c r="B154" t="str">
+        <v>2025-09-24</v>
+      </c>
+      <c r="C154" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
+      </c>
+      <c r="D154" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E154" t="str">
+        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
+      </c>
+      <c r="F154" t="str">
+        <v/>
+      </c>
+      <c r="G154" t="str">
+        <v/>
+      </c>
+      <c r="H154" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I154" t="str">
+        <v/>
+      </c>
+      <c r="J154" t="str">
+        <v/>
+      </c>
+      <c r="K154" t="str">
+        <v>אד שירן Play</v>
+      </c>
+      <c r="L154" t="str">
+        <v/>
+      </c>
+      <c r="M154" t="str">
+        <v/>
+      </c>
+      <c r="N154" t="str">
+        <v/>
+      </c>
+      <c r="O154" t="str">
+        <v/>
+      </c>
+      <c r="P154" t="str">
+        <v/>
+      </c>
+      <c r="Q154" t="str">
+        <v/>
+      </c>
+      <c r="R154" t="str">
+        <v/>
+      </c>
+      <c r="S154" t="str">
+        <v/>
+      </c>
+      <c r="T154" t="str">
+        <v/>
+      </c>
+      <c r="U154" t="str">
+        <v/>
+      </c>
+      <c r="V154" t="str">
+        <v/>
+      </c>
+      <c r="W154" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+      </c>
+      <c r="B155" t="str">
+        <v>2025-09-21</v>
+      </c>
+      <c r="C155" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
+      </c>
+      <c r="D155" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E155" t="str">
+        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
+      </c>
+      <c r="F155" t="str">
+        <v/>
+      </c>
+      <c r="G155" t="str">
+        <v/>
+      </c>
+      <c r="H155" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I155" t="str">
+        <v/>
+      </c>
+      <c r="J155" t="str">
+        <v/>
+      </c>
+      <c r="K155" t="str">
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+      </c>
+      <c r="L155" t="str">
+        <v/>
+      </c>
+      <c r="M155" t="str">
+        <v/>
+      </c>
+      <c r="N155" t="str">
+        <v/>
+      </c>
+      <c r="O155" t="str">
+        <v/>
+      </c>
+      <c r="P155" t="str">
+        <v/>
+      </c>
+      <c r="Q155" t="str">
+        <v/>
+      </c>
+      <c r="R155" t="str">
+        <v/>
+      </c>
+      <c r="S155" t="str">
+        <v/>
+      </c>
+      <c r="T155" t="str">
+        <v/>
+      </c>
+      <c r="U155" t="str">
+        <v/>
+      </c>
+      <c r="V155" t="str">
+        <v/>
+      </c>
+      <c r="W155" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>סוויד Antidepressants</v>
+      </c>
+      <c r="B156" t="str">
+        <v>2025-09-12</v>
+      </c>
+      <c r="C156" t="str">
+        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
+      </c>
+      <c r="D156" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E156" t="str">
+        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
+      </c>
+      <c r="F156" t="str">
+        <v/>
+      </c>
+      <c r="G156" t="str">
+        <v/>
+      </c>
+      <c r="H156" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I156" t="str">
+        <v/>
+      </c>
+      <c r="J156" t="str">
+        <v/>
+      </c>
+      <c r="K156" t="str">
+        <v>סוויד Antidepressants</v>
+      </c>
+      <c r="L156" t="str">
+        <v/>
+      </c>
+      <c r="M156" t="str">
+        <v/>
+      </c>
+      <c r="N156" t="str">
+        <v/>
+      </c>
+      <c r="O156" t="str">
+        <v/>
+      </c>
+      <c r="P156" t="str">
+        <v/>
+      </c>
+      <c r="Q156" t="str">
+        <v/>
+      </c>
+      <c r="R156" t="str">
+        <v/>
+      </c>
+      <c r="S156" t="str">
+        <v/>
+      </c>
+      <c r="T156" t="str">
+        <v/>
+      </c>
+      <c r="U156" t="str">
+        <v/>
+      </c>
+      <c r="V156" t="str">
+        <v/>
+      </c>
+      <c r="W156" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>וולף אליס The Clearing</v>
+      </c>
+      <c r="B157" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="C157" t="str">
+        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
+      </c>
+      <c r="D157" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E157" t="str">
+        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
+      </c>
+      <c r="F157" t="str">
+        <v/>
+      </c>
+      <c r="G157" t="str">
+        <v/>
+      </c>
+      <c r="H157" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I157" t="str">
+        <v/>
+      </c>
+      <c r="J157" t="str">
+        <v/>
+      </c>
+      <c r="K157" t="str">
+        <v>וולף אליס The Clearing</v>
+      </c>
+      <c r="L157" t="str">
+        <v/>
+      </c>
+      <c r="M157" t="str">
+        <v/>
+      </c>
+      <c r="N157" t="str">
+        <v/>
+      </c>
+      <c r="O157" t="str">
+        <v/>
+      </c>
+      <c r="P157" t="str">
+        <v/>
+      </c>
+      <c r="Q157" t="str">
+        <v/>
+      </c>
+      <c r="R157" t="str">
+        <v/>
+      </c>
+      <c r="S157" t="str">
+        <v/>
+      </c>
+      <c r="T157" t="str">
+        <v/>
+      </c>
+      <c r="U157" t="str">
+        <v/>
+      </c>
+      <c r="V157" t="str">
+        <v/>
+      </c>
+      <c r="W157" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+      </c>
+      <c r="B158" t="str">
+        <v>2025-08-29</v>
+      </c>
+      <c r="C158" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
+      </c>
+      <c r="D158" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E158" t="str">
+        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
+      </c>
+      <c r="F158" t="str">
+        <v/>
+      </c>
+      <c r="G158" t="str">
+        <v/>
+      </c>
+      <c r="H158" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I158" t="str">
+        <v/>
+      </c>
+      <c r="J158" t="str">
+        <v/>
+      </c>
+      <c r="K158" t="str">
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+      </c>
+      <c r="L158" t="str">
+        <v/>
+      </c>
+      <c r="M158" t="str">
+        <v/>
+      </c>
+      <c r="N158" t="str">
+        <v/>
+      </c>
+      <c r="O158" t="str">
+        <v/>
+      </c>
+      <c r="P158" t="str">
+        <v/>
+      </c>
+      <c r="Q158" t="str">
+        <v/>
+      </c>
+      <c r="R158" t="str">
+        <v/>
+      </c>
+      <c r="S158" t="str">
+        <v/>
+      </c>
+      <c r="T158" t="str">
+        <v/>
+      </c>
+      <c r="U158" t="str">
+        <v/>
+      </c>
+      <c r="V158" t="str">
+        <v/>
+      </c>
+      <c r="W158" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+      </c>
+      <c r="B159" t="str">
+        <v>2025-08-24</v>
+      </c>
+      <c r="C159" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
+      </c>
+      <c r="D159" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E159" t="str">
+        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
+      </c>
+      <c r="F159" t="str">
+        <v/>
+      </c>
+      <c r="G159" t="str">
+        <v/>
+      </c>
+      <c r="H159" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I159" t="str">
+        <v/>
+      </c>
+      <c r="J159" t="str">
+        <v/>
+      </c>
+      <c r="K159" t="str">
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+      </c>
+      <c r="L159" t="str">
+        <v/>
+      </c>
+      <c r="M159" t="str">
+        <v/>
+      </c>
+      <c r="N159" t="str">
+        <v/>
+      </c>
+      <c r="O159" t="str">
+        <v/>
+      </c>
+      <c r="P159" t="str">
+        <v/>
+      </c>
+      <c r="Q159" t="str">
+        <v/>
+      </c>
+      <c r="R159" t="str">
+        <v/>
+      </c>
+      <c r="S159" t="str">
+        <v/>
+      </c>
+      <c r="T159" t="str">
+        <v/>
+      </c>
+      <c r="U159" t="str">
+        <v/>
+      </c>
+      <c r="V159" t="str">
+        <v/>
+      </c>
+      <c r="W159" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+      </c>
+      <c r="B160" t="str">
+        <v>2025-08-21</v>
+      </c>
+      <c r="C160" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
+      </c>
+      <c r="D160" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E160" t="str">
+        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
+      </c>
+      <c r="F160" t="str">
+        <v/>
+      </c>
+      <c r="G160" t="str">
+        <v/>
+      </c>
+      <c r="H160" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I160" t="str">
+        <v/>
+      </c>
+      <c r="J160" t="str">
+        <v/>
+      </c>
+      <c r="K160" t="str">
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+      </c>
+      <c r="L160" t="str">
+        <v/>
+      </c>
+      <c r="M160" t="str">
+        <v/>
+      </c>
+      <c r="N160" t="str">
+        <v/>
+      </c>
+      <c r="O160" t="str">
+        <v/>
+      </c>
+      <c r="P160" t="str">
+        <v/>
+      </c>
+      <c r="Q160" t="str">
+        <v/>
+      </c>
+      <c r="R160" t="str">
+        <v/>
+      </c>
+      <c r="S160" t="str">
+        <v/>
+      </c>
+      <c r="T160" t="str">
+        <v/>
+      </c>
+      <c r="U160" t="str">
+        <v/>
+      </c>
+      <c r="V160" t="str">
+        <v/>
+      </c>
+      <c r="W160" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>אברהם טל – חי</v>
+      </c>
+      <c r="B161" t="str">
+        <v>2025-08-17</v>
+      </c>
+      <c r="C161" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
+      </c>
+      <c r="D161" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E161" t="str">
+        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
+      </c>
+      <c r="F161" t="str">
+        <v/>
+      </c>
+      <c r="G161" t="str">
+        <v/>
+      </c>
+      <c r="H161" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I161" t="str">
+        <v/>
+      </c>
+      <c r="J161" t="str">
+        <v/>
+      </c>
+      <c r="K161" t="str">
+        <v>אברהם טל – חי</v>
+      </c>
+      <c r="L161" t="str">
+        <v/>
+      </c>
+      <c r="M161" t="str">
+        <v/>
+      </c>
+      <c r="N161" t="str">
+        <v/>
+      </c>
+      <c r="O161" t="str">
+        <v/>
+      </c>
+      <c r="P161" t="str">
+        <v/>
+      </c>
+      <c r="Q161" t="str">
+        <v/>
+      </c>
+      <c r="R161" t="str">
+        <v/>
+      </c>
+      <c r="S161" t="str">
+        <v/>
+      </c>
+      <c r="T161" t="str">
+        <v/>
+      </c>
+      <c r="U161" t="str">
+        <v/>
+      </c>
+      <c r="V161" t="str">
+        <v/>
+      </c>
+      <c r="W161" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>רנה ראפ Bite Me</v>
+      </c>
+      <c r="B162" t="str">
+        <v>2025-08-12</v>
+      </c>
+      <c r="C162" t="str">
+        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
+      </c>
+      <c r="D162" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E162" t="str">
+        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
+      </c>
+      <c r="F162" t="str">
+        <v/>
+      </c>
+      <c r="G162" t="str">
+        <v/>
+      </c>
+      <c r="H162" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I162" t="str">
+        <v/>
+      </c>
+      <c r="J162" t="str">
+        <v/>
+      </c>
+      <c r="K162" t="str">
+        <v>רנה ראפ Bite Me</v>
+      </c>
+      <c r="L162" t="str">
+        <v/>
+      </c>
+      <c r="M162" t="str">
+        <v/>
+      </c>
+      <c r="N162" t="str">
+        <v/>
+      </c>
+      <c r="O162" t="str">
+        <v/>
+      </c>
+      <c r="P162" t="str">
+        <v/>
+      </c>
+      <c r="Q162" t="str">
+        <v/>
+      </c>
+      <c r="R162" t="str">
+        <v/>
+      </c>
+      <c r="S162" t="str">
+        <v/>
+      </c>
+      <c r="T162" t="str">
+        <v/>
+      </c>
+      <c r="U162" t="str">
+        <v/>
+      </c>
+      <c r="V162" t="str">
+        <v/>
+      </c>
+      <c r="W162" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>The K's – Pretty On The Internet</v>
+      </c>
+      <c r="B163" t="str">
+        <v>2025-08-03</v>
+      </c>
+      <c r="C163" t="str">
+        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
+      </c>
+      <c r="D163" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E163" t="str">
+        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
+      </c>
+      <c r="F163" t="str">
+        <v/>
+      </c>
+      <c r="G163" t="str">
+        <v/>
+      </c>
+      <c r="H163" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I163" t="str">
+        <v/>
+      </c>
+      <c r="J163" t="str">
+        <v/>
+      </c>
+      <c r="K163" t="str">
+        <v>The K's – Pretty On The Internet</v>
+      </c>
+      <c r="L163" t="str">
+        <v/>
+      </c>
+      <c r="M163" t="str">
+        <v/>
+      </c>
+      <c r="N163" t="str">
+        <v/>
+      </c>
+      <c r="O163" t="str">
+        <v/>
+      </c>
+      <c r="P163" t="str">
+        <v/>
+      </c>
+      <c r="Q163" t="str">
+        <v/>
+      </c>
+      <c r="R163" t="str">
+        <v/>
+      </c>
+      <c r="S163" t="str">
+        <v/>
+      </c>
+      <c r="T163" t="str">
+        <v/>
+      </c>
+      <c r="U163" t="str">
+        <v/>
+      </c>
+      <c r="V163" t="str">
+        <v/>
+      </c>
+      <c r="W163" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>עדן בן זקן - רולקס וקסקט</v>
+      </c>
+      <c r="B164" t="str">
+        <v>2026  08:41-01-14</v>
+      </c>
+      <c r="C164" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24436&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D164" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E164" t="str">
+        <v/>
+      </c>
+      <c r="F164" t="str">
+        <v/>
+      </c>
+      <c r="G164" t="str">
+        <v/>
+      </c>
+      <c r="H164" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I164" t="str">
+        <v/>
+      </c>
+      <c r="J164" t="str">
+        <v/>
+      </c>
+      <c r="K164" t="str">
+        <v>עדן בן זקן - רולקס וקסקט</v>
+      </c>
+      <c r="L164" t="str">
+        <v/>
+      </c>
+      <c r="M164" t="str">
+        <v/>
+      </c>
+      <c r="N164" t="str">
+        <v/>
+      </c>
+      <c r="O164" t="str">
+        <v/>
+      </c>
+      <c r="P164" t="str">
+        <v/>
+      </c>
+      <c r="Q164" t="str">
+        <v/>
+      </c>
+      <c r="R164" t="str">
+        <v/>
+      </c>
+      <c r="S164" t="str">
+        <v/>
+      </c>
+      <c r="T164" t="str">
+        <v/>
+      </c>
+      <c r="U164" t="str">
+        <v/>
+      </c>
+      <c r="V164" t="str">
+        <v/>
+      </c>
+      <c r="W164" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
+      </c>
+      <c r="B165" t="str">
+        <v>2026  08:40-01-14</v>
+      </c>
+      <c r="C165" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24439&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D165" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E165" t="str">
+        <v/>
+      </c>
+      <c r="F165" t="str">
+        <v/>
+      </c>
+      <c r="G165" t="str">
+        <v/>
+      </c>
+      <c r="H165" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I165" t="str">
+        <v/>
+      </c>
+      <c r="J165" t="str">
+        <v/>
+      </c>
+      <c r="K165" t="str">
+        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
+      </c>
+      <c r="L165" t="str">
+        <v/>
+      </c>
+      <c r="M165" t="str">
+        <v/>
+      </c>
+      <c r="N165" t="str">
+        <v/>
+      </c>
+      <c r="O165" t="str">
+        <v/>
+      </c>
+      <c r="P165" t="str">
+        <v/>
+      </c>
+      <c r="Q165" t="str">
+        <v/>
+      </c>
+      <c r="R165" t="str">
+        <v/>
+      </c>
+      <c r="S165" t="str">
+        <v/>
+      </c>
+      <c r="T165" t="str">
+        <v/>
+      </c>
+      <c r="U165" t="str">
+        <v/>
+      </c>
+      <c r="V165" t="str">
+        <v/>
+      </c>
+      <c r="W165" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>אייל גולן - בית מפואר</v>
+      </c>
+      <c r="B166" t="str">
+        <v>2025  02:18-12-31</v>
+      </c>
+      <c r="C166" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D166" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E166" t="str">
+        <v/>
+      </c>
+      <c r="F166" t="str">
+        <v/>
+      </c>
+      <c r="G166" t="str">
+        <v/>
+      </c>
+      <c r="H166" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I166" t="str">
+        <v/>
+      </c>
+      <c r="J166" t="str">
+        <v/>
+      </c>
+      <c r="K166" t="str">
+        <v>אייל גולן - בית מפואר</v>
+      </c>
+      <c r="L166" t="str">
+        <v/>
+      </c>
+      <c r="M166" t="str">
+        <v/>
+      </c>
+      <c r="N166" t="str">
+        <v/>
+      </c>
+      <c r="O166" t="str">
+        <v/>
+      </c>
+      <c r="P166" t="str">
+        <v/>
+      </c>
+      <c r="Q166" t="str">
+        <v/>
+      </c>
+      <c r="R166" t="str">
+        <v/>
+      </c>
+      <c r="S166" t="str">
+        <v/>
+      </c>
+      <c r="T166" t="str">
+        <v/>
+      </c>
+      <c r="U166" t="str">
+        <v/>
+      </c>
+      <c r="V166" t="str">
+        <v/>
+      </c>
+      <c r="W166" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
+      </c>
+      <c r="B167" t="str">
+        <v>2025  02:16-12-31</v>
+      </c>
+      <c r="C167" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D167" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E167" t="str">
+        <v/>
+      </c>
+      <c r="F167" t="str">
+        <v/>
+      </c>
+      <c r="G167" t="str">
+        <v/>
+      </c>
+      <c r="H167" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I167" t="str">
+        <v/>
+      </c>
+      <c r="J167" t="str">
+        <v/>
+      </c>
+      <c r="K167" t="str">
+        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
+      </c>
+      <c r="L167" t="str">
+        <v/>
+      </c>
+      <c r="M167" t="str">
+        <v/>
+      </c>
+      <c r="N167" t="str">
+        <v/>
+      </c>
+      <c r="O167" t="str">
+        <v/>
+      </c>
+      <c r="P167" t="str">
+        <v/>
+      </c>
+      <c r="Q167" t="str">
+        <v/>
+      </c>
+      <c r="R167" t="str">
+        <v/>
+      </c>
+      <c r="S167" t="str">
+        <v/>
+      </c>
+      <c r="T167" t="str">
+        <v/>
+      </c>
+      <c r="U167" t="str">
+        <v/>
+      </c>
+      <c r="V167" t="str">
+        <v/>
+      </c>
+      <c r="W167" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>שיר לוי - ילד מוזר</v>
+      </c>
+      <c r="B168" t="str">
+        <v>2025  02:14-12-31</v>
+      </c>
+      <c r="C168" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D168" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E168" t="str">
+        <v/>
+      </c>
+      <c r="F168" t="str">
+        <v/>
+      </c>
+      <c r="G168" t="str">
+        <v/>
+      </c>
+      <c r="H168" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I168" t="str">
+        <v/>
+      </c>
+      <c r="J168" t="str">
+        <v/>
+      </c>
+      <c r="K168" t="str">
+        <v>שיר לוי - ילד מוזר</v>
+      </c>
+      <c r="L168" t="str">
+        <v/>
+      </c>
+      <c r="M168" t="str">
+        <v/>
+      </c>
+      <c r="N168" t="str">
+        <v/>
+      </c>
+      <c r="O168" t="str">
+        <v/>
+      </c>
+      <c r="P168" t="str">
+        <v/>
+      </c>
+      <c r="Q168" t="str">
+        <v/>
+      </c>
+      <c r="R168" t="str">
+        <v/>
+      </c>
+      <c r="S168" t="str">
+        <v/>
+      </c>
+      <c r="T168" t="str">
+        <v/>
+      </c>
+      <c r="U168" t="str">
+        <v/>
+      </c>
+      <c r="V168" t="str">
+        <v/>
+      </c>
+      <c r="W168" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>פיטר רוט - 50</v>
+      </c>
+      <c r="B169" t="str">
+        <v>2025  02:13-12-31</v>
+      </c>
+      <c r="C169" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D169" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E169" t="str">
+        <v/>
+      </c>
+      <c r="F169" t="str">
+        <v/>
+      </c>
+      <c r="G169" t="str">
+        <v/>
+      </c>
+      <c r="H169" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I169" t="str">
+        <v/>
+      </c>
+      <c r="J169" t="str">
+        <v/>
+      </c>
+      <c r="K169" t="str">
+        <v>פיטר רוט - 50</v>
+      </c>
+      <c r="L169" t="str">
+        <v/>
+      </c>
+      <c r="M169" t="str">
+        <v/>
+      </c>
+      <c r="N169" t="str">
+        <v/>
+      </c>
+      <c r="O169" t="str">
+        <v/>
+      </c>
+      <c r="P169" t="str">
+        <v/>
+      </c>
+      <c r="Q169" t="str">
+        <v/>
+      </c>
+      <c r="R169" t="str">
+        <v/>
+      </c>
+      <c r="S169" t="str">
+        <v/>
+      </c>
+      <c r="T169" t="str">
+        <v/>
+      </c>
+      <c r="U169" t="str">
+        <v/>
+      </c>
+      <c r="V169" t="str">
+        <v/>
+      </c>
+      <c r="W169" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>אגם בוחבוט - עשרים ואחת</v>
+      </c>
+      <c r="B170" t="str">
+        <v>2025  02:11-12-31</v>
+      </c>
+      <c r="C170" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D170" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E170" t="str">
+        <v/>
+      </c>
+      <c r="F170" t="str">
+        <v/>
+      </c>
+      <c r="G170" t="str">
+        <v/>
+      </c>
+      <c r="H170" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I170" t="str">
+        <v/>
+      </c>
+      <c r="J170" t="str">
+        <v/>
+      </c>
+      <c r="K170" t="str">
+        <v>אגם בוחבוט - עשרים ואחת</v>
+      </c>
+      <c r="L170" t="str">
+        <v/>
+      </c>
+      <c r="M170" t="str">
+        <v/>
+      </c>
+      <c r="N170" t="str">
+        <v/>
+      </c>
+      <c r="O170" t="str">
+        <v/>
+      </c>
+      <c r="P170" t="str">
+        <v/>
+      </c>
+      <c r="Q170" t="str">
+        <v/>
+      </c>
+      <c r="R170" t="str">
+        <v/>
+      </c>
+      <c r="S170" t="str">
+        <v/>
+      </c>
+      <c r="T170" t="str">
+        <v/>
+      </c>
+      <c r="U170" t="str">
+        <v/>
+      </c>
+      <c r="V170" t="str">
+        <v/>
+      </c>
+      <c r="W170" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>רבקה זוהר - רסיסים של אור</v>
+      </c>
+      <c r="B171" t="str">
+        <v>2025  02:09-12-31</v>
+      </c>
+      <c r="C171" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D171" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E171" t="str">
+        <v/>
+      </c>
+      <c r="F171" t="str">
+        <v/>
+      </c>
+      <c r="G171" t="str">
+        <v/>
+      </c>
+      <c r="H171" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I171" t="str">
+        <v/>
+      </c>
+      <c r="J171" t="str">
+        <v/>
+      </c>
+      <c r="K171" t="str">
+        <v>רבקה זוהר - רסיסים של אור</v>
+      </c>
+      <c r="L171" t="str">
+        <v/>
+      </c>
+      <c r="M171" t="str">
+        <v/>
+      </c>
+      <c r="N171" t="str">
+        <v/>
+      </c>
+      <c r="O171" t="str">
+        <v/>
+      </c>
+      <c r="P171" t="str">
+        <v/>
+      </c>
+      <c r="Q171" t="str">
+        <v/>
+      </c>
+      <c r="R171" t="str">
+        <v/>
+      </c>
+      <c r="S171" t="str">
+        <v/>
+      </c>
+      <c r="T171" t="str">
+        <v/>
+      </c>
+      <c r="U171" t="str">
+        <v/>
+      </c>
+      <c r="V171" t="str">
+        <v/>
+      </c>
+      <c r="W171" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
+      </c>
+      <c r="B172" t="str">
+        <v>2025  02:08-12-31</v>
+      </c>
+      <c r="C172" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D172" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E172" t="str">
+        <v/>
+      </c>
+      <c r="F172" t="str">
+        <v/>
+      </c>
+      <c r="G172" t="str">
+        <v/>
+      </c>
+      <c r="H172" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I172" t="str">
+        <v/>
+      </c>
+      <c r="J172" t="str">
+        <v/>
+      </c>
+      <c r="K172" t="str">
+        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
+      </c>
+      <c r="L172" t="str">
+        <v/>
+      </c>
+      <c r="M172" t="str">
+        <v/>
+      </c>
+      <c r="N172" t="str">
+        <v/>
+      </c>
+      <c r="O172" t="str">
+        <v/>
+      </c>
+      <c r="P172" t="str">
+        <v/>
+      </c>
+      <c r="Q172" t="str">
+        <v/>
+      </c>
+      <c r="R172" t="str">
+        <v/>
+      </c>
+      <c r="S172" t="str">
+        <v/>
+      </c>
+      <c r="T172" t="str">
+        <v/>
+      </c>
+      <c r="U172" t="str">
+        <v/>
+      </c>
+      <c r="V172" t="str">
+        <v/>
+      </c>
+      <c r="W172" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
+      </c>
+      <c r="B173" t="str">
+        <v>2025  02:05-12-31</v>
+      </c>
+      <c r="C173" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D173" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E173" t="str">
+        <v/>
+      </c>
+      <c r="F173" t="str">
+        <v/>
+      </c>
+      <c r="G173" t="str">
+        <v/>
+      </c>
+      <c r="H173" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I173" t="str">
+        <v/>
+      </c>
+      <c r="J173" t="str">
+        <v/>
+      </c>
+      <c r="K173" t="str">
+        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
+      </c>
+      <c r="L173" t="str">
+        <v/>
+      </c>
+      <c r="M173" t="str">
+        <v/>
+      </c>
+      <c r="N173" t="str">
+        <v/>
+      </c>
+      <c r="O173" t="str">
+        <v/>
+      </c>
+      <c r="P173" t="str">
+        <v/>
+      </c>
+      <c r="Q173" t="str">
+        <v/>
+      </c>
+      <c r="R173" t="str">
+        <v/>
+      </c>
+      <c r="S173" t="str">
+        <v/>
+      </c>
+      <c r="T173" t="str">
+        <v/>
+      </c>
+      <c r="U173" t="str">
+        <v/>
+      </c>
+      <c r="V173" t="str">
+        <v/>
+      </c>
+      <c r="W173" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>Imagine פסטיגל - שירי התחרות</v>
+      </c>
+      <c r="B174" t="str">
+        <v>2025  02:04-12-31</v>
+      </c>
+      <c r="C174" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D174" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E174" t="str">
+        <v/>
+      </c>
+      <c r="F174" t="str">
+        <v/>
+      </c>
+      <c r="G174" t="str">
+        <v/>
+      </c>
+      <c r="H174" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I174" t="str">
+        <v/>
+      </c>
+      <c r="J174" t="str">
+        <v/>
+      </c>
+      <c r="K174" t="str">
+        <v>Imagine פסטיגל - שירי התחרות</v>
+      </c>
+      <c r="L174" t="str">
+        <v/>
+      </c>
+      <c r="M174" t="str">
+        <v/>
+      </c>
+      <c r="N174" t="str">
+        <v/>
+      </c>
+      <c r="O174" t="str">
+        <v/>
+      </c>
+      <c r="P174" t="str">
+        <v/>
+      </c>
+      <c r="Q174" t="str">
+        <v/>
+      </c>
+      <c r="R174" t="str">
+        <v/>
+      </c>
+      <c r="S174" t="str">
+        <v/>
+      </c>
+      <c r="T174" t="str">
+        <v/>
+      </c>
+      <c r="U174" t="str">
+        <v/>
+      </c>
+      <c r="V174" t="str">
+        <v/>
+      </c>
+      <c r="W174" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>השמחות - חובות אבודים</v>
+      </c>
+      <c r="B175" t="str">
+        <v>2025  02:02-12-31</v>
+      </c>
+      <c r="C175" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D175" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E175" t="str">
+        <v/>
+      </c>
+      <c r="F175" t="str">
+        <v/>
+      </c>
+      <c r="G175" t="str">
+        <v/>
+      </c>
+      <c r="H175" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I175" t="str">
+        <v/>
+      </c>
+      <c r="J175" t="str">
+        <v/>
+      </c>
+      <c r="K175" t="str">
+        <v>השמחות - חובות אבודים</v>
+      </c>
+      <c r="L175" t="str">
+        <v/>
+      </c>
+      <c r="M175" t="str">
+        <v/>
+      </c>
+      <c r="N175" t="str">
+        <v/>
+      </c>
+      <c r="O175" t="str">
+        <v/>
+      </c>
+      <c r="P175" t="str">
+        <v/>
+      </c>
+      <c r="Q175" t="str">
+        <v/>
+      </c>
+      <c r="R175" t="str">
+        <v/>
+      </c>
+      <c r="S175" t="str">
+        <v/>
+      </c>
+      <c r="T175" t="str">
+        <v/>
+      </c>
+      <c r="U175" t="str">
+        <v/>
+      </c>
+      <c r="V175" t="str">
+        <v/>
+      </c>
+      <c r="W175" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>שלמה גרוניך - כמו כוכבים</v>
+      </c>
+      <c r="B176" t="str">
+        <v>2025  02:00-12-31</v>
+      </c>
+      <c r="C176" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D176" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E176" t="str">
+        <v/>
+      </c>
+      <c r="F176" t="str">
+        <v/>
+      </c>
+      <c r="G176" t="str">
+        <v/>
+      </c>
+      <c r="H176" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I176" t="str">
+        <v/>
+      </c>
+      <c r="J176" t="str">
+        <v/>
+      </c>
+      <c r="K176" t="str">
+        <v>שלמה גרוניך - כמו כוכבים</v>
+      </c>
+      <c r="L176" t="str">
+        <v/>
+      </c>
+      <c r="M176" t="str">
+        <v/>
+      </c>
+      <c r="N176" t="str">
+        <v/>
+      </c>
+      <c r="O176" t="str">
+        <v/>
+      </c>
+      <c r="P176" t="str">
+        <v/>
+      </c>
+      <c r="Q176" t="str">
+        <v/>
+      </c>
+      <c r="R176" t="str">
+        <v/>
+      </c>
+      <c r="S176" t="str">
+        <v/>
+      </c>
+      <c r="T176" t="str">
+        <v/>
+      </c>
+      <c r="U176" t="str">
+        <v/>
+      </c>
+      <c r="V176" t="str">
+        <v/>
+      </c>
+      <c r="W176" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>יוני רועה - מפוזרים</v>
+      </c>
+      <c r="B177" t="str">
+        <v>2025  01:56-12-31</v>
+      </c>
+      <c r="C177" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D177" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E177" t="str">
+        <v/>
+      </c>
+      <c r="F177" t="str">
+        <v/>
+      </c>
+      <c r="G177" t="str">
+        <v/>
+      </c>
+      <c r="H177" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I177" t="str">
+        <v/>
+      </c>
+      <c r="J177" t="str">
+        <v/>
+      </c>
+      <c r="K177" t="str">
+        <v>יוני רועה - מפוזרים</v>
+      </c>
+      <c r="L177" t="str">
+        <v/>
+      </c>
+      <c r="M177" t="str">
+        <v/>
+      </c>
+      <c r="N177" t="str">
+        <v/>
+      </c>
+      <c r="O177" t="str">
+        <v/>
+      </c>
+      <c r="P177" t="str">
+        <v/>
+      </c>
+      <c r="Q177" t="str">
+        <v/>
+      </c>
+      <c r="R177" t="str">
+        <v/>
+      </c>
+      <c r="S177" t="str">
+        <v/>
+      </c>
+      <c r="T177" t="str">
+        <v/>
+      </c>
+      <c r="U177" t="str">
+        <v/>
+      </c>
+      <c r="V177" t="str">
+        <v/>
+      </c>
+      <c r="W177" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S133"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:W177"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W177"/>
+  <dimension ref="A1:AA221"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -8773,7 +8773,7 @@
         <v>עדן בן זקן - רולקס וקסקט</v>
       </c>
       <c r="B164" t="str">
-        <v>2026  08:41-01-14</v>
+        <v>2026  08:41-01-14 | מאת</v>
       </c>
       <c r="C164" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24436&amp;forum=music&amp;viewmode=all</v>
@@ -8844,7 +8844,7 @@
         <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
       </c>
       <c r="B165" t="str">
-        <v>2026  08:40-01-14</v>
+        <v>2026  08:40-01-14 | מאת</v>
       </c>
       <c r="C165" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24439&amp;forum=music&amp;viewmode=all</v>
@@ -8915,7 +8915,7 @@
         <v>אייל גולן - בית מפואר</v>
       </c>
       <c r="B166" t="str">
-        <v>2025  02:18-12-31</v>
+        <v>2025  02:18-12-31 | מאת</v>
       </c>
       <c r="C166" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
@@ -8986,7 +8986,7 @@
         <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
       </c>
       <c r="B167" t="str">
-        <v>2025  02:16-12-31</v>
+        <v>2025  02:16-12-31 | מאת</v>
       </c>
       <c r="C167" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
@@ -9057,7 +9057,7 @@
         <v>שיר לוי - ילד מוזר</v>
       </c>
       <c r="B168" t="str">
-        <v>2025  02:14-12-31</v>
+        <v>2025  02:14-12-31 | מאת</v>
       </c>
       <c r="C168" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
@@ -9128,7 +9128,7 @@
         <v>פיטר רוט - 50</v>
       </c>
       <c r="B169" t="str">
-        <v>2025  02:13-12-31</v>
+        <v>2025  02:13-12-31 | מאת</v>
       </c>
       <c r="C169" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
@@ -9199,7 +9199,7 @@
         <v>אגם בוחבוט - עשרים ואחת</v>
       </c>
       <c r="B170" t="str">
-        <v>2025  02:11-12-31</v>
+        <v>2025  02:11-12-31 | מאת</v>
       </c>
       <c r="C170" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
@@ -9270,7 +9270,7 @@
         <v>רבקה זוהר - רסיסים של אור</v>
       </c>
       <c r="B171" t="str">
-        <v>2025  02:09-12-31</v>
+        <v>2025  02:09-12-31 | מאת</v>
       </c>
       <c r="C171" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
@@ -9341,7 +9341,7 @@
         <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
       </c>
       <c r="B172" t="str">
-        <v>2025  02:08-12-31</v>
+        <v>2025  02:08-12-31 | מאת</v>
       </c>
       <c r="C172" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
@@ -9412,7 +9412,7 @@
         <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
       </c>
       <c r="B173" t="str">
-        <v>2025  02:05-12-31</v>
+        <v>2025  02:05-12-31 | מאת</v>
       </c>
       <c r="C173" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
@@ -9483,7 +9483,7 @@
         <v>Imagine פסטיגל - שירי התחרות</v>
       </c>
       <c r="B174" t="str">
-        <v>2025  02:04-12-31</v>
+        <v>2025  02:04-12-31 | מאת</v>
       </c>
       <c r="C174" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
@@ -9554,7 +9554,7 @@
         <v>השמחות - חובות אבודים</v>
       </c>
       <c r="B175" t="str">
-        <v>2025  02:02-12-31</v>
+        <v>2025  02:02-12-31 | מאת</v>
       </c>
       <c r="C175" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
@@ -9625,7 +9625,7 @@
         <v>שלמה גרוניך - כמו כוכבים</v>
       </c>
       <c r="B176" t="str">
-        <v>2025  02:00-12-31</v>
+        <v>2025  02:00-12-31 | מאת</v>
       </c>
       <c r="C176" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
@@ -9696,7 +9696,7 @@
         <v>יוני רועה - מפוזרים</v>
       </c>
       <c r="B177" t="str">
-        <v>2025  01:56-12-31</v>
+        <v>2025  01:56-12-31 | מאת</v>
       </c>
       <c r="C177" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
@@ -9762,9 +9762,3661 @@
         <v/>
       </c>
     </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>פטריק סבג Hotel Mogador</v>
+      </c>
+      <c r="B178" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C178" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
+      </c>
+      <c r="D178" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E178" t="str">
+        <v>האלבום של פטריק סבג אינו אוסף שירים אקראי, אלא מרחב. מקום לשהות בו.  נכנסים, שומעים, ויוצאים קצת אחרים. הבחירה בשם "הוטל מוגדור” היא כבר הצהרה. מלון = מקום מעבר, לא בית קבוע, מוגדור = עיר נמל, תנועה, ערבוב תרבויות. כך</v>
+      </c>
+      <c r="F178" t="str">
+        <v/>
+      </c>
+      <c r="G178" t="str">
+        <v/>
+      </c>
+      <c r="H178" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I178" t="str">
+        <v/>
+      </c>
+      <c r="J178" t="str">
+        <v/>
+      </c>
+      <c r="K178" t="str">
+        <v>פטריק סבג Hotel Mogador</v>
+      </c>
+      <c r="L178" t="str">
+        <v/>
+      </c>
+      <c r="M178" t="str">
+        <v/>
+      </c>
+      <c r="N178" t="str">
+        <v/>
+      </c>
+      <c r="O178" t="str">
+        <v/>
+      </c>
+      <c r="P178" t="str">
+        <v/>
+      </c>
+      <c r="Q178" t="str">
+        <v/>
+      </c>
+      <c r="R178" t="str">
+        <v/>
+      </c>
+      <c r="S178" t="str">
+        <v/>
+      </c>
+      <c r="T178" t="str">
+        <v/>
+      </c>
+      <c r="U178" t="str">
+        <v/>
+      </c>
+      <c r="V178" t="str">
+        <v/>
+      </c>
+      <c r="W178" t="str">
+        <v/>
+      </c>
+      <c r="X178" t="str">
+        <v/>
+      </c>
+      <c r="Y178" t="str">
+        <v/>
+      </c>
+      <c r="Z178" t="str">
+        <v/>
+      </c>
+      <c r="AA178" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
+      </c>
+      <c r="B179" t="str">
+        <v>2026-01-09</v>
+      </c>
+      <c r="C179" t="str">
+        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
+      </c>
+      <c r="D179" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E179" t="str">
+        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
+      </c>
+      <c r="F179" t="str">
+        <v/>
+      </c>
+      <c r="G179" t="str">
+        <v/>
+      </c>
+      <c r="H179" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I179" t="str">
+        <v/>
+      </c>
+      <c r="J179" t="str">
+        <v/>
+      </c>
+      <c r="K179" t="str">
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
+      </c>
+      <c r="L179" t="str">
+        <v/>
+      </c>
+      <c r="M179" t="str">
+        <v/>
+      </c>
+      <c r="N179" t="str">
+        <v/>
+      </c>
+      <c r="O179" t="str">
+        <v/>
+      </c>
+      <c r="P179" t="str">
+        <v/>
+      </c>
+      <c r="Q179" t="str">
+        <v/>
+      </c>
+      <c r="R179" t="str">
+        <v/>
+      </c>
+      <c r="S179" t="str">
+        <v/>
+      </c>
+      <c r="T179" t="str">
+        <v/>
+      </c>
+      <c r="U179" t="str">
+        <v/>
+      </c>
+      <c r="V179" t="str">
+        <v/>
+      </c>
+      <c r="W179" t="str">
+        <v/>
+      </c>
+      <c r="X179" t="str">
+        <v/>
+      </c>
+      <c r="Y179" t="str">
+        <v/>
+      </c>
+      <c r="Z179" t="str">
+        <v/>
+      </c>
+      <c r="AA179" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>אוליביה דין The Art of Loving</v>
+      </c>
+      <c r="B180" t="str">
+        <v>2026-01-04</v>
+      </c>
+      <c r="C180" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
+      </c>
+      <c r="D180" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E180" t="str">
+        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
+      </c>
+      <c r="F180" t="str">
+        <v/>
+      </c>
+      <c r="G180" t="str">
+        <v/>
+      </c>
+      <c r="H180" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I180" t="str">
+        <v/>
+      </c>
+      <c r="J180" t="str">
+        <v/>
+      </c>
+      <c r="K180" t="str">
+        <v>אוליביה דין The Art of Loving</v>
+      </c>
+      <c r="L180" t="str">
+        <v/>
+      </c>
+      <c r="M180" t="str">
+        <v/>
+      </c>
+      <c r="N180" t="str">
+        <v/>
+      </c>
+      <c r="O180" t="str">
+        <v/>
+      </c>
+      <c r="P180" t="str">
+        <v/>
+      </c>
+      <c r="Q180" t="str">
+        <v/>
+      </c>
+      <c r="R180" t="str">
+        <v/>
+      </c>
+      <c r="S180" t="str">
+        <v/>
+      </c>
+      <c r="T180" t="str">
+        <v/>
+      </c>
+      <c r="U180" t="str">
+        <v/>
+      </c>
+      <c r="V180" t="str">
+        <v/>
+      </c>
+      <c r="W180" t="str">
+        <v/>
+      </c>
+      <c r="X180" t="str">
+        <v/>
+      </c>
+      <c r="Y180" t="str">
+        <v/>
+      </c>
+      <c r="Z180" t="str">
+        <v/>
+      </c>
+      <c r="AA180" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>Geese Getting Killed</v>
+      </c>
+      <c r="B181" t="str">
+        <v>2025-12-29</v>
+      </c>
+      <c r="C181" t="str">
+        <v>https://yosmusic.com/geese-getting-killed/</v>
+      </c>
+      <c r="D181" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E181" t="str">
+        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
+      </c>
+      <c r="F181" t="str">
+        <v/>
+      </c>
+      <c r="G181" t="str">
+        <v/>
+      </c>
+      <c r="H181" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I181" t="str">
+        <v/>
+      </c>
+      <c r="J181" t="str">
+        <v/>
+      </c>
+      <c r="K181" t="str">
+        <v>Geese Getting Killed</v>
+      </c>
+      <c r="L181" t="str">
+        <v/>
+      </c>
+      <c r="M181" t="str">
+        <v/>
+      </c>
+      <c r="N181" t="str">
+        <v/>
+      </c>
+      <c r="O181" t="str">
+        <v/>
+      </c>
+      <c r="P181" t="str">
+        <v/>
+      </c>
+      <c r="Q181" t="str">
+        <v/>
+      </c>
+      <c r="R181" t="str">
+        <v/>
+      </c>
+      <c r="S181" t="str">
+        <v/>
+      </c>
+      <c r="T181" t="str">
+        <v/>
+      </c>
+      <c r="U181" t="str">
+        <v/>
+      </c>
+      <c r="V181" t="str">
+        <v/>
+      </c>
+      <c r="W181" t="str">
+        <v/>
+      </c>
+      <c r="X181" t="str">
+        <v/>
+      </c>
+      <c r="Y181" t="str">
+        <v/>
+      </c>
+      <c r="Z181" t="str">
+        <v/>
+      </c>
+      <c r="AA181" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>רוסליה Lux</v>
+      </c>
+      <c r="B182" t="str">
+        <v>2025-12-25</v>
+      </c>
+      <c r="C182" t="str">
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
+      </c>
+      <c r="D182" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E182" t="str">
+        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
+      </c>
+      <c r="F182" t="str">
+        <v/>
+      </c>
+      <c r="G182" t="str">
+        <v/>
+      </c>
+      <c r="H182" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I182" t="str">
+        <v/>
+      </c>
+      <c r="J182" t="str">
+        <v/>
+      </c>
+      <c r="K182" t="str">
+        <v>רוסליה Lux</v>
+      </c>
+      <c r="L182" t="str">
+        <v/>
+      </c>
+      <c r="M182" t="str">
+        <v/>
+      </c>
+      <c r="N182" t="str">
+        <v/>
+      </c>
+      <c r="O182" t="str">
+        <v/>
+      </c>
+      <c r="P182" t="str">
+        <v/>
+      </c>
+      <c r="Q182" t="str">
+        <v/>
+      </c>
+      <c r="R182" t="str">
+        <v/>
+      </c>
+      <c r="S182" t="str">
+        <v/>
+      </c>
+      <c r="T182" t="str">
+        <v/>
+      </c>
+      <c r="U182" t="str">
+        <v/>
+      </c>
+      <c r="V182" t="str">
+        <v/>
+      </c>
+      <c r="W182" t="str">
+        <v/>
+      </c>
+      <c r="X182" t="str">
+        <v/>
+      </c>
+      <c r="Y182" t="str">
+        <v/>
+      </c>
+      <c r="Z182" t="str">
+        <v/>
+      </c>
+      <c r="AA182" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>יאנגבלאד אירוסמית' one more time</v>
+      </c>
+      <c r="B183" t="str">
+        <v>2025-12-17</v>
+      </c>
+      <c r="C183" t="str">
+        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
+      </c>
+      <c r="D183" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E183" t="str">
+        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
+      </c>
+      <c r="F183" t="str">
+        <v/>
+      </c>
+      <c r="G183" t="str">
+        <v/>
+      </c>
+      <c r="H183" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I183" t="str">
+        <v/>
+      </c>
+      <c r="J183" t="str">
+        <v/>
+      </c>
+      <c r="K183" t="str">
+        <v>יאנגבלאד אירוסמית' one more time</v>
+      </c>
+      <c r="L183" t="str">
+        <v/>
+      </c>
+      <c r="M183" t="str">
+        <v/>
+      </c>
+      <c r="N183" t="str">
+        <v/>
+      </c>
+      <c r="O183" t="str">
+        <v/>
+      </c>
+      <c r="P183" t="str">
+        <v/>
+      </c>
+      <c r="Q183" t="str">
+        <v/>
+      </c>
+      <c r="R183" t="str">
+        <v/>
+      </c>
+      <c r="S183" t="str">
+        <v/>
+      </c>
+      <c r="T183" t="str">
+        <v/>
+      </c>
+      <c r="U183" t="str">
+        <v/>
+      </c>
+      <c r="V183" t="str">
+        <v/>
+      </c>
+      <c r="W183" t="str">
+        <v/>
+      </c>
+      <c r="X183" t="str">
+        <v/>
+      </c>
+      <c r="Y183" t="str">
+        <v/>
+      </c>
+      <c r="Z183" t="str">
+        <v/>
+      </c>
+      <c r="AA183" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>פינק פלויד Wish You Were Here 50</v>
+      </c>
+      <c r="B184" t="str">
+        <v>2025-12-14</v>
+      </c>
+      <c r="C184" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
+      </c>
+      <c r="D184" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E184" t="str">
+        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
+      </c>
+      <c r="F184" t="str">
+        <v/>
+      </c>
+      <c r="G184" t="str">
+        <v/>
+      </c>
+      <c r="H184" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I184" t="str">
+        <v/>
+      </c>
+      <c r="J184" t="str">
+        <v/>
+      </c>
+      <c r="K184" t="str">
+        <v>פינק פלויד Wish You Were Here 50</v>
+      </c>
+      <c r="L184" t="str">
+        <v/>
+      </c>
+      <c r="M184" t="str">
+        <v/>
+      </c>
+      <c r="N184" t="str">
+        <v/>
+      </c>
+      <c r="O184" t="str">
+        <v/>
+      </c>
+      <c r="P184" t="str">
+        <v/>
+      </c>
+      <c r="Q184" t="str">
+        <v/>
+      </c>
+      <c r="R184" t="str">
+        <v/>
+      </c>
+      <c r="S184" t="str">
+        <v/>
+      </c>
+      <c r="T184" t="str">
+        <v/>
+      </c>
+      <c r="U184" t="str">
+        <v/>
+      </c>
+      <c r="V184" t="str">
+        <v/>
+      </c>
+      <c r="W184" t="str">
+        <v/>
+      </c>
+      <c r="X184" t="str">
+        <v/>
+      </c>
+      <c r="Y184" t="str">
+        <v/>
+      </c>
+      <c r="Z184" t="str">
+        <v/>
+      </c>
+      <c r="AA184" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+      </c>
+      <c r="B185" t="str">
+        <v>2025-12-08</v>
+      </c>
+      <c r="C185" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
+      </c>
+      <c r="D185" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E185" t="str">
+        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
+      </c>
+      <c r="F185" t="str">
+        <v/>
+      </c>
+      <c r="G185" t="str">
+        <v/>
+      </c>
+      <c r="H185" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I185" t="str">
+        <v/>
+      </c>
+      <c r="J185" t="str">
+        <v/>
+      </c>
+      <c r="K185" t="str">
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+      </c>
+      <c r="L185" t="str">
+        <v/>
+      </c>
+      <c r="M185" t="str">
+        <v/>
+      </c>
+      <c r="N185" t="str">
+        <v/>
+      </c>
+      <c r="O185" t="str">
+        <v/>
+      </c>
+      <c r="P185" t="str">
+        <v/>
+      </c>
+      <c r="Q185" t="str">
+        <v/>
+      </c>
+      <c r="R185" t="str">
+        <v/>
+      </c>
+      <c r="S185" t="str">
+        <v/>
+      </c>
+      <c r="T185" t="str">
+        <v/>
+      </c>
+      <c r="U185" t="str">
+        <v/>
+      </c>
+      <c r="V185" t="str">
+        <v/>
+      </c>
+      <c r="W185" t="str">
+        <v/>
+      </c>
+      <c r="X185" t="str">
+        <v/>
+      </c>
+      <c r="Y185" t="str">
+        <v/>
+      </c>
+      <c r="Z185" t="str">
+        <v/>
+      </c>
+      <c r="AA185" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>סטריי קידס DO IT EP</v>
+      </c>
+      <c r="B186" t="str">
+        <v>2025-12-04</v>
+      </c>
+      <c r="C186" t="str">
+        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
+      </c>
+      <c r="D186" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E186" t="str">
+        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
+      </c>
+      <c r="F186" t="str">
+        <v/>
+      </c>
+      <c r="G186" t="str">
+        <v/>
+      </c>
+      <c r="H186" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I186" t="str">
+        <v/>
+      </c>
+      <c r="J186" t="str">
+        <v/>
+      </c>
+      <c r="K186" t="str">
+        <v>סטריי קידס DO IT EP</v>
+      </c>
+      <c r="L186" t="str">
+        <v/>
+      </c>
+      <c r="M186" t="str">
+        <v/>
+      </c>
+      <c r="N186" t="str">
+        <v/>
+      </c>
+      <c r="O186" t="str">
+        <v/>
+      </c>
+      <c r="P186" t="str">
+        <v/>
+      </c>
+      <c r="Q186" t="str">
+        <v/>
+      </c>
+      <c r="R186" t="str">
+        <v/>
+      </c>
+      <c r="S186" t="str">
+        <v/>
+      </c>
+      <c r="T186" t="str">
+        <v/>
+      </c>
+      <c r="U186" t="str">
+        <v/>
+      </c>
+      <c r="V186" t="str">
+        <v/>
+      </c>
+      <c r="W186" t="str">
+        <v/>
+      </c>
+      <c r="X186" t="str">
+        <v/>
+      </c>
+      <c r="Y186" t="str">
+        <v/>
+      </c>
+      <c r="Z186" t="str">
+        <v/>
+      </c>
+      <c r="AA186" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>דויד ברוזה BROZAJAZZ</v>
+      </c>
+      <c r="B187" t="str">
+        <v>2025-11-30</v>
+      </c>
+      <c r="C187" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
+      </c>
+      <c r="D187" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E187" t="str">
+        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
+      </c>
+      <c r="F187" t="str">
+        <v/>
+      </c>
+      <c r="G187" t="str">
+        <v/>
+      </c>
+      <c r="H187" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I187" t="str">
+        <v/>
+      </c>
+      <c r="J187" t="str">
+        <v/>
+      </c>
+      <c r="K187" t="str">
+        <v>דויד ברוזה BROZAJAZZ</v>
+      </c>
+      <c r="L187" t="str">
+        <v/>
+      </c>
+      <c r="M187" t="str">
+        <v/>
+      </c>
+      <c r="N187" t="str">
+        <v/>
+      </c>
+      <c r="O187" t="str">
+        <v/>
+      </c>
+      <c r="P187" t="str">
+        <v/>
+      </c>
+      <c r="Q187" t="str">
+        <v/>
+      </c>
+      <c r="R187" t="str">
+        <v/>
+      </c>
+      <c r="S187" t="str">
+        <v/>
+      </c>
+      <c r="T187" t="str">
+        <v/>
+      </c>
+      <c r="U187" t="str">
+        <v/>
+      </c>
+      <c r="V187" t="str">
+        <v/>
+      </c>
+      <c r="W187" t="str">
+        <v/>
+      </c>
+      <c r="X187" t="str">
+        <v/>
+      </c>
+      <c r="Y187" t="str">
+        <v/>
+      </c>
+      <c r="Z187" t="str">
+        <v/>
+      </c>
+      <c r="AA187" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>Five Seconds of Summer – Everyone's A Star</v>
+      </c>
+      <c r="B188" t="str">
+        <v>2025-11-24</v>
+      </c>
+      <c r="C188" t="str">
+        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
+      </c>
+      <c r="D188" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E188" t="str">
+        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
+      </c>
+      <c r="F188" t="str">
+        <v/>
+      </c>
+      <c r="G188" t="str">
+        <v/>
+      </c>
+      <c r="H188" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I188" t="str">
+        <v/>
+      </c>
+      <c r="J188" t="str">
+        <v/>
+      </c>
+      <c r="K188" t="str">
+        <v>Five Seconds of Summer – Everyone's A Star</v>
+      </c>
+      <c r="L188" t="str">
+        <v/>
+      </c>
+      <c r="M188" t="str">
+        <v/>
+      </c>
+      <c r="N188" t="str">
+        <v/>
+      </c>
+      <c r="O188" t="str">
+        <v/>
+      </c>
+      <c r="P188" t="str">
+        <v/>
+      </c>
+      <c r="Q188" t="str">
+        <v/>
+      </c>
+      <c r="R188" t="str">
+        <v/>
+      </c>
+      <c r="S188" t="str">
+        <v/>
+      </c>
+      <c r="T188" t="str">
+        <v/>
+      </c>
+      <c r="U188" t="str">
+        <v/>
+      </c>
+      <c r="V188" t="str">
+        <v/>
+      </c>
+      <c r="W188" t="str">
+        <v/>
+      </c>
+      <c r="X188" t="str">
+        <v/>
+      </c>
+      <c r="Y188" t="str">
+        <v/>
+      </c>
+      <c r="Z188" t="str">
+        <v/>
+      </c>
+      <c r="AA188" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>התקווה 6 – ויהי אור</v>
+      </c>
+      <c r="B189" t="str">
+        <v>2025-11-20</v>
+      </c>
+      <c r="C189" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
+      </c>
+      <c r="D189" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E189" t="str">
+        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
+      </c>
+      <c r="F189" t="str">
+        <v/>
+      </c>
+      <c r="G189" t="str">
+        <v/>
+      </c>
+      <c r="H189" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I189" t="str">
+        <v/>
+      </c>
+      <c r="J189" t="str">
+        <v/>
+      </c>
+      <c r="K189" t="str">
+        <v>התקווה 6 – ויהי אור</v>
+      </c>
+      <c r="L189" t="str">
+        <v/>
+      </c>
+      <c r="M189" t="str">
+        <v/>
+      </c>
+      <c r="N189" t="str">
+        <v/>
+      </c>
+      <c r="O189" t="str">
+        <v/>
+      </c>
+      <c r="P189" t="str">
+        <v/>
+      </c>
+      <c r="Q189" t="str">
+        <v/>
+      </c>
+      <c r="R189" t="str">
+        <v/>
+      </c>
+      <c r="S189" t="str">
+        <v/>
+      </c>
+      <c r="T189" t="str">
+        <v/>
+      </c>
+      <c r="U189" t="str">
+        <v/>
+      </c>
+      <c r="V189" t="str">
+        <v/>
+      </c>
+      <c r="W189" t="str">
+        <v/>
+      </c>
+      <c r="X189" t="str">
+        <v/>
+      </c>
+      <c r="Y189" t="str">
+        <v/>
+      </c>
+      <c r="Z189" t="str">
+        <v/>
+      </c>
+      <c r="AA189" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>פלורנס אנד דה משין Everybody Scream</v>
+      </c>
+      <c r="B190" t="str">
+        <v>2025-11-13</v>
+      </c>
+      <c r="C190" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
+      </c>
+      <c r="D190" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E190" t="str">
+        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
+      </c>
+      <c r="F190" t="str">
+        <v/>
+      </c>
+      <c r="G190" t="str">
+        <v/>
+      </c>
+      <c r="H190" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I190" t="str">
+        <v/>
+      </c>
+      <c r="J190" t="str">
+        <v/>
+      </c>
+      <c r="K190" t="str">
+        <v>פלורנס אנד דה משין Everybody Scream</v>
+      </c>
+      <c r="L190" t="str">
+        <v/>
+      </c>
+      <c r="M190" t="str">
+        <v/>
+      </c>
+      <c r="N190" t="str">
+        <v/>
+      </c>
+      <c r="O190" t="str">
+        <v/>
+      </c>
+      <c r="P190" t="str">
+        <v/>
+      </c>
+      <c r="Q190" t="str">
+        <v/>
+      </c>
+      <c r="R190" t="str">
+        <v/>
+      </c>
+      <c r="S190" t="str">
+        <v/>
+      </c>
+      <c r="T190" t="str">
+        <v/>
+      </c>
+      <c r="U190" t="str">
+        <v/>
+      </c>
+      <c r="V190" t="str">
+        <v/>
+      </c>
+      <c r="W190" t="str">
+        <v/>
+      </c>
+      <c r="X190" t="str">
+        <v/>
+      </c>
+      <c r="Y190" t="str">
+        <v/>
+      </c>
+      <c r="Z190" t="str">
+        <v/>
+      </c>
+      <c r="AA190" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>טיים אימפלה Deadbeat</v>
+      </c>
+      <c r="B191" t="str">
+        <v>2025-11-03</v>
+      </c>
+      <c r="C191" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
+      </c>
+      <c r="D191" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E191" t="str">
+        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
+      </c>
+      <c r="F191" t="str">
+        <v/>
+      </c>
+      <c r="G191" t="str">
+        <v/>
+      </c>
+      <c r="H191" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I191" t="str">
+        <v/>
+      </c>
+      <c r="J191" t="str">
+        <v/>
+      </c>
+      <c r="K191" t="str">
+        <v>טיים אימפלה Deadbeat</v>
+      </c>
+      <c r="L191" t="str">
+        <v/>
+      </c>
+      <c r="M191" t="str">
+        <v/>
+      </c>
+      <c r="N191" t="str">
+        <v/>
+      </c>
+      <c r="O191" t="str">
+        <v/>
+      </c>
+      <c r="P191" t="str">
+        <v/>
+      </c>
+      <c r="Q191" t="str">
+        <v/>
+      </c>
+      <c r="R191" t="str">
+        <v/>
+      </c>
+      <c r="S191" t="str">
+        <v/>
+      </c>
+      <c r="T191" t="str">
+        <v/>
+      </c>
+      <c r="U191" t="str">
+        <v/>
+      </c>
+      <c r="V191" t="str">
+        <v/>
+      </c>
+      <c r="W191" t="str">
+        <v/>
+      </c>
+      <c r="X191" t="str">
+        <v/>
+      </c>
+      <c r="Y191" t="str">
+        <v/>
+      </c>
+      <c r="Z191" t="str">
+        <v/>
+      </c>
+      <c r="AA191" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+      </c>
+      <c r="B192" t="str">
+        <v>2025-10-20</v>
+      </c>
+      <c r="C192" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
+      </c>
+      <c r="D192" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E192" t="str">
+        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
+      </c>
+      <c r="F192" t="str">
+        <v/>
+      </c>
+      <c r="G192" t="str">
+        <v/>
+      </c>
+      <c r="H192" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I192" t="str">
+        <v/>
+      </c>
+      <c r="J192" t="str">
+        <v/>
+      </c>
+      <c r="K192" t="str">
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+      </c>
+      <c r="L192" t="str">
+        <v/>
+      </c>
+      <c r="M192" t="str">
+        <v/>
+      </c>
+      <c r="N192" t="str">
+        <v/>
+      </c>
+      <c r="O192" t="str">
+        <v/>
+      </c>
+      <c r="P192" t="str">
+        <v/>
+      </c>
+      <c r="Q192" t="str">
+        <v/>
+      </c>
+      <c r="R192" t="str">
+        <v/>
+      </c>
+      <c r="S192" t="str">
+        <v/>
+      </c>
+      <c r="T192" t="str">
+        <v/>
+      </c>
+      <c r="U192" t="str">
+        <v/>
+      </c>
+      <c r="V192" t="str">
+        <v/>
+      </c>
+      <c r="W192" t="str">
+        <v/>
+      </c>
+      <c r="X192" t="str">
+        <v/>
+      </c>
+      <c r="Y192" t="str">
+        <v/>
+      </c>
+      <c r="Z192" t="str">
+        <v/>
+      </c>
+      <c r="AA192" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>שלמה גרוניך – תודה אהבה</v>
+      </c>
+      <c r="B193" t="str">
+        <v>2025-10-18</v>
+      </c>
+      <c r="C193" t="str">
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
+      </c>
+      <c r="D193" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E193" t="str">
+        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
+      </c>
+      <c r="F193" t="str">
+        <v/>
+      </c>
+      <c r="G193" t="str">
+        <v/>
+      </c>
+      <c r="H193" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I193" t="str">
+        <v/>
+      </c>
+      <c r="J193" t="str">
+        <v/>
+      </c>
+      <c r="K193" t="str">
+        <v>שלמה גרוניך – תודה אהבה</v>
+      </c>
+      <c r="L193" t="str">
+        <v/>
+      </c>
+      <c r="M193" t="str">
+        <v/>
+      </c>
+      <c r="N193" t="str">
+        <v/>
+      </c>
+      <c r="O193" t="str">
+        <v/>
+      </c>
+      <c r="P193" t="str">
+        <v/>
+      </c>
+      <c r="Q193" t="str">
+        <v/>
+      </c>
+      <c r="R193" t="str">
+        <v/>
+      </c>
+      <c r="S193" t="str">
+        <v/>
+      </c>
+      <c r="T193" t="str">
+        <v/>
+      </c>
+      <c r="U193" t="str">
+        <v/>
+      </c>
+      <c r="V193" t="str">
+        <v/>
+      </c>
+      <c r="W193" t="str">
+        <v/>
+      </c>
+      <c r="X193" t="str">
+        <v/>
+      </c>
+      <c r="Y193" t="str">
+        <v/>
+      </c>
+      <c r="Z193" t="str">
+        <v/>
+      </c>
+      <c r="AA193" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
+      </c>
+      <c r="B194" t="str">
+        <v>2025-10-11</v>
+      </c>
+      <c r="C194" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
+      </c>
+      <c r="D194" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E194" t="str">
+        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
+      </c>
+      <c r="F194" t="str">
+        <v/>
+      </c>
+      <c r="G194" t="str">
+        <v/>
+      </c>
+      <c r="H194" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I194" t="str">
+        <v/>
+      </c>
+      <c r="J194" t="str">
+        <v/>
+      </c>
+      <c r="K194" t="str">
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
+      </c>
+      <c r="L194" t="str">
+        <v/>
+      </c>
+      <c r="M194" t="str">
+        <v/>
+      </c>
+      <c r="N194" t="str">
+        <v/>
+      </c>
+      <c r="O194" t="str">
+        <v/>
+      </c>
+      <c r="P194" t="str">
+        <v/>
+      </c>
+      <c r="Q194" t="str">
+        <v/>
+      </c>
+      <c r="R194" t="str">
+        <v/>
+      </c>
+      <c r="S194" t="str">
+        <v/>
+      </c>
+      <c r="T194" t="str">
+        <v/>
+      </c>
+      <c r="U194" t="str">
+        <v/>
+      </c>
+      <c r="V194" t="str">
+        <v/>
+      </c>
+      <c r="W194" t="str">
+        <v/>
+      </c>
+      <c r="X194" t="str">
+        <v/>
+      </c>
+      <c r="Y194" t="str">
+        <v/>
+      </c>
+      <c r="Z194" t="str">
+        <v/>
+      </c>
+      <c r="AA194" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>דוג'ה קאט Vie</v>
+      </c>
+      <c r="B195" t="str">
+        <v>2025-10-04</v>
+      </c>
+      <c r="C195" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
+      </c>
+      <c r="D195" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E195" t="str">
+        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
+      </c>
+      <c r="F195" t="str">
+        <v/>
+      </c>
+      <c r="G195" t="str">
+        <v/>
+      </c>
+      <c r="H195" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I195" t="str">
+        <v/>
+      </c>
+      <c r="J195" t="str">
+        <v/>
+      </c>
+      <c r="K195" t="str">
+        <v>דוג'ה קאט Vie</v>
+      </c>
+      <c r="L195" t="str">
+        <v/>
+      </c>
+      <c r="M195" t="str">
+        <v/>
+      </c>
+      <c r="N195" t="str">
+        <v/>
+      </c>
+      <c r="O195" t="str">
+        <v/>
+      </c>
+      <c r="P195" t="str">
+        <v/>
+      </c>
+      <c r="Q195" t="str">
+        <v/>
+      </c>
+      <c r="R195" t="str">
+        <v/>
+      </c>
+      <c r="S195" t="str">
+        <v/>
+      </c>
+      <c r="T195" t="str">
+        <v/>
+      </c>
+      <c r="U195" t="str">
+        <v/>
+      </c>
+      <c r="V195" t="str">
+        <v/>
+      </c>
+      <c r="W195" t="str">
+        <v/>
+      </c>
+      <c r="X195" t="str">
+        <v/>
+      </c>
+      <c r="Y195" t="str">
+        <v/>
+      </c>
+      <c r="Z195" t="str">
+        <v/>
+      </c>
+      <c r="AA195" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>ג'וי קרוקס Juniper</v>
+      </c>
+      <c r="B196" t="str">
+        <v>2025-10-03</v>
+      </c>
+      <c r="C196" t="str">
+        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
+      </c>
+      <c r="D196" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E196" t="str">
+        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
+      </c>
+      <c r="F196" t="str">
+        <v/>
+      </c>
+      <c r="G196" t="str">
+        <v/>
+      </c>
+      <c r="H196" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I196" t="str">
+        <v/>
+      </c>
+      <c r="J196" t="str">
+        <v/>
+      </c>
+      <c r="K196" t="str">
+        <v>ג'וי קרוקס Juniper</v>
+      </c>
+      <c r="L196" t="str">
+        <v/>
+      </c>
+      <c r="M196" t="str">
+        <v/>
+      </c>
+      <c r="N196" t="str">
+        <v/>
+      </c>
+      <c r="O196" t="str">
+        <v/>
+      </c>
+      <c r="P196" t="str">
+        <v/>
+      </c>
+      <c r="Q196" t="str">
+        <v/>
+      </c>
+      <c r="R196" t="str">
+        <v/>
+      </c>
+      <c r="S196" t="str">
+        <v/>
+      </c>
+      <c r="T196" t="str">
+        <v/>
+      </c>
+      <c r="U196" t="str">
+        <v/>
+      </c>
+      <c r="V196" t="str">
+        <v/>
+      </c>
+      <c r="W196" t="str">
+        <v/>
+      </c>
+      <c r="X196" t="str">
+        <v/>
+      </c>
+      <c r="Y196" t="str">
+        <v/>
+      </c>
+      <c r="Z196" t="str">
+        <v/>
+      </c>
+      <c r="AA196" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>ביפי קליירו Futique</v>
+      </c>
+      <c r="B197" t="str">
+        <v>2025-09-30</v>
+      </c>
+      <c r="C197" t="str">
+        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
+      </c>
+      <c r="D197" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E197" t="str">
+        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
+      </c>
+      <c r="F197" t="str">
+        <v/>
+      </c>
+      <c r="G197" t="str">
+        <v/>
+      </c>
+      <c r="H197" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I197" t="str">
+        <v/>
+      </c>
+      <c r="J197" t="str">
+        <v/>
+      </c>
+      <c r="K197" t="str">
+        <v>ביפי קליירו Futique</v>
+      </c>
+      <c r="L197" t="str">
+        <v/>
+      </c>
+      <c r="M197" t="str">
+        <v/>
+      </c>
+      <c r="N197" t="str">
+        <v/>
+      </c>
+      <c r="O197" t="str">
+        <v/>
+      </c>
+      <c r="P197" t="str">
+        <v/>
+      </c>
+      <c r="Q197" t="str">
+        <v/>
+      </c>
+      <c r="R197" t="str">
+        <v/>
+      </c>
+      <c r="S197" t="str">
+        <v/>
+      </c>
+      <c r="T197" t="str">
+        <v/>
+      </c>
+      <c r="U197" t="str">
+        <v/>
+      </c>
+      <c r="V197" t="str">
+        <v/>
+      </c>
+      <c r="W197" t="str">
+        <v/>
+      </c>
+      <c r="X197" t="str">
+        <v/>
+      </c>
+      <c r="Y197" t="str">
+        <v/>
+      </c>
+      <c r="Z197" t="str">
+        <v/>
+      </c>
+      <c r="AA197" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>אד שירן Play</v>
+      </c>
+      <c r="B198" t="str">
+        <v>2025-09-24</v>
+      </c>
+      <c r="C198" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
+      </c>
+      <c r="D198" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E198" t="str">
+        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
+      </c>
+      <c r="F198" t="str">
+        <v/>
+      </c>
+      <c r="G198" t="str">
+        <v/>
+      </c>
+      <c r="H198" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I198" t="str">
+        <v/>
+      </c>
+      <c r="J198" t="str">
+        <v/>
+      </c>
+      <c r="K198" t="str">
+        <v>אד שירן Play</v>
+      </c>
+      <c r="L198" t="str">
+        <v/>
+      </c>
+      <c r="M198" t="str">
+        <v/>
+      </c>
+      <c r="N198" t="str">
+        <v/>
+      </c>
+      <c r="O198" t="str">
+        <v/>
+      </c>
+      <c r="P198" t="str">
+        <v/>
+      </c>
+      <c r="Q198" t="str">
+        <v/>
+      </c>
+      <c r="R198" t="str">
+        <v/>
+      </c>
+      <c r="S198" t="str">
+        <v/>
+      </c>
+      <c r="T198" t="str">
+        <v/>
+      </c>
+      <c r="U198" t="str">
+        <v/>
+      </c>
+      <c r="V198" t="str">
+        <v/>
+      </c>
+      <c r="W198" t="str">
+        <v/>
+      </c>
+      <c r="X198" t="str">
+        <v/>
+      </c>
+      <c r="Y198" t="str">
+        <v/>
+      </c>
+      <c r="Z198" t="str">
+        <v/>
+      </c>
+      <c r="AA198" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+      </c>
+      <c r="B199" t="str">
+        <v>2025-09-21</v>
+      </c>
+      <c r="C199" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
+      </c>
+      <c r="D199" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E199" t="str">
+        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
+      </c>
+      <c r="F199" t="str">
+        <v/>
+      </c>
+      <c r="G199" t="str">
+        <v/>
+      </c>
+      <c r="H199" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I199" t="str">
+        <v/>
+      </c>
+      <c r="J199" t="str">
+        <v/>
+      </c>
+      <c r="K199" t="str">
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+      </c>
+      <c r="L199" t="str">
+        <v/>
+      </c>
+      <c r="M199" t="str">
+        <v/>
+      </c>
+      <c r="N199" t="str">
+        <v/>
+      </c>
+      <c r="O199" t="str">
+        <v/>
+      </c>
+      <c r="P199" t="str">
+        <v/>
+      </c>
+      <c r="Q199" t="str">
+        <v/>
+      </c>
+      <c r="R199" t="str">
+        <v/>
+      </c>
+      <c r="S199" t="str">
+        <v/>
+      </c>
+      <c r="T199" t="str">
+        <v/>
+      </c>
+      <c r="U199" t="str">
+        <v/>
+      </c>
+      <c r="V199" t="str">
+        <v/>
+      </c>
+      <c r="W199" t="str">
+        <v/>
+      </c>
+      <c r="X199" t="str">
+        <v/>
+      </c>
+      <c r="Y199" t="str">
+        <v/>
+      </c>
+      <c r="Z199" t="str">
+        <v/>
+      </c>
+      <c r="AA199" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>סוויד Antidepressants</v>
+      </c>
+      <c r="B200" t="str">
+        <v>2025-09-12</v>
+      </c>
+      <c r="C200" t="str">
+        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
+      </c>
+      <c r="D200" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E200" t="str">
+        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
+      </c>
+      <c r="F200" t="str">
+        <v/>
+      </c>
+      <c r="G200" t="str">
+        <v/>
+      </c>
+      <c r="H200" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I200" t="str">
+        <v/>
+      </c>
+      <c r="J200" t="str">
+        <v/>
+      </c>
+      <c r="K200" t="str">
+        <v>סוויד Antidepressants</v>
+      </c>
+      <c r="L200" t="str">
+        <v/>
+      </c>
+      <c r="M200" t="str">
+        <v/>
+      </c>
+      <c r="N200" t="str">
+        <v/>
+      </c>
+      <c r="O200" t="str">
+        <v/>
+      </c>
+      <c r="P200" t="str">
+        <v/>
+      </c>
+      <c r="Q200" t="str">
+        <v/>
+      </c>
+      <c r="R200" t="str">
+        <v/>
+      </c>
+      <c r="S200" t="str">
+        <v/>
+      </c>
+      <c r="T200" t="str">
+        <v/>
+      </c>
+      <c r="U200" t="str">
+        <v/>
+      </c>
+      <c r="V200" t="str">
+        <v/>
+      </c>
+      <c r="W200" t="str">
+        <v/>
+      </c>
+      <c r="X200" t="str">
+        <v/>
+      </c>
+      <c r="Y200" t="str">
+        <v/>
+      </c>
+      <c r="Z200" t="str">
+        <v/>
+      </c>
+      <c r="AA200" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>וולף אליס The Clearing</v>
+      </c>
+      <c r="B201" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="C201" t="str">
+        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
+      </c>
+      <c r="D201" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E201" t="str">
+        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
+      </c>
+      <c r="F201" t="str">
+        <v/>
+      </c>
+      <c r="G201" t="str">
+        <v/>
+      </c>
+      <c r="H201" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I201" t="str">
+        <v/>
+      </c>
+      <c r="J201" t="str">
+        <v/>
+      </c>
+      <c r="K201" t="str">
+        <v>וולף אליס The Clearing</v>
+      </c>
+      <c r="L201" t="str">
+        <v/>
+      </c>
+      <c r="M201" t="str">
+        <v/>
+      </c>
+      <c r="N201" t="str">
+        <v/>
+      </c>
+      <c r="O201" t="str">
+        <v/>
+      </c>
+      <c r="P201" t="str">
+        <v/>
+      </c>
+      <c r="Q201" t="str">
+        <v/>
+      </c>
+      <c r="R201" t="str">
+        <v/>
+      </c>
+      <c r="S201" t="str">
+        <v/>
+      </c>
+      <c r="T201" t="str">
+        <v/>
+      </c>
+      <c r="U201" t="str">
+        <v/>
+      </c>
+      <c r="V201" t="str">
+        <v/>
+      </c>
+      <c r="W201" t="str">
+        <v/>
+      </c>
+      <c r="X201" t="str">
+        <v/>
+      </c>
+      <c r="Y201" t="str">
+        <v/>
+      </c>
+      <c r="Z201" t="str">
+        <v/>
+      </c>
+      <c r="AA201" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+      </c>
+      <c r="B202" t="str">
+        <v>2025-08-29</v>
+      </c>
+      <c r="C202" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
+      </c>
+      <c r="D202" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E202" t="str">
+        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
+      </c>
+      <c r="F202" t="str">
+        <v/>
+      </c>
+      <c r="G202" t="str">
+        <v/>
+      </c>
+      <c r="H202" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I202" t="str">
+        <v/>
+      </c>
+      <c r="J202" t="str">
+        <v/>
+      </c>
+      <c r="K202" t="str">
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+      </c>
+      <c r="L202" t="str">
+        <v/>
+      </c>
+      <c r="M202" t="str">
+        <v/>
+      </c>
+      <c r="N202" t="str">
+        <v/>
+      </c>
+      <c r="O202" t="str">
+        <v/>
+      </c>
+      <c r="P202" t="str">
+        <v/>
+      </c>
+      <c r="Q202" t="str">
+        <v/>
+      </c>
+      <c r="R202" t="str">
+        <v/>
+      </c>
+      <c r="S202" t="str">
+        <v/>
+      </c>
+      <c r="T202" t="str">
+        <v/>
+      </c>
+      <c r="U202" t="str">
+        <v/>
+      </c>
+      <c r="V202" t="str">
+        <v/>
+      </c>
+      <c r="W202" t="str">
+        <v/>
+      </c>
+      <c r="X202" t="str">
+        <v/>
+      </c>
+      <c r="Y202" t="str">
+        <v/>
+      </c>
+      <c r="Z202" t="str">
+        <v/>
+      </c>
+      <c r="AA202" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+      </c>
+      <c r="B203" t="str">
+        <v>2025-08-24</v>
+      </c>
+      <c r="C203" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
+      </c>
+      <c r="D203" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E203" t="str">
+        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
+      </c>
+      <c r="F203" t="str">
+        <v/>
+      </c>
+      <c r="G203" t="str">
+        <v/>
+      </c>
+      <c r="H203" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I203" t="str">
+        <v/>
+      </c>
+      <c r="J203" t="str">
+        <v/>
+      </c>
+      <c r="K203" t="str">
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+      </c>
+      <c r="L203" t="str">
+        <v/>
+      </c>
+      <c r="M203" t="str">
+        <v/>
+      </c>
+      <c r="N203" t="str">
+        <v/>
+      </c>
+      <c r="O203" t="str">
+        <v/>
+      </c>
+      <c r="P203" t="str">
+        <v/>
+      </c>
+      <c r="Q203" t="str">
+        <v/>
+      </c>
+      <c r="R203" t="str">
+        <v/>
+      </c>
+      <c r="S203" t="str">
+        <v/>
+      </c>
+      <c r="T203" t="str">
+        <v/>
+      </c>
+      <c r="U203" t="str">
+        <v/>
+      </c>
+      <c r="V203" t="str">
+        <v/>
+      </c>
+      <c r="W203" t="str">
+        <v/>
+      </c>
+      <c r="X203" t="str">
+        <v/>
+      </c>
+      <c r="Y203" t="str">
+        <v/>
+      </c>
+      <c r="Z203" t="str">
+        <v/>
+      </c>
+      <c r="AA203" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+      </c>
+      <c r="B204" t="str">
+        <v>2025-08-21</v>
+      </c>
+      <c r="C204" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
+      </c>
+      <c r="D204" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E204" t="str">
+        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
+      </c>
+      <c r="F204" t="str">
+        <v/>
+      </c>
+      <c r="G204" t="str">
+        <v/>
+      </c>
+      <c r="H204" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I204" t="str">
+        <v/>
+      </c>
+      <c r="J204" t="str">
+        <v/>
+      </c>
+      <c r="K204" t="str">
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+      </c>
+      <c r="L204" t="str">
+        <v/>
+      </c>
+      <c r="M204" t="str">
+        <v/>
+      </c>
+      <c r="N204" t="str">
+        <v/>
+      </c>
+      <c r="O204" t="str">
+        <v/>
+      </c>
+      <c r="P204" t="str">
+        <v/>
+      </c>
+      <c r="Q204" t="str">
+        <v/>
+      </c>
+      <c r="R204" t="str">
+        <v/>
+      </c>
+      <c r="S204" t="str">
+        <v/>
+      </c>
+      <c r="T204" t="str">
+        <v/>
+      </c>
+      <c r="U204" t="str">
+        <v/>
+      </c>
+      <c r="V204" t="str">
+        <v/>
+      </c>
+      <c r="W204" t="str">
+        <v/>
+      </c>
+      <c r="X204" t="str">
+        <v/>
+      </c>
+      <c r="Y204" t="str">
+        <v/>
+      </c>
+      <c r="Z204" t="str">
+        <v/>
+      </c>
+      <c r="AA204" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>אברהם טל – חי</v>
+      </c>
+      <c r="B205" t="str">
+        <v>2025-08-17</v>
+      </c>
+      <c r="C205" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
+      </c>
+      <c r="D205" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E205" t="str">
+        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
+      </c>
+      <c r="F205" t="str">
+        <v/>
+      </c>
+      <c r="G205" t="str">
+        <v/>
+      </c>
+      <c r="H205" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I205" t="str">
+        <v/>
+      </c>
+      <c r="J205" t="str">
+        <v/>
+      </c>
+      <c r="K205" t="str">
+        <v>אברהם טל – חי</v>
+      </c>
+      <c r="L205" t="str">
+        <v/>
+      </c>
+      <c r="M205" t="str">
+        <v/>
+      </c>
+      <c r="N205" t="str">
+        <v/>
+      </c>
+      <c r="O205" t="str">
+        <v/>
+      </c>
+      <c r="P205" t="str">
+        <v/>
+      </c>
+      <c r="Q205" t="str">
+        <v/>
+      </c>
+      <c r="R205" t="str">
+        <v/>
+      </c>
+      <c r="S205" t="str">
+        <v/>
+      </c>
+      <c r="T205" t="str">
+        <v/>
+      </c>
+      <c r="U205" t="str">
+        <v/>
+      </c>
+      <c r="V205" t="str">
+        <v/>
+      </c>
+      <c r="W205" t="str">
+        <v/>
+      </c>
+      <c r="X205" t="str">
+        <v/>
+      </c>
+      <c r="Y205" t="str">
+        <v/>
+      </c>
+      <c r="Z205" t="str">
+        <v/>
+      </c>
+      <c r="AA205" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>רנה ראפ Bite Me</v>
+      </c>
+      <c r="B206" t="str">
+        <v>2025-08-12</v>
+      </c>
+      <c r="C206" t="str">
+        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
+      </c>
+      <c r="D206" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E206" t="str">
+        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
+      </c>
+      <c r="F206" t="str">
+        <v/>
+      </c>
+      <c r="G206" t="str">
+        <v/>
+      </c>
+      <c r="H206" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I206" t="str">
+        <v/>
+      </c>
+      <c r="J206" t="str">
+        <v/>
+      </c>
+      <c r="K206" t="str">
+        <v>רנה ראפ Bite Me</v>
+      </c>
+      <c r="L206" t="str">
+        <v/>
+      </c>
+      <c r="M206" t="str">
+        <v/>
+      </c>
+      <c r="N206" t="str">
+        <v/>
+      </c>
+      <c r="O206" t="str">
+        <v/>
+      </c>
+      <c r="P206" t="str">
+        <v/>
+      </c>
+      <c r="Q206" t="str">
+        <v/>
+      </c>
+      <c r="R206" t="str">
+        <v/>
+      </c>
+      <c r="S206" t="str">
+        <v/>
+      </c>
+      <c r="T206" t="str">
+        <v/>
+      </c>
+      <c r="U206" t="str">
+        <v/>
+      </c>
+      <c r="V206" t="str">
+        <v/>
+      </c>
+      <c r="W206" t="str">
+        <v/>
+      </c>
+      <c r="X206" t="str">
+        <v/>
+      </c>
+      <c r="Y206" t="str">
+        <v/>
+      </c>
+      <c r="Z206" t="str">
+        <v/>
+      </c>
+      <c r="AA206" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>The K's – Pretty On The Internet</v>
+      </c>
+      <c r="B207" t="str">
+        <v>2025-08-03</v>
+      </c>
+      <c r="C207" t="str">
+        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
+      </c>
+      <c r="D207" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E207" t="str">
+        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
+      </c>
+      <c r="F207" t="str">
+        <v/>
+      </c>
+      <c r="G207" t="str">
+        <v/>
+      </c>
+      <c r="H207" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I207" t="str">
+        <v/>
+      </c>
+      <c r="J207" t="str">
+        <v/>
+      </c>
+      <c r="K207" t="str">
+        <v>The K's – Pretty On The Internet</v>
+      </c>
+      <c r="L207" t="str">
+        <v/>
+      </c>
+      <c r="M207" t="str">
+        <v/>
+      </c>
+      <c r="N207" t="str">
+        <v/>
+      </c>
+      <c r="O207" t="str">
+        <v/>
+      </c>
+      <c r="P207" t="str">
+        <v/>
+      </c>
+      <c r="Q207" t="str">
+        <v/>
+      </c>
+      <c r="R207" t="str">
+        <v/>
+      </c>
+      <c r="S207" t="str">
+        <v/>
+      </c>
+      <c r="T207" t="str">
+        <v/>
+      </c>
+      <c r="U207" t="str">
+        <v/>
+      </c>
+      <c r="V207" t="str">
+        <v/>
+      </c>
+      <c r="W207" t="str">
+        <v/>
+      </c>
+      <c r="X207" t="str">
+        <v/>
+      </c>
+      <c r="Y207" t="str">
+        <v/>
+      </c>
+      <c r="Z207" t="str">
+        <v/>
+      </c>
+      <c r="AA207" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>עדן בן זקן - רולקס וקסקט</v>
+      </c>
+      <c r="B208" t="str">
+        <v>2026  08:41-01-14</v>
+      </c>
+      <c r="C208" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24436&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D208" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E208" t="str">
+        <v/>
+      </c>
+      <c r="F208" t="str">
+        <v/>
+      </c>
+      <c r="G208" t="str">
+        <v/>
+      </c>
+      <c r="H208" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I208" t="str">
+        <v/>
+      </c>
+      <c r="J208" t="str">
+        <v/>
+      </c>
+      <c r="K208" t="str">
+        <v>עדן בן זקן - רולקס וקסקט</v>
+      </c>
+      <c r="L208" t="str">
+        <v/>
+      </c>
+      <c r="M208" t="str">
+        <v/>
+      </c>
+      <c r="N208" t="str">
+        <v/>
+      </c>
+      <c r="O208" t="str">
+        <v/>
+      </c>
+      <c r="P208" t="str">
+        <v/>
+      </c>
+      <c r="Q208" t="str">
+        <v/>
+      </c>
+      <c r="R208" t="str">
+        <v/>
+      </c>
+      <c r="S208" t="str">
+        <v/>
+      </c>
+      <c r="T208" t="str">
+        <v/>
+      </c>
+      <c r="U208" t="str">
+        <v/>
+      </c>
+      <c r="V208" t="str">
+        <v/>
+      </c>
+      <c r="W208" t="str">
+        <v/>
+      </c>
+      <c r="X208" t="str">
+        <v/>
+      </c>
+      <c r="Y208" t="str">
+        <v/>
+      </c>
+      <c r="Z208" t="str">
+        <v/>
+      </c>
+      <c r="AA208" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
+      </c>
+      <c r="B209" t="str">
+        <v>2026  08:40-01-14</v>
+      </c>
+      <c r="C209" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24439&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D209" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E209" t="str">
+        <v/>
+      </c>
+      <c r="F209" t="str">
+        <v/>
+      </c>
+      <c r="G209" t="str">
+        <v/>
+      </c>
+      <c r="H209" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I209" t="str">
+        <v/>
+      </c>
+      <c r="J209" t="str">
+        <v/>
+      </c>
+      <c r="K209" t="str">
+        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
+      </c>
+      <c r="L209" t="str">
+        <v/>
+      </c>
+      <c r="M209" t="str">
+        <v/>
+      </c>
+      <c r="N209" t="str">
+        <v/>
+      </c>
+      <c r="O209" t="str">
+        <v/>
+      </c>
+      <c r="P209" t="str">
+        <v/>
+      </c>
+      <c r="Q209" t="str">
+        <v/>
+      </c>
+      <c r="R209" t="str">
+        <v/>
+      </c>
+      <c r="S209" t="str">
+        <v/>
+      </c>
+      <c r="T209" t="str">
+        <v/>
+      </c>
+      <c r="U209" t="str">
+        <v/>
+      </c>
+      <c r="V209" t="str">
+        <v/>
+      </c>
+      <c r="W209" t="str">
+        <v/>
+      </c>
+      <c r="X209" t="str">
+        <v/>
+      </c>
+      <c r="Y209" t="str">
+        <v/>
+      </c>
+      <c r="Z209" t="str">
+        <v/>
+      </c>
+      <c r="AA209" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>אייל גולן - בית מפואר</v>
+      </c>
+      <c r="B210" t="str">
+        <v>2025  02:18-12-31</v>
+      </c>
+      <c r="C210" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D210" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E210" t="str">
+        <v/>
+      </c>
+      <c r="F210" t="str">
+        <v/>
+      </c>
+      <c r="G210" t="str">
+        <v/>
+      </c>
+      <c r="H210" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I210" t="str">
+        <v/>
+      </c>
+      <c r="J210" t="str">
+        <v/>
+      </c>
+      <c r="K210" t="str">
+        <v>אייל גולן - בית מפואר</v>
+      </c>
+      <c r="L210" t="str">
+        <v/>
+      </c>
+      <c r="M210" t="str">
+        <v/>
+      </c>
+      <c r="N210" t="str">
+        <v/>
+      </c>
+      <c r="O210" t="str">
+        <v/>
+      </c>
+      <c r="P210" t="str">
+        <v/>
+      </c>
+      <c r="Q210" t="str">
+        <v/>
+      </c>
+      <c r="R210" t="str">
+        <v/>
+      </c>
+      <c r="S210" t="str">
+        <v/>
+      </c>
+      <c r="T210" t="str">
+        <v/>
+      </c>
+      <c r="U210" t="str">
+        <v/>
+      </c>
+      <c r="V210" t="str">
+        <v/>
+      </c>
+      <c r="W210" t="str">
+        <v/>
+      </c>
+      <c r="X210" t="str">
+        <v/>
+      </c>
+      <c r="Y210" t="str">
+        <v/>
+      </c>
+      <c r="Z210" t="str">
+        <v/>
+      </c>
+      <c r="AA210" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
+      </c>
+      <c r="B211" t="str">
+        <v>2025  02:16-12-31</v>
+      </c>
+      <c r="C211" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D211" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E211" t="str">
+        <v/>
+      </c>
+      <c r="F211" t="str">
+        <v/>
+      </c>
+      <c r="G211" t="str">
+        <v/>
+      </c>
+      <c r="H211" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I211" t="str">
+        <v/>
+      </c>
+      <c r="J211" t="str">
+        <v/>
+      </c>
+      <c r="K211" t="str">
+        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
+      </c>
+      <c r="L211" t="str">
+        <v/>
+      </c>
+      <c r="M211" t="str">
+        <v/>
+      </c>
+      <c r="N211" t="str">
+        <v/>
+      </c>
+      <c r="O211" t="str">
+        <v/>
+      </c>
+      <c r="P211" t="str">
+        <v/>
+      </c>
+      <c r="Q211" t="str">
+        <v/>
+      </c>
+      <c r="R211" t="str">
+        <v/>
+      </c>
+      <c r="S211" t="str">
+        <v/>
+      </c>
+      <c r="T211" t="str">
+        <v/>
+      </c>
+      <c r="U211" t="str">
+        <v/>
+      </c>
+      <c r="V211" t="str">
+        <v/>
+      </c>
+      <c r="W211" t="str">
+        <v/>
+      </c>
+      <c r="X211" t="str">
+        <v/>
+      </c>
+      <c r="Y211" t="str">
+        <v/>
+      </c>
+      <c r="Z211" t="str">
+        <v/>
+      </c>
+      <c r="AA211" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>שיר לוי - ילד מוזר</v>
+      </c>
+      <c r="B212" t="str">
+        <v>2025  02:14-12-31</v>
+      </c>
+      <c r="C212" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D212" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E212" t="str">
+        <v/>
+      </c>
+      <c r="F212" t="str">
+        <v/>
+      </c>
+      <c r="G212" t="str">
+        <v/>
+      </c>
+      <c r="H212" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I212" t="str">
+        <v/>
+      </c>
+      <c r="J212" t="str">
+        <v/>
+      </c>
+      <c r="K212" t="str">
+        <v>שיר לוי - ילד מוזר</v>
+      </c>
+      <c r="L212" t="str">
+        <v/>
+      </c>
+      <c r="M212" t="str">
+        <v/>
+      </c>
+      <c r="N212" t="str">
+        <v/>
+      </c>
+      <c r="O212" t="str">
+        <v/>
+      </c>
+      <c r="P212" t="str">
+        <v/>
+      </c>
+      <c r="Q212" t="str">
+        <v/>
+      </c>
+      <c r="R212" t="str">
+        <v/>
+      </c>
+      <c r="S212" t="str">
+        <v/>
+      </c>
+      <c r="T212" t="str">
+        <v/>
+      </c>
+      <c r="U212" t="str">
+        <v/>
+      </c>
+      <c r="V212" t="str">
+        <v/>
+      </c>
+      <c r="W212" t="str">
+        <v/>
+      </c>
+      <c r="X212" t="str">
+        <v/>
+      </c>
+      <c r="Y212" t="str">
+        <v/>
+      </c>
+      <c r="Z212" t="str">
+        <v/>
+      </c>
+      <c r="AA212" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>פיטר רוט - 50</v>
+      </c>
+      <c r="B213" t="str">
+        <v>2025  02:13-12-31</v>
+      </c>
+      <c r="C213" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D213" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E213" t="str">
+        <v/>
+      </c>
+      <c r="F213" t="str">
+        <v/>
+      </c>
+      <c r="G213" t="str">
+        <v/>
+      </c>
+      <c r="H213" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I213" t="str">
+        <v/>
+      </c>
+      <c r="J213" t="str">
+        <v/>
+      </c>
+      <c r="K213" t="str">
+        <v>פיטר רוט - 50</v>
+      </c>
+      <c r="L213" t="str">
+        <v/>
+      </c>
+      <c r="M213" t="str">
+        <v/>
+      </c>
+      <c r="N213" t="str">
+        <v/>
+      </c>
+      <c r="O213" t="str">
+        <v/>
+      </c>
+      <c r="P213" t="str">
+        <v/>
+      </c>
+      <c r="Q213" t="str">
+        <v/>
+      </c>
+      <c r="R213" t="str">
+        <v/>
+      </c>
+      <c r="S213" t="str">
+        <v/>
+      </c>
+      <c r="T213" t="str">
+        <v/>
+      </c>
+      <c r="U213" t="str">
+        <v/>
+      </c>
+      <c r="V213" t="str">
+        <v/>
+      </c>
+      <c r="W213" t="str">
+        <v/>
+      </c>
+      <c r="X213" t="str">
+        <v/>
+      </c>
+      <c r="Y213" t="str">
+        <v/>
+      </c>
+      <c r="Z213" t="str">
+        <v/>
+      </c>
+      <c r="AA213" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>אגם בוחבוט - עשרים ואחת</v>
+      </c>
+      <c r="B214" t="str">
+        <v>2025  02:11-12-31</v>
+      </c>
+      <c r="C214" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D214" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E214" t="str">
+        <v/>
+      </c>
+      <c r="F214" t="str">
+        <v/>
+      </c>
+      <c r="G214" t="str">
+        <v/>
+      </c>
+      <c r="H214" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I214" t="str">
+        <v/>
+      </c>
+      <c r="J214" t="str">
+        <v/>
+      </c>
+      <c r="K214" t="str">
+        <v>אגם בוחבוט - עשרים ואחת</v>
+      </c>
+      <c r="L214" t="str">
+        <v/>
+      </c>
+      <c r="M214" t="str">
+        <v/>
+      </c>
+      <c r="N214" t="str">
+        <v/>
+      </c>
+      <c r="O214" t="str">
+        <v/>
+      </c>
+      <c r="P214" t="str">
+        <v/>
+      </c>
+      <c r="Q214" t="str">
+        <v/>
+      </c>
+      <c r="R214" t="str">
+        <v/>
+      </c>
+      <c r="S214" t="str">
+        <v/>
+      </c>
+      <c r="T214" t="str">
+        <v/>
+      </c>
+      <c r="U214" t="str">
+        <v/>
+      </c>
+      <c r="V214" t="str">
+        <v/>
+      </c>
+      <c r="W214" t="str">
+        <v/>
+      </c>
+      <c r="X214" t="str">
+        <v/>
+      </c>
+      <c r="Y214" t="str">
+        <v/>
+      </c>
+      <c r="Z214" t="str">
+        <v/>
+      </c>
+      <c r="AA214" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>רבקה זוהר - רסיסים של אור</v>
+      </c>
+      <c r="B215" t="str">
+        <v>2025  02:09-12-31</v>
+      </c>
+      <c r="C215" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D215" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E215" t="str">
+        <v/>
+      </c>
+      <c r="F215" t="str">
+        <v/>
+      </c>
+      <c r="G215" t="str">
+        <v/>
+      </c>
+      <c r="H215" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I215" t="str">
+        <v/>
+      </c>
+      <c r="J215" t="str">
+        <v/>
+      </c>
+      <c r="K215" t="str">
+        <v>רבקה זוהר - רסיסים של אור</v>
+      </c>
+      <c r="L215" t="str">
+        <v/>
+      </c>
+      <c r="M215" t="str">
+        <v/>
+      </c>
+      <c r="N215" t="str">
+        <v/>
+      </c>
+      <c r="O215" t="str">
+        <v/>
+      </c>
+      <c r="P215" t="str">
+        <v/>
+      </c>
+      <c r="Q215" t="str">
+        <v/>
+      </c>
+      <c r="R215" t="str">
+        <v/>
+      </c>
+      <c r="S215" t="str">
+        <v/>
+      </c>
+      <c r="T215" t="str">
+        <v/>
+      </c>
+      <c r="U215" t="str">
+        <v/>
+      </c>
+      <c r="V215" t="str">
+        <v/>
+      </c>
+      <c r="W215" t="str">
+        <v/>
+      </c>
+      <c r="X215" t="str">
+        <v/>
+      </c>
+      <c r="Y215" t="str">
+        <v/>
+      </c>
+      <c r="Z215" t="str">
+        <v/>
+      </c>
+      <c r="AA215" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
+      </c>
+      <c r="B216" t="str">
+        <v>2025  02:08-12-31</v>
+      </c>
+      <c r="C216" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D216" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E216" t="str">
+        <v/>
+      </c>
+      <c r="F216" t="str">
+        <v/>
+      </c>
+      <c r="G216" t="str">
+        <v/>
+      </c>
+      <c r="H216" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I216" t="str">
+        <v/>
+      </c>
+      <c r="J216" t="str">
+        <v/>
+      </c>
+      <c r="K216" t="str">
+        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
+      </c>
+      <c r="L216" t="str">
+        <v/>
+      </c>
+      <c r="M216" t="str">
+        <v/>
+      </c>
+      <c r="N216" t="str">
+        <v/>
+      </c>
+      <c r="O216" t="str">
+        <v/>
+      </c>
+      <c r="P216" t="str">
+        <v/>
+      </c>
+      <c r="Q216" t="str">
+        <v/>
+      </c>
+      <c r="R216" t="str">
+        <v/>
+      </c>
+      <c r="S216" t="str">
+        <v/>
+      </c>
+      <c r="T216" t="str">
+        <v/>
+      </c>
+      <c r="U216" t="str">
+        <v/>
+      </c>
+      <c r="V216" t="str">
+        <v/>
+      </c>
+      <c r="W216" t="str">
+        <v/>
+      </c>
+      <c r="X216" t="str">
+        <v/>
+      </c>
+      <c r="Y216" t="str">
+        <v/>
+      </c>
+      <c r="Z216" t="str">
+        <v/>
+      </c>
+      <c r="AA216" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
+      </c>
+      <c r="B217" t="str">
+        <v>2025  02:05-12-31</v>
+      </c>
+      <c r="C217" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D217" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E217" t="str">
+        <v/>
+      </c>
+      <c r="F217" t="str">
+        <v/>
+      </c>
+      <c r="G217" t="str">
+        <v/>
+      </c>
+      <c r="H217" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I217" t="str">
+        <v/>
+      </c>
+      <c r="J217" t="str">
+        <v/>
+      </c>
+      <c r="K217" t="str">
+        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
+      </c>
+      <c r="L217" t="str">
+        <v/>
+      </c>
+      <c r="M217" t="str">
+        <v/>
+      </c>
+      <c r="N217" t="str">
+        <v/>
+      </c>
+      <c r="O217" t="str">
+        <v/>
+      </c>
+      <c r="P217" t="str">
+        <v/>
+      </c>
+      <c r="Q217" t="str">
+        <v/>
+      </c>
+      <c r="R217" t="str">
+        <v/>
+      </c>
+      <c r="S217" t="str">
+        <v/>
+      </c>
+      <c r="T217" t="str">
+        <v/>
+      </c>
+      <c r="U217" t="str">
+        <v/>
+      </c>
+      <c r="V217" t="str">
+        <v/>
+      </c>
+      <c r="W217" t="str">
+        <v/>
+      </c>
+      <c r="X217" t="str">
+        <v/>
+      </c>
+      <c r="Y217" t="str">
+        <v/>
+      </c>
+      <c r="Z217" t="str">
+        <v/>
+      </c>
+      <c r="AA217" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>Imagine פסטיגל - שירי התחרות</v>
+      </c>
+      <c r="B218" t="str">
+        <v>2025  02:04-12-31</v>
+      </c>
+      <c r="C218" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D218" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E218" t="str">
+        <v/>
+      </c>
+      <c r="F218" t="str">
+        <v/>
+      </c>
+      <c r="G218" t="str">
+        <v/>
+      </c>
+      <c r="H218" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I218" t="str">
+        <v/>
+      </c>
+      <c r="J218" t="str">
+        <v/>
+      </c>
+      <c r="K218" t="str">
+        <v>Imagine פסטיגל - שירי התחרות</v>
+      </c>
+      <c r="L218" t="str">
+        <v/>
+      </c>
+      <c r="M218" t="str">
+        <v/>
+      </c>
+      <c r="N218" t="str">
+        <v/>
+      </c>
+      <c r="O218" t="str">
+        <v/>
+      </c>
+      <c r="P218" t="str">
+        <v/>
+      </c>
+      <c r="Q218" t="str">
+        <v/>
+      </c>
+      <c r="R218" t="str">
+        <v/>
+      </c>
+      <c r="S218" t="str">
+        <v/>
+      </c>
+      <c r="T218" t="str">
+        <v/>
+      </c>
+      <c r="U218" t="str">
+        <v/>
+      </c>
+      <c r="V218" t="str">
+        <v/>
+      </c>
+      <c r="W218" t="str">
+        <v/>
+      </c>
+      <c r="X218" t="str">
+        <v/>
+      </c>
+      <c r="Y218" t="str">
+        <v/>
+      </c>
+      <c r="Z218" t="str">
+        <v/>
+      </c>
+      <c r="AA218" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>השמחות - חובות אבודים</v>
+      </c>
+      <c r="B219" t="str">
+        <v>2025  02:02-12-31</v>
+      </c>
+      <c r="C219" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D219" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E219" t="str">
+        <v/>
+      </c>
+      <c r="F219" t="str">
+        <v/>
+      </c>
+      <c r="G219" t="str">
+        <v/>
+      </c>
+      <c r="H219" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I219" t="str">
+        <v/>
+      </c>
+      <c r="J219" t="str">
+        <v/>
+      </c>
+      <c r="K219" t="str">
+        <v>השמחות - חובות אבודים</v>
+      </c>
+      <c r="L219" t="str">
+        <v/>
+      </c>
+      <c r="M219" t="str">
+        <v/>
+      </c>
+      <c r="N219" t="str">
+        <v/>
+      </c>
+      <c r="O219" t="str">
+        <v/>
+      </c>
+      <c r="P219" t="str">
+        <v/>
+      </c>
+      <c r="Q219" t="str">
+        <v/>
+      </c>
+      <c r="R219" t="str">
+        <v/>
+      </c>
+      <c r="S219" t="str">
+        <v/>
+      </c>
+      <c r="T219" t="str">
+        <v/>
+      </c>
+      <c r="U219" t="str">
+        <v/>
+      </c>
+      <c r="V219" t="str">
+        <v/>
+      </c>
+      <c r="W219" t="str">
+        <v/>
+      </c>
+      <c r="X219" t="str">
+        <v/>
+      </c>
+      <c r="Y219" t="str">
+        <v/>
+      </c>
+      <c r="Z219" t="str">
+        <v/>
+      </c>
+      <c r="AA219" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>שלמה גרוניך - כמו כוכבים</v>
+      </c>
+      <c r="B220" t="str">
+        <v>2025  02:00-12-31</v>
+      </c>
+      <c r="C220" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D220" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E220" t="str">
+        <v/>
+      </c>
+      <c r="F220" t="str">
+        <v/>
+      </c>
+      <c r="G220" t="str">
+        <v/>
+      </c>
+      <c r="H220" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I220" t="str">
+        <v/>
+      </c>
+      <c r="J220" t="str">
+        <v/>
+      </c>
+      <c r="K220" t="str">
+        <v>שלמה גרוניך - כמו כוכבים</v>
+      </c>
+      <c r="L220" t="str">
+        <v/>
+      </c>
+      <c r="M220" t="str">
+        <v/>
+      </c>
+      <c r="N220" t="str">
+        <v/>
+      </c>
+      <c r="O220" t="str">
+        <v/>
+      </c>
+      <c r="P220" t="str">
+        <v/>
+      </c>
+      <c r="Q220" t="str">
+        <v/>
+      </c>
+      <c r="R220" t="str">
+        <v/>
+      </c>
+      <c r="S220" t="str">
+        <v/>
+      </c>
+      <c r="T220" t="str">
+        <v/>
+      </c>
+      <c r="U220" t="str">
+        <v/>
+      </c>
+      <c r="V220" t="str">
+        <v/>
+      </c>
+      <c r="W220" t="str">
+        <v/>
+      </c>
+      <c r="X220" t="str">
+        <v/>
+      </c>
+      <c r="Y220" t="str">
+        <v/>
+      </c>
+      <c r="Z220" t="str">
+        <v/>
+      </c>
+      <c r="AA220" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>יוני רועה - מפוזרים</v>
+      </c>
+      <c r="B221" t="str">
+        <v>2025  01:56-12-31</v>
+      </c>
+      <c r="C221" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D221" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E221" t="str">
+        <v/>
+      </c>
+      <c r="F221" t="str">
+        <v/>
+      </c>
+      <c r="G221" t="str">
+        <v/>
+      </c>
+      <c r="H221" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I221" t="str">
+        <v/>
+      </c>
+      <c r="J221" t="str">
+        <v/>
+      </c>
+      <c r="K221" t="str">
+        <v>יוני רועה - מפוזרים</v>
+      </c>
+      <c r="L221" t="str">
+        <v/>
+      </c>
+      <c r="M221" t="str">
+        <v/>
+      </c>
+      <c r="N221" t="str">
+        <v/>
+      </c>
+      <c r="O221" t="str">
+        <v/>
+      </c>
+      <c r="P221" t="str">
+        <v/>
+      </c>
+      <c r="Q221" t="str">
+        <v/>
+      </c>
+      <c r="R221" t="str">
+        <v/>
+      </c>
+      <c r="S221" t="str">
+        <v/>
+      </c>
+      <c r="T221" t="str">
+        <v/>
+      </c>
+      <c r="U221" t="str">
+        <v/>
+      </c>
+      <c r="V221" t="str">
+        <v/>
+      </c>
+      <c r="W221" t="str">
+        <v/>
+      </c>
+      <c r="X221" t="str">
+        <v/>
+      </c>
+      <c r="Y221" t="str">
+        <v/>
+      </c>
+      <c r="Z221" t="str">
+        <v/>
+      </c>
+      <c r="AA221" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:W177"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AA221"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA221"/>
+  <dimension ref="A1:AE265"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -12257,7 +12257,7 @@
         <v>עדן בן זקן - רולקס וקסקט</v>
       </c>
       <c r="B208" t="str">
-        <v>2026  08:41-01-14</v>
+        <v>2026  08:41-01-14 | מאת</v>
       </c>
       <c r="C208" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24436&amp;forum=music&amp;viewmode=all</v>
@@ -12340,7 +12340,7 @@
         <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
       </c>
       <c r="B209" t="str">
-        <v>2026  08:40-01-14</v>
+        <v>2026  08:40-01-14 | מאת</v>
       </c>
       <c r="C209" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24439&amp;forum=music&amp;viewmode=all</v>
@@ -12423,7 +12423,7 @@
         <v>אייל גולן - בית מפואר</v>
       </c>
       <c r="B210" t="str">
-        <v>2025  02:18-12-31</v>
+        <v>2025  02:18-12-31 | מאת</v>
       </c>
       <c r="C210" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
@@ -12506,7 +12506,7 @@
         <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
       </c>
       <c r="B211" t="str">
-        <v>2025  02:16-12-31</v>
+        <v>2025  02:16-12-31 | מאת</v>
       </c>
       <c r="C211" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
@@ -12589,7 +12589,7 @@
         <v>שיר לוי - ילד מוזר</v>
       </c>
       <c r="B212" t="str">
-        <v>2025  02:14-12-31</v>
+        <v>2025  02:14-12-31 | מאת</v>
       </c>
       <c r="C212" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
@@ -12672,7 +12672,7 @@
         <v>פיטר רוט - 50</v>
       </c>
       <c r="B213" t="str">
-        <v>2025  02:13-12-31</v>
+        <v>2025  02:13-12-31 | מאת</v>
       </c>
       <c r="C213" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
@@ -12755,7 +12755,7 @@
         <v>אגם בוחבוט - עשרים ואחת</v>
       </c>
       <c r="B214" t="str">
-        <v>2025  02:11-12-31</v>
+        <v>2025  02:11-12-31 | מאת</v>
       </c>
       <c r="C214" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
@@ -12838,7 +12838,7 @@
         <v>רבקה זוהר - רסיסים של אור</v>
       </c>
       <c r="B215" t="str">
-        <v>2025  02:09-12-31</v>
+        <v>2025  02:09-12-31 | מאת</v>
       </c>
       <c r="C215" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
@@ -12921,7 +12921,7 @@
         <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
       </c>
       <c r="B216" t="str">
-        <v>2025  02:08-12-31</v>
+        <v>2025  02:08-12-31 | מאת</v>
       </c>
       <c r="C216" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
@@ -13004,7 +13004,7 @@
         <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
       </c>
       <c r="B217" t="str">
-        <v>2025  02:05-12-31</v>
+        <v>2025  02:05-12-31 | מאת</v>
       </c>
       <c r="C217" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
@@ -13087,7 +13087,7 @@
         <v>Imagine פסטיגל - שירי התחרות</v>
       </c>
       <c r="B218" t="str">
-        <v>2025  02:04-12-31</v>
+        <v>2025  02:04-12-31 | מאת</v>
       </c>
       <c r="C218" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
@@ -13170,7 +13170,7 @@
         <v>השמחות - חובות אבודים</v>
       </c>
       <c r="B219" t="str">
-        <v>2025  02:02-12-31</v>
+        <v>2025  02:02-12-31 | מאת</v>
       </c>
       <c r="C219" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
@@ -13253,7 +13253,7 @@
         <v>שלמה גרוניך - כמו כוכבים</v>
       </c>
       <c r="B220" t="str">
-        <v>2025  02:00-12-31</v>
+        <v>2025  02:00-12-31 | מאת</v>
       </c>
       <c r="C220" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
@@ -13336,7 +13336,7 @@
         <v>יוני רועה - מפוזרים</v>
       </c>
       <c r="B221" t="str">
-        <v>2025  01:56-12-31</v>
+        <v>2025  01:56-12-31 | מאת</v>
       </c>
       <c r="C221" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
@@ -13414,9 +13414,4189 @@
         <v/>
       </c>
     </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>פטריק סבג Hotel Mogador</v>
+      </c>
+      <c r="B222" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C222" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
+      </c>
+      <c r="D222" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E222" t="str">
+        <v>האלבום של פטריק סבג אינו אוסף שירים אקראי, אלא מרחב. מקום לשהות בו.  נכנסים, שומעים, ויוצאים קצת אחרים. הבחירה בשם "הוטל מוגדור” היא כבר הצהרה. מלון = מקום מעבר, לא בית קבוע, מוגדור = עיר נמל, תנועה, ערבוב תרבויות. כך</v>
+      </c>
+      <c r="F222" t="str">
+        <v/>
+      </c>
+      <c r="G222" t="str">
+        <v/>
+      </c>
+      <c r="H222" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I222" t="str">
+        <v/>
+      </c>
+      <c r="J222" t="str">
+        <v/>
+      </c>
+      <c r="K222" t="str">
+        <v>פטריק סבג Hotel Mogador</v>
+      </c>
+      <c r="L222" t="str">
+        <v/>
+      </c>
+      <c r="M222" t="str">
+        <v/>
+      </c>
+      <c r="N222" t="str">
+        <v/>
+      </c>
+      <c r="O222" t="str">
+        <v/>
+      </c>
+      <c r="P222" t="str">
+        <v/>
+      </c>
+      <c r="Q222" t="str">
+        <v/>
+      </c>
+      <c r="R222" t="str">
+        <v/>
+      </c>
+      <c r="S222" t="str">
+        <v/>
+      </c>
+      <c r="T222" t="str">
+        <v/>
+      </c>
+      <c r="U222" t="str">
+        <v/>
+      </c>
+      <c r="V222" t="str">
+        <v/>
+      </c>
+      <c r="W222" t="str">
+        <v/>
+      </c>
+      <c r="X222" t="str">
+        <v/>
+      </c>
+      <c r="Y222" t="str">
+        <v/>
+      </c>
+      <c r="Z222" t="str">
+        <v/>
+      </c>
+      <c r="AA222" t="str">
+        <v/>
+      </c>
+      <c r="AB222" t="str">
+        <v/>
+      </c>
+      <c r="AC222" t="str">
+        <v/>
+      </c>
+      <c r="AD222" t="str">
+        <v/>
+      </c>
+      <c r="AE222" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
+      </c>
+      <c r="B223" t="str">
+        <v>2026-01-09</v>
+      </c>
+      <c r="C223" t="str">
+        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
+      </c>
+      <c r="D223" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E223" t="str">
+        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
+      </c>
+      <c r="F223" t="str">
+        <v/>
+      </c>
+      <c r="G223" t="str">
+        <v/>
+      </c>
+      <c r="H223" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I223" t="str">
+        <v/>
+      </c>
+      <c r="J223" t="str">
+        <v/>
+      </c>
+      <c r="K223" t="str">
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
+      </c>
+      <c r="L223" t="str">
+        <v/>
+      </c>
+      <c r="M223" t="str">
+        <v/>
+      </c>
+      <c r="N223" t="str">
+        <v/>
+      </c>
+      <c r="O223" t="str">
+        <v/>
+      </c>
+      <c r="P223" t="str">
+        <v/>
+      </c>
+      <c r="Q223" t="str">
+        <v/>
+      </c>
+      <c r="R223" t="str">
+        <v/>
+      </c>
+      <c r="S223" t="str">
+        <v/>
+      </c>
+      <c r="T223" t="str">
+        <v/>
+      </c>
+      <c r="U223" t="str">
+        <v/>
+      </c>
+      <c r="V223" t="str">
+        <v/>
+      </c>
+      <c r="W223" t="str">
+        <v/>
+      </c>
+      <c r="X223" t="str">
+        <v/>
+      </c>
+      <c r="Y223" t="str">
+        <v/>
+      </c>
+      <c r="Z223" t="str">
+        <v/>
+      </c>
+      <c r="AA223" t="str">
+        <v/>
+      </c>
+      <c r="AB223" t="str">
+        <v/>
+      </c>
+      <c r="AC223" t="str">
+        <v/>
+      </c>
+      <c r="AD223" t="str">
+        <v/>
+      </c>
+      <c r="AE223" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>אוליביה דין The Art of Loving</v>
+      </c>
+      <c r="B224" t="str">
+        <v>2026-01-04</v>
+      </c>
+      <c r="C224" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
+      </c>
+      <c r="D224" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E224" t="str">
+        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
+      </c>
+      <c r="F224" t="str">
+        <v/>
+      </c>
+      <c r="G224" t="str">
+        <v/>
+      </c>
+      <c r="H224" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I224" t="str">
+        <v/>
+      </c>
+      <c r="J224" t="str">
+        <v/>
+      </c>
+      <c r="K224" t="str">
+        <v>אוליביה דין The Art of Loving</v>
+      </c>
+      <c r="L224" t="str">
+        <v/>
+      </c>
+      <c r="M224" t="str">
+        <v/>
+      </c>
+      <c r="N224" t="str">
+        <v/>
+      </c>
+      <c r="O224" t="str">
+        <v/>
+      </c>
+      <c r="P224" t="str">
+        <v/>
+      </c>
+      <c r="Q224" t="str">
+        <v/>
+      </c>
+      <c r="R224" t="str">
+        <v/>
+      </c>
+      <c r="S224" t="str">
+        <v/>
+      </c>
+      <c r="T224" t="str">
+        <v/>
+      </c>
+      <c r="U224" t="str">
+        <v/>
+      </c>
+      <c r="V224" t="str">
+        <v/>
+      </c>
+      <c r="W224" t="str">
+        <v/>
+      </c>
+      <c r="X224" t="str">
+        <v/>
+      </c>
+      <c r="Y224" t="str">
+        <v/>
+      </c>
+      <c r="Z224" t="str">
+        <v/>
+      </c>
+      <c r="AA224" t="str">
+        <v/>
+      </c>
+      <c r="AB224" t="str">
+        <v/>
+      </c>
+      <c r="AC224" t="str">
+        <v/>
+      </c>
+      <c r="AD224" t="str">
+        <v/>
+      </c>
+      <c r="AE224" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>Geese Getting Killed</v>
+      </c>
+      <c r="B225" t="str">
+        <v>2025-12-29</v>
+      </c>
+      <c r="C225" t="str">
+        <v>https://yosmusic.com/geese-getting-killed/</v>
+      </c>
+      <c r="D225" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E225" t="str">
+        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
+      </c>
+      <c r="F225" t="str">
+        <v/>
+      </c>
+      <c r="G225" t="str">
+        <v/>
+      </c>
+      <c r="H225" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I225" t="str">
+        <v/>
+      </c>
+      <c r="J225" t="str">
+        <v/>
+      </c>
+      <c r="K225" t="str">
+        <v>Geese Getting Killed</v>
+      </c>
+      <c r="L225" t="str">
+        <v/>
+      </c>
+      <c r="M225" t="str">
+        <v/>
+      </c>
+      <c r="N225" t="str">
+        <v/>
+      </c>
+      <c r="O225" t="str">
+        <v/>
+      </c>
+      <c r="P225" t="str">
+        <v/>
+      </c>
+      <c r="Q225" t="str">
+        <v/>
+      </c>
+      <c r="R225" t="str">
+        <v/>
+      </c>
+      <c r="S225" t="str">
+        <v/>
+      </c>
+      <c r="T225" t="str">
+        <v/>
+      </c>
+      <c r="U225" t="str">
+        <v/>
+      </c>
+      <c r="V225" t="str">
+        <v/>
+      </c>
+      <c r="W225" t="str">
+        <v/>
+      </c>
+      <c r="X225" t="str">
+        <v/>
+      </c>
+      <c r="Y225" t="str">
+        <v/>
+      </c>
+      <c r="Z225" t="str">
+        <v/>
+      </c>
+      <c r="AA225" t="str">
+        <v/>
+      </c>
+      <c r="AB225" t="str">
+        <v/>
+      </c>
+      <c r="AC225" t="str">
+        <v/>
+      </c>
+      <c r="AD225" t="str">
+        <v/>
+      </c>
+      <c r="AE225" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>רוסליה Lux</v>
+      </c>
+      <c r="B226" t="str">
+        <v>2025-12-25</v>
+      </c>
+      <c r="C226" t="str">
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
+      </c>
+      <c r="D226" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E226" t="str">
+        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
+      </c>
+      <c r="F226" t="str">
+        <v/>
+      </c>
+      <c r="G226" t="str">
+        <v/>
+      </c>
+      <c r="H226" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I226" t="str">
+        <v/>
+      </c>
+      <c r="J226" t="str">
+        <v/>
+      </c>
+      <c r="K226" t="str">
+        <v>רוסליה Lux</v>
+      </c>
+      <c r="L226" t="str">
+        <v/>
+      </c>
+      <c r="M226" t="str">
+        <v/>
+      </c>
+      <c r="N226" t="str">
+        <v/>
+      </c>
+      <c r="O226" t="str">
+        <v/>
+      </c>
+      <c r="P226" t="str">
+        <v/>
+      </c>
+      <c r="Q226" t="str">
+        <v/>
+      </c>
+      <c r="R226" t="str">
+        <v/>
+      </c>
+      <c r="S226" t="str">
+        <v/>
+      </c>
+      <c r="T226" t="str">
+        <v/>
+      </c>
+      <c r="U226" t="str">
+        <v/>
+      </c>
+      <c r="V226" t="str">
+        <v/>
+      </c>
+      <c r="W226" t="str">
+        <v/>
+      </c>
+      <c r="X226" t="str">
+        <v/>
+      </c>
+      <c r="Y226" t="str">
+        <v/>
+      </c>
+      <c r="Z226" t="str">
+        <v/>
+      </c>
+      <c r="AA226" t="str">
+        <v/>
+      </c>
+      <c r="AB226" t="str">
+        <v/>
+      </c>
+      <c r="AC226" t="str">
+        <v/>
+      </c>
+      <c r="AD226" t="str">
+        <v/>
+      </c>
+      <c r="AE226" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>יאנגבלאד אירוסמית' one more time</v>
+      </c>
+      <c r="B227" t="str">
+        <v>2025-12-17</v>
+      </c>
+      <c r="C227" t="str">
+        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
+      </c>
+      <c r="D227" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E227" t="str">
+        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
+      </c>
+      <c r="F227" t="str">
+        <v/>
+      </c>
+      <c r="G227" t="str">
+        <v/>
+      </c>
+      <c r="H227" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I227" t="str">
+        <v/>
+      </c>
+      <c r="J227" t="str">
+        <v/>
+      </c>
+      <c r="K227" t="str">
+        <v>יאנגבלאד אירוסמית' one more time</v>
+      </c>
+      <c r="L227" t="str">
+        <v/>
+      </c>
+      <c r="M227" t="str">
+        <v/>
+      </c>
+      <c r="N227" t="str">
+        <v/>
+      </c>
+      <c r="O227" t="str">
+        <v/>
+      </c>
+      <c r="P227" t="str">
+        <v/>
+      </c>
+      <c r="Q227" t="str">
+        <v/>
+      </c>
+      <c r="R227" t="str">
+        <v/>
+      </c>
+      <c r="S227" t="str">
+        <v/>
+      </c>
+      <c r="T227" t="str">
+        <v/>
+      </c>
+      <c r="U227" t="str">
+        <v/>
+      </c>
+      <c r="V227" t="str">
+        <v/>
+      </c>
+      <c r="W227" t="str">
+        <v/>
+      </c>
+      <c r="X227" t="str">
+        <v/>
+      </c>
+      <c r="Y227" t="str">
+        <v/>
+      </c>
+      <c r="Z227" t="str">
+        <v/>
+      </c>
+      <c r="AA227" t="str">
+        <v/>
+      </c>
+      <c r="AB227" t="str">
+        <v/>
+      </c>
+      <c r="AC227" t="str">
+        <v/>
+      </c>
+      <c r="AD227" t="str">
+        <v/>
+      </c>
+      <c r="AE227" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>פינק פלויד Wish You Were Here 50</v>
+      </c>
+      <c r="B228" t="str">
+        <v>2025-12-14</v>
+      </c>
+      <c r="C228" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
+      </c>
+      <c r="D228" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E228" t="str">
+        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
+      </c>
+      <c r="F228" t="str">
+        <v/>
+      </c>
+      <c r="G228" t="str">
+        <v/>
+      </c>
+      <c r="H228" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I228" t="str">
+        <v/>
+      </c>
+      <c r="J228" t="str">
+        <v/>
+      </c>
+      <c r="K228" t="str">
+        <v>פינק פלויד Wish You Were Here 50</v>
+      </c>
+      <c r="L228" t="str">
+        <v/>
+      </c>
+      <c r="M228" t="str">
+        <v/>
+      </c>
+      <c r="N228" t="str">
+        <v/>
+      </c>
+      <c r="O228" t="str">
+        <v/>
+      </c>
+      <c r="P228" t="str">
+        <v/>
+      </c>
+      <c r="Q228" t="str">
+        <v/>
+      </c>
+      <c r="R228" t="str">
+        <v/>
+      </c>
+      <c r="S228" t="str">
+        <v/>
+      </c>
+      <c r="T228" t="str">
+        <v/>
+      </c>
+      <c r="U228" t="str">
+        <v/>
+      </c>
+      <c r="V228" t="str">
+        <v/>
+      </c>
+      <c r="W228" t="str">
+        <v/>
+      </c>
+      <c r="X228" t="str">
+        <v/>
+      </c>
+      <c r="Y228" t="str">
+        <v/>
+      </c>
+      <c r="Z228" t="str">
+        <v/>
+      </c>
+      <c r="AA228" t="str">
+        <v/>
+      </c>
+      <c r="AB228" t="str">
+        <v/>
+      </c>
+      <c r="AC228" t="str">
+        <v/>
+      </c>
+      <c r="AD228" t="str">
+        <v/>
+      </c>
+      <c r="AE228" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+      </c>
+      <c r="B229" t="str">
+        <v>2025-12-08</v>
+      </c>
+      <c r="C229" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
+      </c>
+      <c r="D229" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E229" t="str">
+        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
+      </c>
+      <c r="F229" t="str">
+        <v/>
+      </c>
+      <c r="G229" t="str">
+        <v/>
+      </c>
+      <c r="H229" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I229" t="str">
+        <v/>
+      </c>
+      <c r="J229" t="str">
+        <v/>
+      </c>
+      <c r="K229" t="str">
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+      </c>
+      <c r="L229" t="str">
+        <v/>
+      </c>
+      <c r="M229" t="str">
+        <v/>
+      </c>
+      <c r="N229" t="str">
+        <v/>
+      </c>
+      <c r="O229" t="str">
+        <v/>
+      </c>
+      <c r="P229" t="str">
+        <v/>
+      </c>
+      <c r="Q229" t="str">
+        <v/>
+      </c>
+      <c r="R229" t="str">
+        <v/>
+      </c>
+      <c r="S229" t="str">
+        <v/>
+      </c>
+      <c r="T229" t="str">
+        <v/>
+      </c>
+      <c r="U229" t="str">
+        <v/>
+      </c>
+      <c r="V229" t="str">
+        <v/>
+      </c>
+      <c r="W229" t="str">
+        <v/>
+      </c>
+      <c r="X229" t="str">
+        <v/>
+      </c>
+      <c r="Y229" t="str">
+        <v/>
+      </c>
+      <c r="Z229" t="str">
+        <v/>
+      </c>
+      <c r="AA229" t="str">
+        <v/>
+      </c>
+      <c r="AB229" t="str">
+        <v/>
+      </c>
+      <c r="AC229" t="str">
+        <v/>
+      </c>
+      <c r="AD229" t="str">
+        <v/>
+      </c>
+      <c r="AE229" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>סטריי קידס DO IT EP</v>
+      </c>
+      <c r="B230" t="str">
+        <v>2025-12-04</v>
+      </c>
+      <c r="C230" t="str">
+        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
+      </c>
+      <c r="D230" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E230" t="str">
+        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
+      </c>
+      <c r="F230" t="str">
+        <v/>
+      </c>
+      <c r="G230" t="str">
+        <v/>
+      </c>
+      <c r="H230" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I230" t="str">
+        <v/>
+      </c>
+      <c r="J230" t="str">
+        <v/>
+      </c>
+      <c r="K230" t="str">
+        <v>סטריי קידס DO IT EP</v>
+      </c>
+      <c r="L230" t="str">
+        <v/>
+      </c>
+      <c r="M230" t="str">
+        <v/>
+      </c>
+      <c r="N230" t="str">
+        <v/>
+      </c>
+      <c r="O230" t="str">
+        <v/>
+      </c>
+      <c r="P230" t="str">
+        <v/>
+      </c>
+      <c r="Q230" t="str">
+        <v/>
+      </c>
+      <c r="R230" t="str">
+        <v/>
+      </c>
+      <c r="S230" t="str">
+        <v/>
+      </c>
+      <c r="T230" t="str">
+        <v/>
+      </c>
+      <c r="U230" t="str">
+        <v/>
+      </c>
+      <c r="V230" t="str">
+        <v/>
+      </c>
+      <c r="W230" t="str">
+        <v/>
+      </c>
+      <c r="X230" t="str">
+        <v/>
+      </c>
+      <c r="Y230" t="str">
+        <v/>
+      </c>
+      <c r="Z230" t="str">
+        <v/>
+      </c>
+      <c r="AA230" t="str">
+        <v/>
+      </c>
+      <c r="AB230" t="str">
+        <v/>
+      </c>
+      <c r="AC230" t="str">
+        <v/>
+      </c>
+      <c r="AD230" t="str">
+        <v/>
+      </c>
+      <c r="AE230" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>דויד ברוזה BROZAJAZZ</v>
+      </c>
+      <c r="B231" t="str">
+        <v>2025-11-30</v>
+      </c>
+      <c r="C231" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
+      </c>
+      <c r="D231" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E231" t="str">
+        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
+      </c>
+      <c r="F231" t="str">
+        <v/>
+      </c>
+      <c r="G231" t="str">
+        <v/>
+      </c>
+      <c r="H231" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I231" t="str">
+        <v/>
+      </c>
+      <c r="J231" t="str">
+        <v/>
+      </c>
+      <c r="K231" t="str">
+        <v>דויד ברוזה BROZAJAZZ</v>
+      </c>
+      <c r="L231" t="str">
+        <v/>
+      </c>
+      <c r="M231" t="str">
+        <v/>
+      </c>
+      <c r="N231" t="str">
+        <v/>
+      </c>
+      <c r="O231" t="str">
+        <v/>
+      </c>
+      <c r="P231" t="str">
+        <v/>
+      </c>
+      <c r="Q231" t="str">
+        <v/>
+      </c>
+      <c r="R231" t="str">
+        <v/>
+      </c>
+      <c r="S231" t="str">
+        <v/>
+      </c>
+      <c r="T231" t="str">
+        <v/>
+      </c>
+      <c r="U231" t="str">
+        <v/>
+      </c>
+      <c r="V231" t="str">
+        <v/>
+      </c>
+      <c r="W231" t="str">
+        <v/>
+      </c>
+      <c r="X231" t="str">
+        <v/>
+      </c>
+      <c r="Y231" t="str">
+        <v/>
+      </c>
+      <c r="Z231" t="str">
+        <v/>
+      </c>
+      <c r="AA231" t="str">
+        <v/>
+      </c>
+      <c r="AB231" t="str">
+        <v/>
+      </c>
+      <c r="AC231" t="str">
+        <v/>
+      </c>
+      <c r="AD231" t="str">
+        <v/>
+      </c>
+      <c r="AE231" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>Five Seconds of Summer – Everyone's A Star</v>
+      </c>
+      <c r="B232" t="str">
+        <v>2025-11-24</v>
+      </c>
+      <c r="C232" t="str">
+        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
+      </c>
+      <c r="D232" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E232" t="str">
+        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
+      </c>
+      <c r="F232" t="str">
+        <v/>
+      </c>
+      <c r="G232" t="str">
+        <v/>
+      </c>
+      <c r="H232" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I232" t="str">
+        <v/>
+      </c>
+      <c r="J232" t="str">
+        <v/>
+      </c>
+      <c r="K232" t="str">
+        <v>Five Seconds of Summer – Everyone's A Star</v>
+      </c>
+      <c r="L232" t="str">
+        <v/>
+      </c>
+      <c r="M232" t="str">
+        <v/>
+      </c>
+      <c r="N232" t="str">
+        <v/>
+      </c>
+      <c r="O232" t="str">
+        <v/>
+      </c>
+      <c r="P232" t="str">
+        <v/>
+      </c>
+      <c r="Q232" t="str">
+        <v/>
+      </c>
+      <c r="R232" t="str">
+        <v/>
+      </c>
+      <c r="S232" t="str">
+        <v/>
+      </c>
+      <c r="T232" t="str">
+        <v/>
+      </c>
+      <c r="U232" t="str">
+        <v/>
+      </c>
+      <c r="V232" t="str">
+        <v/>
+      </c>
+      <c r="W232" t="str">
+        <v/>
+      </c>
+      <c r="X232" t="str">
+        <v/>
+      </c>
+      <c r="Y232" t="str">
+        <v/>
+      </c>
+      <c r="Z232" t="str">
+        <v/>
+      </c>
+      <c r="AA232" t="str">
+        <v/>
+      </c>
+      <c r="AB232" t="str">
+        <v/>
+      </c>
+      <c r="AC232" t="str">
+        <v/>
+      </c>
+      <c r="AD232" t="str">
+        <v/>
+      </c>
+      <c r="AE232" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>התקווה 6 – ויהי אור</v>
+      </c>
+      <c r="B233" t="str">
+        <v>2025-11-20</v>
+      </c>
+      <c r="C233" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
+      </c>
+      <c r="D233" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E233" t="str">
+        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
+      </c>
+      <c r="F233" t="str">
+        <v/>
+      </c>
+      <c r="G233" t="str">
+        <v/>
+      </c>
+      <c r="H233" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I233" t="str">
+        <v/>
+      </c>
+      <c r="J233" t="str">
+        <v/>
+      </c>
+      <c r="K233" t="str">
+        <v>התקווה 6 – ויהי אור</v>
+      </c>
+      <c r="L233" t="str">
+        <v/>
+      </c>
+      <c r="M233" t="str">
+        <v/>
+      </c>
+      <c r="N233" t="str">
+        <v/>
+      </c>
+      <c r="O233" t="str">
+        <v/>
+      </c>
+      <c r="P233" t="str">
+        <v/>
+      </c>
+      <c r="Q233" t="str">
+        <v/>
+      </c>
+      <c r="R233" t="str">
+        <v/>
+      </c>
+      <c r="S233" t="str">
+        <v/>
+      </c>
+      <c r="T233" t="str">
+        <v/>
+      </c>
+      <c r="U233" t="str">
+        <v/>
+      </c>
+      <c r="V233" t="str">
+        <v/>
+      </c>
+      <c r="W233" t="str">
+        <v/>
+      </c>
+      <c r="X233" t="str">
+        <v/>
+      </c>
+      <c r="Y233" t="str">
+        <v/>
+      </c>
+      <c r="Z233" t="str">
+        <v/>
+      </c>
+      <c r="AA233" t="str">
+        <v/>
+      </c>
+      <c r="AB233" t="str">
+        <v/>
+      </c>
+      <c r="AC233" t="str">
+        <v/>
+      </c>
+      <c r="AD233" t="str">
+        <v/>
+      </c>
+      <c r="AE233" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>פלורנס אנד דה משין Everybody Scream</v>
+      </c>
+      <c r="B234" t="str">
+        <v>2025-11-13</v>
+      </c>
+      <c r="C234" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
+      </c>
+      <c r="D234" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E234" t="str">
+        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
+      </c>
+      <c r="F234" t="str">
+        <v/>
+      </c>
+      <c r="G234" t="str">
+        <v/>
+      </c>
+      <c r="H234" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I234" t="str">
+        <v/>
+      </c>
+      <c r="J234" t="str">
+        <v/>
+      </c>
+      <c r="K234" t="str">
+        <v>פלורנס אנד דה משין Everybody Scream</v>
+      </c>
+      <c r="L234" t="str">
+        <v/>
+      </c>
+      <c r="M234" t="str">
+        <v/>
+      </c>
+      <c r="N234" t="str">
+        <v/>
+      </c>
+      <c r="O234" t="str">
+        <v/>
+      </c>
+      <c r="P234" t="str">
+        <v/>
+      </c>
+      <c r="Q234" t="str">
+        <v/>
+      </c>
+      <c r="R234" t="str">
+        <v/>
+      </c>
+      <c r="S234" t="str">
+        <v/>
+      </c>
+      <c r="T234" t="str">
+        <v/>
+      </c>
+      <c r="U234" t="str">
+        <v/>
+      </c>
+      <c r="V234" t="str">
+        <v/>
+      </c>
+      <c r="W234" t="str">
+        <v/>
+      </c>
+      <c r="X234" t="str">
+        <v/>
+      </c>
+      <c r="Y234" t="str">
+        <v/>
+      </c>
+      <c r="Z234" t="str">
+        <v/>
+      </c>
+      <c r="AA234" t="str">
+        <v/>
+      </c>
+      <c r="AB234" t="str">
+        <v/>
+      </c>
+      <c r="AC234" t="str">
+        <v/>
+      </c>
+      <c r="AD234" t="str">
+        <v/>
+      </c>
+      <c r="AE234" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>טיים אימפלה Deadbeat</v>
+      </c>
+      <c r="B235" t="str">
+        <v>2025-11-03</v>
+      </c>
+      <c r="C235" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
+      </c>
+      <c r="D235" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E235" t="str">
+        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
+      </c>
+      <c r="F235" t="str">
+        <v/>
+      </c>
+      <c r="G235" t="str">
+        <v/>
+      </c>
+      <c r="H235" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I235" t="str">
+        <v/>
+      </c>
+      <c r="J235" t="str">
+        <v/>
+      </c>
+      <c r="K235" t="str">
+        <v>טיים אימפלה Deadbeat</v>
+      </c>
+      <c r="L235" t="str">
+        <v/>
+      </c>
+      <c r="M235" t="str">
+        <v/>
+      </c>
+      <c r="N235" t="str">
+        <v/>
+      </c>
+      <c r="O235" t="str">
+        <v/>
+      </c>
+      <c r="P235" t="str">
+        <v/>
+      </c>
+      <c r="Q235" t="str">
+        <v/>
+      </c>
+      <c r="R235" t="str">
+        <v/>
+      </c>
+      <c r="S235" t="str">
+        <v/>
+      </c>
+      <c r="T235" t="str">
+        <v/>
+      </c>
+      <c r="U235" t="str">
+        <v/>
+      </c>
+      <c r="V235" t="str">
+        <v/>
+      </c>
+      <c r="W235" t="str">
+        <v/>
+      </c>
+      <c r="X235" t="str">
+        <v/>
+      </c>
+      <c r="Y235" t="str">
+        <v/>
+      </c>
+      <c r="Z235" t="str">
+        <v/>
+      </c>
+      <c r="AA235" t="str">
+        <v/>
+      </c>
+      <c r="AB235" t="str">
+        <v/>
+      </c>
+      <c r="AC235" t="str">
+        <v/>
+      </c>
+      <c r="AD235" t="str">
+        <v/>
+      </c>
+      <c r="AE235" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+      </c>
+      <c r="B236" t="str">
+        <v>2025-10-20</v>
+      </c>
+      <c r="C236" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
+      </c>
+      <c r="D236" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E236" t="str">
+        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
+      </c>
+      <c r="F236" t="str">
+        <v/>
+      </c>
+      <c r="G236" t="str">
+        <v/>
+      </c>
+      <c r="H236" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I236" t="str">
+        <v/>
+      </c>
+      <c r="J236" t="str">
+        <v/>
+      </c>
+      <c r="K236" t="str">
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+      </c>
+      <c r="L236" t="str">
+        <v/>
+      </c>
+      <c r="M236" t="str">
+        <v/>
+      </c>
+      <c r="N236" t="str">
+        <v/>
+      </c>
+      <c r="O236" t="str">
+        <v/>
+      </c>
+      <c r="P236" t="str">
+        <v/>
+      </c>
+      <c r="Q236" t="str">
+        <v/>
+      </c>
+      <c r="R236" t="str">
+        <v/>
+      </c>
+      <c r="S236" t="str">
+        <v/>
+      </c>
+      <c r="T236" t="str">
+        <v/>
+      </c>
+      <c r="U236" t="str">
+        <v/>
+      </c>
+      <c r="V236" t="str">
+        <v/>
+      </c>
+      <c r="W236" t="str">
+        <v/>
+      </c>
+      <c r="X236" t="str">
+        <v/>
+      </c>
+      <c r="Y236" t="str">
+        <v/>
+      </c>
+      <c r="Z236" t="str">
+        <v/>
+      </c>
+      <c r="AA236" t="str">
+        <v/>
+      </c>
+      <c r="AB236" t="str">
+        <v/>
+      </c>
+      <c r="AC236" t="str">
+        <v/>
+      </c>
+      <c r="AD236" t="str">
+        <v/>
+      </c>
+      <c r="AE236" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>שלמה גרוניך – תודה אהבה</v>
+      </c>
+      <c r="B237" t="str">
+        <v>2025-10-18</v>
+      </c>
+      <c r="C237" t="str">
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
+      </c>
+      <c r="D237" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E237" t="str">
+        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
+      </c>
+      <c r="F237" t="str">
+        <v/>
+      </c>
+      <c r="G237" t="str">
+        <v/>
+      </c>
+      <c r="H237" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I237" t="str">
+        <v/>
+      </c>
+      <c r="J237" t="str">
+        <v/>
+      </c>
+      <c r="K237" t="str">
+        <v>שלמה גרוניך – תודה אהבה</v>
+      </c>
+      <c r="L237" t="str">
+        <v/>
+      </c>
+      <c r="M237" t="str">
+        <v/>
+      </c>
+      <c r="N237" t="str">
+        <v/>
+      </c>
+      <c r="O237" t="str">
+        <v/>
+      </c>
+      <c r="P237" t="str">
+        <v/>
+      </c>
+      <c r="Q237" t="str">
+        <v/>
+      </c>
+      <c r="R237" t="str">
+        <v/>
+      </c>
+      <c r="S237" t="str">
+        <v/>
+      </c>
+      <c r="T237" t="str">
+        <v/>
+      </c>
+      <c r="U237" t="str">
+        <v/>
+      </c>
+      <c r="V237" t="str">
+        <v/>
+      </c>
+      <c r="W237" t="str">
+        <v/>
+      </c>
+      <c r="X237" t="str">
+        <v/>
+      </c>
+      <c r="Y237" t="str">
+        <v/>
+      </c>
+      <c r="Z237" t="str">
+        <v/>
+      </c>
+      <c r="AA237" t="str">
+        <v/>
+      </c>
+      <c r="AB237" t="str">
+        <v/>
+      </c>
+      <c r="AC237" t="str">
+        <v/>
+      </c>
+      <c r="AD237" t="str">
+        <v/>
+      </c>
+      <c r="AE237" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
+      </c>
+      <c r="B238" t="str">
+        <v>2025-10-11</v>
+      </c>
+      <c r="C238" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
+      </c>
+      <c r="D238" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E238" t="str">
+        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
+      </c>
+      <c r="F238" t="str">
+        <v/>
+      </c>
+      <c r="G238" t="str">
+        <v/>
+      </c>
+      <c r="H238" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I238" t="str">
+        <v/>
+      </c>
+      <c r="J238" t="str">
+        <v/>
+      </c>
+      <c r="K238" t="str">
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
+      </c>
+      <c r="L238" t="str">
+        <v/>
+      </c>
+      <c r="M238" t="str">
+        <v/>
+      </c>
+      <c r="N238" t="str">
+        <v/>
+      </c>
+      <c r="O238" t="str">
+        <v/>
+      </c>
+      <c r="P238" t="str">
+        <v/>
+      </c>
+      <c r="Q238" t="str">
+        <v/>
+      </c>
+      <c r="R238" t="str">
+        <v/>
+      </c>
+      <c r="S238" t="str">
+        <v/>
+      </c>
+      <c r="T238" t="str">
+        <v/>
+      </c>
+      <c r="U238" t="str">
+        <v/>
+      </c>
+      <c r="V238" t="str">
+        <v/>
+      </c>
+      <c r="W238" t="str">
+        <v/>
+      </c>
+      <c r="X238" t="str">
+        <v/>
+      </c>
+      <c r="Y238" t="str">
+        <v/>
+      </c>
+      <c r="Z238" t="str">
+        <v/>
+      </c>
+      <c r="AA238" t="str">
+        <v/>
+      </c>
+      <c r="AB238" t="str">
+        <v/>
+      </c>
+      <c r="AC238" t="str">
+        <v/>
+      </c>
+      <c r="AD238" t="str">
+        <v/>
+      </c>
+      <c r="AE238" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>דוג'ה קאט Vie</v>
+      </c>
+      <c r="B239" t="str">
+        <v>2025-10-04</v>
+      </c>
+      <c r="C239" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
+      </c>
+      <c r="D239" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E239" t="str">
+        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
+      </c>
+      <c r="F239" t="str">
+        <v/>
+      </c>
+      <c r="G239" t="str">
+        <v/>
+      </c>
+      <c r="H239" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I239" t="str">
+        <v/>
+      </c>
+      <c r="J239" t="str">
+        <v/>
+      </c>
+      <c r="K239" t="str">
+        <v>דוג'ה קאט Vie</v>
+      </c>
+      <c r="L239" t="str">
+        <v/>
+      </c>
+      <c r="M239" t="str">
+        <v/>
+      </c>
+      <c r="N239" t="str">
+        <v/>
+      </c>
+      <c r="O239" t="str">
+        <v/>
+      </c>
+      <c r="P239" t="str">
+        <v/>
+      </c>
+      <c r="Q239" t="str">
+        <v/>
+      </c>
+      <c r="R239" t="str">
+        <v/>
+      </c>
+      <c r="S239" t="str">
+        <v/>
+      </c>
+      <c r="T239" t="str">
+        <v/>
+      </c>
+      <c r="U239" t="str">
+        <v/>
+      </c>
+      <c r="V239" t="str">
+        <v/>
+      </c>
+      <c r="W239" t="str">
+        <v/>
+      </c>
+      <c r="X239" t="str">
+        <v/>
+      </c>
+      <c r="Y239" t="str">
+        <v/>
+      </c>
+      <c r="Z239" t="str">
+        <v/>
+      </c>
+      <c r="AA239" t="str">
+        <v/>
+      </c>
+      <c r="AB239" t="str">
+        <v/>
+      </c>
+      <c r="AC239" t="str">
+        <v/>
+      </c>
+      <c r="AD239" t="str">
+        <v/>
+      </c>
+      <c r="AE239" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>ג'וי קרוקס Juniper</v>
+      </c>
+      <c r="B240" t="str">
+        <v>2025-10-03</v>
+      </c>
+      <c r="C240" t="str">
+        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
+      </c>
+      <c r="D240" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E240" t="str">
+        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
+      </c>
+      <c r="F240" t="str">
+        <v/>
+      </c>
+      <c r="G240" t="str">
+        <v/>
+      </c>
+      <c r="H240" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I240" t="str">
+        <v/>
+      </c>
+      <c r="J240" t="str">
+        <v/>
+      </c>
+      <c r="K240" t="str">
+        <v>ג'וי קרוקס Juniper</v>
+      </c>
+      <c r="L240" t="str">
+        <v/>
+      </c>
+      <c r="M240" t="str">
+        <v/>
+      </c>
+      <c r="N240" t="str">
+        <v/>
+      </c>
+      <c r="O240" t="str">
+        <v/>
+      </c>
+      <c r="P240" t="str">
+        <v/>
+      </c>
+      <c r="Q240" t="str">
+        <v/>
+      </c>
+      <c r="R240" t="str">
+        <v/>
+      </c>
+      <c r="S240" t="str">
+        <v/>
+      </c>
+      <c r="T240" t="str">
+        <v/>
+      </c>
+      <c r="U240" t="str">
+        <v/>
+      </c>
+      <c r="V240" t="str">
+        <v/>
+      </c>
+      <c r="W240" t="str">
+        <v/>
+      </c>
+      <c r="X240" t="str">
+        <v/>
+      </c>
+      <c r="Y240" t="str">
+        <v/>
+      </c>
+      <c r="Z240" t="str">
+        <v/>
+      </c>
+      <c r="AA240" t="str">
+        <v/>
+      </c>
+      <c r="AB240" t="str">
+        <v/>
+      </c>
+      <c r="AC240" t="str">
+        <v/>
+      </c>
+      <c r="AD240" t="str">
+        <v/>
+      </c>
+      <c r="AE240" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>ביפי קליירו Futique</v>
+      </c>
+      <c r="B241" t="str">
+        <v>2025-09-30</v>
+      </c>
+      <c r="C241" t="str">
+        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
+      </c>
+      <c r="D241" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E241" t="str">
+        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
+      </c>
+      <c r="F241" t="str">
+        <v/>
+      </c>
+      <c r="G241" t="str">
+        <v/>
+      </c>
+      <c r="H241" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I241" t="str">
+        <v/>
+      </c>
+      <c r="J241" t="str">
+        <v/>
+      </c>
+      <c r="K241" t="str">
+        <v>ביפי קליירו Futique</v>
+      </c>
+      <c r="L241" t="str">
+        <v/>
+      </c>
+      <c r="M241" t="str">
+        <v/>
+      </c>
+      <c r="N241" t="str">
+        <v/>
+      </c>
+      <c r="O241" t="str">
+        <v/>
+      </c>
+      <c r="P241" t="str">
+        <v/>
+      </c>
+      <c r="Q241" t="str">
+        <v/>
+      </c>
+      <c r="R241" t="str">
+        <v/>
+      </c>
+      <c r="S241" t="str">
+        <v/>
+      </c>
+      <c r="T241" t="str">
+        <v/>
+      </c>
+      <c r="U241" t="str">
+        <v/>
+      </c>
+      <c r="V241" t="str">
+        <v/>
+      </c>
+      <c r="W241" t="str">
+        <v/>
+      </c>
+      <c r="X241" t="str">
+        <v/>
+      </c>
+      <c r="Y241" t="str">
+        <v/>
+      </c>
+      <c r="Z241" t="str">
+        <v/>
+      </c>
+      <c r="AA241" t="str">
+        <v/>
+      </c>
+      <c r="AB241" t="str">
+        <v/>
+      </c>
+      <c r="AC241" t="str">
+        <v/>
+      </c>
+      <c r="AD241" t="str">
+        <v/>
+      </c>
+      <c r="AE241" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>אד שירן Play</v>
+      </c>
+      <c r="B242" t="str">
+        <v>2025-09-24</v>
+      </c>
+      <c r="C242" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
+      </c>
+      <c r="D242" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E242" t="str">
+        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
+      </c>
+      <c r="F242" t="str">
+        <v/>
+      </c>
+      <c r="G242" t="str">
+        <v/>
+      </c>
+      <c r="H242" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I242" t="str">
+        <v/>
+      </c>
+      <c r="J242" t="str">
+        <v/>
+      </c>
+      <c r="K242" t="str">
+        <v>אד שירן Play</v>
+      </c>
+      <c r="L242" t="str">
+        <v/>
+      </c>
+      <c r="M242" t="str">
+        <v/>
+      </c>
+      <c r="N242" t="str">
+        <v/>
+      </c>
+      <c r="O242" t="str">
+        <v/>
+      </c>
+      <c r="P242" t="str">
+        <v/>
+      </c>
+      <c r="Q242" t="str">
+        <v/>
+      </c>
+      <c r="R242" t="str">
+        <v/>
+      </c>
+      <c r="S242" t="str">
+        <v/>
+      </c>
+      <c r="T242" t="str">
+        <v/>
+      </c>
+      <c r="U242" t="str">
+        <v/>
+      </c>
+      <c r="V242" t="str">
+        <v/>
+      </c>
+      <c r="W242" t="str">
+        <v/>
+      </c>
+      <c r="X242" t="str">
+        <v/>
+      </c>
+      <c r="Y242" t="str">
+        <v/>
+      </c>
+      <c r="Z242" t="str">
+        <v/>
+      </c>
+      <c r="AA242" t="str">
+        <v/>
+      </c>
+      <c r="AB242" t="str">
+        <v/>
+      </c>
+      <c r="AC242" t="str">
+        <v/>
+      </c>
+      <c r="AD242" t="str">
+        <v/>
+      </c>
+      <c r="AE242" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+      </c>
+      <c r="B243" t="str">
+        <v>2025-09-21</v>
+      </c>
+      <c r="C243" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
+      </c>
+      <c r="D243" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E243" t="str">
+        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
+      </c>
+      <c r="F243" t="str">
+        <v/>
+      </c>
+      <c r="G243" t="str">
+        <v/>
+      </c>
+      <c r="H243" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I243" t="str">
+        <v/>
+      </c>
+      <c r="J243" t="str">
+        <v/>
+      </c>
+      <c r="K243" t="str">
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+      </c>
+      <c r="L243" t="str">
+        <v/>
+      </c>
+      <c r="M243" t="str">
+        <v/>
+      </c>
+      <c r="N243" t="str">
+        <v/>
+      </c>
+      <c r="O243" t="str">
+        <v/>
+      </c>
+      <c r="P243" t="str">
+        <v/>
+      </c>
+      <c r="Q243" t="str">
+        <v/>
+      </c>
+      <c r="R243" t="str">
+        <v/>
+      </c>
+      <c r="S243" t="str">
+        <v/>
+      </c>
+      <c r="T243" t="str">
+        <v/>
+      </c>
+      <c r="U243" t="str">
+        <v/>
+      </c>
+      <c r="V243" t="str">
+        <v/>
+      </c>
+      <c r="W243" t="str">
+        <v/>
+      </c>
+      <c r="X243" t="str">
+        <v/>
+      </c>
+      <c r="Y243" t="str">
+        <v/>
+      </c>
+      <c r="Z243" t="str">
+        <v/>
+      </c>
+      <c r="AA243" t="str">
+        <v/>
+      </c>
+      <c r="AB243" t="str">
+        <v/>
+      </c>
+      <c r="AC243" t="str">
+        <v/>
+      </c>
+      <c r="AD243" t="str">
+        <v/>
+      </c>
+      <c r="AE243" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>סוויד Antidepressants</v>
+      </c>
+      <c r="B244" t="str">
+        <v>2025-09-12</v>
+      </c>
+      <c r="C244" t="str">
+        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
+      </c>
+      <c r="D244" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E244" t="str">
+        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
+      </c>
+      <c r="F244" t="str">
+        <v/>
+      </c>
+      <c r="G244" t="str">
+        <v/>
+      </c>
+      <c r="H244" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I244" t="str">
+        <v/>
+      </c>
+      <c r="J244" t="str">
+        <v/>
+      </c>
+      <c r="K244" t="str">
+        <v>סוויד Antidepressants</v>
+      </c>
+      <c r="L244" t="str">
+        <v/>
+      </c>
+      <c r="M244" t="str">
+        <v/>
+      </c>
+      <c r="N244" t="str">
+        <v/>
+      </c>
+      <c r="O244" t="str">
+        <v/>
+      </c>
+      <c r="P244" t="str">
+        <v/>
+      </c>
+      <c r="Q244" t="str">
+        <v/>
+      </c>
+      <c r="R244" t="str">
+        <v/>
+      </c>
+      <c r="S244" t="str">
+        <v/>
+      </c>
+      <c r="T244" t="str">
+        <v/>
+      </c>
+      <c r="U244" t="str">
+        <v/>
+      </c>
+      <c r="V244" t="str">
+        <v/>
+      </c>
+      <c r="W244" t="str">
+        <v/>
+      </c>
+      <c r="X244" t="str">
+        <v/>
+      </c>
+      <c r="Y244" t="str">
+        <v/>
+      </c>
+      <c r="Z244" t="str">
+        <v/>
+      </c>
+      <c r="AA244" t="str">
+        <v/>
+      </c>
+      <c r="AB244" t="str">
+        <v/>
+      </c>
+      <c r="AC244" t="str">
+        <v/>
+      </c>
+      <c r="AD244" t="str">
+        <v/>
+      </c>
+      <c r="AE244" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>וולף אליס The Clearing</v>
+      </c>
+      <c r="B245" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="C245" t="str">
+        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
+      </c>
+      <c r="D245" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E245" t="str">
+        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
+      </c>
+      <c r="F245" t="str">
+        <v/>
+      </c>
+      <c r="G245" t="str">
+        <v/>
+      </c>
+      <c r="H245" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I245" t="str">
+        <v/>
+      </c>
+      <c r="J245" t="str">
+        <v/>
+      </c>
+      <c r="K245" t="str">
+        <v>וולף אליס The Clearing</v>
+      </c>
+      <c r="L245" t="str">
+        <v/>
+      </c>
+      <c r="M245" t="str">
+        <v/>
+      </c>
+      <c r="N245" t="str">
+        <v/>
+      </c>
+      <c r="O245" t="str">
+        <v/>
+      </c>
+      <c r="P245" t="str">
+        <v/>
+      </c>
+      <c r="Q245" t="str">
+        <v/>
+      </c>
+      <c r="R245" t="str">
+        <v/>
+      </c>
+      <c r="S245" t="str">
+        <v/>
+      </c>
+      <c r="T245" t="str">
+        <v/>
+      </c>
+      <c r="U245" t="str">
+        <v/>
+      </c>
+      <c r="V245" t="str">
+        <v/>
+      </c>
+      <c r="W245" t="str">
+        <v/>
+      </c>
+      <c r="X245" t="str">
+        <v/>
+      </c>
+      <c r="Y245" t="str">
+        <v/>
+      </c>
+      <c r="Z245" t="str">
+        <v/>
+      </c>
+      <c r="AA245" t="str">
+        <v/>
+      </c>
+      <c r="AB245" t="str">
+        <v/>
+      </c>
+      <c r="AC245" t="str">
+        <v/>
+      </c>
+      <c r="AD245" t="str">
+        <v/>
+      </c>
+      <c r="AE245" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+      </c>
+      <c r="B246" t="str">
+        <v>2025-08-29</v>
+      </c>
+      <c r="C246" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
+      </c>
+      <c r="D246" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E246" t="str">
+        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
+      </c>
+      <c r="F246" t="str">
+        <v/>
+      </c>
+      <c r="G246" t="str">
+        <v/>
+      </c>
+      <c r="H246" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I246" t="str">
+        <v/>
+      </c>
+      <c r="J246" t="str">
+        <v/>
+      </c>
+      <c r="K246" t="str">
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+      </c>
+      <c r="L246" t="str">
+        <v/>
+      </c>
+      <c r="M246" t="str">
+        <v/>
+      </c>
+      <c r="N246" t="str">
+        <v/>
+      </c>
+      <c r="O246" t="str">
+        <v/>
+      </c>
+      <c r="P246" t="str">
+        <v/>
+      </c>
+      <c r="Q246" t="str">
+        <v/>
+      </c>
+      <c r="R246" t="str">
+        <v/>
+      </c>
+      <c r="S246" t="str">
+        <v/>
+      </c>
+      <c r="T246" t="str">
+        <v/>
+      </c>
+      <c r="U246" t="str">
+        <v/>
+      </c>
+      <c r="V246" t="str">
+        <v/>
+      </c>
+      <c r="W246" t="str">
+        <v/>
+      </c>
+      <c r="X246" t="str">
+        <v/>
+      </c>
+      <c r="Y246" t="str">
+        <v/>
+      </c>
+      <c r="Z246" t="str">
+        <v/>
+      </c>
+      <c r="AA246" t="str">
+        <v/>
+      </c>
+      <c r="AB246" t="str">
+        <v/>
+      </c>
+      <c r="AC246" t="str">
+        <v/>
+      </c>
+      <c r="AD246" t="str">
+        <v/>
+      </c>
+      <c r="AE246" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+      </c>
+      <c r="B247" t="str">
+        <v>2025-08-24</v>
+      </c>
+      <c r="C247" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
+      </c>
+      <c r="D247" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E247" t="str">
+        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
+      </c>
+      <c r="F247" t="str">
+        <v/>
+      </c>
+      <c r="G247" t="str">
+        <v/>
+      </c>
+      <c r="H247" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I247" t="str">
+        <v/>
+      </c>
+      <c r="J247" t="str">
+        <v/>
+      </c>
+      <c r="K247" t="str">
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+      </c>
+      <c r="L247" t="str">
+        <v/>
+      </c>
+      <c r="M247" t="str">
+        <v/>
+      </c>
+      <c r="N247" t="str">
+        <v/>
+      </c>
+      <c r="O247" t="str">
+        <v/>
+      </c>
+      <c r="P247" t="str">
+        <v/>
+      </c>
+      <c r="Q247" t="str">
+        <v/>
+      </c>
+      <c r="R247" t="str">
+        <v/>
+      </c>
+      <c r="S247" t="str">
+        <v/>
+      </c>
+      <c r="T247" t="str">
+        <v/>
+      </c>
+      <c r="U247" t="str">
+        <v/>
+      </c>
+      <c r="V247" t="str">
+        <v/>
+      </c>
+      <c r="W247" t="str">
+        <v/>
+      </c>
+      <c r="X247" t="str">
+        <v/>
+      </c>
+      <c r="Y247" t="str">
+        <v/>
+      </c>
+      <c r="Z247" t="str">
+        <v/>
+      </c>
+      <c r="AA247" t="str">
+        <v/>
+      </c>
+      <c r="AB247" t="str">
+        <v/>
+      </c>
+      <c r="AC247" t="str">
+        <v/>
+      </c>
+      <c r="AD247" t="str">
+        <v/>
+      </c>
+      <c r="AE247" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+      </c>
+      <c r="B248" t="str">
+        <v>2025-08-21</v>
+      </c>
+      <c r="C248" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
+      </c>
+      <c r="D248" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E248" t="str">
+        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
+      </c>
+      <c r="F248" t="str">
+        <v/>
+      </c>
+      <c r="G248" t="str">
+        <v/>
+      </c>
+      <c r="H248" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I248" t="str">
+        <v/>
+      </c>
+      <c r="J248" t="str">
+        <v/>
+      </c>
+      <c r="K248" t="str">
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+      </c>
+      <c r="L248" t="str">
+        <v/>
+      </c>
+      <c r="M248" t="str">
+        <v/>
+      </c>
+      <c r="N248" t="str">
+        <v/>
+      </c>
+      <c r="O248" t="str">
+        <v/>
+      </c>
+      <c r="P248" t="str">
+        <v/>
+      </c>
+      <c r="Q248" t="str">
+        <v/>
+      </c>
+      <c r="R248" t="str">
+        <v/>
+      </c>
+      <c r="S248" t="str">
+        <v/>
+      </c>
+      <c r="T248" t="str">
+        <v/>
+      </c>
+      <c r="U248" t="str">
+        <v/>
+      </c>
+      <c r="V248" t="str">
+        <v/>
+      </c>
+      <c r="W248" t="str">
+        <v/>
+      </c>
+      <c r="X248" t="str">
+        <v/>
+      </c>
+      <c r="Y248" t="str">
+        <v/>
+      </c>
+      <c r="Z248" t="str">
+        <v/>
+      </c>
+      <c r="AA248" t="str">
+        <v/>
+      </c>
+      <c r="AB248" t="str">
+        <v/>
+      </c>
+      <c r="AC248" t="str">
+        <v/>
+      </c>
+      <c r="AD248" t="str">
+        <v/>
+      </c>
+      <c r="AE248" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>אברהם טל – חי</v>
+      </c>
+      <c r="B249" t="str">
+        <v>2025-08-17</v>
+      </c>
+      <c r="C249" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
+      </c>
+      <c r="D249" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E249" t="str">
+        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
+      </c>
+      <c r="F249" t="str">
+        <v/>
+      </c>
+      <c r="G249" t="str">
+        <v/>
+      </c>
+      <c r="H249" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I249" t="str">
+        <v/>
+      </c>
+      <c r="J249" t="str">
+        <v/>
+      </c>
+      <c r="K249" t="str">
+        <v>אברהם טל – חי</v>
+      </c>
+      <c r="L249" t="str">
+        <v/>
+      </c>
+      <c r="M249" t="str">
+        <v/>
+      </c>
+      <c r="N249" t="str">
+        <v/>
+      </c>
+      <c r="O249" t="str">
+        <v/>
+      </c>
+      <c r="P249" t="str">
+        <v/>
+      </c>
+      <c r="Q249" t="str">
+        <v/>
+      </c>
+      <c r="R249" t="str">
+        <v/>
+      </c>
+      <c r="S249" t="str">
+        <v/>
+      </c>
+      <c r="T249" t="str">
+        <v/>
+      </c>
+      <c r="U249" t="str">
+        <v/>
+      </c>
+      <c r="V249" t="str">
+        <v/>
+      </c>
+      <c r="W249" t="str">
+        <v/>
+      </c>
+      <c r="X249" t="str">
+        <v/>
+      </c>
+      <c r="Y249" t="str">
+        <v/>
+      </c>
+      <c r="Z249" t="str">
+        <v/>
+      </c>
+      <c r="AA249" t="str">
+        <v/>
+      </c>
+      <c r="AB249" t="str">
+        <v/>
+      </c>
+      <c r="AC249" t="str">
+        <v/>
+      </c>
+      <c r="AD249" t="str">
+        <v/>
+      </c>
+      <c r="AE249" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>רנה ראפ Bite Me</v>
+      </c>
+      <c r="B250" t="str">
+        <v>2025-08-12</v>
+      </c>
+      <c r="C250" t="str">
+        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
+      </c>
+      <c r="D250" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E250" t="str">
+        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
+      </c>
+      <c r="F250" t="str">
+        <v/>
+      </c>
+      <c r="G250" t="str">
+        <v/>
+      </c>
+      <c r="H250" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I250" t="str">
+        <v/>
+      </c>
+      <c r="J250" t="str">
+        <v/>
+      </c>
+      <c r="K250" t="str">
+        <v>רנה ראפ Bite Me</v>
+      </c>
+      <c r="L250" t="str">
+        <v/>
+      </c>
+      <c r="M250" t="str">
+        <v/>
+      </c>
+      <c r="N250" t="str">
+        <v/>
+      </c>
+      <c r="O250" t="str">
+        <v/>
+      </c>
+      <c r="P250" t="str">
+        <v/>
+      </c>
+      <c r="Q250" t="str">
+        <v/>
+      </c>
+      <c r="R250" t="str">
+        <v/>
+      </c>
+      <c r="S250" t="str">
+        <v/>
+      </c>
+      <c r="T250" t="str">
+        <v/>
+      </c>
+      <c r="U250" t="str">
+        <v/>
+      </c>
+      <c r="V250" t="str">
+        <v/>
+      </c>
+      <c r="W250" t="str">
+        <v/>
+      </c>
+      <c r="X250" t="str">
+        <v/>
+      </c>
+      <c r="Y250" t="str">
+        <v/>
+      </c>
+      <c r="Z250" t="str">
+        <v/>
+      </c>
+      <c r="AA250" t="str">
+        <v/>
+      </c>
+      <c r="AB250" t="str">
+        <v/>
+      </c>
+      <c r="AC250" t="str">
+        <v/>
+      </c>
+      <c r="AD250" t="str">
+        <v/>
+      </c>
+      <c r="AE250" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>The K's – Pretty On The Internet</v>
+      </c>
+      <c r="B251" t="str">
+        <v>2025-08-03</v>
+      </c>
+      <c r="C251" t="str">
+        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
+      </c>
+      <c r="D251" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E251" t="str">
+        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
+      </c>
+      <c r="F251" t="str">
+        <v/>
+      </c>
+      <c r="G251" t="str">
+        <v/>
+      </c>
+      <c r="H251" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I251" t="str">
+        <v/>
+      </c>
+      <c r="J251" t="str">
+        <v/>
+      </c>
+      <c r="K251" t="str">
+        <v>The K's – Pretty On The Internet</v>
+      </c>
+      <c r="L251" t="str">
+        <v/>
+      </c>
+      <c r="M251" t="str">
+        <v/>
+      </c>
+      <c r="N251" t="str">
+        <v/>
+      </c>
+      <c r="O251" t="str">
+        <v/>
+      </c>
+      <c r="P251" t="str">
+        <v/>
+      </c>
+      <c r="Q251" t="str">
+        <v/>
+      </c>
+      <c r="R251" t="str">
+        <v/>
+      </c>
+      <c r="S251" t="str">
+        <v/>
+      </c>
+      <c r="T251" t="str">
+        <v/>
+      </c>
+      <c r="U251" t="str">
+        <v/>
+      </c>
+      <c r="V251" t="str">
+        <v/>
+      </c>
+      <c r="W251" t="str">
+        <v/>
+      </c>
+      <c r="X251" t="str">
+        <v/>
+      </c>
+      <c r="Y251" t="str">
+        <v/>
+      </c>
+      <c r="Z251" t="str">
+        <v/>
+      </c>
+      <c r="AA251" t="str">
+        <v/>
+      </c>
+      <c r="AB251" t="str">
+        <v/>
+      </c>
+      <c r="AC251" t="str">
+        <v/>
+      </c>
+      <c r="AD251" t="str">
+        <v/>
+      </c>
+      <c r="AE251" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>עדן בן זקן - רולקס וקסקט</v>
+      </c>
+      <c r="B252" t="str">
+        <v>2026  08:41-01-14</v>
+      </c>
+      <c r="C252" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24436&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D252" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E252" t="str">
+        <v/>
+      </c>
+      <c r="F252" t="str">
+        <v/>
+      </c>
+      <c r="G252" t="str">
+        <v/>
+      </c>
+      <c r="H252" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I252" t="str">
+        <v/>
+      </c>
+      <c r="J252" t="str">
+        <v/>
+      </c>
+      <c r="K252" t="str">
+        <v>עדן בן זקן - רולקס וקסקט</v>
+      </c>
+      <c r="L252" t="str">
+        <v/>
+      </c>
+      <c r="M252" t="str">
+        <v/>
+      </c>
+      <c r="N252" t="str">
+        <v/>
+      </c>
+      <c r="O252" t="str">
+        <v/>
+      </c>
+      <c r="P252" t="str">
+        <v/>
+      </c>
+      <c r="Q252" t="str">
+        <v/>
+      </c>
+      <c r="R252" t="str">
+        <v/>
+      </c>
+      <c r="S252" t="str">
+        <v/>
+      </c>
+      <c r="T252" t="str">
+        <v/>
+      </c>
+      <c r="U252" t="str">
+        <v/>
+      </c>
+      <c r="V252" t="str">
+        <v/>
+      </c>
+      <c r="W252" t="str">
+        <v/>
+      </c>
+      <c r="X252" t="str">
+        <v/>
+      </c>
+      <c r="Y252" t="str">
+        <v/>
+      </c>
+      <c r="Z252" t="str">
+        <v/>
+      </c>
+      <c r="AA252" t="str">
+        <v/>
+      </c>
+      <c r="AB252" t="str">
+        <v/>
+      </c>
+      <c r="AC252" t="str">
+        <v/>
+      </c>
+      <c r="AD252" t="str">
+        <v/>
+      </c>
+      <c r="AE252" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
+      </c>
+      <c r="B253" t="str">
+        <v>2026  08:40-01-14</v>
+      </c>
+      <c r="C253" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24439&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D253" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E253" t="str">
+        <v/>
+      </c>
+      <c r="F253" t="str">
+        <v/>
+      </c>
+      <c r="G253" t="str">
+        <v/>
+      </c>
+      <c r="H253" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I253" t="str">
+        <v/>
+      </c>
+      <c r="J253" t="str">
+        <v/>
+      </c>
+      <c r="K253" t="str">
+        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
+      </c>
+      <c r="L253" t="str">
+        <v/>
+      </c>
+      <c r="M253" t="str">
+        <v/>
+      </c>
+      <c r="N253" t="str">
+        <v/>
+      </c>
+      <c r="O253" t="str">
+        <v/>
+      </c>
+      <c r="P253" t="str">
+        <v/>
+      </c>
+      <c r="Q253" t="str">
+        <v/>
+      </c>
+      <c r="R253" t="str">
+        <v/>
+      </c>
+      <c r="S253" t="str">
+        <v/>
+      </c>
+      <c r="T253" t="str">
+        <v/>
+      </c>
+      <c r="U253" t="str">
+        <v/>
+      </c>
+      <c r="V253" t="str">
+        <v/>
+      </c>
+      <c r="W253" t="str">
+        <v/>
+      </c>
+      <c r="X253" t="str">
+        <v/>
+      </c>
+      <c r="Y253" t="str">
+        <v/>
+      </c>
+      <c r="Z253" t="str">
+        <v/>
+      </c>
+      <c r="AA253" t="str">
+        <v/>
+      </c>
+      <c r="AB253" t="str">
+        <v/>
+      </c>
+      <c r="AC253" t="str">
+        <v/>
+      </c>
+      <c r="AD253" t="str">
+        <v/>
+      </c>
+      <c r="AE253" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>אייל גולן - בית מפואר</v>
+      </c>
+      <c r="B254" t="str">
+        <v>2025  02:18-12-31</v>
+      </c>
+      <c r="C254" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D254" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E254" t="str">
+        <v/>
+      </c>
+      <c r="F254" t="str">
+        <v/>
+      </c>
+      <c r="G254" t="str">
+        <v/>
+      </c>
+      <c r="H254" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I254" t="str">
+        <v/>
+      </c>
+      <c r="J254" t="str">
+        <v/>
+      </c>
+      <c r="K254" t="str">
+        <v>אייל גולן - בית מפואר</v>
+      </c>
+      <c r="L254" t="str">
+        <v/>
+      </c>
+      <c r="M254" t="str">
+        <v/>
+      </c>
+      <c r="N254" t="str">
+        <v/>
+      </c>
+      <c r="O254" t="str">
+        <v/>
+      </c>
+      <c r="P254" t="str">
+        <v/>
+      </c>
+      <c r="Q254" t="str">
+        <v/>
+      </c>
+      <c r="R254" t="str">
+        <v/>
+      </c>
+      <c r="S254" t="str">
+        <v/>
+      </c>
+      <c r="T254" t="str">
+        <v/>
+      </c>
+      <c r="U254" t="str">
+        <v/>
+      </c>
+      <c r="V254" t="str">
+        <v/>
+      </c>
+      <c r="W254" t="str">
+        <v/>
+      </c>
+      <c r="X254" t="str">
+        <v/>
+      </c>
+      <c r="Y254" t="str">
+        <v/>
+      </c>
+      <c r="Z254" t="str">
+        <v/>
+      </c>
+      <c r="AA254" t="str">
+        <v/>
+      </c>
+      <c r="AB254" t="str">
+        <v/>
+      </c>
+      <c r="AC254" t="str">
+        <v/>
+      </c>
+      <c r="AD254" t="str">
+        <v/>
+      </c>
+      <c r="AE254" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
+      </c>
+      <c r="B255" t="str">
+        <v>2025  02:16-12-31</v>
+      </c>
+      <c r="C255" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D255" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E255" t="str">
+        <v/>
+      </c>
+      <c r="F255" t="str">
+        <v/>
+      </c>
+      <c r="G255" t="str">
+        <v/>
+      </c>
+      <c r="H255" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I255" t="str">
+        <v/>
+      </c>
+      <c r="J255" t="str">
+        <v/>
+      </c>
+      <c r="K255" t="str">
+        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
+      </c>
+      <c r="L255" t="str">
+        <v/>
+      </c>
+      <c r="M255" t="str">
+        <v/>
+      </c>
+      <c r="N255" t="str">
+        <v/>
+      </c>
+      <c r="O255" t="str">
+        <v/>
+      </c>
+      <c r="P255" t="str">
+        <v/>
+      </c>
+      <c r="Q255" t="str">
+        <v/>
+      </c>
+      <c r="R255" t="str">
+        <v/>
+      </c>
+      <c r="S255" t="str">
+        <v/>
+      </c>
+      <c r="T255" t="str">
+        <v/>
+      </c>
+      <c r="U255" t="str">
+        <v/>
+      </c>
+      <c r="V255" t="str">
+        <v/>
+      </c>
+      <c r="W255" t="str">
+        <v/>
+      </c>
+      <c r="X255" t="str">
+        <v/>
+      </c>
+      <c r="Y255" t="str">
+        <v/>
+      </c>
+      <c r="Z255" t="str">
+        <v/>
+      </c>
+      <c r="AA255" t="str">
+        <v/>
+      </c>
+      <c r="AB255" t="str">
+        <v/>
+      </c>
+      <c r="AC255" t="str">
+        <v/>
+      </c>
+      <c r="AD255" t="str">
+        <v/>
+      </c>
+      <c r="AE255" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>שיר לוי - ילד מוזר</v>
+      </c>
+      <c r="B256" t="str">
+        <v>2025  02:14-12-31</v>
+      </c>
+      <c r="C256" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D256" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E256" t="str">
+        <v/>
+      </c>
+      <c r="F256" t="str">
+        <v/>
+      </c>
+      <c r="G256" t="str">
+        <v/>
+      </c>
+      <c r="H256" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I256" t="str">
+        <v/>
+      </c>
+      <c r="J256" t="str">
+        <v/>
+      </c>
+      <c r="K256" t="str">
+        <v>שיר לוי - ילד מוזר</v>
+      </c>
+      <c r="L256" t="str">
+        <v/>
+      </c>
+      <c r="M256" t="str">
+        <v/>
+      </c>
+      <c r="N256" t="str">
+        <v/>
+      </c>
+      <c r="O256" t="str">
+        <v/>
+      </c>
+      <c r="P256" t="str">
+        <v/>
+      </c>
+      <c r="Q256" t="str">
+        <v/>
+      </c>
+      <c r="R256" t="str">
+        <v/>
+      </c>
+      <c r="S256" t="str">
+        <v/>
+      </c>
+      <c r="T256" t="str">
+        <v/>
+      </c>
+      <c r="U256" t="str">
+        <v/>
+      </c>
+      <c r="V256" t="str">
+        <v/>
+      </c>
+      <c r="W256" t="str">
+        <v/>
+      </c>
+      <c r="X256" t="str">
+        <v/>
+      </c>
+      <c r="Y256" t="str">
+        <v/>
+      </c>
+      <c r="Z256" t="str">
+        <v/>
+      </c>
+      <c r="AA256" t="str">
+        <v/>
+      </c>
+      <c r="AB256" t="str">
+        <v/>
+      </c>
+      <c r="AC256" t="str">
+        <v/>
+      </c>
+      <c r="AD256" t="str">
+        <v/>
+      </c>
+      <c r="AE256" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>פיטר רוט - 50</v>
+      </c>
+      <c r="B257" t="str">
+        <v>2025  02:13-12-31</v>
+      </c>
+      <c r="C257" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D257" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E257" t="str">
+        <v/>
+      </c>
+      <c r="F257" t="str">
+        <v/>
+      </c>
+      <c r="G257" t="str">
+        <v/>
+      </c>
+      <c r="H257" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I257" t="str">
+        <v/>
+      </c>
+      <c r="J257" t="str">
+        <v/>
+      </c>
+      <c r="K257" t="str">
+        <v>פיטר רוט - 50</v>
+      </c>
+      <c r="L257" t="str">
+        <v/>
+      </c>
+      <c r="M257" t="str">
+        <v/>
+      </c>
+      <c r="N257" t="str">
+        <v/>
+      </c>
+      <c r="O257" t="str">
+        <v/>
+      </c>
+      <c r="P257" t="str">
+        <v/>
+      </c>
+      <c r="Q257" t="str">
+        <v/>
+      </c>
+      <c r="R257" t="str">
+        <v/>
+      </c>
+      <c r="S257" t="str">
+        <v/>
+      </c>
+      <c r="T257" t="str">
+        <v/>
+      </c>
+      <c r="U257" t="str">
+        <v/>
+      </c>
+      <c r="V257" t="str">
+        <v/>
+      </c>
+      <c r="W257" t="str">
+        <v/>
+      </c>
+      <c r="X257" t="str">
+        <v/>
+      </c>
+      <c r="Y257" t="str">
+        <v/>
+      </c>
+      <c r="Z257" t="str">
+        <v/>
+      </c>
+      <c r="AA257" t="str">
+        <v/>
+      </c>
+      <c r="AB257" t="str">
+        <v/>
+      </c>
+      <c r="AC257" t="str">
+        <v/>
+      </c>
+      <c r="AD257" t="str">
+        <v/>
+      </c>
+      <c r="AE257" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>אגם בוחבוט - עשרים ואחת</v>
+      </c>
+      <c r="B258" t="str">
+        <v>2025  02:11-12-31</v>
+      </c>
+      <c r="C258" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D258" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E258" t="str">
+        <v/>
+      </c>
+      <c r="F258" t="str">
+        <v/>
+      </c>
+      <c r="G258" t="str">
+        <v/>
+      </c>
+      <c r="H258" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I258" t="str">
+        <v/>
+      </c>
+      <c r="J258" t="str">
+        <v/>
+      </c>
+      <c r="K258" t="str">
+        <v>אגם בוחבוט - עשרים ואחת</v>
+      </c>
+      <c r="L258" t="str">
+        <v/>
+      </c>
+      <c r="M258" t="str">
+        <v/>
+      </c>
+      <c r="N258" t="str">
+        <v/>
+      </c>
+      <c r="O258" t="str">
+        <v/>
+      </c>
+      <c r="P258" t="str">
+        <v/>
+      </c>
+      <c r="Q258" t="str">
+        <v/>
+      </c>
+      <c r="R258" t="str">
+        <v/>
+      </c>
+      <c r="S258" t="str">
+        <v/>
+      </c>
+      <c r="T258" t="str">
+        <v/>
+      </c>
+      <c r="U258" t="str">
+        <v/>
+      </c>
+      <c r="V258" t="str">
+        <v/>
+      </c>
+      <c r="W258" t="str">
+        <v/>
+      </c>
+      <c r="X258" t="str">
+        <v/>
+      </c>
+      <c r="Y258" t="str">
+        <v/>
+      </c>
+      <c r="Z258" t="str">
+        <v/>
+      </c>
+      <c r="AA258" t="str">
+        <v/>
+      </c>
+      <c r="AB258" t="str">
+        <v/>
+      </c>
+      <c r="AC258" t="str">
+        <v/>
+      </c>
+      <c r="AD258" t="str">
+        <v/>
+      </c>
+      <c r="AE258" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>רבקה זוהר - רסיסים של אור</v>
+      </c>
+      <c r="B259" t="str">
+        <v>2025  02:09-12-31</v>
+      </c>
+      <c r="C259" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D259" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E259" t="str">
+        <v/>
+      </c>
+      <c r="F259" t="str">
+        <v/>
+      </c>
+      <c r="G259" t="str">
+        <v/>
+      </c>
+      <c r="H259" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I259" t="str">
+        <v/>
+      </c>
+      <c r="J259" t="str">
+        <v/>
+      </c>
+      <c r="K259" t="str">
+        <v>רבקה זוהר - רסיסים של אור</v>
+      </c>
+      <c r="L259" t="str">
+        <v/>
+      </c>
+      <c r="M259" t="str">
+        <v/>
+      </c>
+      <c r="N259" t="str">
+        <v/>
+      </c>
+      <c r="O259" t="str">
+        <v/>
+      </c>
+      <c r="P259" t="str">
+        <v/>
+      </c>
+      <c r="Q259" t="str">
+        <v/>
+      </c>
+      <c r="R259" t="str">
+        <v/>
+      </c>
+      <c r="S259" t="str">
+        <v/>
+      </c>
+      <c r="T259" t="str">
+        <v/>
+      </c>
+      <c r="U259" t="str">
+        <v/>
+      </c>
+      <c r="V259" t="str">
+        <v/>
+      </c>
+      <c r="W259" t="str">
+        <v/>
+      </c>
+      <c r="X259" t="str">
+        <v/>
+      </c>
+      <c r="Y259" t="str">
+        <v/>
+      </c>
+      <c r="Z259" t="str">
+        <v/>
+      </c>
+      <c r="AA259" t="str">
+        <v/>
+      </c>
+      <c r="AB259" t="str">
+        <v/>
+      </c>
+      <c r="AC259" t="str">
+        <v/>
+      </c>
+      <c r="AD259" t="str">
+        <v/>
+      </c>
+      <c r="AE259" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
+      </c>
+      <c r="B260" t="str">
+        <v>2025  02:08-12-31</v>
+      </c>
+      <c r="C260" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D260" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E260" t="str">
+        <v/>
+      </c>
+      <c r="F260" t="str">
+        <v/>
+      </c>
+      <c r="G260" t="str">
+        <v/>
+      </c>
+      <c r="H260" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I260" t="str">
+        <v/>
+      </c>
+      <c r="J260" t="str">
+        <v/>
+      </c>
+      <c r="K260" t="str">
+        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
+      </c>
+      <c r="L260" t="str">
+        <v/>
+      </c>
+      <c r="M260" t="str">
+        <v/>
+      </c>
+      <c r="N260" t="str">
+        <v/>
+      </c>
+      <c r="O260" t="str">
+        <v/>
+      </c>
+      <c r="P260" t="str">
+        <v/>
+      </c>
+      <c r="Q260" t="str">
+        <v/>
+      </c>
+      <c r="R260" t="str">
+        <v/>
+      </c>
+      <c r="S260" t="str">
+        <v/>
+      </c>
+      <c r="T260" t="str">
+        <v/>
+      </c>
+      <c r="U260" t="str">
+        <v/>
+      </c>
+      <c r="V260" t="str">
+        <v/>
+      </c>
+      <c r="W260" t="str">
+        <v/>
+      </c>
+      <c r="X260" t="str">
+        <v/>
+      </c>
+      <c r="Y260" t="str">
+        <v/>
+      </c>
+      <c r="Z260" t="str">
+        <v/>
+      </c>
+      <c r="AA260" t="str">
+        <v/>
+      </c>
+      <c r="AB260" t="str">
+        <v/>
+      </c>
+      <c r="AC260" t="str">
+        <v/>
+      </c>
+      <c r="AD260" t="str">
+        <v/>
+      </c>
+      <c r="AE260" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
+      </c>
+      <c r="B261" t="str">
+        <v>2025  02:05-12-31</v>
+      </c>
+      <c r="C261" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D261" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E261" t="str">
+        <v/>
+      </c>
+      <c r="F261" t="str">
+        <v/>
+      </c>
+      <c r="G261" t="str">
+        <v/>
+      </c>
+      <c r="H261" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I261" t="str">
+        <v/>
+      </c>
+      <c r="J261" t="str">
+        <v/>
+      </c>
+      <c r="K261" t="str">
+        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
+      </c>
+      <c r="L261" t="str">
+        <v/>
+      </c>
+      <c r="M261" t="str">
+        <v/>
+      </c>
+      <c r="N261" t="str">
+        <v/>
+      </c>
+      <c r="O261" t="str">
+        <v/>
+      </c>
+      <c r="P261" t="str">
+        <v/>
+      </c>
+      <c r="Q261" t="str">
+        <v/>
+      </c>
+      <c r="R261" t="str">
+        <v/>
+      </c>
+      <c r="S261" t="str">
+        <v/>
+      </c>
+      <c r="T261" t="str">
+        <v/>
+      </c>
+      <c r="U261" t="str">
+        <v/>
+      </c>
+      <c r="V261" t="str">
+        <v/>
+      </c>
+      <c r="W261" t="str">
+        <v/>
+      </c>
+      <c r="X261" t="str">
+        <v/>
+      </c>
+      <c r="Y261" t="str">
+        <v/>
+      </c>
+      <c r="Z261" t="str">
+        <v/>
+      </c>
+      <c r="AA261" t="str">
+        <v/>
+      </c>
+      <c r="AB261" t="str">
+        <v/>
+      </c>
+      <c r="AC261" t="str">
+        <v/>
+      </c>
+      <c r="AD261" t="str">
+        <v/>
+      </c>
+      <c r="AE261" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>Imagine פסטיגל - שירי התחרות</v>
+      </c>
+      <c r="B262" t="str">
+        <v>2025  02:04-12-31</v>
+      </c>
+      <c r="C262" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D262" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E262" t="str">
+        <v/>
+      </c>
+      <c r="F262" t="str">
+        <v/>
+      </c>
+      <c r="G262" t="str">
+        <v/>
+      </c>
+      <c r="H262" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I262" t="str">
+        <v/>
+      </c>
+      <c r="J262" t="str">
+        <v/>
+      </c>
+      <c r="K262" t="str">
+        <v>Imagine פסטיגל - שירי התחרות</v>
+      </c>
+      <c r="L262" t="str">
+        <v/>
+      </c>
+      <c r="M262" t="str">
+        <v/>
+      </c>
+      <c r="N262" t="str">
+        <v/>
+      </c>
+      <c r="O262" t="str">
+        <v/>
+      </c>
+      <c r="P262" t="str">
+        <v/>
+      </c>
+      <c r="Q262" t="str">
+        <v/>
+      </c>
+      <c r="R262" t="str">
+        <v/>
+      </c>
+      <c r="S262" t="str">
+        <v/>
+      </c>
+      <c r="T262" t="str">
+        <v/>
+      </c>
+      <c r="U262" t="str">
+        <v/>
+      </c>
+      <c r="V262" t="str">
+        <v/>
+      </c>
+      <c r="W262" t="str">
+        <v/>
+      </c>
+      <c r="X262" t="str">
+        <v/>
+      </c>
+      <c r="Y262" t="str">
+        <v/>
+      </c>
+      <c r="Z262" t="str">
+        <v/>
+      </c>
+      <c r="AA262" t="str">
+        <v/>
+      </c>
+      <c r="AB262" t="str">
+        <v/>
+      </c>
+      <c r="AC262" t="str">
+        <v/>
+      </c>
+      <c r="AD262" t="str">
+        <v/>
+      </c>
+      <c r="AE262" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>השמחות - חובות אבודים</v>
+      </c>
+      <c r="B263" t="str">
+        <v>2025  02:02-12-31</v>
+      </c>
+      <c r="C263" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D263" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E263" t="str">
+        <v/>
+      </c>
+      <c r="F263" t="str">
+        <v/>
+      </c>
+      <c r="G263" t="str">
+        <v/>
+      </c>
+      <c r="H263" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I263" t="str">
+        <v/>
+      </c>
+      <c r="J263" t="str">
+        <v/>
+      </c>
+      <c r="K263" t="str">
+        <v>השמחות - חובות אבודים</v>
+      </c>
+      <c r="L263" t="str">
+        <v/>
+      </c>
+      <c r="M263" t="str">
+        <v/>
+      </c>
+      <c r="N263" t="str">
+        <v/>
+      </c>
+      <c r="O263" t="str">
+        <v/>
+      </c>
+      <c r="P263" t="str">
+        <v/>
+      </c>
+      <c r="Q263" t="str">
+        <v/>
+      </c>
+      <c r="R263" t="str">
+        <v/>
+      </c>
+      <c r="S263" t="str">
+        <v/>
+      </c>
+      <c r="T263" t="str">
+        <v/>
+      </c>
+      <c r="U263" t="str">
+        <v/>
+      </c>
+      <c r="V263" t="str">
+        <v/>
+      </c>
+      <c r="W263" t="str">
+        <v/>
+      </c>
+      <c r="X263" t="str">
+        <v/>
+      </c>
+      <c r="Y263" t="str">
+        <v/>
+      </c>
+      <c r="Z263" t="str">
+        <v/>
+      </c>
+      <c r="AA263" t="str">
+        <v/>
+      </c>
+      <c r="AB263" t="str">
+        <v/>
+      </c>
+      <c r="AC263" t="str">
+        <v/>
+      </c>
+      <c r="AD263" t="str">
+        <v/>
+      </c>
+      <c r="AE263" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>שלמה גרוניך - כמו כוכבים</v>
+      </c>
+      <c r="B264" t="str">
+        <v>2025  02:00-12-31</v>
+      </c>
+      <c r="C264" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D264" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E264" t="str">
+        <v/>
+      </c>
+      <c r="F264" t="str">
+        <v/>
+      </c>
+      <c r="G264" t="str">
+        <v/>
+      </c>
+      <c r="H264" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I264" t="str">
+        <v/>
+      </c>
+      <c r="J264" t="str">
+        <v/>
+      </c>
+      <c r="K264" t="str">
+        <v>שלמה גרוניך - כמו כוכבים</v>
+      </c>
+      <c r="L264" t="str">
+        <v/>
+      </c>
+      <c r="M264" t="str">
+        <v/>
+      </c>
+      <c r="N264" t="str">
+        <v/>
+      </c>
+      <c r="O264" t="str">
+        <v/>
+      </c>
+      <c r="P264" t="str">
+        <v/>
+      </c>
+      <c r="Q264" t="str">
+        <v/>
+      </c>
+      <c r="R264" t="str">
+        <v/>
+      </c>
+      <c r="S264" t="str">
+        <v/>
+      </c>
+      <c r="T264" t="str">
+        <v/>
+      </c>
+      <c r="U264" t="str">
+        <v/>
+      </c>
+      <c r="V264" t="str">
+        <v/>
+      </c>
+      <c r="W264" t="str">
+        <v/>
+      </c>
+      <c r="X264" t="str">
+        <v/>
+      </c>
+      <c r="Y264" t="str">
+        <v/>
+      </c>
+      <c r="Z264" t="str">
+        <v/>
+      </c>
+      <c r="AA264" t="str">
+        <v/>
+      </c>
+      <c r="AB264" t="str">
+        <v/>
+      </c>
+      <c r="AC264" t="str">
+        <v/>
+      </c>
+      <c r="AD264" t="str">
+        <v/>
+      </c>
+      <c r="AE264" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>יוני רועה - מפוזרים</v>
+      </c>
+      <c r="B265" t="str">
+        <v>2025  01:56-12-31</v>
+      </c>
+      <c r="C265" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D265" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E265" t="str">
+        <v/>
+      </c>
+      <c r="F265" t="str">
+        <v/>
+      </c>
+      <c r="G265" t="str">
+        <v/>
+      </c>
+      <c r="H265" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I265" t="str">
+        <v/>
+      </c>
+      <c r="J265" t="str">
+        <v/>
+      </c>
+      <c r="K265" t="str">
+        <v>יוני רועה - מפוזרים</v>
+      </c>
+      <c r="L265" t="str">
+        <v/>
+      </c>
+      <c r="M265" t="str">
+        <v/>
+      </c>
+      <c r="N265" t="str">
+        <v/>
+      </c>
+      <c r="O265" t="str">
+        <v/>
+      </c>
+      <c r="P265" t="str">
+        <v/>
+      </c>
+      <c r="Q265" t="str">
+        <v/>
+      </c>
+      <c r="R265" t="str">
+        <v/>
+      </c>
+      <c r="S265" t="str">
+        <v/>
+      </c>
+      <c r="T265" t="str">
+        <v/>
+      </c>
+      <c r="U265" t="str">
+        <v/>
+      </c>
+      <c r="V265" t="str">
+        <v/>
+      </c>
+      <c r="W265" t="str">
+        <v/>
+      </c>
+      <c r="X265" t="str">
+        <v/>
+      </c>
+      <c r="Y265" t="str">
+        <v/>
+      </c>
+      <c r="Z265" t="str">
+        <v/>
+      </c>
+      <c r="AA265" t="str">
+        <v/>
+      </c>
+      <c r="AB265" t="str">
+        <v/>
+      </c>
+      <c r="AC265" t="str">
+        <v/>
+      </c>
+      <c r="AD265" t="str">
+        <v/>
+      </c>
+      <c r="AE265" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AA221"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AE265"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:L45"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -413,7 +413,7 @@
         <v>תאריך סריקה</v>
       </c>
       <c r="E1" t="str">
-        <v>תיאור</v>
+        <v>שעה</v>
       </c>
       <c r="F1" t="str">
         <v>משך</v>
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>רוקפור והקאמרטה הישראלית ירושלים - רוקפור והתזמורת LIVE</v>
+        <v>רובי ויליאמס Britpop</v>
       </c>
       <c r="B2" t="str">
-        <v>2026  11:10-01-21</v>
+        <v>2026-01-20</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24438&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%91%d7%99-%d7%95%d7%99%d7%9c%d7%99%d7%90%d7%9e%d7%a1-britpop/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-22</v>
@@ -451,33 +451,36 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>רובי וויליאמס הודה בכנות שהוא מעכב את יציאת האלבום בגלל שאינו רוצה להתחרות ב־The Life of a Showgirl של טיילור סוויפט. כעת האלבום הופיע לפתע, ללא הסבר, שבועיים בלבד לתוך ינואר, ככל הנראה משום שלוויליאמס יהיו פחות מתחרים במצעד האלבומים</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
       </c>
       <c r="K2" t="str">
-        <v>רוקפור והקאמרטה הישראלית ירושלים - רוקפור והתזמורת LIVE</v>
+        <v/>
+      </c>
+      <c r="L2" t="str">
+        <v>רובי ויליאמס Britpop</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>חנן בן ארי - חנן בן ארי - Live 2022</v>
+        <v>עוז זהבי תור זהבי</v>
       </c>
       <c r="B3" t="str">
-        <v>2026  11:48-01-17</v>
+        <v>2026-01-18</v>
       </c>
       <c r="C3" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24100&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%a2%d7%95%d7%96-%d7%96%d7%94%d7%91%d7%99-%d7%aa%d7%95%d7%a8-%d7%96%d7%94%d7%91%d7%99/</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-22</v>
@@ -486,33 +489,36 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>את ההופעה הזו קיבלתי ביוטיוב (*), שיטה יעילה למי שנפשו לא חשקה לשרך דרכו למועדונים בלילות הקרים. הוידיאו נשלח לרגל יציאת אלבומו "תור זהבי", ששיר הנושא הוא ראפ עצבני בניחוח מזרחי, שיר אגו ביקורתי, אירוני ומודע לעצמו מלא בדאחקות, הגזמות,</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J3" t="str">
         <v/>
       </c>
       <c r="K3" t="str">
-        <v>חנן בן ארי - חנן בן ארי - Live 2022</v>
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>עוז זהבי תור זהבי</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>עדן בן זקן - רולקס וקסקט</v>
+        <v>פטריק סבג Hotel Mogador</v>
       </c>
       <c r="B4" t="str">
-        <v>2026  08:41-01-14</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C4" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24436&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-22</v>
@@ -521,33 +527,36 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>האלבום של פטריק סבג אינו אוסף שירים אקראי, אלא מרחב. מקום לשהות בו.  נכנסים, שומעים, ויוצאים קצת אחרים. הבחירה בשם "הוטל מוגדור” היא כבר הצהרה. מלון = מקום מעבר, לא בית קבוע, מוגדור = עיר נמל, תנועה, ערבוב תרבויות. כך</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J4" t="str">
         <v/>
       </c>
       <c r="K4" t="str">
-        <v>עדן בן זקן - רולקס וקסקט</v>
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>פטריק סבג Hotel Mogador</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
       </c>
       <c r="B5" t="str">
-        <v>2026  08:40-01-14</v>
+        <v>2026-01-09</v>
       </c>
       <c r="C5" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24439&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-22</v>
@@ -556,33 +565,36 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J5" t="str">
         <v/>
       </c>
       <c r="K5" t="str">
-        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>אייל גולן - בית מפואר</v>
+        <v>אוליביה דין The Art of Loving</v>
       </c>
       <c r="B6" t="str">
-        <v>2025  02:18-12-31</v>
+        <v>2026-01-04</v>
       </c>
       <c r="C6" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-22</v>
@@ -591,33 +603,36 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J6" t="str">
         <v/>
       </c>
       <c r="K6" t="str">
-        <v>אייל גולן - בית מפואר</v>
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>אוליביה דין The Art of Loving</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
+        <v>Geese Getting Killed</v>
       </c>
       <c r="B7" t="str">
-        <v>2025  02:16-12-31</v>
+        <v>2025-12-29</v>
       </c>
       <c r="C7" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/geese-getting-killed/</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-22</v>
@@ -626,33 +641,36 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I7" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J7" t="str">
         <v/>
       </c>
       <c r="K7" t="str">
-        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>Geese Getting Killed</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>שיר לוי - ילד מוזר</v>
+        <v>רוסליה Lux</v>
       </c>
       <c r="B8" t="str">
-        <v>2025  02:14-12-31</v>
+        <v>2025-12-25</v>
       </c>
       <c r="C8" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-22</v>
@@ -661,33 +679,36 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v/>
+        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J8" t="str">
         <v/>
       </c>
       <c r="K8" t="str">
-        <v>שיר לוי - ילד מוזר</v>
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>רוסליה Lux</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>פיטר רוט - 50</v>
+        <v>יאנגבלאד אירוסמית' one more time</v>
       </c>
       <c r="B9" t="str">
-        <v>2025  02:13-12-31</v>
+        <v>2025-12-17</v>
       </c>
       <c r="C9" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-22</v>
@@ -696,33 +717,36 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v/>
+        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J9" t="str">
         <v/>
       </c>
       <c r="K9" t="str">
-        <v>פיטר רוט - 50</v>
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>יאנגבלאד אירוסמית' one more time</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>אגם בוחבוט - עשרים ואחת</v>
+        <v>פינק פלויד Wish You Were Here 50</v>
       </c>
       <c r="B10" t="str">
-        <v>2025  02:11-12-31</v>
+        <v>2025-12-14</v>
       </c>
       <c r="C10" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-22</v>
@@ -731,33 +755,36 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I10" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J10" t="str">
         <v/>
       </c>
       <c r="K10" t="str">
-        <v>אגם בוחבוט - עשרים ואחת</v>
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>פינק פלויד Wish You Were Here 50</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>רבקה זוהר - רסיסים של אור</v>
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
       </c>
       <c r="B11" t="str">
-        <v>2025  02:09-12-31</v>
+        <v>2025-12-08</v>
       </c>
       <c r="C11" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-22</v>
@@ -766,33 +793,36 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v/>
+        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I11" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J11" t="str">
         <v/>
       </c>
       <c r="K11" t="str">
-        <v>רבקה זוהר - רסיסים של אור</v>
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
+        <v>סטריי קידס DO IT (EP)</v>
       </c>
       <c r="B12" t="str">
-        <v>2025  02:08-12-31</v>
+        <v>2025-12-04</v>
       </c>
       <c r="C12" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-22</v>
@@ -801,33 +831,36 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v/>
+        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I12" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J12" t="str">
         <v/>
       </c>
       <c r="K12" t="str">
-        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>סטריי קידס DO IT (EP)</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
+        <v>דויד ברוזה BROZAJAZZ</v>
       </c>
       <c r="B13" t="str">
-        <v>2025  02:05-12-31</v>
+        <v>2025-11-30</v>
       </c>
       <c r="C13" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-22</v>
@@ -836,33 +869,36 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v/>
+        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I13" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J13" t="str">
         <v/>
       </c>
       <c r="K13" t="str">
-        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>דויד ברוזה BROZAJAZZ</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Imagine פסטיגל - שירי התחרות</v>
+        <v>Five Seconds of Summer – Everyone's A Star</v>
       </c>
       <c r="B14" t="str">
-        <v>2025  02:04-12-31</v>
+        <v>2025-11-24</v>
       </c>
       <c r="C14" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-22</v>
@@ -871,62 +907,1208 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v/>
+        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I14" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J14" t="str">
         <v/>
       </c>
       <c r="K14" t="str">
-        <v>Imagine פסטיגל - שירי התחרות</v>
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>Five Seconds of Summer – Everyone's A Star</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
+        <v>התקווה 6 – ויהי אור</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2025-11-20</v>
+      </c>
+      <c r="C15" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>התקווה 6 – ויהי אור</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>פלורנס אנד דה משין Everybody Scream</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2025-11-13</v>
+      </c>
+      <c r="C16" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>פלורנס אנד דה משין Everybody Scream</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>טיים אימפלה Deadbeat</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2025-11-03</v>
+      </c>
+      <c r="C17" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v>טיים אימפלה Deadbeat</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2025-10-20</v>
+      </c>
+      <c r="C18" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
+      </c>
+      <c r="D18" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>שלמה גרוניך – תודה אהבה</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2025-10-18</v>
+      </c>
+      <c r="C19" t="str">
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
+      </c>
+      <c r="D19" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
+        <v>שלמה גרוניך – תודה אהבה</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2025-10-11</v>
+      </c>
+      <c r="C20" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
+      </c>
+      <c r="D20" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>דוג'ה קאט Vie</v>
+      </c>
+      <c r="B21" t="str">
+        <v>2025-10-04</v>
+      </c>
+      <c r="C21" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
+      </c>
+      <c r="D21" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
+        <v>דוג'ה קאט Vie</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>ג'וי קרוקס Juniper</v>
+      </c>
+      <c r="B22" t="str">
+        <v>2025-10-03</v>
+      </c>
+      <c r="C22" t="str">
+        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
+      </c>
+      <c r="D22" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
+        <v>ג'וי קרוקס Juniper</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>ביפי קליירו Futique</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2025-09-30</v>
+      </c>
+      <c r="C23" t="str">
+        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
+      </c>
+      <c r="D23" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
+        <v>ביפי קליירו Futique</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>אד שירן Play</v>
+      </c>
+      <c r="B24" t="str">
+        <v>2025-09-24</v>
+      </c>
+      <c r="C24" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
+      </c>
+      <c r="D24" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
+        <v>אד שירן Play</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+      </c>
+      <c r="B25" t="str">
+        <v>2025-09-21</v>
+      </c>
+      <c r="C25" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
+      </c>
+      <c r="D25" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J25" t="str">
+        <v/>
+      </c>
+      <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>סוויד Antidepressants</v>
+      </c>
+      <c r="B26" t="str">
+        <v>2025-09-12</v>
+      </c>
+      <c r="C26" t="str">
+        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
+      </c>
+      <c r="D26" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J26" t="str">
+        <v/>
+      </c>
+      <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
+        <v>סוויד Antidepressants</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>וולף אליס The Clearing</v>
+      </c>
+      <c r="B27" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="C27" t="str">
+        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
+      </c>
+      <c r="D27" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J27" t="str">
+        <v/>
+      </c>
+      <c r="K27" t="str">
+        <v/>
+      </c>
+      <c r="L27" t="str">
+        <v>וולף אליס The Clearing</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+      </c>
+      <c r="B28" t="str">
+        <v>2025-08-29</v>
+      </c>
+      <c r="C28" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
+      </c>
+      <c r="D28" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J28" t="str">
+        <v/>
+      </c>
+      <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28" t="str">
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+      </c>
+      <c r="B29" t="str">
+        <v>2025-08-24</v>
+      </c>
+      <c r="C29" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
+      </c>
+      <c r="D29" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J29" t="str">
+        <v/>
+      </c>
+      <c r="K29" t="str">
+        <v/>
+      </c>
+      <c r="L29" t="str">
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+      </c>
+      <c r="B30" t="str">
+        <v>2025-08-21</v>
+      </c>
+      <c r="C30" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
+      </c>
+      <c r="D30" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
+        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30" t="str">
+        <v/>
+      </c>
+      <c r="I30" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J30" t="str">
+        <v/>
+      </c>
+      <c r="K30" t="str">
+        <v/>
+      </c>
+      <c r="L30" t="str">
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>אברהם טל – חי</v>
+      </c>
+      <c r="B31" t="str">
+        <v>2025-08-17</v>
+      </c>
+      <c r="C31" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
+      </c>
+      <c r="D31" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+      <c r="H31" t="str">
+        <v/>
+      </c>
+      <c r="I31" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J31" t="str">
+        <v/>
+      </c>
+      <c r="K31" t="str">
+        <v/>
+      </c>
+      <c r="L31" t="str">
+        <v>אברהם טל – חי</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>רוקפור והקאמרטה הישראלית ירושלים - רוקפור והתזמורת LIVE</v>
+      </c>
+      <c r="B32" t="str">
+        <v>2026-01-21</v>
+      </c>
+      <c r="C32" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24438&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D32" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
+        <v>11:10</v>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+      <c r="H32" t="str">
+        <v/>
+      </c>
+      <c r="I32" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J32" t="str">
+        <v/>
+      </c>
+      <c r="K32" t="str">
+        <v/>
+      </c>
+      <c r="L32" t="str">
+        <v>רוקפור והקאמרטה הישראלית ירושלים - רוקפור והתזמורת LIVE</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>חנן בן ארי - חנן בן ארי - Live 2022</v>
+      </c>
+      <c r="B33" t="str">
+        <v>2026-01-17</v>
+      </c>
+      <c r="C33" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24100&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D33" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <v>11:48</v>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+      <c r="H33" t="str">
+        <v/>
+      </c>
+      <c r="I33" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J33" t="str">
+        <v/>
+      </c>
+      <c r="K33" t="str">
+        <v/>
+      </c>
+      <c r="L33" t="str">
+        <v>חנן בן ארי - חנן בן ארי - Live 2022</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>עדן בן זקן - רולקס וקסקט</v>
+      </c>
+      <c r="B34" t="str">
+        <v>2026-01-14</v>
+      </c>
+      <c r="C34" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24436&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D34" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <v>08:41</v>
+      </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
+      <c r="H34" t="str">
+        <v/>
+      </c>
+      <c r="I34" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J34" t="str">
+        <v/>
+      </c>
+      <c r="K34" t="str">
+        <v/>
+      </c>
+      <c r="L34" t="str">
+        <v>עדן בן זקן - רולקס וקסקט</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
+      </c>
+      <c r="B35" t="str">
+        <v>2026-01-14</v>
+      </c>
+      <c r="C35" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24439&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D35" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v>08:40</v>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+      <c r="H35" t="str">
+        <v/>
+      </c>
+      <c r="I35" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J35" t="str">
+        <v/>
+      </c>
+      <c r="K35" t="str">
+        <v/>
+      </c>
+      <c r="L35" t="str">
+        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>אייל גולן - בית מפואר</v>
+      </c>
+      <c r="B36" t="str">
+        <v>2025-12-31</v>
+      </c>
+      <c r="C36" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D36" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
+        <v>02:18</v>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+      <c r="H36" t="str">
+        <v/>
+      </c>
+      <c r="I36" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J36" t="str">
+        <v/>
+      </c>
+      <c r="K36" t="str">
+        <v/>
+      </c>
+      <c r="L36" t="str">
+        <v>אייל גולן - בית מפואר</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
+      </c>
+      <c r="B37" t="str">
+        <v>2025-12-31</v>
+      </c>
+      <c r="C37" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D37" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v>02:16</v>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str">
+        <v/>
+      </c>
+      <c r="I37" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J37" t="str">
+        <v/>
+      </c>
+      <c r="K37" t="str">
+        <v/>
+      </c>
+      <c r="L37" t="str">
+        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>שיר לוי - ילד מוזר</v>
+      </c>
+      <c r="B38" t="str">
+        <v>2025-12-31</v>
+      </c>
+      <c r="C38" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D38" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <v>02:14</v>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str">
+        <v/>
+      </c>
+      <c r="I38" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J38" t="str">
+        <v/>
+      </c>
+      <c r="K38" t="str">
+        <v/>
+      </c>
+      <c r="L38" t="str">
+        <v>שיר לוי - ילד מוזר</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>פיטר רוט - 50</v>
+      </c>
+      <c r="B39" t="str">
+        <v>2025-12-31</v>
+      </c>
+      <c r="C39" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D39" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v>02:13</v>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+      <c r="H39" t="str">
+        <v/>
+      </c>
+      <c r="I39" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J39" t="str">
+        <v/>
+      </c>
+      <c r="K39" t="str">
+        <v/>
+      </c>
+      <c r="L39" t="str">
+        <v>פיטר רוט - 50</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>אגם בוחבוט - עשרים ואחת</v>
+      </c>
+      <c r="B40" t="str">
+        <v>2025-12-31</v>
+      </c>
+      <c r="C40" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D40" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v>02:11</v>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+      <c r="H40" t="str">
+        <v/>
+      </c>
+      <c r="I40" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J40" t="str">
+        <v/>
+      </c>
+      <c r="K40" t="str">
+        <v/>
+      </c>
+      <c r="L40" t="str">
+        <v>אגם בוחבוט - עשרים ואחת</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>רבקה זוהר - רסיסים של אור</v>
+      </c>
+      <c r="B41" t="str">
+        <v>2025-12-31</v>
+      </c>
+      <c r="C41" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D41" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <v>02:09</v>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+      <c r="H41" t="str">
+        <v/>
+      </c>
+      <c r="I41" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J41" t="str">
+        <v/>
+      </c>
+      <c r="K41" t="str">
+        <v/>
+      </c>
+      <c r="L41" t="str">
+        <v>רבקה זוהר - רסיסים של אור</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
+      </c>
+      <c r="B42" t="str">
+        <v>2025-12-31</v>
+      </c>
+      <c r="C42" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D42" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <v>02:08</v>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+      <c r="I42" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J42" t="str">
+        <v/>
+      </c>
+      <c r="K42" t="str">
+        <v/>
+      </c>
+      <c r="L42" t="str">
+        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
+      </c>
+      <c r="B43" t="str">
+        <v>2025-12-31</v>
+      </c>
+      <c r="C43" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D43" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v>02:05</v>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
+      <c r="I43" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J43" t="str">
+        <v/>
+      </c>
+      <c r="K43" t="str">
+        <v/>
+      </c>
+      <c r="L43" t="str">
+        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Imagine פסטיגל - שירי התחרות</v>
+      </c>
+      <c r="B44" t="str">
+        <v>2025-12-31</v>
+      </c>
+      <c r="C44" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D44" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <v>02:04</v>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
+      <c r="I44" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J44" t="str">
+        <v/>
+      </c>
+      <c r="K44" t="str">
+        <v/>
+      </c>
+      <c r="L44" t="str">
+        <v>Imagine פסטיגל - שירי התחרות</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
         <v>השמחות - חובות אבודים</v>
       </c>
-      <c r="B15" t="str">
-        <v>2025  02:02-12-31</v>
-      </c>
-      <c r="C15" t="str">
+      <c r="B45" t="str">
+        <v>2025-12-31</v>
+      </c>
+      <c r="C45" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
       </c>
-      <c r="D15" t="str">
-        <v>2026-01-22</v>
-      </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
-      <c r="H15" t="str">
-        <v>אלבומים חדשים</v>
-      </c>
-      <c r="I15" t="str">
-        <v/>
-      </c>
-      <c r="J15" t="str">
-        <v/>
-      </c>
-      <c r="K15" t="str">
+      <c r="D45" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+      <c r="F45" t="str">
+        <v>02:02</v>
+      </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
+      <c r="H45" t="str">
+        <v/>
+      </c>
+      <c r="I45" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J45" t="str">
+        <v/>
+      </c>
+      <c r="K45" t="str">
+        <v/>
+      </c>
+      <c r="L45" t="str">
         <v>השמחות - חובות אבודים</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L45"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://yosmusic.com/%d7%a8%d7%95%d7%91%d7%99-%d7%95%d7%99%d7%9c%d7%99%d7%90%d7%9e%d7%a1-britpop/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://yosmusic.com/%d7%a2%d7%95%d7%96-%d7%96%d7%94%d7%91%d7%99-%d7%aa%d7%95%d7%a8-%d7%96%d7%94%d7%91%d7%99/</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://yosmusic.com/geese-getting-killed/</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24438&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24100&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24436&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24439&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E45" t="str">
         <v/>

--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נדב גדג’ - בלי יד על הדופק</v>
+        <v>מיקי גבריאלוב - שלום</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24441&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-23</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>23:52</v>
+        <v>22:43</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,88 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נדב גדג’ - בלי יד על הדופק</v>
+        <v>מיקי גבריאלוב - שלום</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>בזכרי ימים ימימה - מחווה לצלילי הכרם</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2025-12-31</v>
+      </c>
+      <c r="C3" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v>02:12</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>בזכרי ימים ימימה - מחווה לצלילי הכרם</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>עדן בן זקן - עוד פעם סטלה עוד פעם דכאון</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2025-12-31</v>
+      </c>
+      <c r="C4" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v>02:10</v>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>עדן בן זקן - עוד פעם סטלה עוד פעם דכאון</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L45"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מיקי גבריאלוב - שלום</v>
+        <v>רובי ויליאמס Britpop</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-20</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%91%d7%99-%d7%95%d7%99%d7%9c%d7%99%d7%90%d7%9e%d7%a1-britpop/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>22:43</v>
+        <v>רובי וויליאמס הודה בכנות שהוא מעכב את יציאת האלבום בגלל שאינו רוצה להתחרות ב־The Life of a Showgirl של טיילור סוויפט. כעת האלבום הופיע לפתע, ללא הסבר, שבועיים בלבד לתוך ינואר, ככל הנראה משום שלוויליאמס יהיו פחות מתחרים במצעד האלבומים</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,27 +469,27 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מיקי גבריאלוב - שלום</v>
+        <v>רובי ויליאמס Britpop</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>בזכרי ימים ימימה - מחווה לצלילי הכרם</v>
+        <v>עוז זהבי תור זהבי</v>
       </c>
       <c r="B3" t="str">
-        <v>2025-12-31</v>
+        <v>2026-01-18</v>
       </c>
       <c r="C3" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%a2%d7%95%d7%96-%d7%96%d7%94%d7%91%d7%99-%d7%aa%d7%95%d7%a8-%d7%96%d7%94%d7%91%d7%99/</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>02:12</v>
+        <v>את ההופעה הזו קיבלתי ביוטיוב (*), שיטה יעילה למי שנפשו לא חשקה לשרך דרכו למועדונים בלילות הקרים. הוידיאו נשלח לרגל יציאת אלבומו "תור זהבי", ששיר הנושא הוא ראפ עצבני בניחוח מזרחי, שיר אגו ביקורתי, אירוני ומודע לעצמו מלא בדאחקות, הגזמות,</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -507,50 +507,1608 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>בזכרי ימים ימימה - מחווה לצלילי הכרם</v>
+        <v>עוז זהבי תור זהבי</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
+        <v>פטריק סבג Hotel Mogador</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C4" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v>האלבום של פטריק סבג אינו אוסף שירים אקראי, אלא מרחב. מקום לשהות בו.  נכנסים, שומעים, ויוצאים קצת אחרים. הבחירה בשם "הוטל מוגדור” היא כבר הצהרה. מלון = מקום מעבר, לא בית קבוע, מוגדור = עיר נמל, תנועה, ערבוב תרבויות. כך</v>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>פטריק סבג Hotel Mogador</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-01-09</v>
+      </c>
+      <c r="C5" t="str">
+        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>אוליביה דין The Art of Loving</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-01-04</v>
+      </c>
+      <c r="C6" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>אוליביה דין The Art of Loving</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Geese Getting Killed</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2025-12-29</v>
+      </c>
+      <c r="C7" t="str">
+        <v>https://yosmusic.com/geese-getting-killed/</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>Geese Getting Killed</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>רוסליה Lux</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2025-12-25</v>
+      </c>
+      <c r="C8" t="str">
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>רוסליה Lux</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>יאנגבלאד אירוסמית' one more time</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2025-12-17</v>
+      </c>
+      <c r="C9" t="str">
+        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>יאנגבלאד אירוסמית' one more time</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>פינק פלויד Wish You Were Here 50</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2025-12-14</v>
+      </c>
+      <c r="C10" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>פינק פלויד Wish You Were Here 50</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2025-12-08</v>
+      </c>
+      <c r="C11" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>סטריי קידס DO IT (EP)</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2025-12-04</v>
+      </c>
+      <c r="C12" t="str">
+        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>סטריי קידס DO IT (EP)</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>דויד ברוזה BROZAJAZZ</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2025-11-30</v>
+      </c>
+      <c r="C13" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>דויד ברוזה BROZAJAZZ</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Five Seconds of Summer – Everyone's A Star</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2025-11-24</v>
+      </c>
+      <c r="C14" t="str">
+        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>Five Seconds of Summer – Everyone's A Star</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>התקווה 6 – ויהי אור</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2025-11-20</v>
+      </c>
+      <c r="C15" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>התקווה 6 – ויהי אור</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>פלורנס אנד דה משין Everybody Scream</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2025-11-13</v>
+      </c>
+      <c r="C16" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>פלורנס אנד דה משין Everybody Scream</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>טיים אימפלה Deadbeat</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2025-11-03</v>
+      </c>
+      <c r="C17" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v>טיים אימפלה Deadbeat</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2025-10-20</v>
+      </c>
+      <c r="C18" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
+      </c>
+      <c r="D18" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>שלמה גרוניך – תודה אהבה</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2025-10-18</v>
+      </c>
+      <c r="C19" t="str">
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
+      </c>
+      <c r="D19" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
+        <v>שלמה גרוניך – תודה אהבה</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2025-10-11</v>
+      </c>
+      <c r="C20" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
+      </c>
+      <c r="D20" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>דוג'ה קאט Vie</v>
+      </c>
+      <c r="B21" t="str">
+        <v>2025-10-04</v>
+      </c>
+      <c r="C21" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
+      </c>
+      <c r="D21" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
+        <v>דוג'ה קאט Vie</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>ג'וי קרוקס Juniper</v>
+      </c>
+      <c r="B22" t="str">
+        <v>2025-10-03</v>
+      </c>
+      <c r="C22" t="str">
+        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
+      </c>
+      <c r="D22" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
+        <v>ג'וי קרוקס Juniper</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>ביפי קליירו Futique</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2025-09-30</v>
+      </c>
+      <c r="C23" t="str">
+        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
+      </c>
+      <c r="D23" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
+        <v>ביפי קליירו Futique</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>אד שירן Play</v>
+      </c>
+      <c r="B24" t="str">
+        <v>2025-09-24</v>
+      </c>
+      <c r="C24" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
+      </c>
+      <c r="D24" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
+        <v>אד שירן Play</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+      </c>
+      <c r="B25" t="str">
+        <v>2025-09-21</v>
+      </c>
+      <c r="C25" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
+      </c>
+      <c r="D25" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J25" t="str">
+        <v/>
+      </c>
+      <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>סוויד Antidepressants</v>
+      </c>
+      <c r="B26" t="str">
+        <v>2025-09-12</v>
+      </c>
+      <c r="C26" t="str">
+        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
+      </c>
+      <c r="D26" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J26" t="str">
+        <v/>
+      </c>
+      <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
+        <v>סוויד Antidepressants</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>וולף אליס The Clearing</v>
+      </c>
+      <c r="B27" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="C27" t="str">
+        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
+      </c>
+      <c r="D27" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J27" t="str">
+        <v/>
+      </c>
+      <c r="K27" t="str">
+        <v/>
+      </c>
+      <c r="L27" t="str">
+        <v>וולף אליס The Clearing</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+      </c>
+      <c r="B28" t="str">
+        <v>2025-08-29</v>
+      </c>
+      <c r="C28" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
+      </c>
+      <c r="D28" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J28" t="str">
+        <v/>
+      </c>
+      <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28" t="str">
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+      </c>
+      <c r="B29" t="str">
+        <v>2025-08-24</v>
+      </c>
+      <c r="C29" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
+      </c>
+      <c r="D29" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J29" t="str">
+        <v/>
+      </c>
+      <c r="K29" t="str">
+        <v/>
+      </c>
+      <c r="L29" t="str">
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+      </c>
+      <c r="B30" t="str">
+        <v>2025-08-21</v>
+      </c>
+      <c r="C30" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
+      </c>
+      <c r="D30" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
+        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30" t="str">
+        <v/>
+      </c>
+      <c r="I30" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J30" t="str">
+        <v/>
+      </c>
+      <c r="K30" t="str">
+        <v/>
+      </c>
+      <c r="L30" t="str">
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>אברהם טל – חי</v>
+      </c>
+      <c r="B31" t="str">
+        <v>2025-08-17</v>
+      </c>
+      <c r="C31" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
+      </c>
+      <c r="D31" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+      <c r="H31" t="str">
+        <v/>
+      </c>
+      <c r="I31" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J31" t="str">
+        <v/>
+      </c>
+      <c r="K31" t="str">
+        <v/>
+      </c>
+      <c r="L31" t="str">
+        <v>אברהם טל – חי</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>מיקי גבריאלוב - שלום</v>
+      </c>
+      <c r="B32" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="C32" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D32" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
+        <v>22:43</v>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+      <c r="H32" t="str">
+        <v/>
+      </c>
+      <c r="I32" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J32" t="str">
+        <v/>
+      </c>
+      <c r="K32" t="str">
+        <v/>
+      </c>
+      <c r="L32" t="str">
+        <v>מיקי גבריאלוב - שלום</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>נדב גדג’ - בלי יד על הדופק</v>
+      </c>
+      <c r="B33" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="C33" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24441&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D33" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <v>23:52</v>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+      <c r="H33" t="str">
+        <v/>
+      </c>
+      <c r="I33" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J33" t="str">
+        <v/>
+      </c>
+      <c r="K33" t="str">
+        <v/>
+      </c>
+      <c r="L33" t="str">
+        <v>נדב גדג’ - בלי יד על הדופק</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>חנן בן ארי - חנן בן ארי - Live 2022</v>
+      </c>
+      <c r="B34" t="str">
+        <v>2026-01-17</v>
+      </c>
+      <c r="C34" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24100&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D34" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <v>11:48</v>
+      </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
+      <c r="H34" t="str">
+        <v/>
+      </c>
+      <c r="I34" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J34" t="str">
+        <v/>
+      </c>
+      <c r="K34" t="str">
+        <v/>
+      </c>
+      <c r="L34" t="str">
+        <v>חנן בן ארי - חנן בן ארי - Live 2022</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>עדן בן זקן - רולקס וקסקט</v>
+      </c>
+      <c r="B35" t="str">
+        <v>2026-01-14</v>
+      </c>
+      <c r="C35" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24436&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D35" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v>08:41</v>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+      <c r="H35" t="str">
+        <v/>
+      </c>
+      <c r="I35" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J35" t="str">
+        <v/>
+      </c>
+      <c r="K35" t="str">
+        <v/>
+      </c>
+      <c r="L35" t="str">
+        <v>עדן בן זקן - רולקס וקסקט</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
+      </c>
+      <c r="B36" t="str">
+        <v>2026-01-14</v>
+      </c>
+      <c r="C36" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24439&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D36" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
+        <v>08:40</v>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+      <c r="H36" t="str">
+        <v/>
+      </c>
+      <c r="I36" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J36" t="str">
+        <v/>
+      </c>
+      <c r="K36" t="str">
+        <v/>
+      </c>
+      <c r="L36" t="str">
+        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>אייל גולן - בית מפואר</v>
+      </c>
+      <c r="B37" t="str">
+        <v>2025-12-31</v>
+      </c>
+      <c r="C37" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D37" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v>02:18</v>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str">
+        <v/>
+      </c>
+      <c r="I37" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J37" t="str">
+        <v/>
+      </c>
+      <c r="K37" t="str">
+        <v/>
+      </c>
+      <c r="L37" t="str">
+        <v>אייל גולן - בית מפואר</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
+      </c>
+      <c r="B38" t="str">
+        <v>2025-12-31</v>
+      </c>
+      <c r="C38" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D38" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <v>02:16</v>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str">
+        <v/>
+      </c>
+      <c r="I38" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J38" t="str">
+        <v/>
+      </c>
+      <c r="K38" t="str">
+        <v/>
+      </c>
+      <c r="L38" t="str">
+        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>שיר לוי - ילד מוזר</v>
+      </c>
+      <c r="B39" t="str">
+        <v>2025-12-31</v>
+      </c>
+      <c r="C39" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D39" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v>02:14</v>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+      <c r="H39" t="str">
+        <v/>
+      </c>
+      <c r="I39" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J39" t="str">
+        <v/>
+      </c>
+      <c r="K39" t="str">
+        <v/>
+      </c>
+      <c r="L39" t="str">
+        <v>שיר לוי - ילד מוזר</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>בזכרי ימים ימימה - מחווה לצלילי הכרם</v>
+      </c>
+      <c r="B40" t="str">
+        <v>2025-12-31</v>
+      </c>
+      <c r="C40" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D40" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v>02:12</v>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+      <c r="H40" t="str">
+        <v/>
+      </c>
+      <c r="I40" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J40" t="str">
+        <v/>
+      </c>
+      <c r="K40" t="str">
+        <v/>
+      </c>
+      <c r="L40" t="str">
+        <v>בזכרי ימים ימימה - מחווה לצלילי הכרם</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
         <v>עדן בן זקן - עוד פעם סטלה עוד פעם דכאון</v>
       </c>
-      <c r="B4" t="str">
+      <c r="B41" t="str">
         <v>2025-12-31</v>
       </c>
-      <c r="C4" t="str">
+      <c r="C41" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
-      <c r="D4" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
+      <c r="D41" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
         <v>02:10</v>
       </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>אלבומים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
+      <c r="G41" t="str">
+        <v/>
+      </c>
+      <c r="H41" t="str">
+        <v/>
+      </c>
+      <c r="I41" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J41" t="str">
+        <v/>
+      </c>
+      <c r="K41" t="str">
+        <v/>
+      </c>
+      <c r="L41" t="str">
         <v>עדן בן זקן - עוד פעם סטלה עוד פעם דכאון</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
+      </c>
+      <c r="B42" t="str">
+        <v>2025-12-31</v>
+      </c>
+      <c r="C42" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D42" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <v>02:08</v>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+      <c r="I42" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J42" t="str">
+        <v/>
+      </c>
+      <c r="K42" t="str">
+        <v/>
+      </c>
+      <c r="L42" t="str">
+        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
+      </c>
+      <c r="B43" t="str">
+        <v>2025-12-31</v>
+      </c>
+      <c r="C43" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D43" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v>02:05</v>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
+      <c r="I43" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J43" t="str">
+        <v/>
+      </c>
+      <c r="K43" t="str">
+        <v/>
+      </c>
+      <c r="L43" t="str">
+        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Imagine פסטיגל - שירי התחרות</v>
+      </c>
+      <c r="B44" t="str">
+        <v>2025-12-31</v>
+      </c>
+      <c r="C44" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D44" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <v>02:04</v>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
+      <c r="I44" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J44" t="str">
+        <v/>
+      </c>
+      <c r="K44" t="str">
+        <v/>
+      </c>
+      <c r="L44" t="str">
+        <v>Imagine פסטיגל - שירי התחרות</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>השמחות - חובות אבודים</v>
+      </c>
+      <c r="B45" t="str">
+        <v>2025-12-31</v>
+      </c>
+      <c r="C45" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D45" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+      <c r="F45" t="str">
+        <v>02:02</v>
+      </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
+      <c r="H45" t="str">
+        <v/>
+      </c>
+      <c r="I45" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J45" t="str">
+        <v/>
+      </c>
+      <c r="K45" t="str">
+        <v/>
+      </c>
+      <c r="L45" t="str">
+        <v>השמחות - חובות אבודים</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L45"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מאור כהן - אתה תגיד</v>
+        <v>לואיס טומלינסון How Did I Get Here</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-03</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24442&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%9c%d7%95%d7%90%d7%99%d7%a1-%d7%98%d7%95%d7%9e%d7%9c%d7%99%d7%a0%d7%a1%d7%95%d7%9f-how-did-i-get-here/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>18:55</v>
+        <v>מוזיקת פופ היא עניין דו־צדדי: מצד אחד, היא לא הייתה נקראת פופ אם לא הייתה מכוונת לקהל רחב ככל האפשר, ומצד שני – בשל המהות שלה והאופן שבו היא נוצרת – היא זוכה לא פעם ליחס ספקני מצד מבקרי מוזיקה.</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מאור כהן - אתה תגיד</v>
+        <v>לואיס טומלינסון How Did I Get Here</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>לואיס טומלינסון How Did I Get Here</v>
+        <v>ליידי גאגא MAYHEM אלבום הפופ הווקאלי הטוב ביותר בגראמי</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-07</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9c%d7%95%d7%90%d7%99%d7%a1-%d7%98%d7%95%d7%9e%d7%9c%d7%99%d7%a0%d7%a1%d7%95%d7%9f-how-did-i-get-here/</v>
+        <v>https://yosmusic.com/%d7%9c%d7%99%d7%99%d7%93%d7%99-%d7%92%d7%90%d7%92%d7%90-mayhem/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-07</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>מוזיקת פופ היא עניין דו־צדדי: מצד אחד, היא לא הייתה נקראת פופ אם לא הייתה מכוונת לקהל רחב ככל האפשר, ומצד שני – בשל המהות שלה והאופן שבו היא נוצרת – היא זוכה לא פעם ליחס ספקני מצד מבקרי מוזיקה.</v>
+        <v>כשליידי גאגא הכריזה לראשונה על 'Mayhem' בינואר, היא אמרה שזה "התחיל כשהתמודדתי עם הפחד שלי לחזור למוזיקת ​​הפופ שהמעריצים הראשונים שלי אהבו". היא לא ממש ניסתה לשחזר את הצליל של 2008 אבל גאגא התחברה לאזוור הרגשי הזה מחדש. "פנטום רחבת</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>לואיס טומלינסון How Did I Get Here</v>
+        <v>ליידי גאגא MAYHEM אלבום הפופ הווקאלי הטוב ביותר בגראמי</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>NEVER ENOUGH של טרנסטייל הוכתר כאלבום הרוק הטוב ביותר בגראמי</v>
+        <v>עברי לידר – אין לך מילה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-11</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/never-enough-%d7%a9%d7%9c-%d7%98%d7%a8%d7%a0%d7%a1%d7%98%d7%99%d7%99%d7%9c-%d7%94%d7%95%d7%9b%d7%aa%d7%a8-%d7%9b%d7%90%d7%9c%d7%91%d7%95%d7%9d-%d7%94%d7%a8%d7%95%d7%a7-%d7%94%d7%98%d7%95%d7%91-%d7%91/</v>
+        <v>https://yosmusic.com/%d7%a2%d7%91%d7%a8%d7%99-%d7%9c%d7%99%d7%93%d7%a8-%d7%90%d7%99%d7%9f-%d7%9c%d7%9a-%d7%9e%d7%99%d7%9c%d7%94/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>האלבום רחב היריעה הוא התפתחות חסרת מנוחה ומלהיבה של הצליל שובר־הז’אנרים של הלהקה. זהו מסע טרנספורמטיבי – חסר פחד ומלא חיים – של אחת הלהקות החדשניות והמשפיעות ביותר בדור שלה. טרנסטייל (Turnstile) מגיעים מהארדקור של בולטימור, אבל ב־NEVER ENOUGH הם</v>
+        <v>ה-EP "אין לך מילה" של עברי לידר הוא מהלך אמנותי חריג ומשמעותי בקריירה שלו – גם בגלל הוויתור על כתיבה אישית לטובת טל קסטיאל, וגם בגלל האימוץ המלא של קול נשי כנקודת מוצא רגשית. זה לא “רק” שינוי טקסטואלי –</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>NEVER ENOUGH של טרנסטייל הוכתר כאלבום הרוק הטוב ביותר בגראמי</v>
+        <v>עברי לידר – אין לך מילה</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>דודו טסה – אי</v>
+        <v>אייל גולן - GOLD 2025</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-17</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%95%d7%93%d7%95-%d7%98%d7%a1%d7%94-%d7%90%d7%99/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24446&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>מי מוציא היום אלבום של 18 שירים? התשובה: דודו טסה. הוא עזב את הכאוס המקומי, יצא לאי ביוון עם עלמה זוהר ויונתן דסקל, והנה התוצאה. שווה היה להתנתק. הנה מה שהאי הוליד. שווה מאוד להקשיב. האלבום נפתח ב"עמנואל" – לא</v>
+        <v>00:20</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,27 +469,27 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>דודו טסה – אי</v>
+        <v>אייל גולן - GOLD 2025</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>עברי לידר - אין לך מילה</v>
+        <v>דודו טסה - אי</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-15</v>
       </c>
       <c r="C3" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24444&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24449&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>19:24</v>
+        <v>19:23</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>עברי לידר - אין לך מילה</v>
+        <v>דודו טסה - אי</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>יובל בנאי - אודיסאוס של הרכבת התחתית</v>
+        <v>אתי אנקרי - אורייתא</v>
       </c>
       <c r="B4" t="str">
         <v>2026-02-15</v>
       </c>
       <c r="C4" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24445&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24447&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,88 +545,12 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>יובל בנאי - אודיסאוס של הרכבת התחתית</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>מתי כספי ז''ל הזמר, מענקי המוזיקה שלנו הלך הלילה לעולמו - יהי זכרו ברוך</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-02-14</v>
-      </c>
-      <c r="C5" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24443&amp;forum=music&amp;viewmode=all</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v>07:49</v>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>אלבומים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>מתי כספי ז''ל הזמר, מענקי המוזיקה שלנו הלך הלילה לעולמו - יהי זכרו ברוך</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>הפטריקים - הפרויקט של דודי לוי ואבטיפוס - להיטי הזהב</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-02-13</v>
-      </c>
-      <c r="C6" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24448&amp;forum=music&amp;viewmode=all</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v>00:30</v>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>אלבומים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>הפטריקים - הפרויקט של דודי לוי ואבטיפוס - להיטי הזהב</v>
+        <v>אתי אנקרי - אורייתא</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אייל גולן - GOLD 2025</v>
+        <v>אייל גולן - בדרך ל-30 EP</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-17</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24446&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24450&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>00:20</v>
+        <v>04:00</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,88 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אייל גולן - GOLD 2025</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>דודו טסה - אי</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="C3" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24449&amp;forum=music&amp;viewmode=all</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-02-16</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v>19:23</v>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>אלבומים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>דודו טסה - אי</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>אתי אנקרי - אורייתא</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="C4" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24447&amp;forum=music&amp;viewmode=all</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-02-16</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v>19:23</v>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>אלבומים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>אתי אנקרי - אורייתא</v>
+        <v>אייל גולן - בדרך ל-30 EP</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אייל גולן - בדרך ל-30 EP</v>
+        <v>אילן וירצברג - אילן בן עשרים</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-17</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24450&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24451&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>04:00</v>
+        <v>22:01</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אייל גולן - בדרך ל-30 EP</v>
+        <v>אילן וירצברג - אילן בן עשרים</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אילן וירצברג - אילן בן עשרים</v>
+        <v>עומר אדם - חלק מהנצח</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-19</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24451&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24453&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>22:01</v>
+        <v>20:42</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אילן וירצברג - אילן בן עשרים</v>
+        <v>עומר אדם - חלק מהנצח</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עומר אדם - חלק מהנצח</v>
+        <v>שלומי שבן - חי בגימל בהיכל התרבות</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-19</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24453&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24454&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-19</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>20:42</v>
+        <v>20:44</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עומר אדם - חלק מהנצח</v>
+        <v>שלומי שבן - חי בגימל בהיכל התרבות</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שלומי שבן - חי בגימל בהיכל התרבות</v>
+        <v>שלומי שבן חי בגימל בהיכל התרבות</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24454&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%95%d7%9e%d7%99-%d7%a9%d7%91%d7%9f-%d7%97%d7%99-%d7%91%d7%92%d7%99%d7%9e%d7%9c-%d7%91%d7%94%d7%99%d7%9b%d7%9c-%d7%94%d7%aa%d7%a8%d7%91%d7%95%d7%aa/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>20:44</v>
+        <v>יש סיבה לחזור להיכל התרבות הריק מאדם למפגשי הקורונה של שלומי שבן.  האלבום "חי בגימל בהיכל התרבות" של שלומי שבן שנולד בתקופת הסגרים בקורונה, הוא לא עוד פרויקט קאברים – הוא תיעוד של מצב תרבותי חריג: אין קהל, אין להקה,</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שלומי שבן - חי בגימל בהיכל התרבות</v>
+        <v>שלומי שבן חי בגימל בהיכל התרבות</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שלומי שבן חי בגימל בהיכל התרבות</v>
+        <v>Wuthering Heights צ'רלי XCX</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-23</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%95%d7%9e%d7%99-%d7%a9%d7%91%d7%9f-%d7%97%d7%99-%d7%91%d7%92%d7%99%d7%9e%d7%9c-%d7%91%d7%94%d7%99%d7%9b%d7%9c-%d7%94%d7%aa%d7%a8%d7%91%d7%95%d7%aa/</v>
+        <v>https://yosmusic.com/wuthering-heights-%d7%a6%d7%a8%d7%9c%d7%99-xcx/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>יש סיבה לחזור להיכל התרבות הריק מאדם למפגשי הקורונה של שלומי שבן.  האלבום "חי בגימל בהיכל התרבות" של שלומי שבן שנולד בתקופת הסגרים בקורונה, הוא לא עוד פרויקט קאברים – הוא תיעוד של מצב תרבותי חריג: אין קהל, אין להקה,</v>
+        <v>Wuthering Heights הוא אלבום האולפן השביעי של צ'רלי XCX. האלבום נוצר כאלבום קונספט ופסקול נלווה לעיבוד הקולנועי של אמרלד פנל לרומן הקלאסי "אנקת גבהים" (מאת אמילי ברונטה), בכיכובם של מרגו רובי וג'ייקוב אלורד מדובר בשינוי כיוון דרסטי מבחינתה מעבר מאסתטיקה של פופ</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שלומי שבן חי בגימל בהיכל התרבות</v>
+        <v>Wuthering Heights צ'רלי XCX</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Wuthering Heights צ'רלי XCX</v>
+        <v>רותם כהן - הבן של נורית</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-20</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/wuthering-heights-%d7%a6%d7%a8%d7%9c%d7%99-xcx/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24452&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-23</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>Wuthering Heights הוא אלבום האולפן השביעי של צ'רלי XCX. האלבום נוצר כאלבום קונספט ופסקול נלווה לעיבוד הקולנועי של אמרלד פנל לרומן הקלאסי "אנקת גבהים" (מאת אמילי ברונטה), בכיכובם של מרגו רובי וג'ייקוב אלורד מדובר בשינוי כיוון דרסטי מבחינתה מעבר מאסתטיקה של פופ</v>
+        <v>13:35</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Wuthering Heights צ'רלי XCX</v>
+        <v>רותם כהן - הבן של נורית</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>רותם כהן - הבן של נורית</v>
+        <v>רינת בר - 300 EP</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-24</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24452&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24455&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>13:35</v>
+        <v>22:41</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>רותם כהן - הבן של נורית</v>
+        <v>רינת בר - 300 EP</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>רינת בר - 300 EP</v>
+        <v>אפרת גוש - לרדוף אחרי השמש</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24455&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24456&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>22:41</v>
+        <v>15:20</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>רינת בר - 300 EP</v>
+        <v>אפרת גוש - לרדוף אחרי השמש</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אפרת גוש - לרדוף אחרי השמש</v>
+        <v>עומר אדם – חלק מהנצח</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-27</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24456&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%a2%d7%95%d7%9e%d7%a8-%d7%90%d7%93%d7%9d-%d7%97%d7%9c%d7%a7-%d7%9e%d7%94%d7%a0%d7%a6%d7%97/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>15:20</v>
+        <v>"משפחה וכבוד" הפותח את אלבומו העשירי  של עומר אדם מציב הצהרה אמנותית: זו אינה רק בלדת אהבה, אלא בלדה על מחיר ההצלחה. השיר יושב על קו התפר שבין עולם חומרי נוצץ לבין נאמנות פנימית, בין אהבה הרסנית לבין ערכי יסוד.</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אפרת גוש - לרדוף אחרי השמש</v>
+        <v>עומר אדם – חלק מהנצח</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עומר אדם – חלק מהנצח</v>
+        <v>ג'ייקוב אלון In Limerence</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-27</v>
+        <v>2026-03-03</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a2%d7%95%d7%9e%d7%a8-%d7%90%d7%93%d7%9d-%d7%97%d7%9c%d7%a7-%d7%9e%d7%94%d7%a0%d7%a6%d7%97/</v>
+        <v>https://yosmusic.com/%d7%92%d7%99%d7%99%d7%a7%d7%95%d7%91-%d7%90%d7%9c%d7%95%d7%9f-in-limerence/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-27</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"משפחה וכבוד" הפותח את אלבומו העשירי  של עומר אדם מציב הצהרה אמנותית: זו אינה רק בלדת אהבה, אלא בלדה על מחיר ההצלחה. השיר יושב על קו התפר שבין עולם חומרי נוצץ לבין נאמנות פנימית, בין אהבה הרסנית לבין ערכי יסוד.</v>
+        <v>מדי פעם מופיע קול חדש עם השילוב האלכימי של יופי שברירי ופואטיות – כזה שיש לו את הכוח לגרום לזמן להיראות כאילו עצר מלכת. זהו אותו קסם שהפך את עמודי התווך של המוזיקה האלטרנטיבית, ג׳ף באקלי ולורה מרלינג, למה שהם,</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עומר אדם – חלק מהנצח</v>
+        <v>ג'ייקוב אלון In Limerence</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ג'ייקוב אלון In Limerence</v>
+        <v>הארי סטיילס Kiss All The Time. Disco Occasionally</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-07</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%92%d7%99%d7%99%d7%a7%d7%95%d7%91-%d7%90%d7%9c%d7%95%d7%9f-in-limerence/</v>
+        <v>https://yosmusic.com/%d7%94%d7%90%d7%a8%d7%99-%d7%a1%d7%98%d7%99%d7%99%d7%9c%d7%a1-kiss-all-the-time-disco-occasionally/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>מדי פעם מופיע קול חדש עם השילוב האלכימי של יופי שברירי ופואטיות – כזה שיש לו את הכוח לגרום לזמן להיראות כאילו עצר מלכת. זהו אותו קסם שהפך את עמודי התווך של המוזיקה האלטרנטיבית, ג׳ף באקלי ולורה מרלינג, למה שהם,</v>
+        <v>מאז האלבום האחרון של הארי סטיילס, “Harry’s House” מ-2022, כוכב הפופ עשה כמה שינויים בחייו. האלבום ההוא יצא בתקופה של רכילות והשערות בלתי פוסקות סביב חייו האישיים, ובשנים שעברו מאז הוא ניסה להשיב לעצמו שליטה על הפרטיות שלו, כשהוא מנצל</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ג'ייקוב אלון In Limerence</v>
+        <v>הארי סטיילס Kiss All The Time. Disco Occasionally</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>הארי סטיילס Kiss All The Time. Disco Occasionally</v>
+        <v>יבבה Jean</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-07</v>
+        <v>2026-03-10</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%90%d7%a8%d7%99-%d7%a1%d7%98%d7%99%d7%99%d7%9c%d7%a1-kiss-all-the-time-disco-occasionally/</v>
+        <v>https://yosmusic.com/%d7%99%d7%91%d7%91%d7%94-jean/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-07</v>
+        <v>2026-03-10</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>מאז האלבום האחרון של הארי סטיילס, “Harry’s House” מ-2022, כוכב הפופ עשה כמה שינויים בחייו. האלבום ההוא יצא בתקופה של רכילות והשערות בלתי פוסקות סביב חייו האישיים, ובשנים שעברו מאז הוא ניסה להשיב לעצמו שליטה על הפרטיות שלו, כשהוא מנצל</v>
+        <v>זה אלבומה השני של יבבה (Yebba) הזמרת-יוצרת, ילידת ארקנסו המוכרת מהשיר הנפלא October Sky.  זהו  אוסף שירים בעל ניחוח פולקי עם השפעות גוספל – יצירה בוגרת יותר בסגנון פופ עכשווי שמגיעה אחרי אלבום הבכורה שלה Dawn. האלבום נקרא על שם</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>הארי סטיילס Kiss All The Time. Disco Occasionally</v>
+        <v>יבבה Jean</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יבבה Jean</v>
+        <v>גורילז The Mountain</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-13</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%91%d7%91%d7%94-jean/</v>
+        <v>https://yosmusic.com/%d7%92%d7%95%d7%a8%d7%99%d7%9c%d7%96-the-mountain/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-13</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>זה אלבומה השני של יבבה (Yebba) הזמרת-יוצרת, ילידת ארקנסו המוכרת מהשיר הנפלא October Sky.  זהו  אוסף שירים בעל ניחוח פולקי עם השפעות גוספל – יצירה בוגרת יותר בסגנון פופ עכשווי שמגיעה אחרי אלבום הבכורה שלה Dawn. האלבום נקרא על שם</v>
+        <v>בשלב מסוים במהלך השיר Orange County הבנתי שאני לא רק נהנה מהאלבום The Mountain, אלא שאני גם קצת המום מהייחוד שלו. לאורך 15 שירים מאזינים לתערובת מסחררת של מצבי רוח, סגנונות, תרבויות, שפות ותקופות The Mountain הוא אלבום האולפן התשיעי</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יבבה Jean</v>
+        <v>גורילז The Mountain</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ג'יימס בלייק Trying Time</v>
+        <v>הילה רוח – שחור זוהר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-25</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%92%d7%99%d7%99%d7%9e%d7%a1-%d7%91%d7%9c%d7%99%d7%99%d7%a7-trying-time/</v>
+        <v>https://yosmusic.com/%d7%94%d7%99%d7%9c%d7%94-%d7%a8%d7%95%d7%97-%d7%a9%d7%97%d7%95%d7%a8-%d7%96%d7%95%d7%94%d7%a8/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>מבין כל הדברים שאפשר לצפות מאלבום של ג'יימס בלייק James Blake – מינימליזם מעודן, עיוותים ווקאליים מלאי כאב, ואורחים מעולם ההיפ-הופ מהשורה הראשונה – פרשנות סוציו־פוליטית מעמיקה היא כנראה לא אחד מהם. אבל כפי שמרמז השם, המצוקה הנוכחית שלנו היא</v>
+        <v>"שחור זוהר" של הילה רוח הוא יצירה בת 15 שירים שמנסה להלך על קו עדין בין פופ נגיש לבין אמירה כמעט אוונגרדית.  זה לא אלבום שמבקש לרצות אלא  להטרי, לעורר, ולפעמים גם לבלבל. הסינגלים "טבע" ו־"זאת השנה" מתפקדים כשער כניסה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ג'יימס בלייק Trying Time</v>
+        <v>הילה רוח – שחור זוהר</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אייל גולן - 30 חלק ב</v>
+        <v>רובין Sexistential</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24462&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%91%d7%99%d7%9f-sexistential/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>16:05</v>
+        <v>בקריירה שנמשכת כבר שני עשורים, רובין (Robyn), הזמרת השוודית, יצרה כמה מהלהיטים הבולטים בפופ – ובראשם “Dancing On My Own”, המנון נצחי ואיקוני על מציאת הדרך האישית מתוך שברון לב. אך באלבומה התשיעי “Sexistential”, אנו פוגשים אותה חסרת עוגן ותוהה,</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,27 +469,27 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אייל גולן - 30 חלק ב</v>
+        <v>רובין Sexistential</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אגם בוחבוט - פריפריה אקספרס</v>
+        <v>עידן רייכל - הד</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="C3" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24460&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24457&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>15:58</v>
+        <v>01:19</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -507,27 +507,27 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אגם בוחבוט - פריפריה אקספרס</v>
+        <v>עידן רייכל - הד</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>עדן בן זקן - היכל מנורה 2025 LIVE</v>
+        <v>אייל גולן - 30 - חלק א</v>
       </c>
       <c r="B4" t="str">
         <v>2026-03-27</v>
       </c>
       <c r="C4" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24458&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24461&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>15:52</v>
+        <v>16:00</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -545,7 +545,7 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>עדן בן זקן - היכל מנורה 2025 LIVE</v>
+        <v>אייל גולן - 30 - חלק א</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>BTS Arirang</v>
+        <v>אייל גולן - 30 חלק ג</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-03</v>
+        <v>2026-04-06</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/bts-arirang/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24463&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-03</v>
+        <v>2026-04-06</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>האלבום Arirang של BTS (שיצא במרץ 2026) הפך בתוך שבועות ספורים לאחד התקליטים המבוקשים בעולם גם פיזית (ויניל/מהדורות אספנים) וגם סטרימינג, וזה לא במקרה. מדובר בשילוב נדיר של אירוע תרבותי, מהלך מוזיקלי מחושב, ורגע רגשי של קאמבק. בעיני המעריצים, זה</v>
+        <v>21:10</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,50 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>BTS Arirang</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>אֶריק ברמן - אהבה ואלוהים אחרים 2017</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="C3" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=23054&amp;forum=music&amp;viewmode=all</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v>08:36</v>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>אלבומים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>אֶריק ברמן - אהבה ואלוהים אחרים 2017</v>
+        <v>אייל גולן - 30 חלק ג</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אייל גולן - 30 חלק ג</v>
+        <v>מחווה לשירי יאיר רוזנבלום בכאן גימל - המנגינה היא שקובעת</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-06</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24463&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24464&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-07</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>21:10</v>
+        <v>21:11</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אייל גולן - 30 חלק ג</v>
+        <v>מחווה לשירי יאיר רוזנבלום בכאן גימל - המנגינה היא שקובעת</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מחווה לשירי יאיר רוזנבלום בכאן גימל - המנגינה היא שקובעת</v>
+        <v>ריי – This Music May Contain Hope</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-07</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24464&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%a8%d7%99%d7%99-this-music-may-contain-hope/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-07</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>21:11</v>
+        <v>האלבום "This Music May Contain Hope" של  ריי RAYE הוא יצירה טעונה רגשית, שממשיכה את הקו האישי והחשוף שהיא ביססה מאז הפריצה העצמאית שלה. כבר בשם יש פרובוקציה עדינה: במקום אזהרה שלילית (“עלול להכיל תכנים קשים”), היא מציעה אפשרות הפוכה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,50 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מחווה לשירי יאיר רוזנבלום בכאן גימל - המנגינה היא שקובעת</v>
+        <v>ריי – This Music May Contain Hope</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>אוסף ענק: וזוהי רק ההתחלה - 300 השירים הגדולים של הלהקות הצבאיות</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="C3" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=21671&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-04-07</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v>11:50</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>אוסף ענק: וזוהי רק ההתחלה - 300 השירים הגדולים של הלהקות הצבאיות</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מייקל ג'קסון Songs From The Motion Picture</v>
+        <v>ינון מועלם Aegina's Secret</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%99%d7%99%d7%a7%d7%9c-%d7%92%d7%a7%d7%a1%d7%95%d7%9f-songs-from-the-motion-picture/</v>
+        <v>https://yosmusic.com/%d7%99%d7%a0%d7%95%d7%9f-%d7%9e%d7%95%d7%a2%d7%9c%d7%9d-aeginas-secret/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>האלבום Michael – Songs From The Motion Picture” (2026), שמלווה את הסרט הביוגרפי על מייקל ג'קסון, עומד בפני אתגר מורכב בהרבה מפסקול רגיל: הוא לא רק צריך לשרת סרט, אלא גם לייצג מורשת מוזיקלית מהגדולות בהיסטוריה. לכן הוא נע בין</v>
+        <v>הרעיון ל־Aegina’s Secret נולד אצל המוסיקאי ינון מועלם לאחר ביקור באי אגינה, אחד מאיי סרוניקוס הסמוכים לאתונה. המפגשים שחווה שם, האנשים המגוונים שפגש והאווירה הייחודית של האי העניקו לו השראה ליצור מוסיקה. האלבום מורכב בעיקר מיצירות מקוריות לצד כמה קאברים</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מייקל ג'קסון Songs From The Motion Picture</v>
+        <v>ינון מועלם Aegina's Secret</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ינון מועלם Aegina's Secret</v>
+        <v>פו פייטרס Your Favorite Toy</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-27</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%a0%d7%95%d7%9f-%d7%9e%d7%95%d7%a2%d7%9c%d7%9d-aeginas-secret/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%95-%d7%a4%d7%99%d7%99%d7%98%d7%a8%d7%a1-your-favorite-toy/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הרעיון ל־Aegina’s Secret נולד אצל המוסיקאי ינון מועלם לאחר ביקור באי אגינה, אחד מאיי סרוניקוס הסמוכים לאתונה. המפגשים שחווה שם, האנשים המגוונים שפגש והאווירה הייחודית של האי העניקו לו השראה ליצור מוסיקה. האלבום מורכב בעיקר מיצירות מקוריות לצד כמה קאברים</v>
+        <v>במשך שני העשורים האחרונים, דייב גרוהל Dave Grohl תמיד מצא רעיון מרכזי שעליו נשען כל אלבום חדש של פו פייטרס Foo Fighters.האלבום In Your Honor היה אלבום כפול שהתפצל בין צד "קשוח” לצד "רך”, ואילו האלבום שאחריו, Echoes, Silence, Patience</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ינון מועלם Aegina's Secret</v>
+        <v>פו פייטרס Your Favorite Toy</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>סקינרד You got this</v>
+        <v>מיקה קרני ואודי תורג'מן - ברית</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-01</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%a7%d7%99%d7%a0%d7%a8%d7%93-you-got-this/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24466&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-01</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הרכב הרגאיי-מטאל מניופורט, סקינרד Skindred, מוכרים כלהקה חיה סוחפת במיוחד, אבל האלבום “Smile” מ-2023 שינה את כללי המשחק. הוא הגיע למקום השני במצעדים בבריטניה, הוביל להופעת סולד אאוט באולם וומבלי ארנה, ולזכייה גאה בפרס להקת האלטרנטיב הטובה ביותר בטקס פרסי</v>
+        <v>19:31</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>סקינרד You got this</v>
+        <v>מיקה קרני ואודי תורג'מן - ברית</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מיקה קרני ואודי תורג'מן - ברית</v>
+        <v>נואה קאהן The Great Divide</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-05</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24466&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%a0%d7%95%d7%90%d7%94-%d7%a7%d7%90%d7%94%d7%9f-the-great-divide/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>19:31</v>
+        <v>נואה קאהן פרסם ב־X: “מבקרים שאומרים שהאלבום ארוך מדי — לעזאזל, אני לא חושב שהוא מספיק ארוך.”בהתחשב בכך ש־The Great Divide נמשך לא פחות מ־77 דקות על פני 17 שירים, אפשר להבין מנין הביקורת מגיעה. אורך כשלעצמו אינו דבר רע.</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מיקה קרני ואודי תורג'מן - ברית</v>
+        <v>נואה קאהן The Great Divide</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נואה קאהן The Great Divide</v>
+        <v>קובי פרץ - כל עולמי EP</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-09</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%95%d7%90%d7%94-%d7%a7%d7%90%d7%94%d7%9f-the-great-divide/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24468&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>נואה קאהן פרסם ב־X: “מבקרים שאומרים שהאלבום ארוך מדי — לעזאזל, אני לא חושב שהוא מספיק ארוך.”בהתחשב בכך ש־The Great Divide נמשך לא פחות מ־77 דקות על פני 17 שירים, אפשר להבין מנין הביקורת מגיעה. אורך כשלעצמו אינו דבר רע.</v>
+        <v>19:35</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נואה קאהן The Great Divide</v>
+        <v>קובי פרץ - כל עולמי EP</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אריק סיני – כל השירים היפים באמת</v>
+        <v>זהו זה - עונה 8</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-10</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%a8%d7%99%d7%a7-%d7%a1%d7%99%d7%a0%d7%99-%d7%9b%d7%9c-%d7%94%d7%a9%d7%99%d7%a8%d7%99%d7%9d-%d7%94%d7%99%d7%a4%d7%99%d7%9d-%d7%91%d7%90%d7%9e%d7%aa/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24469&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-10</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>האלבום "כל השירים היפים באמת” של אריק סיני הוא לא סתם אוסף קאברים אלא אלבום פרשנות. סיני לא מנסה “לעדכן” את השירים בכוח או להתחרות בביצועים המקוריים, אלא להפוך אותם לחלק מהעולם הפנימי והקולי שלו. זה אלבום שמבוסס פחות על</v>
+        <v>09:37</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אריק סיני – כל השירים היפים באמת</v>
+        <v>זהו זה - עונה 8</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>זהו זה - עונה 8</v>
+        <v>זארה לארסון Midnight Sun</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-13</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24469&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%96%d7%90%d7%a8%d7%94-%d7%9c%d7%90%d7%a8%d7%a1%d7%95%d7%9f-midnight-sun/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>09:37</v>
+        <v>״אמרתי שעד גיל 20 אמלא אצטדיונים״,  שרה זארה לארסון ב־Midnight Sun, ואילו ב״Saturn’s Return״ אחד השרים היפים באלבום – . ״זה לא קרה, אז פשוט דחיתי את הדדליין״ השילוב המושך הזה בין נחישות לפגיעוּת זורם לאורך אלבום הדאנס־פופ המסחרר של</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>זהו זה - עונה 8</v>
+        <v>זארה לארסון Midnight Sun</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>זהו זה - זהו זה 2020 עונה 5 (2023)</v>
+        <v>זהו זה - זהו זה 2020 עונה 4 (2022)</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-15</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24191&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24068&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>06:50</v>
+        <v>06:51</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,50 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>זהו זה - זהו זה 2020 עונה 5 (2023)</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>אריק סיני - כל השירים היפים באמת</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="C3" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24470&amp;forum=music&amp;viewmode=all</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v>06:45</v>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>אלבומים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>אריק סיני - כל השירים היפים באמת</v>
+        <v>זהו זה - זהו זה 2020 עונה 4 (2022)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>זהו זה - זהו זה 2020 עונה 4 (2022)</v>
+        <v>עומר אדם - אלבום הופעה איצטדיון רמת גן 2026</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-22</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24068&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24471&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>06:51</v>
+        <v>14:04</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>זהו זה - זהו זה 2020 עונה 4 (2022)</v>
+        <v>עומר אדם - אלבום הופעה איצטדיון רמת גן 2026</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יוני רכטר – סגור פתוח סגור</v>
+        <v>פול מקרטני The Boys Of Dungeon Lane</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-31</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%95%d7%a0%d7%99-%d7%a8%d7%9b%d7%98%d7%a8-%d7%a1%d7%92%d7%95%d7%a8-%d7%a4%d7%aa%d7%95%d7%97-%d7%a1%d7%92%d7%95%d7%a8/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%95%d7%9c-%d7%9e%d7%a7%d7%a8%d7%98%d7%a0%d7%99-the-boys-of-dungeon-lane/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-31</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>יוני רכטר לא הקליט אלבום אינסטרומנטלי מאז האלבום 'ממש עכשיו – מנגנים יוני רכטר' (1991). ההזדמנות להקליט אחד כזה פעם נוספת התאפשרה בעקבות הטריו שהקים לפני מספר שנים, שכולל מלבדו בפסנתר את נגן הקונטרבס ברק מורי והמתופפת רוני כספי. הקטע</v>
+        <v>יש מי שהגדיר את האלבום החדש שת פול מקרטני "סיור מודרך בדרך הארוכה והמפותלת" (a guided tour of the long and winding road Paul)  בנוסח שירו המוכר. המניה של מקרטני לא הייתה בשיא כזה מאז בערך 1966. מוזר ככל שזה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יוני רכטר – סגור פתוח סגור</v>
+        <v>פול מקרטני The Boys Of Dungeon Lane</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>פרויקט אסי עזר - כל מה שעוזר</v>
+        <v>אלבום הפסקול הרשמי של גביע העולם בכדורגל 2026 של פיפ"א</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24473&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%90%d7%9c%d7%91%d7%95%d7%9d-%d7%94%d7%a4%d7%a1%d7%a7%d7%95%d7%9c-%d7%94%d7%a8%d7%a9%d7%9e%d7%99-%d7%a9%d7%9c-%d7%92%d7%91%d7%99%d7%a2-%d7%94%d7%a2%d7%95%d7%9c%d7%9d-%d7%91%d7%9b%d7%93%d7%95%d7%a8/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>19:49</v>
+        <v>זהן אוסף בן שעה אחת ו־18 רצועות, המורכב ברובו משיתופי פעולה בין אמנים שנעים בין סטורמזי ושאקירה לבין ג'לי רול והרולינג סטונז? לאורך השנים נוצרה הרבה מוזיקה בהשראת כדורגל. אבל האם נמצא ממנה משהו כאן שהופך את האוסף למיוחד בסוגו?</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>פרויקט אסי עזר - כל מה שעוזר</v>
+        <v>אלבום הפסקול הרשמי של גביע העולם בכדורגל 2026 של פיפ"א</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/global/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אלבום הפסקול הרשמי של גביע העולם בכדורגל 2026 של פיפ"א</v>
+        <v>נינט טייב - אני נינה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-07</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%9c%d7%91%d7%95%d7%9d-%d7%94%d7%a4%d7%a1%d7%a7%d7%95%d7%9c-%d7%94%d7%a8%d7%a9%d7%9e%d7%99-%d7%a9%d7%9c-%d7%92%d7%91%d7%99%d7%a2-%d7%94%d7%a2%d7%95%d7%9c%d7%9d-%d7%91%d7%9b%d7%93%d7%95%d7%a8/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24474&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-07</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>זהן אוסף בן שעה אחת ו־18 רצועות, המורכב ברובו משיתופי פעולה בין אמנים שנעים בין סטורמזי ושאקירה לבין ג'לי רול והרולינג סטונז? לאורך השנים נוצרה הרבה מוזיקה בהשראת כדורגל. אבל האם נמצא ממנה משהו כאן שהופך את האוסף למיוחד בסוגו?</v>
+        <v>09:26</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אלבום הפסקול הרשמי של גביע העולם בכדורגל 2026 של פיפ"א</v>
+        <v>נינט טייב - אני נינה</v>
       </c>
     </row>
   </sheetData>
